--- a/data/berita_antara_2026-08-03.xlsx
+++ b/data/berita_antara_2026-08-03.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$152</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G136"/>
+  <dimension ref="A1:G152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -476,61 +476,61 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KPK lakukan 762 penyadapan selama semester I 2026</t>
+          <t>Advokat ingatkan RUU Perampasan Aset tidak boleh jadi alat politik</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:33:32 +0700</t>
+          <t>Mon, 03 Aug 2026 13:22:07 +0700</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dewan Pengawas Komisi Pemberantasan Korupsi (Dewas KPK) menyatakan lembaga antirasuah telah melakukan 762 penyadapan ...</t>
+          <t>Advokat Juniver Girsang mengingatkan kepada DPR RI agar Rancangan Undang-Undang (RUU) Perampasan Aset tidak justru ...</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677415/kpk-lakukan-762-penyadapan-selama-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5677329/advokat-ingatkan-ruu-perampasan-aset-tidak-boleh-jadi-alat-politik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_8172.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001295469.jpg</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jasaraharja Putera menjamin santunan korban KMP Mutiara Sentosa II</t>
+          <t>Hoaks! Febrie Adriansyah bebas karena emas dan uang sitaan dinyatakan palsu</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:30:17 +0700</t>
+          <t>Mon, 03 Aug 2026 13:20:23 +0700</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PT Jasaraharja Putera menjamin perlindungan dan santunan bagi seluruh korban kebakaran Kapal Motor Penyeberangan (KMP) ...</t>
+          <t>Jakarta (ANTARA/JACX) – Sebuah unggahan di Facebook menarasikan bahwa mantan Jaksa Agung Muda Bidang ...</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677412/jasaraharja-putera-menjamin-santunan-korban-kmp-mutiara-sentosa-ii</t>
+          <t>https://www.antaranews.com/berita/5677328/hoaks-febrie-adriansyah-bebas-karena-emas-dan-uang-sitaan-dinyatakan-palsu</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176259.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/11/Konferensi-pers-Jampidsus-100726-Ada-2.jpg</t>
         </is>
       </c>
     </row>
@@ -542,61 +542,61 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Petani di Jakut harap pemerintah beri bantuan hadapi musim kemarau</t>
+          <t>Hoaks! Komdigi terapkan balik nama ponsel bekas seperti kendaraan pada Juli 2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:29:53 +0700</t>
+          <t>Mon, 03 Aug 2026 13:19:15 +0700</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Petani di Kelurahan Rorotan, Cilincing Jakarta Utara berharap pemerintah dapat memberikan bantuan untuk menunjang ...</t>
+          <t>Jakarta (ANTARA/JACX) – Sebuah unggahan video di Facebook menarasikan bahwa Kementerian Komunikasi ...</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677408/petani-di-jakut-harap-pemerintah-beri-bantuan-hadapi-musim-kemarau</t>
+          <t>https://www.antaranews.com/berita/5677324/hoaks-komdigi-terapkan-balik-nama-ponsel-bekas-seperti-kendaraan-pada-juli-2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/13/IMG_20260713_140727.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/08/1000135509.jpg</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GMR bidik Indonesia dalam perluasan rute Bandara Bhogapuram India</t>
+          <t>Tebang 10 pohon peneduh, pengelola padel dipanggil Pemkot Bandung</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:29:34 +0700</t>
+          <t>Mon, 03 Aug 2026 13:17:41 +0700</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GMR Airports Limited (GMR Airports), salah satu pengelola jaringan bandara internasional, memprioritaskan Indonesia ...</t>
+          <t>Pemerintah Kota (Pemkot) Bandung, Jawa Barat, memanggil pengelola lapang Padel Six Nine untuk dimintai keterangan ...</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677407/gmr-bidik-indonesia-dalam-perluasan-rute-bandara-bhogapuram-india</t>
+          <t>https://www.antaranews.com/berita/5677320/tebang-10-pohon-peneduh-pengelola-padel-dipanggil-pemkot-bandung</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0725.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/5b6bcd7b-f3c3-4ea6-ba5f-55c5deba8a39.jpeg</t>
         </is>
       </c>
     </row>
@@ -608,28 +608,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BPJS Kesehatan gandeng empat K/L perkuat ekosistem Program JKN</t>
+          <t>Cek fakta, utang Indonesia tembus Rp10.000 triliun</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:28:03 +0700</t>
+          <t>Mon, 03 Aug 2026 13:17:18 +0700</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BPJS Kesehatan menjalin kerja sama strategis dengan empat Kementerian dan Lembaga (K/L) sebagai upaya memperkuat ...</t>
+          <t>Jakarta (ANTARA/JACX) – Sebuah unggahan video di Facebook berdurasi sekitar satu menit menarasikan ...</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677404/bpjs-kesehatan-gandeng-empat-k-l-perkuat-ekosistem-program-jkn</t>
+          <t>https://www.antaranews.com/berita/5677319/cek-fakta-utang-indonesia-tembus-rp10000-triliun</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-14.08.02.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/02/17/Utang-Luar-Negeri-Kuartal-III-Turun-161122-Adm-3.jpg</t>
         </is>
       </c>
     </row>
@@ -641,28 +641,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rusia tetap terbuka berunding dengan Ukraina</t>
+          <t>AS-Iran mulai perundingan 3 Agustus, Trump singgung Hormuz dan denuklirisasi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:23:43 +0700</t>
+          <t>Mon, 03 Aug 2026 13:14:21 +0700</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rusia menegaskan tetap membuka peluang perundingan dengan Ukraina dan siap mempertimbangkan berbagai usulan yang ...</t>
+          <t>Presiden AS Donald Trump mengatakan pada Minggu (2/8) bahwa negosiasi dengan Iran akan dimulai Senin sore, seraya ...</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677403/rusia-tetap-terbuka-berunding-dengan-ukraina</t>
+          <t>https://www.antaranews.com/berita/5677311/as-iran-mulai-perundingan-3-agustus-trump-singgung-hormuz-dan-denuklirisasi</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/06/thumbs_b2_e27328c11fef925beee70a6fbdcf61b4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CjkinzN000006_20260803_CBMFN0A001.png</t>
         </is>
       </c>
     </row>
@@ -674,61 +674,61 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kejati NTB minta data pajak PT GNE ke Kemenkeu untuk penyidikan</t>
+          <t>Menag: Fungsi masjid perlu terus diperluas dalam memberdayakan umat</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:23:27 +0700</t>
+          <t>Mon, 03 Aug 2026 13:10:48 +0700</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kejaksaan Tinggi Nusa Tenggara Barat meminta data pajak PT Gerbang NTB Emas (GNE) kepada Kementerian Keuangan sebagai ...</t>
+          <t>Menteri Agama (Menag) Nasaruddin Umar menegaskan fungsi masjid perlu terus diperluas sebagai pusat pemberdayaan ...</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677400/kejati-ntb-minta-data-pajak-pt-gne-ke-kemenkeu-untuk-penyidikan</t>
+          <t>https://www.antaranews.com/berita/5677307/menag-fungsi-masjid-perlu-terus-diperluas-dalam-memberdayakan-umat</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/aspidsus-kejati-ntb-zulkifli-said-9.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176377.jpg</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BPS: Wisman per Juni capai 7,45 juta kunjungan, tertinggi sejak 2020</t>
+          <t>Kemerdekaan, demokrasi, dan kesejahteraan rakyat</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:22:48 +0700</t>
+          <t>Mon, 03 Aug 2026 13:10:15 +0700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat total kunjungan wisatawan mancanegara dari Januari hingga bulan Juni 2026 mencapai ...</t>
+          <t>Kemerdekaan dan demokrasi adalah hulu, sementara kesejahteraan rakyat merupakan hilir. Imajinasi ini bersinggungan ...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677399/bps-wisman-per-juni-capai-745-juta-kunjungan-tertinggi-sejak-2020</t>
+          <t>https://www.antaranews.com/berita/5677303/kemerdekaan-demokrasi-dan-kesejahteraan-rakyat</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/pelepasliaran-500-ekor-tukik-bali-290726-nhw-3_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/penjualan-pernak-pernik-hut-ri-di-jakarta-2832459.jpg</t>
         </is>
       </c>
     </row>
@@ -740,28 +740,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Menkomdigi panggil YouTube imbas temuan konten promosi vape sasar anak</t>
+          <t>Inggris terancam resesi jika Selat Hormuz terus tutup sampai 2027</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:22:09 +0700</t>
+          <t>Mon, 03 Aug 2026 13:04:05 +0700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid merencanakan pemanggilan terhadap platform digital YouTube ...</t>
+          <t>Inggris terancam mengalami resesi ekonomi pada 2027 apabila Selat Hormuz tak kunjung dibuka, menurut laporan surat ...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677396/menkomdigi-panggil-youtube-imbas-temuan-konten-promosi-vape-sasar-anak</t>
+          <t>https://www.antaranews.com/berita/5677293/inggris-terancam-resesi-jika-selat-hormuz-terus-tutup-sampai-2027</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0225.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/24/CmxztpE000057_20260128_PEPFN0A001.jpg</t>
         </is>
       </c>
     </row>
@@ -773,28 +773,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pemprov Jatim siap tanggung biaya RS korban KMP Mutiara yang terbakar</t>
+          <t>Pentingnya memantau asupan serat bagi wanita</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:19:46 +0700</t>
+          <t>Mon, 03 Aug 2026 13:03:51 +0700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pemerintah Provinsi (Pemprov) Jawa Timur (Jatim) mengatakan siap menanggung biaya rumah sakit korban kebakaran ...</t>
+          <t>Ahli gizi Brenna Larson, M.S., RD mengatakan idealnya tiap wanita harus menargetkan 25 gram serat per hari karena ...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677395/pemprov-jatim-siap-tanggung-biaya-rs-korban-kmp-mutiara-yang-terbakar</t>
+          <t>https://www.antaranews.com/berita/5677291/pentingnya-memantau-asupan-serat-bagi-wanita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/261107.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/19/Sayur.jpg</t>
         </is>
       </c>
     </row>
@@ -806,193 +806,193 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Resmi dibuka, Sekolah Rakyat Terintegrasi 2 Kendari tampung 339 siswa</t>
+          <t>Komandan Kodaeral IX pastikan kesiapan lomba selam OBA 2026 Ambon</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:15:20 +0700</t>
+          <t>Mon, 03 Aug 2026 12:58:33 +0700</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ANTARA - Sekolah Rakyat Terintegrasi 2 Kota Kendari resmi dibuka pada Senin (3/8), yang ditandai dengan Masa Pengenalan ...</t>
+          <t>Komandan Kodaeral (Dankodaeral) IX Laksda TNI Hanarko Djodi Pamungkas memastikan kesiapan penyelenggaraan lomba selam ...</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5677373/resmi-dibuka-sekolah-rakyat-terintegrasi-2-kendari-tampung-339-siswa</t>
+          <t>https://www.antaranews.com/berita/5677288/komandan-kodaeral-ix-pastikan-kesiapan-lomba-selam-oba-2026-ambon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/RESMI-DIBUKA-SEKOLAH-RAKYAT-TERINTEGRASI-2-KENDARI-TAMPUNG-339-SISWA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001838324.jpg</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aston Martin percaya diri bisa pertahankan Alonso untuk musim 2027</t>
+          <t>Ekonomi RI alami inflasi tahunan sebesar 2,88 persen pada Juli 2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:14:16 +0700</t>
+          <t>Mon, 03 Aug 2026 11:31:08 +0700</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kepala Tim Aston Martin Adrian Newey percaya diri bisa mempertahankan jasa dari pembalapnya Fernando Alonso untuk ...</t>
+          <t>Badan Pusat Statistik (BPS) mencatat perekonomian Indonesia mengalami inflasi sebesar 2,88 persen secara tahunan ...</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677393/aston-martin-percaya-diri-bisa-pertahankan-alonso-untuk-musim-2027</t>
+          <t>https://www.antaranews.com/berita/5677207/ekonomi-ri-alami-inflasi-tahunan-sebesar-288-persen-pada-juli-2026</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/05/29/Alonso.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/01/WhatsApp-Image-2026-07-01-at-10.59.31_edit_549938834278582_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Warga Jakarta tanggapi pro-kontra soal pemasangan pagar di mal</t>
+          <t>Kementan dorong pengembangan gula tumbu alternatif hilirisasi tebu</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:13:58 +0700</t>
+          <t>Mon, 03 Aug 2026 11:13:22 +0700</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sejumlah warga di Jakarta Selatan menyampaikan beragam pendapat mereka dengan pro dan kontra dalam ...</t>
+          <t>Direktorat Jenderal Perkebunan Kementerian Pertanian mendorong pengembangan industri gula tumbu sebagai alternatif ...</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677391/warga-jakarta-tanggapi-pro-kontra-soal-pemasangan-pagar-di-mal</t>
+          <t>https://www.antaranews.com/berita/5677183/kementan-dorong-pengembangan-gula-tumbu-alternatif-hilirisasi-tebu</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001010075.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001046969.jpg</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kemenhaj perkuat kemitraan dengan Saudi bangun rantai pasok haji-umrah</t>
+          <t>KSP: Pemerintah sempurnakan regulasi terkait LTJ dan unsur radioaktif</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:09:33 +0700</t>
+          <t>Mon, 03 Aug 2026 11:05:02 +0700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kementerian Haji dan Umrah (Kemenhaj)RI mendorong penguatan kemitraan strategis antara Indonesia dan Arab Saudi guna ...</t>
+          <t>Kantor Staf Presiden (KSP) menyatakan pemerintah kini tengah menyempurnakan regulasi yang mengatur ...</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677388/kemenhaj-perkuat-kemitraan-dengan-saudi-bangun-rantai-pasok-haji-umrah</t>
+          <t>https://www.antaranews.com/berita/5677179/ksp-pemerintah-sempurnakan-regulasi-terkait-ltj-dan-unsur-radioaktif</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176390.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_5412.jpeg</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ketua KY sampaikan permintaan maaf kepada MA dan hakim</t>
+          <t>Daftar lengkap harga emas tiga jenama di Pegadaian pada Senin</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:03:28 +0700</t>
+          <t>Mon, 03 Aug 2026 10:41:19 +0700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ketua Komisi Yudisial Abdul Chair Ramadhan menyampaikan permohonan maaf kepada Ketua Mahkamah Agung dan para hakim ...</t>
+          <t>Harga emas di laman Pegadaian dikutip dari Jakarta, Senin, pukul 10.30 WIB, menunjukkan produk dari Galeri24, Antam, ...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677385/ketua-ky-sampaikan-permintaan-maaf-kepada-ma-dan-hakim</t>
+          <t>https://www.antaranews.com/berita/5677164/daftar-lengkap-harga-emas-tiga-jenama-di-pegadaian-pada-senin</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000012884.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/23/Harga-Emas-Antam-Naik-Jakarta-1.jpg</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kekeringan ancam operasional PLTN Paks di Hungaria berhenti total</t>
+          <t>Wamenaker:Penguatan kompetensi vokasi dan bahasa perluas peluang kerja</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:49:52 +0700</t>
+          <t>Mon, 03 Aug 2026 10:12:46 +0700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kekeringan yang ditimbulkan gelombang panas ekstrem membuat tinggi muka air di Sungai Danube turun dan mengancam ...</t>
+          <t>Wakil Menteri Ketenagakerjaan (Wamenaker) Afriansyah Noor menekankan pentingnya penguatan kompetensi dan kemampuan ...</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677383/kekeringan-ancam-operasional-pltn-paks-di-hungaria-berhenti-total</t>
+          <t>https://www.antaranews.com/berita/5677136/wamenakerpenguatan-kompetensi-vokasi-dan-bahasa-perluas-peluang-kerja</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CjkinzN000007_20260803_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/5cf5bd9f-4b4b-4451-9d28-2cef5e460156.jpeg</t>
         </is>
       </c>
     </row>
@@ -1004,61 +1004,61 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Anggota DPR: Penyelematan korban kapal terbakar di Sumenep harus cepat</t>
+          <t>Koalisi buruh serahkan usulan RUU Ketenagakerjaan ke pimpinan DPR</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:48:41 +0700</t>
+          <t>Mon, 03 Aug 2026 15:05:55 +0700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Anggota DPR RI Bambang Haryo Soekartono (BHS) menyatakan waktu tanggap (response time) penyelamatan terhadap ...</t>
+          <t>Koalisi dari berbagai konfederasi buruh menyerahkan draf usulan untuk penyusunan Rancangan Undang-Undang (RUU) ...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677380/anggota-dpr-penyelematan-korban-kapal-terbakar-di-sumenep-harus-cepat</t>
+          <t>https://www.antaranews.com/berita/5677460/koalisi-buruh-serahkan-usulan-ruu-ketenagakerjaan-ke-pimpinan-dpr</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1319103.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001295553.jpg</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>KPK periksa Kadis PUPR Kota Bengkulu usai geledah dan sita Rp4 miliar</t>
+          <t>BPS catat pengeluaran wisman triwulan II-2026 mencapai 1.285 dolar AS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:46:34 +0700</t>
+          <t>Mon, 03 Aug 2026 14:56:12 +0700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Komisi Pemberantasan Korupsi memeriksa Kepala Dinas Pekerjaan Umum dan Penataan Ruang (PUPR) Kota Bengkulu Noprisman ...</t>
+          <t>Badan Pusat Statistik (BPS) mencatat perkembangan pengeluaran wisatawan mancanegara (wisman) pada triwulan II tahun ...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677377/kpk-periksa-kadis-pupr-kota-bengkulu-usai-geledah-dan-sita-rp4-miliar</t>
+          <t>https://www.antaranews.com/berita/5677457/bps-catat-pengeluaran-wisman-triwulan-ii-2026-mencapai-1285-dolar-as</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_7724.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG-20260731-WA0028.jpg</t>
         </is>
       </c>
     </row>
@@ -1070,28 +1070,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pengaruh makan timun terhadap kesehatan tubuh</t>
+          <t>Charles Honoris dorong putusan MK soal MBG diterapkan pada APBN 2027</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:45:30 +0700</t>
+          <t>Mon, 03 Aug 2026 14:56:05 +0700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Profesor madya di bidang nutrisi dan kesehatan masyarakat dari Fakultas Kedokteran Universitas Tufts Kimberly Dong ...</t>
+          <t>Wakil Ketua Komisi IX DPR RI Charles Honoris mendorong putusan Mahkamah Konstitusi (MK) mengenai anggaran program Makan ...</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677375/pengaruh-makan-timun-terhadap-kesehatan-tubuh</t>
+          <t>https://www.antaranews.com/berita/5677456/charles-honoris-dorong-putusan-mk-soal-mbg-diterapkan-pada-apbn-2027</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2022/11/03/antarafoto-pasokan-buah-timun-terdampak-cuaca-di-pulau-bacan-3112022-ans-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/upscalemedia-transformed-167.jpeg</t>
         </is>
       </c>
     </row>
@@ -1103,259 +1103,259 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jaksel catat mobil klinik hewan layani 226 ekor kucing hingga domba</t>
+          <t>Wamensos: Kolaborasi data perkuatkan bantuan JKN lebih akuntabel</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:38:38 +0700</t>
+          <t>Mon, 03 Aug 2026 14:54:53 +0700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Suku Dinas Ketahanan Pangan, Kelautan, dan Pertanian Jakarta Selatan (KPKP Jaksel) mencatat Mobil Klinik Hewan ...</t>
+          <t>Wakil Menteri Sosial (Wamensos) Agus Jabo Priyono mengatakan kolaborasi strategis yang dilakukan bersama BPJS ...</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677369/jaksel-catat-mobil-klinik-hewan-layani-226-ekor-kucing-hingga-domba</t>
+          <t>https://www.antaranews.com/berita/5677453/wamensos-kolaborasi-data-perkuatkan-bantuan-jkn-lebih-akuntabel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001010031.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-14.44.56-1.jpeg</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>lifestyle, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10 ide lomba 17 Agustus untuk anak PAUD dan TK yang seru, edukatif, dan mudah digelar</t>
+          <t>Presiden Iran: AS harus tetap patuhi nota kesepahaman</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:38:29 +0700</t>
+          <t>Mon, 03 Aug 2026 14:54:11 +0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Perayaan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 dapat menjadi momen bagi anak usia PAUD dan TK ...</t>
+          <t>Presiden Iran Masoud Pezeshkian mengatakan pada Minggu (2/8) bahwa Amerika Serikat harus tetap berkomitmen pada nota ...</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677368/10-ide-lomba-17-agustus-untuk-anak-paud-dan-tk-yang-seru-edukatif-dan-mudah-digelar</t>
+          <t>https://www.antaranews.com/berita/5677449/presiden-iran-as-harus-tetap-patuhi-nota-kesepahaman</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/08/03/WhatsApp-Image-2024-08-03-at-20.37.28.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CjkinzN000008_20260803_CBMFN0A001.jpeg</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini, top-news</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kemnaker: Magang Nasional diharapkan menekan angka pengangguran muda</t>
+          <t>Kapal Pertamina selamatkan 17 korban KMP Mutiara Sentosa 2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:37:57 +0700</t>
+          <t>Mon, 03 Aug 2026 14:52:47 +0700</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kementerian Ketenagakerjaan (Kemnaker) mengatakan program Magang Nasional (MagangHub) untuk mempersiapkan kompetensi ...</t>
+          <t>Kapal Pertamina Patra Niaga MT Transko Arafura berhasil mengevakuasi 17 orang korban KMP Mutiara Sentosa 2 yang ...</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677364/kemnaker-magang-nasional-diharapkan-menekan-angka-pengangguran-muda</t>
+          <t>https://www.antaranews.com/berita/5677445/kapal-pertamina-selamatkan-17-korban-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/13/KUM2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-14.30.38.jpeg</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>terkini, top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kemenag perkuat transformasi madrasah lewat revitalisasi-digitalisasi</t>
+          <t>Ekonomi kelautan China catat pertumbuhan stabil pada H1 2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:36:36 +0700</t>
+          <t>Mon, 03 Aug 2026 14:50:44 +0700</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Menteri Agama (Menag) Nasaruddin Umar menegaskan transformasi madrasah terus diperkuat melalui revitalisasi ...</t>
+          <t>Produk laut bruto (PLB) China mencapai 5,5 triliun yuan (1 yuan = Rp2.676) pada paruh pertama (H1) 2026, naik 5,1 ...</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677363/kemenag-perkuat-transformasi-madrasah-lewat-revitalisasi-digitalisasi</t>
+          <t>https://www.antaranews.com/berita/5677441/ekonomi-kelautan-china-catat-pertumbuhan-stabil-pada-h1-2026</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000173935.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CjkinzN000010_20260803_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wali Kota pastikan fasilitas SRT Kendari dukung perkembangan siswa</t>
+          <t>PGN sasar pemanfaatan jargas untuk hotel hingga UMKM</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:36:17 +0700</t>
+          <t>Mon, 03 Aug 2026 14:50:20 +0700</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wali Kota Kendari Siska Karina Imran memastikan bahwa fasilitas yang ada di Sekolah Rakyat Terintegrasi (SRT) 2 Kota ...</t>
+          <t>PT Perusahaan Gas Negara (Persero) Tbk (PGN) menyasar pemanfaatan jaringan gas (jargas) tidak hanya rumah ...</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677359/wali-kota-pastikan-fasilitas-srt-kendari-dukung-perkembangan-siswa</t>
+          <t>https://www.antaranews.com/berita/5677439/pgn-sasar-pemanfaatan-jargas-untuk-hotel-hingga-umkm</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/aeea98a9-b62b-4a35-a533-805d3c8ac339.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_2395.jpeg</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>lifestyle, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sering terbangun tengah malam? Kenali 7 penyebab dan cara mengatasinya</t>
+          <t>TNI AL tuntaskan latihan gabungan dengan AL Australia</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:35:20 +0700</t>
+          <t>Mon, 03 Aug 2026 14:46:09 +0700</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bangun di tengah malam sesekali merupakan hal yang normal. Namun, jika kondisi ini terjadi hampir setiap malam dan ...</t>
+          <t>TNI AL menuntaskan kegiatan latihan gabungan dengan AL Australia atau Royal Australian Navy (RAN) dalam ajang Cassowary ...</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677357/sering-terbangun-tengah-malam-kenali-7-penyebab-dan-cara-mengatasinya</t>
+          <t>https://www.antaranews.com/berita/5677436/tni-al-tuntaskan-latihan-gabungan-dengan-al-australia</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/20/Penumpang-rela-menginap-menunggu-kereta-pertama-di-Stasiun-Cikarang-150726-ryl-5.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001554245.jpg</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini, top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lisensi IP Global Buka Peluang Bisnis Baru bagi Kreator Indonesia</t>
+          <t>Wamenkomdigi: TVRI institusi strategis penjaga ruang informasi bangsa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:34:30 +0700</t>
+          <t>Mon, 03 Aug 2026 14:45:19 +0700</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wakil Menteri Ekonomi Kreatif Irene Umar mengatakan kolaborasi antara pemilik kekayaan intelektual (Intellectual ...</t>
+          <t>Wakil Menteri Komunikasi dan Digital (Wamenkomdigi) Angga Raka Prabowo menyatakan Lembaga Penyiaran Publik (LPP) TVRI ...</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677353/lisensi-ip-global-buka-peluang-bisnis-baru-bagi-kreator-indonesia</t>
+          <t>https://www.antaranews.com/berita/5677432/wamenkomdigi-tvri-institusi-strategis-penjaga-ruang-informasi-bangsa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000589873.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0224.jpg</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>photo, terkini</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Gempa bermagnitudo 5,3 guncang Mesir timur laut</t>
+          <t>Petani berbagi air sumur demi selamatkan tanaman tembakau</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:32:32 +0700</t>
+          <t>Mon, 03 Aug 2026 14:44:51 +0700</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sebuah gempa bermagnitudo 5,3 mengguncang Provinsi Ismailia di Mesir timur laut pada Senin pagi waktu setempat, menurut ...</t>
+          <t>Petani mengambil air dari sumur untuk menyiram tanaman tembakau di Lengkong, Nganjuk, Jawa Timur, Senin (3/8/2026). ...</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677351/gempa-bermagnitudo-53-guncang-mesir-timur-laut</t>
+          <t>https://www.antaranews.com/foto/5677428/petani-berbagi-air-sumur-demi-selamatkan-tanaman-tembakau</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/18/ilustrasi-gempa-2_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/petani-tembakau-berbagi-air-sumur-antisipasi-dampak-el-nino-030826-mm-1.jpg</t>
         </is>
       </c>
     </row>
@@ -1367,61 +1367,61 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dedi Kusnandar: Persib siap hadapi Persija di semifinal Piala Presiden</t>
+          <t>BPK berikan opini WTP kepada Kemenko Kumham Imipas atas LK 2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:31:31 +0700</t>
+          <t>Mon, 03 Aug 2026 14:44:20 +0700</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gelandang Persib Bandung Dedi Kusnandar menegaskan timnya siap menghadapi Persija Jakarta pada babak semifinal Piala ...</t>
+          <t>Badan Pemeriksa Keuangan RI memberikan opini Wajar Tanpa Pengecualian (WTP) kepada seluruh kementerian di bawah ...</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677349/dedi-kusnandar-persib-siap-hadapi-persija-di-semifinal-piala-presiden</t>
+          <t>https://www.antaranews.com/berita/5677427/bpk-berikan-opini-wtp-kepada-kemenko-kumham-imipas-atas-lk-2025</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_9111.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001216320.jpg</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Wakil Ketua DPR salurkan beasiswa PIP ke ribuan pelajar Lombok Timur</t>
+          <t>Nusron sebut banyak laut di Batam telah dikapling tanpa prosedur sah</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:30:16 +0700</t>
+          <t>Mon, 03 Aug 2026 14:44:05 +0700</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wakil Ketua DPR RI Sari Yuliati menyerahkan bantuan beasiswa Program Indonesia Pintar (PIP) 2026 kepada ribuan pelajar ...</t>
+          <t>Menteri Agraria dan Tata Ruang (ATR)/Kepala Badan Pertanahan Nasional (BPN) Nusron Wahid mengatakan, menerima banyak ...</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677345/wakil-ketua-dpr-salurkan-beasiswa-pip-ke-ribuan-pelajar-lombok-timur</t>
+          <t>https://www.antaranews.com/berita/5677425/nusron-sebut-banyak-laut-di-batam-telah-dikapling-tanpa-prosedur-sah</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1005724306.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_142345.jpg</t>
         </is>
       </c>
     </row>
@@ -1433,94 +1433,94 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dinkop UKM Cilegon targetkan 21 gerai baru KKMP beroperasi September</t>
+          <t>Bareskrim gagalkan peredaran ganja 20 kilogram ke Kampung Bahari</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:27:17 +0700</t>
+          <t>Mon, 03 Aug 2026 14:41:18 +0700</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ANTARA - Dinas Koperasi Usaha Kecil dan Menengah (Dinkop UKM) Kota Cilegon menargetkan pembangunan  21 gedung ...</t>
+          <t>Direktorat Tindak Pidana Narkoba Bareskrim Polri berhasil menggagalkan peredaran narkoba jenis ganja seberat 20 ...</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5677301/dinkop-ukm-cilegon-targetkan-21-gerai-baru-kkmp-beroperasi-september</t>
+          <t>https://www.antaranews.com/berita/5677421/bareskrim-gagalkan-peredaran-ganja-20-kilogram-ke-kampung-bahari</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/DINKOP-UKM-CILEGON-TARGETKAN-21-GERAI-BARU-KKMP-BEROPERASI-SEPTEMBER.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000087102.jpg</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>humaniora, terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bantuan beras 30 kg cair mulai 17 Agustus 2026, ini jadwal dan cara cek penerimanya</t>
+          <t>CORE: Harga Pertamax turun beri sentimen positif bagi inflasi</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:27:14 +0700</t>
+          <t>Mon, 03 Aug 2026 14:40:44 +0700</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pemerintah memastikan penyaluran bantuan pangan beras tahap II tahun 2026 akan dimulai pada 17 Agustus 2026. Bantuan ...</t>
+          <t>Ekonom Center of Reform on Economics (CORE) Yusuf Rendy Manilet menyampaikan penurunan harga Pertamax pada bulan ...</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677341/bantuan-beras-30-kg-cair-mulai-17-agustus-2026-ini-jadwal-dan-cara-cek-penerimanya</t>
+          <t>https://www.antaranews.com/berita/5677420/core-harga-pertamax-turun-beri-sentimen-positif-bagi-inflasi</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/26/kemensos-percepat-penyaluran-bansos-pkh-dan-bpnt-2778877.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/penurunan-harga-bbm-jenis-pertamax-2831783.jpg</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Puluhan santri Ponpes Darul Amanah Kendal kunjungi Istana Presiden</t>
+          <t>Askrindo bukukan laba Rp1,69 T pada 2025 ditopang tiga lini bisnis</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:24:08 +0700</t>
+          <t>Mon, 03 Aug 2026 14:38:49 +0700</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Puluhan santri beserta pengajar Pondok Pesantren Darul Amanah Sukorejo, Kendal, Jawa Tengah, melakukan kunjungan ...</t>
+          <t>PT Asuransi Kredit Indonesia (Persero) atau Askrindo membukukan laba setelah pajak sebesar Rp1,69 triliun pada 2025 ...</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677337/puluhan-santri-ponpes-darul-amanah-kendal-kunjungi-istana-presiden</t>
+          <t>https://www.antaranews.com/berita/5677419/askrindo-bukukan-laba-rp169-t-pada-2025-ditopang-tiga-lini-bisnis</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_3918.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-08.51.32.jpeg</t>
         </is>
       </c>
     </row>
@@ -1532,61 +1532,61 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cek fakta, Pemprov Jabar resmi adakan kembali SPP untuk sekolah negeri pada Juli 2026</t>
+          <t>KPK lakukan 762 penyadapan selama semester I 2026</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:23:04 +0700</t>
+          <t>Mon, 03 Aug 2026 14:33:32 +0700</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Jakarta (ANTARA/JACX) – Sebuah unggahan di Facebook menarasikan bahwa Pemerintah Provinsi Jawa Barat ...</t>
+          <t>Dewan Pengawas Komisi Pemberantasan Korupsi (Dewas KPK) menyatakan lembaga antirasuah telah melakukan 762 penyadapan ...</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677333/cek-fakta-pemprov-jabar-resmi-adakan-kembali-spp-untuk-sekolah-negeri-pada-juli-2026</t>
+          <t>https://www.antaranews.com/berita/5677415/kpk-lakukan-762-penyadapan-selama-semester-i-2026</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/17/WhatsApp-Image-2026-06-17-at-20.14.04.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_8172.jpg</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>lifestyle, terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bahaya paparan pornografi pada anak: Dampak bagi otak, mental, dan perilaku</t>
+          <t>Jasaraharja Putera menjamin santunan korban KMP Mutiara Sentosa II</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:23:03 +0700</t>
+          <t>Mon, 03 Aug 2026 14:30:17 +0700</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Perkembangan teknologi membuat anak-anak dan remaja semakin akrab dengan internet sejak usia dini. Di satu sisi, ...</t>
+          <t>PT Jasaraharja Putera menjamin perlindungan dan santunan bagi seluruh korban kebakaran Kapal Motor Penyeberangan (KMP) ...</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677332/bahaya-paparan-pornografi-pada-anak-dampak-bagi-otak-mental-dan-perilaku</t>
+          <t>https://www.antaranews.com/berita/5677412/jasaraharja-putera-menjamin-santunan-korban-kmp-mutiara-sentosa-ii</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/02/ilustrasi-konten-berbau-pornografi.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176259.jpg</t>
         </is>
       </c>
     </row>
@@ -1598,61 +1598,61 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Advokat ingatkan RUU Perampasan Aset tidak boleh jadi alat politik</t>
+          <t>Petani di Jakut harap pemerintah beri bantuan hadapi musim kemarau</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:22:07 +0700</t>
+          <t>Mon, 03 Aug 2026 14:29:53 +0700</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Advokat Juniver Girsang mengingatkan kepada DPR RI agar Rancangan Undang-Undang (RUU) Perampasan Aset tidak justru ...</t>
+          <t>Petani di Kelurahan Rorotan, Cilincing Jakarta Utara berharap pemerintah dapat memberikan bantuan untuk menunjang ...</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677329/advokat-ingatkan-ruu-perampasan-aset-tidak-boleh-jadi-alat-politik</t>
+          <t>https://www.antaranews.com/berita/5677408/petani-di-jakut-harap-pemerintah-beri-bantuan-hadapi-musim-kemarau</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001295469.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/13/IMG_20260713_140727.jpg</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hoaks! Febrie Adriansyah bebas karena emas dan uang sitaan dinyatakan palsu</t>
+          <t>GMR bidik Indonesia dalam perluasan rute Bandara Bhogapuram India</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:20:23 +0700</t>
+          <t>Mon, 03 Aug 2026 14:29:34 +0700</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jakarta (ANTARA/JACX) – Sebuah unggahan di Facebook menarasikan bahwa mantan Jaksa Agung Muda Bidang ...</t>
+          <t>GMR Airports Limited (GMR Airports), salah satu pengelola jaringan bandara internasional, memprioritaskan Indonesia ...</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677328/hoaks-febrie-adriansyah-bebas-karena-emas-dan-uang-sitaan-dinyatakan-palsu</t>
+          <t>https://www.antaranews.com/berita/5677407/gmr-bidik-indonesia-dalam-perluasan-rute-bandara-bhogapuram-india</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/11/Konferensi-pers-Jampidsus-100726-Ada-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0725.jpeg</t>
         </is>
       </c>
     </row>
@@ -1664,61 +1664,61 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Hoaks! Komdigi terapkan balik nama ponsel bekas seperti kendaraan pada Juli 2026</t>
+          <t>BPJS Kesehatan gandeng empat K/L perkuat ekosistem Program JKN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:19:15 +0700</t>
+          <t>Mon, 03 Aug 2026 14:28:03 +0700</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Jakarta (ANTARA/JACX) – Sebuah unggahan video di Facebook menarasikan bahwa Kementerian Komunikasi ...</t>
+          <t>BPJS Kesehatan menjalin kerja sama strategis dengan empat Kementerian dan Lembaga (K/L) sebagai upaya memperkuat ...</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677324/hoaks-komdigi-terapkan-balik-nama-ponsel-bekas-seperti-kendaraan-pada-juli-2026</t>
+          <t>https://www.antaranews.com/berita/5677404/bpjs-kesehatan-gandeng-empat-k-l-perkuat-ekosistem-program-jkn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/08/1000135509.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-14.08.02.jpg</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BPS catat nilai tukar petani di level 127,84 pada Juli 2026</t>
+          <t>Rusia tetap terbuka berunding dengan Ukraina</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:18:40 +0700</t>
+          <t>Mon, 03 Aug 2026 14:23:43 +0700</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat nilai tukar petani (NTP) secara nasional pada bulan Juli 2026 berada di level ...</t>
+          <t>Rusia menegaskan tetap membuka peluang perundingan dengan Ukraina dan siap mempertimbangkan berbagai usulan yang ...</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677323/bps-catat-nilai-tukar-petani-di-level-12784-pada-juli-2026</t>
+          <t>https://www.antaranews.com/berita/5677403/rusia-tetap-terbuka-berunding-dengan-ukraina</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/02/20260302_083324.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/06/thumbs_b2_e27328c11fef925beee70a6fbdcf61b4.jpg</t>
         </is>
       </c>
     </row>
@@ -1730,127 +1730,127 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tebang 10 pohon peneduh, pengelola padel dipanggil Pemkot Bandung</t>
+          <t>Kejati NTB minta data pajak PT GNE ke Kemenkeu untuk penyidikan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:17:41 +0700</t>
+          <t>Mon, 03 Aug 2026 14:23:27 +0700</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pemerintah Kota (Pemkot) Bandung, Jawa Barat, memanggil pengelola lapang Padel Six Nine untuk dimintai keterangan ...</t>
+          <t>Kejaksaan Tinggi Nusa Tenggara Barat meminta data pajak PT Gerbang NTB Emas (GNE) kepada Kementerian Keuangan sebagai ...</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677320/tebang-10-pohon-peneduh-pengelola-padel-dipanggil-pemkot-bandung</t>
+          <t>https://www.antaranews.com/berita/5677400/kejati-ntb-minta-data-pajak-pt-gne-ke-kemenkeu-untuk-penyidikan</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/5b6bcd7b-f3c3-4ea6-ba5f-55c5deba8a39.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/aspidsus-kejati-ntb-zulkifli-said-9.jpg</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cek fakta, utang Indonesia tembus Rp10.000 triliun</t>
+          <t>BPS: Wisman per Juni capai 7,45 juta kunjungan, tertinggi sejak 2020</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:17:18 +0700</t>
+          <t>Mon, 03 Aug 2026 14:22:48 +0700</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Jakarta (ANTARA/JACX) – Sebuah unggahan video di Facebook berdurasi sekitar satu menit menarasikan ...</t>
+          <t>Badan Pusat Statistik (BPS) mencatat total kunjungan wisatawan mancanegara dari Januari hingga bulan Juni 2026 mencapai ...</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677319/cek-fakta-utang-indonesia-tembus-rp10000-triliun</t>
+          <t>https://www.antaranews.com/berita/5677399/bps-wisman-per-juni-capai-745-juta-kunjungan-tertinggi-sejak-2020</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/02/17/Utang-Luar-Negeri-Kuartal-III-Turun-161122-Adm-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/pelepasliaran-500-ekor-tukik-bali-290726-nhw-3_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini, top-news</t>
+          <t>terkini, top-news</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nilai ekspor perdagangan RI Januari-Juni capai 140,81 miliar dolar AS</t>
+          <t>Menkomdigi panggil YouTube imbas temuan konten promosi vape sasar anak</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:16:17 +0700</t>
+          <t>Mon, 03 Aug 2026 14:22:09 +0700</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat nilai ekspor Indonesia secara kumulatif dari Januari-Juni 2026 mencapai 140,81 ...</t>
+          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid merencanakan pemanggilan terhadap platform digital YouTube ...</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677315/nilai-ekspor-perdagangan-ri-januari-juni-capai-14081-miliar-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5677396/menkomdigi-panggil-youtube-imbas-temuan-konten-promosi-vape-sasar-anak</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/neraca-perdagangan-januari-mei-2026-surplus-2815779.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0225.jpg</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>tekno, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cara mengganti password WiFi lewat HP dan laptop dengan mudah</t>
+          <t>Pemprov Jatim siap tanggung biaya RS korban KMP Mutiara yang terbakar</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:16:14 +0700</t>
+          <t>Mon, 03 Aug 2026 14:19:46 +0700</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>WiFi yang tiba-tiba terasa lambat padahal sinyal penuh dan kuota internet masih banyak tentu membuat kesal. Salah satu ...</t>
+          <t>Pemerintah Provinsi (Pemprov) Jawa Timur (Jatim) mengatakan siap menanggung biaya rumah sakit korban kebakaran ...</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677312/cara-mengganti-password-wifi-lewat-hp-dan-laptop-dengan-mudah</t>
+          <t>https://www.antaranews.com/berita/5677395/pemprov-jatim-siap-tanggung-biaya-rs-korban-kmp-mutiara-yang-terbakar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2020/08/19/antarafoto-warga-sediakan-internet-gratis-bagi-pelajar-190820-ief-2-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/261107.jpg</t>
         </is>
       </c>
     </row>
@@ -1862,61 +1862,61 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AS-Iran mulai perundingan 3 Agustus, Trump singgung Hormuz dan denuklirisasi</t>
+          <t>Resmi dibuka, Sekolah Rakyat Terintegrasi 2 Kendari tampung 339 siswa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:14:21 +0700</t>
+          <t>Mon, 03 Aug 2026 14:15:20 +0700</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Presiden AS Donald Trump mengatakan pada Minggu (2/8) bahwa negosiasi dengan Iran akan dimulai Senin sore, seraya ...</t>
+          <t>ANTARA - Sekolah Rakyat Terintegrasi 2 Kota Kendari resmi dibuka pada Senin (3/8), yang ditandai dengan Masa Pengenalan ...</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677311/as-iran-mulai-perundingan-3-agustus-trump-singgung-hormuz-dan-denuklirisasi</t>
+          <t>https://www.antaranews.com/video/5677373/resmi-dibuka-sekolah-rakyat-terintegrasi-2-kendari-tampung-339-siswa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CjkinzN000006_20260803_CBMFN0A001.png</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/RESMI-DIBUKA-SEKOLAH-RAKYAT-TERINTEGRASI-2-KENDARI-TAMPUNG-339-SISWA.jpg</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Menteri ATR sebut 400 Kantah sudah terapkan pengukuran terjadwal</t>
+          <t>Aston Martin percaya diri bisa pertahankan Alonso untuk musim 2027</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:13:29 +0700</t>
+          <t>Mon, 03 Aug 2026 14:14:16 +0700</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Menteri Agraria dan Tata Ruang/Kepala Badan Pertanahan Nasional (ATR/BPN) Nusron Wahid mengatakan bahwa sudah ada 400 ...</t>
+          <t>Kepala Tim Aston Martin Adrian Newey percaya diri bisa mempertahankan jasa dari pembalapnya Fernando Alonso untuk ...</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677308/menteri-atr-sebut-400-kantah-sudah-terapkan-pengukuran-terjadwal</t>
+          <t>https://www.antaranews.com/berita/5677393/aston-martin-percaya-diri-bisa-pertahankan-alonso-untuk-musim-2027</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_125328.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/05/29/Alonso.jpg</t>
         </is>
       </c>
     </row>
@@ -1928,28 +1928,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Menag: Fungsi masjid perlu terus diperluas dalam memberdayakan umat</t>
+          <t>Warga Jakarta tanggapi pro-kontra soal pemasangan pagar di mal</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:10:48 +0700</t>
+          <t>Mon, 03 Aug 2026 14:13:58 +0700</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Menteri Agama (Menag) Nasaruddin Umar menegaskan fungsi masjid perlu terus diperluas sebagai pusat pemberdayaan ...</t>
+          <t>Sejumlah warga di Jakarta Selatan menyampaikan beragam pendapat mereka dengan pro dan kontra dalam ...</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677307/menag-fungsi-masjid-perlu-terus-diperluas-dalam-memberdayakan-umat</t>
+          <t>https://www.antaranews.com/berita/5677391/warga-jakarta-tanggapi-pro-kontra-soal-pemasangan-pagar-di-mal</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176377.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001010075.jpg</t>
         </is>
       </c>
     </row>
@@ -1961,61 +1961,61 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kemerdekaan, demokrasi, dan kesejahteraan rakyat</t>
+          <t>Kemenhaj perkuat kemitraan dengan Saudi bangun rantai pasok haji-umrah</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:10:15 +0700</t>
+          <t>Mon, 03 Aug 2026 14:09:33 +0700</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kemerdekaan dan demokrasi adalah hulu, sementara kesejahteraan rakyat merupakan hilir. Imajinasi ini bersinggungan ...</t>
+          <t>Kementerian Haji dan Umrah (Kemenhaj)RI mendorong penguatan kemitraan strategis antara Indonesia dan Arab Saudi guna ...</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677303/kemerdekaan-demokrasi-dan-kesejahteraan-rakyat</t>
+          <t>https://www.antaranews.com/berita/5677388/kemenhaj-perkuat-kemitraan-dengan-saudi-bangun-rantai-pasok-haji-umrah</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/penjualan-pernak-pernik-hut-ri-di-jakarta-2832459.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176390.jpg</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>terkini, top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Korban KMP Mutiara Sentosa II dievakuasi ke Pelabuhan Tanjung Perak</t>
+          <t>Ketua KY sampaikan permintaan maaf kepada MA dan hakim</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:06:15 +0700</t>
+          <t>Mon, 03 Aug 2026 14:03:28 +0700</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tim SAR gabungan terus melakukan evakuasi korban terbakarnya KMP Mutiara Sentosa 2 ke darat, tepatnya ke Pelabuhan ...</t>
+          <t>Ketua Komisi Yudisial Abdul Chair Ramadhan menyampaikan permohonan maaf kepada Ketua Mahkamah Agung dan para hakim ...</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677297/korban-kmp-mutiara-sentosa-ii-dievakuasi-ke-pelabuhan-tanjung-perak</t>
+          <t>https://www.antaranews.com/berita/5677385/ketua-ky-sampaikan-permintaan-maaf-kepada-ma-dan-hakim</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/260821.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000012884.jpg</t>
         </is>
       </c>
     </row>
@@ -2027,28 +2027,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Inggris terancam resesi jika Selat Hormuz terus tutup sampai 2027</t>
+          <t>Kekeringan ancam operasional PLTN Paks di Hungaria berhenti total</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:04:05 +0700</t>
+          <t>Mon, 03 Aug 2026 13:49:52 +0700</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Inggris terancam mengalami resesi ekonomi pada 2027 apabila Selat Hormuz tak kunjung dibuka, menurut laporan surat ...</t>
+          <t>Kekeringan yang ditimbulkan gelombang panas ekstrem membuat tinggi muka air di Sungai Danube turun dan mengancam ...</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677293/inggris-terancam-resesi-jika-selat-hormuz-terus-tutup-sampai-2027</t>
+          <t>https://www.antaranews.com/berita/5677383/kekeringan-ancam-operasional-pltn-paks-di-hungaria-berhenti-total</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/24/CmxztpE000057_20260128_PEPFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CjkinzN000007_20260803_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
@@ -2060,28 +2060,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pentingnya memantau asupan serat bagi wanita</t>
+          <t>Anggota DPR: Penyelematan korban kapal terbakar di Sumenep harus cepat</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:03:51 +0700</t>
+          <t>Mon, 03 Aug 2026 13:48:41 +0700</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ahli gizi Brenna Larson, M.S., RD mengatakan idealnya tiap wanita harus menargetkan 25 gram serat per hari karena ...</t>
+          <t>Anggota DPR RI Bambang Haryo Soekartono (BHS) menyatakan waktu tanggap (response time) penyelamatan terhadap ...</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677291/pentingnya-memantau-asupan-serat-bagi-wanita</t>
+          <t>https://www.antaranews.com/berita/5677380/anggota-dpr-penyelematan-korban-kapal-terbakar-di-sumenep-harus-cepat</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/02/19/Sayur.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1319103.jpg</t>
         </is>
       </c>
     </row>
@@ -2093,2858 +2093,3386 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Komandan Kodaeral IX pastikan kesiapan lomba selam OBA 2026 Ambon</t>
+          <t>KPK periksa Kadis PUPR Kota Bengkulu usai geledah dan sita Rp4 miliar</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:58:33 +0700</t>
+          <t>Mon, 03 Aug 2026 13:46:34 +0700</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Komandan Kodaeral (Dankodaeral) IX Laksda TNI Hanarko Djodi Pamungkas memastikan kesiapan penyelenggaraan lomba selam ...</t>
+          <t>Komisi Pemberantasan Korupsi memeriksa Kepala Dinas Pekerjaan Umum dan Penataan Ruang (PUPR) Kota Bengkulu Noprisman ...</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677288/komandan-kodaeral-ix-pastikan-kesiapan-lomba-selam-oba-2026-ambon</t>
+          <t>https://www.antaranews.com/berita/5677377/kpk-periksa-kadis-pupr-kota-bengkulu-usai-geledah-dan-sita-rp4-miliar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001838324.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_7724.jpg</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Aktor senior Diding Boneng meninggal dunia</t>
+          <t>Pengaruh makan timun terhadap kesehatan tubuh</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:39:03 +0700</t>
+          <t>Mon, 03 Aug 2026 13:45:30 +0700</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aktor sekaligus komedian tanah air, Zainal Abidin alias Diding Boneng dikabarkan meninggal dunia pada Senin (3/8) dalam ...</t>
+          <t>Profesor madya di bidang nutrisi dan kesehatan masyarakat dari Fakultas Kedokteran Universitas Tufts Kimberly Dong ...</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677209/aktor-senior-diding-boneng-meninggal-dunia</t>
+          <t>https://www.antaranews.com/berita/5677375/pengaruh-makan-timun-terhadap-kesehatan-tubuh</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/26f1eb88-3301-4ae1-badd-bed5078fe3dd.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/11/03/antarafoto-pasokan-buah-timun-terdampak-cuaca-di-pulau-bacan-3112022-ans-1.jpg</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Seskab: Prabowo dorong sinergi pemerintah dan dunia usaha</t>
+          <t>Jaksel catat mobil klinik hewan layani 226 ekor kucing hingga domba</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:17:50 +0700</t>
+          <t>Mon, 03 Aug 2026 13:38:38 +0700</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sekretaris Kabinet Teddy Indra Wijaya menyampaikan bahwa Presiden Prabowo Subianto menekankan pentingnya sinergi antara ...</t>
+          <t>Suku Dinas Ketahanan Pangan, Kelautan, dan Pertanian Jakarta Selatan (KPKP Jaksel) mencatat Mobil Klinik Hewan ...</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677191/seskab-prabowo-dorong-sinergi-pemerintah-dan-dunia-usaha</t>
+          <t>https://www.antaranews.com/berita/5677369/jaksel-catat-mobil-klinik-hewan-layani-226-ekor-kucing-hingga-domba</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0891.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001010031.jpg</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>lifestyle, terkini</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Red Velvet bersiap kembali lewat EP baru "Velvet Summer"</t>
+          <t>10 ide lomba 17 Agustus untuk anak PAUD dan TK yang seru, edukatif, dan mudah digelar</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:24:37 +0700</t>
+          <t>Mon, 03 Aug 2026 13:38:29 +0700</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Grup idola K-pop Red Velvet akan kembali lewat rilis mini album atau extended play (EP) baru bertajuk “Velvet ...</t>
+          <t>Perayaan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 dapat menjadi momen bagi anak usia PAUD dan TK ...</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677151/red-velvet-bersiap-kembali-lewat-ep-baru-velvet-summer</t>
+          <t>https://www.antaranews.com/berita/5677368/10-ide-lomba-17-agustus-untuk-anak-paud-dan-tk-yang-seru-edukatif-dan-mudah-digelar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/ca97a3a8-aa17-45fc-be71-d36051dd9dcd.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/08/03/WhatsApp-Image-2024-08-03-at-20.37.28.jpeg</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, top-news</t>
+          <t>ekonomi-bisnis, terkini, top-news</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Menaker pastikan komitmen pemerintah perkuat kesejahteraan pekerja</t>
+          <t>Kemnaker: Magang Nasional diharapkan menekan angka pengangguran muda</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:16:19 +0700</t>
+          <t>Mon, 03 Aug 2026 13:37:57 +0700</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Menteri Ketenagakerjaan (Menaker) Yassierli memastikan pemerintah berkomitmen untuk memperkuat kesejahteraan, ...</t>
+          <t>Kementerian Ketenagakerjaan (Kemnaker) mengatakan program Magang Nasional (MagangHub) untuk mempersiapkan kompetensi ...</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677148/menaker-pastikan-komitmen-pemerintah-perkuat-kesejahteraan-pekerja</t>
+          <t>https://www.antaranews.com/berita/5677364/kemnaker-magang-nasional-diharapkan-menekan-angka-pengangguran-muda</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/09/20/pelepasan-peserta-pemagangan-ke-jepang-di-jawa-barat-2627513.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/ff63afaf-7778-47fe-833d-5a8068af9a51_1.jpeg</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini, top-news</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>23 calon hakim agung dan ad hoc ikuti seleksi wawancara akhir</t>
+          <t>Kemenag perkuat transformasi madrasah lewat revitalisasi-digitalisasi</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:15:01 +0700</t>
+          <t>Mon, 03 Aug 2026 13:36:36 +0700</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sebanyak 23 orang calon hakim agung dan ad hoc Mahkamah Agung Tahun 2026 mengikuti seleksi wawancara tahap akhir di ...</t>
+          <t>Menteri Agama (Menag) Nasaruddin Umar menegaskan transformasi madrasah terus diperkuat melalui revitalisasi ...</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677137/23-calon-hakim-agung-dan-ad-hoc-ikuti-seleksi-wawancara-akhir</t>
+          <t>https://www.antaranews.com/berita/5677363/kemenag-perkuat-transformasi-madrasah-lewat-revitalisasi-digitalisasi</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000012883_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/14/1000173935_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BRIN perkuat kajian sungai bawah tanah di Kebumen untuk ketahanan air</t>
+          <t>Wali Kota pastikan fasilitas SRT Kendari dukung perkembangan siswa</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:57:19 +0700</t>
+          <t>Mon, 03 Aug 2026 13:36:17 +0700</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Badan Riset dan Inovasi Nasional (BRIN) memperkuat riset ketahanan air melalui pengembangan teknologi dan penelitian ...</t>
+          <t>Wali Kota Kendari Siska Karina Imran memastikan bahwa fasilitas yang ada di Sekolah Rakyat Terintegrasi (SRT) 2 Kota ...</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677120/brin-perkuat-kajian-sungai-bawah-tanah-di-kebumen-untuk-ketahanan-air</t>
+          <t>https://www.antaranews.com/berita/5677359/wali-kota-pastikan-fasilitas-srt-kendari-dukung-perkembangan-siswa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1785706440-47672950-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/aeea98a9-b62b-4a35-a533-805d3c8ac339.jpeg</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>lifestyle, terkini</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Harga bensin turun pada pekan pertama Agustus</t>
+          <t>Sering terbangun tengah malam? Kenali 7 penyebab dan cara mengatasinya</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:51:00 +0700</t>
+          <t>Mon, 03 Aug 2026 13:35:20 +0700</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Harga bahan bakar minyak (BBM) jenis bensin di stasiun pengisian bahan bakar umum (SPBU) Pertamina, Shell, dan bp ...</t>
+          <t>Bangun di tengah malam sesekali merupakan hal yang normal. Namun, jika kondisi ini terjadi hampir setiap malam dan ...</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677109/harga-bensin-turun-pada-pekan-pertama-agustus</t>
+          <t>https://www.antaranews.com/berita/5677357/sering-terbangun-tengah-malam-kenali-7-penyebab-dan-cara-mengatasinya</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/10/02/penuruanan-harga-bbm-011024-aaa-7.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/20/Penumpang-rela-menginap-menunggu-kereta-pertama-di-Stasiun-Cikarang-150726-ryl-5.jpg</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-bisnis, terkini, top-news</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sean Gelael berbagi pengalaman di dunia balap ke pengunjung GIIAS 2026</t>
+          <t>Lisensi IP Global Buka Peluang Bisnis Baru bagi Kreator Indonesia</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:34:53 +0700</t>
+          <t>Mon, 03 Aug 2026 13:34:30 +0700</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Pembalap Indonesia Sean Gelael berbagi pengalamannya di dunia balap ke pengunjung GAIKINDO Indonesia International ...</t>
+          <t>Wakil Menteri Ekonomi Kreatif Irene Umar mengatakan kolaborasi antara pemilik kekayaan intelektual (Intellectual ...</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677103/sean-gelael-berbagi-pengalaman-di-dunia-balap-ke-pengunjung-giias-2026</t>
+          <t>https://www.antaranews.com/berita/5677353/lisensi-ip-global-buka-peluang-bisnis-baru-bagi-kreator-indonesia</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/16b70b87-326f-479a-a806-580ab846cc6f_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000589873.jpg</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ekonomi-bursa, top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IHSG Senin dibuka menguat 36,49 poin ke posisi 6.272</t>
+          <t>Gempa bermagnitudo 5,3 guncang Mesir timur laut</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:11:26 +0700</t>
+          <t>Mon, 03 Aug 2026 13:32:32 +0700</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin pagi dibuka menguat 36,49 poin atau 0,59 ...</t>
+          <t>Sebuah gempa bermagnitudo 5,3 mengguncang Provinsi Ismailia di Mesir timur laut pada Senin pagi waktu setempat, menurut ...</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677071/ihsg-senin-dibuka-menguat-3649-poin-ke-posisi-6272</t>
+          <t>https://www.antaranews.com/berita/5677351/gempa-bermagnitudo-53-guncang-mesir-timur-laut</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/pergerakan-indeks-harga-saham-gabungan-2828631.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/18/ilustrasi-gempa-2_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PLN Jakarta pastikan pasokan listrik sudah berhasil dipulihkan</t>
+          <t>Dedi Kusnandar: Persib siap hadapi Persija di semifinal Piala Presiden</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 08:36:26 +0700</t>
+          <t>Mon, 03 Aug 2026 13:31:31 +0700</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PT PLN (Persero) Unit Induk Distribusi Jakarta Raya mengungkapkan pasokan listrik telah berhasil ...</t>
+          <t>Gelandang Persib Bandung Dedi Kusnandar menegaskan timnya siap menghadapi Persija Jakarta pada babak semifinal Piala ...</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677043/pln-jakarta-pastikan-pasokan-listrik-sudah-berhasil-dipulihkan</t>
+          <t>https://www.antaranews.com/berita/5677349/dedi-kusnandar-persib-siap-hadapi-persija-di-semifinal-piala-presiden</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20231217-WA0015-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_9111.jpeg</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ledakan di kantor polisi Pakistan tewaskan 14 orang</t>
+          <t>Wakil Ketua DPR salurkan beasiswa PIP ke ribuan pelajar Lombok Timur</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 07:44:23 +0700</t>
+          <t>Mon, 03 Aug 2026 13:30:16 +0700</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sebuah ledakan terjadi di luar sebuah kantor polisi di Kota Kabal, Pakistan, mengakibatkan 14 orang tewas dan 14 orang ...</t>
+          <t>Wakil Ketua DPR RI Sari Yuliati menyerahkan bantuan beasiswa Program Indonesia Pintar (PIP) 2026 kepada ribuan pelajar ...</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677020/ledakan-di-kantor-polisi-pakistan-tewaskan-14-orang</t>
+          <t>https://www.antaranews.com/berita/5677345/wakil-ketua-dpr-salurkan-beasiswa-pip-ke-ribuan-pelajar-lombok-timur</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CmxztpE000019_20260803_PEPFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1005724306.jpg</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ratusan korban selamat KMP Mutiara Santosa 2 tiba di Tanjung Perak</t>
+          <t>Dinkop UKM Cilegon targetkan 21 gerai baru KKMP beroperasi September</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:37:38 +0700</t>
+          <t>Mon, 03 Aug 2026 13:27:17 +0700</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sebanyak 111 korban selamat dan dua meninggal dunia akibat kebakaran KMP Mutiara Santosa II di Perairan Utara ...</t>
+          <t>ANTARA - Dinas Koperasi Usaha Kecil dan Menengah (Dinkop UKM) Kota Cilegon menargetkan pembangunan  21 gedung ...</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676983/ratusan-korban-selamat-kmp-mutiara-santosa-2-tiba-di-tanjung-perak</t>
+          <t>https://www.antaranews.com/video/5677301/dinkop-ukm-cilegon-targetkan-21-gerai-baru-kkmp-beroperasi-september</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/259549_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/DINKOP-UKM-CILEGON-TARGETKAN-21-GERAI-BARU-KKMP-BEROPERASI-SEPTEMBER.jpg</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>humaniora, terkini</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sebagian Jakarta diguyur hujan ringan pada Senin sore hingga malam</t>
+          <t>Bantuan beras 30 kg cair mulai 17 Agustus 2026, ini jadwal dan cara cek penerimanya</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:11:02 +0700</t>
+          <t>Mon, 03 Aug 2026 13:27:14 +0700</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) memprakirakan hujan ringan akan melanda sebagian wilayah Jakarta ...</t>
+          <t>Pemerintah memastikan penyaluran bantuan pangan beras tahap II tahun 2026 akan dimulai pada 17 Agustus 2026. Bantuan ...</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676963/sebagian-jakarta-diguyur-hujan-ringan-pada-senin-sore-hingga-malam</t>
+          <t>https://www.antaranews.com/berita/5677341/bantuan-beras-30-kg-cair-mulai-17-agustus-2026-ini-jadwal-dan-cara-cek-penerimanya</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/01/IMG_20260301_073711.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/26/kemensos-percepat-penyaluran-bansos-pkh-dan-bpnt-2778877.jpg</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Atlet-atlet nasional borong 18 medali Poomsae Indonesia Open 2026</t>
+          <t>Puluhan santri Ponpes Darul Amanah Kendal kunjungi Istana Presiden</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 04:18:40 +0700</t>
+          <t>Mon, 03 Aug 2026 13:24:08 +0700</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Atlet-atlet tuan rumah Indonesia tampil impresif pada nomor Poomsae 8th Asian Taekwondo, Indonesia Open ...</t>
+          <t>Puluhan santri beserta pengajar Pondok Pesantren Darul Amanah Sukorejo, Kendal, Jawa Tengah, melakukan kunjungan ...</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676947/atlet-atlet-nasional-borong-18-medali-poomsae-indonesia-open-2026</t>
+          <t>https://www.antaranews.com/berita/5677337/puluhan-santri-ponpes-darul-amanah-kendal-kunjungi-istana-presiden</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships-2026-020826-dr-04.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_3918.jpeg</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kemenhub kerahkan kapal patroli evakuasi KM Mutiara Sentosa II</t>
+          <t>Cek fakta, Pemprov Jabar resmi adakan kembali SPP untuk sekolah negeri pada Juli 2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 00:03:37 +0700</t>
+          <t>Mon, 03 Aug 2026 13:23:04 +0700</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kementerian Perhubungan mengerahkan kapal patroli Kesatuan Penjagaan Laut dan Pantai (KPLP) serta memperkuat koordinasi ...</t>
+          <t>Jakarta (ANTARA/JACX) – Sebuah unggahan di Facebook menarasikan bahwa Pemerintah Provinsi Jawa Barat ...</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676931/kemenhub-kerahkan-kapal-patroli-evakuasi-km-mutiara-sentosa-ii</t>
+          <t>https://www.antaranews.com/berita/5677333/cek-fakta-pemprov-jabar-resmi-adakan-kembali-spp-untuk-sekolah-negeri-pada-juli-2026</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/17/WhatsApp-Image-2026-06-17-at-20.14.04.jpeg</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>lifestyle, terkini</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Rupiah diperkirakan menguat seiring AS batalkan rencana serang Iran</t>
+          <t>Bahaya paparan pornografi pada anak: Dampak bagi otak, mental, dan perilaku</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:12:26 +0700</t>
+          <t>Mon, 03 Aug 2026 13:23:03 +0700</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Analis Doo Financial Futures, Lukman Leong memperkirakan rupiah menguat seiring Amerika Serikat (AS) membatalkan ...</t>
+          <t>Perkembangan teknologi membuat anak-anak dan remaja semakin akrab dengan internet sejak usia dini. Di satu sisi, ...</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677132/rupiah-diperkirakan-menguat-seiring-as-batalkan-rencana-serang-iran</t>
+          <t>https://www.antaranews.com/berita/5677332/bahaya-paparan-pornografi-pada-anak-dampak-bagi-otak-mental-dan-perilaku</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828847.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/02/ilustrasi-konten-berbau-pornografi.jpg</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>ekonomi-bisnis, top-news</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Rupiah pada Senin pagi melemah jadi Rp18.031 per dolar AS</t>
+          <t>Nilai ekspor perdagangan RI Januari-Juni capai 140,81 miliar dolar AS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:05:50 +0700</t>
+          <t>Mon, 03 Aug 2026 13:16:17 +0700</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nilai tukar rupiah pada Senin pagi bergerak melemah 9 poin atau 0,05 persen menjadi Rp18.031 per dolar AS dibandingkan ...</t>
+          <t>Badan Pusat Statistik (BPS) mencatat nilai ekspor Indonesia secara kumulatif dari Januari-Juni 2026 mencapai 140,81 ...</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677063/rupiah-pada-senin-pagi-melemah-jadi-rp18031-per-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5677315/nilai-ekspor-perdagangan-ri-januari-juni-capai-14081-miliar-dolar-as</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/neraca-perdagangan-januari-mei-2026-surplus-2815779.jpg</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Komisi XI: PFII peluang RI tangkap momentum perpindahan modal global</t>
+          <t>Korban KMP Mutiara Sentosa II dievakuasi ke Pelabuhan Tanjung Perak</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:53:34 +0700</t>
+          <t>Mon, 03 Aug 2026 13:06:15 +0700</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Wakil Ketua Komisi XI DPR RI Mohamad Hekal mengatakan percepatan pembentukan Pusat Finansial Internasional Indonesia ...</t>
+          <t>Tim SAR gabungan terus melakukan evakuasi korban terbakarnya KMP Mutiara Sentosa 2 ke darat, tepatnya ke Pelabuhan ...</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676995/komisi-xi-pfii-peluang-ri-tangkap-momentum-perpindahan-modal-global</t>
+          <t>https://www.antaranews.com/berita/5677297/korban-kmp-mutiara-sentosa-ii-dievakuasi-ke-pelabuhan-tanjung-perak</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Saham-dan-oblogasi.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/260821.jpg</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BUMA International Group bukukan pertumbuhan EBITDA semester I/2026</t>
+          <t>Aktor senior Diding Boneng meninggal dunia</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:17:40 +0700</t>
+          <t>Mon, 03 Aug 2026 11:39:03 +0700</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>PT BUMA Internasional Gorup membukukan pertumbuhan EBITDA pada semester pertama 2026 (1H26) di tengah penurunan ...</t>
+          <t>Aktor sekaligus komedian tanah air, Zainal Abidin alias Diding Boneng dikabarkan meninggal dunia pada Senin (3/8) dalam ...</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676967/buma-international-group-bukukan-pertumbuhan-ebitda-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5677209/aktor-senior-diding-boneng-meninggal-dunia</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/buma.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/26f1eb88-3301-4ae1-badd-bed5078fe3dd.jpeg</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PT PAL-BRIN wujudkan galangan kapal hijau dukung industri perkapalan</t>
+          <t>Seskab: Prabowo dorong sinergi pemerintah dan dunia usaha</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:43:28 +0700</t>
+          <t>Mon, 03 Aug 2026 11:17:50 +0700</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>PT PAL Indonesia bersama Badan Riset dan Inovasi Nasional (BRIN) berkolaborasi mewujudkan transformasi green ...</t>
+          <t>Sekretaris Kabinet Teddy Indra Wijaya menyampaikan bahwa Presiden Prabowo Subianto menekankan pentingnya sinergi antara ...</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677267/pt-pal-brin-wujudkan-galangan-kapal-hijau-dukung-industri-perkapalan</t>
+          <t>https://www.antaranews.com/berita/5677191/seskab-prabowo-dorong-sinergi-pemerintah-dan-dunia-usaha</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/a647aa30-a843-4000-98a0-07d27228a41e.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0891.jpeg</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Pangan, transportasi, dan emas perhiasan dorong inflasi pada Juli 2026</t>
+          <t>Red Velvet bersiap kembali lewat EP baru "Velvet Summer"</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:32:11 +0700</t>
+          <t>Mon, 03 Aug 2026 10:24:37 +0700</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat kelompok makanan, minuman, dan tembakau, transportasi, serta perawatan pribadi dan ...</t>
+          <t>Grup idola K-pop Red Velvet akan kembali lewat rilis mini album atau extended play (EP) baru bertajuk “Velvet ...</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677256/pangan-transportasi-dan-emas-perhiasan-dorong-inflasi-pada-juli-2026</t>
+          <t>https://www.antaranews.com/berita/5677151/red-velvet-bersiap-kembali-lewat-ep-baru-velvet-summer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/bps.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/ca97a3a8-aa17-45fc-be71-d36051dd9dcd.jpeg</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BPS: Neraca perdagangan Januari-Juni 2026 surplus 3,58 miliar dolar AS</t>
+          <t>Menaker pastikan komitmen pemerintah perkuat kesejahteraan pekerja</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:27:18 +0700</t>
+          <t>Mon, 03 Aug 2026 10:16:19 +0700</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat bahwa neraca perdagangan barang Indonesia mengalami surplus senilai 3,58 miliar ...</t>
+          <t>Menteri Ketenagakerjaan (Menaker) Yassierli memastikan pemerintah berkomitmen untuk memperkuat kesejahteraan, ...</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677252/bps-neraca-perdagangan-januari-juni-2026-surplus-358-miliar-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5677148/menaker-pastikan-komitmen-pemerintah-perkuat-kesejahteraan-pekerja</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/bps.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/09/20/pelepasan-peserta-pemagangan-ke-jepang-di-jawa-barat-2627513.jpg</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Laba bersih Tugu Insurance capai Rp480,29 miliar pada semester I 2026</t>
+          <t>23 calon hakim agung dan ad hoc ikuti seleksi wawancara akhir</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:24:56 +0700</t>
+          <t>Mon, 03 Aug 2026 10:15:01 +0700</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>PT Asuransi Tugu Pratama Indonesia Tbk atau Tugu Insurance membukukan laba tahun berjalan yang dapat diatribusikan ...</t>
+          <t>Sebanyak 23 orang calon hakim agung dan ad hoc Mahkamah Agung Tahun 2026 mengikuti seleksi wawancara tahap akhir di ...</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677249/laba-bersih-tugu-insurance-capai-rp48029-miliar-pada-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5677137/23-calon-hakim-agung-dan-ad-hoc-ikuti-seleksi-wawancara-akhir</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-11.02.17.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000012883_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BPS: Indonesia catat deflasi bulanan 0,14 persen pada Juli 2026</t>
+          <t>BRIN perkuat kajian sungai bawah tanah di Kebumen untuk ketahanan air</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:20:12 +0700</t>
+          <t>Mon, 03 Aug 2026 09:57:19 +0700</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat Indonesia mengalami deflasi sebesar 0,14 persen secara bulanan ...</t>
+          <t>Badan Riset dan Inovasi Nasional (BRIN) memperkuat riset ketahanan air melalui pengembangan teknologi dan penelitian ...</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677247/bps-indonesia-catat-deflasi-bulanan-014-persen-pada-juli-2026</t>
+          <t>https://www.antaranews.com/berita/5677120/brin-perkuat-kajian-sungai-bawah-tanah-di-kebumen-untuk-ketahanan-air</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/bps.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1785706440-47672950-1.jpg</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Kemendag kantongi potensi ekspor Rp1,87 miliar ke Chile</t>
+          <t>Harga bensin turun pada pekan pertama Agustus</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:16:02 +0700</t>
+          <t>Mon, 03 Aug 2026 09:51:00 +0700</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kementerian Perdagangan (Kemendag) melalui Indonesia Trade Promotion Center (ITPC) Santiago di Chile menggelar ...</t>
+          <t>Harga bahan bakar minyak (BBM) jenis bensin di stasiun pengisian bahan bakar umum (SPBU) Pertamina, Shell, dan bp ...</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677237/kemendag-kantongi-potensi-ekspor-rp187-miliar-ke-chile</t>
+          <t>https://www.antaranews.com/berita/5677109/harga-bensin-turun-pada-pekan-pertama-agustus</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/03/IMG_3208.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/10/02/penuruanan-harga-bbm-011024-aaa-7.jpg</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ekonomi RI alami inflasi tahunan sebesar 2,88 persen pada Juli 2026</t>
+          <t>Sean Gelael berbagi pengalaman di dunia balap ke pengunjung GIIAS 2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:31:08 +0700</t>
+          <t>Mon, 03 Aug 2026 09:34:53 +0700</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat perekonomian Indonesia mengalami inflasi sebesar 2,88 persen secara tahunan ...</t>
+          <t>Pembalap Indonesia Sean Gelael berbagi pengalamannya di dunia balap ke pengunjung GAIKINDO Indonesia International ...</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677207/ekonomi-ri-alami-inflasi-tahunan-sebesar-288-persen-pada-juli-2026</t>
+          <t>https://www.antaranews.com/berita/5677103/sean-gelael-berbagi-pengalaman-di-dunia-balap-ke-pengunjung-giias-2026</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/01/WhatsApp-Image-2026-07-01-at-10.59.31_edit_549938834278582_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/16b70b87-326f-479a-a806-580ab846cc6f_1.jpeg</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>ekonomi-bursa, top-news</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Kementan dorong pengembangan gula tumbu alternatif hilirisasi tebu</t>
+          <t>IHSG Senin dibuka menguat 36,49 poin ke posisi 6.272</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:13:22 +0700</t>
+          <t>Mon, 03 Aug 2026 09:11:26 +0700</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Direktorat Jenderal Perkebunan Kementerian Pertanian mendorong pengembangan industri gula tumbu sebagai alternatif ...</t>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin pagi dibuka menguat 36,49 poin atau 0,59 ...</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677183/kementan-dorong-pengembangan-gula-tumbu-alternatif-hilirisasi-tebu</t>
+          <t>https://www.antaranews.com/berita/5677071/ihsg-senin-dibuka-menguat-3649-poin-ke-posisi-6272</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001046969.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/pergerakan-indeks-harga-saham-gabungan-2828631.jpg</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>KSP: Pemerintah sempurnakan regulasi terkait LTJ dan unsur radioaktif</t>
+          <t>PLN Jakarta pastikan pasokan listrik sudah berhasil dipulihkan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:05:02 +0700</t>
+          <t>Mon, 03 Aug 2026 08:36:26 +0700</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kantor Staf Presiden (KSP) menyatakan pemerintah kini tengah menyempurnakan regulasi yang mengatur ...</t>
+          <t>PT PLN (Persero) Unit Induk Distribusi Jakarta Raya mengungkapkan pasokan listrik telah berhasil ...</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677179/ksp-pemerintah-sempurnakan-regulasi-terkait-ltj-dan-unsur-radioaktif</t>
+          <t>https://www.antaranews.com/berita/5677043/pln-jakarta-pastikan-pasokan-listrik-sudah-berhasil-dipulihkan</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_5412.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20231217-WA0015-1.jpg</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Daftar lengkap harga emas tiga jenama di Pegadaian pada Senin</t>
+          <t>Ledakan di kantor polisi Pakistan tewaskan 14 orang</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:41:19 +0700</t>
+          <t>Mon, 03 Aug 2026 07:44:23 +0700</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Harga emas di laman Pegadaian dikutip dari Jakarta, Senin, pukul 10.30 WIB, menunjukkan produk dari Galeri24, Antam, ...</t>
+          <t>Sebuah ledakan terjadi di luar sebuah kantor polisi di Kota Kabal, Pakistan, mengakibatkan 14 orang tewas dan 14 orang ...</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677164/daftar-lengkap-harga-emas-tiga-jenama-di-pegadaian-pada-senin</t>
+          <t>https://www.antaranews.com/berita/5677020/ledakan-di-kantor-polisi-pakistan-tewaskan-14-orang</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/02/23/Harga-Emas-Antam-Naik-Jakarta-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CmxztpE000019_20260803_PEPFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Wamenaker:Penguatan kompetensi vokasi dan bahasa perluas peluang kerja</t>
+          <t>Ratusan korban selamat KMP Mutiara Santosa 2 tiba di Tanjung Perak</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:12:46 +0700</t>
+          <t>Mon, 03 Aug 2026 06:37:38 +0700</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Wakil Menteri Ketenagakerjaan (Wamenaker) Afriansyah Noor menekankan pentingnya penguatan kompetensi dan kemampuan ...</t>
+          <t>Sebanyak 111 korban selamat dan dua meninggal dunia akibat kebakaran KMP Mutiara Santosa II di Perairan Utara ...</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677136/wamenakerpenguatan-kompetensi-vokasi-dan-bahasa-perluas-peluang-kerja</t>
+          <t>https://www.antaranews.com/berita/5676983/ratusan-korban-selamat-kmp-mutiara-santosa-2-tiba-di-tanjung-perak</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/5cf5bd9f-4b4b-4451-9d28-2cef5e460156.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/259549_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IHSG awal pekan berpotensi variatif seiring sentimen global-domestik</t>
+          <t>Sebagian Jakarta diguyur hujan ringan pada Senin sore hingga malam</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:42:28 +0700</t>
+          <t>Mon, 03 Aug 2026 06:11:02 +0700</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin berpotensi bergerak variatif dipicu oleh ...</t>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) memprakirakan hujan ringan akan melanda sebagian wilayah Jakarta ...</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677104/ihsg-awal-pekan-berpotensi-variatif-seiring-sentimen-global-domestik</t>
+          <t>https://www.antaranews.com/berita/5676963/sebagian-jakarta-diguyur-hujan-ringan-pada-senin-sore-hingga-malam</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/12/12/ihsg-ditutup-menguat-2688871.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/01/IMG_20260301_073711.jpg</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Sudah ngantuk tapi sulit tidur pulas? Ini penyebab dan cara atasinya</t>
+          <t>Atlet-atlet nasional borong 18 medali Poomsae Indonesia Open 2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:28:54 +0700</t>
+          <t>Mon, 03 Aug 2026 04:18:40 +0700</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rasa kantuk yang muncul di malam hari seharusnya menjadi pertanda bahwa tubuh siap beristirahat. Namun, tidak sedikit ...</t>
+          <t>Atlet-atlet tuan rumah Indonesia tampil impresif pada nomor Poomsae 8th Asian Taekwondo, Indonesia Open ...</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677203/sudah-ngantuk-tapi-sulit-tidur-pulas-ini-penyebab-dan-cara-atasinya</t>
+          <t>https://www.antaranews.com/berita/5676947/atlet-atlet-nasional-borong-18-medali-poomsae-indonesia-open-2026</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/17/Nafas.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships-2026-020826-dr-04.jpg</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cara cepat tidur dalam 5 menit, efektif untuk yang sulit pulas</t>
+          <t>Kemenhub kerahkan kapal patroli evakuasi KM Mutiara Sentosa II</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:25:40 +0700</t>
+          <t>Mon, 03 Aug 2026 00:03:37 +0700</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sulit tidur meski badan sudah terasa lelah merupakan masalah yang kerap dialami banyak orang. Kondisi ini sering ...</t>
+          <t>Kementerian Perhubungan mengerahkan kapal patroli Kesatuan Penjagaan Laut dan Pantai (KPLP) serta memperkuat koordinasi ...</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677199/cara-cepat-tidur-dalam-5-menit-efektif-untuk-yang-sulit-pulas</t>
+          <t>https://www.antaranews.com/berita/5676931/kemenhub-kerahkan-kapal-patroli-evakuasi-km-mutiara-sentosa-ii</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/11/04/tidua.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Pemerintah bangun 1.416 Jembatan Garuda untuk hubungkan desa terpencil</t>
+          <t>Rupiah diperkirakan menguat seiring AS batalkan rencana serang Iran</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:53:00 +0700</t>
+          <t>Mon, 03 Aug 2026 10:12:26 +0700</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Foto udara pengendara sepeda motor melintasi Jembatan Gantung Garuda yang menghubungkan Desa Kertarahayu dan Desa Jayasampurna di Kabupaten Bekasi, Jawa Barat, Senin (3/8/2026). Hingga akhir Juli 2026, pemerintah telah membangun 1.416 unit Jembatan Garuda di daerah terpencil yang menghubungkan 7.371 desa dan kelurahan untuk mempermudah akses masyarakat serta mempersingkat waktu tempuh. ANTARA FOTO/Darryl Ramadhan/tom.</t>
+          <t>Analis Doo Financial Futures, Lukman Leong memperkirakan rupiah menguat seiring Amerika Serikat (AS) membatalkan ...</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5677284/pemerintah-bangun-1416-jembatan-garuda-untuk-hubungkan-desa-terpencil</t>
+          <t>https://www.antaranews.com/berita/5677132/rupiah-diperkirakan-menguat-seiring-as-batalkan-rencana-serang-iran</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/Pembangunan-Jembatan-Garuda-percepat-akses-desa-030826-ryl-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828847.jpg</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Petugas evakuasi dua jenazah korban kebakaran KM Mutiara Sentosa II</t>
+          <t>Rupiah pada Senin pagi melemah jadi Rp18.031 per dolar AS</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:03:11 +0700</t>
+          <t>Mon, 03 Aug 2026 09:05:50 +0700</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sejumlah petugas mengangkat kantong berisi jenazah korban kebakaran KM Mutiara Sentosa II setelah tiba di Dermaga Jamrud Utara, Pelabuhan Tanjung Perak, Surabaya, Jawa Timur, Senin (3/8/2026). Kapal kargo Meratus Pematang Siantar mengevakuasi 111 penumpang selamat dan dua jenazah korban kebakaran KM Mutiara Sentosa II di perairan utara Madura pada Minggu (2/8). ANTARA FOTO/Didik Suhartono/tom.</t>
+          <t>Nilai tukar rupiah pada Senin pagi bergerak melemah 9 poin atau 0,05 persen menjadi Rp18.031 per dolar AS dibandingkan ...</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5677056/petugas-evakuasi-dua-jenazah-korban-kebakaran-km-mutiara-sentosa-ii</t>
+          <t>https://www.antaranews.com/berita/5677063/rupiah-pada-senin-pagi-melemah-jadi-rp18031-per-dolar-as</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/korban-kebakaran-km-mutiara-sentosa-2-030826-Ds-4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Resmi dibuka, Sekolah Rakyat Terintegrasi 2 Kendari tampung 339 siswa</t>
+          <t>Komisi XI: PFII peluang RI tangkap momentum perpindahan modal global</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
+          <t>Mon, 03 Aug 2026 06:53:34 +0700</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
+          <t>Wakil Ketua Komisi XI DPR RI Mohamad Hekal mengatakan percepatan pembentukan Pusat Finansial Internasional Indonesia ...</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676995/komisi-xi-pfii-peluang-ri-tangkap-momentum-perpindahan-modal-global</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Saham-dan-oblogasi.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>BUMA International Group bukukan pertumbuhan EBITDA semester I/2026</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 06:17:40 +0700</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>PT BUMA Internasional Gorup membukukan pertumbuhan EBITDA pada semester pertama 2026 (1H26) di tengah penurunan ...</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676967/buma-international-group-bukukan-pertumbuhan-ebitda-semester-i-2026</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/buma.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>BPS catat nilai tukar petani di level 127,84 pada Juli 2026</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:18:40 +0700</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) mencatat nilai tukar petani (NTP) secara nasional pada bulan Juli 2026 berada di level ...</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677323/bps-catat-nilai-tukar-petani-di-level-12784-pada-juli-2026</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/02/20260302_083324.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Menteri ATR sebut 400 Kantah sudah terapkan pengukuran terjadwal</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:13:29 +0700</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Menteri Agraria dan Tata Ruang/Kepala Badan Pertanahan Nasional (ATR/BPN) Nusron Wahid mengatakan bahwa sudah ada 400 ...</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677308/menteri-atr-sebut-400-kantah-sudah-terapkan-pengukuran-terjadwal</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_125328.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>PT PAL-BRIN wujudkan galangan kapal hijau dukung industri perkapalan</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 12:43:28 +0700</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>PT PAL Indonesia bersama Badan Riset dan Inovasi Nasional (BRIN) berkolaborasi mewujudkan transformasi green ...</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677267/pt-pal-brin-wujudkan-galangan-kapal-hijau-dukung-industri-perkapalan</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/a647aa30-a843-4000-98a0-07d27228a41e.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Pangan, transportasi, dan emas perhiasan dorong inflasi pada Juli 2026</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 12:32:11 +0700</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) mencatat kelompok makanan, minuman, dan tembakau, transportasi, serta perawatan pribadi dan ...</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677256/pangan-transportasi-dan-emas-perhiasan-dorong-inflasi-pada-juli-2026</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/bps.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>BPS: Neraca perdagangan Januari-Juni 2026 surplus 3,58 miliar dolar AS</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 12:27:18 +0700</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) mencatat bahwa neraca perdagangan barang Indonesia mengalami surplus senilai 3,58 miliar ...</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677252/bps-neraca-perdagangan-januari-juni-2026-surplus-358-miliar-dolar-as</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/bps.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Laba bersih Tugu Insurance capai Rp480,29 miliar pada semester I 2026</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 12:24:56 +0700</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>PT Asuransi Tugu Pratama Indonesia Tbk atau Tugu Insurance membukukan laba tahun berjalan yang dapat diatribusikan ...</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677249/laba-bersih-tugu-insurance-capai-rp48029-miliar-pada-semester-i-2026</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-11.02.17.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>BPS: Indonesia catat deflasi bulanan 0,14 persen pada Juli 2026</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 12:20:12 +0700</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) mencatat Indonesia mengalami deflasi sebesar 0,14 persen secara bulanan ...</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677247/bps-indonesia-catat-deflasi-bulanan-014-persen-pada-juli-2026</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/bps.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Kemendag kantongi potensi ekspor Rp1,87 miliar ke Chile</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 12:16:02 +0700</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Kementerian Perdagangan (Kemendag) melalui Indonesia Trade Promotion Center (ITPC) Santiago di Chile menggelar ...</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677237/kemendag-kantongi-potensi-ekspor-rp187-miliar-ke-chile</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/03/IMG_3208.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ekonomi-bursa</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>IHSG awal pekan berpotensi variatif seiring sentimen global-domestik</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 09:42:28 +0700</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin berpotensi bergerak variatif dipicu oleh ...</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677104/ihsg-awal-pekan-berpotensi-variatif-seiring-sentimen-global-domestik</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/12/12/ihsg-ditutup-menguat-2688871.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Sudah ngantuk tapi sulit tidur pulas? Ini penyebab dan cara atasinya</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 11:28:54 +0700</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Rasa kantuk yang muncul di malam hari seharusnya menjadi pertanda bahwa tubuh siap beristirahat. Namun, tidak sedikit ...</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677203/sudah-ngantuk-tapi-sulit-tidur-pulas-ini-penyebab-dan-cara-atasinya</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/17/Nafas.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Cara cepat tidur dalam 5 menit, efektif untuk yang sulit pulas</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 11:25:40 +0700</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Sulit tidur meski badan sudah terasa lelah merupakan masalah yang kerap dialami banyak orang. Kondisi ini sering ...</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677199/cara-cepat-tidur-dalam-5-menit-efektif-untuk-yang-sulit-pulas</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/04/tidua.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>tekno</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Cara mengganti password WiFi lewat HP dan laptop dengan mudah</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:16:14 +0700</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>WiFi yang tiba-tiba terasa lambat padahal sinyal penuh dan kuota internet masih banyak tentu membuat kesal. Salah satu ...</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677312/cara-mengganti-password-wifi-lewat-hp-dan-laptop-dengan-mudah</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2020/08/19/antarafoto-warga-sediakan-internet-gratis-bagi-pelajar-190820-ief-2-1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Pemerintah bangun 1.416 Jembatan Garuda untuk hubungkan desa terpencil</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 12:53:00 +0700</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Foto udara pengendara sepeda motor melintasi Jembatan Gantung Garuda yang menghubungkan Desa Kertarahayu dan Desa Jayasampurna di Kabupaten Bekasi, Jawa Barat, Senin (3/8/2026). Hingga akhir Juli 2026, pemerintah telah membangun 1.416 unit Jembatan Garuda di daerah terpencil yang menghubungkan 7.371 desa dan kelurahan untuk mempermudah akses masyarakat serta mempersingkat waktu tempuh. ANTARA FOTO/Darryl Ramadhan/tom.</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5677284/pemerintah-bangun-1416-jembatan-garuda-untuk-hubungkan-desa-terpencil</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/Pembangunan-Jembatan-Garuda-percepat-akses-desa-030826-ryl-1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Petugas evakuasi dua jenazah korban kebakaran KM Mutiara Sentosa II</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 09:03:11 +0700</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Sejumlah petugas mengangkat kantong berisi jenazah korban kebakaran KM Mutiara Sentosa II setelah tiba di Dermaga Jamrud Utara, Pelabuhan Tanjung Perak, Surabaya, Jawa Timur, Senin (3/8/2026). Kapal kargo Meratus Pematang Siantar mengevakuasi 111 penumpang selamat dan dua jenazah korban kebakaran KM Mutiara Sentosa II di perairan utara Madura pada Minggu (2/8). ANTARA FOTO/Didik Suhartono/tom.</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5677056/petugas-evakuasi-dua-jenazah-korban-kebakaran-km-mutiara-sentosa-ii</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/korban-kebakaran-km-mutiara-sentosa-2-030826-Ds-4.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Resmi dibuka, Sekolah Rakyat Terintegrasi 2 Kendari tampung 339 siswa</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
           <t>ANTARA - Sekolah Rakyat Terintegrasi 2 Kota Kendari resmi dibuka pada Senin (3/8), yang ditandai dengan Masa Pengenalan Lingkungan Sekolah (MPLS). Sekolah tersebut menampung total sebanyak 339 siswa untuk tahun ajaran 2026/2027, yang terdiri dari jenjang SD, SMP dan SMA.
 (Saharudin/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677373/resmi-dibuka-sekolah-rakyat-terintegrasi-2-kendari-tampung-339-siswa</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/RESMI-DIBUKA-SEKOLAH-RAKYAT-TERINTEGRASI-2-KENDARI-TAMPUNG-339-SISWA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>Dinkop UKM Cilegon targetkan 21 gerai baru KKMP beroperasi September</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Koperasi Usaha Kecil dan Menengah (Dinkop UKM) Kota Cilegon menargetkan pembangunan  21 gedung gerai Koperasi Kelurahan Merah Putih (KKMP) di wilayah setempat dapat selesai dan beroperasi pada bulan September mendatang. Kepala Dinkop UKM Kota Cilegon, Suhendi pada Senin (3/8) mengatakan saat ini tercatat baru sebanyak 10 gedung yang telah selesai dibangun.
 (Susmiatun Hayati/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677301/dinkop-ukm-cilegon-targetkan-21-gerai-baru-kkmp-beroperasi-september</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/DINKOP-UKM-CILEGON-TARGETKAN-21-GERAI-BARU-KKMP-BEROPERASI-SEPTEMBER.jpg</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+    <row r="105">
+      <c r="A105" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>Menhub sebut segera evaluasi operator KMP Mutiara Sentosa 2</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah akan segera mengevaluasi kinerja PT Atosim Lampung Pelayaran yang merupakan operator KMP Mutiara Sentosa II. Hal tersebut disampaikan Menteri Perhubungan Dudy Purwagandhi saat meninjau para korban kebakaran KMP Mutiara Sentosa II di Surabaya, Jawa Timur, Senin (3/8). (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677187/menhub-sebut-segera-evaluasi-operator-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/MENHUB-SEBUT-SEGERA-EVALUASI-OPERATOR-KMP-MUTIARA-SENTOSA-2.jpg</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+    <row r="106">
+      <c r="A106" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>Keluarga dengan dua balita selamat dari maut KMP Mutiara Sentosa 2</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
         <is>
           <t>ANTARA - Pasangan suami istri muda, Karhap dan Krisnawati bersama dua anak balitanya sempat terpisah saat terjun ke laut menyelamatkan diri dari kapal penumpang KMP Mutiara Sentosa 2 yang terbakar di perairan sebelah utara Pulau Madura pada Minggu (2/8). Keluarga kecil asal Sidenreng Rappang, Sulawesi Selatan tersebut kembali berkumpul pada Senin (3/8) setelah dievakuasi oleh kapal kargo Meratus Pematang Siantar yang kebetulan melintas di lokasi musibah terjadi. (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677141/keluarga-dengan-dua-balita-selamat-dari-maut-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KELUARGA-DENGAN-DUA-BALITA-SELAMAT-DARI-MAUT-KMP-MUTIARA-SENTOSA-2.jpg</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+    <row r="107">
+      <c r="A107" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>Lebih dari 100 korban KMP Mutiara Sentosa 2 tiba di Tanjung Perak</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr">
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
         <is>
           <t>ANTARA - Tim pencarian dan pertolongan (SAR) gabungan hingga Senin (3/8), telah mengevakuasi 234 penumpang KMP Mutiara Sentosa 2 yang sebelumnya terbakar di perairan sebelah utara Pulau Madura pada Minggu (2/8). Sebanyak 113 korban di antaranya, kini telah tiba di Pelabuhan Tanjung Perak Surabaya setelah diangkut menggunakan kapal kargo Meratus Pematang Siantar.  (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677085/lebih-dari-100-korban-kmp-mutiara-sentosa-2-tiba-di-tanjung-perak</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/LEBIH-DARI-100-KORBAN-KMP-MUTIARA-SENTOSA-2-TIBA-DI-TANJUNG-PERAK.jpg</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="108">
+      <c r="A108" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>SAR evakuasi penumpang KM Mutiara Santosa 2 yang terbakar</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
         <is>
           <t>ANTARA - Tim pencarian dan pertolongan (SAR) gabungan telah mengevakuasi sebanyak 236 penumpang KM Mutiara Santosa 2 yang terbakar di perairan sebelah utara Pulau Madura, Minggu malam (2/8). Lima korban di antaranya meninggal dunia.(Hanif Nasrullah/Denno Ramdha Asmara/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676992/sar-evakuasi-penumpang-km-mutiara-santosa-2-yang-terbakar</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SAR-EVAKUASI-PENUMPANG-KM-MUTIARA-SANTOSA-2-YANG-TERBAKAR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="109">
+      <c r="A109" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>John Herdman tunggu hasil pemeriksaan Marselino jelang jamu Vietnam</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
         <is>
           <t>ANTARA - Pelatih Timnas Indonesia John Herdman di Jakarta, Minggu,(2/8), mengatakan kondisi kesehatan dan status gelandang Marselino Ferdinan dalam turnamen baru akan ditentukan setelah mendapat laporan lengkap dari tim medis. Hal itu disampaikan Herdman, usai Marselino kembali absen dalam latihan jelang laga Grup A Piala AFF 2026 melawan Timnas Vietnam pada Senin (2/8). (Anggah/Sandy Arizona/Gracia Simanjuntak)</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676945/john-herdman-tunggu-hasil-pemeriksaan-marselino-jelang-jamu-vietnam</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_JOHN-HERDMAN-TUNGGU-HASIL-PEMERIKSAAN-MARSELINO-JELANG-JAMU-VIETNAM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+    <row r="110">
+      <c r="A110" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>John Herdman sebut laga RI Vs Vietnam ujian sangat berat</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr">
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
         <is>
           <t>ANTARA - Pelatih Timnas Indonesia John Herdman di Jakarta, Minggu(2/8), mengaku pertandingan melawan Timnas Vietnam akan menjadi ujian sangat berat bagi skuad Garuda di Grup A Piala AFF 2026 (ASEAN Championship 2026). Menurut Herdman. laga tersebut juga merupakan peluang untuk mengambil alih kendali grup dan memastikan langkah ke babak berikutnya. (Anggah/Sandy Arizona/Gracia Simanjuntak)</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676944/john-herdman-sebut-laga-ri-vs-vietnam-ujian-sangat-berat</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_JOHN-HERDMAN-SEBUT-LAGA-RI-VS-VIETNAM-UJIAN-SANGAT-BERAT.jpg</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>BI targetkan bawa wastra Sulsel ke pasar global</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr">
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
         <is>
           <t>ANTARA - Kantor Perwakilan Bank Indonesia Provinsi Sulawesi Selatan bersama Pemerintah Provinsi Sulsel menyasar penguatan pasar produk kain tradisional (wastra) di tingkat nasional hingga mancanegara melalui "Wastra Heritage Market 2026". Hal itu dikemukakan Kepala Kantor Perwakilan BI Sulsel Rizki Ernadi Wimanda di Makassar, Minggu (2/8). (Suriani Mappong/Sandy Arizona/Gracia Simanjuntak)</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676935/bi-targetkan-bawa-wastra-sulsel-ke-pasar-global</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_BI-TARGETKAN-BAWA-WASTRA-SULSEL-KE-PASAR-GLOBAL.jpg</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+    <row r="112">
+      <c r="A112" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>Tong Tong Night Market masuk KEN, angkat UMKM dan budaya lokal</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr">
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
         <is>
           <t>ANTARA - ‎Memasuki satu dekade penyelenggaraan, Tong Tong Night Market kembali meramaikan Kota Malang. Festival budaya dan kuliner yang masuk dalam Karisma Event Nusantara (KEN) itu tak hanya menghadirkan nuansa tempo dulu, tetapi juga menjadi ajang promosi puluhan UMKM sekaligus upaya melestarikan budaya lokal. (Achmad Saif Hajarani/Sandy Arizona/Gracia Simanjuntak)</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="F112" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676927/tong-tong-night-market-masuk-ken-angkat-umkm-dan-budaya-lokal</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_TONG-TONG-NIGHT-MARKET-MASUK-KEN-ANGKAT-UMKM-DAN-BUDAYA-LOKAL_1.jpg</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+    <row r="113">
+      <c r="A113" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>Perputaran ekonomi Piala Presiden 2026 tembus Rp70 miliar</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
         <is>
           <t>ANTARA - Ketua Steering Committee Piala Presiden 2026 Maruarar Sirait menyebut perputaran ekonomi selama babak penyisihan turnamen di Surabaya dan Bandung telah mencapai lebih dari Rp70 miliar. Dampak ekonomi tersebut turut dirasakan pelaku usaha mikro, kecil, dan menengah (UMKM) serta dimanfaatkan untuk menyubsidi harga tiket pertandingan.
 (Hanif Nasrullah/Sandy Arizona/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676895/perputaran-ekonomi-piala-presiden-2026-tembus-rp70-miliar</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_PERPUTARAN-EKONOMI-PIALA-PRESIDEN-2026-TEMBUS-RP70-MILIAR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+    <row r="114">
+      <c r="A114" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>Bahlil prioritaskan legalisasi 25 ribu sumur minyak rakyat di Sumsel</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyebut Sumatera Selatan menjadi salah satu daerah prioritas penerapan kebijakan legalisasi sumur minyak rakyat. Menurutnya, sekitar 25 ribu dari 45 ribu sumur minyak rakyat di Indonesia berada di provinsi tersebut sehingga pemerintah memfokuskan implementasi Peraturan Menteri ESDM Nomor 18 Tahun 2025 di wilayah itu.
 (Winda Tri Agustina/Sandy Arizona/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676868/bahlil-prioritaskan-legalisasi-25-ribu-sumur-minyak-rakyat-di-sumsel</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_BAHLIL-PRIORITASKAN-LEGALISASI-25-RIBU-SUMUR-MINYAK-RAKYAT-DI-SUMSEL.jpg</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+    <row r="115">
+      <c r="A115" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>Golkar optimistis tingkatkan perolehan kursi di Sumsel</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
         <is>
           <t>ANTARA - Ketua Umum Partai Golkar Bahlil Lahadalia meminta seluruh jajaran partai memperkuat konsolidasi organisasi hingga tingkat desa sebagai strategi meningkatkan perolehan kursi legislatif pada Pemilu 2029, termasuk di Sumatera Selatan.
 (Winda Tri Agustina/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F115" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676837/golkar-optimistis-tingkatkan-perolehan-kursi-di-sumsel</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/GOLKAR-OPTIMISTIS-TINGKATKAN-PEROLEHAN-KURSI-DI-SUMSEL.jpg</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+    <row r="116">
+      <c r="A116" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>Presiden AS Trump tunda serangan baru ke Iran</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
         <is>
           <t>ANTARA - Presiden Amerika Serikat Donald Trump menunda rencana serangan baru terhadap Iran setelah mengklaim terdapat peluang kesepakatan. Namun, Trump menegaskan opsi militer tetap terbuka jika negosiasi gagal.
 (XINHUA/Arsy Fitriady/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F116" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676776/presiden-as-trump-tunda-serangan-baru-ke-iran</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-AS-TRUMP-TUNDA-SERANGAN-BARU-KE-IRAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+    <row r="117">
+      <c r="A117" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>TNI AU gelar pameran enam pesawat F-16 di Batam</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr">
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
         <is>
           <t>ANTARA - TNI Angkatan Udara menggelar pameran enam pesawat tempur F-16 yang dapat dikunjungi masyarakat secara gratis dalam kegiatan Batam Open Base di Bandara Internasional Hang Nadim, Batam. Kegiatan ini menjadi bagian dari peringatan Hari Ulang Tahun ke-81 Kemerdekaan Republik Indonesia sekaligus upaya mendekatkan TNI AU kepada masyarakat.
 (Angiela Chantiequ/Jessica Allifia Jaya Hidayat/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F117" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676735/tni-au-gelar-pameran-enam-pesawat-f-16-di-batam</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/TNI-AU-GELAR-PAMERAN-ENAM-PESAWAT-F-16-DI-BATAM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>TNI kerahkan delapan helikopter salurkan bantuan ke Puncak</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr">
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
         <is>
           <t>ANTARA - Komando Gabungan Wilayah Pertahanan (Kogabwilhan) III mengerahkan delapan helikopter TNI Angkatan Darat dan TNI Angkatan Udara untuk menyalurkan bantuan kemanusiaan ke tiga distrik di Kabupaten Puncak, Papua Tengah, yang terdampak kekeringan berkepanjangan hingga memicu krisis pangan. (Laksa Mahendra/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F118" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676720/tni-kerahkan-delapan-helikopter-salurkan-bantuan-ke-puncak</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/TNI-KERAHKAN-DELAPAN-HELIKOPTER-SALURKAN-BANTUAN-KE-PUNCAK.jpg</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+    <row r="119">
+      <c r="A119" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>Jakarta Watersport Festival dorong sport tourism di Danau Sunter</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr">
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
         <is>
           <t>ANTARA - Jakarta Watersport Festival 2026 digelar di Danau Sunter, Jakarta Utara, pada 1–2 Agustus. Festival ini menghadirkan kompetisi olahraga air, hiburan, dan bazar UMKM sebagai upaya mendorong sport tourism serta aktivitas ekonomi kreatif di ibu kota. (Nabila Athifa/Setyanka Harviana Putri/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676713/jakarta-watersport-festival-dorong-sport-tourism-di-danau-sunter</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/JAKARTA-WATERSPORT-FESTIVAL-DORONG-SPORT-TOURISM-DI-DANAU-SUNTER.jpg</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+    <row r="120">
+      <c r="A120" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>Ledakan restoran di Moskow tewaskan tiga orang</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr">
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
         <is>
           <t>ANTARA - Tiga orang tewas dan sedikitnya 21 lainnya luka-luka setelah ledakan alat peledak rakitan terjadi di sebuah restoran di kawasan Kudrinskaya Square, pusat Kota Moskow, Rusia, Sabtu (1/8). Menurut Komite Antiterorisme Nasional Rusia, ledakan terjadi ketika seorang perempuan berupaya membawa alat peledak ke dalam restoran, namun dihentikan petugas keamanan. Penyelidikan terkait motif serangan masih berlangsung. (Arsy Fitriady/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F120" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676660/ledakan-restoran-di-moskow-tewaskan-tiga-orang</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G120" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/LEDAKAN-RESTORAN-DI-MOSKOW-TEWASKAN-TIGA-ORANG_1.jpg</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+    <row r="121">
+      <c r="A121" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>DKPPP Temanggung edukasi warga cegah zoonosis dari hewan piaraan</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr">
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Ketahanan Pangan, Pertanian, dan Perikanan (DKPPP) Kabupaten Temanggung bersama komunitas pecinta hewan mengedukasi masyarakat tentang pentingnya menjaga kesehatan hewan piaraan untuk mencegah zoonosis atau penyakit yang dapat menular dari hewan ke manusia. Edukasi meliputi pemberian nutrisi, vaksinasi, kebersihan, dan pemeriksaan kesehatan hewan secara berkala. (Firman Eko Handy/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F121" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676647/dkppp-temanggung-edukasi-warga-cegah-zoonosis-dari-hewan-piaraan</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="G121" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/DKPPP-TEMANGGUNG-EDUKASI-WARGA-CEGAH-ZOONOSIS-DARI-HEWAN-PIARAAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+    <row r="122">
+      <c r="A122" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>BP Batam siapkan Sekolah Terintegrasi Merah Putih di Rempang</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pengusahaan (BP) Batam menyiapkan pembangunan Sekolah Terintegrasi Merah Putih di Rempang, Kepulauan Riau, sebagai sekolah gratis bagi siswa berprestasi. Sekolah yang dibangun di atas lahan seluas 18 hektare itu akan melayani jenjang sekolah dasar hingga sekolah menengah atas dengan fasilitas pendidikan dan olahraga yang lengkap. (Angiela Chantiequ/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F122" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676644/bp-batam-siapkan-sekolah-terintegrasi-merah-putih-di-rempang</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="G122" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/BP-BATAM-SIAPKAN-SEKOLAH-TERINTEGRASI-MERAH-PUTIH-DI-REMPANG.jpg</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+    <row r="123">
+      <c r="A123" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>Aldila Sutjiadi juarai WTA 500 Mubadala DC Open 2026</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr">
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
         <is>
           <t>ANTARA - Petenis ganda putri Indonesia Aldila Sutjiadi menjuarai nomor ganda Women's Tennis Association (WTA) 500 Mubadala DC Open 2026 di Washington, Amerika Serikat. Berpasangan dengan petenis Selandia Baru Erin Routliffe, Aldila mengalahkan Andreja Klepac dari Slovenia dan Makoto Ninomiya dari Jepang dua set langsung 6-4, 6-1 pada partai final. Gelar tersebut menjadi trofi WTA kedelapan dalam karier Aldila di nomor ganda sekaligus gelar kedua bersama Routliffe pada musim 2026.
 (Arsy Fitriady/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F123" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676629/aldila-sutjiadi-juarai-wta-500-mubadala-dc-open-2026</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="G123" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/ALDILA-SUTJIADI-JUARAI-WTA-500-MUBADALA-DC-OPEN-2026.jpg</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
+    <row r="124">
+      <c r="A124" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>KM Mutiara Sentosa 2 Terbakar Saat Berlayar ke Makassar</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr">
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
         <is>
           <t>ANTARA - Kapal Motor (KM) Mutiara Sentosa 2 terbakar di perairan utara Pulau Madura saat berlayar dari Pelabuhan Tanjung Perak Surabaya menuju Makassar, Minggu (2/8). Kapal tersebut mengangkut sekitar 250 orang. Tim SAR gabungan masih melakukan evakuasi penumpang, sementara penyebab kebakaran masih dalam penyelidikan. (Hanif Nasrullah/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676617/km-mutiara-sentosa-2-terbakar-saat-berlayar-ke-makassar</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="G124" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KM-MUTIARA-SENTOSA-2-TERBAKAR-SAAT-BERLAYAR-KE-MAKASSAR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
+    <row r="125">
+      <c r="A125" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>BI dan Pemkot Kendari Perkuat Digitalisasi UMKM</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr">
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
         <is>
           <t>ANTARA - Kantor Perwakilan Bank Indonesia Sulawesi Tenggara bersama Pemerintah Kota Kendari menggelar Festival Kuliner Sultra Maimo 2026 untuk memperkuat digitalisasi usaha mikro, kecil, dan menengah atau UMKM. Festival yang berlangsung pada 2 hingga 9 Agustus itu juga mendorong perluasan transaksi non-tunai berbasis QRIS. (Saharudin/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676607/bi-dan-pemkot-kendari-perkuat-digitalisasi-umkm</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/BI-DAN-PEMKOT-KENDARI-PERKUAT-DIGITALISASI-UMKM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
+    <row r="126">
+      <c r="A126" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>El Nino menguat, negara fokus jaga ketersediaan air &amp; tangani karhutla</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr">
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
         <is>
           <t>ANTARA - Gelombang panas sebagai akibat El Nino mulai dirasakan dampaknya di sejumlah belahan dunia. Kebakaran hutan dan lahan atau karhutla, juga mulai terjadi di dalam negeri, seperti di Pulau Sumatera dan Kalimantan.Selain kebakaran, bencana ekologi yang terjadi ialah kekeringan. Beberapa daerah di Pulau Jawa seperti Temanggung, Sukoharjo, Lumajang, Banten, lalu daerah luar Jawa seperti Nusa Tenggara Barat dan Timur, hingga Bangka Belitung mulai mengalami krisis air bersih.Presiden pun memanggil sejumlah kepala kementerian dan lembaga terkait, untuk memberi pemaparan dan masukan guna meredam dampak El Nino.Lalu bagaimana sikap antisipatif yang disiapkan pemerintah pada musim kemarau dan el nino tahun ini? Selengkapnya dalam PerANTARA! (Roy Rosa Bachtiar/Suci Nurhaliza/Gunawan Wibisono/Rizky Bagus Dhermawan/Farah Khadija)</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F126" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676540/el-nino-menguat-negara-fokus-jaga-ketersediaan-air-tangani-karhutla</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="G126" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/DF.jpg</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
+    <row r="127">
+      <c r="A127" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>Padang Padang Cup Bali jadi ajang peselancar Nasional unjuk kehebatan</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr">
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
         <is>
           <t>ANTARA - Kompetisi selancar ombak Internasional Rip Curl Cup Padang Padang kembali digelar dan berlangsung pada 1-31 Agustus 2026, di Pantai Padang Padang, Labuan Sait Pecatu, Kuta Selatan, Bali. Ajang ini menjadi ruang bagi peselancar Nasional menunjukkan kehebatan mereka bersaing dengan peselancar Internasional. (Rita Laura/Sandy Arizona/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676257/padang-padang-cup-bali-jadi-ajang-peselancar-nasional-unjuk-kehebatan</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_PADANG-PADANG-CUP-BALI-JADI-AJANG-PESELANCAR-NASIONAL-UNJUK-KEHEBATAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
+    <row r="128">
+      <c r="A128" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>Bekuk Port FC, Persebaya gandeng Persija ke semifinal</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr">
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
         <is>
           <t>ANTARA - Persebaya membekuk Port FC 2 - 1 di laga terakhir Grup B turnamen sepak Piala Presiden 2026. Dengan hasil ini Persija lolos ke babak semifinal bersama Persebaya sebagai wakil Grup B. (Hanif Nasrullah/Sandy Arizona/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F128" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676252/bekuk-port-fc-persebaya-gandeng-persija-ke-semifinal</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_BEKUK-PORT-FC-PERSEBAYA-GANDENG-PERSIJA-KE-SEMIFINAL.jpg</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>Aston Villa unggul 3-1 dari Indonesia All Stars dalam tur pramusim</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr">
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
         <is>
           <t>ANTARA - Tim Indonesia All Stars, harus mengakui keunggulan atas Aston Villa dengan skor 3-1, saat laga Friendly Match di Stadion Utama Gelora Bung Karno (SUGBK) Senayan, Jakarta, pada Sabtu (1/8). Penjaga Gawang Aston Villa, James Wright, saat ditemui media di GBK mengapresiasi para pemain Indonesia All Stars, karena dinilai memiliki kualitas yang baik. (Ryan Rahman/Sandy Arizona/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F129" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676239/aston-villa-unggul-3-1-dari-indonesia-all-stars-dalam-tur-pramusim</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_ASTON-VILLA-UNGGUL-3-1-DARI-INDONESIA-ALL-STARS-DALAM-TUR-PRAMUSIM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>Joko Widodo dinobatkan sebagai sesepuh oleh sembilan Raja Timor</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr">
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
         <is>
           <t>ANTARA - Ribuan warga memadati kawasan Pantai Lahi Lai Bissi Kopan (LLBK) Kota Kupang, Nusa Tenggara Timur, untuk menyaksikan Karnaval Budaya yang dihadiri Presiden ke-7 Republik Indonesia, Joko Widodo. Dalam prosesi adat yang menjadi puncak acara, Joko Widodo dinobatkan sebagai sesepuh atau saudara oleh sembilan raja dari kerajaan-kerajaan di Pulau Timor sebagai bentuk penghormatan terhadap nilai persaudaraan dan budaya masyarakat Timor. (Johanes Viandinando/Sandy Arizona/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676205/joko-widodo-dinobatkan-sebagai-sesepuh-oleh-sembilan-raja-timor</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="G130" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_JOKO-WIDODO-DINOBATKAN-SEBAGAI-SESEPUH-OLEH-SEMBILAN-RAJA-TIMOR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
+    <row r="131">
+      <c r="A131" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>Menag: Indeks kerukunan umat beragama RI jadi 77,89 persen di 2025</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr">
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Agama Nasaruddin Umar menyebut indeks kerukunan umat beragama naik menjadi 77,89 persen pada tahun 2025, dari sebelumnya, yakni 76,47 persen pada tahun 2024. Hal tersebut disampaikan oleh Menag saat mengahdiri agenda Zikir dan Doa Kebangsaan "Indonesia Berdaulat, Adil dan Makmur" di Lapangan Silang Monas, Jakarta, Sabtu (1/8).
 (Afra Augesti/Nico Anggriawan/Sandy Arizona/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676188/menag-indeks-kerukunan-umat-beragama-ri-jadi-7789-persen-di-2025</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_MENAG-INDEKS-KERUKUNAN-UMAT-BERAGAMA-RI-JADI-77-89-PERSEN-DI-2025.jpg</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
+    <row r="132">
+      <c r="A132" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>KKP bantu pelaku usaha perikanan terdampak bencana di Sumbar</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr">
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
         <is>
           <t>ANTARA - Kementerian Kelautan dan Perikanan (KKP) bersama Tim Satuan Tugas Percepatan Rehabilitasi dan Rekonstruksi (PRR) Provinsi Sumatera Barat, mempercepat dan memastikan operasionalisasi budi daya, nelayan serta pengolahan ikan segera berjalan pascabencana hidrometeorologi yang terjadi akhir November tahun lalu. Untuk itu, KKP memberikan bantuan awal berupa bibit ikan dan pakan, dan ekskavator, kepada pelaku usaha perikanan yang terdampak bencana hidrometeorologis di Kota Padang, Kabupaten Padang Pariaman, Kabupaten Solok dan Kabupaten Agam.
 (Melani Friati/Sandy Arizona/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676172/kkp-bantu-pelaku-usaha-perikanan-terdampak-bencana-di-sumbar</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_KKP-BANTU-PELAKU-USAHA-PERIKANAN-TERDAMPAK-BENCANA-DI-SUMBAR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
+    <row r="133">
+      <c r="A133" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>INZS 2026 perkuat komitmen Indonesia hadapi krisis iklim</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr">
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah Indonesia terus mempercepat transisi energi sebagai bagian dari upaya mengatasi perubahan iklim melalui berbagai proyek yang mulai direalisasikan. Komitmen tersebut mengemuka dalam Indonesia Net Zero Summit (INZS) 2026 di Balai Kartini, Jakarta, Sabtu (1/8). Pendiri Foreign Policy Community of Indonesia (FPCI), Dino Patti Djalal, menegaskan bahwa penanganan perubahan iklim harus menjadi prioritas karena dampaknya menyentuh hampir seluruh aspek kehidupan manusia.
 (Irfan Hardiansah/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676087/inzs-2026-perkuat-komitmen-indonesia-hadapi-krisis-iklim</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/INZS-2026-PERKUAT-KOMITMEN-INDONESIA-HADAPI-KRISIS-IKLIM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
+    <row r="134">
+      <c r="A134" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>Kemeriahan menyambut bulan kemerdekaan Indonesia di Malaysia</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr">
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
         <is>
           <t>ANTARA - Kegembiraan menyambut bulan kemerdekaan Republik Indonesia turut dirasakan para warga negara Indonesia yang berada di negeri jiran Malaysia. WNI dengan penuh antusias mengikuti berbagai perlombaan yang diselenggarakan Kedutaan Besar Republik Indonesia (KBRI) di Kuala Lumpur, Malaysia, Sabtu (1/8).
 (Rangga Pandu Asmara Jingga/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676063/kemeriahan-menyambut-bulan-kemerdekaan-indonesia-di-malaysia</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KEMERIAHAN-MENYAMBUT-BULAN-KEMERDEKAAN-INDONESIA-DI-MALAYSIA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
+    <row r="135">
+      <c r="A135" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>Cari Bibit unggul, Bogor gelar sirkuit panjat tebing anak dan remaja</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr">
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
         <is>
           <t>ANTARA - Federasi Panjat Tebing Indonesia (FPTI) Kota Bogor menggelar Sirkuit Panjat Tebing se-Kota Bogor sebagai ajang pencarian bibit atlet muda, Sabtu (1/8). Dengan diikuti 100 peserta anak-anak dan remaja, kegiatan itu mempertandingkan kategori lead dan speed untuk kelompok umur under 11, under 13, dan under 19.
 (Fadzar Ilham Pangestu/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676021/cari-bibit-unggul-bogor-gelar-sirkuit-panjat-tebing-anak-dan-remaja</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="G135" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/CARI-BIBIT-UNGGUL-BOGOR-GELAR-SIRKUIT-PANJAT-TEBING-ANAK-DAN-REMAJA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
+    <row r="136">
+      <c r="A136" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>Karhutla Tumbang Nusa meluas, 104 hektar gambut terbakar</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr">
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
         <is>
           <t>ANTARA - Kebakaran hutan dan lahan (karhutla) di Desa Tumbang Nusa, Kecamatan Jabiren Raya, Kabupaten Pulang Pisau, Kalimantan Tengah, telah menghanguskan sekitar 104 hektare lahan gambut, Sabtu (1/8). Peristiwa tersebut memicu operasi penanganan terpadu yang melibatkan sekitar 416 personel gabungan melalui jalur darat, serta didukung dua unit helikopter water bombing untuk mempercepat pemadaman yang jauh dari tim darat. 
 (Redianto Tumon Sp/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="F136" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676013/karhutla-tumbang-nusa-meluas-104-hektar-gambut-terbakar</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="G136" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KARHUTLA-TUMBANG-NUSA-MELUAS-104-HEKTAR-GAMBUT-TERBAKAR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
+    <row r="137">
+      <c r="A137" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>54 Atlet menembak Kalsel, bertanding pada Kejuaraan Wali Kota Cup</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr">
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah Kota Banjarmasin bersama Perbakin menggelar kejuaraan menembak Wali Kota Cup 2026. Kejuaraan diikuti oleh 54 atlet dari berbagai daerah di Kalsel sebagai wadah seleksi dan persiapan atlet kalimantan selatan menuju Pra-PON.
 (Latif Thohir/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="F137" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675995/54-atlet-menembak-kalsel-bertanding-pada-kejuaraan-wali-kota-cup</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="G137" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/54-ATLET-MENEMBAK-KALSEL-BERTANDING-PADA-KEJUARAAN-WALI-KOTA-CUP.jpg</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
+    <row r="138">
+      <c r="A138" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>Polda Riau kirim Tim Ekspedisi Merah Putih Presisi ke 17 desa 3T</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr">
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
         <is>
           <t>ANTARA - Kapolda Riau Irjen Pol Herry Heryawan melepas Tim Ekspedisi Merah Putih Presisi Polda Riau yang akan bertugas di 17 desa wilayah tertinggal, terdepan, dan terluar atau 3T, Sabtu (1/8). Ekspedisi yang berlangsung hingga 17 Agustus mendatang itu membawa berbagai program sosial, lingkungan, dan penguatan kebangsaan bagi masyarakat pesisir serta wilayah terluar di Provinsi Riau.
 (Farah Khadija/Annisa Firdausi/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="F138" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675964/polda-riau-kirim-tim-ekspedisi-merah-putih-presisi-ke-17-desa-3t</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="G138" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/POLDA-RIAU-KIRIM-TIM-EKSPEDISI-MERAH-PUTIH-PRESISI-KE-17-DESA-3T.jpg</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
+    <row r="139">
+      <c r="A139" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>Hadapi El Nino, pemerintah tingkatkan mitigasi karhutla</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr">
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah memperkuat langkah antisipasi menghadapi potensi el nino yang diperkirakan meningkatkan risiko kebakaran hutan dan lahan. Menteri Lingkungan Hidup, Muhammad Jumhur Hidayat usai membuka Indonesia Net Zero Summit (INZS) 2026 yang diselenggarakan di Balai Kartini, Jakarta, pada Sabtu (1/8) menyebutkan, pihaknya menekan potensi karhutla sejak dini, salah satunya dengan membangun kanal blocking.
 (Irfan Hardiansah/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675936/hadapi-el-nino-pemerintah-tingkatkan-mitigasi-karhutla</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="G139" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/HADAPI-EL-NINO-PEMERINTAH-TINGKATKAN-MITIGASI-KARHUTLA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
+    <row r="140">
+      <c r="A140" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>Mensos resmikan Sekolah Rakyat Terintegrasi 1 Sukoharjo</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr">
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Sosial Republik Indonesia Saifullah Yusuf membuka pelaksanaan Masa Pengenalan Lingkungan Sekolah (MPLS) di Sekolah Rakyat Terintegrasi (SRT) 1 Kabupaten Sukoharjo, Sabtu (1/8). Mensos menyebut meski proses pembangunan fisik belum sepenuhnya rampung, pihaknya memastikan kegiatan belajar mengajar sudah dapat dilaksanakan karena progres pembangunan telah mencapai sekitar 98 persen.(Denik Apriyani/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F140" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675924/mensos-resmikan-sekolah-rakyat-terintegrasi-1-sukoharjo</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="G140" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/MENSOS-RESMIKAN-SEKOLAH-RAKYAT-TERINTEGRASI-1-SUKOHARJO.jpg</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
+    <row r="141">
+      <c r="A141" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>Lanud Sjamsudin Noor gelar Bakti Sosial Hari Bakti TNI AU ke-79</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr">
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
         <is>
           <t>ANTARA - Ratusan warga di Banjarbaru, Kalimantan Selatan, antusias mengikuti kegiatan bakti sosial yang diselenggarakan oleh Pangkalan Udara (Lanud) Sjamsudin Noor pada Sabtu (1/8). Kegiatan ini dilaksanakan sebagai rangkaian peringatan Hari Bhakti TNI Angkatan Udara Ke-79
 (Latif Thohir/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F141" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675872/lanud-sjamsudin-noor-gelar-bakti-sosial-hari-bakti-tni-au-ke-79</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="G141" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/LANUD-SJAMSUDIN-NOOR-GELAR-BAKTI-SOSIAL-HARI-BAKTI-TNI-AU-KE-79.jpg</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
+    <row r="142">
+      <c r="A142" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>Prancis perketat pemeriksaan produk tani, lawan praktik francization</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr">
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
         <is>
           <t>ANTARA - Prancis memperketat pemeriksaan terhadap asal-usul produk pertanian guna memberantas praktik "francization", yaitu pelabelan ulang produk impor agar tampak sebagai hasil produksi dalam negeri. Langkah ini diambil untuk melindungi konsumen dan produsen lokal, dengan pelanggar terancam denda hingga 300.000 euro dan hukuman penjara.(XINHUA/ Nabila Anisya Charisty/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="F142" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675865/prancis-perketat-pemeriksaan-produk-tani-lawan-praktik-francization</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="G142" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PRANCIS-PERKETAT-PEMERIKSAAN-PRODUK-TANI-LAWAN-PRAKTIK-FRANCIZATION.jpg</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>KM. Prince Soya terbakar saat bersandar di Pelabuhan Samarinda</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr">
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
         <is>
           <t>ANTARA - Kapal Motor (KM) Prince Soya terbakar pada Sabtu (1/8) saat bersandar di Pelabuhan Samarinda, Kalimantan Timur. Kapal penumpang yang biasa melayani rute Samarinda - Pare-Pare, Sulawesi Selatan itu terbakar di bagian dek sebelah kanan yang diduga bersumber dari tangki berisi pelumas mesin. (Hanifan Ma'ruf/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675853/km-prince-soya-terbakar-saat-bersandar-di-pelabuhan-samarinda</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="G143" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KM.PRINCE-SOYA-TERBAKAR-SAAT-BERSANDAR-DI-PELABUHAN-SAMARINDA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
+    <row r="144">
+      <c r="A144" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>St. Petersburg luncurkan festival sepeda motor untuk pertama kalinya</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr">
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
         <is>
           <t>ANTARA - Saint Petersburg Motor Festival resmi dibuka, Jumat (31/7) selama tiga hari berturut-turut dalam pembukaan perdananya. Acara tersebut digelar untuk menghibur para penikmat sepeda motor, musik, serta pengunjung umum lainnya.(XINHUA/ Nabila Anisya Charisty/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675828/st-petersburg-luncurkan-festival-sepeda-motor-untuk-pertama-kalinya</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="G144" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/ST.PETERSBURG-LUNCURKAN-FESTIVAL-SEPEDA-MOTOR-UNTUK-PERTAMA-KALINYA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
+    <row r="145">
+      <c r="A145" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>KPHL Batam dan Akar Bhumi Indonesia berkolaborasi lestarikan bakau</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr">
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
         <is>
           <t>ANTARA - Kesatuan Pengelolaan Hutan Lindung (KPHL) Kota Batam bersama Lembaga Swadaya Masyarakat (LSM) Akar Bhumi Indonesia menanam 450 bibit bakau di Batam, Kepulauan Riau, Sabtu (1/8). Penanaman bibit bakau tersebut dilakukan untuk memastikan daerah pesisir Kota Batam terlindungi di tengah perubahan iklim, sekaligus memperimgati Hari Mangrove Sedunia 2026.(Angiela Chantique/ Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F145" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675804/kphl-batam-dan-akar-bhumi-indonesia-berkolaborasi-lestarikan-bakau</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="G145" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KPHL-BATAM-DAN-AKAR-BHUMI-INDONESIA-BERKOLABORASI-LESTARIKAN-BAKAU.jpg</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
+    <row r="146">
+      <c r="A146" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>Ribuan warga padati Jalan El Tari saat kunjungan Jokowi di Kupang, NTT</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr">
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
         <is>
           <t>ANTARA - Ribuan warga Kota Kupang dan sekitarnya memadati kawasan "Car Free Day" di Jalan El Tari, Kota Kupang, Nusa Tenggara Timur, Sabtu (1/8),  untuk menyambut kunjungan Joko Widodo. Dalam suasana penuh antusias, masyarakat bersalaman dan meminta swafoto bersama sosok Presiden ke-7 Republik Indonesia tersebut.
 (Johanes Viandinando/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F146" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675784/ribuan-warga-padati-jalan-el-tari-saat-kunjungan-jokowi-di-kupang-ntt</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="G146" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/RIBUAN-WARGA-PADATI-JALAN-EL-TARI-SAAT-KUNJUNGAN-JOKOWI-DI-KUPANG-NTT.jpg</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
+    <row r="147">
+      <c r="A147" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B147" t="inlineStr">
         <is>
           <t>Populasi Malaysia naik menjadi 34,4 juta jiwa di 2026</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr">
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
         <is>
           <t>ANTARA - Populasi diperkirakan naik menjadi 34,4 juta jiwa pada 2026. Angka tersebut naik 0,5 persen dibandingkan tahun sebelumnya dengan persentase penduduk asli atau warga Bumiputera masih menjadi kelompok terbesar. 
 (XINHUA/ Nabila Anisya Charisty/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F147" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675756/populasi-malaysia-naik-menjadi-344-juta-jiwa-di-2026</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="G147" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/POPULASI-MALAYSIA-NAIK-MENJADI-34-4-JUTA-JIWA-DI-2026.jpg</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
+    <row r="148">
+      <c r="A148" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>KAI Sumut siapkan empat pos kesehatan demi kenyamanan penumpang</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr">
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
         <is>
           <t>ANTARA - PT Kereta Api Indonesia (KAI) Divisi Regional (Divre) I Sumatera Utara menyiagakan empat Pos Kesehatan (Poskes) yang tersebar di stasiun-stasiun strategis guna memastikan keselamatan, kesehatan, serta kenyamanan seluruh penumpang selama perjalanan. Fasilitas Pos Kesehatan tersebut beroperasi di Stasiun Medan, Stasiun Tebing Tinggi, Stasiun Kisaran, dan Stasiun Rantauprapat.(M. Valery Maulidzar S/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="F148" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675753/kai-sumut-siapkan-empat-pos-kesehatan-demi-kenyamanan-penumpang</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
+      <c r="G148" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KAI-SUMUT-SIAPKAN-EMPAT-POS-KESEHATAN-DEMI-KENYAMANAN-PENUMPANG.jpg</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
+    <row r="149">
+      <c r="A149" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B149" t="inlineStr">
         <is>
           <t>Optimalisasi lahan tingkatkan pola tanam sawah di Kaltim</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr">
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
         <is>
           <t>ANTARA - Langkah optimalisasi lahan (Oplah) untuk memaksimalkan potensi pertanian di Kalimantan Timur mampu meningkatkan pola tanam petani dari satu kali menjadi dua kali setahun. Melalui sistem pertanian yang ditunjang teknologi, program oplah ini ditujukan untuk mendongkrak frekuensi panen serta jumlah produksi padi di Kaltim.(Hanifan Ma'ruf/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="F149" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675737/optimalisasi-lahan-tingkatkan-pola-tanam-sawah-di-kaltim</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="G149" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/OPTIMALISASI-LAHAN-TINGKATKAN-POLA-TANAM-SAWAH-DI-KALTIM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
+    <row r="150">
+      <c r="A150" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>Pasukan matra laut bertolak ke Dabo Singkep untuk gelar Latopsfib</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr">
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
         <is>
           <t>ANTARA - Tentara Nasional Indonesia (TNI) Angkatan Laut pada Sabtu (1/8) memberangkatkan pasukan beserta alat utama sistem senjata (alutsista) untuk mengikuti latihan operasi Amfibi (Latopsfib) di Dabo Singkep, Kepulauan Riau. Kegiatan ini merupakan bagian dari Latihan TNI Terintegrasi 2026 yang melibatkan ribuan personel dari tiga matra untuk menguji kesiapsiagaan dalam menghadapi kemungkinan situasi yang berada di luar kendali.(Hanif Nasrullah/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="F150" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675732/pasukan-matra-laut-bertolak-ke-dabo-singkep-untuk-gelar-latopsfib</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="G150" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PASUKAN-MATRA-LAUT-BERTOLAK-KE-DABO-SINGKEP-UNTUK-GELAR-LATOPSFIB.jpg</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
+    <row r="151">
+      <c r="A151" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B151" t="inlineStr">
         <is>
           <t>Apartemen ikan, napas baru wisata Bahari Desa Namu</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr">
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
         <is>
           <t>ANTARA - Sejumlah mahasiswa Kuliah Kerja Nyata (KKN) dari beberapa kampus besama pemerintah Desa Wisata Namu, Kabupaten Konawe Selatan, Sulawesi Tenggara membuat apartemen ikan di bawah laut Desa Namu. Langkah tersebut dilakukan untuk melestarikan kosistem laut dan menjaga keberlanjutan pariwisata di wilayah  setempat.(Saharudin/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="F151" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675719/apartemen-ikan-napas-baru-wisata-bahari-desa-namu</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
+      <c r="G151" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/APARTEMEN-IKAN-NAPAS-BARU-WISATA-BAHARI-DESA-NAMU.jpg</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
+    <row r="152">
+      <c r="A152" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>Koops TNI Habema evakuasi satu jenazah korban tembakan OPM di Yahukimo</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 14:35:01 +0700</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr">
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
         <is>
           <t>ANTARA - Koops TNI Habema pada Jumat (31/8), mengevakuasi satu dari tiga jenazah korban penembakan yang diduga dilakukan kelompok organisasi papua merdeka (OPM) Kodap XVI Yahukimo. Korban bernama Teina Alya ditemukan di lokasi longsoran Kali Kolof, Distrik Seradala, Kabupaten Yahukimo, Papua Pegunungan dan telah diserahkan kepada pihak keluarga untuk di makamkan.(Laksa Mahendra/Rizky Bagus Dhermawan/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
+      <c r="F152" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675675/koops-tni-habema-evakuasi-satu-jenazah-korban-tembakan-opm-di-yahukimo</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
+      <c r="G152" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-01-141537.jpg</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G136"/>
+  <autoFilter ref="A1:G152"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_antara_2026-08-03.xlsx
+++ b/data/berita_antara_2026-08-03.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$195</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G152"/>
+  <dimension ref="A1:G195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1004,61 +1004,61 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Koalisi buruh serahkan usulan RUU Ketenagakerjaan ke pimpinan DPR</t>
+          <t>Bareskrim gagalkan peredaran ganja 20 kilogram ke Kampung Bahari</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:05:55 +0700</t>
+          <t>Mon, 03 Aug 2026 14:41:18 +0700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Koalisi dari berbagai konfederasi buruh menyerahkan draf usulan untuk penyusunan Rancangan Undang-Undang (RUU) ...</t>
+          <t>Direktorat Tindak Pidana Narkoba Bareskrim Polri berhasil menggagalkan peredaran narkoba jenis ganja seberat 20 ...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677460/koalisi-buruh-serahkan-usulan-ruu-ketenagakerjaan-ke-pimpinan-dpr</t>
+          <t>https://www.antaranews.com/berita/5677421/bareskrim-gagalkan-peredaran-ganja-20-kilogram-ke-kampung-bahari</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001295553.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000087102.jpg</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BPS catat pengeluaran wisman triwulan II-2026 mencapai 1.285 dolar AS</t>
+          <t>KPK lakukan 762 penyadapan selama semester I 2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:56:12 +0700</t>
+          <t>Mon, 03 Aug 2026 14:33:32 +0700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat perkembangan pengeluaran wisatawan mancanegara (wisman) pada triwulan II tahun ...</t>
+          <t>Dewan Pengawas Komisi Pemberantasan Korupsi (Dewas KPK) menyatakan lembaga antirasuah telah melakukan 762 penyadapan ...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677457/bps-catat-pengeluaran-wisman-triwulan-ii-2026-mencapai-1285-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5677415/kpk-lakukan-762-penyadapan-selama-semester-i-2026</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG-20260731-WA0028.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_8172.jpg</t>
         </is>
       </c>
     </row>
@@ -1070,28 +1070,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Charles Honoris dorong putusan MK soal MBG diterapkan pada APBN 2027</t>
+          <t>Petani di Jakut harap pemerintah beri bantuan hadapi musim kemarau</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:56:05 +0700</t>
+          <t>Mon, 03 Aug 2026 14:29:53 +0700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wakil Ketua Komisi IX DPR RI Charles Honoris mendorong putusan Mahkamah Konstitusi (MK) mengenai anggaran program Makan ...</t>
+          <t>Petani di Kelurahan Rorotan, Cilincing Jakarta Utara berharap pemerintah dapat memberikan bantuan untuk menunjang ...</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677456/charles-honoris-dorong-putusan-mk-soal-mbg-diterapkan-pada-apbn-2027</t>
+          <t>https://www.antaranews.com/berita/5677408/petani-di-jakut-harap-pemerintah-beri-bantuan-hadapi-musim-kemarau</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/upscalemedia-transformed-167.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/13/IMG_20260713_140727.jpg</t>
         </is>
       </c>
     </row>
@@ -1103,28 +1103,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wamensos: Kolaborasi data perkuatkan bantuan JKN lebih akuntabel</t>
+          <t>BPJS Kesehatan gandeng empat K/L perkuat ekosistem Program JKN</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:54:53 +0700</t>
+          <t>Mon, 03 Aug 2026 14:28:03 +0700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wakil Menteri Sosial (Wamensos) Agus Jabo Priyono mengatakan kolaborasi strategis yang dilakukan bersama BPJS ...</t>
+          <t>BPJS Kesehatan menjalin kerja sama strategis dengan empat Kementerian dan Lembaga (K/L) sebagai upaya memperkuat ...</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677453/wamensos-kolaborasi-data-perkuatkan-bantuan-jkn-lebih-akuntabel</t>
+          <t>https://www.antaranews.com/berita/5677404/bpjs-kesehatan-gandeng-empat-k-l-perkuat-ekosistem-program-jkn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-14.44.56-1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-14.08.02.jpg</t>
         </is>
       </c>
     </row>
@@ -1136,61 +1136,61 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Presiden Iran: AS harus tetap patuhi nota kesepahaman</t>
+          <t>Rusia tetap terbuka berunding dengan Ukraina</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:54:11 +0700</t>
+          <t>Mon, 03 Aug 2026 14:23:43 +0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Presiden Iran Masoud Pezeshkian mengatakan pada Minggu (2/8) bahwa Amerika Serikat harus tetap berkomitmen pada nota ...</t>
+          <t>Rusia menegaskan tetap membuka peluang perundingan dengan Ukraina dan siap mempertimbangkan berbagai usulan yang ...</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677449/presiden-iran-as-harus-tetap-patuhi-nota-kesepahaman</t>
+          <t>https://www.antaranews.com/berita/5677403/rusia-tetap-terbuka-berunding-dengan-ukraina</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CjkinzN000008_20260803_CBMFN0A001.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/06/thumbs_b2_e27328c11fef925beee70a6fbdcf61b4.jpg</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kapal Pertamina selamatkan 17 korban KMP Mutiara Sentosa 2</t>
+          <t>Kejati NTB minta data pajak PT GNE ke Kemenkeu untuk penyidikan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:52:47 +0700</t>
+          <t>Mon, 03 Aug 2026 14:23:27 +0700</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kapal Pertamina Patra Niaga MT Transko Arafura berhasil mengevakuasi 17 orang korban KMP Mutiara Sentosa 2 yang ...</t>
+          <t>Kejaksaan Tinggi Nusa Tenggara Barat meminta data pajak PT Gerbang NTB Emas (GNE) kepada Kementerian Keuangan sebagai ...</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677445/kapal-pertamina-selamatkan-17-korban-kmp-mutiara-sentosa-2</t>
+          <t>https://www.antaranews.com/berita/5677400/kejati-ntb-minta-data-pajak-pt-gne-ke-kemenkeu-untuk-penyidikan</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-14.30.38.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/aspidsus-kejati-ntb-zulkifli-said-9.jpg</t>
         </is>
       </c>
     </row>
@@ -1202,61 +1202,61 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ekonomi kelautan China catat pertumbuhan stabil pada H1 2026</t>
+          <t>Pemprov Jatim siap tanggung biaya RS korban KMP Mutiara yang terbakar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:50:44 +0700</t>
+          <t>Mon, 03 Aug 2026 14:19:46 +0700</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Produk laut bruto (PLB) China mencapai 5,5 triliun yuan (1 yuan = Rp2.676) pada paruh pertama (H1) 2026, naik 5,1 ...</t>
+          <t>Pemerintah Provinsi (Pemprov) Jawa Timur (Jatim) mengatakan siap menanggung biaya rumah sakit korban kebakaran ...</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677441/ekonomi-kelautan-china-catat-pertumbuhan-stabil-pada-h1-2026</t>
+          <t>https://www.antaranews.com/berita/5677395/pemprov-jatim-siap-tanggung-biaya-rs-korban-kmp-mutiara-yang-terbakar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CjkinzN000010_20260803_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/261107.jpg</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PGN sasar pemanfaatan jargas untuk hotel hingga UMKM</t>
+          <t>Resmi dibuka, Sekolah Rakyat Terintegrasi 2 Kendari tampung 339 siswa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:50:20 +0700</t>
+          <t>Mon, 03 Aug 2026 14:15:20 +0700</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PT Perusahaan Gas Negara (Persero) Tbk (PGN) menyasar pemanfaatan jaringan gas (jargas) tidak hanya rumah ...</t>
+          <t>ANTARA - Sekolah Rakyat Terintegrasi 2 Kota Kendari resmi dibuka pada Senin (3/8), yang ditandai dengan Masa Pengenalan ...</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677439/pgn-sasar-pemanfaatan-jargas-untuk-hotel-hingga-umkm</t>
+          <t>https://www.antaranews.com/video/5677373/resmi-dibuka-sekolah-rakyat-terintegrasi-2-kendari-tampung-339-siswa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_2395.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/RESMI-DIBUKA-SEKOLAH-RAKYAT-TERINTEGRASI-2-KENDARI-TAMPUNG-339-SISWA.jpg</t>
         </is>
       </c>
     </row>
@@ -1268,28 +1268,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TNI AL tuntaskan latihan gabungan dengan AL Australia</t>
+          <t>Aston Martin percaya diri bisa pertahankan Alonso untuk musim 2027</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:46:09 +0700</t>
+          <t>Mon, 03 Aug 2026 14:14:16 +0700</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>TNI AL menuntaskan kegiatan latihan gabungan dengan AL Australia atau Royal Australian Navy (RAN) dalam ajang Cassowary ...</t>
+          <t>Kepala Tim Aston Martin Adrian Newey percaya diri bisa mempertahankan jasa dari pembalapnya Fernando Alonso untuk ...</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677436/tni-al-tuntaskan-latihan-gabungan-dengan-al-australia</t>
+          <t>https://www.antaranews.com/berita/5677393/aston-martin-percaya-diri-bisa-pertahankan-alonso-untuk-musim-2027</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001554245.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/05/29/Alonso.jpg</t>
         </is>
       </c>
     </row>
@@ -1301,61 +1301,61 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wamenkomdigi: TVRI institusi strategis penjaga ruang informasi bangsa</t>
+          <t>Warga Jakarta tanggapi pro-kontra soal pemasangan pagar di mal</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:45:19 +0700</t>
+          <t>Mon, 03 Aug 2026 14:13:58 +0700</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wakil Menteri Komunikasi dan Digital (Wamenkomdigi) Angga Raka Prabowo menyatakan Lembaga Penyiaran Publik (LPP) TVRI ...</t>
+          <t>Sejumlah warga di Jakarta Selatan menyampaikan beragam pendapat mereka dengan pro dan kontra dalam ...</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677432/wamenkomdigi-tvri-institusi-strategis-penjaga-ruang-informasi-bangsa</t>
+          <t>https://www.antaranews.com/berita/5677391/warga-jakarta-tanggapi-pro-kontra-soal-pemasangan-pagar-di-mal</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0224.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001010075.jpg</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>photo, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Petani berbagi air sumur demi selamatkan tanaman tembakau</t>
+          <t>Kemenhaj perkuat kemitraan dengan Saudi bangun rantai pasok haji-umrah</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:44:51 +0700</t>
+          <t>Mon, 03 Aug 2026 14:09:33 +0700</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Petani mengambil air dari sumur untuk menyiram tanaman tembakau di Lengkong, Nganjuk, Jawa Timur, Senin (3/8/2026). ...</t>
+          <t>Kementerian Haji dan Umrah (Kemenhaj)RI mendorong penguatan kemitraan strategis antara Indonesia dan Arab Saudi guna ...</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5677428/petani-berbagi-air-sumur-demi-selamatkan-tanaman-tembakau</t>
+          <t>https://www.antaranews.com/berita/5677388/kemenhaj-perkuat-kemitraan-dengan-saudi-bangun-rantai-pasok-haji-umrah</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/petani-tembakau-berbagi-air-sumur-antisipasi-dampak-el-nino-030826-mm-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176390.jpg</t>
         </is>
       </c>
     </row>
@@ -1367,61 +1367,61 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BPK berikan opini WTP kepada Kemenko Kumham Imipas atas LK 2025</t>
+          <t>Ketua KY sampaikan permintaan maaf kepada MA dan hakim</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:44:20 +0700</t>
+          <t>Mon, 03 Aug 2026 14:03:28 +0700</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Badan Pemeriksa Keuangan RI memberikan opini Wajar Tanpa Pengecualian (WTP) kepada seluruh kementerian di bawah ...</t>
+          <t>Ketua Komisi Yudisial Abdul Chair Ramadhan menyampaikan permohonan maaf kepada Ketua Mahkamah Agung dan para hakim ...</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677427/bpk-berikan-opini-wtp-kepada-kemenko-kumham-imipas-atas-lk-2025</t>
+          <t>https://www.antaranews.com/berita/5677385/ketua-ky-sampaikan-permintaan-maaf-kepada-ma-dan-hakim</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001216320.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000012884.jpg</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nusron sebut banyak laut di Batam telah dikapling tanpa prosedur sah</t>
+          <t>Kekeringan ancam operasional PLTN Paks di Hungaria berhenti total</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:44:05 +0700</t>
+          <t>Mon, 03 Aug 2026 13:49:52 +0700</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Menteri Agraria dan Tata Ruang (ATR)/Kepala Badan Pertanahan Nasional (BPN) Nusron Wahid mengatakan, menerima banyak ...</t>
+          <t>Kekeringan yang ditimbulkan gelombang panas ekstrem membuat tinggi muka air di Sungai Danube turun dan mengancam ...</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677425/nusron-sebut-banyak-laut-di-batam-telah-dikapling-tanpa-prosedur-sah</t>
+          <t>https://www.antaranews.com/berita/5677383/kekeringan-ancam-operasional-pltn-paks-di-hungaria-berhenti-total</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_142345.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CjkinzN000007_20260803_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
@@ -1433,94 +1433,94 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bareskrim gagalkan peredaran ganja 20 kilogram ke Kampung Bahari</t>
+          <t>Anggota DPR: Penyelematan korban kapal terbakar di Sumenep harus cepat</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:41:18 +0700</t>
+          <t>Mon, 03 Aug 2026 13:48:41 +0700</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Direktorat Tindak Pidana Narkoba Bareskrim Polri berhasil menggagalkan peredaran narkoba jenis ganja seberat 20 ...</t>
+          <t>Anggota DPR RI Bambang Haryo Soekartono (BHS) menyatakan waktu tanggap (response time) penyelamatan terhadap ...</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677421/bareskrim-gagalkan-peredaran-ganja-20-kilogram-ke-kampung-bahari</t>
+          <t>https://www.antaranews.com/berita/5677380/anggota-dpr-penyelematan-korban-kapal-terbakar-di-sumenep-harus-cepat</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000087102.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1319103.jpg</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CORE: Harga Pertamax turun beri sentimen positif bagi inflasi</t>
+          <t>KPK periksa Kadis PUPR Kota Bengkulu usai geledah dan sita Rp4 miliar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:40:44 +0700</t>
+          <t>Mon, 03 Aug 2026 13:46:34 +0700</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ekonom Center of Reform on Economics (CORE) Yusuf Rendy Manilet menyampaikan penurunan harga Pertamax pada bulan ...</t>
+          <t>Komisi Pemberantasan Korupsi memeriksa Kepala Dinas Pekerjaan Umum dan Penataan Ruang (PUPR) Kota Bengkulu Noprisman ...</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677420/core-harga-pertamax-turun-beri-sentimen-positif-bagi-inflasi</t>
+          <t>https://www.antaranews.com/berita/5677377/kpk-periksa-kadis-pupr-kota-bengkulu-usai-geledah-dan-sita-rp4-miliar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/penurunan-harga-bbm-jenis-pertamax-2831783.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_7724.jpg</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Askrindo bukukan laba Rp1,69 T pada 2025 ditopang tiga lini bisnis</t>
+          <t>Pengaruh makan timun terhadap kesehatan tubuh</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:38:49 +0700</t>
+          <t>Mon, 03 Aug 2026 13:45:30 +0700</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PT Asuransi Kredit Indonesia (Persero) atau Askrindo membukukan laba setelah pajak sebesar Rp1,69 triliun pada 2025 ...</t>
+          <t>Profesor madya di bidang nutrisi dan kesehatan masyarakat dari Fakultas Kedokteran Universitas Tufts Kimberly Dong ...</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677419/askrindo-bukukan-laba-rp169-t-pada-2025-ditopang-tiga-lini-bisnis</t>
+          <t>https://www.antaranews.com/berita/5677375/pengaruh-makan-timun-terhadap-kesehatan-tubuh</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-08.51.32.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/11/03/antarafoto-pasokan-buah-timun-terdampak-cuaca-di-pulau-bacan-3112022-ans-1.jpg</t>
         </is>
       </c>
     </row>
@@ -1532,61 +1532,61 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>KPK lakukan 762 penyadapan selama semester I 2026</t>
+          <t>Jaksel catat mobil klinik hewan layani 226 ekor kucing hingga domba</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:33:32 +0700</t>
+          <t>Mon, 03 Aug 2026 13:38:38 +0700</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dewan Pengawas Komisi Pemberantasan Korupsi (Dewas KPK) menyatakan lembaga antirasuah telah melakukan 762 penyadapan ...</t>
+          <t>Suku Dinas Ketahanan Pangan, Kelautan, dan Pertanian Jakarta Selatan (KPKP Jaksel) mencatat Mobil Klinik Hewan ...</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677415/kpk-lakukan-762-penyadapan-selama-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5677369/jaksel-catat-mobil-klinik-hewan-layani-226-ekor-kucing-hingga-domba</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_8172.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001010031.jpg</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jasaraharja Putera menjamin santunan korban KMP Mutiara Sentosa II</t>
+          <t>Wali Kota pastikan fasilitas SRT Kendari dukung perkembangan siswa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:30:17 +0700</t>
+          <t>Mon, 03 Aug 2026 13:36:17 +0700</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PT Jasaraharja Putera menjamin perlindungan dan santunan bagi seluruh korban kebakaran Kapal Motor Penyeberangan (KMP) ...</t>
+          <t>Wali Kota Kendari Siska Karina Imran memastikan bahwa fasilitas yang ada di Sekolah Rakyat Terintegrasi (SRT) 2 Kota ...</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677412/jasaraharja-putera-menjamin-santunan-korban-kmp-mutiara-sentosa-ii</t>
+          <t>https://www.antaranews.com/berita/5677359/wali-kota-pastikan-fasilitas-srt-kendari-dukung-perkembangan-siswa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176259.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/aeea98a9-b62b-4a35-a533-805d3c8ac339.jpeg</t>
         </is>
       </c>
     </row>
@@ -1598,61 +1598,61 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Petani di Jakut harap pemerintah beri bantuan hadapi musim kemarau</t>
+          <t>Gempa bermagnitudo 5,3 guncang Mesir timur laut</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:29:53 +0700</t>
+          <t>Mon, 03 Aug 2026 13:32:32 +0700</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Petani di Kelurahan Rorotan, Cilincing Jakarta Utara berharap pemerintah dapat memberikan bantuan untuk menunjang ...</t>
+          <t>Sebuah gempa bermagnitudo 5,3 mengguncang Provinsi Ismailia di Mesir timur laut pada Senin pagi waktu setempat, menurut ...</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677408/petani-di-jakut-harap-pemerintah-beri-bantuan-hadapi-musim-kemarau</t>
+          <t>https://www.antaranews.com/berita/5677351/gempa-bermagnitudo-53-guncang-mesir-timur-laut</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/13/IMG_20260713_140727.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/18/ilustrasi-gempa-2_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GMR bidik Indonesia dalam perluasan rute Bandara Bhogapuram India</t>
+          <t>Dedi Kusnandar: Persib siap hadapi Persija di semifinal Piala Presiden</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:29:34 +0700</t>
+          <t>Mon, 03 Aug 2026 13:31:31 +0700</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GMR Airports Limited (GMR Airports), salah satu pengelola jaringan bandara internasional, memprioritaskan Indonesia ...</t>
+          <t>Gelandang Persib Bandung Dedi Kusnandar menegaskan timnya siap menghadapi Persija Jakarta pada babak semifinal Piala ...</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677407/gmr-bidik-indonesia-dalam-perluasan-rute-bandara-bhogapuram-india</t>
+          <t>https://www.antaranews.com/berita/5677349/dedi-kusnandar-persib-siap-hadapi-persija-di-semifinal-piala-presiden</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0725.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_9111.jpeg</t>
         </is>
       </c>
     </row>
@@ -1664,28 +1664,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BPJS Kesehatan gandeng empat K/L perkuat ekosistem Program JKN</t>
+          <t>Wakil Ketua DPR salurkan beasiswa PIP ke ribuan pelajar Lombok Timur</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:28:03 +0700</t>
+          <t>Mon, 03 Aug 2026 13:30:16 +0700</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>BPJS Kesehatan menjalin kerja sama strategis dengan empat Kementerian dan Lembaga (K/L) sebagai upaya memperkuat ...</t>
+          <t>Wakil Ketua DPR RI Sari Yuliati menyerahkan bantuan beasiswa Program Indonesia Pintar (PIP) 2026 kepada ribuan pelajar ...</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677404/bpjs-kesehatan-gandeng-empat-k-l-perkuat-ekosistem-program-jkn</t>
+          <t>https://www.antaranews.com/berita/5677345/wakil-ketua-dpr-salurkan-beasiswa-pip-ke-ribuan-pelajar-lombok-timur</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-14.08.02.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1005724306.jpg</t>
         </is>
       </c>
     </row>
@@ -1697,28 +1697,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Rusia tetap terbuka berunding dengan Ukraina</t>
+          <t>Dinkop UKM Cilegon targetkan 21 gerai baru KKMP beroperasi September</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:23:43 +0700</t>
+          <t>Mon, 03 Aug 2026 13:27:17 +0700</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rusia menegaskan tetap membuka peluang perundingan dengan Ukraina dan siap mempertimbangkan berbagai usulan yang ...</t>
+          <t>ANTARA - Dinas Koperasi Usaha Kecil dan Menengah (Dinkop UKM) Kota Cilegon menargetkan pembangunan  21 gedung ...</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677403/rusia-tetap-terbuka-berunding-dengan-ukraina</t>
+          <t>https://www.antaranews.com/video/5677301/dinkop-ukm-cilegon-targetkan-21-gerai-baru-kkmp-beroperasi-september</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/06/thumbs_b2_e27328c11fef925beee70a6fbdcf61b4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/DINKOP-UKM-CILEGON-TARGETKAN-21-GERAI-BARU-KKMP-BEROPERASI-SEPTEMBER.jpg</t>
         </is>
       </c>
     </row>
@@ -1730,325 +1730,326 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kejati NTB minta data pajak PT GNE ke Kemenkeu untuk penyidikan</t>
+          <t>Puluhan santri Ponpes Darul Amanah Kendal kunjungi Istana Presiden</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:23:27 +0700</t>
+          <t>Mon, 03 Aug 2026 13:24:08 +0700</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kejaksaan Tinggi Nusa Tenggara Barat meminta data pajak PT Gerbang NTB Emas (GNE) kepada Kementerian Keuangan sebagai ...</t>
+          <t>Puluhan santri beserta pengajar Pondok Pesantren Darul Amanah Sukorejo, Kendal, Jawa Tengah, melakukan kunjungan ...</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677400/kejati-ntb-minta-data-pajak-pt-gne-ke-kemenkeu-untuk-penyidikan</t>
+          <t>https://www.antaranews.com/berita/5677337/puluhan-santri-ponpes-darul-amanah-kendal-kunjungi-istana-presiden</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/aspidsus-kejati-ntb-zulkifli-said-9.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_3918.jpeg</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BPS: Wisman per Juni capai 7,45 juta kunjungan, tertinggi sejak 2020</t>
+          <t>Cek fakta, Pemprov Jabar resmi adakan kembali SPP untuk sekolah negeri pada Juli 2026</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:22:48 +0700</t>
+          <t>Mon, 03 Aug 2026 13:23:04 +0700</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat total kunjungan wisatawan mancanegara dari Januari hingga bulan Juni 2026 mencapai ...</t>
+          <t>Jakarta (ANTARA/JACX) – Sebuah unggahan di Facebook menarasikan bahwa Pemerintah Provinsi Jawa Barat ...</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677399/bps-wisman-per-juni-capai-745-juta-kunjungan-tertinggi-sejak-2020</t>
+          <t>https://www.antaranews.com/berita/5677333/cek-fakta-pemprov-jabar-resmi-adakan-kembali-spp-untuk-sekolah-negeri-pada-juli-2026</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/pelepasliaran-500-ekor-tukik-bali-290726-nhw-3_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/17/WhatsApp-Image-2026-06-17-at-20.14.04.jpeg</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>terkini, top-news</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Menkomdigi panggil YouTube imbas temuan konten promosi vape sasar anak</t>
+          <t>BPS: Indonesia catat deflasi bulanan 0,14 persen pada Juli 2026</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:22:09 +0700</t>
+          <t>Mon, 03 Aug 2026 12:20:12 +0700</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid merencanakan pemanggilan terhadap platform digital YouTube ...</t>
+          <t>Badan Pusat Statistik (BPS) mencatat Indonesia mengalami deflasi sebesar 0,14 persen secara bulanan ...</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677396/menkomdigi-panggil-youtube-imbas-temuan-konten-promosi-vape-sasar-anak</t>
+          <t>https://www.antaranews.com/berita/5677247/bps-indonesia-catat-deflasi-bulanan-014-persen-pada-juli-2026</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0225.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/bps.jpeg</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pemprov Jatim siap tanggung biaya RS korban KMP Mutiara yang terbakar</t>
+          <t>Kemendag kantongi potensi ekspor Rp1,87 miliar ke Chile</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:19:46 +0700</t>
+          <t>Mon, 03 Aug 2026 12:16:02 +0700</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pemerintah Provinsi (Pemprov) Jawa Timur (Jatim) mengatakan siap menanggung biaya rumah sakit korban kebakaran ...</t>
+          <t>Kementerian Perdagangan (Kemendag) melalui Indonesia Trade Promotion Center (ITPC) Santiago di Chile menggelar ...</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677395/pemprov-jatim-siap-tanggung-biaya-rs-korban-kmp-mutiara-yang-terbakar</t>
+          <t>https://www.antaranews.com/berita/5677237/kemendag-kantongi-potensi-ekspor-rp187-miliar-ke-chile</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/261107.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/03/IMG_3208.jpeg</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Resmi dibuka, Sekolah Rakyat Terintegrasi 2 Kendari tampung 339 siswa</t>
+          <t>Populasi Malaysia naik menjadi 34,4 juta jiwa di 2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:15:20 +0700</t>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ANTARA - Sekolah Rakyat Terintegrasi 2 Kota Kendari resmi dibuka pada Senin (3/8), yang ditandai dengan Masa Pengenalan ...</t>
+          <t>ANTARA - Populasi diperkirakan naik menjadi 34,4 juta jiwa pada 2026. Angka tersebut naik 0,5 persen dibandingkan tahun sebelumnya dengan persentase penduduk asli atau warga Bumiputera masih menjadi kelompok terbesar. 
+(XINHUA/ Nabila Anisya Charisty/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5677373/resmi-dibuka-sekolah-rakyat-terintegrasi-2-kendari-tampung-339-siswa</t>
+          <t>https://www.antaranews.com/berita/5675756/populasi-malaysia-naik-menjadi-344-juta-jiwa-di-2026</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/RESMI-DIBUKA-SEKOLAH-RAKYAT-TERINTEGRASI-2-KENDARI-TAMPUNG-339-SISWA.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/POPULASI-MALAYSIA-NAIK-MENJADI-34-4-JUTA-JIWA-DI-2026.jpg</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Aston Martin percaya diri bisa pertahankan Alonso untuk musim 2027</t>
+          <t>KAI Sumut siapkan empat pos kesehatan demi kenyamanan penumpang</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:14:16 +0700</t>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kepala Tim Aston Martin Adrian Newey percaya diri bisa mempertahankan jasa dari pembalapnya Fernando Alonso untuk ...</t>
+          <t>ANTARA - PT Kereta Api Indonesia (KAI) Divisi Regional (Divre) I Sumatera Utara menyiagakan empat Pos Kesehatan (Poskes) yang tersebar di stasiun-stasiun strategis guna memastikan keselamatan, kesehatan, serta kenyamanan seluruh penumpang selama perjalanan. Fasilitas Pos Kesehatan tersebut beroperasi di Stasiun Medan, Stasiun Tebing Tinggi, Stasiun Kisaran, dan Stasiun Rantauprapat.(M. Valery Maulidzar S/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677393/aston-martin-percaya-diri-bisa-pertahankan-alonso-untuk-musim-2027</t>
+          <t>https://www.antaranews.com/berita/5675753/kai-sumut-siapkan-empat-pos-kesehatan-demi-kenyamanan-penumpang</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/05/29/Alonso.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/KAI-SUMUT-SIAPKAN-EMPAT-POS-KESEHATAN-DEMI-KENYAMANAN-PENUMPANG.jpg</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Warga Jakarta tanggapi pro-kontra soal pemasangan pagar di mal</t>
+          <t>Optimalisasi lahan tingkatkan pola tanam sawah di Kaltim</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:13:58 +0700</t>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sejumlah warga di Jakarta Selatan menyampaikan beragam pendapat mereka dengan pro dan kontra dalam ...</t>
+          <t>ANTARA - Langkah optimalisasi lahan (Oplah) untuk memaksimalkan potensi pertanian di Kalimantan Timur mampu meningkatkan pola tanam petani dari satu kali menjadi dua kali setahun. Melalui sistem pertanian yang ditunjang teknologi, program oplah ini ditujukan untuk mendongkrak frekuensi panen serta jumlah produksi padi di Kaltim.(Hanifan Ma'ruf/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677391/warga-jakarta-tanggapi-pro-kontra-soal-pemasangan-pagar-di-mal</t>
+          <t>https://www.antaranews.com/berita/5675737/optimalisasi-lahan-tingkatkan-pola-tanam-sawah-di-kaltim</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001010075.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/OPTIMALISASI-LAHAN-TINGKATKAN-POLA-TANAM-SAWAH-DI-KALTIM.jpg</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kemenhaj perkuat kemitraan dengan Saudi bangun rantai pasok haji-umrah</t>
+          <t>Pasukan matra laut bertolak ke Dabo Singkep untuk gelar Latopsfib</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:09:33 +0700</t>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kementerian Haji dan Umrah (Kemenhaj)RI mendorong penguatan kemitraan strategis antara Indonesia dan Arab Saudi guna ...</t>
+          <t>ANTARA - Tentara Nasional Indonesia (TNI) Angkatan Laut pada Sabtu (1/8) memberangkatkan pasukan beserta alat utama sistem senjata (alutsista) untuk mengikuti latihan operasi Amfibi (Latopsfib) di Dabo Singkep, Kepulauan Riau. Kegiatan ini merupakan bagian dari Latihan TNI Terintegrasi 2026 yang melibatkan ribuan personel dari tiga matra untuk menguji kesiapsiagaan dalam menghadapi kemungkinan situasi yang berada di luar kendali.(Hanif Nasrullah/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677388/kemenhaj-perkuat-kemitraan-dengan-saudi-bangun-rantai-pasok-haji-umrah</t>
+          <t>https://www.antaranews.com/berita/5675732/pasukan-matra-laut-bertolak-ke-dabo-singkep-untuk-gelar-latopsfib</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176390.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PASUKAN-MATRA-LAUT-BERTOLAK-KE-DABO-SINGKEP-UNTUK-GELAR-LATOPSFIB.jpg</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ketua KY sampaikan permintaan maaf kepada MA dan hakim</t>
+          <t>Apartemen ikan, napas baru wisata Bahari Desa Namu</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:03:28 +0700</t>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ketua Komisi Yudisial Abdul Chair Ramadhan menyampaikan permohonan maaf kepada Ketua Mahkamah Agung dan para hakim ...</t>
+          <t>ANTARA - Sejumlah mahasiswa Kuliah Kerja Nyata (KKN) dari beberapa kampus besama pemerintah Desa Wisata Namu, Kabupaten Konawe Selatan, Sulawesi Tenggara membuat apartemen ikan di bawah laut Desa Namu. Langkah tersebut dilakukan untuk melestarikan kosistem laut dan menjaga keberlanjutan pariwisata di wilayah  setempat.(Saharudin/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677385/ketua-ky-sampaikan-permintaan-maaf-kepada-ma-dan-hakim</t>
+          <t>https://www.antaranews.com/berita/5675719/apartemen-ikan-napas-baru-wisata-bahari-desa-namu</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000012884.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/APARTEMEN-IKAN-NAPAS-BARU-WISATA-BAHARI-DESA-NAMU.jpg</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kekeringan ancam operasional PLTN Paks di Hungaria berhenti total</t>
+          <t>Koops TNI Habema evakuasi satu jenazah korban tembakan OPM di Yahukimo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:49:52 +0700</t>
+          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kekeringan yang ditimbulkan gelombang panas ekstrem membuat tinggi muka air di Sungai Danube turun dan mengancam ...</t>
+          <t>ANTARA - Koops TNI Habema pada Jumat (31/8), mengevakuasi satu dari tiga jenazah korban penembakan yang diduga dilakukan kelompok organisasi papua merdeka (OPM) Kodap XVI Yahukimo. Korban bernama Teina Alya ditemukan di lokasi longsoran Kali Kolof, Distrik Seradala, Kabupaten Yahukimo, Papua Pegunungan dan telah diserahkan kepada pihak keluarga untuk di makamkan.(Laksa Mahendra/Rizky Bagus Dhermawan/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677383/kekeringan-ancam-operasional-pltn-paks-di-hungaria-berhenti-total</t>
+          <t>https://www.antaranews.com/berita/5675675/koops-tni-habema-evakuasi-satu-jenazah-korban-tembakan-opm-di-yahukimo</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CjkinzN000007_20260803_CBMFN0A001.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-01-141537.jpg</t>
         </is>
       </c>
     </row>
@@ -2060,28 +2061,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Anggota DPR: Penyelematan korban kapal terbakar di Sumenep harus cepat</t>
+          <t>Prabowo terima laporan Bahlil soal program ketahanan energi</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:48:41 +0700</t>
+          <t>Mon, 03 Aug 2026 16:02:25 +0700</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Anggota DPR RI Bambang Haryo Soekartono (BHS) menyatakan waktu tanggap (response time) penyelamatan terhadap ...</t>
+          <t>Presiden Prabowo Subianto menerima laporan terbaru dari Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil ...</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677380/anggota-dpr-penyelematan-korban-kapal-terbakar-di-sumenep-harus-cepat</t>
+          <t>https://www.antaranews.com/berita/5677561/prabowo-terima-laporan-bahlil-soal-program-ketahanan-energi</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1319103.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_5125.jpeg</t>
         </is>
       </c>
     </row>
@@ -2093,28 +2094,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>KPK periksa Kadis PUPR Kota Bengkulu usai geledah dan sita Rp4 miliar</t>
+          <t>Menlu Iran sebut pembicaraan soal Selat Hormuz dengan Oman masuki tahap akhir</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:46:34 +0700</t>
+          <t>Mon, 03 Aug 2026 16:01:55 +0700</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Komisi Pemberantasan Korupsi memeriksa Kepala Dinas Pekerjaan Umum dan Penataan Ruang (PUPR) Kota Bengkulu Noprisman ...</t>
+          <t>Menteri Luar Negeri Iran Abbas Araghchi  mengatakan pembicaraan soal Selat Hormuz dengan Oman masuki tahap ...</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677377/kpk-periksa-kadis-pupr-kota-bengkulu-usai-geledah-dan-sita-rp4-miliar</t>
+          <t>https://www.antaranews.com/berita/5677557/menlu-iran-sebut-pembicaraan-soal-selat-hormuz-dengan-oman-masuki-tahap-akhir</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_7724.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/HormuzXinhuaWangQiang_aa.jpg</t>
         </is>
       </c>
     </row>
@@ -2126,28 +2127,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pengaruh makan timun terhadap kesehatan tubuh</t>
+          <t>Wamendiktisaintek dorong kampus di Riau dan Kepri bangun konsorsium</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:45:30 +0700</t>
+          <t>Mon, 03 Aug 2026 16:01:51 +0700</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Profesor madya di bidang nutrisi dan kesehatan masyarakat dari Fakultas Kedokteran Universitas Tufts Kimberly Dong ...</t>
+          <t>Wakil Menteri Pendidikan Tinggi, Sains, dan Teknologi (Wamendiktisaintek) Fauzan mendorong perguruan tinggi di Provinsi ...</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677375/pengaruh-makan-timun-terhadap-kesehatan-tubuh</t>
+          <t>https://www.antaranews.com/berita/5677555/wamendiktisaintek-dorong-kampus-di-riau-dan-kepri-bangun-konsorsium</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2022/11/03/antarafoto-pasokan-buah-timun-terdampak-cuaca-di-pulau-bacan-3112022-ans-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/18/1000428031.jpg</t>
         </is>
       </c>
     </row>
@@ -2159,127 +2160,127 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Jaksel catat mobil klinik hewan layani 226 ekor kucing hingga domba</t>
+          <t>Partai Buruh Brasil calonkan Lula da Silva untuk masa jabatan keempat</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:38:38 +0700</t>
+          <t>Mon, 03 Aug 2026 16:01:22 +0700</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Suku Dinas Ketahanan Pangan, Kelautan, dan Pertanian Jakarta Selatan (KPKP Jaksel) mencatat Mobil Klinik Hewan ...</t>
+          <t>ANTARA - Partai Buruh di Brasil pada Minggu (2/8) waktu setempat, resmi mencalonkan petahana Luiz Inacio Lula da Silva ...</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677369/jaksel-catat-mobil-klinik-hewan-layani-226-ekor-kucing-hingga-domba</t>
+          <t>https://www.antaranews.com/video/5677541/partai-buruh-brasil-calonkan-lula-da-silva-untuk-masa-jabatan-keempat</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001010031.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-03-154005.jpg</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>lifestyle, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10 ide lomba 17 Agustus untuk anak PAUD dan TK yang seru, edukatif, dan mudah digelar</t>
+          <t>Program konservasi Pulau Sabira PLN raih penghargaan nasional</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:38:29 +0700</t>
+          <t>Mon, 03 Aug 2026 16:00:04 +0700</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Perayaan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 dapat menjadi momen bagi anak usia PAUD dan TK ...</t>
+          <t>PT PLN (Persero) Unit Induk Distribusi (UID) Jakarta Raya meraih penghargaan "Predikat Platinum Alignment" ...</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677368/10-ide-lomba-17-agustus-untuk-anak-paud-dan-tk-yang-seru-edukatif-dan-mudah-digelar</t>
+          <t>https://www.antaranews.com/berita/5677551/program-konservasi-pulau-sabira-pln-raih-penghargaan-nasional</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/08/03/WhatsApp-Image-2024-08-03-at-20.37.28.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/e9219a6c-ccd6-473e-bf06-a7dd465568bd.jpeg</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini, top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kemnaker: Magang Nasional diharapkan menekan angka pengangguran muda</t>
+          <t>Pemkot Ambon salurkan air bersih gratis jika kekeringan terjadi</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:37:57 +0700</t>
+          <t>Mon, 03 Aug 2026 15:59:59 +0700</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kementerian Ketenagakerjaan (Kemnaker) mengatakan program Magang Nasional (MagangHub) untuk mempersiapkan kompetensi ...</t>
+          <t>ANTARA - Pemerintah Kota Ambon, Maluku, menyiapkan langkah antisipasi untuk menjamin ketersediaan air bersih bagi ...</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677364/kemnaker-magang-nasional-diharapkan-menekan-angka-pengangguran-muda</t>
+          <t>https://www.antaranews.com/video/5677489/pemkot-ambon-salurkan-air-bersih-gratis-jika-kekeringan-terjadi</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/ff63afaf-7778-47fe-833d-5a8068af9a51_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-03-151844.jpg</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>terkini, top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Kemenag perkuat transformasi madrasah lewat revitalisasi-digitalisasi</t>
+          <t>Razia balap liar, Polres Temanggung sita 106 motor</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:36:36 +0700</t>
+          <t>Mon, 03 Aug 2026 15:58:54 +0700</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Menteri Agama (Menag) Nasaruddin Umar menegaskan transformasi madrasah terus diperkuat melalui revitalisasi ...</t>
+          <t>ANTARA - Kepolisian Resor (Polres) Temanggung, Jawa Tengah menyita 106 sepeda motor dalam razia balap liar yang digelar ...</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677363/kemenag-perkuat-transformasi-madrasah-lewat-revitalisasi-digitalisasi</t>
+          <t>https://www.antaranews.com/video/5677488/razia-balap-liar-polres-temanggung-sita-106-motor</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/14/1000173935_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_RAZIA-BALAP-LIAR-POLRES-TEMANGGUNG-SITA-106-MOTOR.jpg</t>
         </is>
       </c>
     </row>
@@ -2291,127 +2292,127 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Wali Kota pastikan fasilitas SRT Kendari dukung perkembangan siswa</t>
+          <t>Pemain muda Barcelona incar tempat di tim utama 2026/2027</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:36:17 +0700</t>
+          <t>Mon, 03 Aug 2026 15:57:56 +0700</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Wali Kota Kendari Siska Karina Imran memastikan bahwa fasilitas yang ada di Sekolah Rakyat Terintegrasi (SRT) 2 Kota ...</t>
+          <t>Para pemain muda Barcelona, khususnya yang kini memperkuat Barcelona Atletic (Barcelona B), mengincar tempat di tim ...</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677359/wali-kota-pastikan-fasilitas-srt-kendari-dukung-perkembangan-siswa</t>
+          <t>https://www.antaranews.com/berita/5677547/pemain-muda-barcelona-incar-tempat-di-tim-utama-2026-2027</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/aeea98a9-b62b-4a35-a533-805d3c8ac339.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_154443.jpg</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>lifestyle, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sering terbangun tengah malam? Kenali 7 penyebab dan cara mengatasinya</t>
+          <t>HYBE siapkan debut girl group Tuide</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:35:20 +0700</t>
+          <t>Mon, 03 Aug 2026 15:57:13 +0700</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bangun di tengah malam sesekali merupakan hal yang normal. Namun, jika kondisi ini terjadi hampir setiap malam dan ...</t>
+          <t>Perusahaan hiburan Korea Selatan, HYBE melalui label naungannya ABD tengah mempersiapkan debut girl group Kpop bernama ...</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677357/sering-terbangun-tengah-malam-kenali-7-penyebab-dan-cara-mengatasinya</t>
+          <t>https://www.antaranews.com/berita/5677544/hybe-siapkan-debut-girl-group-tuide</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/20/Penumpang-rela-menginap-menunggu-kereta-pertama-di-Stasiun-Cikarang-150726-ryl-5.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/644817de-49b2-42cd-92a5-0d0a14d911ce.jpeg</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini, top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lisensi IP Global Buka Peluang Bisnis Baru bagi Kreator Indonesia</t>
+          <t>Pemkot Jakut edukasi pelajar tentang teknik pertanian di perkotaan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:34:30 +0700</t>
+          <t>Mon, 03 Aug 2026 15:52:39 +0700</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Wakil Menteri Ekonomi Kreatif Irene Umar mengatakan kolaborasi antara pemilik kekayaan intelektual (Intellectual ...</t>
+          <t>Suku Dinas Ketahanan Pangan, Kelautan dan Pertanian (KPKP) Jakarta Utara mengedukasi puluhan pelajar dari enam sekolah ...</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677353/lisensi-ip-global-buka-peluang-bisnis-baru-bagi-kreator-indonesia</t>
+          <t>https://www.antaranews.com/berita/5677540/pemkot-jakut-edukasi-pelajar-tentang-teknik-pertanian-di-perkotaan</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000589873.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/2dfab961fe56.jpeg</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>photo, terkini</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Gempa bermagnitudo 5,3 guncang Mesir timur laut</t>
+          <t>Jelang HUT RI, Polda Kepri bagikan bendera ke warga di pulau-pulau terluar</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:32:32 +0700</t>
+          <t>Mon, 03 Aug 2026 15:51:09 +0700</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sebuah gempa bermagnitudo 5,3 mengguncang Provinsi Ismailia di Mesir timur laut pada Senin pagi waktu setempat, menurut ...</t>
+          <t>Warga memasang Bendera Merah Putih di perahu serta pekarangan rumah panggung yang dibagikan Polda Kepri di Pulau Dapur ...</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677351/gempa-bermagnitudo-53-guncang-mesir-timur-laut</t>
+          <t>https://www.antaranews.com/foto/5677539/jelang-hut-ri-polda-kepri-bagikan-bendera-ke-warga-di-pulau-pulau-terluar</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/18/ilustrasi-gempa-2_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Pembagian-Bendera-Merah-Putih-Di-Pulau-Pulau-Terluar-030826-tpp-2.jpg</t>
         </is>
       </c>
     </row>
@@ -2423,28 +2424,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dedi Kusnandar: Persib siap hadapi Persija di semifinal Piala Presiden</t>
+          <t>Pelindo siagakan posko terpadu bagi korban KMP Mutiara Sentosa II</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:31:31 +0700</t>
+          <t>Mon, 03 Aug 2026 15:45:16 +0700</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Gelandang Persib Bandung Dedi Kusnandar menegaskan timnya siap menghadapi Persija Jakarta pada babak semifinal Piala ...</t>
+          <t>PT Pelabuhan Indonesia (Persero) Regional 3 Sub Regional Jawa menyiagakan posko terpadu korban kebakaran Kapal Motor ...</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677349/dedi-kusnandar-persib-siap-hadapi-persija-di-semifinal-piala-presiden</t>
+          <t>https://www.antaranews.com/berita/5677537/pelindo-siagakan-posko-terpadu-bagi-korban-kmp-mutiara-sentosa-ii</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_9111.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/260405.jpg</t>
         </is>
       </c>
     </row>
@@ -2456,28 +2457,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Wakil Ketua DPR salurkan beasiswa PIP ke ribuan pelajar Lombok Timur</t>
+          <t>MPR undang Presiden Prabowo hadiri sidang tahunan pada 14 Agustus</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:30:16 +0700</t>
+          <t>Mon, 03 Aug 2026 15:43:18 +0700</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wakil Ketua DPR RI Sari Yuliati menyerahkan bantuan beasiswa Program Indonesia Pintar (PIP) 2026 kepada ribuan pelajar ...</t>
+          <t>Pimpinan MPR mengundang Presiden Prabowo Subianto menghadiri Sidang Tahunan MPR yang rencananya digelar pada Jumat, 14 ...</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677345/wakil-ketua-dpr-salurkan-beasiswa-pip-ke-ribuan-pelajar-lombok-timur</t>
+          <t>https://www.antaranews.com/berita/5677536/mpr-undang-presiden-prabowo-hadiri-sidang-tahunan-pada-14-agustus</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1005724306.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000398675.jpg</t>
         </is>
       </c>
     </row>
@@ -2489,61 +2490,61 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Dinkop UKM Cilegon targetkan 21 gerai baru KKMP beroperasi September</t>
+          <t>Kesbangpol Pontianak antisipasi konflik sosial akibat karhutla</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:27:17 +0700</t>
+          <t>Mon, 03 Aug 2026 15:42:51 +0700</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ANTARA - Dinas Koperasi Usaha Kecil dan Menengah (Dinkop UKM) Kota Cilegon menargetkan pembangunan  21 gedung ...</t>
+          <t>ANTARA - Badan Kesatuan Bangsa dan Politik (Kesbangpol) Kota Pontianak mengidentifikasi potensi gangguan keamanan dan ...</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5677301/dinkop-ukm-cilegon-targetkan-21-gerai-baru-kkmp-beroperasi-september</t>
+          <t>https://www.antaranews.com/video/5677519/kesbangpol-pontianak-antisipasi-konflik-sosial-akibat-karhutla</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/DINKOP-UKM-CILEGON-TARGETKAN-21-GERAI-BARU-KKMP-BEROPERASI-SEPTEMBER.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KESBANGPOL-PONTIANAK-ANTISIPASI-KONFLIK-SOSIAL-AKIBAT-KARHUTLA.jpg</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>humaniora, terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bantuan beras 30 kg cair mulai 17 Agustus 2026, ini jadwal dan cara cek penerimanya</t>
+          <t>Data untuk Indonesia, bakti untuk negeri</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:27:14 +0700</t>
+          <t>Mon, 03 Aug 2026 15:42:25 +0700</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Pemerintah memastikan penyaluran bantuan pangan beras tahap II tahun 2026 akan dimulai pada 17 Agustus 2026. Bantuan ...</t>
+          <t>Bulan Agustus selalu menghadirkan suasana yang berbeda. Bendera Merah Putih berkibar di halaman rumah, berbagai ...</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677341/bantuan-beras-30-kg-cair-mulai-17-agustus-2026-ini-jadwal-dan-cara-cek-penerimanya</t>
+          <t>https://www.antaranews.com/berita/5677535/data-untuk-indonesia-bakti-untuk-negeri</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/26/kemensos-percepat-penyaluran-bansos-pkh-dan-bpnt-2778877.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/1001511288.jpg</t>
         </is>
       </c>
     </row>
@@ -2555,28 +2556,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Puluhan santri Ponpes Darul Amanah Kendal kunjungi Istana Presiden</t>
+          <t>Prabowo: Persatuan selalu terlihat saat timnas Indonesia bermain</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:24:08 +0700</t>
+          <t>Mon, 03 Aug 2026 15:40:54 +0700</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Puluhan santri beserta pengajar Pondok Pesantren Darul Amanah Sukorejo, Kendal, Jawa Tengah, melakukan kunjungan ...</t>
+          <t>Presiden Republik Indonesia Prabowo Subianto mengaku selalu melihat persatuan setiap kali timnas Indonesia ...</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677337/puluhan-santri-ponpes-darul-amanah-kendal-kunjungi-istana-presiden</t>
+          <t>https://www.antaranews.com/berita/5677532/prabowo-persatuan-selalu-terlihat-saat-timnas-indonesia-bermain</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_3918.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0003_3.jpg</t>
         </is>
       </c>
     </row>
@@ -2588,2891 +2589,4309 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cek fakta, Pemprov Jabar resmi adakan kembali SPP untuk sekolah negeri pada Juli 2026</t>
+          <t>PSEL Serang Raya jadi solusi pengelolaan sampah tiga daerah</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:23:04 +0700</t>
+          <t>Mon, 03 Aug 2026 15:40:46 +0700</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Jakarta (ANTARA/JACX) – Sebuah unggahan di Facebook menarasikan bahwa Pemerintah Provinsi Jawa Barat ...</t>
+          <t>ANTARA - Fasilitas Pengolahan Sampah menjadi Energi Listrik (PSEL) Serang Raya akan dibangun di TPSA Cilowong, Kota ...</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677333/cek-fakta-pemprov-jabar-resmi-adakan-kembali-spp-untuk-sekolah-negeri-pada-juli-2026</t>
+          <t>https://www.antaranews.com/video/5677492/psel-serang-raya-jadi-solusi-pengelolaan-sampah-tiga-daerah</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/17/WhatsApp-Image-2026-06-17-at-20.14.04.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AYM_PSEL-SERANG-RAYA-JADI-SOLUSI-PENGELOLAAN-SAMPAH.jpg</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>lifestyle, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Bahaya paparan pornografi pada anak: Dampak bagi otak, mental, dan perilaku</t>
+          <t>Dewas KPK sempurnakan Perdewas untuk atur etik PNYD hingga potong gaji</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:23:03 +0700</t>
+          <t>Mon, 03 Aug 2026 15:39:59 +0700</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Perkembangan teknologi membuat anak-anak dan remaja semakin akrab dengan internet sejak usia dini. Di satu sisi, ...</t>
+          <t>Dewan Pengawas Komisi Pemberantasan Korupsi (Dewas KPK) tengah menyempurnakan peraturan Dewas KPK (Perdewas) untuk ...</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677332/bahaya-paparan-pornografi-pada-anak-dampak-bagi-otak-mental-dan-perilaku</t>
+          <t>https://www.antaranews.com/berita/5677531/dewas-kpk-sempurnakan-perdewas-untuk-atur-etik-pnyd-hingga-potong-gaji</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/02/ilustrasi-konten-berbau-pornografi.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_8184.jpg</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nilai ekspor perdagangan RI Januari-Juni capai 140,81 miliar dolar AS</t>
+          <t>Kelurahan Dukuh Jaktim perketat pengawasan TPS liar pascakebakaran</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:16:17 +0700</t>
+          <t>Mon, 03 Aug 2026 15:39:50 +0700</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat nilai ekspor Indonesia secara kumulatif dari Januari-Juni 2026 mencapai 140,81 ...</t>
+          <t>Kelurahan Dukuh, Jakarta Timur, bersama pengurus RT 013 dan RW 03 memperketat pengawasan tempat penampungan sementara ...</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677315/nilai-ekspor-perdagangan-ri-januari-juni-capai-14081-miliar-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5677527/kelurahan-dukuh-jaktim-perketat-pengawasan-tps-liar-pascakebakaran</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/neraca-perdagangan-januari-mei-2026-surplus-2815779.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/InShot_20260803_145658796.jpg</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Korban KMP Mutiara Sentosa II dievakuasi ke Pelabuhan Tanjung Perak</t>
+          <t>BPBD Sulbar intensifkan edukasi pencegahan karhutla</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:06:15 +0700</t>
+          <t>Mon, 03 Aug 2026 15:38:10 +0700</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Tim SAR gabungan terus melakukan evakuasi korban terbakarnya KMP Mutiara Sentosa 2 ke darat, tepatnya ke Pelabuhan ...</t>
+          <t>Badan Penanggulangan Bencana Daerah (BPBD) Provinsi Sulawesi Barat mengintensifkan edukasi dan peningkatan kesadaran ...</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677297/korban-kmp-mutiara-sentosa-ii-dievakuasi-ke-pelabuhan-tanjung-perak</t>
+          <t>https://www.antaranews.com/berita/5677523/bpbd-sulbar-intensifkan-edukasi-pencegahan-karhutla</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/260821.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260309_224833.jpg</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Aktor senior Diding Boneng meninggal dunia</t>
+          <t>Presiden Prabowo memandang Indonesia layak tampil di Piala Dunia 2030</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:39:03 +0700</t>
+          <t>Mon, 03 Aug 2026 15:35:54 +0700</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aktor sekaligus komedian tanah air, Zainal Abidin alias Diding Boneng dikabarkan meninggal dunia pada Senin (3/8) dalam ...</t>
+          <t>Presiden Republik Indonesia Prabowo Subianto dalam pidatonya pada pembukaan Kongres Biasa PSSI 2026 di Jakarta, Senin, ...</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677209/aktor-senior-diding-boneng-meninggal-dunia</t>
+          <t>https://www.antaranews.com/berita/5677516/presiden-prabowo-memandang-indonesia-layak-tampil-di-piala-dunia-2030</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/26f1eb88-3301-4ae1-badd-bed5078fe3dd.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0004.jpg</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Seskab: Prabowo dorong sinergi pemerintah dan dunia usaha</t>
+          <t>BPK dorong kementerian terapkan prinsip ESG dalam pengelolaan anggaran</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:17:50 +0700</t>
+          <t>Mon, 03 Aug 2026 15:35:12 +0700</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sekretaris Kabinet Teddy Indra Wijaya menyampaikan bahwa Presiden Prabowo Subianto menekankan pentingnya sinergi antara ...</t>
+          <t>Badan Pemeriksa Keuangan (BPK) RI mendorong kementerian dan lembaga mulai menerapkan prinsip Environmental, Social, and ...</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677191/seskab-prabowo-dorong-sinergi-pemerintah-dan-dunia-usaha</t>
+          <t>https://www.antaranews.com/berita/5677512/bpk-dorong-kementerian-terapkan-prinsip-esg-dalam-pengelolaan-anggaran</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0891.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001216419.jpg</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Red Velvet bersiap kembali lewat EP baru "Velvet Summer"</t>
+          <t>BNPB: 1.485 jiwa terdampak kebakaran TPA Troketon Klaten</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:24:37 +0700</t>
+          <t>Mon, 03 Aug 2026 15:33:32 +0700</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Grup idola K-pop Red Velvet akan kembali lewat rilis mini album atau extended play (EP) baru bertajuk “Velvet ...</t>
+          <t>Badan Nasional Penanggulangan Bencana (BNPB) mengoordinasikan penanganan dampak kebakaran Tempat Pemrosesan Akhir (TPA) ...</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677151/red-velvet-bersiap-kembali-lewat-ep-baru-velvet-summer</t>
+          <t>https://www.antaranews.com/berita/5677509/bnpb-1485-jiwa-terdampak-kebakaran-tpa-troketon-klaten</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/ca97a3a8-aa17-45fc-be71-d36051dd9dcd.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/10/16/33.jpg</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Menaker pastikan komitmen pemerintah perkuat kesejahteraan pekerja</t>
+          <t>Menkomdigi sebut kreator rekam konten tanpa izin langgar UU PDP</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:16:19 +0700</t>
+          <t>Mon, 03 Aug 2026 15:32:10 +0700</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Menteri Ketenagakerjaan (Menaker) Yassierli memastikan pemerintah berkomitmen untuk memperkuat kesejahteraan, ...</t>
+          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid menyebutkan kreator konten yang merekam video tanpa ...</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677148/menaker-pastikan-komitmen-pemerintah-perkuat-kesejahteraan-pekerja</t>
+          <t>https://www.antaranews.com/berita/5677508/menkomdigi-sebut-kreator-rekam-konten-tanpa-izin-langgar-uu-pdp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/09/20/pelepasan-peserta-pemagangan-ke-jepang-di-jawa-barat-2627513.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0252.jpg</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>23 calon hakim agung dan ad hoc ikuti seleksi wawancara akhir</t>
+          <t>Survei LKPI: Kepuasan publik terhadap Prabowo capai 79,3 persen</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:15:01 +0700</t>
+          <t>Mon, 03 Aug 2026 15:31:44 +0700</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sebanyak 23 orang calon hakim agung dan ad hoc Mahkamah Agung Tahun 2026 mengikuti seleksi wawancara tahap akhir di ...</t>
+          <t>Survei Lembaga Kajian Pemilu Indonesia (LKPI) menunjukkan tingkat kepuasan publik terhadap kinerja Presiden Prabowo ...</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677137/23-calon-hakim-agung-dan-ad-hoc-ikuti-seleksi-wawancara-akhir</t>
+          <t>https://www.antaranews.com/berita/5677504/survei-lkpi-kepuasan-publik-terhadap-prabowo-capai-793-persen</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000012883_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG_3632.jpeg</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BRIN perkuat kajian sungai bawah tanah di Kebumen untuk ketahanan air</t>
+          <t>KONI Pusat harap Kongres Biasa PSSI diskusikan pembinaan prestasi</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:57:19 +0700</t>
+          <t>Mon, 03 Aug 2026 15:29:28 +0700</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Badan Riset dan Inovasi Nasional (BRIN) memperkuat riset ketahanan air melalui pengembangan teknologi dan penelitian ...</t>
+          <t>Ketua Umum Komite Olahraga Nasional Indonesia (KONI) Pusat Letjen TNI Purn. Marciano Norman berharap Kongres Biasa ...</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677120/brin-perkuat-kajian-sungai-bawah-tanah-di-kebumen-untuk-ketahanan-air</t>
+          <t>https://www.antaranews.com/berita/5677500/koni-pusat-harap-kongres-biasa-pssi-diskusikan-pembinaan-prestasi</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1785706440-47672950-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/11/Ketua-KONI-Pusat-Marciano-Norman.jpg</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Harga bensin turun pada pekan pertama Agustus</t>
+          <t>KPK panggil anggota DPR RI Anwar Sadad pada kasus dana hibah Jatim</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:51:00 +0700</t>
+          <t>Mon, 03 Aug 2026 15:28:20 +0700</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Harga bahan bakar minyak (BBM) jenis bensin di stasiun pengisian bahan bakar umum (SPBU) Pertamina, Shell, dan bp ...</t>
+          <t>Komisi Pemberantasan Korupsi (KPK) memanggil anggota DPR RI Anwar Sadad (AS) untuk diperiksa dalam penyidikan kasus ...</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677109/harga-bensin-turun-pada-pekan-pertama-agustus</t>
+          <t>https://www.antaranews.com/berita/5677496/kpk-panggil-anggota-dpr-ri-anwar-sadad-pada-kasus-dana-hibah-jatim</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/10/02/penuruanan-harga-bbm-011024-aaa-7.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/07/23/IMG-20230723-WA0032.jpg</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Sean Gelael berbagi pengalaman di dunia balap ke pengunjung GIIAS 2026</t>
+          <t>Ditjenpas Kaltim gelar CKG bagi 12 ribu warga binaan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:34:53 +0700</t>
+          <t>Mon, 03 Aug 2026 15:23:58 +0700</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Pembalap Indonesia Sean Gelael berbagi pengalamannya di dunia balap ke pengunjung GAIKINDO Indonesia International ...</t>
+          <t>ANTARA - Program Cek Kesehatan Gratis (CKG) menyasar warga binaan di Lembaga Pemasyarakatan (Lapas) dan Rumah Tahanan ...</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677103/sean-gelael-berbagi-pengalaman-di-dunia-balap-ke-pengunjung-giias-2026</t>
+          <t>https://www.antaranews.com/video/5677480/ditjenpas-kaltim-gelar-ckg-bagi-12-ribu-warga-binaan</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/16b70b87-326f-479a-a806-580ab846cc6f_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AYM_DITJENPAS-KALTIM-GELAR-CKG.jpg</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ekonomi-bursa, top-news</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IHSG Senin dibuka menguat 36,49 poin ke posisi 6.272</t>
+          <t>BPS prediksi produksi beras RI 28,71 juta ton hingga September 2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:11:26 +0700</t>
+          <t>Mon, 03 Aug 2026 15:23:12 +0700</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin pagi dibuka menguat 36,49 poin atau 0,59 ...</t>
+          <t>Badan Pusat Statistik (BPS) memprediksi produksi beras sepanjang Januari–September 2026 mencapai 28,71 juta ton, ...</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677071/ihsg-senin-dibuka-menguat-3649-poin-ke-posisi-6272</t>
+          <t>https://www.antaranews.com/berita/5677485/bps-prediksi-produksi-beras-ri-2871-juta-ton-hingga-september-2026</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/pergerakan-indeks-harga-saham-gabungan-2828631.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/proyeksi-produksi-beras-konsumsi-2815573.jpg</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PLN Jakarta pastikan pasokan listrik sudah berhasil dipulihkan</t>
+          <t>Polda Jatim kerahkan 30 personel evakuasi KMP Mutiara Sentosa 2</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 08:36:26 +0700</t>
+          <t>Mon, 03 Aug 2026 15:22:46 +0700</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>PT PLN (Persero) Unit Induk Distribusi Jakarta Raya mengungkapkan pasokan listrik telah berhasil ...</t>
+          <t>Kepolisian Daerah (Polda) Jawa Timur (Jatim) mengerahkan 30 personel SAR Direktorat Kepolisian Perairan dan Udara ...</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677043/pln-jakarta-pastikan-pasokan-listrik-sudah-berhasil-dipulihkan</t>
+          <t>https://www.antaranews.com/berita/5677483/polda-jatim-kerahkan-30-personel-evakuasi-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20231217-WA0015-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1319202.jpg</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ledakan di kantor polisi Pakistan tewaskan 14 orang</t>
+          <t>Komisi IX DPR: Putusan MK jadi momentum BGN desain ulang MBG</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 07:44:23 +0700</t>
+          <t>Mon, 03 Aug 2026 15:19:16 +0700</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sebuah ledakan terjadi di luar sebuah kantor polisi di Kota Kabal, Pakistan, mengakibatkan 14 orang tewas dan 14 orang ...</t>
+          <t>Wakil Ketua Komisi IX DPR RI Charles Honoris mengatakan putusan Mahkamah Konstitusi Nomor 40/PUU-XXIV/2026 menjadi ...</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677020/ledakan-di-kantor-polisi-pakistan-tewaskan-14-orang</t>
+          <t>https://www.antaranews.com/berita/5677477/komisi-ix-dpr-putusan-mk-jadi-momentum-bgn-desain-ulang-mbg</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CmxztpE000019_20260803_PEPFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/15/tempImageigZXJC.jpg</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ratusan korban selamat KMP Mutiara Santosa 2 tiba di Tanjung Perak</t>
+          <t>Ke Jepara, Mendikdasmen: Lahan SNT harus benar-benar siap dikembangkan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:37:38 +0700</t>
+          <t>Mon, 03 Aug 2026 15:17:55 +0700</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sebanyak 111 korban selamat dan dua meninggal dunia akibat kebakaran KMP Mutiara Santosa II di Perairan Utara ...</t>
+          <t>Menteri Pendidikan Dasar dan Menengah (Mendikdasmen) Abdul Mu’ti meninjau langsung kesiapan lahan untuk ...</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676983/ratusan-korban-selamat-kmp-mutiara-santosa-2-tiba-di-tanjung-perak</t>
+          <t>https://www.antaranews.com/berita/5677475/ke-jepara-mendikdasmen-lahan-snt-harus-benar-benar-siap-dikembangkan</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/259549_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/21/1000216743.jpg</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Sebagian Jakarta diguyur hujan ringan pada Senin sore hingga malam</t>
+          <t>Jepang dan AS lakukan intervensi bersama di pasar valuta asing</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:11:02 +0700</t>
+          <t>Mon, 03 Aug 2026 15:17:09 +0700</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) memprakirakan hujan ringan akan melanda sebagian wilayah Jakarta ...</t>
+          <t>Menteri Keuangan Satsuki Katayama mengatakan bahwa Jepang dan Amerika Serikat telah melakukan intervensi pembelian yen ...</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676963/sebagian-jakarta-diguyur-hujan-ringan-pada-senin-sore-hingga-malam</t>
+          <t>https://www.antaranews.com/berita/5677472/jepang-dan-as-lakukan-intervensi-bersama-di-pasar-valuta-asing</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/01/IMG_20260301_073711.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CjkinzN000009_20260803_CBMFN0A001.jpeg</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Atlet-atlet nasional borong 18 medali Poomsae Indonesia Open 2026</t>
+          <t>TNI AU dan AU Kamboja perkuat hubungan dengan jalin kerja sama militer</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 04:18:40 +0700</t>
+          <t>Mon, 03 Aug 2026 15:15:59 +0700</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Atlet-atlet tuan rumah Indonesia tampil impresif pada nomor Poomsae 8th Asian Taekwondo, Indonesia Open ...</t>
+          <t>TNI Angkatan Udara (AU) memperkuat hubungan dengan AU Kamboja atau Cambodian Air Force (CAF) dengan menyepakati ...</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676947/atlet-atlet-nasional-borong-18-medali-poomsae-indonesia-open-2026</t>
+          <t>https://www.antaranews.com/berita/5677468/tni-au-dan-au-kamboja-perkuat-hubungan-dengan-jalin-kerja-sama-militer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships-2026-020826-dr-04.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001554368.jpg</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Kemenhub kerahkan kapal patroli evakuasi KM Mutiara Sentosa II</t>
+          <t>KPK geledah tujuh lokasi pada 30 Juli-1 Agustus terkait kasus Pemalang</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 00:03:37 +0700</t>
+          <t>Mon, 03 Aug 2026 15:14:49 +0700</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kementerian Perhubungan mengerahkan kapal patroli Kesatuan Penjagaan Laut dan Pantai (KPLP) serta memperkuat koordinasi ...</t>
+          <t>Komisi Pemberantasan Korupsi (KPK) menggeledah tujuh lokasi pada 30 Juli–1 Agustus 2026 terkait penyidikan kasus ...</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676931/kemenhub-kerahkan-kapal-patroli-evakuasi-km-mutiara-sentosa-ii</t>
+          <t>https://www.antaranews.com/berita/5677465/kpk-geledah-tujuh-lokasi-pada-30-juli-1-agustus-terkait-kasus-pemalang</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/kpk-tahan-bupati-pemalang-2830443.jpg</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Rupiah diperkirakan menguat seiring AS batalkan rencana serang Iran</t>
+          <t>Paus Leo XIV prihatin atas situasi krisis migran di Ceuta</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:12:26 +0700</t>
+          <t>Mon, 03 Aug 2026 15:14:34 +0700</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Analis Doo Financial Futures, Lukman Leong memperkirakan rupiah menguat seiring Amerika Serikat (AS) membatalkan ...</t>
+          <t>ANTARA - Paus Leo XIV  menyampaikan keprihatinan atas situasi krisis migran di Enklave, Spanyol, Ceuta.  Saat ...</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677132/rupiah-diperkirakan-menguat-seiring-as-batalkan-rencana-serang-iran</t>
+          <t>https://www.antaranews.com/video/5677384/paus-leo-xiv-prihatin-atas-situasi-krisis-migran-di-ceuta</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828847.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AYM_PAUS-LEO-XIV-PRIHATIN-ATAS-SITUASI-KRISIS.jpg</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Rupiah pada Senin pagi melemah jadi Rp18.031 per dolar AS</t>
+          <t>BMKG: Musim kemarau Papua Pegunungan bakal berakhir pada akhir Agustus</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:05:50 +0700</t>
+          <t>Mon, 03 Aug 2026 15:07:50 +0700</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Nilai tukar rupiah pada Senin pagi bergerak melemah 9 poin atau 0,05 persen menjadi Rp18.031 per dolar AS dibandingkan ...</t>
+          <t>Badan Meteorologi, Klimatologi dan Geofisika (BMKG) melalui Stasiun Meteorologi Kelas III Wamena, Kabupaten Jayawijaya, ...</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677063/rupiah-pada-senin-pagi-melemah-jadi-rp18031-per-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5677463/bmkg-musim-kemarau-papua-pegunungan-bakal-berakhir-pada-akhir-agustus</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260730-WA0008.jpg</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Komisi XI: PFII peluang RI tangkap momentum perpindahan modal global</t>
+          <t>Koalisi buruh serahkan usulan RUU Ketenagakerjaan ke pimpinan DPR</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:53:34 +0700</t>
+          <t>Mon, 03 Aug 2026 15:05:55 +0700</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Wakil Ketua Komisi XI DPR RI Mohamad Hekal mengatakan percepatan pembentukan Pusat Finansial Internasional Indonesia ...</t>
+          <t>Koalisi dari berbagai konfederasi buruh menyerahkan draf usulan untuk penyusunan Rancangan Undang-Undang (RUU) ...</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676995/komisi-xi-pfii-peluang-ri-tangkap-momentum-perpindahan-modal-global</t>
+          <t>https://www.antaranews.com/berita/5677460/koalisi-buruh-serahkan-usulan-ruu-ketenagakerjaan-ke-pimpinan-dpr</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Saham-dan-oblogasi.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001295553.jpg</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BUMA International Group bukukan pertumbuhan EBITDA semester I/2026</t>
+          <t>BPS catat pengeluaran wisman triwulan II-2026 mencapai 1.285 dolar AS</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:17:40 +0700</t>
+          <t>Mon, 03 Aug 2026 14:56:12 +0700</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>PT BUMA Internasional Gorup membukukan pertumbuhan EBITDA pada semester pertama 2026 (1H26) di tengah penurunan ...</t>
+          <t>Badan Pusat Statistik (BPS) mencatat perkembangan pengeluaran wisatawan mancanegara (wisman) pada triwulan II tahun ...</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676967/buma-international-group-bukukan-pertumbuhan-ebitda-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5677457/bps-catat-pengeluaran-wisman-triwulan-ii-2026-mencapai-1285-dolar-as</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/buma.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG-20260731-WA0028.jpg</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BPS catat nilai tukar petani di level 127,84 pada Juli 2026</t>
+          <t>Charles Honoris dorong putusan MK soal MBG diterapkan pada APBN 2027</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:18:40 +0700</t>
+          <t>Mon, 03 Aug 2026 14:56:05 +0700</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat nilai tukar petani (NTP) secara nasional pada bulan Juli 2026 berada di level ...</t>
+          <t>Wakil Ketua Komisi IX DPR RI Charles Honoris mendorong putusan Mahkamah Konstitusi (MK) mengenai anggaran program Makan ...</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677323/bps-catat-nilai-tukar-petani-di-level-12784-pada-juli-2026</t>
+          <t>https://www.antaranews.com/berita/5677456/charles-honoris-dorong-putusan-mk-soal-mbg-diterapkan-pada-apbn-2027</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/02/20260302_083324.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/upscalemedia-transformed-167.jpeg</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Menteri ATR sebut 400 Kantah sudah terapkan pengukuran terjadwal</t>
+          <t>Wamensos: Kolaborasi data perkuatkan bantuan JKN lebih akuntabel</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:13:29 +0700</t>
+          <t>Mon, 03 Aug 2026 14:54:53 +0700</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Menteri Agraria dan Tata Ruang/Kepala Badan Pertanahan Nasional (ATR/BPN) Nusron Wahid mengatakan bahwa sudah ada 400 ...</t>
+          <t>Wakil Menteri Sosial (Wamensos) Agus Jabo Priyono mengatakan kolaborasi strategis yang dilakukan bersama BPJS ...</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677308/menteri-atr-sebut-400-kantah-sudah-terapkan-pengukuran-terjadwal</t>
+          <t>https://www.antaranews.com/berita/5677453/wamensos-kolaborasi-data-perkuatkan-bantuan-jkn-lebih-akuntabel</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_125328.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-14.44.56-1.jpeg</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PT PAL-BRIN wujudkan galangan kapal hijau dukung industri perkapalan</t>
+          <t>Presiden Iran: AS harus tetap patuhi nota kesepahaman</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:43:28 +0700</t>
+          <t>Mon, 03 Aug 2026 14:54:11 +0700</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>PT PAL Indonesia bersama Badan Riset dan Inovasi Nasional (BRIN) berkolaborasi mewujudkan transformasi green ...</t>
+          <t>Presiden Iran Masoud Pezeshkian mengatakan pada Minggu (2/8) bahwa Amerika Serikat harus tetap berkomitmen pada nota ...</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677267/pt-pal-brin-wujudkan-galangan-kapal-hijau-dukung-industri-perkapalan</t>
+          <t>https://www.antaranews.com/berita/5677449/presiden-iran-as-harus-tetap-patuhi-nota-kesepahaman</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/a647aa30-a843-4000-98a0-07d27228a41e.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CjkinzN000008_20260803_CBMFN0A001.jpeg</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Pangan, transportasi, dan emas perhiasan dorong inflasi pada Juli 2026</t>
+          <t>Kapal Pertamina selamatkan 17 korban KMP Mutiara Sentosa 2</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:32:11 +0700</t>
+          <t>Mon, 03 Aug 2026 14:52:47 +0700</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat kelompok makanan, minuman, dan tembakau, transportasi, serta perawatan pribadi dan ...</t>
+          <t>Kapal Pertamina Patra Niaga MT Transko Arafura berhasil mengevakuasi 17 orang korban KMP Mutiara Sentosa 2 yang ...</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677256/pangan-transportasi-dan-emas-perhiasan-dorong-inflasi-pada-juli-2026</t>
+          <t>https://www.antaranews.com/berita/5677445/kapal-pertamina-selamatkan-17-korban-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/bps.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-14.30.38.jpeg</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BPS: Neraca perdagangan Januari-Juni 2026 surplus 3,58 miliar dolar AS</t>
+          <t>Ekonomi kelautan China catat pertumbuhan stabil pada H1 2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:27:18 +0700</t>
+          <t>Mon, 03 Aug 2026 14:50:44 +0700</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat bahwa neraca perdagangan barang Indonesia mengalami surplus senilai 3,58 miliar ...</t>
+          <t>Produk laut bruto (PLB) China mencapai 5,5 triliun yuan (1 yuan = Rp2.676) pada paruh pertama (H1) 2026, naik 5,1 ...</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677252/bps-neraca-perdagangan-januari-juni-2026-surplus-358-miliar-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5677441/ekonomi-kelautan-china-catat-pertumbuhan-stabil-pada-h1-2026</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/bps.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CjkinzN000010_20260803_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Laba bersih Tugu Insurance capai Rp480,29 miliar pada semester I 2026</t>
+          <t>PGN sasar pemanfaatan jargas untuk hotel hingga UMKM</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:24:56 +0700</t>
+          <t>Mon, 03 Aug 2026 14:50:20 +0700</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>PT Asuransi Tugu Pratama Indonesia Tbk atau Tugu Insurance membukukan laba tahun berjalan yang dapat diatribusikan ...</t>
+          <t>PT Perusahaan Gas Negara (Persero) Tbk (PGN) menyasar pemanfaatan jaringan gas (jargas) tidak hanya rumah ...</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677249/laba-bersih-tugu-insurance-capai-rp48029-miliar-pada-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5677439/pgn-sasar-pemanfaatan-jargas-untuk-hotel-hingga-umkm</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-11.02.17.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_2395.jpeg</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BPS: Indonesia catat deflasi bulanan 0,14 persen pada Juli 2026</t>
+          <t>TNI AL tuntaskan latihan gabungan dengan AL Australia</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:20:12 +0700</t>
+          <t>Mon, 03 Aug 2026 14:46:09 +0700</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat Indonesia mengalami deflasi sebesar 0,14 persen secara bulanan ...</t>
+          <t>TNI AL menuntaskan kegiatan latihan gabungan dengan AL Australia atau Royal Australian Navy (RAN) dalam ajang Cassowary ...</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677247/bps-indonesia-catat-deflasi-bulanan-014-persen-pada-juli-2026</t>
+          <t>https://www.antaranews.com/berita/5677436/tni-al-tuntaskan-latihan-gabungan-dengan-al-australia</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/bps.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001554245.jpg</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Kemendag kantongi potensi ekspor Rp1,87 miliar ke Chile</t>
+          <t>Wamenkomdigi: TVRI institusi strategis penjaga ruang informasi bangsa</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:16:02 +0700</t>
+          <t>Mon, 03 Aug 2026 14:45:19 +0700</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kementerian Perdagangan (Kemendag) melalui Indonesia Trade Promotion Center (ITPC) Santiago di Chile menggelar ...</t>
+          <t>Wakil Menteri Komunikasi dan Digital (Wamenkomdigi) Angga Raka Prabowo menyatakan Lembaga Penyiaran Publik (LPP) TVRI ...</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677237/kemendag-kantongi-potensi-ekspor-rp187-miliar-ke-chile</t>
+          <t>https://www.antaranews.com/berita/5677432/wamenkomdigi-tvri-institusi-strategis-penjaga-ruang-informasi-bangsa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/03/IMG_3208.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0224.jpg</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>photo, terkini</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>IHSG awal pekan berpotensi variatif seiring sentimen global-domestik</t>
+          <t>Petani berbagi air sumur demi selamatkan tanaman tembakau</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:42:28 +0700</t>
+          <t>Mon, 03 Aug 2026 14:44:51 +0700</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin berpotensi bergerak variatif dipicu oleh ...</t>
+          <t>Petani mengambil air dari sumur untuk menyiram tanaman tembakau di Lengkong, Nganjuk, Jawa Timur, Senin (3/8/2026). ...</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677104/ihsg-awal-pekan-berpotensi-variatif-seiring-sentimen-global-domestik</t>
+          <t>https://www.antaranews.com/foto/5677428/petani-berbagi-air-sumur-demi-selamatkan-tanaman-tembakau</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/12/12/ihsg-ditutup-menguat-2688871.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/petani-tembakau-berbagi-air-sumur-antisipasi-dampak-el-nino-030826-mm-1.jpg</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Sudah ngantuk tapi sulit tidur pulas? Ini penyebab dan cara atasinya</t>
+          <t>BPK berikan opini WTP kepada Kemenko Kumham Imipas atas LK 2025</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:28:54 +0700</t>
+          <t>Mon, 03 Aug 2026 14:44:20 +0700</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Rasa kantuk yang muncul di malam hari seharusnya menjadi pertanda bahwa tubuh siap beristirahat. Namun, tidak sedikit ...</t>
+          <t>Badan Pemeriksa Keuangan RI memberikan opini Wajar Tanpa Pengecualian (WTP) kepada seluruh kementerian di bawah ...</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677203/sudah-ngantuk-tapi-sulit-tidur-pulas-ini-penyebab-dan-cara-atasinya</t>
+          <t>https://www.antaranews.com/berita/5677427/bpk-berikan-opini-wtp-kepada-kemenko-kumham-imipas-atas-lk-2025</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/17/Nafas.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001216320.jpg</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>ekonomi-bisnis, terkini, top-news</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cara cepat tidur dalam 5 menit, efektif untuk yang sulit pulas</t>
+          <t>Nusron sebut banyak laut di Batam telah dikapling tanpa prosedur sah</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:25:40 +0700</t>
+          <t>Mon, 03 Aug 2026 14:44:05 +0700</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sulit tidur meski badan sudah terasa lelah merupakan masalah yang kerap dialami banyak orang. Kondisi ini sering ...</t>
+          <t>Menteri Agraria dan Tata Ruang (ATR)/Kepala Badan Pertanahan Nasional (BPN) Nusron Wahid mengatakan, menerima banyak ...</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677199/cara-cepat-tidur-dalam-5-menit-efektif-untuk-yang-sulit-pulas</t>
+          <t>https://www.antaranews.com/berita/5677425/nusron-sebut-banyak-laut-di-batam-telah-dikapling-tanpa-prosedur-sah</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/11/04/tidua.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_142345.jpg</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>tekno</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Cara mengganti password WiFi lewat HP dan laptop dengan mudah</t>
+          <t>Menkomdigi panggil YouTube imbas temuan konten promosi vape sasar anak</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:16:14 +0700</t>
+          <t>Mon, 03 Aug 2026 14:22:09 +0700</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>WiFi yang tiba-tiba terasa lambat padahal sinyal penuh dan kuota internet masih banyak tentu membuat kesal. Salah satu ...</t>
+          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid merencanakan pemanggilan terhadap platform digital YouTube ...</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677312/cara-mengganti-password-wifi-lewat-hp-dan-laptop-dengan-mudah</t>
+          <t>https://www.antaranews.com/berita/5677396/menkomdigi-panggil-youtube-imbas-temuan-konten-promosi-vape-sasar-anak</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2020/08/19/antarafoto-warga-sediakan-internet-gratis-bagi-pelajar-190820-ief-2-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0225.jpg</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>ekonomi-bisnis, top-news</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Pemerintah bangun 1.416 Jembatan Garuda untuk hubungkan desa terpencil</t>
+          <t>Kemnaker: Magang Nasional diharapkan menekan angka pengangguran muda</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:53:00 +0700</t>
+          <t>Mon, 03 Aug 2026 13:37:57 +0700</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Foto udara pengendara sepeda motor melintasi Jembatan Gantung Garuda yang menghubungkan Desa Kertarahayu dan Desa Jayasampurna di Kabupaten Bekasi, Jawa Barat, Senin (3/8/2026). Hingga akhir Juli 2026, pemerintah telah membangun 1.416 unit Jembatan Garuda di daerah terpencil yang menghubungkan 7.371 desa dan kelurahan untuk mempermudah akses masyarakat serta mempersingkat waktu tempuh. ANTARA FOTO/Darryl Ramadhan/tom.</t>
+          <t>Kementerian Ketenagakerjaan (Kemnaker) mengatakan program Magang Nasional (MagangHub) untuk mempersiapkan kompetensi ...</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5677284/pemerintah-bangun-1416-jembatan-garuda-untuk-hubungkan-desa-terpencil</t>
+          <t>https://www.antaranews.com/berita/5677364/kemnaker-magang-nasional-diharapkan-menekan-angka-pengangguran-muda</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/Pembangunan-Jembatan-Garuda-percepat-akses-desa-030826-ryl-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/ff63afaf-7778-47fe-833d-5a8068af9a51_1.jpeg</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Petugas evakuasi dua jenazah korban kebakaran KM Mutiara Sentosa II</t>
+          <t>Kemenag perkuat transformasi madrasah lewat revitalisasi-digitalisasi</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:03:11 +0700</t>
+          <t>Mon, 03 Aug 2026 13:36:36 +0700</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sejumlah petugas mengangkat kantong berisi jenazah korban kebakaran KM Mutiara Sentosa II setelah tiba di Dermaga Jamrud Utara, Pelabuhan Tanjung Perak, Surabaya, Jawa Timur, Senin (3/8/2026). Kapal kargo Meratus Pematang Siantar mengevakuasi 111 penumpang selamat dan dua jenazah korban kebakaran KM Mutiara Sentosa II di perairan utara Madura pada Minggu (2/8). ANTARA FOTO/Didik Suhartono/tom.</t>
+          <t>Menteri Agama (Menag) Nasaruddin Umar menegaskan transformasi madrasah terus diperkuat melalui revitalisasi ...</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5677056/petugas-evakuasi-dua-jenazah-korban-kebakaran-km-mutiara-sentosa-ii</t>
+          <t>https://www.antaranews.com/berita/5677363/kemenag-perkuat-transformasi-madrasah-lewat-revitalisasi-digitalisasi</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/korban-kebakaran-km-mutiara-sentosa-2-030826-Ds-4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/14/1000173935_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis, top-news</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Resmi dibuka, Sekolah Rakyat Terintegrasi 2 Kendari tampung 339 siswa</t>
+          <t>Lisensi IP Global Buka Peluang Bisnis Baru bagi Kreator Indonesia</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
+          <t>Mon, 03 Aug 2026 13:34:30 +0700</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
+          <t>Wakil Menteri Ekonomi Kreatif Irene Umar mengatakan kolaborasi antara pemilik kekayaan intelektual (Intellectual ...</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677353/lisensi-ip-global-buka-peluang-bisnis-baru-bagi-kreator-indonesia</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000589873.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, top-news</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Nilai ekspor perdagangan RI Januari-Juni capai 140,81 miliar dolar AS</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:16:17 +0700</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) mencatat nilai ekspor Indonesia secara kumulatif dari Januari-Juni 2026 mencapai 140,81 ...</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677315/nilai-ekspor-perdagangan-ri-januari-juni-capai-14081-miliar-dolar-as</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/neraca-perdagangan-januari-mei-2026-surplus-2815779.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Korban KMP Mutiara Sentosa II dievakuasi ke Pelabuhan Tanjung Perak</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:06:15 +0700</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Tim SAR gabungan terus melakukan evakuasi korban terbakarnya KMP Mutiara Sentosa 2 ke darat, tepatnya ke Pelabuhan ...</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677297/korban-kmp-mutiara-sentosa-ii-dievakuasi-ke-pelabuhan-tanjung-perak</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/260821_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Aktor senior Diding Boneng meninggal dunia</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 11:39:03 +0700</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Aktor sekaligus komedian tanah air, Zainal Abidin alias Diding Boneng dikabarkan meninggal dunia pada Senin (3/8) dalam ...</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677209/aktor-senior-diding-boneng-meninggal-dunia</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/26f1eb88-3301-4ae1-badd-bed5078fe3dd.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Seskab: Prabowo dorong sinergi pemerintah dan dunia usaha</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 11:17:50 +0700</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Sekretaris Kabinet Teddy Indra Wijaya menyampaikan bahwa Presiden Prabowo Subianto menekankan pentingnya sinergi antara ...</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677191/seskab-prabowo-dorong-sinergi-pemerintah-dan-dunia-usaha</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0891.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Red Velvet bersiap kembali lewat EP baru "Velvet Summer"</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 10:24:37 +0700</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Grup idola K-pop Red Velvet akan kembali lewat rilis mini album atau extended play (EP) baru bertajuk “Velvet ...</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677151/red-velvet-bersiap-kembali-lewat-ep-baru-velvet-summer</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/ca97a3a8-aa17-45fc-be71-d36051dd9dcd.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Menaker pastikan komitmen pemerintah perkuat kesejahteraan pekerja</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 10:16:19 +0700</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Menteri Ketenagakerjaan (Menaker) Yassierli memastikan pemerintah berkomitmen untuk memperkuat kesejahteraan, ...</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677148/menaker-pastikan-komitmen-pemerintah-perkuat-kesejahteraan-pekerja</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/09/20/pelepasan-peserta-pemagangan-ke-jepang-di-jawa-barat-2627513.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>23 calon hakim agung dan ad hoc ikuti seleksi wawancara akhir</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 10:15:01 +0700</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Sebanyak 23 orang calon hakim agung dan ad hoc Mahkamah Agung Tahun 2026 mengikuti seleksi wawancara tahap akhir di ...</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677137/23-calon-hakim-agung-dan-ad-hoc-ikuti-seleksi-wawancara-akhir</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000012883_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>BRIN perkuat kajian sungai bawah tanah di Kebumen untuk ketahanan air</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 09:57:19 +0700</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Badan Riset dan Inovasi Nasional (BRIN) memperkuat riset ketahanan air melalui pengembangan teknologi dan penelitian ...</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677120/brin-perkuat-kajian-sungai-bawah-tanah-di-kebumen-untuk-ketahanan-air</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1785706440-47672950-1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Harga bensin turun pada pekan pertama Agustus</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 09:51:00 +0700</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Harga bahan bakar minyak (BBM) jenis bensin di stasiun pengisian bahan bakar umum (SPBU) Pertamina, Shell, dan bp ...</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677109/harga-bensin-turun-pada-pekan-pertama-agustus</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/10/02/penuruanan-harga-bbm-011024-aaa-7.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Sean Gelael berbagi pengalaman di dunia balap ke pengunjung GIIAS 2026</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 09:34:53 +0700</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Pembalap Indonesia Sean Gelael berbagi pengalamannya di dunia balap ke pengunjung GAIKINDO Indonesia International ...</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677103/sean-gelael-berbagi-pengalaman-di-dunia-balap-ke-pengunjung-giias-2026</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/16b70b87-326f-479a-a806-580ab846cc6f_1.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>ekonomi-bursa, top-news</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>IHSG Senin dibuka menguat 36,49 poin ke posisi 6.272</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 09:11:26 +0700</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin pagi dibuka menguat 36,49 poin atau 0,59 ...</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677071/ihsg-senin-dibuka-menguat-3649-poin-ke-posisi-6272</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/pergerakan-indeks-harga-saham-gabungan-2828631.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>PLN Jakarta pastikan pasokan listrik sudah berhasil dipulihkan</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 08:36:26 +0700</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>PT PLN (Persero) Unit Induk Distribusi Jakarta Raya mengungkapkan pasokan listrik telah berhasil ...</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677043/pln-jakarta-pastikan-pasokan-listrik-sudah-berhasil-dipulihkan</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20231217-WA0015-1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Ledakan di kantor polisi Pakistan tewaskan 14 orang</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 07:44:23 +0700</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Sebuah ledakan terjadi di luar sebuah kantor polisi di Kota Kabal, Pakistan, mengakibatkan 14 orang tewas dan 14 orang ...</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677020/ledakan-di-kantor-polisi-pakistan-tewaskan-14-orang</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CmxztpE000019_20260803_PEPFN0A001.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Ratusan korban selamat KMP Mutiara Santosa 2 tiba di Tanjung Perak</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 06:37:38 +0700</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Sebanyak 111 korban selamat dan dua meninggal dunia akibat kebakaran KMP Mutiara Santosa II di Perairan Utara ...</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676983/ratusan-korban-selamat-kmp-mutiara-santosa-2-tiba-di-tanjung-perak</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/259549_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Sebagian Jakarta diguyur hujan ringan pada Senin sore hingga malam</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 06:11:02 +0700</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) memprakirakan hujan ringan akan melanda sebagian wilayah Jakarta ...</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676963/sebagian-jakarta-diguyur-hujan-ringan-pada-senin-sore-hingga-malam</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/01/IMG_20260301_073711.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Atlet-atlet nasional borong 18 medali Poomsae Indonesia Open 2026</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 04:18:40 +0700</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Atlet-atlet tuan rumah Indonesia tampil impresif pada nomor Poomsae 8th Asian Taekwondo, Indonesia Open ...</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676947/atlet-atlet-nasional-borong-18-medali-poomsae-indonesia-open-2026</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships-2026-020826-dr-04.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Kemenhub kerahkan kapal patroli evakuasi KM Mutiara Sentosa II</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 00:03:37 +0700</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Kementerian Perhubungan mengerahkan kapal patroli Kesatuan Penjagaan Laut dan Pantai (KPLP) serta memperkuat koordinasi ...</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676931/kemenhub-kerahkan-kapal-patroli-evakuasi-km-mutiara-sentosa-ii</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Rupiah diperkirakan menguat seiring AS batalkan rencana serang Iran</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 10:12:26 +0700</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Analis Doo Financial Futures, Lukman Leong memperkirakan rupiah menguat seiring Amerika Serikat (AS) membatalkan ...</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677132/rupiah-diperkirakan-menguat-seiring-as-batalkan-rencana-serang-iran</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828847.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Rupiah pada Senin pagi melemah jadi Rp18.031 per dolar AS</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 09:05:50 +0700</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah pada Senin pagi bergerak melemah 9 poin atau 0,05 persen menjadi Rp18.031 per dolar AS dibandingkan ...</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677063/rupiah-pada-senin-pagi-melemah-jadi-rp18031-per-dolar-as</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Komisi XI: PFII peluang RI tangkap momentum perpindahan modal global</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 06:53:34 +0700</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Komisi XI DPR RI Mohamad Hekal mengatakan percepatan pembentukan Pusat Finansial Internasional Indonesia ...</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676995/komisi-xi-pfii-peluang-ri-tangkap-momentum-perpindahan-modal-global</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Saham-dan-oblogasi.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>BUMA International Group bukukan pertumbuhan EBITDA semester I/2026</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 06:17:40 +0700</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>PT BUMA Internasional Gorup membukukan pertumbuhan EBITDA pada semester pertama 2026 (1H26) di tengah penurunan ...</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676967/buma-international-group-bukukan-pertumbuhan-ebitda-semester-i-2026</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/buma.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>CORE: Harga Pertamax turun beri sentimen positif bagi inflasi</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 14:40:44 +0700</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Ekonom Center of Reform on Economics (CORE) Yusuf Rendy Manilet menyampaikan penurunan harga Pertamax pada bulan ...</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677420/core-harga-pertamax-turun-beri-sentimen-positif-bagi-inflasi</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/penurunan-harga-bbm-jenis-pertamax-2831783.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Askrindo bukukan laba Rp1,69 T pada 2025 ditopang tiga lini bisnis</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 14:38:49 +0700</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>PT Asuransi Kredit Indonesia (Persero) atau Askrindo membukukan laba setelah pajak sebesar Rp1,69 triliun pada 2025 ...</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677419/askrindo-bukukan-laba-rp169-t-pada-2025-ditopang-tiga-lini-bisnis</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-08.51.32.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Jasaraharja Putera menjamin santunan korban KMP Mutiara Sentosa II</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 14:30:17 +0700</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>PT Jasaraharja Putera menjamin perlindungan dan santunan bagi seluruh korban kebakaran Kapal Motor Penyeberangan (KMP) ...</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677412/jasaraharja-putera-menjamin-santunan-korban-kmp-mutiara-sentosa-ii</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176259.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>GMR bidik Indonesia dalam perluasan rute Bandara Bhogapuram India</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 14:29:34 +0700</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>GMR Airports Limited (GMR Airports), salah satu pengelola jaringan bandara internasional, memprioritaskan Indonesia ...</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677407/gmr-bidik-indonesia-dalam-perluasan-rute-bandara-bhogapuram-india</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0725.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>BPS: Wisman per Juni capai 7,45 juta kunjungan, tertinggi sejak 2020</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 14:22:48 +0700</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) mencatat total kunjungan wisatawan mancanegara dari Januari hingga bulan Juni 2026 mencapai ...</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677399/bps-wisman-per-juni-capai-745-juta-kunjungan-tertinggi-sejak-2020</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/pelepasliaran-500-ekor-tukik-bali-290726-nhw-3_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>BPS catat nilai tukar petani di level 127,84 pada Juli 2026</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:18:40 +0700</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) mencatat nilai tukar petani (NTP) secara nasional pada bulan Juli 2026 berada di level ...</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677323/bps-catat-nilai-tukar-petani-di-level-12784-pada-juli-2026</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/02/20260302_083324.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Menteri ATR sebut 400 Kantah sudah terapkan pengukuran terjadwal</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:13:29 +0700</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Menteri Agraria dan Tata Ruang/Kepala Badan Pertanahan Nasional (ATR/BPN) Nusron Wahid mengatakan bahwa sudah ada 400 ...</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677308/menteri-atr-sebut-400-kantah-sudah-terapkan-pengukuran-terjadwal</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_125328.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>PT PAL-BRIN wujudkan galangan kapal hijau dukung industri perkapalan</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 12:43:28 +0700</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>PT PAL Indonesia bersama Badan Riset dan Inovasi Nasional (BRIN) berkolaborasi mewujudkan transformasi green ...</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677267/pt-pal-brin-wujudkan-galangan-kapal-hijau-dukung-industri-perkapalan</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/a647aa30-a843-4000-98a0-07d27228a41e.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Pangan, transportasi, dan emas perhiasan dorong inflasi pada Juli 2026</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 12:32:11 +0700</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) mencatat kelompok makanan, minuman, dan tembakau, transportasi, serta perawatan pribadi dan ...</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677256/pangan-transportasi-dan-emas-perhiasan-dorong-inflasi-pada-juli-2026</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/bps.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>BPS: Neraca perdagangan Januari-Juni 2026 surplus 3,58 miliar dolar AS</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 12:27:18 +0700</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) mencatat bahwa neraca perdagangan barang Indonesia mengalami surplus senilai 3,58 miliar ...</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677252/bps-neraca-perdagangan-januari-juni-2026-surplus-358-miliar-dolar-as</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/bps.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Laba bersih Tugu Insurance capai Rp480,29 miliar pada semester I 2026</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 12:24:56 +0700</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>PT Asuransi Tugu Pratama Indonesia Tbk atau Tugu Insurance membukukan laba tahun berjalan yang dapat diatribusikan ...</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677249/laba-bersih-tugu-insurance-capai-rp48029-miliar-pada-semester-i-2026</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-11.02.17.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ekonomi-bursa</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>IHSG awal pekan berpotensi variatif seiring sentimen global-domestik</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 09:42:28 +0700</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin berpotensi bergerak variatif dipicu oleh ...</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677104/ihsg-awal-pekan-berpotensi-variatif-seiring-sentimen-global-domestik</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/12/12/ihsg-ditutup-menguat-2688871.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>humaniora</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Bantuan beras 30 kg cair mulai 17 Agustus 2026, ini jadwal dan cara cek penerimanya</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:27:14 +0700</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Pemerintah memastikan penyaluran bantuan pangan beras tahap II tahun 2026 akan dimulai pada 17 Agustus 2026. Bantuan ...</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677341/bantuan-beras-30-kg-cair-mulai-17-agustus-2026-ini-jadwal-dan-cara-cek-penerimanya</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/26/kemensos-percepat-penyaluran-bansos-pkh-dan-bpnt-2778877.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>10 ide lomba 17 Agustus untuk anak PAUD dan TK yang seru, edukatif, dan mudah digelar</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:38:29 +0700</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Perayaan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 dapat menjadi momen bagi anak usia PAUD dan TK ...</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677368/10-ide-lomba-17-agustus-untuk-anak-paud-dan-tk-yang-seru-edukatif-dan-mudah-digelar</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/08/03/WhatsApp-Image-2024-08-03-at-20.37.28.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Sering terbangun tengah malam? Kenali 7 penyebab dan cara mengatasinya</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:35:20 +0700</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Bangun di tengah malam sesekali merupakan hal yang normal. Namun, jika kondisi ini terjadi hampir setiap malam dan ...</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677357/sering-terbangun-tengah-malam-kenali-7-penyebab-dan-cara-mengatasinya</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/20/Penumpang-rela-menginap-menunggu-kereta-pertama-di-Stasiun-Cikarang-150726-ryl-5.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Bahaya paparan pornografi pada anak: Dampak bagi otak, mental, dan perilaku</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:23:03 +0700</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Perkembangan teknologi membuat anak-anak dan remaja semakin akrab dengan internet sejak usia dini. Di satu sisi, ...</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677332/bahaya-paparan-pornografi-pada-anak-dampak-bagi-otak-mental-dan-perilaku</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/02/ilustrasi-konten-berbau-pornografi.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Sudah ngantuk tapi sulit tidur pulas? Ini penyebab dan cara atasinya</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 11:28:54 +0700</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Rasa kantuk yang muncul di malam hari seharusnya menjadi pertanda bahwa tubuh siap beristirahat. Namun, tidak sedikit ...</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677203/sudah-ngantuk-tapi-sulit-tidur-pulas-ini-penyebab-dan-cara-atasinya</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/17/Nafas.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Cara cepat tidur dalam 5 menit, efektif untuk yang sulit pulas</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 11:25:40 +0700</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Sulit tidur meski badan sudah terasa lelah merupakan masalah yang kerap dialami banyak orang. Kondisi ini sering ...</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677199/cara-cepat-tidur-dalam-5-menit-efektif-untuk-yang-sulit-pulas</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/04/tidua.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>tekno</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Cara mengganti password WiFi lewat HP dan laptop dengan mudah</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:16:14 +0700</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>WiFi yang tiba-tiba terasa lambat padahal sinyal penuh dan kuota internet masih banyak tentu membuat kesal. Salah satu ...</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677312/cara-mengganti-password-wifi-lewat-hp-dan-laptop-dengan-mudah</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2020/08/19/antarafoto-warga-sediakan-internet-gratis-bagi-pelajar-190820-ief-2-1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Pemerintah bangun 1.416 Jembatan Garuda untuk hubungkan desa terpencil</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 12:53:00 +0700</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Foto udara pengendara sepeda motor melintasi Jembatan Gantung Garuda yang menghubungkan Desa Kertarahayu dan Desa Jayasampurna di Kabupaten Bekasi, Jawa Barat, Senin (3/8/2026). Hingga akhir Juli 2026, pemerintah telah membangun 1.416 unit Jembatan Garuda di daerah terpencil yang menghubungkan 7.371 desa dan kelurahan untuk mempermudah akses masyarakat serta mempersingkat waktu tempuh. ANTARA FOTO/Darryl Ramadhan/tom.</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5677284/pemerintah-bangun-1416-jembatan-garuda-untuk-hubungkan-desa-terpencil</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/Pembangunan-Jembatan-Garuda-percepat-akses-desa-030826-ryl-1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Petugas evakuasi dua jenazah korban kebakaran KM Mutiara Sentosa II</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 09:03:11 +0700</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Sejumlah petugas mengangkat kantong berisi jenazah korban kebakaran KM Mutiara Sentosa II setelah tiba di Dermaga Jamrud Utara, Pelabuhan Tanjung Perak, Surabaya, Jawa Timur, Senin (3/8/2026). Kapal kargo Meratus Pematang Siantar mengevakuasi 111 penumpang selamat dan dua jenazah korban kebakaran KM Mutiara Sentosa II di perairan utara Madura pada Minggu (2/8). ANTARA FOTO/Didik Suhartono/tom.</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5677056/petugas-evakuasi-dua-jenazah-korban-kebakaran-km-mutiara-sentosa-ii</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/korban-kebakaran-km-mutiara-sentosa-2-030826-Ds-4.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Kesbangpol Pontianak antisipasi konflik sosial akibat karhutla</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Kesatuan Bangsa dan Politik (Kesbangpol) Kota Pontianak mengidentifikasi potensi gangguan keamanan dan konflik sosial akibat kebakaran hutan dan lahan (karhutla), Senin (3/8). Langkah yang dilakukan meliputi koordinasi lintas sektor, pemantauan situasi, hingga mediasi untuk menjaga kondusivitas selama penanganan karhutla. (Indra Budi Santoso/Rizky Bagus Dhermawan/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677519/kesbangpol-pontianak-antisipasi-konflik-sosial-akibat-karhutla</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/KESBANGPOL-PONTIANAK-ANTISIPASI-KONFLIK-SOSIAL-AKIBAT-KARHUTLA.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>PSEL Serang Raya jadi solusi pengelolaan sampah tiga daerah</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>ANTARA - Fasilitas Pengolahan Sampah menjadi Energi Listrik (PSEL) Serang Raya akan dibangun di TPSA Cilowong, Kota Serang, untuk melayani pengelolaan sampah Kabupaten Serang, Kota Serang, dan Kota Cilegon. Fasilitas berkapasitas 1.161 ton sampah per hari itu diharapkan mampu mengurangi beban tempat pemrosesan akhir sekaligus mengubah sampah menjadi energi listrik. (Susmiatun Hayati/Agha Yuninda Maulana/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677492/psel-serang-raya-jadi-solusi-pengelolaan-sampah-tiga-daerah</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PSEL-SERANG-RAYA-JADI-SOLUSI-PENGELOLAAN-SAMPAH.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Pemkot Ambon salurkan air bersih gratis jika kekeringan terjadi</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Kota Ambon, Maluku, menyiapkan langkah antisipasi untuk menjamin ketersediaan air bersih bagi masyarakat dalam menghadapi potensi musim kemarau panjang akibat fenomena El Nino. Wali kota Ambon Bodewin Wattimena, Senin (3/8), mengatakan, pemerintah melakukan pemetaan wilayah yang rawan lalu mendistribusikan air bersih ke wilayah terdampak kekeringan. (Alfian Sanusi/Rizky Bagus Dhermawan/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677489/pemkot-ambon-salurkan-air-bersih-gratis-jika-kekeringan-terjadi</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-151844.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Razia balap liar, Polres Temanggung sita 106 motor</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepolisian Resor (Polres) Temanggung, Jawa Tengah menyita 106 sepeda motor dalam razia balap liar yang digelar Minggu malam (2/8). Kegiatan razia tersebut digelar sebagai bagian  upaya kepolisian dalam menekan aksi balap liar  di Temanggung.(Firman Eko Handy/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677488/razia-balap-liar-polres-temanggung-sita-106-motor</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_RAZIA-BALAP-LIAR-POLRES-TEMANGGUNG-SITA-106-MOTOR.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Ditjenpas Kaltim gelar CKG bagi 12 ribu warga binaan</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>ANTARA - Program Cek Kesehatan Gratis (CKG) menyasar warga binaan di Lembaga Pemasyarakatan (Lapas) dan Rumah Tahanan (Rutan) di Kalimantan Timur. CKG untuk 12 ribu warga binaan bertujuan mengantisipasi penyebaran risiko penyakit menular di lapas. (Hanifan Ma'ruf/Agha Yuninda Maulana/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677480/ditjenpas-kaltim-gelar-ckg-bagi-12-ribu-warga-binaan</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_DITJENPAS-KALTIM-GELAR-CKG.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Paus Leo XIV prihatin atas situasi krisis migran di Ceuta</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>ANTARA - Paus Leo XIV  menyampaikan keprihatinan atas situasi krisis migran di Enklave, Spanyol, Ceuta.  Saat memimpin doa angelus di Vatikan, Minggu (2/8), Paus berdoa agar terdapat solusi yang membawa perdamaian dan keadilan atas kondisi tersebut. (Ludmila Yusufin Diah Nastiti/Agha Yuninda Maulana/Winanto)</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677384/paus-leo-xiv-prihatin-atas-situasi-krisis-migran-di-ceuta</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PAUS-LEO-XIV-PRIHATIN-ATAS-SITUASI-KRISIS.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Resmi dibuka, Sekolah Rakyat Terintegrasi 2 Kendari tampung 339 siswa</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
           <t>ANTARA - Sekolah Rakyat Terintegrasi 2 Kota Kendari resmi dibuka pada Senin (3/8), yang ditandai dengan Masa Pengenalan Lingkungan Sekolah (MPLS). Sekolah tersebut menampung total sebanyak 339 siswa untuk tahun ajaran 2026/2027, yang terdiri dari jenjang SD, SMP dan SMA.
 (Saharudin/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F152" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677373/resmi-dibuka-sekolah-rakyat-terintegrasi-2-kendari-tampung-339-siswa</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G152" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/RESMI-DIBUKA-SEKOLAH-RAKYAT-TERINTEGRASI-2-KENDARI-TAMPUNG-339-SISWA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+    <row r="153">
+      <c r="A153" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B153" t="inlineStr">
         <is>
           <t>Dinkop UKM Cilegon targetkan 21 gerai baru KKMP beroperasi September</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr">
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Koperasi Usaha Kecil dan Menengah (Dinkop UKM) Kota Cilegon menargetkan pembangunan  21 gedung gerai Koperasi Kelurahan Merah Putih (KKMP) di wilayah setempat dapat selesai dan beroperasi pada bulan September mendatang. Kepala Dinkop UKM Kota Cilegon, Suhendi pada Senin (3/8) mengatakan saat ini tercatat baru sebanyak 10 gedung yang telah selesai dibangun.
 (Susmiatun Hayati/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F153" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677301/dinkop-ukm-cilegon-targetkan-21-gerai-baru-kkmp-beroperasi-september</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G153" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/DINKOP-UKM-CILEGON-TARGETKAN-21-GERAI-BARU-KKMP-BEROPERASI-SEPTEMBER.jpg</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+    <row r="154">
+      <c r="A154" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>Menhub sebut segera evaluasi operator KMP Mutiara Sentosa 2</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr">
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah akan segera mengevaluasi kinerja PT Atosim Lampung Pelayaran yang merupakan operator KMP Mutiara Sentosa II. Hal tersebut disampaikan Menteri Perhubungan Dudy Purwagandhi saat meninjau para korban kebakaran KMP Mutiara Sentosa II di Surabaya, Jawa Timur, Senin (3/8). (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F154" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677187/menhub-sebut-segera-evaluasi-operator-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="G154" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/MENHUB-SEBUT-SEGERA-EVALUASI-OPERATOR-KMP-MUTIARA-SENTOSA-2.jpg</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+    <row r="155">
+      <c r="A155" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>Keluarga dengan dua balita selamat dari maut KMP Mutiara Sentosa 2</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
         <is>
           <t>ANTARA - Pasangan suami istri muda, Karhap dan Krisnawati bersama dua anak balitanya sempat terpisah saat terjun ke laut menyelamatkan diri dari kapal penumpang KMP Mutiara Sentosa 2 yang terbakar di perairan sebelah utara Pulau Madura pada Minggu (2/8). Keluarga kecil asal Sidenreng Rappang, Sulawesi Selatan tersebut kembali berkumpul pada Senin (3/8) setelah dievakuasi oleh kapal kargo Meratus Pematang Siantar yang kebetulan melintas di lokasi musibah terjadi. (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F155" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677141/keluarga-dengan-dua-balita-selamat-dari-maut-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="G155" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KELUARGA-DENGAN-DUA-BALITA-SELAMAT-DARI-MAUT-KMP-MUTIARA-SENTOSA-2.jpg</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+    <row r="156">
+      <c r="A156" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>Lebih dari 100 korban KMP Mutiara Sentosa 2 tiba di Tanjung Perak</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr">
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
         <is>
           <t>ANTARA - Tim pencarian dan pertolongan (SAR) gabungan hingga Senin (3/8), telah mengevakuasi 234 penumpang KMP Mutiara Sentosa 2 yang sebelumnya terbakar di perairan sebelah utara Pulau Madura pada Minggu (2/8). Sebanyak 113 korban di antaranya, kini telah tiba di Pelabuhan Tanjung Perak Surabaya setelah diangkut menggunakan kapal kargo Meratus Pematang Siantar.  (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F156" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677085/lebih-dari-100-korban-kmp-mutiara-sentosa-2-tiba-di-tanjung-perak</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="G156" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/LEBIH-DARI-100-KORBAN-KMP-MUTIARA-SENTOSA-2-TIBA-DI-TANJUNG-PERAK.jpg</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
+    <row r="157">
+      <c r="A157" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B157" t="inlineStr">
         <is>
           <t>SAR evakuasi penumpang KM Mutiara Santosa 2 yang terbakar</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr">
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
         <is>
           <t>ANTARA - Tim pencarian dan pertolongan (SAR) gabungan telah mengevakuasi sebanyak 236 penumpang KM Mutiara Santosa 2 yang terbakar di perairan sebelah utara Pulau Madura, Minggu malam (2/8). Lima korban di antaranya meninggal dunia.(Hanif Nasrullah/Denno Ramdha Asmara/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F157" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676992/sar-evakuasi-penumpang-km-mutiara-santosa-2-yang-terbakar</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="G157" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SAR-EVAKUASI-PENUMPANG-KM-MUTIARA-SANTOSA-2-YANG-TERBAKAR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
+    <row r="158">
+      <c r="A158" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>John Herdman tunggu hasil pemeriksaan Marselino jelang jamu Vietnam</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr">
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
         <is>
           <t>ANTARA - Pelatih Timnas Indonesia John Herdman di Jakarta, Minggu,(2/8), mengatakan kondisi kesehatan dan status gelandang Marselino Ferdinan dalam turnamen baru akan ditentukan setelah mendapat laporan lengkap dari tim medis. Hal itu disampaikan Herdman, usai Marselino kembali absen dalam latihan jelang laga Grup A Piala AFF 2026 melawan Timnas Vietnam pada Senin (2/8). (Anggah/Sandy Arizona/Gracia Simanjuntak)</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F158" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676945/john-herdman-tunggu-hasil-pemeriksaan-marselino-jelang-jamu-vietnam</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="G158" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_JOHN-HERDMAN-TUNGGU-HASIL-PEMERIKSAAN-MARSELINO-JELANG-JAMU-VIETNAM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
+    <row r="159">
+      <c r="A159" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B159" t="inlineStr">
         <is>
           <t>John Herdman sebut laga RI Vs Vietnam ujian sangat berat</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr">
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
         <is>
           <t>ANTARA - Pelatih Timnas Indonesia John Herdman di Jakarta, Minggu(2/8), mengaku pertandingan melawan Timnas Vietnam akan menjadi ujian sangat berat bagi skuad Garuda di Grup A Piala AFF 2026 (ASEAN Championship 2026). Menurut Herdman. laga tersebut juga merupakan peluang untuk mengambil alih kendali grup dan memastikan langkah ke babak berikutnya. (Anggah/Sandy Arizona/Gracia Simanjuntak)</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F159" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676944/john-herdman-sebut-laga-ri-vs-vietnam-ujian-sangat-berat</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="G159" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_JOHN-HERDMAN-SEBUT-LAGA-RI-VS-VIETNAM-UJIAN-SANGAT-BERAT.jpg</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
+    <row r="160">
+      <c r="A160" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B160" t="inlineStr">
         <is>
           <t>BI targetkan bawa wastra Sulsel ke pasar global</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr">
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
         <is>
           <t>ANTARA - Kantor Perwakilan Bank Indonesia Provinsi Sulawesi Selatan bersama Pemerintah Provinsi Sulsel menyasar penguatan pasar produk kain tradisional (wastra) di tingkat nasional hingga mancanegara melalui "Wastra Heritage Market 2026". Hal itu dikemukakan Kepala Kantor Perwakilan BI Sulsel Rizki Ernadi Wimanda di Makassar, Minggu (2/8). (Suriani Mappong/Sandy Arizona/Gracia Simanjuntak)</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F160" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676935/bi-targetkan-bawa-wastra-sulsel-ke-pasar-global</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="G160" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_BI-TARGETKAN-BAWA-WASTRA-SULSEL-KE-PASAR-GLOBAL.jpg</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
+    <row r="161">
+      <c r="A161" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>Tong Tong Night Market masuk KEN, angkat UMKM dan budaya lokal</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr">
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
         <is>
           <t>ANTARA - ‎Memasuki satu dekade penyelenggaraan, Tong Tong Night Market kembali meramaikan Kota Malang. Festival budaya dan kuliner yang masuk dalam Karisma Event Nusantara (KEN) itu tak hanya menghadirkan nuansa tempo dulu, tetapi juga menjadi ajang promosi puluhan UMKM sekaligus upaya melestarikan budaya lokal. (Achmad Saif Hajarani/Sandy Arizona/Gracia Simanjuntak)</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F161" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676927/tong-tong-night-market-masuk-ken-angkat-umkm-dan-budaya-lokal</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="G161" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_TONG-TONG-NIGHT-MARKET-MASUK-KEN-ANGKAT-UMKM-DAN-BUDAYA-LOKAL_1.jpg</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
+    <row r="162">
+      <c r="A162" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B162" t="inlineStr">
         <is>
           <t>Perputaran ekonomi Piala Presiden 2026 tembus Rp70 miliar</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr">
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
         <is>
           <t>ANTARA - Ketua Steering Committee Piala Presiden 2026 Maruarar Sirait menyebut perputaran ekonomi selama babak penyisihan turnamen di Surabaya dan Bandung telah mencapai lebih dari Rp70 miliar. Dampak ekonomi tersebut turut dirasakan pelaku usaha mikro, kecil, dan menengah (UMKM) serta dimanfaatkan untuk menyubsidi harga tiket pertandingan.
 (Hanif Nasrullah/Sandy Arizona/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F162" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676895/perputaran-ekonomi-piala-presiden-2026-tembus-rp70-miliar</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="G162" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_PERPUTARAN-EKONOMI-PIALA-PRESIDEN-2026-TEMBUS-RP70-MILIAR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
+    <row r="163">
+      <c r="A163" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B163" t="inlineStr">
         <is>
           <t>Bahlil prioritaskan legalisasi 25 ribu sumur minyak rakyat di Sumsel</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr">
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyebut Sumatera Selatan menjadi salah satu daerah prioritas penerapan kebijakan legalisasi sumur minyak rakyat. Menurutnya, sekitar 25 ribu dari 45 ribu sumur minyak rakyat di Indonesia berada di provinsi tersebut sehingga pemerintah memfokuskan implementasi Peraturan Menteri ESDM Nomor 18 Tahun 2025 di wilayah itu.
 (Winda Tri Agustina/Sandy Arizona/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F163" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676868/bahlil-prioritaskan-legalisasi-25-ribu-sumur-minyak-rakyat-di-sumsel</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="G163" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_BAHLIL-PRIORITASKAN-LEGALISASI-25-RIBU-SUMUR-MINYAK-RAKYAT-DI-SUMSEL.jpg</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
+    <row r="164">
+      <c r="A164" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>Golkar optimistis tingkatkan perolehan kursi di Sumsel</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr">
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
         <is>
           <t>ANTARA - Ketua Umum Partai Golkar Bahlil Lahadalia meminta seluruh jajaran partai memperkuat konsolidasi organisasi hingga tingkat desa sebagai strategi meningkatkan perolehan kursi legislatif pada Pemilu 2029, termasuk di Sumatera Selatan.
 (Winda Tri Agustina/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="F164" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676837/golkar-optimistis-tingkatkan-perolehan-kursi-di-sumsel</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="G164" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/GOLKAR-OPTIMISTIS-TINGKATKAN-PEROLEHAN-KURSI-DI-SUMSEL.jpg</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
+    <row r="165">
+      <c r="A165" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B165" t="inlineStr">
         <is>
           <t>Presiden AS Trump tunda serangan baru ke Iran</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr">
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
         <is>
           <t>ANTARA - Presiden Amerika Serikat Donald Trump menunda rencana serangan baru terhadap Iran setelah mengklaim terdapat peluang kesepakatan. Namun, Trump menegaskan opsi militer tetap terbuka jika negosiasi gagal.
 (XINHUA/Arsy Fitriady/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F165" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676776/presiden-as-trump-tunda-serangan-baru-ke-iran</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="G165" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-AS-TRUMP-TUNDA-SERANGAN-BARU-KE-IRAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
+    <row r="166">
+      <c r="A166" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B166" t="inlineStr">
         <is>
           <t>TNI AU gelar pameran enam pesawat F-16 di Batam</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr">
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
         <is>
           <t>ANTARA - TNI Angkatan Udara menggelar pameran enam pesawat tempur F-16 yang dapat dikunjungi masyarakat secara gratis dalam kegiatan Batam Open Base di Bandara Internasional Hang Nadim, Batam. Kegiatan ini menjadi bagian dari peringatan Hari Ulang Tahun ke-81 Kemerdekaan Republik Indonesia sekaligus upaya mendekatkan TNI AU kepada masyarakat.
 (Angiela Chantiequ/Jessica Allifia Jaya Hidayat/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F166" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676735/tni-au-gelar-pameran-enam-pesawat-f-16-di-batam</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G166" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/TNI-AU-GELAR-PAMERAN-ENAM-PESAWAT-F-16-DI-BATAM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
+    <row r="167">
+      <c r="A167" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B167" t="inlineStr">
         <is>
           <t>TNI kerahkan delapan helikopter salurkan bantuan ke Puncak</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr">
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
         <is>
           <t>ANTARA - Komando Gabungan Wilayah Pertahanan (Kogabwilhan) III mengerahkan delapan helikopter TNI Angkatan Darat dan TNI Angkatan Udara untuk menyalurkan bantuan kemanusiaan ke tiga distrik di Kabupaten Puncak, Papua Tengah, yang terdampak kekeringan berkepanjangan hingga memicu krisis pangan. (Laksa Mahendra/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="F167" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676720/tni-kerahkan-delapan-helikopter-salurkan-bantuan-ke-puncak</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="G167" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/TNI-KERAHKAN-DELAPAN-HELIKOPTER-SALURKAN-BANTUAN-KE-PUNCAK.jpg</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
+    <row r="168">
+      <c r="A168" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B168" t="inlineStr">
         <is>
           <t>Jakarta Watersport Festival dorong sport tourism di Danau Sunter</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr">
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
         <is>
           <t>ANTARA - Jakarta Watersport Festival 2026 digelar di Danau Sunter, Jakarta Utara, pada 1–2 Agustus. Festival ini menghadirkan kompetisi olahraga air, hiburan, dan bazar UMKM sebagai upaya mendorong sport tourism serta aktivitas ekonomi kreatif di ibu kota. (Nabila Athifa/Setyanka Harviana Putri/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="F168" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676713/jakarta-watersport-festival-dorong-sport-tourism-di-danau-sunter</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="G168" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/JAKARTA-WATERSPORT-FESTIVAL-DORONG-SPORT-TOURISM-DI-DANAU-SUNTER.jpg</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
+    <row r="169">
+      <c r="A169" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B169" t="inlineStr">
         <is>
           <t>Ledakan restoran di Moskow tewaskan tiga orang</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr">
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
         <is>
           <t>ANTARA - Tiga orang tewas dan sedikitnya 21 lainnya luka-luka setelah ledakan alat peledak rakitan terjadi di sebuah restoran di kawasan Kudrinskaya Square, pusat Kota Moskow, Rusia, Sabtu (1/8). Menurut Komite Antiterorisme Nasional Rusia, ledakan terjadi ketika seorang perempuan berupaya membawa alat peledak ke dalam restoran, namun dihentikan petugas keamanan. Penyelidikan terkait motif serangan masih berlangsung. (Arsy Fitriady/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="F169" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676660/ledakan-restoran-di-moskow-tewaskan-tiga-orang</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="G169" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/LEDAKAN-RESTORAN-DI-MOSKOW-TEWASKAN-TIGA-ORANG_1.jpg</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
+    <row r="170">
+      <c r="A170" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B170" t="inlineStr">
         <is>
           <t>DKPPP Temanggung edukasi warga cegah zoonosis dari hewan piaraan</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr">
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Ketahanan Pangan, Pertanian, dan Perikanan (DKPPP) Kabupaten Temanggung bersama komunitas pecinta hewan mengedukasi masyarakat tentang pentingnya menjaga kesehatan hewan piaraan untuk mencegah zoonosis atau penyakit yang dapat menular dari hewan ke manusia. Edukasi meliputi pemberian nutrisi, vaksinasi, kebersihan, dan pemeriksaan kesehatan hewan secara berkala. (Firman Eko Handy/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="F170" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676647/dkppp-temanggung-edukasi-warga-cegah-zoonosis-dari-hewan-piaraan</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="G170" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/DKPPP-TEMANGGUNG-EDUKASI-WARGA-CEGAH-ZOONOSIS-DARI-HEWAN-PIARAAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
+    <row r="171">
+      <c r="A171" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>BP Batam siapkan Sekolah Terintegrasi Merah Putih di Rempang</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr">
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pengusahaan (BP) Batam menyiapkan pembangunan Sekolah Terintegrasi Merah Putih di Rempang, Kepulauan Riau, sebagai sekolah gratis bagi siswa berprestasi. Sekolah yang dibangun di atas lahan seluas 18 hektare itu akan melayani jenjang sekolah dasar hingga sekolah menengah atas dengan fasilitas pendidikan dan olahraga yang lengkap. (Angiela Chantiequ/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="F171" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676644/bp-batam-siapkan-sekolah-terintegrasi-merah-putih-di-rempang</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="G171" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/BP-BATAM-SIAPKAN-SEKOLAH-TERINTEGRASI-MERAH-PUTIH-DI-REMPANG.jpg</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
+    <row r="172">
+      <c r="A172" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>Aldila Sutjiadi juarai WTA 500 Mubadala DC Open 2026</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr">
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
         <is>
           <t>ANTARA - Petenis ganda putri Indonesia Aldila Sutjiadi menjuarai nomor ganda Women's Tennis Association (WTA) 500 Mubadala DC Open 2026 di Washington, Amerika Serikat. Berpasangan dengan petenis Selandia Baru Erin Routliffe, Aldila mengalahkan Andreja Klepac dari Slovenia dan Makoto Ninomiya dari Jepang dua set langsung 6-4, 6-1 pada partai final. Gelar tersebut menjadi trofi WTA kedelapan dalam karier Aldila di nomor ganda sekaligus gelar kedua bersama Routliffe pada musim 2026.
 (Arsy Fitriady/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F172" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676629/aldila-sutjiadi-juarai-wta-500-mubadala-dc-open-2026</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="G172" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/ALDILA-SUTJIADI-JUARAI-WTA-500-MUBADALA-DC-OPEN-2026.jpg</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
+    <row r="173">
+      <c r="A173" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B173" t="inlineStr">
         <is>
           <t>KM Mutiara Sentosa 2 Terbakar Saat Berlayar ke Makassar</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr">
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
         <is>
           <t>ANTARA - Kapal Motor (KM) Mutiara Sentosa 2 terbakar di perairan utara Pulau Madura saat berlayar dari Pelabuhan Tanjung Perak Surabaya menuju Makassar, Minggu (2/8). Kapal tersebut mengangkut sekitar 250 orang. Tim SAR gabungan masih melakukan evakuasi penumpang, sementara penyebab kebakaran masih dalam penyelidikan. (Hanif Nasrullah/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F173" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676617/km-mutiara-sentosa-2-terbakar-saat-berlayar-ke-makassar</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="G173" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KM-MUTIARA-SENTOSA-2-TERBAKAR-SAAT-BERLAYAR-KE-MAKASSAR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
+    <row r="174">
+      <c r="A174" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>BI dan Pemkot Kendari Perkuat Digitalisasi UMKM</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr">
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
         <is>
           <t>ANTARA - Kantor Perwakilan Bank Indonesia Sulawesi Tenggara bersama Pemerintah Kota Kendari menggelar Festival Kuliner Sultra Maimo 2026 untuk memperkuat digitalisasi usaha mikro, kecil, dan menengah atau UMKM. Festival yang berlangsung pada 2 hingga 9 Agustus itu juga mendorong perluasan transaksi non-tunai berbasis QRIS. (Saharudin/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F174" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676607/bi-dan-pemkot-kendari-perkuat-digitalisasi-umkm</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="G174" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/BI-DAN-PEMKOT-KENDARI-PERKUAT-DIGITALISASI-UMKM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
+    <row r="175">
+      <c r="A175" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B175" t="inlineStr">
         <is>
           <t>El Nino menguat, negara fokus jaga ketersediaan air &amp; tangani karhutla</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr">
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
         <is>
           <t>ANTARA - Gelombang panas sebagai akibat El Nino mulai dirasakan dampaknya di sejumlah belahan dunia. Kebakaran hutan dan lahan atau karhutla, juga mulai terjadi di dalam negeri, seperti di Pulau Sumatera dan Kalimantan.Selain kebakaran, bencana ekologi yang terjadi ialah kekeringan. Beberapa daerah di Pulau Jawa seperti Temanggung, Sukoharjo, Lumajang, Banten, lalu daerah luar Jawa seperti Nusa Tenggara Barat dan Timur, hingga Bangka Belitung mulai mengalami krisis air bersih.Presiden pun memanggil sejumlah kepala kementerian dan lembaga terkait, untuk memberi pemaparan dan masukan guna meredam dampak El Nino.Lalu bagaimana sikap antisipatif yang disiapkan pemerintah pada musim kemarau dan el nino tahun ini? Selengkapnya dalam PerANTARA! (Roy Rosa Bachtiar/Suci Nurhaliza/Gunawan Wibisono/Rizky Bagus Dhermawan/Farah Khadija)</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="F175" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676540/el-nino-menguat-negara-fokus-jaga-ketersediaan-air-tangani-karhutla</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="G175" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/DF.jpg</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
+    <row r="176">
+      <c r="A176" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>Padang Padang Cup Bali jadi ajang peselancar Nasional unjuk kehebatan</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr">
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
         <is>
           <t>ANTARA - Kompetisi selancar ombak Internasional Rip Curl Cup Padang Padang kembali digelar dan berlangsung pada 1-31 Agustus 2026, di Pantai Padang Padang, Labuan Sait Pecatu, Kuta Selatan, Bali. Ajang ini menjadi ruang bagi peselancar Nasional menunjukkan kehebatan mereka bersaing dengan peselancar Internasional. (Rita Laura/Sandy Arizona/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F176" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676257/padang-padang-cup-bali-jadi-ajang-peselancar-nasional-unjuk-kehebatan</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="G176" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_PADANG-PADANG-CUP-BALI-JADI-AJANG-PESELANCAR-NASIONAL-UNJUK-KEHEBATAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
+    <row r="177">
+      <c r="A177" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B177" t="inlineStr">
         <is>
           <t>Bekuk Port FC, Persebaya gandeng Persija ke semifinal</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr">
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
         <is>
           <t>ANTARA - Persebaya membekuk Port FC 2 - 1 di laga terakhir Grup B turnamen sepak Piala Presiden 2026. Dengan hasil ini Persija lolos ke babak semifinal bersama Persebaya sebagai wakil Grup B. (Hanif Nasrullah/Sandy Arizona/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="F177" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676252/bekuk-port-fc-persebaya-gandeng-persija-ke-semifinal</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="G177" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_BEKUK-PORT-FC-PERSEBAYA-GANDENG-PERSIJA-KE-SEMIFINAL.jpg</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
+    <row r="178">
+      <c r="A178" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B178" t="inlineStr">
         <is>
           <t>Aston Villa unggul 3-1 dari Indonesia All Stars dalam tur pramusim</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr">
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
         <is>
           <t>ANTARA - Tim Indonesia All Stars, harus mengakui keunggulan atas Aston Villa dengan skor 3-1, saat laga Friendly Match di Stadion Utama Gelora Bung Karno (SUGBK) Senayan, Jakarta, pada Sabtu (1/8). Penjaga Gawang Aston Villa, James Wright, saat ditemui media di GBK mengapresiasi para pemain Indonesia All Stars, karena dinilai memiliki kualitas yang baik. (Ryan Rahman/Sandy Arizona/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F178" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676239/aston-villa-unggul-3-1-dari-indonesia-all-stars-dalam-tur-pramusim</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="G178" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_ASTON-VILLA-UNGGUL-3-1-DARI-INDONESIA-ALL-STARS-DALAM-TUR-PRAMUSIM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
+    <row r="179">
+      <c r="A179" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B179" t="inlineStr">
         <is>
           <t>Joko Widodo dinobatkan sebagai sesepuh oleh sembilan Raja Timor</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr">
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
         <is>
           <t>ANTARA - Ribuan warga memadati kawasan Pantai Lahi Lai Bissi Kopan (LLBK) Kota Kupang, Nusa Tenggara Timur, untuk menyaksikan Karnaval Budaya yang dihadiri Presiden ke-7 Republik Indonesia, Joko Widodo. Dalam prosesi adat yang menjadi puncak acara, Joko Widodo dinobatkan sebagai sesepuh atau saudara oleh sembilan raja dari kerajaan-kerajaan di Pulau Timor sebagai bentuk penghormatan terhadap nilai persaudaraan dan budaya masyarakat Timor. (Johanes Viandinando/Sandy Arizona/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F179" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676205/joko-widodo-dinobatkan-sebagai-sesepuh-oleh-sembilan-raja-timor</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="G179" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_JOKO-WIDODO-DINOBATKAN-SEBAGAI-SESEPUH-OLEH-SEMBILAN-RAJA-TIMOR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
+    <row r="180">
+      <c r="A180" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B180" t="inlineStr">
         <is>
           <t>Menag: Indeks kerukunan umat beragama RI jadi 77,89 persen di 2025</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr">
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Agama Nasaruddin Umar menyebut indeks kerukunan umat beragama naik menjadi 77,89 persen pada tahun 2025, dari sebelumnya, yakni 76,47 persen pada tahun 2024. Hal tersebut disampaikan oleh Menag saat mengahdiri agenda Zikir dan Doa Kebangsaan "Indonesia Berdaulat, Adil dan Makmur" di Lapangan Silang Monas, Jakarta, Sabtu (1/8).
 (Afra Augesti/Nico Anggriawan/Sandy Arizona/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F180" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676188/menag-indeks-kerukunan-umat-beragama-ri-jadi-7789-persen-di-2025</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="G180" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_MENAG-INDEKS-KERUKUNAN-UMAT-BERAGAMA-RI-JADI-77-89-PERSEN-DI-2025.jpg</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
+    <row r="181">
+      <c r="A181" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B181" t="inlineStr">
         <is>
           <t>KKP bantu pelaku usaha perikanan terdampak bencana di Sumbar</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr">
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
         <is>
           <t>ANTARA - Kementerian Kelautan dan Perikanan (KKP) bersama Tim Satuan Tugas Percepatan Rehabilitasi dan Rekonstruksi (PRR) Provinsi Sumatera Barat, mempercepat dan memastikan operasionalisasi budi daya, nelayan serta pengolahan ikan segera berjalan pascabencana hidrometeorologi yang terjadi akhir November tahun lalu. Untuk itu, KKP memberikan bantuan awal berupa bibit ikan dan pakan, dan ekskavator, kepada pelaku usaha perikanan yang terdampak bencana hidrometeorologis di Kota Padang, Kabupaten Padang Pariaman, Kabupaten Solok dan Kabupaten Agam.
 (Melani Friati/Sandy Arizona/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="F181" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676172/kkp-bantu-pelaku-usaha-perikanan-terdampak-bencana-di-sumbar</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
+      <c r="G181" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_KKP-BANTU-PELAKU-USAHA-PERIKANAN-TERDAMPAK-BENCANA-DI-SUMBAR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
+    <row r="182">
+      <c r="A182" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>INZS 2026 perkuat komitmen Indonesia hadapi krisis iklim</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr">
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah Indonesia terus mempercepat transisi energi sebagai bagian dari upaya mengatasi perubahan iklim melalui berbagai proyek yang mulai direalisasikan. Komitmen tersebut mengemuka dalam Indonesia Net Zero Summit (INZS) 2026 di Balai Kartini, Jakarta, Sabtu (1/8). Pendiri Foreign Policy Community of Indonesia (FPCI), Dino Patti Djalal, menegaskan bahwa penanganan perubahan iklim harus menjadi prioritas karena dampaknya menyentuh hampir seluruh aspek kehidupan manusia.
 (Irfan Hardiansah/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="F182" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676087/inzs-2026-perkuat-komitmen-indonesia-hadapi-krisis-iklim</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="G182" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/INZS-2026-PERKUAT-KOMITMEN-INDONESIA-HADAPI-KRISIS-IKLIM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
+    <row r="183">
+      <c r="A183" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B183" t="inlineStr">
         <is>
           <t>Kemeriahan menyambut bulan kemerdekaan Indonesia di Malaysia</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr">
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
         <is>
           <t>ANTARA - Kegembiraan menyambut bulan kemerdekaan Republik Indonesia turut dirasakan para warga negara Indonesia yang berada di negeri jiran Malaysia. WNI dengan penuh antusias mengikuti berbagai perlombaan yang diselenggarakan Kedutaan Besar Republik Indonesia (KBRI) di Kuala Lumpur, Malaysia, Sabtu (1/8).
 (Rangga Pandu Asmara Jingga/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="F183" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676063/kemeriahan-menyambut-bulan-kemerdekaan-indonesia-di-malaysia</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="G183" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KEMERIAHAN-MENYAMBUT-BULAN-KEMERDEKAAN-INDONESIA-DI-MALAYSIA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
+    <row r="184">
+      <c r="A184" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B184" t="inlineStr">
         <is>
           <t>Cari Bibit unggul, Bogor gelar sirkuit panjat tebing anak dan remaja</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr">
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
         <is>
           <t>ANTARA - Federasi Panjat Tebing Indonesia (FPTI) Kota Bogor menggelar Sirkuit Panjat Tebing se-Kota Bogor sebagai ajang pencarian bibit atlet muda, Sabtu (1/8). Dengan diikuti 100 peserta anak-anak dan remaja, kegiatan itu mempertandingkan kategori lead dan speed untuk kelompok umur under 11, under 13, dan under 19.
 (Fadzar Ilham Pangestu/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="F184" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676021/cari-bibit-unggul-bogor-gelar-sirkuit-panjat-tebing-anak-dan-remaja</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
+      <c r="G184" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/CARI-BIBIT-UNGGUL-BOGOR-GELAR-SIRKUIT-PANJAT-TEBING-ANAK-DAN-REMAJA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
+    <row r="185">
+      <c r="A185" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B185" t="inlineStr">
         <is>
           <t>Karhutla Tumbang Nusa meluas, 104 hektar gambut terbakar</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr">
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
         <is>
           <t>ANTARA - Kebakaran hutan dan lahan (karhutla) di Desa Tumbang Nusa, Kecamatan Jabiren Raya, Kabupaten Pulang Pisau, Kalimantan Tengah, telah menghanguskan sekitar 104 hektare lahan gambut, Sabtu (1/8). Peristiwa tersebut memicu operasi penanganan terpadu yang melibatkan sekitar 416 personel gabungan melalui jalur darat, serta didukung dua unit helikopter water bombing untuk mempercepat pemadaman yang jauh dari tim darat. 
 (Redianto Tumon Sp/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
+      <c r="F185" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676013/karhutla-tumbang-nusa-meluas-104-hektar-gambut-terbakar</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
+      <c r="G185" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KARHUTLA-TUMBANG-NUSA-MELUAS-104-HEKTAR-GAMBUT-TERBAKAR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
+    <row r="186">
+      <c r="A186" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B186" t="inlineStr">
         <is>
           <t>54 Atlet menembak Kalsel, bertanding pada Kejuaraan Wali Kota Cup</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr">
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah Kota Banjarmasin bersama Perbakin menggelar kejuaraan menembak Wali Kota Cup 2026. Kejuaraan diikuti oleh 54 atlet dari berbagai daerah di Kalsel sebagai wadah seleksi dan persiapan atlet kalimantan selatan menuju Pra-PON.
 (Latif Thohir/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
+      <c r="F186" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675995/54-atlet-menembak-kalsel-bertanding-pada-kejuaraan-wali-kota-cup</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
+      <c r="G186" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/54-ATLET-MENEMBAK-KALSEL-BERTANDING-PADA-KEJUARAAN-WALI-KOTA-CUP.jpg</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
+    <row r="187">
+      <c r="A187" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B187" t="inlineStr">
         <is>
           <t>Polda Riau kirim Tim Ekspedisi Merah Putih Presisi ke 17 desa 3T</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr">
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
         <is>
           <t>ANTARA - Kapolda Riau Irjen Pol Herry Heryawan melepas Tim Ekspedisi Merah Putih Presisi Polda Riau yang akan bertugas di 17 desa wilayah tertinggal, terdepan, dan terluar atau 3T, Sabtu (1/8). Ekspedisi yang berlangsung hingga 17 Agustus mendatang itu membawa berbagai program sosial, lingkungan, dan penguatan kebangsaan bagi masyarakat pesisir serta wilayah terluar di Provinsi Riau.
 (Farah Khadija/Annisa Firdausi/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="F187" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675964/polda-riau-kirim-tim-ekspedisi-merah-putih-presisi-ke-17-desa-3t</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
+      <c r="G187" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/POLDA-RIAU-KIRIM-TIM-EKSPEDISI-MERAH-PUTIH-PRESISI-KE-17-DESA-3T.jpg</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
+    <row r="188">
+      <c r="A188" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B188" t="inlineStr">
         <is>
           <t>Hadapi El Nino, pemerintah tingkatkan mitigasi karhutla</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr">
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah memperkuat langkah antisipasi menghadapi potensi el nino yang diperkirakan meningkatkan risiko kebakaran hutan dan lahan. Menteri Lingkungan Hidup, Muhammad Jumhur Hidayat usai membuka Indonesia Net Zero Summit (INZS) 2026 yang diselenggarakan di Balai Kartini, Jakarta, pada Sabtu (1/8) menyebutkan, pihaknya menekan potensi karhutla sejak dini, salah satunya dengan membangun kanal blocking.
 (Irfan Hardiansah/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="F188" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675936/hadapi-el-nino-pemerintah-tingkatkan-mitigasi-karhutla</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
+      <c r="G188" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/HADAPI-EL-NINO-PEMERINTAH-TINGKATKAN-MITIGASI-KARHUTLA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
+    <row r="189">
+      <c r="A189" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B189" t="inlineStr">
         <is>
           <t>Mensos resmikan Sekolah Rakyat Terintegrasi 1 Sukoharjo</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr">
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Sosial Republik Indonesia Saifullah Yusuf membuka pelaksanaan Masa Pengenalan Lingkungan Sekolah (MPLS) di Sekolah Rakyat Terintegrasi (SRT) 1 Kabupaten Sukoharjo, Sabtu (1/8). Mensos menyebut meski proses pembangunan fisik belum sepenuhnya rampung, pihaknya memastikan kegiatan belajar mengajar sudah dapat dilaksanakan karena progres pembangunan telah mencapai sekitar 98 persen.(Denik Apriyani/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
+      <c r="F189" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675924/mensos-resmikan-sekolah-rakyat-terintegrasi-1-sukoharjo</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
+      <c r="G189" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/MENSOS-RESMIKAN-SEKOLAH-RAKYAT-TERINTEGRASI-1-SUKOHARJO.jpg</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
+    <row r="190">
+      <c r="A190" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B190" t="inlineStr">
         <is>
           <t>Lanud Sjamsudin Noor gelar Bakti Sosial Hari Bakti TNI AU ke-79</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr">
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
         <is>
           <t>ANTARA - Ratusan warga di Banjarbaru, Kalimantan Selatan, antusias mengikuti kegiatan bakti sosial yang diselenggarakan oleh Pangkalan Udara (Lanud) Sjamsudin Noor pada Sabtu (1/8). Kegiatan ini dilaksanakan sebagai rangkaian peringatan Hari Bhakti TNI Angkatan Udara Ke-79
 (Latif Thohir/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
+      <c r="F190" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675872/lanud-sjamsudin-noor-gelar-bakti-sosial-hari-bakti-tni-au-ke-79</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
+      <c r="G190" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/LANUD-SJAMSUDIN-NOOR-GELAR-BAKTI-SOSIAL-HARI-BAKTI-TNI-AU-KE-79.jpg</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
+    <row r="191">
+      <c r="A191" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B191" t="inlineStr">
         <is>
           <t>Prancis perketat pemeriksaan produk tani, lawan praktik francization</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr">
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
         <is>
           <t>ANTARA - Prancis memperketat pemeriksaan terhadap asal-usul produk pertanian guna memberantas praktik "francization", yaitu pelabelan ulang produk impor agar tampak sebagai hasil produksi dalam negeri. Langkah ini diambil untuk melindungi konsumen dan produsen lokal, dengan pelanggar terancam denda hingga 300.000 euro dan hukuman penjara.(XINHUA/ Nabila Anisya Charisty/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="F191" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675865/prancis-perketat-pemeriksaan-produk-tani-lawan-praktik-francization</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="G191" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PRANCIS-PERKETAT-PEMERIKSAAN-PRODUK-TANI-LAWAN-PRAKTIK-FRANCIZATION.jpg</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
+    <row r="192">
+      <c r="A192" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B192" t="inlineStr">
         <is>
           <t>KM. Prince Soya terbakar saat bersandar di Pelabuhan Samarinda</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr">
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
         <is>
           <t>ANTARA - Kapal Motor (KM) Prince Soya terbakar pada Sabtu (1/8) saat bersandar di Pelabuhan Samarinda, Kalimantan Timur. Kapal penumpang yang biasa melayani rute Samarinda - Pare-Pare, Sulawesi Selatan itu terbakar di bagian dek sebelah kanan yang diduga bersumber dari tangki berisi pelumas mesin. (Hanifan Ma'ruf/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
+      <c r="F192" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675853/km-prince-soya-terbakar-saat-bersandar-di-pelabuhan-samarinda</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="G192" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KM.PRINCE-SOYA-TERBAKAR-SAAT-BERSANDAR-DI-PELABUHAN-SAMARINDA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
+    <row r="193">
+      <c r="A193" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B193" t="inlineStr">
         <is>
           <t>St. Petersburg luncurkan festival sepeda motor untuk pertama kalinya</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr">
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
         <is>
           <t>ANTARA - Saint Petersburg Motor Festival resmi dibuka, Jumat (31/7) selama tiga hari berturut-turut dalam pembukaan perdananya. Acara tersebut digelar untuk menghibur para penikmat sepeda motor, musik, serta pengunjung umum lainnya.(XINHUA/ Nabila Anisya Charisty/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
+      <c r="F193" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675828/st-petersburg-luncurkan-festival-sepeda-motor-untuk-pertama-kalinya</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
+      <c r="G193" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/ST.PETERSBURG-LUNCURKAN-FESTIVAL-SEPEDA-MOTOR-UNTUK-PERTAMA-KALINYA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
+    <row r="194">
+      <c r="A194" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="B194" t="inlineStr">
         <is>
           <t>KPHL Batam dan Akar Bhumi Indonesia berkolaborasi lestarikan bakau</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr">
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
         <is>
           <t>ANTARA - Kesatuan Pengelolaan Hutan Lindung (KPHL) Kota Batam bersama Lembaga Swadaya Masyarakat (LSM) Akar Bhumi Indonesia menanam 450 bibit bakau di Batam, Kepulauan Riau, Sabtu (1/8). Penanaman bibit bakau tersebut dilakukan untuk memastikan daerah pesisir Kota Batam terlindungi di tengah perubahan iklim, sekaligus memperimgati Hari Mangrove Sedunia 2026.(Angiela Chantique/ Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
+      <c r="F194" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675804/kphl-batam-dan-akar-bhumi-indonesia-berkolaborasi-lestarikan-bakau</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
+      <c r="G194" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KPHL-BATAM-DAN-AKAR-BHUMI-INDONESIA-BERKOLABORASI-LESTARIKAN-BAKAU.jpg</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
+    <row r="195">
+      <c r="A195" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
+      <c r="B195" t="inlineStr">
         <is>
           <t>Ribuan warga padati Jalan El Tari saat kunjungan Jokowi di Kupang, NTT</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr">
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
         <is>
           <t>ANTARA - Ribuan warga Kota Kupang dan sekitarnya memadati kawasan "Car Free Day" di Jalan El Tari, Kota Kupang, Nusa Tenggara Timur, Sabtu (1/8),  untuk menyambut kunjungan Joko Widodo. Dalam suasana penuh antusias, masyarakat bersalaman dan meminta swafoto bersama sosok Presiden ke-7 Republik Indonesia tersebut.
 (Johanes Viandinando/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="F195" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675784/ribuan-warga-padati-jalan-el-tari-saat-kunjungan-jokowi-di-kupang-ntt</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="G195" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/RIBUAN-WARGA-PADATI-JALAN-EL-TARI-SAAT-KUNJUNGAN-JOKOWI-DI-KUPANG-NTT.jpg</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Populasi Malaysia naik menjadi 34,4 juta jiwa di 2026</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>ANTARA - Populasi diperkirakan naik menjadi 34,4 juta jiwa pada 2026. Angka tersebut naik 0,5 persen dibandingkan tahun sebelumnya dengan persentase penduduk asli atau warga Bumiputera masih menjadi kelompok terbesar. 
-(XINHUA/ Nabila Anisya Charisty/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5675756/populasi-malaysia-naik-menjadi-344-juta-jiwa-di-2026</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/POPULASI-MALAYSIA-NAIK-MENJADI-34-4-JUTA-JIWA-DI-2026.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>KAI Sumut siapkan empat pos kesehatan demi kenyamanan penumpang</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>ANTARA - PT Kereta Api Indonesia (KAI) Divisi Regional (Divre) I Sumatera Utara menyiagakan empat Pos Kesehatan (Poskes) yang tersebar di stasiun-stasiun strategis guna memastikan keselamatan, kesehatan, serta kenyamanan seluruh penumpang selama perjalanan. Fasilitas Pos Kesehatan tersebut beroperasi di Stasiun Medan, Stasiun Tebing Tinggi, Stasiun Kisaran, dan Stasiun Rantauprapat.(M. Valery Maulidzar S/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5675753/kai-sumut-siapkan-empat-pos-kesehatan-demi-kenyamanan-penumpang</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/KAI-SUMUT-SIAPKAN-EMPAT-POS-KESEHATAN-DEMI-KENYAMANAN-PENUMPANG.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Optimalisasi lahan tingkatkan pola tanam sawah di Kaltim</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>ANTARA - Langkah optimalisasi lahan (Oplah) untuk memaksimalkan potensi pertanian di Kalimantan Timur mampu meningkatkan pola tanam petani dari satu kali menjadi dua kali setahun. Melalui sistem pertanian yang ditunjang teknologi, program oplah ini ditujukan untuk mendongkrak frekuensi panen serta jumlah produksi padi di Kaltim.(Hanifan Ma'ruf/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5675737/optimalisasi-lahan-tingkatkan-pola-tanam-sawah-di-kaltim</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/OPTIMALISASI-LAHAN-TINGKATKAN-POLA-TANAM-SAWAH-DI-KALTIM.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Pasukan matra laut bertolak ke Dabo Singkep untuk gelar Latopsfib</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>ANTARA - Tentara Nasional Indonesia (TNI) Angkatan Laut pada Sabtu (1/8) memberangkatkan pasukan beserta alat utama sistem senjata (alutsista) untuk mengikuti latihan operasi Amfibi (Latopsfib) di Dabo Singkep, Kepulauan Riau. Kegiatan ini merupakan bagian dari Latihan TNI Terintegrasi 2026 yang melibatkan ribuan personel dari tiga matra untuk menguji kesiapsiagaan dalam menghadapi kemungkinan situasi yang berada di luar kendali.(Hanif Nasrullah/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5675732/pasukan-matra-laut-bertolak-ke-dabo-singkep-untuk-gelar-latopsfib</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PASUKAN-MATRA-LAUT-BERTOLAK-KE-DABO-SINGKEP-UNTUK-GELAR-LATOPSFIB.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Apartemen ikan, napas baru wisata Bahari Desa Namu</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>ANTARA - Sejumlah mahasiswa Kuliah Kerja Nyata (KKN) dari beberapa kampus besama pemerintah Desa Wisata Namu, Kabupaten Konawe Selatan, Sulawesi Tenggara membuat apartemen ikan di bawah laut Desa Namu. Langkah tersebut dilakukan untuk melestarikan kosistem laut dan menjaga keberlanjutan pariwisata di wilayah  setempat.(Saharudin/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5675719/apartemen-ikan-napas-baru-wisata-bahari-desa-namu</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/APARTEMEN-IKAN-NAPAS-BARU-WISATA-BAHARI-DESA-NAMU.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Koops TNI Habema evakuasi satu jenazah korban tembakan OPM di Yahukimo</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 15:05:01 +0700</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>ANTARA - Koops TNI Habema pada Jumat (31/8), mengevakuasi satu dari tiga jenazah korban penembakan yang diduga dilakukan kelompok organisasi papua merdeka (OPM) Kodap XVI Yahukimo. Korban bernama Teina Alya ditemukan di lokasi longsoran Kali Kolof, Distrik Seradala, Kabupaten Yahukimo, Papua Pegunungan dan telah diserahkan kepada pihak keluarga untuk di makamkan.(Laksa Mahendra/Rizky Bagus Dhermawan/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5675675/koops-tni-habema-evakuasi-satu-jenazah-korban-tembakan-opm-di-yahukimo</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-01-141537.jpg</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G152"/>
+  <autoFilter ref="A1:G195"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_antara_2026-08-03.xlsx
+++ b/data/berita_antara_2026-08-03.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$195</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$216</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,10 +419,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G195"/>
+  <dimension ref="A1:G216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -2061,28 +2061,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Prabowo terima laporan Bahlil soal program ketahanan energi</t>
+          <t>Ke Jepara, Mendikdasmen: Lahan SNT harus benar-benar siap dikembangkan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:02:25 +0700</t>
+          <t>Mon, 03 Aug 2026 15:17:55 +0700</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Presiden Prabowo Subianto menerima laporan terbaru dari Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil ...</t>
+          <t>Menteri Pendidikan Dasar dan Menengah (Mendikdasmen) Abdul Mu’ti meninjau langsung kesiapan lahan untuk ...</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677561/prabowo-terima-laporan-bahlil-soal-program-ketahanan-energi</t>
+          <t>https://www.antaranews.com/berita/5677475/ke-jepara-mendikdasmen-lahan-snt-harus-benar-benar-siap-dikembangkan</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_5125.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/21/1000216743.jpg</t>
         </is>
       </c>
     </row>
@@ -2094,28 +2094,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Menlu Iran sebut pembicaraan soal Selat Hormuz dengan Oman masuki tahap akhir</t>
+          <t>Jepang dan AS lakukan intervensi bersama di pasar valuta asing</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:01:55 +0700</t>
+          <t>Mon, 03 Aug 2026 15:17:09 +0700</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Menteri Luar Negeri Iran Abbas Araghchi  mengatakan pembicaraan soal Selat Hormuz dengan Oman masuki tahap ...</t>
+          <t>Menteri Keuangan Satsuki Katayama mengatakan bahwa Jepang dan Amerika Serikat telah melakukan intervensi pembelian yen ...</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677557/menlu-iran-sebut-pembicaraan-soal-selat-hormuz-dengan-oman-masuki-tahap-akhir</t>
+          <t>https://www.antaranews.com/berita/5677472/jepang-dan-as-lakukan-intervensi-bersama-di-pasar-valuta-asing</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/HormuzXinhuaWangQiang_aa.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CjkinzN000009_20260803_CBMFN0A001.jpeg</t>
         </is>
       </c>
     </row>
@@ -2127,28 +2127,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Wamendiktisaintek dorong kampus di Riau dan Kepri bangun konsorsium</t>
+          <t>TNI AU dan AU Kamboja perkuat hubungan dengan jalin kerja sama militer</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:01:51 +0700</t>
+          <t>Mon, 03 Aug 2026 15:15:59 +0700</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wakil Menteri Pendidikan Tinggi, Sains, dan Teknologi (Wamendiktisaintek) Fauzan mendorong perguruan tinggi di Provinsi ...</t>
+          <t>TNI Angkatan Udara (AU) memperkuat hubungan dengan AU Kamboja atau Cambodian Air Force (CAF) dengan menyepakati ...</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677555/wamendiktisaintek-dorong-kampus-di-riau-dan-kepri-bangun-konsorsium</t>
+          <t>https://www.antaranews.com/berita/5677468/tni-au-dan-au-kamboja-perkuat-hubungan-dengan-jalin-kerja-sama-militer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/18/1000428031.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001554368.jpg</t>
         </is>
       </c>
     </row>
@@ -2160,28 +2160,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Partai Buruh Brasil calonkan Lula da Silva untuk masa jabatan keempat</t>
+          <t>KPK geledah tujuh lokasi pada 30 Juli-1 Agustus terkait kasus Pemalang</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:01:22 +0700</t>
+          <t>Mon, 03 Aug 2026 15:14:49 +0700</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ANTARA - Partai Buruh di Brasil pada Minggu (2/8) waktu setempat, resmi mencalonkan petahana Luiz Inacio Lula da Silva ...</t>
+          <t>Komisi Pemberantasan Korupsi (KPK) menggeledah tujuh lokasi pada 30 Juli–1 Agustus 2026 terkait penyidikan kasus ...</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5677541/partai-buruh-brasil-calonkan-lula-da-silva-untuk-masa-jabatan-keempat</t>
+          <t>https://www.antaranews.com/berita/5677465/kpk-geledah-tujuh-lokasi-pada-30-juli-1-agustus-terkait-kasus-pemalang</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-03-154005.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/kpk-tahan-bupati-pemalang-2830443.jpg</t>
         </is>
       </c>
     </row>
@@ -2193,28 +2193,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Program konservasi Pulau Sabira PLN raih penghargaan nasional</t>
+          <t>Paus Leo XIV prihatin atas situasi krisis migran di Ceuta</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:00:04 +0700</t>
+          <t>Mon, 03 Aug 2026 15:14:34 +0700</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>PT PLN (Persero) Unit Induk Distribusi (UID) Jakarta Raya meraih penghargaan "Predikat Platinum Alignment" ...</t>
+          <t>ANTARA - Paus Leo XIV  menyampaikan keprihatinan atas situasi krisis migran di Enklave, Spanyol, Ceuta.  Saat ...</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677551/program-konservasi-pulau-sabira-pln-raih-penghargaan-nasional</t>
+          <t>https://www.antaranews.com/video/5677384/paus-leo-xiv-prihatin-atas-situasi-krisis-migran-di-ceuta</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/e9219a6c-ccd6-473e-bf06-a7dd465568bd.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AYM_PAUS-LEO-XIV-PRIHATIN-ATAS-SITUASI-KRISIS.jpg</t>
         </is>
       </c>
     </row>
@@ -2226,28 +2226,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Pemkot Ambon salurkan air bersih gratis jika kekeringan terjadi</t>
+          <t>BMKG: Musim kemarau Papua Pegunungan bakal berakhir pada akhir Agustus</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:59:59 +0700</t>
+          <t>Mon, 03 Aug 2026 15:07:50 +0700</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ANTARA - Pemerintah Kota Ambon, Maluku, menyiapkan langkah antisipasi untuk menjamin ketersediaan air bersih bagi ...</t>
+          <t>Badan Meteorologi, Klimatologi dan Geofisika (BMKG) melalui Stasiun Meteorologi Kelas III Wamena, Kabupaten Jayawijaya, ...</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5677489/pemkot-ambon-salurkan-air-bersih-gratis-jika-kekeringan-terjadi</t>
+          <t>https://www.antaranews.com/berita/5677463/bmkg-musim-kemarau-papua-pegunungan-bakal-berakhir-pada-akhir-agustus</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-03-151844.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260730-WA0008.jpg</t>
         </is>
       </c>
     </row>
@@ -2259,28 +2259,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Razia balap liar, Polres Temanggung sita 106 motor</t>
+          <t>Koalisi buruh serahkan usulan RUU Ketenagakerjaan ke pimpinan DPR</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:58:54 +0700</t>
+          <t>Mon, 03 Aug 2026 15:05:55 +0700</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ANTARA - Kepolisian Resor (Polres) Temanggung, Jawa Tengah menyita 106 sepeda motor dalam razia balap liar yang digelar ...</t>
+          <t>Koalisi dari berbagai konfederasi buruh menyerahkan draf usulan untuk penyusunan Rancangan Undang-Undang (RUU) ...</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5677488/razia-balap-liar-polres-temanggung-sita-106-motor</t>
+          <t>https://www.antaranews.com/berita/5677460/koalisi-buruh-serahkan-usulan-ruu-ketenagakerjaan-ke-pimpinan-dpr</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_RAZIA-BALAP-LIAR-POLRES-TEMANGGUNG-SITA-106-MOTOR.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001295553.jpg</t>
         </is>
       </c>
     </row>
@@ -2292,28 +2292,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Pemain muda Barcelona incar tempat di tim utama 2026/2027</t>
+          <t>Charles Honoris dorong putusan MK soal MBG diterapkan pada APBN 2027</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:57:56 +0700</t>
+          <t>Mon, 03 Aug 2026 14:56:05 +0700</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Para pemain muda Barcelona, khususnya yang kini memperkuat Barcelona Atletic (Barcelona B), mengincar tempat di tim ...</t>
+          <t>Wakil Ketua Komisi IX DPR RI Charles Honoris mendorong putusan Mahkamah Konstitusi (MK) mengenai anggaran program Makan ...</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677547/pemain-muda-barcelona-incar-tempat-di-tim-utama-2026-2027</t>
+          <t>https://www.antaranews.com/berita/5677456/charles-honoris-dorong-putusan-mk-soal-mbg-diterapkan-pada-apbn-2027</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_154443.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/upscalemedia-transformed-167.jpeg</t>
         </is>
       </c>
     </row>
@@ -2325,28 +2325,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>HYBE siapkan debut girl group Tuide</t>
+          <t>Wamensos: Kolaborasi data perkuatkan bantuan JKN lebih akuntabel</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:57:13 +0700</t>
+          <t>Mon, 03 Aug 2026 14:54:53 +0700</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Perusahaan hiburan Korea Selatan, HYBE melalui label naungannya ABD tengah mempersiapkan debut girl group Kpop bernama ...</t>
+          <t>Wakil Menteri Sosial (Wamensos) Agus Jabo Priyono mengatakan kolaborasi strategis yang dilakukan bersama BPJS ...</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677544/hybe-siapkan-debut-girl-group-tuide</t>
+          <t>https://www.antaranews.com/berita/5677453/wamensos-kolaborasi-data-perkuatkan-bantuan-jkn-lebih-akuntabel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/644817de-49b2-42cd-92a5-0d0a14d911ce.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-14.44.56-1.jpeg</t>
         </is>
       </c>
     </row>
@@ -2358,61 +2358,61 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Pemkot Jakut edukasi pelajar tentang teknik pertanian di perkotaan</t>
+          <t>Presiden Iran: AS harus tetap patuhi nota kesepahaman</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:52:39 +0700</t>
+          <t>Mon, 03 Aug 2026 14:54:11 +0700</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Suku Dinas Ketahanan Pangan, Kelautan dan Pertanian (KPKP) Jakarta Utara mengedukasi puluhan pelajar dari enam sekolah ...</t>
+          <t>Presiden Iran Masoud Pezeshkian mengatakan pada Minggu (2/8) bahwa Amerika Serikat harus tetap berkomitmen pada nota ...</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677540/pemkot-jakut-edukasi-pelajar-tentang-teknik-pertanian-di-perkotaan</t>
+          <t>https://www.antaranews.com/berita/5677449/presiden-iran-as-harus-tetap-patuhi-nota-kesepahaman</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/2dfab961fe56.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CjkinzN000008_20260803_CBMFN0A001.jpeg</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>photo, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Jelang HUT RI, Polda Kepri bagikan bendera ke warga di pulau-pulau terluar</t>
+          <t>Ekonomi kelautan China catat pertumbuhan stabil pada H1 2026</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:51:09 +0700</t>
+          <t>Mon, 03 Aug 2026 14:50:44 +0700</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Warga memasang Bendera Merah Putih di perahu serta pekarangan rumah panggung yang dibagikan Polda Kepri di Pulau Dapur ...</t>
+          <t>Produk laut bruto (PLB) China mencapai 5,5 triliun yuan (1 yuan = Rp2.676) pada paruh pertama (H1) 2026, naik 5,1 ...</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5677539/jelang-hut-ri-polda-kepri-bagikan-bendera-ke-warga-di-pulau-pulau-terluar</t>
+          <t>https://www.antaranews.com/berita/5677441/ekonomi-kelautan-china-catat-pertumbuhan-stabil-pada-h1-2026</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Pembagian-Bendera-Merah-Putih-Di-Pulau-Pulau-Terluar-030826-tpp-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CjkinzN000010_20260803_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
@@ -2424,28 +2424,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Pelindo siagakan posko terpadu bagi korban KMP Mutiara Sentosa II</t>
+          <t>TNI AL tuntaskan latihan gabungan dengan AL Australia</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:45:16 +0700</t>
+          <t>Mon, 03 Aug 2026 14:46:09 +0700</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PT Pelabuhan Indonesia (Persero) Regional 3 Sub Regional Jawa menyiagakan posko terpadu korban kebakaran Kapal Motor ...</t>
+          <t>TNI AL menuntaskan kegiatan latihan gabungan dengan AL Australia atau Royal Australian Navy (RAN) dalam ajang Cassowary ...</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677537/pelindo-siagakan-posko-terpadu-bagi-korban-kmp-mutiara-sentosa-ii</t>
+          <t>https://www.antaranews.com/berita/5677436/tni-al-tuntaskan-latihan-gabungan-dengan-al-australia</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/260405.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001554245.jpg</t>
         </is>
       </c>
     </row>
@@ -2457,28 +2457,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MPR undang Presiden Prabowo hadiri sidang tahunan pada 14 Agustus</t>
+          <t>Wamenkomdigi: TVRI institusi strategis penjaga ruang informasi bangsa</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:43:18 +0700</t>
+          <t>Mon, 03 Aug 2026 14:45:19 +0700</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Pimpinan MPR mengundang Presiden Prabowo Subianto menghadiri Sidang Tahunan MPR yang rencananya digelar pada Jumat, 14 ...</t>
+          <t>Wakil Menteri Komunikasi dan Digital (Wamenkomdigi) Angga Raka Prabowo menyatakan Lembaga Penyiaran Publik (LPP) TVRI ...</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677536/mpr-undang-presiden-prabowo-hadiri-sidang-tahunan-pada-14-agustus</t>
+          <t>https://www.antaranews.com/berita/5677432/wamenkomdigi-tvri-institusi-strategis-penjaga-ruang-informasi-bangsa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000398675.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0224.jpg</t>
         </is>
       </c>
     </row>
@@ -2490,259 +2490,260 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Kesbangpol Pontianak antisipasi konflik sosial akibat karhutla</t>
+          <t>BPK berikan opini WTP kepada Kemenko Kumham Imipas atas LK 2025</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:42:51 +0700</t>
+          <t>Mon, 03 Aug 2026 14:44:20 +0700</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ANTARA - Badan Kesatuan Bangsa dan Politik (Kesbangpol) Kota Pontianak mengidentifikasi potensi gangguan keamanan dan ...</t>
+          <t>Badan Pemeriksa Keuangan RI memberikan opini Wajar Tanpa Pengecualian (WTP) kepada seluruh kementerian di bawah ...</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5677519/kesbangpol-pontianak-antisipasi-konflik-sosial-akibat-karhutla</t>
+          <t>https://www.antaranews.com/berita/5677427/bpk-berikan-opini-wtp-kepada-kemenko-kumham-imipas-atas-lk-2025</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KESBANGPOL-PONTIANAK-ANTISIPASI-KONFLIK-SOSIAL-AKIBAT-KARHUTLA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001216320.jpg</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Data untuk Indonesia, bakti untuk negeri</t>
+          <t>PT PAL-BRIN wujudkan galangan kapal hijau dukung industri perkapalan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:42:25 +0700</t>
+          <t>Mon, 03 Aug 2026 12:43:28 +0700</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bulan Agustus selalu menghadirkan suasana yang berbeda. Bendera Merah Putih berkibar di halaman rumah, berbagai ...</t>
+          <t>PT PAL Indonesia bersama Badan Riset dan Inovasi Nasional (BRIN) berkolaborasi mewujudkan transformasi green ...</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677535/data-untuk-indonesia-bakti-untuk-negeri</t>
+          <t>https://www.antaranews.com/berita/5677267/pt-pal-brin-wujudkan-galangan-kapal-hijau-dukung-industri-perkapalan</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/1001511288.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/a647aa30-a843-4000-98a0-07d27228a41e.jpeg</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Prabowo: Persatuan selalu terlihat saat timnas Indonesia bermain</t>
+          <t>Pangan, transportasi, dan emas perhiasan dorong inflasi pada Juli 2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:40:54 +0700</t>
+          <t>Mon, 03 Aug 2026 12:32:11 +0700</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Presiden Republik Indonesia Prabowo Subianto mengaku selalu melihat persatuan setiap kali timnas Indonesia ...</t>
+          <t>Badan Pusat Statistik (BPS) mencatat kelompok makanan, minuman, dan tembakau, transportasi, serta perawatan pribadi dan ...</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677532/prabowo-persatuan-selalu-terlihat-saat-timnas-indonesia-bermain</t>
+          <t>https://www.antaranews.com/berita/5677256/pangan-transportasi-dan-emas-perhiasan-dorong-inflasi-pada-juli-2026</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0003_3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/bps.jpeg</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PSEL Serang Raya jadi solusi pengelolaan sampah tiga daerah</t>
+          <t>BPS: Neraca perdagangan Januari-Juni 2026 surplus 3,58 miliar dolar AS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:40:46 +0700</t>
+          <t>Mon, 03 Aug 2026 12:27:18 +0700</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ANTARA - Fasilitas Pengolahan Sampah menjadi Energi Listrik (PSEL) Serang Raya akan dibangun di TPSA Cilowong, Kota ...</t>
+          <t>Badan Pusat Statistik (BPS) mencatat bahwa neraca perdagangan barang Indonesia mengalami surplus senilai 3,58 miliar ...</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5677492/psel-serang-raya-jadi-solusi-pengelolaan-sampah-tiga-daerah</t>
+          <t>https://www.antaranews.com/berita/5677252/bps-neraca-perdagangan-januari-juni-2026-surplus-358-miliar-dolar-as</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AYM_PSEL-SERANG-RAYA-JADI-SOLUSI-PENGELOLAAN-SAMPAH.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/bps.jpeg</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Dewas KPK sempurnakan Perdewas untuk atur etik PNYD hingga potong gaji</t>
+          <t>Laba bersih Tugu Insurance capai Rp480,29 miliar pada semester I 2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:39:59 +0700</t>
+          <t>Mon, 03 Aug 2026 12:24:56 +0700</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dewan Pengawas Komisi Pemberantasan Korupsi (Dewas KPK) tengah menyempurnakan peraturan Dewas KPK (Perdewas) untuk ...</t>
+          <t>PT Asuransi Tugu Pratama Indonesia Tbk atau Tugu Insurance membukukan laba tahun berjalan yang dapat diatribusikan ...</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677531/dewas-kpk-sempurnakan-perdewas-untuk-atur-etik-pnyd-hingga-potong-gaji</t>
+          <t>https://www.antaranews.com/berita/5677249/laba-bersih-tugu-insurance-capai-rp48029-miliar-pada-semester-i-2026</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_8184.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-11.02.17.jpeg</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Kelurahan Dukuh Jaktim perketat pengawasan TPS liar pascakebakaran</t>
+          <t>KPHL Batam dan Akar Bhumi Indonesia berkolaborasi lestarikan bakau</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:39:50 +0700</t>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kelurahan Dukuh, Jakarta Timur, bersama pengurus RT 013 dan RW 03 memperketat pengawasan tempat penampungan sementara ...</t>
+          <t>ANTARA - Kesatuan Pengelolaan Hutan Lindung (KPHL) Kota Batam bersama Lembaga Swadaya Masyarakat (LSM) Akar Bhumi Indonesia menanam 450 bibit bakau di Batam, Kepulauan Riau, Sabtu (1/8). Penanaman bibit bakau tersebut dilakukan untuk memastikan daerah pesisir Kota Batam terlindungi di tengah perubahan iklim, sekaligus memperimgati Hari Mangrove Sedunia 2026.(Angiela Chantique/ Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677527/kelurahan-dukuh-jaktim-perketat-pengawasan-tps-liar-pascakebakaran</t>
+          <t>https://www.antaranews.com/berita/5675804/kphl-batam-dan-akar-bhumi-indonesia-berkolaborasi-lestarikan-bakau</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/InShot_20260803_145658796.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/KPHL-BATAM-DAN-AKAR-BHUMI-INDONESIA-BERKOLABORASI-LESTARIKAN-BAKAU.jpg</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BPBD Sulbar intensifkan edukasi pencegahan karhutla</t>
+          <t>Ribuan warga padati Jalan El Tari saat kunjungan Jokowi di Kupang, NTT</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:38:10 +0700</t>
+          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Badan Penanggulangan Bencana Daerah (BPBD) Provinsi Sulawesi Barat mengintensifkan edukasi dan peningkatan kesadaran ...</t>
+          <t>ANTARA - Ribuan warga Kota Kupang dan sekitarnya memadati kawasan "Car Free Day" di Jalan El Tari, Kota Kupang, Nusa Tenggara Timur, Sabtu (1/8),  untuk menyambut kunjungan Joko Widodo. Dalam suasana penuh antusias, masyarakat bersalaman dan meminta swafoto bersama sosok Presiden ke-7 Republik Indonesia tersebut.
+(Johanes Viandinando/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677523/bpbd-sulbar-intensifkan-edukasi-pencegahan-karhutla</t>
+          <t>https://www.antaranews.com/berita/5675784/ribuan-warga-padati-jalan-el-tari-saat-kunjungan-jokowi-di-kupang-ntt</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260309_224833.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/RIBUAN-WARGA-PADATI-JALAN-EL-TARI-SAAT-KUNJUNGAN-JOKOWI-DI-KUPANG-NTT.jpg</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Presiden Prabowo memandang Indonesia layak tampil di Piala Dunia 2030</t>
+          <t>Proyeksi BPS: Produksi jagung Januari-September 2026 turun 1,07 persen</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:35:54 +0700</t>
+          <t>Mon, 03 Aug 2026 16:22:40 +0700</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Presiden Republik Indonesia Prabowo Subianto dalam pidatonya pada pembukaan Kongres Biasa PSSI 2026 di Jakarta, Senin, ...</t>
+          <t>Badan Pusat Statistik (BPS) memproyeksikan produksi jagung sepanjang Januari hingga September 2026 mencapai 12,67 juta ...</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677516/presiden-prabowo-memandang-indonesia-layak-tampil-di-piala-dunia-2030</t>
+          <t>https://www.antaranews.com/berita/5677621/proyeksi-bps-produksi-jagung-januari-september-2026-turun-107-persen</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0004.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/01/09/E4F127D0-D171-4325-B719-6BA92F68E3F7.jpeg</t>
         </is>
       </c>
     </row>
@@ -2754,28 +2755,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BPK dorong kementerian terapkan prinsip ESG dalam pengelolaan anggaran</t>
+          <t>Polda Metro Jaya siap hadapi praperadilan keempat Roy Suryo</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:35:12 +0700</t>
+          <t>Mon, 03 Aug 2026 16:22:32 +0700</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Badan Pemeriksa Keuangan (BPK) RI mendorong kementerian dan lembaga mulai menerapkan prinsip Environmental, Social, and ...</t>
+          <t>Polda Metro Jaya menyatakan siap menghadapi permohonan praperadilan keempat yang diajukan oleh Roy Suryo apabila ...</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677512/bpk-dorong-kementerian-terapkan-prinsip-esg-dalam-pengelolaan-anggaran</t>
+          <t>https://www.antaranews.com/berita/5677620/polda-metro-jaya-siap-hadapi-praperadilan-keempat-roy-suryo</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001216419.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/10/1000972604.jpg</t>
         </is>
       </c>
     </row>
@@ -2787,61 +2788,61 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BNPB: 1.485 jiwa terdampak kebakaran TPA Troketon Klaten</t>
+          <t>Menkomdigi kukuhkan komisioner KI Pusat, perkuat keterbukaan informasi</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:33:32 +0700</t>
+          <t>Mon, 03 Aug 2026 16:20:44 +0700</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Badan Nasional Penanggulangan Bencana (BNPB) mengoordinasikan penanganan dampak kebakaran Tempat Pemrosesan Akhir (TPA) ...</t>
+          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengambil sumpah jabatan dan mengukuhkan tujuh anggota Komisi ...</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677509/bnpb-1485-jiwa-terdampak-kebakaran-tpa-troketon-klaten</t>
+          <t>https://www.antaranews.com/video/5677604/menkomdigi-kukuhkan-komisioner-ki-pusat-perkuat-keterbukaan-informasi</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/10/16/33.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_MENKOMDIGI-KUKUHKAN-KOMISIONER-KI-PUSAT-PERKUAT-KETERBUKAAN-INFORMASI.jpg</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Menkomdigi sebut kreator rekam konten tanpa izin langgar UU PDP</t>
+          <t>BPS: Perjalanan wisnus naik 0,97 persen pada triwulan II 2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:32:10 +0700</t>
+          <t>Mon, 03 Aug 2026 16:18:58 +0700</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid menyebutkan kreator konten yang merekam video tanpa ...</t>
+          <t>Badan Pusat Statistik (BPS) mencatat jumlah perjalanan wisatawan nusantara (wisnus) sepanjang Januari hingga Juni 2026 ...</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677508/menkomdigi-sebut-kreator-rekam-konten-tanpa-izin-langgar-uu-pdp</t>
+          <t>https://www.antaranews.com/berita/5677616/bps-perjalanan-wisnus-naik-097-persen-pada-triwulan-ii-2026</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0252.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/06/peningkatan-perjalanan-wisatawan-nusantara-2817128.jpg</t>
         </is>
       </c>
     </row>
@@ -2853,28 +2854,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Survei LKPI: Kepuasan publik terhadap Prabowo capai 79,3 persen</t>
+          <t>Gempa Bumi bermagnitudo 5,5 guncang Mesir, getaran terasa di Kairo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:31:44 +0700</t>
+          <t>Mon, 03 Aug 2026 16:18:07 +0700</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Survei Lembaga Kajian Pemilu Indonesia (LKPI) menunjukkan tingkat kepuasan publik terhadap kinerja Presiden Prabowo ...</t>
+          <t>Gempa bumi bermagnitudo 5,5 mengguncang wilayah timur laut Sharm el-Sheikh pada Senin (3/8) pagi waktu setempat, ...</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677504/survei-lkpi-kepuasan-publik-terhadap-prabowo-capai-793-persen</t>
+          <t>https://www.antaranews.com/berita/5677615/gempa-bumi-bermagnitudo-55-guncang-mesir-getaran-terasa-di-kairo</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG_3632.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CjkinzN000015_20260803_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
@@ -2886,28 +2887,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>KONI Pusat harap Kongres Biasa PSSI diskusikan pembinaan prestasi</t>
+          <t>Kemenhaj ancam sanksi tegas biro umrah yang telantarkan jamaah</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:29:28 +0700</t>
+          <t>Mon, 03 Aug 2026 16:17:28 +0700</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ketua Umum Komite Olahraga Nasional Indonesia (KONI) Pusat Letjen TNI Purn. Marciano Norman berharap Kongres Biasa ...</t>
+          <t>Kementerian Haji dan Umrah RI mengancam akan memberikan sanksi tegas kepada Penyelenggara Perjalanan Ibadah Umrah ...</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677500/koni-pusat-harap-kongres-biasa-pssi-diskusikan-pembinaan-prestasi</t>
+          <t>https://www.antaranews.com/berita/5677611/kemenhaj-ancam-sanksi-tegas-biro-umrah-yang-telantarkan-jamaah</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/11/Ketua-KONI-Pusat-Marciano-Norman.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/18/1000296584.jpg</t>
         </is>
       </c>
     </row>
@@ -2919,28 +2920,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>KPK panggil anggota DPR RI Anwar Sadad pada kasus dana hibah Jatim</t>
+          <t>Inflasi tahunan Jakarta pada Juli 2026 capai 2,5 persen</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:28:20 +0700</t>
+          <t>Mon, 03 Aug 2026 16:16:46 +0700</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Komisi Pemberantasan Korupsi (KPK) memanggil anggota DPR RI Anwar Sadad (AS) untuk diperiksa dalam penyidikan kasus ...</t>
+          <t>Badan Pusat Statistik (BPS) DKI Jakarta mencatat inflasi tahunan Jakarta pada Juli 2026 sebesar 2,5 persen, didorong ...</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677496/kpk-panggil-anggota-dpr-ri-anwar-sadad-pada-kasus-dana-hibah-jatim</t>
+          <t>https://www.antaranews.com/berita/5677608/inflasi-tahunan-jakarta-pada-juli-2026-capai-25-persen</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/07/23/IMG-20230723-WA0032.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000313673.jpg</t>
         </is>
       </c>
     </row>
@@ -2952,28 +2953,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ditjenpas Kaltim gelar CKG bagi 12 ribu warga binaan</t>
+          <t>Anggota DPR: Kenaikan tukin TNI harus berdampak pada kualitas kinerja</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:23:58 +0700</t>
+          <t>Mon, 03 Aug 2026 16:16:15 +0700</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ANTARA - Program Cek Kesehatan Gratis (CKG) menyasar warga binaan di Lembaga Pemasyarakatan (Lapas) dan Rumah Tahanan ...</t>
+          <t>Anggota Komisi I DPR RI Oleh Soleh mengatakan kenaikan tunjangan kinerja (tukin) untuk prajurit Tentara Nasional ...</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5677480/ditjenpas-kaltim-gelar-ckg-bagi-12-ribu-warga-binaan</t>
+          <t>https://www.antaranews.com/berita/5677600/anggota-dpr-kenaikan-tukin-tni-harus-berdampak-pada-kualitas-kinerja</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AYM_DITJENPAS-KALTIM-GELAR-CKG.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/04/11/IMG-20250411-WA0012.jpg</t>
         </is>
       </c>
     </row>
@@ -2985,28 +2986,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BPS prediksi produksi beras RI 28,71 juta ton hingga September 2026</t>
+          <t>Mentan: NTP Juli 2026 capai 127,84, kesejahteraan petani menguat</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:23:12 +0700</t>
+          <t>Mon, 03 Aug 2026 16:15:14 +0700</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) memprediksi produksi beras sepanjang Januari–September 2026 mencapai 28,71 juta ton, ...</t>
+          <t>Menteri Pertanian (Mentan) Andi Amran Sulaiman menyatakan Nilai Tukar Petani (NTP) Juli 2026 mencapai 127,84 sebagai ...</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677485/bps-prediksi-produksi-beras-ri-2871-juta-ton-hingga-september-2026</t>
+          <t>https://www.antaranews.com/berita/5677599/mentan-ntp-juli-2026-capai-12784-kesejahteraan-petani-menguat</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/proyeksi-produksi-beras-konsumsi-2815573.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/35C6992A-F389-4999-9FFF-6B97C5415206.jpeg</t>
         </is>
       </c>
     </row>
@@ -3018,28 +3019,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Polda Jatim kerahkan 30 personel evakuasi KMP Mutiara Sentosa 2</t>
+          <t>Juara WBC Geisler Ap menang TKO atas Bambang Rusiadi</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:22:46 +0700</t>
+          <t>Mon, 03 Aug 2026 16:15:02 +0700</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kepolisian Daerah (Polda) Jawa Timur (Jatim) mengerahkan 30 personel SAR Direktorat Kepolisian Perairan dan Udara ...</t>
+          <t>Juara kelas menengah super World Boxing Council (WBC) Kontinental Geisler Ap menang technical knockout atau TKO atas ...</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677483/polda-jatim-kerahkan-30-personel-evakuasi-kmp-mutiara-sentosa-2</t>
+          <t>https://www.antaranews.com/berita/5677597/juara-wbc-geisler-ap-menang-tko-atas-bambang-rusiadi</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1319202.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_153646.jpg</t>
         </is>
       </c>
     </row>
@@ -3051,28 +3052,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Komisi IX DPR: Putusan MK jadi momentum BGN desain ulang MBG</t>
+          <t>BNPB koordinasikan pemadaman karhutla di Beltim dan Bangka Barat</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:19:16 +0700</t>
+          <t>Mon, 03 Aug 2026 16:12:41 +0700</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Wakil Ketua Komisi IX DPR RI Charles Honoris mengatakan putusan Mahkamah Konstitusi Nomor 40/PUU-XXIV/2026 menjadi ...</t>
+          <t>Badan Nasional Penanggulangan Bencana (BNPB) mengoordinasikan penanganan kebakaran hutan dan lahan (karhutla) yang ...</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677477/komisi-ix-dpr-putusan-mk-jadi-momentum-bgn-desain-ulang-mbg</t>
+          <t>https://www.antaranews.com/berita/5677593/bnpb-koordinasikan-pemadaman-karhutla-di-beltim-dan-bangka-barat</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/15/tempImageigZXJC.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0012.jpg</t>
         </is>
       </c>
     </row>
@@ -3084,28 +3085,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ke Jepara, Mendikdasmen: Lahan SNT harus benar-benar siap dikembangkan</t>
+          <t>Kementrans kirim Tim Ekspedisi Patriot lakukan riset di Manokwari</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:17:55 +0700</t>
+          <t>Mon, 03 Aug 2026 16:11:25 +0700</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Menteri Pendidikan Dasar dan Menengah (Mendikdasmen) Abdul Mu’ti meninjau langsung kesiapan lahan untuk ...</t>
+          <t>Kementerian Transmigrasi mengirimkan sebanyak 20 Tim Ekspedisi Patriot dari Universitas Airlangga Surabaya untuk ...</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677475/ke-jepara-mendikdasmen-lahan-snt-harus-benar-benar-siap-dikembangkan</t>
+          <t>https://www.antaranews.com/berita/5677589/kementrans-kirim-tim-ekspedisi-patriot-lakukan-riset-di-manokwari</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/21/1000216743.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/23716.jpg</t>
         </is>
       </c>
     </row>
@@ -3117,28 +3118,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Jepang dan AS lakukan intervensi bersama di pasar valuta asing</t>
+          <t>Dedi Mulyadi targetkan penataan Teras Cihampelas rampung Oktober 2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:17:09 +0700</t>
+          <t>Mon, 03 Aug 2026 16:11:19 +0700</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Satsuki Katayama mengatakan bahwa Jepang dan Amerika Serikat telah melakukan intervensi pembelian yen ...</t>
+          <t>Pemerintah Provinsi (Pemprov) Jawa Barat (Jabar) menargetkan pembongkaran dan penataan Teras Cihampelas yang kini ...</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677472/jepang-dan-as-lakukan-intervensi-bersama-di-pasar-valuta-asing</t>
+          <t>https://www.antaranews.com/berita/5677587/dedi-mulyadi-targetkan-penataan-teras-cihampelas-rampung-oktober-2026</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CjkinzN000009_20260803_CBMFN0A001.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000032578.jpg</t>
         </is>
       </c>
     </row>
@@ -3150,61 +3151,61 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TNI AU dan AU Kamboja perkuat hubungan dengan jalin kerja sama militer</t>
+          <t>Jakarta alami deflasi 0,15 persen pada Juli 2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:15:59 +0700</t>
+          <t>Mon, 03 Aug 2026 16:10:32 +0700</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>TNI Angkatan Udara (AU) memperkuat hubungan dengan AU Kamboja atau Cambodian Air Force (CAF) dengan menyepakati ...</t>
+          <t>Badan Pusat Statistik (BPS) DKI Jakarta mengemukakan DKI Jakarta secara bulanan mengalami deflasi sebesar 0,15 persen ...</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677468/tni-au-dan-au-kamboja-perkuat-hubungan-dengan-jalin-kerja-sama-militer</t>
+          <t>https://www.antaranews.com/berita/5677583/jakarta-alami-deflasi-015-persen-pada-juli-2026</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001554368.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000313675.jpg</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>KPK geledah tujuh lokasi pada 30 Juli-1 Agustus terkait kasus Pemalang</t>
+          <t>Menhub: Penyebab kebakaran KM Mutiara Sentosa diinvestigasi</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:14:49 +0700</t>
+          <t>Mon, 03 Aug 2026 16:10:14 +0700</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Komisi Pemberantasan Korupsi (KPK) menggeledah tujuh lokasi pada 30 Juli–1 Agustus 2026 terkait penyidikan kasus ...</t>
+          <t>Menteri Perhubungan (Menhub) Dudy Purwagandhi memastikan investigasi dilakukan untuk mengetahui penyebab kebakaran KMP ...</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677465/kpk-geledah-tujuh-lokasi-pada-30-juli-1-agustus-terkait-kasus-pemalang</t>
+          <t>https://www.antaranews.com/berita/5677580/menhub-penyebab-kebakaran-km-mutiara-sentosa-diinvestigasi</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/kpk-tahan-bupati-pemalang-2830443.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1D125204-38F4-4DC5-835F-9517A0EAE33A.jpeg</t>
         </is>
       </c>
     </row>
@@ -3216,28 +3217,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Paus Leo XIV prihatin atas situasi krisis migran di Ceuta</t>
+          <t>Polda Metro Jaya tangkap perempuan penyebar hoaks ajakan demonstrasi</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:14:34 +0700</t>
+          <t>Mon, 03 Aug 2026 16:09:47 +0700</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ANTARA - Paus Leo XIV  menyampaikan keprihatinan atas situasi krisis migran di Enklave, Spanyol, Ceuta.  Saat ...</t>
+          <t>Direktorat Reserse Siber Polda Metro Jaya menangkap seorang perempuan berinisial DM (45) di Kabupaten Ciamis, Jawa ...</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5677384/paus-leo-xiv-prihatin-atas-situasi-krisis-migran-di-ceuta</t>
+          <t>https://www.antaranews.com/berita/5677577/polda-metro-jaya-tangkap-perempuan-penyebar-hoaks-ajakan-demonstrasi</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AYM_PAUS-LEO-XIV-PRIHATIN-ATAS-SITUASI-KRISIS.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/19/ilustrasi-narkoba-1.jpg</t>
         </is>
       </c>
     </row>
@@ -3249,28 +3250,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BMKG: Musim kemarau Papua Pegunungan bakal berakhir pada akhir Agustus</t>
+          <t>BRIN gandeng UGM kembangkan teknologi benih bawang putih sehat</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:07:50 +0700</t>
+          <t>Mon, 03 Aug 2026 16:09:08 +0700</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Badan Meteorologi, Klimatologi dan Geofisika (BMKG) melalui Stasiun Meteorologi Kelas III Wamena, Kabupaten Jayawijaya, ...</t>
+          <t>Pusat Riset Hortikultura Badan Riset dan Inovasi Nasional (BRIN) bersama Fakultas Pertanian Universitas Gadjah Mada ...</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677463/bmkg-musim-kemarau-papua-pegunungan-bakal-berakhir-pada-akhir-agustus</t>
+          <t>https://www.antaranews.com/berita/5677573/brin-gandeng-ugm-kembangkan-teknologi-benih-bawang-putih-sehat</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260730-WA0008.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/06/24/bawang.jpeg</t>
         </is>
       </c>
     </row>
@@ -3282,61 +3283,61 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Koalisi buruh serahkan usulan RUU Ketenagakerjaan ke pimpinan DPR</t>
+          <t>Menjaga independensi KPK dalam pemberantasan korupsi</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:05:55 +0700</t>
+          <t>Mon, 03 Aug 2026 16:05:54 +0700</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Koalisi dari berbagai konfederasi buruh menyerahkan draf usulan untuk penyusunan Rancangan Undang-Undang (RUU) ...</t>
+          <t>Meskipun pemerintah tengah menerapkan kebijakan pemangkasan anggaran daerah demi mencegah penyelewengan, ruang ...</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677460/koalisi-buruh-serahkan-usulan-ruu-ketenagakerjaan-ke-pimpinan-dpr</t>
+          <t>https://www.antaranews.com/berita/5677569/menjaga-independensi-kpk-dalam-pemberantasan-korupsi</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001295553.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG_8099.jpg</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>ekonomi-finansial, terkini</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BPS catat pengeluaran wisman triwulan II-2026 mencapai 1.285 dolar AS</t>
+          <t>Menjaga pintu air perekonomian Indonesia</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:56:12 +0700</t>
+          <t>Mon, 03 Aug 2026 16:04:40 +0700</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat perkembangan pengeluaran wisatawan mancanegara (wisman) pada triwulan II tahun ...</t>
+          <t>Bayangkan perekonomian Indonesia sebagai sebuah bendungan raksasa yang mengairi hamparan persawahan. Air yang mengalir ...</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677457/bps-catat-pengeluaran-wisman-triwulan-ii-2026-mencapai-1285-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5677565/menjaga-pintu-air-perekonomian-indonesia</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG-20260731-WA0028.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/06/peringati-hari-bank-indonesia-doku-perkuat-ekosistem-pembayaran-2817675.jpg</t>
         </is>
       </c>
     </row>
@@ -3348,28 +3349,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Charles Honoris dorong putusan MK soal MBG diterapkan pada APBN 2027</t>
+          <t>Prabowo terima laporan Bahlil soal program ketahanan energi</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:56:05 +0700</t>
+          <t>Mon, 03 Aug 2026 16:02:25 +0700</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Wakil Ketua Komisi IX DPR RI Charles Honoris mendorong putusan Mahkamah Konstitusi (MK) mengenai anggaran program Makan ...</t>
+          <t>Presiden Prabowo Subianto menerima laporan terbaru dari Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil ...</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677456/charles-honoris-dorong-putusan-mk-soal-mbg-diterapkan-pada-apbn-2027</t>
+          <t>https://www.antaranews.com/berita/5677561/prabowo-terima-laporan-bahlil-soal-program-ketahanan-energi</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/upscalemedia-transformed-167.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_5125.jpeg</t>
         </is>
       </c>
     </row>
@@ -3381,28 +3382,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Wamensos: Kolaborasi data perkuatkan bantuan JKN lebih akuntabel</t>
+          <t>Menlu Iran sebut pembicaraan soal Selat Hormuz dengan Oman masuki tahap akhir</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:54:53 +0700</t>
+          <t>Mon, 03 Aug 2026 16:01:55 +0700</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wakil Menteri Sosial (Wamensos) Agus Jabo Priyono mengatakan kolaborasi strategis yang dilakukan bersama BPJS ...</t>
+          <t>Menteri Luar Negeri Iran Abbas Araghchi  mengatakan pembicaraan soal Selat Hormuz dengan Oman masuki tahap ...</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677453/wamensos-kolaborasi-data-perkuatkan-bantuan-jkn-lebih-akuntabel</t>
+          <t>https://www.antaranews.com/berita/5677557/menlu-iran-sebut-pembicaraan-soal-selat-hormuz-dengan-oman-masuki-tahap-akhir</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-14.44.56-1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/HormuzXinhuaWangQiang_aa.jpg</t>
         </is>
       </c>
     </row>
@@ -3414,61 +3415,61 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Presiden Iran: AS harus tetap patuhi nota kesepahaman</t>
+          <t>Wamendiktisaintek dorong kampus di Riau dan Kepri bangun konsorsium</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:54:11 +0700</t>
+          <t>Mon, 03 Aug 2026 16:01:51 +0700</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Presiden Iran Masoud Pezeshkian mengatakan pada Minggu (2/8) bahwa Amerika Serikat harus tetap berkomitmen pada nota ...</t>
+          <t>Wakil Menteri Pendidikan Tinggi, Sains, dan Teknologi (Wamendiktisaintek) Fauzan mendorong perguruan tinggi di Provinsi ...</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677449/presiden-iran-as-harus-tetap-patuhi-nota-kesepahaman</t>
+          <t>https://www.antaranews.com/berita/5677555/wamendiktisaintek-dorong-kampus-di-riau-dan-kepri-bangun-konsorsium</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CjkinzN000008_20260803_CBMFN0A001.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/18/1000428031.jpg</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Kapal Pertamina selamatkan 17 korban KMP Mutiara Sentosa 2</t>
+          <t>Partai Buruh Brasil calonkan Lula da Silva untuk masa jabatan keempat</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:52:47 +0700</t>
+          <t>Mon, 03 Aug 2026 16:01:22 +0700</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kapal Pertamina Patra Niaga MT Transko Arafura berhasil mengevakuasi 17 orang korban KMP Mutiara Sentosa 2 yang ...</t>
+          <t>ANTARA - Partai Buruh di Brasil pada Minggu (2/8) waktu setempat, resmi mencalonkan petahana Luiz Inacio Lula da Silva ...</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677445/kapal-pertamina-selamatkan-17-korban-kmp-mutiara-sentosa-2</t>
+          <t>https://www.antaranews.com/video/5677541/partai-buruh-brasil-calonkan-lula-da-silva-untuk-masa-jabatan-keempat</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-14.30.38.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-03-154005.jpg</t>
         </is>
       </c>
     </row>
@@ -3480,61 +3481,61 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ekonomi kelautan China catat pertumbuhan stabil pada H1 2026</t>
+          <t>Program konservasi Pulau Sabira PLN raih penghargaan nasional</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:50:44 +0700</t>
+          <t>Mon, 03 Aug 2026 16:00:04 +0700</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Produk laut bruto (PLB) China mencapai 5,5 triliun yuan (1 yuan = Rp2.676) pada paruh pertama (H1) 2026, naik 5,1 ...</t>
+          <t>PT PLN (Persero) Unit Induk Distribusi (UID) Jakarta Raya meraih penghargaan "Predikat Platinum Alignment" ...</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677441/ekonomi-kelautan-china-catat-pertumbuhan-stabil-pada-h1-2026</t>
+          <t>https://www.antaranews.com/berita/5677551/program-konservasi-pulau-sabira-pln-raih-penghargaan-nasional</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CjkinzN000010_20260803_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/e9219a6c-ccd6-473e-bf06-a7dd465568bd.jpeg</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PGN sasar pemanfaatan jargas untuk hotel hingga UMKM</t>
+          <t>Pemkot Ambon salurkan air bersih gratis jika kekeringan terjadi</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:50:20 +0700</t>
+          <t>Mon, 03 Aug 2026 15:59:59 +0700</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>PT Perusahaan Gas Negara (Persero) Tbk (PGN) menyasar pemanfaatan jaringan gas (jargas) tidak hanya rumah ...</t>
+          <t>ANTARA - Pemerintah Kota Ambon, Maluku, menyiapkan langkah antisipasi untuk menjamin ketersediaan air bersih bagi ...</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677439/pgn-sasar-pemanfaatan-jargas-untuk-hotel-hingga-umkm</t>
+          <t>https://www.antaranews.com/video/5677489/pemkot-ambon-salurkan-air-bersih-gratis-jika-kekeringan-terjadi</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_2395.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-03-151844.jpg</t>
         </is>
       </c>
     </row>
@@ -3546,28 +3547,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TNI AL tuntaskan latihan gabungan dengan AL Australia</t>
+          <t>Razia balap liar, Polres Temanggung sita 106 motor</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:46:09 +0700</t>
+          <t>Mon, 03 Aug 2026 15:58:54 +0700</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>TNI AL menuntaskan kegiatan latihan gabungan dengan AL Australia atau Royal Australian Navy (RAN) dalam ajang Cassowary ...</t>
+          <t>ANTARA - Kepolisian Resor (Polres) Temanggung, Jawa Tengah menyita 106 sepeda motor dalam razia balap liar yang digelar ...</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677436/tni-al-tuntaskan-latihan-gabungan-dengan-al-australia</t>
+          <t>https://www.antaranews.com/video/5677488/razia-balap-liar-polres-temanggung-sita-106-motor</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001554245.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_RAZIA-BALAP-LIAR-POLRES-TEMANGGUNG-SITA-106-MOTOR.jpg</t>
         </is>
       </c>
     </row>
@@ -3579,61 +3580,61 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Wamenkomdigi: TVRI institusi strategis penjaga ruang informasi bangsa</t>
+          <t>Pemain muda Barcelona incar tempat di tim utama 2026/2027</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:45:19 +0700</t>
+          <t>Mon, 03 Aug 2026 15:57:56 +0700</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Wakil Menteri Komunikasi dan Digital (Wamenkomdigi) Angga Raka Prabowo menyatakan Lembaga Penyiaran Publik (LPP) TVRI ...</t>
+          <t>Para pemain muda Barcelona, khususnya yang kini memperkuat Barcelona Atletic (Barcelona B), mengincar tempat di tim ...</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677432/wamenkomdigi-tvri-institusi-strategis-penjaga-ruang-informasi-bangsa</t>
+          <t>https://www.antaranews.com/berita/5677547/pemain-muda-barcelona-incar-tempat-di-tim-utama-2026-2027</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0224.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_154443.jpg</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>photo, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Petani berbagi air sumur demi selamatkan tanaman tembakau</t>
+          <t>HYBE siapkan debut girl group Tuide</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:44:51 +0700</t>
+          <t>Mon, 03 Aug 2026 15:57:13 +0700</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Petani mengambil air dari sumur untuk menyiram tanaman tembakau di Lengkong, Nganjuk, Jawa Timur, Senin (3/8/2026). ...</t>
+          <t>Perusahaan hiburan Korea Selatan, HYBE melalui label naungannya ABD tengah mempersiapkan debut girl group Kpop bernama ...</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5677428/petani-berbagi-air-sumur-demi-selamatkan-tanaman-tembakau</t>
+          <t>https://www.antaranews.com/berita/5677544/hybe-siapkan-debut-girl-group-tuide</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/petani-tembakau-berbagi-air-sumur-antisipasi-dampak-el-nino-030826-mm-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/644817de-49b2-42cd-92a5-0d0a14d911ce.jpeg</t>
         </is>
       </c>
     </row>
@@ -3645,3253 +3646,3946 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BPK berikan opini WTP kepada Kemenko Kumham Imipas atas LK 2025</t>
+          <t>Pemkot Jakut edukasi pelajar tentang teknik pertanian di perkotaan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:44:20 +0700</t>
+          <t>Mon, 03 Aug 2026 15:52:39 +0700</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Badan Pemeriksa Keuangan RI memberikan opini Wajar Tanpa Pengecualian (WTP) kepada seluruh kementerian di bawah ...</t>
+          <t>Suku Dinas Ketahanan Pangan, Kelautan dan Pertanian (KPKP) Jakarta Utara mengedukasi puluhan pelajar dari enam sekolah ...</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677427/bpk-berikan-opini-wtp-kepada-kemenko-kumham-imipas-atas-lk-2025</t>
+          <t>https://www.antaranews.com/berita/5677540/pemkot-jakut-edukasi-pelajar-tentang-teknik-pertanian-di-perkotaan</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001216320.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/2dfab961fe56.jpeg</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini, top-news</t>
+          <t>photo, terkini</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Nusron sebut banyak laut di Batam telah dikapling tanpa prosedur sah</t>
+          <t>Jelang HUT RI, Polda Kepri bagikan bendera ke warga di pulau-pulau terluar</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:44:05 +0700</t>
+          <t>Mon, 03 Aug 2026 15:51:09 +0700</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Menteri Agraria dan Tata Ruang (ATR)/Kepala Badan Pertanahan Nasional (BPN) Nusron Wahid mengatakan, menerima banyak ...</t>
+          <t>Warga memasang Bendera Merah Putih di perahu serta pekarangan rumah panggung yang dibagikan Polda Kepri di Pulau Dapur ...</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677425/nusron-sebut-banyak-laut-di-batam-telah-dikapling-tanpa-prosedur-sah</t>
+          <t>https://www.antaranews.com/foto/5677539/jelang-hut-ri-polda-kepri-bagikan-bendera-ke-warga-di-pulau-pulau-terluar</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_142345.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Pembagian-Bendera-Merah-Putih-Di-Pulau-Pulau-Terluar-030826-tpp-2.jpg</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Menkomdigi panggil YouTube imbas temuan konten promosi vape sasar anak</t>
+          <t>Pelindo siagakan posko terpadu bagi korban KMP Mutiara Sentosa II</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:22:09 +0700</t>
+          <t>Mon, 03 Aug 2026 15:45:16 +0700</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid merencanakan pemanggilan terhadap platform digital YouTube ...</t>
+          <t>PT Pelabuhan Indonesia (Persero) Regional 3 Sub Regional Jawa menyiagakan posko terpadu korban kebakaran Kapal Motor ...</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677396/menkomdigi-panggil-youtube-imbas-temuan-konten-promosi-vape-sasar-anak</t>
+          <t>https://www.antaranews.com/berita/5677537/pelindo-siagakan-posko-terpadu-bagi-korban-kmp-mutiara-sentosa-ii</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0225.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/260405.jpg</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kemnaker: Magang Nasional diharapkan menekan angka pengangguran muda</t>
+          <t>MPR undang Presiden Prabowo hadiri sidang tahunan pada 14 Agustus</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:37:57 +0700</t>
+          <t>Mon, 03 Aug 2026 15:43:18 +0700</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kementerian Ketenagakerjaan (Kemnaker) mengatakan program Magang Nasional (MagangHub) untuk mempersiapkan kompetensi ...</t>
+          <t>Pimpinan MPR mengundang Presiden Prabowo Subianto menghadiri Sidang Tahunan MPR yang rencananya digelar pada Jumat, 14 ...</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677364/kemnaker-magang-nasional-diharapkan-menekan-angka-pengangguran-muda</t>
+          <t>https://www.antaranews.com/berita/5677536/mpr-undang-presiden-prabowo-hadiri-sidang-tahunan-pada-14-agustus</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/ff63afaf-7778-47fe-833d-5a8068af9a51_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000398675.jpg</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Kemenag perkuat transformasi madrasah lewat revitalisasi-digitalisasi</t>
+          <t>Kesbangpol Pontianak antisipasi konflik sosial akibat karhutla</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:36:36 +0700</t>
+          <t>Mon, 03 Aug 2026 15:42:51 +0700</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Menteri Agama (Menag) Nasaruddin Umar menegaskan transformasi madrasah terus diperkuat melalui revitalisasi ...</t>
+          <t>ANTARA - Badan Kesatuan Bangsa dan Politik (Kesbangpol) Kota Pontianak mengidentifikasi potensi gangguan keamanan dan ...</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677363/kemenag-perkuat-transformasi-madrasah-lewat-revitalisasi-digitalisasi</t>
+          <t>https://www.antaranews.com/video/5677519/kesbangpol-pontianak-antisipasi-konflik-sosial-akibat-karhutla</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/14/1000173935_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KESBANGPOL-PONTIANAK-ANTISIPASI-KONFLIK-SOSIAL-AKIBAT-KARHUTLA.jpg</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, top-news</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Lisensi IP Global Buka Peluang Bisnis Baru bagi Kreator Indonesia</t>
+          <t>Data untuk Indonesia, bakti untuk negeri</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:34:30 +0700</t>
+          <t>Mon, 03 Aug 2026 15:42:25 +0700</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Wakil Menteri Ekonomi Kreatif Irene Umar mengatakan kolaborasi antara pemilik kekayaan intelektual (Intellectual ...</t>
+          <t>Bulan Agustus selalu menghadirkan suasana yang berbeda. Bendera Merah Putih berkibar di halaman rumah, berbagai ...</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677353/lisensi-ip-global-buka-peluang-bisnis-baru-bagi-kreator-indonesia</t>
+          <t>https://www.antaranews.com/berita/5677535/data-untuk-indonesia-bakti-untuk-negeri</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000589873.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/1001511288.jpg</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nilai ekspor perdagangan RI Januari-Juni capai 140,81 miliar dolar AS</t>
+          <t>Prabowo: Persatuan selalu terlihat saat timnas Indonesia bermain</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:16:17 +0700</t>
+          <t>Mon, 03 Aug 2026 15:40:54 +0700</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat nilai ekspor Indonesia secara kumulatif dari Januari-Juni 2026 mencapai 140,81 ...</t>
+          <t>Presiden Republik Indonesia Prabowo Subianto mengaku selalu melihat persatuan setiap kali timnas Indonesia ...</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677315/nilai-ekspor-perdagangan-ri-januari-juni-capai-14081-miliar-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5677532/prabowo-persatuan-selalu-terlihat-saat-timnas-indonesia-bermain</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/neraca-perdagangan-januari-mei-2026-surplus-2815779.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0003_3.jpg</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Korban KMP Mutiara Sentosa II dievakuasi ke Pelabuhan Tanjung Perak</t>
+          <t>PSEL Serang Raya jadi solusi pengelolaan sampah tiga daerah</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:06:15 +0700</t>
+          <t>Mon, 03 Aug 2026 15:40:46 +0700</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Tim SAR gabungan terus melakukan evakuasi korban terbakarnya KMP Mutiara Sentosa 2 ke darat, tepatnya ke Pelabuhan ...</t>
+          <t>ANTARA - Fasilitas Pengolahan Sampah menjadi Energi Listrik (PSEL) Serang Raya akan dibangun di TPSA Cilowong, Kota ...</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677297/korban-kmp-mutiara-sentosa-ii-dievakuasi-ke-pelabuhan-tanjung-perak</t>
+          <t>https://www.antaranews.com/video/5677492/psel-serang-raya-jadi-solusi-pengelolaan-sampah-tiga-daerah</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/260821_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AYM_PSEL-SERANG-RAYA-JADI-SOLUSI-PENGELOLAAN-SAMPAH.jpg</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Aktor senior Diding Boneng meninggal dunia</t>
+          <t>Dewas KPK sempurnakan Perdewas untuk atur etik PNYD hingga potong gaji</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:39:03 +0700</t>
+          <t>Mon, 03 Aug 2026 15:39:59 +0700</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Aktor sekaligus komedian tanah air, Zainal Abidin alias Diding Boneng dikabarkan meninggal dunia pada Senin (3/8) dalam ...</t>
+          <t>Dewan Pengawas Komisi Pemberantasan Korupsi (Dewas KPK) tengah menyempurnakan peraturan Dewas KPK (Perdewas) untuk ...</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677209/aktor-senior-diding-boneng-meninggal-dunia</t>
+          <t>https://www.antaranews.com/berita/5677531/dewas-kpk-sempurnakan-perdewas-untuk-atur-etik-pnyd-hingga-potong-gaji</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/26f1eb88-3301-4ae1-badd-bed5078fe3dd.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_8184.jpg</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Seskab: Prabowo dorong sinergi pemerintah dan dunia usaha</t>
+          <t>Kelurahan Dukuh Jaktim perketat pengawasan TPS liar pascakebakaran</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:17:50 +0700</t>
+          <t>Mon, 03 Aug 2026 15:39:50 +0700</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sekretaris Kabinet Teddy Indra Wijaya menyampaikan bahwa Presiden Prabowo Subianto menekankan pentingnya sinergi antara ...</t>
+          <t>Kelurahan Dukuh, Jakarta Timur, bersama pengurus RT 013 dan RW 03 memperketat pengawasan tempat penampungan sementara ...</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677191/seskab-prabowo-dorong-sinergi-pemerintah-dan-dunia-usaha</t>
+          <t>https://www.antaranews.com/berita/5677527/kelurahan-dukuh-jaktim-perketat-pengawasan-tps-liar-pascakebakaran</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0891.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/InShot_20260803_145658796.jpg</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Red Velvet bersiap kembali lewat EP baru "Velvet Summer"</t>
+          <t>BPBD Sulbar intensifkan edukasi pencegahan karhutla</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:24:37 +0700</t>
+          <t>Mon, 03 Aug 2026 15:38:10 +0700</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Grup idola K-pop Red Velvet akan kembali lewat rilis mini album atau extended play (EP) baru bertajuk “Velvet ...</t>
+          <t>Badan Penanggulangan Bencana Daerah (BPBD) Provinsi Sulawesi Barat mengintensifkan edukasi dan peningkatan kesadaran ...</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677151/red-velvet-bersiap-kembali-lewat-ep-baru-velvet-summer</t>
+          <t>https://www.antaranews.com/berita/5677523/bpbd-sulbar-intensifkan-edukasi-pencegahan-karhutla</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/ca97a3a8-aa17-45fc-be71-d36051dd9dcd.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260309_224833.jpg</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Menaker pastikan komitmen pemerintah perkuat kesejahteraan pekerja</t>
+          <t>Presiden Prabowo memandang Indonesia layak tampil di Piala Dunia 2030</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:16:19 +0700</t>
+          <t>Mon, 03 Aug 2026 15:35:54 +0700</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Menteri Ketenagakerjaan (Menaker) Yassierli memastikan pemerintah berkomitmen untuk memperkuat kesejahteraan, ...</t>
+          <t>Presiden Republik Indonesia Prabowo Subianto dalam pidatonya pada pembukaan Kongres Biasa PSSI 2026 di Jakarta, Senin, ...</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677148/menaker-pastikan-komitmen-pemerintah-perkuat-kesejahteraan-pekerja</t>
+          <t>https://www.antaranews.com/berita/5677516/presiden-prabowo-memandang-indonesia-layak-tampil-di-piala-dunia-2030</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/09/20/pelepasan-peserta-pemagangan-ke-jepang-di-jawa-barat-2627513.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0004.jpg</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>23 calon hakim agung dan ad hoc ikuti seleksi wawancara akhir</t>
+          <t>BPK dorong kementerian terapkan prinsip ESG dalam pengelolaan anggaran</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:15:01 +0700</t>
+          <t>Mon, 03 Aug 2026 15:35:12 +0700</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sebanyak 23 orang calon hakim agung dan ad hoc Mahkamah Agung Tahun 2026 mengikuti seleksi wawancara tahap akhir di ...</t>
+          <t>Badan Pemeriksa Keuangan (BPK) RI mendorong kementerian dan lembaga mulai menerapkan prinsip Environmental, Social, and ...</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677137/23-calon-hakim-agung-dan-ad-hoc-ikuti-seleksi-wawancara-akhir</t>
+          <t>https://www.antaranews.com/berita/5677512/bpk-dorong-kementerian-terapkan-prinsip-esg-dalam-pengelolaan-anggaran</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000012883_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001216419.jpg</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BRIN perkuat kajian sungai bawah tanah di Kebumen untuk ketahanan air</t>
+          <t>BNPB: 1.485 jiwa terdampak kebakaran TPA Troketon Klaten</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:57:19 +0700</t>
+          <t>Mon, 03 Aug 2026 15:33:32 +0700</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Badan Riset dan Inovasi Nasional (BRIN) memperkuat riset ketahanan air melalui pengembangan teknologi dan penelitian ...</t>
+          <t>Badan Nasional Penanggulangan Bencana (BNPB) mengoordinasikan penanganan dampak kebakaran Tempat Pemrosesan Akhir (TPA) ...</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677120/brin-perkuat-kajian-sungai-bawah-tanah-di-kebumen-untuk-ketahanan-air</t>
+          <t>https://www.antaranews.com/berita/5677509/bnpb-1485-jiwa-terdampak-kebakaran-tpa-troketon-klaten</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1785706440-47672950-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/10/16/33.jpg</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Harga bensin turun pada pekan pertama Agustus</t>
+          <t>Menkomdigi sebut kreator rekam konten tanpa izin langgar UU PDP</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:51:00 +0700</t>
+          <t>Mon, 03 Aug 2026 15:32:10 +0700</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Harga bahan bakar minyak (BBM) jenis bensin di stasiun pengisian bahan bakar umum (SPBU) Pertamina, Shell, dan bp ...</t>
+          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid menyebutkan kreator konten yang merekam video tanpa ...</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677109/harga-bensin-turun-pada-pekan-pertama-agustus</t>
+          <t>https://www.antaranews.com/berita/5677508/menkomdigi-sebut-kreator-rekam-konten-tanpa-izin-langgar-uu-pdp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/10/02/penuruanan-harga-bbm-011024-aaa-7.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0252.jpg</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Sean Gelael berbagi pengalaman di dunia balap ke pengunjung GIIAS 2026</t>
+          <t>Survei LKPI: Kepuasan publik terhadap Prabowo capai 79,3 persen</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:34:53 +0700</t>
+          <t>Mon, 03 Aug 2026 15:31:44 +0700</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Pembalap Indonesia Sean Gelael berbagi pengalamannya di dunia balap ke pengunjung GAIKINDO Indonesia International ...</t>
+          <t>Survei Lembaga Kajian Pemilu Indonesia (LKPI) menunjukkan tingkat kepuasan publik terhadap kinerja Presiden Prabowo ...</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677103/sean-gelael-berbagi-pengalaman-di-dunia-balap-ke-pengunjung-giias-2026</t>
+          <t>https://www.antaranews.com/berita/5677504/survei-lkpi-kepuasan-publik-terhadap-prabowo-capai-793-persen</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/16b70b87-326f-479a-a806-580ab846cc6f_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG_3632.jpeg</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ekonomi-bursa, top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>IHSG Senin dibuka menguat 36,49 poin ke posisi 6.272</t>
+          <t>KONI Pusat harap Kongres Biasa PSSI diskusikan pembinaan prestasi</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:11:26 +0700</t>
+          <t>Mon, 03 Aug 2026 15:29:28 +0700</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin pagi dibuka menguat 36,49 poin atau 0,59 ...</t>
+          <t>Ketua Umum Komite Olahraga Nasional Indonesia (KONI) Pusat Letjen TNI Purn. Marciano Norman berharap Kongres Biasa ...</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677071/ihsg-senin-dibuka-menguat-3649-poin-ke-posisi-6272</t>
+          <t>https://www.antaranews.com/berita/5677500/koni-pusat-harap-kongres-biasa-pssi-diskusikan-pembinaan-prestasi</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/pergerakan-indeks-harga-saham-gabungan-2828631.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/11/Ketua-KONI-Pusat-Marciano-Norman.jpg</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PLN Jakarta pastikan pasokan listrik sudah berhasil dipulihkan</t>
+          <t>KPK panggil anggota DPR RI Anwar Sadad pada kasus dana hibah Jatim</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 08:36:26 +0700</t>
+          <t>Mon, 03 Aug 2026 15:28:20 +0700</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>PT PLN (Persero) Unit Induk Distribusi Jakarta Raya mengungkapkan pasokan listrik telah berhasil ...</t>
+          <t>Komisi Pemberantasan Korupsi (KPK) memanggil anggota DPR RI Anwar Sadad (AS) untuk diperiksa dalam penyidikan kasus ...</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677043/pln-jakarta-pastikan-pasokan-listrik-sudah-berhasil-dipulihkan</t>
+          <t>https://www.antaranews.com/berita/5677496/kpk-panggil-anggota-dpr-ri-anwar-sadad-pada-kasus-dana-hibah-jatim</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20231217-WA0015-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/07/23/IMG-20230723-WA0032.jpg</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ledakan di kantor polisi Pakistan tewaskan 14 orang</t>
+          <t>Ditjenpas Kaltim gelar CKG bagi 12 ribu warga binaan</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 07:44:23 +0700</t>
+          <t>Mon, 03 Aug 2026 15:23:58 +0700</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sebuah ledakan terjadi di luar sebuah kantor polisi di Kota Kabal, Pakistan, mengakibatkan 14 orang tewas dan 14 orang ...</t>
+          <t>ANTARA - Program Cek Kesehatan Gratis (CKG) menyasar warga binaan di Lembaga Pemasyarakatan (Lapas) dan Rumah Tahanan ...</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677020/ledakan-di-kantor-polisi-pakistan-tewaskan-14-orang</t>
+          <t>https://www.antaranews.com/video/5677480/ditjenpas-kaltim-gelar-ckg-bagi-12-ribu-warga-binaan</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CmxztpE000019_20260803_PEPFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AYM_DITJENPAS-KALTIM-GELAR-CKG.jpg</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ratusan korban selamat KMP Mutiara Santosa 2 tiba di Tanjung Perak</t>
+          <t>BPS prediksi produksi beras RI 28,71 juta ton hingga September 2026</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:37:38 +0700</t>
+          <t>Mon, 03 Aug 2026 15:23:12 +0700</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sebanyak 111 korban selamat dan dua meninggal dunia akibat kebakaran KMP Mutiara Santosa II di Perairan Utara ...</t>
+          <t>Badan Pusat Statistik (BPS) memprediksi produksi beras sepanjang Januari–September 2026 mencapai 28,71 juta ton, ...</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676983/ratusan-korban-selamat-kmp-mutiara-santosa-2-tiba-di-tanjung-perak</t>
+          <t>https://www.antaranews.com/berita/5677485/bps-prediksi-produksi-beras-ri-2871-juta-ton-hingga-september-2026</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/259549_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/proyeksi-produksi-beras-konsumsi-2815573.jpg</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Sebagian Jakarta diguyur hujan ringan pada Senin sore hingga malam</t>
+          <t>Polda Jatim kerahkan 30 personel evakuasi KMP Mutiara Sentosa 2</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:11:02 +0700</t>
+          <t>Mon, 03 Aug 2026 15:22:46 +0700</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) memprakirakan hujan ringan akan melanda sebagian wilayah Jakarta ...</t>
+          <t>Kepolisian Daerah (Polda) Jawa Timur (Jatim) mengerahkan 30 personel SAR Direktorat Kepolisian Perairan dan Udara ...</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676963/sebagian-jakarta-diguyur-hujan-ringan-pada-senin-sore-hingga-malam</t>
+          <t>https://www.antaranews.com/berita/5677483/polda-jatim-kerahkan-30-personel-evakuasi-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/01/IMG_20260301_073711.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1319202.jpg</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Atlet-atlet nasional borong 18 medali Poomsae Indonesia Open 2026</t>
+          <t>Komisi IX DPR: Putusan MK jadi momentum BGN desain ulang MBG</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 04:18:40 +0700</t>
+          <t>Mon, 03 Aug 2026 15:19:16 +0700</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Atlet-atlet tuan rumah Indonesia tampil impresif pada nomor Poomsae 8th Asian Taekwondo, Indonesia Open ...</t>
+          <t>Wakil Ketua Komisi IX DPR RI Charles Honoris mengatakan putusan Mahkamah Konstitusi Nomor 40/PUU-XXIV/2026 menjadi ...</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676947/atlet-atlet-nasional-borong-18-medali-poomsae-indonesia-open-2026</t>
+          <t>https://www.antaranews.com/berita/5677477/komisi-ix-dpr-putusan-mk-jadi-momentum-bgn-desain-ulang-mbg</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships-2026-020826-dr-04.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/15/tempImageigZXJC.jpg</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-bisnis, top-news</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Kemenhub kerahkan kapal patroli evakuasi KM Mutiara Sentosa II</t>
+          <t>Nusron sebut banyak laut di Batam telah dikapling tanpa prosedur sah</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 00:03:37 +0700</t>
+          <t>Mon, 03 Aug 2026 14:44:05 +0700</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Kementerian Perhubungan mengerahkan kapal patroli Kesatuan Penjagaan Laut dan Pantai (KPLP) serta memperkuat koordinasi ...</t>
+          <t>Menteri Agraria dan Tata Ruang (ATR)/Kepala Badan Pertanahan Nasional (BPN) Nusron Wahid mengatakan, menerima banyak ...</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676931/kemenhub-kerahkan-kapal-patroli-evakuasi-km-mutiara-sentosa-ii</t>
+          <t>https://www.antaranews.com/berita/5677425/nusron-sebut-banyak-laut-di-batam-telah-dikapling-tanpa-prosedur-sah</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_142345.jpg</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Rupiah diperkirakan menguat seiring AS batalkan rencana serang Iran</t>
+          <t>Menkomdigi panggil YouTube imbas temuan konten promosi vape sasar anak</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:12:26 +0700</t>
+          <t>Mon, 03 Aug 2026 14:22:09 +0700</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Analis Doo Financial Futures, Lukman Leong memperkirakan rupiah menguat seiring Amerika Serikat (AS) membatalkan ...</t>
+          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid merencanakan pemanggilan terhadap platform digital YouTube ...</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677132/rupiah-diperkirakan-menguat-seiring-as-batalkan-rencana-serang-iran</t>
+          <t>https://www.antaranews.com/berita/5677396/menkomdigi-panggil-youtube-imbas-temuan-konten-promosi-vape-sasar-anak</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828847.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0225.jpg</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>ekonomi-bisnis, top-news</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Rupiah pada Senin pagi melemah jadi Rp18.031 per dolar AS</t>
+          <t>Kemnaker: Magang Nasional diharapkan menekan angka pengangguran muda</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:05:50 +0700</t>
+          <t>Mon, 03 Aug 2026 13:37:57 +0700</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Nilai tukar rupiah pada Senin pagi bergerak melemah 9 poin atau 0,05 persen menjadi Rp18.031 per dolar AS dibandingkan ...</t>
+          <t>Kementerian Ketenagakerjaan (Kemnaker) mengatakan program Magang Nasional (MagangHub) untuk mempersiapkan kompetensi ...</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677063/rupiah-pada-senin-pagi-melemah-jadi-rp18031-per-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5677364/kemnaker-magang-nasional-diharapkan-menekan-angka-pengangguran-muda</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/ff63afaf-7778-47fe-833d-5a8068af9a51_1.jpeg</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Komisi XI: PFII peluang RI tangkap momentum perpindahan modal global</t>
+          <t>Kemenag perkuat transformasi madrasah lewat revitalisasi-digitalisasi</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:53:34 +0700</t>
+          <t>Mon, 03 Aug 2026 13:36:36 +0700</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Wakil Ketua Komisi XI DPR RI Mohamad Hekal mengatakan percepatan pembentukan Pusat Finansial Internasional Indonesia ...</t>
+          <t>Menteri Agama (Menag) Nasaruddin Umar menegaskan transformasi madrasah terus diperkuat melalui revitalisasi ...</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676995/komisi-xi-pfii-peluang-ri-tangkap-momentum-perpindahan-modal-global</t>
+          <t>https://www.antaranews.com/berita/5677363/kemenag-perkuat-transformasi-madrasah-lewat-revitalisasi-digitalisasi</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Saham-dan-oblogasi.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/14/1000173935_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>ekonomi-bisnis, top-news</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BUMA International Group bukukan pertumbuhan EBITDA semester I/2026</t>
+          <t>Lisensi IP Global Buka Peluang Bisnis Baru bagi Kreator Indonesia</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:17:40 +0700</t>
+          <t>Mon, 03 Aug 2026 13:34:30 +0700</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>PT BUMA Internasional Gorup membukukan pertumbuhan EBITDA pada semester pertama 2026 (1H26) di tengah penurunan ...</t>
+          <t>Wakil Menteri Ekonomi Kreatif Irene Umar mengatakan kolaborasi antara pemilik kekayaan intelektual (Intellectual ...</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676967/buma-international-group-bukukan-pertumbuhan-ebitda-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5677353/lisensi-ip-global-buka-peluang-bisnis-baru-bagi-kreator-indonesia</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/buma.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000589873.jpg</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>ekonomi-bisnis, top-news</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>CORE: Harga Pertamax turun beri sentimen positif bagi inflasi</t>
+          <t>Nilai ekspor perdagangan RI Januari-Juni capai 140,81 miliar dolar AS</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:40:44 +0700</t>
+          <t>Mon, 03 Aug 2026 13:16:17 +0700</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ekonom Center of Reform on Economics (CORE) Yusuf Rendy Manilet menyampaikan penurunan harga Pertamax pada bulan ...</t>
+          <t>Badan Pusat Statistik (BPS) mencatat nilai ekspor Indonesia secara kumulatif dari Januari-Juni 2026 mencapai 140,81 ...</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677420/core-harga-pertamax-turun-beri-sentimen-positif-bagi-inflasi</t>
+          <t>https://www.antaranews.com/berita/5677315/nilai-ekspor-perdagangan-ri-januari-juni-capai-14081-miliar-dolar-as</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/penurunan-harga-bbm-jenis-pertamax-2831783.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/neraca-perdagangan-januari-mei-2026-surplus-2815779.jpg</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Askrindo bukukan laba Rp1,69 T pada 2025 ditopang tiga lini bisnis</t>
+          <t>Korban KMP Mutiara Sentosa II dievakuasi ke Pelabuhan Tanjung Perak</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:38:49 +0700</t>
+          <t>Mon, 03 Aug 2026 13:06:15 +0700</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>PT Asuransi Kredit Indonesia (Persero) atau Askrindo membukukan laba setelah pajak sebesar Rp1,69 triliun pada 2025 ...</t>
+          <t>Tim SAR gabungan terus melakukan evakuasi korban terbakarnya KMP Mutiara Sentosa 2 ke darat, tepatnya ke Pelabuhan ...</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677419/askrindo-bukukan-laba-rp169-t-pada-2025-ditopang-tiga-lini-bisnis</t>
+          <t>https://www.antaranews.com/berita/5677297/korban-kmp-mutiara-sentosa-ii-dievakuasi-ke-pelabuhan-tanjung-perak</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-08.51.32.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/260821_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Jasaraharja Putera menjamin santunan korban KMP Mutiara Sentosa II</t>
+          <t>Aktor senior Diding Boneng meninggal dunia</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:30:17 +0700</t>
+          <t>Mon, 03 Aug 2026 11:39:03 +0700</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>PT Jasaraharja Putera menjamin perlindungan dan santunan bagi seluruh korban kebakaran Kapal Motor Penyeberangan (KMP) ...</t>
+          <t>Aktor sekaligus komedian tanah air, Zainal Abidin alias Diding Boneng dikabarkan meninggal dunia pada Senin (3/8) dalam ...</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677412/jasaraharja-putera-menjamin-santunan-korban-kmp-mutiara-sentosa-ii</t>
+          <t>https://www.antaranews.com/berita/5677209/aktor-senior-diding-boneng-meninggal-dunia</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176259.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/26f1eb88-3301-4ae1-badd-bed5078fe3dd.jpeg</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>GMR bidik Indonesia dalam perluasan rute Bandara Bhogapuram India</t>
+          <t>Seskab: Prabowo dorong sinergi pemerintah dan dunia usaha</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:29:34 +0700</t>
+          <t>Mon, 03 Aug 2026 11:17:50 +0700</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>GMR Airports Limited (GMR Airports), salah satu pengelola jaringan bandara internasional, memprioritaskan Indonesia ...</t>
+          <t>Sekretaris Kabinet Teddy Indra Wijaya menyampaikan bahwa Presiden Prabowo Subianto menekankan pentingnya sinergi antara ...</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677407/gmr-bidik-indonesia-dalam-perluasan-rute-bandara-bhogapuram-india</t>
+          <t>https://www.antaranews.com/berita/5677191/seskab-prabowo-dorong-sinergi-pemerintah-dan-dunia-usaha</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0725.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0891_1.jpeg</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BPS: Wisman per Juni capai 7,45 juta kunjungan, tertinggi sejak 2020</t>
+          <t>Red Velvet bersiap kembali lewat EP baru "Velvet Summer"</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:22:48 +0700</t>
+          <t>Mon, 03 Aug 2026 10:24:37 +0700</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat total kunjungan wisatawan mancanegara dari Januari hingga bulan Juni 2026 mencapai ...</t>
+          <t>Grup idola K-pop Red Velvet akan kembali lewat rilis mini album atau extended play (EP) baru bertajuk “Velvet ...</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677399/bps-wisman-per-juni-capai-745-juta-kunjungan-tertinggi-sejak-2020</t>
+          <t>https://www.antaranews.com/berita/5677151/red-velvet-bersiap-kembali-lewat-ep-baru-velvet-summer</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/pelepasliaran-500-ekor-tukik-bali-290726-nhw-3_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/ca97a3a8-aa17-45fc-be71-d36051dd9dcd.jpeg</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>BPS catat nilai tukar petani di level 127,84 pada Juli 2026</t>
+          <t>Menaker pastikan komitmen pemerintah perkuat kesejahteraan pekerja</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:18:40 +0700</t>
+          <t>Mon, 03 Aug 2026 10:16:19 +0700</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat nilai tukar petani (NTP) secara nasional pada bulan Juli 2026 berada di level ...</t>
+          <t>Menteri Ketenagakerjaan (Menaker) Yassierli memastikan pemerintah berkomitmen untuk memperkuat kesejahteraan, ...</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677323/bps-catat-nilai-tukar-petani-di-level-12784-pada-juli-2026</t>
+          <t>https://www.antaranews.com/berita/5677148/menaker-pastikan-komitmen-pemerintah-perkuat-kesejahteraan-pekerja</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/02/20260302_083324.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/09/20/pelepasan-peserta-pemagangan-ke-jepang-di-jawa-barat-2627513.jpg</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Menteri ATR sebut 400 Kantah sudah terapkan pengukuran terjadwal</t>
+          <t>23 calon hakim agung dan ad hoc ikuti seleksi wawancara akhir</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:13:29 +0700</t>
+          <t>Mon, 03 Aug 2026 10:15:01 +0700</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Menteri Agraria dan Tata Ruang/Kepala Badan Pertanahan Nasional (ATR/BPN) Nusron Wahid mengatakan bahwa sudah ada 400 ...</t>
+          <t>Sebanyak 23 orang calon hakim agung dan ad hoc Mahkamah Agung Tahun 2026 mengikuti seleksi wawancara tahap akhir di ...</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677308/menteri-atr-sebut-400-kantah-sudah-terapkan-pengukuran-terjadwal</t>
+          <t>https://www.antaranews.com/berita/5677137/23-calon-hakim-agung-dan-ad-hoc-ikuti-seleksi-wawancara-akhir</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_125328.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000012883_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PT PAL-BRIN wujudkan galangan kapal hijau dukung industri perkapalan</t>
+          <t>BRIN perkuat kajian sungai bawah tanah di Kebumen untuk ketahanan air</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:43:28 +0700</t>
+          <t>Mon, 03 Aug 2026 09:57:19 +0700</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>PT PAL Indonesia bersama Badan Riset dan Inovasi Nasional (BRIN) berkolaborasi mewujudkan transformasi green ...</t>
+          <t>Badan Riset dan Inovasi Nasional (BRIN) memperkuat riset ketahanan air melalui pengembangan teknologi dan penelitian ...</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677267/pt-pal-brin-wujudkan-galangan-kapal-hijau-dukung-industri-perkapalan</t>
+          <t>https://www.antaranews.com/berita/5677120/brin-perkuat-kajian-sungai-bawah-tanah-di-kebumen-untuk-ketahanan-air</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/a647aa30-a843-4000-98a0-07d27228a41e.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1785706440-47672950-1.jpg</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Pangan, transportasi, dan emas perhiasan dorong inflasi pada Juli 2026</t>
+          <t>Harga bensin turun pada pekan pertama Agustus</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:32:11 +0700</t>
+          <t>Mon, 03 Aug 2026 09:51:00 +0700</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat kelompok makanan, minuman, dan tembakau, transportasi, serta perawatan pribadi dan ...</t>
+          <t>Harga bahan bakar minyak (BBM) jenis bensin di stasiun pengisian bahan bakar umum (SPBU) Pertamina, Shell, dan bp ...</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677256/pangan-transportasi-dan-emas-perhiasan-dorong-inflasi-pada-juli-2026</t>
+          <t>https://www.antaranews.com/berita/5677109/harga-bensin-turun-pada-pekan-pertama-agustus</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/bps.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/10/02/penuruanan-harga-bbm-011024-aaa-7.jpg</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>BPS: Neraca perdagangan Januari-Juni 2026 surplus 3,58 miliar dolar AS</t>
+          <t>Sean Gelael berbagi pengalaman di dunia balap ke pengunjung GIIAS 2026</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:27:18 +0700</t>
+          <t>Mon, 03 Aug 2026 09:34:53 +0700</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat bahwa neraca perdagangan barang Indonesia mengalami surplus senilai 3,58 miliar ...</t>
+          <t>Pembalap Indonesia Sean Gelael berbagi pengalamannya di dunia balap ke pengunjung GAIKINDO Indonesia International ...</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677252/bps-neraca-perdagangan-januari-juni-2026-surplus-358-miliar-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5677103/sean-gelael-berbagi-pengalaman-di-dunia-balap-ke-pengunjung-giias-2026</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/bps.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/16b70b87-326f-479a-a806-580ab846cc6f_1.jpeg</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>ekonomi-bursa, top-news</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Laba bersih Tugu Insurance capai Rp480,29 miliar pada semester I 2026</t>
+          <t>IHSG Senin dibuka menguat 36,49 poin ke posisi 6.272</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:24:56 +0700</t>
+          <t>Mon, 03 Aug 2026 09:11:26 +0700</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>PT Asuransi Tugu Pratama Indonesia Tbk atau Tugu Insurance membukukan laba tahun berjalan yang dapat diatribusikan ...</t>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin pagi dibuka menguat 36,49 poin atau 0,59 ...</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677249/laba-bersih-tugu-insurance-capai-rp48029-miliar-pada-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5677071/ihsg-senin-dibuka-menguat-3649-poin-ke-posisi-6272</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-11.02.17.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/pergerakan-indeks-harga-saham-gabungan-2828631.jpg</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>IHSG awal pekan berpotensi variatif seiring sentimen global-domestik</t>
+          <t>PLN Jakarta pastikan pasokan listrik sudah berhasil dipulihkan</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:42:28 +0700</t>
+          <t>Mon, 03 Aug 2026 08:36:26 +0700</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin berpotensi bergerak variatif dipicu oleh ...</t>
+          <t>PT PLN (Persero) Unit Induk Distribusi Jakarta Raya mengungkapkan pasokan listrik telah berhasil ...</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677104/ihsg-awal-pekan-berpotensi-variatif-seiring-sentimen-global-domestik</t>
+          <t>https://www.antaranews.com/berita/5677043/pln-jakarta-pastikan-pasokan-listrik-sudah-berhasil-dipulihkan</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/12/12/ihsg-ditutup-menguat-2688871.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20231217-WA0015-1.jpg</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>humaniora</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Bantuan beras 30 kg cair mulai 17 Agustus 2026, ini jadwal dan cara cek penerimanya</t>
+          <t>Ledakan di kantor polisi Pakistan tewaskan 14 orang</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:27:14 +0700</t>
+          <t>Mon, 03 Aug 2026 07:44:23 +0700</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Pemerintah memastikan penyaluran bantuan pangan beras tahap II tahun 2026 akan dimulai pada 17 Agustus 2026. Bantuan ...</t>
+          <t>Sebuah ledakan terjadi di luar sebuah kantor polisi di Kota Kabal, Pakistan, mengakibatkan 14 orang tewas dan 14 orang ...</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677341/bantuan-beras-30-kg-cair-mulai-17-agustus-2026-ini-jadwal-dan-cara-cek-penerimanya</t>
+          <t>https://www.antaranews.com/berita/5677020/ledakan-di-kantor-polisi-pakistan-tewaskan-14-orang</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/26/kemensos-percepat-penyaluran-bansos-pkh-dan-bpnt-2778877.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CmxztpE000019_20260803_PEPFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>10 ide lomba 17 Agustus untuk anak PAUD dan TK yang seru, edukatif, dan mudah digelar</t>
+          <t>Ratusan korban selamat KMP Mutiara Santosa 2 tiba di Tanjung Perak</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:38:29 +0700</t>
+          <t>Mon, 03 Aug 2026 06:37:38 +0700</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Perayaan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 dapat menjadi momen bagi anak usia PAUD dan TK ...</t>
+          <t>Sebanyak 111 korban selamat dan dua meninggal dunia akibat kebakaran KMP Mutiara Santosa II di Perairan Utara ...</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677368/10-ide-lomba-17-agustus-untuk-anak-paud-dan-tk-yang-seru-edukatif-dan-mudah-digelar</t>
+          <t>https://www.antaranews.com/berita/5676983/ratusan-korban-selamat-kmp-mutiara-santosa-2-tiba-di-tanjung-perak</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/08/03/WhatsApp-Image-2024-08-03-at-20.37.28.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/259549_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Sering terbangun tengah malam? Kenali 7 penyebab dan cara mengatasinya</t>
+          <t>Sebagian Jakarta diguyur hujan ringan pada Senin sore hingga malam</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:35:20 +0700</t>
+          <t>Mon, 03 Aug 2026 06:11:02 +0700</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bangun di tengah malam sesekali merupakan hal yang normal. Namun, jika kondisi ini terjadi hampir setiap malam dan ...</t>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) memprakirakan hujan ringan akan melanda sebagian wilayah Jakarta ...</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677357/sering-terbangun-tengah-malam-kenali-7-penyebab-dan-cara-mengatasinya</t>
+          <t>https://www.antaranews.com/berita/5676963/sebagian-jakarta-diguyur-hujan-ringan-pada-senin-sore-hingga-malam</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/20/Penumpang-rela-menginap-menunggu-kereta-pertama-di-Stasiun-Cikarang-150726-ryl-5.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/01/IMG_20260301_073711.jpg</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Bahaya paparan pornografi pada anak: Dampak bagi otak, mental, dan perilaku</t>
+          <t>Atlet-atlet nasional borong 18 medali Poomsae Indonesia Open 2026</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:23:03 +0700</t>
+          <t>Mon, 03 Aug 2026 04:18:40 +0700</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Perkembangan teknologi membuat anak-anak dan remaja semakin akrab dengan internet sejak usia dini. Di satu sisi, ...</t>
+          <t>Atlet-atlet tuan rumah Indonesia tampil impresif pada nomor Poomsae 8th Asian Taekwondo, Indonesia Open ...</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677332/bahaya-paparan-pornografi-pada-anak-dampak-bagi-otak-mental-dan-perilaku</t>
+          <t>https://www.antaranews.com/berita/5676947/atlet-atlet-nasional-borong-18-medali-poomsae-indonesia-open-2026</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/02/ilustrasi-konten-berbau-pornografi.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships-2026-020826-dr-04.jpg</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Sudah ngantuk tapi sulit tidur pulas? Ini penyebab dan cara atasinya</t>
+          <t>Kemenhub kerahkan kapal patroli evakuasi KM Mutiara Sentosa II</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:28:54 +0700</t>
+          <t>Mon, 03 Aug 2026 00:03:37 +0700</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Rasa kantuk yang muncul di malam hari seharusnya menjadi pertanda bahwa tubuh siap beristirahat. Namun, tidak sedikit ...</t>
+          <t>Kementerian Perhubungan mengerahkan kapal patroli Kesatuan Penjagaan Laut dan Pantai (KPLP) serta memperkuat koordinasi ...</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677203/sudah-ngantuk-tapi-sulit-tidur-pulas-ini-penyebab-dan-cara-atasinya</t>
+          <t>https://www.antaranews.com/berita/5676931/kemenhub-kerahkan-kapal-patroli-evakuasi-km-mutiara-sentosa-ii</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/17/Nafas.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Cara cepat tidur dalam 5 menit, efektif untuk yang sulit pulas</t>
+          <t>Rupiah diperkirakan menguat seiring AS batalkan rencana serang Iran</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:25:40 +0700</t>
+          <t>Mon, 03 Aug 2026 10:12:26 +0700</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sulit tidur meski badan sudah terasa lelah merupakan masalah yang kerap dialami banyak orang. Kondisi ini sering ...</t>
+          <t>Analis Doo Financial Futures, Lukman Leong memperkirakan rupiah menguat seiring Amerika Serikat (AS) membatalkan ...</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677199/cara-cepat-tidur-dalam-5-menit-efektif-untuk-yang-sulit-pulas</t>
+          <t>https://www.antaranews.com/berita/5677132/rupiah-diperkirakan-menguat-seiring-as-batalkan-rencana-serang-iran</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/11/04/tidua.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828847.jpg</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>tekno</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Cara mengganti password WiFi lewat HP dan laptop dengan mudah</t>
+          <t>Rupiah pada Senin pagi melemah jadi Rp18.031 per dolar AS</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:16:14 +0700</t>
+          <t>Mon, 03 Aug 2026 09:05:50 +0700</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>WiFi yang tiba-tiba terasa lambat padahal sinyal penuh dan kuota internet masih banyak tentu membuat kesal. Salah satu ...</t>
+          <t>Nilai tukar rupiah pada Senin pagi bergerak melemah 9 poin atau 0,05 persen menjadi Rp18.031 per dolar AS dibandingkan ...</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677312/cara-mengganti-password-wifi-lewat-hp-dan-laptop-dengan-mudah</t>
+          <t>https://www.antaranews.com/berita/5677063/rupiah-pada-senin-pagi-melemah-jadi-rp18031-per-dolar-as</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2020/08/19/antarafoto-warga-sediakan-internet-gratis-bagi-pelajar-190820-ief-2-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Pemerintah bangun 1.416 Jembatan Garuda untuk hubungkan desa terpencil</t>
+          <t>Komisi XI: PFII peluang RI tangkap momentum perpindahan modal global</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:53:00 +0700</t>
+          <t>Mon, 03 Aug 2026 06:53:34 +0700</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Foto udara pengendara sepeda motor melintasi Jembatan Gantung Garuda yang menghubungkan Desa Kertarahayu dan Desa Jayasampurna di Kabupaten Bekasi, Jawa Barat, Senin (3/8/2026). Hingga akhir Juli 2026, pemerintah telah membangun 1.416 unit Jembatan Garuda di daerah terpencil yang menghubungkan 7.371 desa dan kelurahan untuk mempermudah akses masyarakat serta mempersingkat waktu tempuh. ANTARA FOTO/Darryl Ramadhan/tom.</t>
+          <t>Wakil Ketua Komisi XI DPR RI Mohamad Hekal mengatakan percepatan pembentukan Pusat Finansial Internasional Indonesia ...</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5677284/pemerintah-bangun-1416-jembatan-garuda-untuk-hubungkan-desa-terpencil</t>
+          <t>https://www.antaranews.com/berita/5676995/komisi-xi-pfii-peluang-ri-tangkap-momentum-perpindahan-modal-global</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/Pembangunan-Jembatan-Garuda-percepat-akses-desa-030826-ryl-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Saham-dan-oblogasi.jpg</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Petugas evakuasi dua jenazah korban kebakaran KM Mutiara Sentosa II</t>
+          <t>BUMA International Group bukukan pertumbuhan EBITDA semester I/2026</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:03:11 +0700</t>
+          <t>Mon, 03 Aug 2026 06:17:40 +0700</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Sejumlah petugas mengangkat kantong berisi jenazah korban kebakaran KM Mutiara Sentosa II setelah tiba di Dermaga Jamrud Utara, Pelabuhan Tanjung Perak, Surabaya, Jawa Timur, Senin (3/8/2026). Kapal kargo Meratus Pematang Siantar mengevakuasi 111 penumpang selamat dan dua jenazah korban kebakaran KM Mutiara Sentosa II di perairan utara Madura pada Minggu (2/8). ANTARA FOTO/Didik Suhartono/tom.</t>
+          <t>PT BUMA Internasional Gorup membukukan pertumbuhan EBITDA pada semester pertama 2026 (1H26) di tengah penurunan ...</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5677056/petugas-evakuasi-dua-jenazah-korban-kebakaran-km-mutiara-sentosa-ii</t>
+          <t>https://www.antaranews.com/berita/5676967/buma-international-group-bukukan-pertumbuhan-ebitda-semester-i-2026</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/korban-kebakaran-km-mutiara-sentosa-2-030826-Ds-4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/buma.jpg</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Kesbangpol Pontianak antisipasi konflik sosial akibat karhutla</t>
+          <t>BPS catat pengeluaran wisman triwulan II-2026 mencapai 1.285 dolar AS</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+          <t>Mon, 03 Aug 2026 14:56:12 +0700</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>ANTARA - Badan Kesatuan Bangsa dan Politik (Kesbangpol) Kota Pontianak mengidentifikasi potensi gangguan keamanan dan konflik sosial akibat kebakaran hutan dan lahan (karhutla), Senin (3/8). Langkah yang dilakukan meliputi koordinasi lintas sektor, pemantauan situasi, hingga mediasi untuk menjaga kondusivitas selama penanganan karhutla. (Indra Budi Santoso/Rizky Bagus Dhermawan/Arsy Fitriady)</t>
+          <t>Badan Pusat Statistik (BPS) mencatat perkembangan pengeluaran wisatawan mancanegara (wisman) pada triwulan II tahun ...</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677519/kesbangpol-pontianak-antisipasi-konflik-sosial-akibat-karhutla</t>
+          <t>https://www.antaranews.com/berita/5677457/bps-catat-pengeluaran-wisman-triwulan-ii-2026-mencapai-1285-dolar-as</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/KESBANGPOL-PONTIANAK-ANTISIPASI-KONFLIK-SOSIAL-AKIBAT-KARHUTLA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG-20260731-WA0028.jpg</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PSEL Serang Raya jadi solusi pengelolaan sampah tiga daerah</t>
+          <t>Kapal Pertamina selamatkan 17 korban KMP Mutiara Sentosa 2</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+          <t>Mon, 03 Aug 2026 14:52:47 +0700</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>ANTARA - Fasilitas Pengolahan Sampah menjadi Energi Listrik (PSEL) Serang Raya akan dibangun di TPSA Cilowong, Kota Serang, untuk melayani pengelolaan sampah Kabupaten Serang, Kota Serang, dan Kota Cilegon. Fasilitas berkapasitas 1.161 ton sampah per hari itu diharapkan mampu mengurangi beban tempat pemrosesan akhir sekaligus mengubah sampah menjadi energi listrik. (Susmiatun Hayati/Agha Yuninda Maulana/Arsy Fitriady)</t>
+          <t>Kapal Pertamina Patra Niaga MT Transko Arafura berhasil mengevakuasi 17 orang korban KMP Mutiara Sentosa 2 yang ...</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677492/psel-serang-raya-jadi-solusi-pengelolaan-sampah-tiga-daerah</t>
+          <t>https://www.antaranews.com/berita/5677445/kapal-pertamina-selamatkan-17-korban-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PSEL-SERANG-RAYA-JADI-SOLUSI-PENGELOLAAN-SAMPAH.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-14.30.38.jpeg</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Pemkot Ambon salurkan air bersih gratis jika kekeringan terjadi</t>
+          <t>PGN sasar pemanfaatan jargas untuk hotel hingga UMKM</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+          <t>Mon, 03 Aug 2026 14:50:20 +0700</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>ANTARA - Pemerintah Kota Ambon, Maluku, menyiapkan langkah antisipasi untuk menjamin ketersediaan air bersih bagi masyarakat dalam menghadapi potensi musim kemarau panjang akibat fenomena El Nino. Wali kota Ambon Bodewin Wattimena, Senin (3/8), mengatakan, pemerintah melakukan pemetaan wilayah yang rawan lalu mendistribusikan air bersih ke wilayah terdampak kekeringan. (Alfian Sanusi/Rizky Bagus Dhermawan/Rijalul Vikry)</t>
+          <t>PT Perusahaan Gas Negara (Persero) Tbk (PGN) menyasar pemanfaatan jaringan gas (jargas) tidak hanya rumah ...</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677489/pemkot-ambon-salurkan-air-bersih-gratis-jika-kekeringan-terjadi</t>
+          <t>https://www.antaranews.com/berita/5677439/pgn-sasar-pemanfaatan-jargas-untuk-hotel-hingga-umkm</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-151844.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_2395.jpeg</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Razia balap liar, Polres Temanggung sita 106 motor</t>
+          <t>CORE: Harga Pertamax turun beri sentimen positif bagi inflasi</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+          <t>Mon, 03 Aug 2026 14:40:44 +0700</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>ANTARA - Kepolisian Resor (Polres) Temanggung, Jawa Tengah menyita 106 sepeda motor dalam razia balap liar yang digelar Minggu malam (2/8). Kegiatan razia tersebut digelar sebagai bagian  upaya kepolisian dalam menekan aksi balap liar  di Temanggung.(Firman Eko Handy/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
+          <t>Ekonom Center of Reform on Economics (CORE) Yusuf Rendy Manilet menyampaikan penurunan harga Pertamax pada bulan ...</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677488/razia-balap-liar-polres-temanggung-sita-106-motor</t>
+          <t>https://www.antaranews.com/berita/5677420/core-harga-pertamax-turun-beri-sentimen-positif-bagi-inflasi</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_RAZIA-BALAP-LIAR-POLRES-TEMANGGUNG-SITA-106-MOTOR.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/penurunan-harga-bbm-jenis-pertamax-2831783.jpg</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ditjenpas Kaltim gelar CKG bagi 12 ribu warga binaan</t>
+          <t>Askrindo bukukan laba Rp1,69 T pada 2025 ditopang tiga lini bisnis</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+          <t>Mon, 03 Aug 2026 14:38:49 +0700</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>ANTARA - Program Cek Kesehatan Gratis (CKG) menyasar warga binaan di Lembaga Pemasyarakatan (Lapas) dan Rumah Tahanan (Rutan) di Kalimantan Timur. CKG untuk 12 ribu warga binaan bertujuan mengantisipasi penyebaran risiko penyakit menular di lapas. (Hanifan Ma'ruf/Agha Yuninda Maulana/Rijalul Vikry)</t>
+          <t>PT Asuransi Kredit Indonesia (Persero) atau Askrindo membukukan laba setelah pajak sebesar Rp1,69 triliun pada 2025 ...</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677480/ditjenpas-kaltim-gelar-ckg-bagi-12-ribu-warga-binaan</t>
+          <t>https://www.antaranews.com/berita/5677419/askrindo-bukukan-laba-rp169-t-pada-2025-ditopang-tiga-lini-bisnis</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_DITJENPAS-KALTIM-GELAR-CKG.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-08.51.32.jpeg</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Paus Leo XIV prihatin atas situasi krisis migran di Ceuta</t>
+          <t>Jasaraharja Putera menjamin santunan korban KMP Mutiara Sentosa II</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+          <t>Mon, 03 Aug 2026 14:30:17 +0700</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>ANTARA - Paus Leo XIV  menyampaikan keprihatinan atas situasi krisis migran di Enklave, Spanyol, Ceuta.  Saat memimpin doa angelus di Vatikan, Minggu (2/8), Paus berdoa agar terdapat solusi yang membawa perdamaian dan keadilan atas kondisi tersebut. (Ludmila Yusufin Diah Nastiti/Agha Yuninda Maulana/Winanto)</t>
+          <t>PT Jasaraharja Putera menjamin perlindungan dan santunan bagi seluruh korban kebakaran Kapal Motor Penyeberangan (KMP) ...</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677384/paus-leo-xiv-prihatin-atas-situasi-krisis-migran-di-ceuta</t>
+          <t>https://www.antaranews.com/berita/5677412/jasaraharja-putera-menjamin-santunan-korban-kmp-mutiara-sentosa-ii</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PAUS-LEO-XIV-PRIHATIN-ATAS-SITUASI-KRISIS.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176259.jpg</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Resmi dibuka, Sekolah Rakyat Terintegrasi 2 Kendari tampung 339 siswa</t>
+          <t>GMR bidik Indonesia dalam perluasan rute Bandara Bhogapuram India</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
+          <t>Mon, 03 Aug 2026 14:29:34 +0700</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
+          <t>GMR Airports Limited (GMR Airports), salah satu pengelola jaringan bandara internasional, memprioritaskan Indonesia ...</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677407/gmr-bidik-indonesia-dalam-perluasan-rute-bandara-bhogapuram-india</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0725.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>BPS: Wisman per Juni capai 7,45 juta kunjungan, tertinggi sejak 2020</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 14:22:48 +0700</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) mencatat total kunjungan wisatawan mancanegara dari Januari hingga bulan Juni 2026 mencapai ...</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677399/bps-wisman-per-juni-capai-745-juta-kunjungan-tertinggi-sejak-2020</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/pelepasliaran-500-ekor-tukik-bali-290726-nhw-3_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>BPS catat nilai tukar petani di level 127,84 pada Juli 2026</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:18:40 +0700</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) mencatat nilai tukar petani (NTP) secara nasional pada bulan Juli 2026 berada di level ...</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677323/bps-catat-nilai-tukar-petani-di-level-12784-pada-juli-2026</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/02/20260302_083324.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Menteri ATR sebut 400 Kantah sudah terapkan pengukuran terjadwal</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:13:29 +0700</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Menteri Agraria dan Tata Ruang/Kepala Badan Pertanahan Nasional (ATR/BPN) Nusron Wahid mengatakan bahwa sudah ada 400 ...</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677308/menteri-atr-sebut-400-kantah-sudah-terapkan-pengukuran-terjadwal</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_125328.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>ekonomi-bursa</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>IHSG awal pekan berpotensi variatif seiring sentimen global-domestik</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 09:42:28 +0700</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin berpotensi bergerak variatif dipicu oleh ...</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677104/ihsg-awal-pekan-berpotensi-variatif-seiring-sentimen-global-domestik</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/12/12/ihsg-ditutup-menguat-2688871.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>humaniora</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Bantuan beras 30 kg cair mulai 17 Agustus 2026, ini jadwal dan cara cek penerimanya</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:27:14 +0700</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Pemerintah memastikan penyaluran bantuan pangan beras tahap II tahun 2026 akan dimulai pada 17 Agustus 2026. Bantuan ...</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677341/bantuan-beras-30-kg-cair-mulai-17-agustus-2026-ini-jadwal-dan-cara-cek-penerimanya</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/26/kemensos-percepat-penyaluran-bansos-pkh-dan-bpnt-2778877.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>10 ide lomba 17 Agustus untuk anak PAUD dan TK yang seru, edukatif, dan mudah digelar</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:38:29 +0700</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Perayaan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 dapat menjadi momen bagi anak usia PAUD dan TK ...</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677368/10-ide-lomba-17-agustus-untuk-anak-paud-dan-tk-yang-seru-edukatif-dan-mudah-digelar</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/08/03/WhatsApp-Image-2024-08-03-at-20.37.28.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Sering terbangun tengah malam? Kenali 7 penyebab dan cara mengatasinya</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:35:20 +0700</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Bangun di tengah malam sesekali merupakan hal yang normal. Namun, jika kondisi ini terjadi hampir setiap malam dan ...</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677357/sering-terbangun-tengah-malam-kenali-7-penyebab-dan-cara-mengatasinya</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/20/Penumpang-rela-menginap-menunggu-kereta-pertama-di-Stasiun-Cikarang-150726-ryl-5.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Bahaya paparan pornografi pada anak: Dampak bagi otak, mental, dan perilaku</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:23:03 +0700</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Perkembangan teknologi membuat anak-anak dan remaja semakin akrab dengan internet sejak usia dini. Di satu sisi, ...</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677332/bahaya-paparan-pornografi-pada-anak-dampak-bagi-otak-mental-dan-perilaku</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/02/ilustrasi-konten-berbau-pornografi.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Sudah ngantuk tapi sulit tidur pulas? Ini penyebab dan cara atasinya</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 11:28:54 +0700</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Rasa kantuk yang muncul di malam hari seharusnya menjadi pertanda bahwa tubuh siap beristirahat. Namun, tidak sedikit ...</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677203/sudah-ngantuk-tapi-sulit-tidur-pulas-ini-penyebab-dan-cara-atasinya</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/17/Nafas.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Cara cepat tidur dalam 5 menit, efektif untuk yang sulit pulas</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 11:25:40 +0700</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Sulit tidur meski badan sudah terasa lelah merupakan masalah yang kerap dialami banyak orang. Kondisi ini sering ...</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677199/cara-cepat-tidur-dalam-5-menit-efektif-untuk-yang-sulit-pulas</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/04/tidua.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>tekno</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Cara mengganti password WiFi lewat HP dan laptop dengan mudah</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:16:14 +0700</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>WiFi yang tiba-tiba terasa lambat padahal sinyal penuh dan kuota internet masih banyak tentu membuat kesal. Salah satu ...</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677312/cara-mengganti-password-wifi-lewat-hp-dan-laptop-dengan-mudah</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2020/08/19/antarafoto-warga-sediakan-internet-gratis-bagi-pelajar-190820-ief-2-1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Petani berbagi air sumur demi selamatkan tanaman tembakau</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 14:44:51 +0700</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Petani mengambil air dari sumur untuk menyiram tanaman tembakau di Lengkong, Nganjuk, Jawa Timur, Senin (3/8/2026). Sejumlah petani di kawasan tersebut saling berbagi air sumur untuk menjaga pasokan air irigasi dan mempertahankan produktivitas lahan di tengah terbatasnya ketersediaan air pada musim kemarau akibat El Nino. ANTARA FOTO/Muhammad Mada/tom.</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5677428/petani-berbagi-air-sumur-demi-selamatkan-tanaman-tembakau</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/petani-tembakau-berbagi-air-sumur-antisipasi-dampak-el-nino-030826-mm-1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Pemerintah bangun 1.416 Jembatan Garuda untuk hubungkan desa terpencil</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 12:53:00 +0700</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Foto udara pengendara sepeda motor melintasi Jembatan Gantung Garuda yang menghubungkan Desa Kertarahayu dan Desa Jayasampurna di Kabupaten Bekasi, Jawa Barat, Senin (3/8/2026). Hingga akhir Juli 2026, pemerintah telah membangun 1.416 unit Jembatan Garuda di daerah terpencil yang menghubungkan 7.371 desa dan kelurahan untuk mempermudah akses masyarakat serta mempersingkat waktu tempuh. ANTARA FOTO/Darryl Ramadhan/tom.</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5677284/pemerintah-bangun-1416-jembatan-garuda-untuk-hubungkan-desa-terpencil</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/Pembangunan-Jembatan-Garuda-percepat-akses-desa-030826-ryl-1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Petugas evakuasi dua jenazah korban kebakaran KM Mutiara Sentosa II</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 09:03:11 +0700</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Sejumlah petugas mengangkat kantong berisi jenazah korban kebakaran KM Mutiara Sentosa II setelah tiba di Dermaga Jamrud Utara, Pelabuhan Tanjung Perak, Surabaya, Jawa Timur, Senin (3/8/2026). Kapal kargo Meratus Pematang Siantar mengevakuasi 111 penumpang selamat dan dua jenazah korban kebakaran KM Mutiara Sentosa II di perairan utara Madura pada Minggu (2/8). ANTARA FOTO/Didik Suhartono/tom.</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5677056/petugas-evakuasi-dua-jenazah-korban-kebakaran-km-mutiara-sentosa-ii</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/korban-kebakaran-km-mutiara-sentosa-2-030826-Ds-4.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Menkomdigi kukuhkan komisioner KI Pusat, perkuat keterbukaan informasi</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengambil sumpah jabatan dan mengukuhkan tujuh anggota Komisi Informasi Pusat (KIP) Periode 2026–2030 di Kantor Kementerian Komdigi Jakarta, Senin (3/8).  Komisioner KI Pusat Periode 2026–2030 akan melanjutkan tugas dan fungsi komisioner sebelumnya, yakni penyelesaian sengketa informasi publik secara adil, menetapkan kebijakan teknis di bidang keterbukaan informasi, dan memperkuat implementasi UU Nomor 14 Tahun 2008 tentang Keterbukaan Informasi Publik. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677604/menkomdigi-kukuhkan-komisioner-ki-pusat-perkuat-keterbukaan-informasi</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-KUKUHKAN-KOMISIONER-KI-PUSAT-PERKUAT-KETERBUKAAN-INFORMASI.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Partai Buruh Brasil calonkan Lula da Silva untuk masa jabatan keempat</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>ANTARA - Partai Buruh di Brasil pada Minggu (2/8) waktu setempat, resmi mencalonkan petahana Luiz Inacio Lula da Silva sebagai kandidat dalam pemilihan presiden mendatang untuk masa jabatan keempat. Pada konvensi nasional partai di Sao Paulo, para delegasi secara resmi menyetujui pasangan Lula dengan Wakil Presiden petahana Geraldo Alckmin dari Partai Sosialis Brasil.
+(XINHUA /Winanto/Rizky Bagus Dhermawan/Ludmila Yusufin Diah Nastiti)</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677541/partai-buruh-brasil-calonkan-lula-da-silva-untuk-masa-jabatan-keempat</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-154005.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Kesbangpol Pontianak antisipasi konflik sosial akibat karhutla</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Kesatuan Bangsa dan Politik (Kesbangpol) Kota Pontianak mengidentifikasi potensi gangguan keamanan dan konflik sosial akibat kebakaran hutan dan lahan (karhutla), Senin (3/8). Langkah yang dilakukan meliputi koordinasi lintas sektor, pemantauan situasi, hingga mediasi untuk menjaga kondusivitas selama penanganan karhutla. (Indra Budi Santoso/Rizky Bagus Dhermawan/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677519/kesbangpol-pontianak-antisipasi-konflik-sosial-akibat-karhutla</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/KESBANGPOL-PONTIANAK-ANTISIPASI-KONFLIK-SOSIAL-AKIBAT-KARHUTLA.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>PSEL Serang Raya jadi solusi pengelolaan sampah tiga daerah</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>ANTARA - Fasilitas Pengolahan Sampah menjadi Energi Listrik (PSEL) Serang Raya akan dibangun di TPSA Cilowong, Kota Serang, untuk melayani pengelolaan sampah Kabupaten Serang, Kota Serang, dan Kota Cilegon. Fasilitas berkapasitas 1.161 ton sampah per hari itu diharapkan mampu mengurangi beban tempat pemrosesan akhir sekaligus mengubah sampah menjadi energi listrik. (Susmiatun Hayati/Agha Yuninda Maulana/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677492/psel-serang-raya-jadi-solusi-pengelolaan-sampah-tiga-daerah</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PSEL-SERANG-RAYA-JADI-SOLUSI-PENGELOLAAN-SAMPAH.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Pemkot Ambon salurkan air bersih gratis jika kekeringan terjadi</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Kota Ambon, Maluku, menyiapkan langkah antisipasi untuk menjamin ketersediaan air bersih bagi masyarakat dalam menghadapi potensi musim kemarau panjang akibat fenomena El Nino. Wali kota Ambon Bodewin Wattimena, Senin (3/8), mengatakan, pemerintah melakukan pemetaan wilayah yang rawan lalu mendistribusikan air bersih ke wilayah terdampak kekeringan. (Alfian Sanusi/Rizky Bagus Dhermawan/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677489/pemkot-ambon-salurkan-air-bersih-gratis-jika-kekeringan-terjadi</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-151844.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Razia balap liar, Polres Temanggung sita 106 motor</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepolisian Resor (Polres) Temanggung, Jawa Tengah menyita 106 sepeda motor dalam razia balap liar yang digelar Minggu malam (2/8). Kegiatan razia tersebut digelar sebagai bagian  upaya kepolisian dalam menekan aksi balap liar  di Temanggung.(Firman Eko Handy/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677488/razia-balap-liar-polres-temanggung-sita-106-motor</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_RAZIA-BALAP-LIAR-POLRES-TEMANGGUNG-SITA-106-MOTOR.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Ditjenpas Kaltim gelar CKG bagi 12 ribu warga binaan</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>ANTARA - Program Cek Kesehatan Gratis (CKG) menyasar warga binaan di Lembaga Pemasyarakatan (Lapas) dan Rumah Tahanan (Rutan) di Kalimantan Timur. CKG untuk 12 ribu warga binaan bertujuan mengantisipasi penyebaran risiko penyakit menular di lapas. (Hanifan Ma'ruf/Agha Yuninda Maulana/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677480/ditjenpas-kaltim-gelar-ckg-bagi-12-ribu-warga-binaan</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_DITJENPAS-KALTIM-GELAR-CKG.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Paus Leo XIV prihatin atas situasi krisis migran di Ceuta</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>ANTARA - Paus Leo XIV  menyampaikan keprihatinan atas situasi krisis migran di Enklave, Spanyol, Ceuta.  Saat memimpin doa angelus di Vatikan, Minggu (2/8), Paus berdoa agar terdapat solusi yang membawa perdamaian dan keadilan atas kondisi tersebut. (Ludmila Yusufin Diah Nastiti/Agha Yuninda Maulana/Winanto)</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677384/paus-leo-xiv-prihatin-atas-situasi-krisis-migran-di-ceuta</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PAUS-LEO-XIV-PRIHATIN-ATAS-SITUASI-KRISIS.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Resmi dibuka, Sekolah Rakyat Terintegrasi 2 Kendari tampung 339 siswa</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
           <t>ANTARA - Sekolah Rakyat Terintegrasi 2 Kota Kendari resmi dibuka pada Senin (3/8), yang ditandai dengan Masa Pengenalan Lingkungan Sekolah (MPLS). Sekolah tersebut menampung total sebanyak 339 siswa untuk tahun ajaran 2026/2027, yang terdiri dari jenjang SD, SMP dan SMA.
 (Saharudin/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
+      <c r="F175" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677373/resmi-dibuka-sekolah-rakyat-terintegrasi-2-kendari-tampung-339-siswa</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
+      <c r="G175" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/RESMI-DIBUKA-SEKOLAH-RAKYAT-TERINTEGRASI-2-KENDARI-TAMPUNG-339-SISWA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
+    <row r="176">
+      <c r="A176" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>Dinkop UKM Cilegon targetkan 21 gerai baru KKMP beroperasi September</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr">
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Koperasi Usaha Kecil dan Menengah (Dinkop UKM) Kota Cilegon menargetkan pembangunan  21 gedung gerai Koperasi Kelurahan Merah Putih (KKMP) di wilayah setempat dapat selesai dan beroperasi pada bulan September mendatang. Kepala Dinkop UKM Kota Cilegon, Suhendi pada Senin (3/8) mengatakan saat ini tercatat baru sebanyak 10 gedung yang telah selesai dibangun.
 (Susmiatun Hayati/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
+      <c r="F176" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677301/dinkop-ukm-cilegon-targetkan-21-gerai-baru-kkmp-beroperasi-september</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
+      <c r="G176" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/DINKOP-UKM-CILEGON-TARGETKAN-21-GERAI-BARU-KKMP-BEROPERASI-SEPTEMBER.jpg</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
+    <row r="177">
+      <c r="A177" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B177" t="inlineStr">
         <is>
           <t>Menhub sebut segera evaluasi operator KMP Mutiara Sentosa 2</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr">
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah akan segera mengevaluasi kinerja PT Atosim Lampung Pelayaran yang merupakan operator KMP Mutiara Sentosa II. Hal tersebut disampaikan Menteri Perhubungan Dudy Purwagandhi saat meninjau para korban kebakaran KMP Mutiara Sentosa II di Surabaya, Jawa Timur, Senin (3/8). (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
+      <c r="F177" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677187/menhub-sebut-segera-evaluasi-operator-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
+      <c r="G177" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/MENHUB-SEBUT-SEGERA-EVALUASI-OPERATOR-KMP-MUTIARA-SENTOSA-2.jpg</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
+    <row r="178">
+      <c r="A178" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B178" t="inlineStr">
         <is>
           <t>Keluarga dengan dua balita selamat dari maut KMP Mutiara Sentosa 2</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr">
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
         <is>
           <t>ANTARA - Pasangan suami istri muda, Karhap dan Krisnawati bersama dua anak balitanya sempat terpisah saat terjun ke laut menyelamatkan diri dari kapal penumpang KMP Mutiara Sentosa 2 yang terbakar di perairan sebelah utara Pulau Madura pada Minggu (2/8). Keluarga kecil asal Sidenreng Rappang, Sulawesi Selatan tersebut kembali berkumpul pada Senin (3/8) setelah dievakuasi oleh kapal kargo Meratus Pematang Siantar yang kebetulan melintas di lokasi musibah terjadi. (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
+      <c r="F178" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677141/keluarga-dengan-dua-balita-selamat-dari-maut-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
+      <c r="G178" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KELUARGA-DENGAN-DUA-BALITA-SELAMAT-DARI-MAUT-KMP-MUTIARA-SENTOSA-2.jpg</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
+    <row r="179">
+      <c r="A179" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B179" t="inlineStr">
         <is>
           <t>Lebih dari 100 korban KMP Mutiara Sentosa 2 tiba di Tanjung Perak</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr">
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
         <is>
           <t>ANTARA - Tim pencarian dan pertolongan (SAR) gabungan hingga Senin (3/8), telah mengevakuasi 234 penumpang KMP Mutiara Sentosa 2 yang sebelumnya terbakar di perairan sebelah utara Pulau Madura pada Minggu (2/8). Sebanyak 113 korban di antaranya, kini telah tiba di Pelabuhan Tanjung Perak Surabaya setelah diangkut menggunakan kapal kargo Meratus Pematang Siantar.  (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
+      <c r="F179" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677085/lebih-dari-100-korban-kmp-mutiara-sentosa-2-tiba-di-tanjung-perak</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
+      <c r="G179" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/LEBIH-DARI-100-KORBAN-KMP-MUTIARA-SENTOSA-2-TIBA-DI-TANJUNG-PERAK.jpg</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
+    <row r="180">
+      <c r="A180" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B180" t="inlineStr">
         <is>
           <t>SAR evakuasi penumpang KM Mutiara Santosa 2 yang terbakar</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr">
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
         <is>
           <t>ANTARA - Tim pencarian dan pertolongan (SAR) gabungan telah mengevakuasi sebanyak 236 penumpang KM Mutiara Santosa 2 yang terbakar di perairan sebelah utara Pulau Madura, Minggu malam (2/8). Lima korban di antaranya meninggal dunia.(Hanif Nasrullah/Denno Ramdha Asmara/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
+      <c r="F180" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676992/sar-evakuasi-penumpang-km-mutiara-santosa-2-yang-terbakar</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr">
+      <c r="G180" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SAR-EVAKUASI-PENUMPANG-KM-MUTIARA-SANTOSA-2-YANG-TERBAKAR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
+    <row r="181">
+      <c r="A181" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B181" t="inlineStr">
         <is>
           <t>John Herdman tunggu hasil pemeriksaan Marselino jelang jamu Vietnam</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr">
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
         <is>
           <t>ANTARA - Pelatih Timnas Indonesia John Herdman di Jakarta, Minggu,(2/8), mengatakan kondisi kesehatan dan status gelandang Marselino Ferdinan dalam turnamen baru akan ditentukan setelah mendapat laporan lengkap dari tim medis. Hal itu disampaikan Herdman, usai Marselino kembali absen dalam latihan jelang laga Grup A Piala AFF 2026 melawan Timnas Vietnam pada Senin (2/8). (Anggah/Sandy Arizona/Gracia Simanjuntak)</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
+      <c r="F181" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676945/john-herdman-tunggu-hasil-pemeriksaan-marselino-jelang-jamu-vietnam</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
+      <c r="G181" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_JOHN-HERDMAN-TUNGGU-HASIL-PEMERIKSAAN-MARSELINO-JELANG-JAMU-VIETNAM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
+    <row r="182">
+      <c r="A182" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>John Herdman sebut laga RI Vs Vietnam ujian sangat berat</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr">
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
         <is>
           <t>ANTARA - Pelatih Timnas Indonesia John Herdman di Jakarta, Minggu(2/8), mengaku pertandingan melawan Timnas Vietnam akan menjadi ujian sangat berat bagi skuad Garuda di Grup A Piala AFF 2026 (ASEAN Championship 2026). Menurut Herdman. laga tersebut juga merupakan peluang untuk mengambil alih kendali grup dan memastikan langkah ke babak berikutnya. (Anggah/Sandy Arizona/Gracia Simanjuntak)</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
+      <c r="F182" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676944/john-herdman-sebut-laga-ri-vs-vietnam-ujian-sangat-berat</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
+      <c r="G182" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_JOHN-HERDMAN-SEBUT-LAGA-RI-VS-VIETNAM-UJIAN-SANGAT-BERAT.jpg</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
+    <row r="183">
+      <c r="A183" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="B183" t="inlineStr">
         <is>
           <t>BI targetkan bawa wastra Sulsel ke pasar global</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr">
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
         <is>
           <t>ANTARA - Kantor Perwakilan Bank Indonesia Provinsi Sulawesi Selatan bersama Pemerintah Provinsi Sulsel menyasar penguatan pasar produk kain tradisional (wastra) di tingkat nasional hingga mancanegara melalui "Wastra Heritage Market 2026". Hal itu dikemukakan Kepala Kantor Perwakilan BI Sulsel Rizki Ernadi Wimanda di Makassar, Minggu (2/8). (Suriani Mappong/Sandy Arizona/Gracia Simanjuntak)</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
+      <c r="F183" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676935/bi-targetkan-bawa-wastra-sulsel-ke-pasar-global</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr">
+      <c r="G183" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_BI-TARGETKAN-BAWA-WASTRA-SULSEL-KE-PASAR-GLOBAL.jpg</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
+    <row r="184">
+      <c r="A184" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
+      <c r="B184" t="inlineStr">
         <is>
           <t>Tong Tong Night Market masuk KEN, angkat UMKM dan budaya lokal</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr">
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
         <is>
           <t>ANTARA - ‎Memasuki satu dekade penyelenggaraan, Tong Tong Night Market kembali meramaikan Kota Malang. Festival budaya dan kuliner yang masuk dalam Karisma Event Nusantara (KEN) itu tak hanya menghadirkan nuansa tempo dulu, tetapi juga menjadi ajang promosi puluhan UMKM sekaligus upaya melestarikan budaya lokal. (Achmad Saif Hajarani/Sandy Arizona/Gracia Simanjuntak)</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
+      <c r="F184" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676927/tong-tong-night-market-masuk-ken-angkat-umkm-dan-budaya-lokal</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
+      <c r="G184" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_TONG-TONG-NIGHT-MARKET-MASUK-KEN-ANGKAT-UMKM-DAN-BUDAYA-LOKAL_1.jpg</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
+    <row r="185">
+      <c r="A185" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
+      <c r="B185" t="inlineStr">
         <is>
           <t>Perputaran ekonomi Piala Presiden 2026 tembus Rp70 miliar</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr">
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
         <is>
           <t>ANTARA - Ketua Steering Committee Piala Presiden 2026 Maruarar Sirait menyebut perputaran ekonomi selama babak penyisihan turnamen di Surabaya dan Bandung telah mencapai lebih dari Rp70 miliar. Dampak ekonomi tersebut turut dirasakan pelaku usaha mikro, kecil, dan menengah (UMKM) serta dimanfaatkan untuk menyubsidi harga tiket pertandingan.
 (Hanif Nasrullah/Sandy Arizona/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
+      <c r="F185" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676895/perputaran-ekonomi-piala-presiden-2026-tembus-rp70-miliar</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
+      <c r="G185" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_PERPUTARAN-EKONOMI-PIALA-PRESIDEN-2026-TEMBUS-RP70-MILIAR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
+    <row r="186">
+      <c r="A186" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="B186" t="inlineStr">
         <is>
           <t>Bahlil prioritaskan legalisasi 25 ribu sumur minyak rakyat di Sumsel</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr">
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyebut Sumatera Selatan menjadi salah satu daerah prioritas penerapan kebijakan legalisasi sumur minyak rakyat. Menurutnya, sekitar 25 ribu dari 45 ribu sumur minyak rakyat di Indonesia berada di provinsi tersebut sehingga pemerintah memfokuskan implementasi Peraturan Menteri ESDM Nomor 18 Tahun 2025 di wilayah itu.
 (Winda Tri Agustina/Sandy Arizona/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
+      <c r="F186" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676868/bahlil-prioritaskan-legalisasi-25-ribu-sumur-minyak-rakyat-di-sumsel</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
+      <c r="G186" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_BAHLIL-PRIORITASKAN-LEGALISASI-25-RIBU-SUMUR-MINYAK-RAKYAT-DI-SUMSEL.jpg</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
+    <row r="187">
+      <c r="A187" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="B187" t="inlineStr">
         <is>
           <t>Golkar optimistis tingkatkan perolehan kursi di Sumsel</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr">
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
         <is>
           <t>ANTARA - Ketua Umum Partai Golkar Bahlil Lahadalia meminta seluruh jajaran partai memperkuat konsolidasi organisasi hingga tingkat desa sebagai strategi meningkatkan perolehan kursi legislatif pada Pemilu 2029, termasuk di Sumatera Selatan.
 (Winda Tri Agustina/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
+      <c r="F187" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676837/golkar-optimistis-tingkatkan-perolehan-kursi-di-sumsel</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
+      <c r="G187" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/GOLKAR-OPTIMISTIS-TINGKATKAN-PEROLEHAN-KURSI-DI-SUMSEL.jpg</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
+    <row r="188">
+      <c r="A188" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="B188" t="inlineStr">
         <is>
           <t>Presiden AS Trump tunda serangan baru ke Iran</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr">
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
         <is>
           <t>ANTARA - Presiden Amerika Serikat Donald Trump menunda rencana serangan baru terhadap Iran setelah mengklaim terdapat peluang kesepakatan. Namun, Trump menegaskan opsi militer tetap terbuka jika negosiasi gagal.
 (XINHUA/Arsy Fitriady/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
+      <c r="F188" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676776/presiden-as-trump-tunda-serangan-baru-ke-iran</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
+      <c r="G188" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-AS-TRUMP-TUNDA-SERANGAN-BARU-KE-IRAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
+    <row r="189">
+      <c r="A189" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
+      <c r="B189" t="inlineStr">
         <is>
           <t>TNI AU gelar pameran enam pesawat F-16 di Batam</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr">
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
         <is>
           <t>ANTARA - TNI Angkatan Udara menggelar pameran enam pesawat tempur F-16 yang dapat dikunjungi masyarakat secara gratis dalam kegiatan Batam Open Base di Bandara Internasional Hang Nadim, Batam. Kegiatan ini menjadi bagian dari peringatan Hari Ulang Tahun ke-81 Kemerdekaan Republik Indonesia sekaligus upaya mendekatkan TNI AU kepada masyarakat.
 (Angiela Chantiequ/Jessica Allifia Jaya Hidayat/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
+      <c r="F189" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676735/tni-au-gelar-pameran-enam-pesawat-f-16-di-batam</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr">
+      <c r="G189" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/TNI-AU-GELAR-PAMERAN-ENAM-PESAWAT-F-16-DI-BATAM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
+    <row r="190">
+      <c r="A190" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
+      <c r="B190" t="inlineStr">
         <is>
           <t>TNI kerahkan delapan helikopter salurkan bantuan ke Puncak</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr">
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
         <is>
           <t>ANTARA - Komando Gabungan Wilayah Pertahanan (Kogabwilhan) III mengerahkan delapan helikopter TNI Angkatan Darat dan TNI Angkatan Udara untuk menyalurkan bantuan kemanusiaan ke tiga distrik di Kabupaten Puncak, Papua Tengah, yang terdampak kekeringan berkepanjangan hingga memicu krisis pangan. (Laksa Mahendra/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
+      <c r="F190" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676720/tni-kerahkan-delapan-helikopter-salurkan-bantuan-ke-puncak</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
+      <c r="G190" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/TNI-KERAHKAN-DELAPAN-HELIKOPTER-SALURKAN-BANTUAN-KE-PUNCAK.jpg</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
+    <row r="191">
+      <c r="A191" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
+      <c r="B191" t="inlineStr">
         <is>
           <t>Jakarta Watersport Festival dorong sport tourism di Danau Sunter</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr">
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
         <is>
           <t>ANTARA - Jakarta Watersport Festival 2026 digelar di Danau Sunter, Jakarta Utara, pada 1–2 Agustus. Festival ini menghadirkan kompetisi olahraga air, hiburan, dan bazar UMKM sebagai upaya mendorong sport tourism serta aktivitas ekonomi kreatif di ibu kota. (Nabila Athifa/Setyanka Harviana Putri/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
+      <c r="F191" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676713/jakarta-watersport-festival-dorong-sport-tourism-di-danau-sunter</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr">
+      <c r="G191" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/JAKARTA-WATERSPORT-FESTIVAL-DORONG-SPORT-TOURISM-DI-DANAU-SUNTER.jpg</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
+    <row r="192">
+      <c r="A192" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
+      <c r="B192" t="inlineStr">
         <is>
           <t>Ledakan restoran di Moskow tewaskan tiga orang</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr">
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
         <is>
           <t>ANTARA - Tiga orang tewas dan sedikitnya 21 lainnya luka-luka setelah ledakan alat peledak rakitan terjadi di sebuah restoran di kawasan Kudrinskaya Square, pusat Kota Moskow, Rusia, Sabtu (1/8). Menurut Komite Antiterorisme Nasional Rusia, ledakan terjadi ketika seorang perempuan berupaya membawa alat peledak ke dalam restoran, namun dihentikan petugas keamanan. Penyelidikan terkait motif serangan masih berlangsung. (Arsy Fitriady/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
+      <c r="F192" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676660/ledakan-restoran-di-moskow-tewaskan-tiga-orang</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
+      <c r="G192" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/LEDAKAN-RESTORAN-DI-MOSKOW-TEWASKAN-TIGA-ORANG_1.jpg</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
+    <row r="193">
+      <c r="A193" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="B193" t="inlineStr">
         <is>
           <t>DKPPP Temanggung edukasi warga cegah zoonosis dari hewan piaraan</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr">
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Ketahanan Pangan, Pertanian, dan Perikanan (DKPPP) Kabupaten Temanggung bersama komunitas pecinta hewan mengedukasi masyarakat tentang pentingnya menjaga kesehatan hewan piaraan untuk mencegah zoonosis atau penyakit yang dapat menular dari hewan ke manusia. Edukasi meliputi pemberian nutrisi, vaksinasi, kebersihan, dan pemeriksaan kesehatan hewan secara berkala. (Firman Eko Handy/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr">
+      <c r="F193" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676647/dkppp-temanggung-edukasi-warga-cegah-zoonosis-dari-hewan-piaraan</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
+      <c r="G193" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/DKPPP-TEMANGGUNG-EDUKASI-WARGA-CEGAH-ZOONOSIS-DARI-HEWAN-PIARAAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
+    <row r="194">
+      <c r="A194" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="B194" t="inlineStr">
         <is>
           <t>BP Batam siapkan Sekolah Terintegrasi Merah Putih di Rempang</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr">
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pengusahaan (BP) Batam menyiapkan pembangunan Sekolah Terintegrasi Merah Putih di Rempang, Kepulauan Riau, sebagai sekolah gratis bagi siswa berprestasi. Sekolah yang dibangun di atas lahan seluas 18 hektare itu akan melayani jenjang sekolah dasar hingga sekolah menengah atas dengan fasilitas pendidikan dan olahraga yang lengkap. (Angiela Chantiequ/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
+      <c r="F194" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676644/bp-batam-siapkan-sekolah-terintegrasi-merah-putih-di-rempang</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
+      <c r="G194" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/BP-BATAM-SIAPKAN-SEKOLAH-TERINTEGRASI-MERAH-PUTIH-DI-REMPANG.jpg</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
+    <row r="195">
+      <c r="A195" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B195" t="inlineStr">
         <is>
           <t>Aldila Sutjiadi juarai WTA 500 Mubadala DC Open 2026</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
         <is>
           <t>ANTARA - Petenis ganda putri Indonesia Aldila Sutjiadi menjuarai nomor ganda Women's Tennis Association (WTA) 500 Mubadala DC Open 2026 di Washington, Amerika Serikat. Berpasangan dengan petenis Selandia Baru Erin Routliffe, Aldila mengalahkan Andreja Klepac dari Slovenia dan Makoto Ninomiya dari Jepang dua set langsung 6-4, 6-1 pada partai final. Gelar tersebut menjadi trofi WTA kedelapan dalam karier Aldila di nomor ganda sekaligus gelar kedua bersama Routliffe pada musim 2026.
 (Arsy Fitriady/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
+      <c r="F195" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676629/aldila-sutjiadi-juarai-wta-500-mubadala-dc-open-2026</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
+      <c r="G195" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/ALDILA-SUTJIADI-JUARAI-WTA-500-MUBADALA-DC-OPEN-2026.jpg</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
+    <row r="196">
+      <c r="A196" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="B196" t="inlineStr">
         <is>
           <t>KM Mutiara Sentosa 2 Terbakar Saat Berlayar ke Makassar</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr">
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
         <is>
           <t>ANTARA - Kapal Motor (KM) Mutiara Sentosa 2 terbakar di perairan utara Pulau Madura saat berlayar dari Pelabuhan Tanjung Perak Surabaya menuju Makassar, Minggu (2/8). Kapal tersebut mengangkut sekitar 250 orang. Tim SAR gabungan masih melakukan evakuasi penumpang, sementara penyebab kebakaran masih dalam penyelidikan. (Hanif Nasrullah/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
+      <c r="F196" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676617/km-mutiara-sentosa-2-terbakar-saat-berlayar-ke-makassar</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
+      <c r="G196" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KM-MUTIARA-SENTOSA-2-TERBAKAR-SAAT-BERLAYAR-KE-MAKASSAR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
+    <row r="197">
+      <c r="A197" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B197" t="inlineStr">
         <is>
           <t>BI dan Pemkot Kendari Perkuat Digitalisasi UMKM</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr">
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
         <is>
           <t>ANTARA - Kantor Perwakilan Bank Indonesia Sulawesi Tenggara bersama Pemerintah Kota Kendari menggelar Festival Kuliner Sultra Maimo 2026 untuk memperkuat digitalisasi usaha mikro, kecil, dan menengah atau UMKM. Festival yang berlangsung pada 2 hingga 9 Agustus itu juga mendorong perluasan transaksi non-tunai berbasis QRIS. (Saharudin/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
+      <c r="F197" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676607/bi-dan-pemkot-kendari-perkuat-digitalisasi-umkm</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
+      <c r="G197" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/BI-DAN-PEMKOT-KENDARI-PERKUAT-DIGITALISASI-UMKM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
+    <row r="198">
+      <c r="A198" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B198" t="inlineStr">
         <is>
           <t>El Nino menguat, negara fokus jaga ketersediaan air &amp; tangani karhutla</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr">
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
         <is>
           <t>ANTARA - Gelombang panas sebagai akibat El Nino mulai dirasakan dampaknya di sejumlah belahan dunia. Kebakaran hutan dan lahan atau karhutla, juga mulai terjadi di dalam negeri, seperti di Pulau Sumatera dan Kalimantan.Selain kebakaran, bencana ekologi yang terjadi ialah kekeringan. Beberapa daerah di Pulau Jawa seperti Temanggung, Sukoharjo, Lumajang, Banten, lalu daerah luar Jawa seperti Nusa Tenggara Barat dan Timur, hingga Bangka Belitung mulai mengalami krisis air bersih.Presiden pun memanggil sejumlah kepala kementerian dan lembaga terkait, untuk memberi pemaparan dan masukan guna meredam dampak El Nino.Lalu bagaimana sikap antisipatif yang disiapkan pemerintah pada musim kemarau dan el nino tahun ini? Selengkapnya dalam PerANTARA! (Roy Rosa Bachtiar/Suci Nurhaliza/Gunawan Wibisono/Rizky Bagus Dhermawan/Farah Khadija)</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
+      <c r="F198" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676540/el-nino-menguat-negara-fokus-jaga-ketersediaan-air-tangani-karhutla</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
+      <c r="G198" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/DF.jpg</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
+    <row r="199">
+      <c r="A199" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B199" t="inlineStr">
         <is>
           <t>Padang Padang Cup Bali jadi ajang peselancar Nasional unjuk kehebatan</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr">
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
         <is>
           <t>ANTARA - Kompetisi selancar ombak Internasional Rip Curl Cup Padang Padang kembali digelar dan berlangsung pada 1-31 Agustus 2026, di Pantai Padang Padang, Labuan Sait Pecatu, Kuta Selatan, Bali. Ajang ini menjadi ruang bagi peselancar Nasional menunjukkan kehebatan mereka bersaing dengan peselancar Internasional. (Rita Laura/Sandy Arizona/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr">
+      <c r="F199" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676257/padang-padang-cup-bali-jadi-ajang-peselancar-nasional-unjuk-kehebatan</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr">
+      <c r="G199" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_PADANG-PADANG-CUP-BALI-JADI-AJANG-PESELANCAR-NASIONAL-UNJUK-KEHEBATAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
+    <row r="200">
+      <c r="A200" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B200" t="inlineStr">
         <is>
           <t>Bekuk Port FC, Persebaya gandeng Persija ke semifinal</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr">
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
         <is>
           <t>ANTARA - Persebaya membekuk Port FC 2 - 1 di laga terakhir Grup B turnamen sepak Piala Presiden 2026. Dengan hasil ini Persija lolos ke babak semifinal bersama Persebaya sebagai wakil Grup B. (Hanif Nasrullah/Sandy Arizona/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
+      <c r="F200" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676252/bekuk-port-fc-persebaya-gandeng-persija-ke-semifinal</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr">
+      <c r="G200" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_BEKUK-PORT-FC-PERSEBAYA-GANDENG-PERSIJA-KE-SEMIFINAL.jpg</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
+    <row r="201">
+      <c r="A201" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="B201" t="inlineStr">
         <is>
           <t>Aston Villa unggul 3-1 dari Indonesia All Stars dalam tur pramusim</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr">
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
         <is>
           <t>ANTARA - Tim Indonesia All Stars, harus mengakui keunggulan atas Aston Villa dengan skor 3-1, saat laga Friendly Match di Stadion Utama Gelora Bung Karno (SUGBK) Senayan, Jakarta, pada Sabtu (1/8). Penjaga Gawang Aston Villa, James Wright, saat ditemui media di GBK mengapresiasi para pemain Indonesia All Stars, karena dinilai memiliki kualitas yang baik. (Ryan Rahman/Sandy Arizona/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr">
+      <c r="F201" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676239/aston-villa-unggul-3-1-dari-indonesia-all-stars-dalam-tur-pramusim</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
+      <c r="G201" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_ASTON-VILLA-UNGGUL-3-1-DARI-INDONESIA-ALL-STARS-DALAM-TUR-PRAMUSIM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
+    <row r="202">
+      <c r="A202" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="B202" t="inlineStr">
         <is>
           <t>Joko Widodo dinobatkan sebagai sesepuh oleh sembilan Raja Timor</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr">
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
         <is>
           <t>ANTARA - Ribuan warga memadati kawasan Pantai Lahi Lai Bissi Kopan (LLBK) Kota Kupang, Nusa Tenggara Timur, untuk menyaksikan Karnaval Budaya yang dihadiri Presiden ke-7 Republik Indonesia, Joko Widodo. Dalam prosesi adat yang menjadi puncak acara, Joko Widodo dinobatkan sebagai sesepuh atau saudara oleh sembilan raja dari kerajaan-kerajaan di Pulau Timor sebagai bentuk penghormatan terhadap nilai persaudaraan dan budaya masyarakat Timor. (Johanes Viandinando/Sandy Arizona/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr">
+      <c r="F202" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676205/joko-widodo-dinobatkan-sebagai-sesepuh-oleh-sembilan-raja-timor</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr">
+      <c r="G202" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_JOKO-WIDODO-DINOBATKAN-SEBAGAI-SESEPUH-OLEH-SEMBILAN-RAJA-TIMOR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
+    <row r="203">
+      <c r="A203" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="B203" t="inlineStr">
         <is>
           <t>Menag: Indeks kerukunan umat beragama RI jadi 77,89 persen di 2025</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr">
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Agama Nasaruddin Umar menyebut indeks kerukunan umat beragama naik menjadi 77,89 persen pada tahun 2025, dari sebelumnya, yakni 76,47 persen pada tahun 2024. Hal tersebut disampaikan oleh Menag saat mengahdiri agenda Zikir dan Doa Kebangsaan "Indonesia Berdaulat, Adil dan Makmur" di Lapangan Silang Monas, Jakarta, Sabtu (1/8).
 (Afra Augesti/Nico Anggriawan/Sandy Arizona/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
+      <c r="F203" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676188/menag-indeks-kerukunan-umat-beragama-ri-jadi-7789-persen-di-2025</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
+      <c r="G203" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_MENAG-INDEKS-KERUKUNAN-UMAT-BERAGAMA-RI-JADI-77-89-PERSEN-DI-2025.jpg</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
+    <row r="204">
+      <c r="A204" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B204" t="inlineStr">
         <is>
           <t>KKP bantu pelaku usaha perikanan terdampak bencana di Sumbar</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr">
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
         <is>
           <t>ANTARA - Kementerian Kelautan dan Perikanan (KKP) bersama Tim Satuan Tugas Percepatan Rehabilitasi dan Rekonstruksi (PRR) Provinsi Sumatera Barat, mempercepat dan memastikan operasionalisasi budi daya, nelayan serta pengolahan ikan segera berjalan pascabencana hidrometeorologi yang terjadi akhir November tahun lalu. Untuk itu, KKP memberikan bantuan awal berupa bibit ikan dan pakan, dan ekskavator, kepada pelaku usaha perikanan yang terdampak bencana hidrometeorologis di Kota Padang, Kabupaten Padang Pariaman, Kabupaten Solok dan Kabupaten Agam.
 (Melani Friati/Sandy Arizona/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
+      <c r="F204" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676172/kkp-bantu-pelaku-usaha-perikanan-terdampak-bencana-di-sumbar</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
+      <c r="G204" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_KKP-BANTU-PELAKU-USAHA-PERIKANAN-TERDAMPAK-BENCANA-DI-SUMBAR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
+    <row r="205">
+      <c r="A205" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B205" t="inlineStr">
         <is>
           <t>INZS 2026 perkuat komitmen Indonesia hadapi krisis iklim</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr">
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah Indonesia terus mempercepat transisi energi sebagai bagian dari upaya mengatasi perubahan iklim melalui berbagai proyek yang mulai direalisasikan. Komitmen tersebut mengemuka dalam Indonesia Net Zero Summit (INZS) 2026 di Balai Kartini, Jakarta, Sabtu (1/8). Pendiri Foreign Policy Community of Indonesia (FPCI), Dino Patti Djalal, menegaskan bahwa penanganan perubahan iklim harus menjadi prioritas karena dampaknya menyentuh hampir seluruh aspek kehidupan manusia.
 (Irfan Hardiansah/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr">
+      <c r="F205" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676087/inzs-2026-perkuat-komitmen-indonesia-hadapi-krisis-iklim</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
+      <c r="G205" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/INZS-2026-PERKUAT-KOMITMEN-INDONESIA-HADAPI-KRISIS-IKLIM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
+    <row r="206">
+      <c r="A206" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B206" t="inlineStr">
         <is>
           <t>Kemeriahan menyambut bulan kemerdekaan Indonesia di Malaysia</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr">
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
         <is>
           <t>ANTARA - Kegembiraan menyambut bulan kemerdekaan Republik Indonesia turut dirasakan para warga negara Indonesia yang berada di negeri jiran Malaysia. WNI dengan penuh antusias mengikuti berbagai perlombaan yang diselenggarakan Kedutaan Besar Republik Indonesia (KBRI) di Kuala Lumpur, Malaysia, Sabtu (1/8).
 (Rangga Pandu Asmara Jingga/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
+      <c r="F206" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676063/kemeriahan-menyambut-bulan-kemerdekaan-indonesia-di-malaysia</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr">
+      <c r="G206" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KEMERIAHAN-MENYAMBUT-BULAN-KEMERDEKAAN-INDONESIA-DI-MALAYSIA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
+    <row r="207">
+      <c r="A207" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="B207" t="inlineStr">
         <is>
           <t>Cari Bibit unggul, Bogor gelar sirkuit panjat tebing anak dan remaja</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr">
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
         <is>
           <t>ANTARA - Federasi Panjat Tebing Indonesia (FPTI) Kota Bogor menggelar Sirkuit Panjat Tebing se-Kota Bogor sebagai ajang pencarian bibit atlet muda, Sabtu (1/8). Dengan diikuti 100 peserta anak-anak dan remaja, kegiatan itu mempertandingkan kategori lead dan speed untuk kelompok umur under 11, under 13, dan under 19.
 (Fadzar Ilham Pangestu/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr">
+      <c r="F207" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676021/cari-bibit-unggul-bogor-gelar-sirkuit-panjat-tebing-anak-dan-remaja</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
+      <c r="G207" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/CARI-BIBIT-UNGGUL-BOGOR-GELAR-SIRKUIT-PANJAT-TEBING-ANAK-DAN-REMAJA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
+    <row r="208">
+      <c r="A208" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B208" t="inlineStr">
         <is>
           <t>Karhutla Tumbang Nusa meluas, 104 hektar gambut terbakar</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr">
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
         <is>
           <t>ANTARA - Kebakaran hutan dan lahan (karhutla) di Desa Tumbang Nusa, Kecamatan Jabiren Raya, Kabupaten Pulang Pisau, Kalimantan Tengah, telah menghanguskan sekitar 104 hektare lahan gambut, Sabtu (1/8). Peristiwa tersebut memicu operasi penanganan terpadu yang melibatkan sekitar 416 personel gabungan melalui jalur darat, serta didukung dua unit helikopter water bombing untuk mempercepat pemadaman yang jauh dari tim darat. 
 (Redianto Tumon Sp/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
+      <c r="F208" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676013/karhutla-tumbang-nusa-meluas-104-hektar-gambut-terbakar</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
+      <c r="G208" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KARHUTLA-TUMBANG-NUSA-MELUAS-104-HEKTAR-GAMBUT-TERBAKAR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
+    <row r="209">
+      <c r="A209" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B209" t="inlineStr">
         <is>
           <t>54 Atlet menembak Kalsel, bertanding pada Kejuaraan Wali Kota Cup</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr">
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah Kota Banjarmasin bersama Perbakin menggelar kejuaraan menembak Wali Kota Cup 2026. Kejuaraan diikuti oleh 54 atlet dari berbagai daerah di Kalsel sebagai wadah seleksi dan persiapan atlet kalimantan selatan menuju Pra-PON.
 (Latif Thohir/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr">
+      <c r="F209" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675995/54-atlet-menembak-kalsel-bertanding-pada-kejuaraan-wali-kota-cup</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr">
+      <c r="G209" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/54-ATLET-MENEMBAK-KALSEL-BERTANDING-PADA-KEJUARAAN-WALI-KOTA-CUP.jpg</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
+    <row r="210">
+      <c r="A210" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
+      <c r="B210" t="inlineStr">
         <is>
           <t>Polda Riau kirim Tim Ekspedisi Merah Putih Presisi ke 17 desa 3T</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr">
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
         <is>
           <t>ANTARA - Kapolda Riau Irjen Pol Herry Heryawan melepas Tim Ekspedisi Merah Putih Presisi Polda Riau yang akan bertugas di 17 desa wilayah tertinggal, terdepan, dan terluar atau 3T, Sabtu (1/8). Ekspedisi yang berlangsung hingga 17 Agustus mendatang itu membawa berbagai program sosial, lingkungan, dan penguatan kebangsaan bagi masyarakat pesisir serta wilayah terluar di Provinsi Riau.
 (Farah Khadija/Annisa Firdausi/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr">
+      <c r="F210" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675964/polda-riau-kirim-tim-ekspedisi-merah-putih-presisi-ke-17-desa-3t</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr">
+      <c r="G210" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/POLDA-RIAU-KIRIM-TIM-EKSPEDISI-MERAH-PUTIH-PRESISI-KE-17-DESA-3T.jpg</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
+    <row r="211">
+      <c r="A211" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
+      <c r="B211" t="inlineStr">
         <is>
           <t>Hadapi El Nino, pemerintah tingkatkan mitigasi karhutla</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr">
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah memperkuat langkah antisipasi menghadapi potensi el nino yang diperkirakan meningkatkan risiko kebakaran hutan dan lahan. Menteri Lingkungan Hidup, Muhammad Jumhur Hidayat usai membuka Indonesia Net Zero Summit (INZS) 2026 yang diselenggarakan di Balai Kartini, Jakarta, pada Sabtu (1/8) menyebutkan, pihaknya menekan potensi karhutla sejak dini, salah satunya dengan membangun kanal blocking.
 (Irfan Hardiansah/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr">
+      <c r="F211" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675936/hadapi-el-nino-pemerintah-tingkatkan-mitigasi-karhutla</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr">
+      <c r="G211" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/HADAPI-EL-NINO-PEMERINTAH-TINGKATKAN-MITIGASI-KARHUTLA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
+    <row r="212">
+      <c r="A212" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
+      <c r="B212" t="inlineStr">
         <is>
           <t>Mensos resmikan Sekolah Rakyat Terintegrasi 1 Sukoharjo</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr">
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Sosial Republik Indonesia Saifullah Yusuf membuka pelaksanaan Masa Pengenalan Lingkungan Sekolah (MPLS) di Sekolah Rakyat Terintegrasi (SRT) 1 Kabupaten Sukoharjo, Sabtu (1/8). Mensos menyebut meski proses pembangunan fisik belum sepenuhnya rampung, pihaknya memastikan kegiatan belajar mengajar sudah dapat dilaksanakan karena progres pembangunan telah mencapai sekitar 98 persen.(Denik Apriyani/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr">
+      <c r="F212" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675924/mensos-resmikan-sekolah-rakyat-terintegrasi-1-sukoharjo</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr">
+      <c r="G212" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/MENSOS-RESMIKAN-SEKOLAH-RAKYAT-TERINTEGRASI-1-SUKOHARJO.jpg</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
+    <row r="213">
+      <c r="A213" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
+      <c r="B213" t="inlineStr">
         <is>
           <t>Lanud Sjamsudin Noor gelar Bakti Sosial Hari Bakti TNI AU ke-79</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr">
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
         <is>
           <t>ANTARA - Ratusan warga di Banjarbaru, Kalimantan Selatan, antusias mengikuti kegiatan bakti sosial yang diselenggarakan oleh Pangkalan Udara (Lanud) Sjamsudin Noor pada Sabtu (1/8). Kegiatan ini dilaksanakan sebagai rangkaian peringatan Hari Bhakti TNI Angkatan Udara Ke-79
 (Latif Thohir/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr">
+      <c r="F213" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675872/lanud-sjamsudin-noor-gelar-bakti-sosial-hari-bakti-tni-au-ke-79</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr">
+      <c r="G213" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/LANUD-SJAMSUDIN-NOOR-GELAR-BAKTI-SOSIAL-HARI-BAKTI-TNI-AU-KE-79.jpg</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
+    <row r="214">
+      <c r="A214" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>Prancis perketat pemeriksaan produk tani, lawan praktik francization</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr">
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
         <is>
           <t>ANTARA - Prancis memperketat pemeriksaan terhadap asal-usul produk pertanian guna memberantas praktik "francization", yaitu pelabelan ulang produk impor agar tampak sebagai hasil produksi dalam negeri. Langkah ini diambil untuk melindungi konsumen dan produsen lokal, dengan pelanggar terancam denda hingga 300.000 euro dan hukuman penjara.(XINHUA/ Nabila Anisya Charisty/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr">
+      <c r="F214" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675865/prancis-perketat-pemeriksaan-produk-tani-lawan-praktik-francization</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr">
+      <c r="G214" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PRANCIS-PERKETAT-PEMERIKSAAN-PRODUK-TANI-LAWAN-PRAKTIK-FRANCIZATION.jpg</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
+    <row r="215">
+      <c r="A215" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="B215" t="inlineStr">
         <is>
           <t>KM. Prince Soya terbakar saat bersandar di Pelabuhan Samarinda</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr">
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
         <is>
           <t>ANTARA - Kapal Motor (KM) Prince Soya terbakar pada Sabtu (1/8) saat bersandar di Pelabuhan Samarinda, Kalimantan Timur. Kapal penumpang yang biasa melayani rute Samarinda - Pare-Pare, Sulawesi Selatan itu terbakar di bagian dek sebelah kanan yang diduga bersumber dari tangki berisi pelumas mesin. (Hanifan Ma'ruf/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr">
+      <c r="F215" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675853/km-prince-soya-terbakar-saat-bersandar-di-pelabuhan-samarinda</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr">
+      <c r="G215" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KM.PRINCE-SOYA-TERBAKAR-SAAT-BERSANDAR-DI-PELABUHAN-SAMARINDA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
+    <row r="216">
+      <c r="A216" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="B216" t="inlineStr">
         <is>
           <t>St. Petersburg luncurkan festival sepeda motor untuk pertama kalinya</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr">
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
         <is>
           <t>ANTARA - Saint Petersburg Motor Festival resmi dibuka, Jumat (31/7) selama tiga hari berturut-turut dalam pembukaan perdananya. Acara tersebut digelar untuk menghibur para penikmat sepeda motor, musik, serta pengunjung umum lainnya.(XINHUA/ Nabila Anisya Charisty/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr">
+      <c r="F216" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5675828/st-petersburg-luncurkan-festival-sepeda-motor-untuk-pertama-kalinya</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr">
+      <c r="G216" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/ST.PETERSBURG-LUNCURKAN-FESTIVAL-SEPEDA-MOTOR-UNTUK-PERTAMA-KALINYA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>KPHL Batam dan Akar Bhumi Indonesia berkolaborasi lestarikan bakau</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>ANTARA - Kesatuan Pengelolaan Hutan Lindung (KPHL) Kota Batam bersama Lembaga Swadaya Masyarakat (LSM) Akar Bhumi Indonesia menanam 450 bibit bakau di Batam, Kepulauan Riau, Sabtu (1/8). Penanaman bibit bakau tersebut dilakukan untuk memastikan daerah pesisir Kota Batam terlindungi di tengah perubahan iklim, sekaligus memperimgati Hari Mangrove Sedunia 2026.(Angiela Chantique/ Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5675804/kphl-batam-dan-akar-bhumi-indonesia-berkolaborasi-lestarikan-bakau</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/KPHL-BATAM-DAN-AKAR-BHUMI-INDONESIA-BERKOLABORASI-LESTARIKAN-BAKAU.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Ribuan warga padati Jalan El Tari saat kunjungan Jokowi di Kupang, NTT</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:00:01 +0700</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>ANTARA - Ribuan warga Kota Kupang dan sekitarnya memadati kawasan "Car Free Day" di Jalan El Tari, Kota Kupang, Nusa Tenggara Timur, Sabtu (1/8),  untuk menyambut kunjungan Joko Widodo. Dalam suasana penuh antusias, masyarakat bersalaman dan meminta swafoto bersama sosok Presiden ke-7 Republik Indonesia tersebut.
-(Johanes Viandinando/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5675784/ribuan-warga-padati-jalan-el-tari-saat-kunjungan-jokowi-di-kupang-ntt</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/RIBUAN-WARGA-PADATI-JALAN-EL-TARI-SAAT-KUNJUNGAN-JOKOWI-DI-KUPANG-NTT.jpg</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G195"/>
+  <autoFilter ref="A1:G216"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_antara_2026-08-03.xlsx
+++ b/data/berita_antara_2026-08-03.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$295</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,10 +419,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G216"/>
+  <dimension ref="A1:G295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -3311,33 +3311,33 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ekonomi-finansial, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Menjaga pintu air perekonomian Indonesia</t>
+          <t>Prabowo terima laporan Bahlil soal program ketahanan energi</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:04:40 +0700</t>
+          <t>Mon, 03 Aug 2026 16:02:25 +0700</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bayangkan perekonomian Indonesia sebagai sebuah bendungan raksasa yang mengairi hamparan persawahan. Air yang mengalir ...</t>
+          <t>Presiden Prabowo Subianto menerima laporan terbaru dari Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil ...</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677565/menjaga-pintu-air-perekonomian-indonesia</t>
+          <t>https://www.antaranews.com/berita/5677561/prabowo-terima-laporan-bahlil-soal-program-ketahanan-energi</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/06/peringati-hari-bank-indonesia-doku-perkuat-ekosistem-pembayaran-2817675.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_5125.jpeg</t>
         </is>
       </c>
     </row>
@@ -3349,28 +3349,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Prabowo terima laporan Bahlil soal program ketahanan energi</t>
+          <t>Menlu Iran sebut pembicaraan soal Selat Hormuz dengan Oman masuki tahap akhir</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:02:25 +0700</t>
+          <t>Mon, 03 Aug 2026 16:01:55 +0700</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Presiden Prabowo Subianto menerima laporan terbaru dari Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil ...</t>
+          <t>Menteri Luar Negeri Iran Abbas Araghchi  mengatakan pembicaraan soal Selat Hormuz dengan Oman masuki tahap ...</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677561/prabowo-terima-laporan-bahlil-soal-program-ketahanan-energi</t>
+          <t>https://www.antaranews.com/berita/5677557/menlu-iran-sebut-pembicaraan-soal-selat-hormuz-dengan-oman-masuki-tahap-akhir</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_5125.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/HormuzXinhuaWangQiang_aa.jpg</t>
         </is>
       </c>
     </row>
@@ -3382,28 +3382,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Menlu Iran sebut pembicaraan soal Selat Hormuz dengan Oman masuki tahap akhir</t>
+          <t>Wamendiktisaintek dorong kampus di Riau dan Kepri bangun konsorsium</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:01:55 +0700</t>
+          <t>Mon, 03 Aug 2026 16:01:51 +0700</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Menteri Luar Negeri Iran Abbas Araghchi  mengatakan pembicaraan soal Selat Hormuz dengan Oman masuki tahap ...</t>
+          <t>Wakil Menteri Pendidikan Tinggi, Sains, dan Teknologi (Wamendiktisaintek) Fauzan mendorong perguruan tinggi di Provinsi ...</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677557/menlu-iran-sebut-pembicaraan-soal-selat-hormuz-dengan-oman-masuki-tahap-akhir</t>
+          <t>https://www.antaranews.com/berita/5677555/wamendiktisaintek-dorong-kampus-di-riau-dan-kepri-bangun-konsorsium</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/HormuzXinhuaWangQiang_aa.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/18/1000428031.jpg</t>
         </is>
       </c>
     </row>
@@ -3415,28 +3415,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Wamendiktisaintek dorong kampus di Riau dan Kepri bangun konsorsium</t>
+          <t>Partai Buruh Brasil calonkan Lula da Silva untuk masa jabatan keempat</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:01:51 +0700</t>
+          <t>Mon, 03 Aug 2026 16:01:22 +0700</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Wakil Menteri Pendidikan Tinggi, Sains, dan Teknologi (Wamendiktisaintek) Fauzan mendorong perguruan tinggi di Provinsi ...</t>
+          <t>ANTARA - Partai Buruh di Brasil pada Minggu (2/8) waktu setempat, resmi mencalonkan petahana Luiz Inacio Lula da Silva ...</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677555/wamendiktisaintek-dorong-kampus-di-riau-dan-kepri-bangun-konsorsium</t>
+          <t>https://www.antaranews.com/video/5677541/partai-buruh-brasil-calonkan-lula-da-silva-untuk-masa-jabatan-keempat</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/18/1000428031.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-03-154005.jpg</t>
         </is>
       </c>
     </row>
@@ -3448,28 +3448,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Partai Buruh Brasil calonkan Lula da Silva untuk masa jabatan keempat</t>
+          <t>Program konservasi Pulau Sabira PLN raih penghargaan nasional</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:01:22 +0700</t>
+          <t>Mon, 03 Aug 2026 16:00:04 +0700</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ANTARA - Partai Buruh di Brasil pada Minggu (2/8) waktu setempat, resmi mencalonkan petahana Luiz Inacio Lula da Silva ...</t>
+          <t>PT PLN (Persero) Unit Induk Distribusi (UID) Jakarta Raya meraih penghargaan "Predikat Platinum Alignment" ...</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5677541/partai-buruh-brasil-calonkan-lula-da-silva-untuk-masa-jabatan-keempat</t>
+          <t>https://www.antaranews.com/berita/5677551/program-konservasi-pulau-sabira-pln-raih-penghargaan-nasional</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-03-154005.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/e9219a6c-ccd6-473e-bf06-a7dd465568bd.jpeg</t>
         </is>
       </c>
     </row>
@@ -3481,28 +3481,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Program konservasi Pulau Sabira PLN raih penghargaan nasional</t>
+          <t>Pemkot Ambon salurkan air bersih gratis jika kekeringan terjadi</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:00:04 +0700</t>
+          <t>Mon, 03 Aug 2026 15:59:59 +0700</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>PT PLN (Persero) Unit Induk Distribusi (UID) Jakarta Raya meraih penghargaan "Predikat Platinum Alignment" ...</t>
+          <t>ANTARA - Pemerintah Kota Ambon, Maluku, menyiapkan langkah antisipasi untuk menjamin ketersediaan air bersih bagi ...</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677551/program-konservasi-pulau-sabira-pln-raih-penghargaan-nasional</t>
+          <t>https://www.antaranews.com/video/5677489/pemkot-ambon-salurkan-air-bersih-gratis-jika-kekeringan-terjadi</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/e9219a6c-ccd6-473e-bf06-a7dd465568bd.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-03-151844.jpg</t>
         </is>
       </c>
     </row>
@@ -3514,28 +3514,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Pemkot Ambon salurkan air bersih gratis jika kekeringan terjadi</t>
+          <t>Razia balap liar, Polres Temanggung sita 106 motor</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:59:59 +0700</t>
+          <t>Mon, 03 Aug 2026 15:58:54 +0700</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ANTARA - Pemerintah Kota Ambon, Maluku, menyiapkan langkah antisipasi untuk menjamin ketersediaan air bersih bagi ...</t>
+          <t>ANTARA - Kepolisian Resor (Polres) Temanggung, Jawa Tengah menyita 106 sepeda motor dalam razia balap liar yang digelar ...</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5677489/pemkot-ambon-salurkan-air-bersih-gratis-jika-kekeringan-terjadi</t>
+          <t>https://www.antaranews.com/video/5677488/razia-balap-liar-polres-temanggung-sita-106-motor</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-03-151844.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_RAZIA-BALAP-LIAR-POLRES-TEMANGGUNG-SITA-106-MOTOR.jpg</t>
         </is>
       </c>
     </row>
@@ -3547,28 +3547,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Razia balap liar, Polres Temanggung sita 106 motor</t>
+          <t>Pemain muda Barcelona incar tempat di tim utama 2026/2027</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:58:54 +0700</t>
+          <t>Mon, 03 Aug 2026 15:57:56 +0700</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ANTARA - Kepolisian Resor (Polres) Temanggung, Jawa Tengah menyita 106 sepeda motor dalam razia balap liar yang digelar ...</t>
+          <t>Para pemain muda Barcelona, khususnya yang kini memperkuat Barcelona Atletic (Barcelona B), mengincar tempat di tim ...</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5677488/razia-balap-liar-polres-temanggung-sita-106-motor</t>
+          <t>https://www.antaranews.com/berita/5677547/pemain-muda-barcelona-incar-tempat-di-tim-utama-2026-2027</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_RAZIA-BALAP-LIAR-POLRES-TEMANGGUNG-SITA-106-MOTOR.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_154443.jpg</t>
         </is>
       </c>
     </row>
@@ -3580,28 +3580,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Pemain muda Barcelona incar tempat di tim utama 2026/2027</t>
+          <t>HYBE siapkan debut girl group Tuide</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:57:56 +0700</t>
+          <t>Mon, 03 Aug 2026 15:57:13 +0700</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Para pemain muda Barcelona, khususnya yang kini memperkuat Barcelona Atletic (Barcelona B), mengincar tempat di tim ...</t>
+          <t>Perusahaan hiburan Korea Selatan, HYBE melalui label naungannya ABD tengah mempersiapkan debut girl group Kpop bernama ...</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677547/pemain-muda-barcelona-incar-tempat-di-tim-utama-2026-2027</t>
+          <t>https://www.antaranews.com/berita/5677544/hybe-siapkan-debut-girl-group-tuide</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_154443.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/644817de-49b2-42cd-92a5-0d0a14d911ce.jpeg</t>
         </is>
       </c>
     </row>
@@ -3613,28 +3613,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>HYBE siapkan debut girl group Tuide</t>
+          <t>Pemkot Jakut edukasi pelajar tentang teknik pertanian di perkotaan</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:57:13 +0700</t>
+          <t>Mon, 03 Aug 2026 15:52:39 +0700</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Perusahaan hiburan Korea Selatan, HYBE melalui label naungannya ABD tengah mempersiapkan debut girl group Kpop bernama ...</t>
+          <t>Suku Dinas Ketahanan Pangan, Kelautan dan Pertanian (KPKP) Jakarta Utara mengedukasi puluhan pelajar dari enam sekolah ...</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677544/hybe-siapkan-debut-girl-group-tuide</t>
+          <t>https://www.antaranews.com/berita/5677540/pemkot-jakut-edukasi-pelajar-tentang-teknik-pertanian-di-perkotaan</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/644817de-49b2-42cd-92a5-0d0a14d911ce.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/2dfab961fe56.jpeg</t>
         </is>
       </c>
     </row>
@@ -3646,61 +3646,61 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Pemkot Jakut edukasi pelajar tentang teknik pertanian di perkotaan</t>
+          <t>Pelindo siagakan posko terpadu bagi korban KMP Mutiara Sentosa II</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:52:39 +0700</t>
+          <t>Mon, 03 Aug 2026 15:45:16 +0700</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Suku Dinas Ketahanan Pangan, Kelautan dan Pertanian (KPKP) Jakarta Utara mengedukasi puluhan pelajar dari enam sekolah ...</t>
+          <t>PT Pelabuhan Indonesia (Persero) Regional 3 Sub Regional Jawa menyiagakan posko terpadu korban kebakaran Kapal Motor ...</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677540/pemkot-jakut-edukasi-pelajar-tentang-teknik-pertanian-di-perkotaan</t>
+          <t>https://www.antaranews.com/berita/5677537/pelindo-siagakan-posko-terpadu-bagi-korban-kmp-mutiara-sentosa-ii</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/2dfab961fe56.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/260405.jpg</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>photo, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Jelang HUT RI, Polda Kepri bagikan bendera ke warga di pulau-pulau terluar</t>
+          <t>MPR undang Presiden Prabowo hadiri sidang tahunan pada 14 Agustus</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:51:09 +0700</t>
+          <t>Mon, 03 Aug 2026 15:43:18 +0700</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Warga memasang Bendera Merah Putih di perahu serta pekarangan rumah panggung yang dibagikan Polda Kepri di Pulau Dapur ...</t>
+          <t>Pimpinan MPR mengundang Presiden Prabowo Subianto menghadiri Sidang Tahunan MPR yang rencananya digelar pada Jumat, 14 ...</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5677539/jelang-hut-ri-polda-kepri-bagikan-bendera-ke-warga-di-pulau-pulau-terluar</t>
+          <t>https://www.antaranews.com/berita/5677536/mpr-undang-presiden-prabowo-hadiri-sidang-tahunan-pada-14-agustus</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Pembagian-Bendera-Merah-Putih-Di-Pulau-Pulau-Terluar-030826-tpp-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000398675.jpg</t>
         </is>
       </c>
     </row>
@@ -3712,61 +3712,61 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Pelindo siagakan posko terpadu bagi korban KMP Mutiara Sentosa II</t>
+          <t>Kesbangpol Pontianak antisipasi konflik sosial akibat karhutla</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:45:16 +0700</t>
+          <t>Mon, 03 Aug 2026 15:42:51 +0700</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>PT Pelabuhan Indonesia (Persero) Regional 3 Sub Regional Jawa menyiagakan posko terpadu korban kebakaran Kapal Motor ...</t>
+          <t>ANTARA - Badan Kesatuan Bangsa dan Politik (Kesbangpol) Kota Pontianak mengidentifikasi potensi gangguan keamanan dan ...</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677537/pelindo-siagakan-posko-terpadu-bagi-korban-kmp-mutiara-sentosa-ii</t>
+          <t>https://www.antaranews.com/video/5677519/kesbangpol-pontianak-antisipasi-konflik-sosial-akibat-karhutla</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/260405.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KESBANGPOL-PONTIANAK-ANTISIPASI-KONFLIK-SOSIAL-AKIBAT-KARHUTLA.jpg</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MPR undang Presiden Prabowo hadiri sidang tahunan pada 14 Agustus</t>
+          <t>Data untuk Indonesia, bakti untuk negeri</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:43:18 +0700</t>
+          <t>Mon, 03 Aug 2026 15:42:25 +0700</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Pimpinan MPR mengundang Presiden Prabowo Subianto menghadiri Sidang Tahunan MPR yang rencananya digelar pada Jumat, 14 ...</t>
+          <t>Bulan Agustus selalu menghadirkan suasana yang berbeda. Bendera Merah Putih berkibar di halaman rumah, berbagai ...</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677536/mpr-undang-presiden-prabowo-hadiri-sidang-tahunan-pada-14-agustus</t>
+          <t>https://www.antaranews.com/berita/5677535/data-untuk-indonesia-bakti-untuk-negeri</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000398675.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/1001511288.jpg</t>
         </is>
       </c>
     </row>
@@ -3778,61 +3778,61 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Kesbangpol Pontianak antisipasi konflik sosial akibat karhutla</t>
+          <t>Prabowo: Persatuan selalu terlihat saat timnas Indonesia bermain</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:42:51 +0700</t>
+          <t>Mon, 03 Aug 2026 15:40:54 +0700</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ANTARA - Badan Kesatuan Bangsa dan Politik (Kesbangpol) Kota Pontianak mengidentifikasi potensi gangguan keamanan dan ...</t>
+          <t>Presiden Republik Indonesia Prabowo Subianto mengaku selalu melihat persatuan setiap kali timnas Indonesia ...</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5677519/kesbangpol-pontianak-antisipasi-konflik-sosial-akibat-karhutla</t>
+          <t>https://www.antaranews.com/berita/5677532/prabowo-persatuan-selalu-terlihat-saat-timnas-indonesia-bermain</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KESBANGPOL-PONTIANAK-ANTISIPASI-KONFLIK-SOSIAL-AKIBAT-KARHUTLA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0003_3.jpg</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Data untuk Indonesia, bakti untuk negeri</t>
+          <t>PSEL Serang Raya jadi solusi pengelolaan sampah tiga daerah</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:42:25 +0700</t>
+          <t>Mon, 03 Aug 2026 15:40:46 +0700</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bulan Agustus selalu menghadirkan suasana yang berbeda. Bendera Merah Putih berkibar di halaman rumah, berbagai ...</t>
+          <t>ANTARA - Fasilitas Pengolahan Sampah menjadi Energi Listrik (PSEL) Serang Raya akan dibangun di TPSA Cilowong, Kota ...</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677535/data-untuk-indonesia-bakti-untuk-negeri</t>
+          <t>https://www.antaranews.com/video/5677492/psel-serang-raya-jadi-solusi-pengelolaan-sampah-tiga-daerah</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/1001511288.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AYM_PSEL-SERANG-RAYA-JADI-SOLUSI-PENGELOLAAN-SAMPAH.jpg</t>
         </is>
       </c>
     </row>
@@ -3844,28 +3844,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Prabowo: Persatuan selalu terlihat saat timnas Indonesia bermain</t>
+          <t>Dewas KPK sempurnakan Perdewas untuk atur etik PNYD hingga potong gaji</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:40:54 +0700</t>
+          <t>Mon, 03 Aug 2026 15:39:59 +0700</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Presiden Republik Indonesia Prabowo Subianto mengaku selalu melihat persatuan setiap kali timnas Indonesia ...</t>
+          <t>Dewan Pengawas Komisi Pemberantasan Korupsi (Dewas KPK) tengah menyempurnakan peraturan Dewas KPK (Perdewas) untuk ...</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677532/prabowo-persatuan-selalu-terlihat-saat-timnas-indonesia-bermain</t>
+          <t>https://www.antaranews.com/berita/5677531/dewas-kpk-sempurnakan-perdewas-untuk-atur-etik-pnyd-hingga-potong-gaji</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0003_3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_8184.jpg</t>
         </is>
       </c>
     </row>
@@ -3877,28 +3877,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PSEL Serang Raya jadi solusi pengelolaan sampah tiga daerah</t>
+          <t>Kelurahan Dukuh Jaktim perketat pengawasan TPS liar pascakebakaran</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:40:46 +0700</t>
+          <t>Mon, 03 Aug 2026 15:39:50 +0700</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>ANTARA - Fasilitas Pengolahan Sampah menjadi Energi Listrik (PSEL) Serang Raya akan dibangun di TPSA Cilowong, Kota ...</t>
+          <t>Kelurahan Dukuh, Jakarta Timur, bersama pengurus RT 013 dan RW 03 memperketat pengawasan tempat penampungan sementara ...</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5677492/psel-serang-raya-jadi-solusi-pengelolaan-sampah-tiga-daerah</t>
+          <t>https://www.antaranews.com/berita/5677527/kelurahan-dukuh-jaktim-perketat-pengawasan-tps-liar-pascakebakaran</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AYM_PSEL-SERANG-RAYA-JADI-SOLUSI-PENGELOLAAN-SAMPAH.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/InShot_20260803_145658796.jpg</t>
         </is>
       </c>
     </row>
@@ -3910,28 +3910,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Dewas KPK sempurnakan Perdewas untuk atur etik PNYD hingga potong gaji</t>
+          <t>BPBD Sulbar intensifkan edukasi pencegahan karhutla</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:39:59 +0700</t>
+          <t>Mon, 03 Aug 2026 15:38:10 +0700</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Dewan Pengawas Komisi Pemberantasan Korupsi (Dewas KPK) tengah menyempurnakan peraturan Dewas KPK (Perdewas) untuk ...</t>
+          <t>Badan Penanggulangan Bencana Daerah (BPBD) Provinsi Sulawesi Barat mengintensifkan edukasi dan peningkatan kesadaran ...</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677531/dewas-kpk-sempurnakan-perdewas-untuk-atur-etik-pnyd-hingga-potong-gaji</t>
+          <t>https://www.antaranews.com/berita/5677523/bpbd-sulbar-intensifkan-edukasi-pencegahan-karhutla</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_8184.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260309_224833.jpg</t>
         </is>
       </c>
     </row>
@@ -3943,28 +3943,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Kelurahan Dukuh Jaktim perketat pengawasan TPS liar pascakebakaran</t>
+          <t>Presiden Prabowo memandang Indonesia layak tampil di Piala Dunia 2030</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:39:50 +0700</t>
+          <t>Mon, 03 Aug 2026 15:35:54 +0700</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Kelurahan Dukuh, Jakarta Timur, bersama pengurus RT 013 dan RW 03 memperketat pengawasan tempat penampungan sementara ...</t>
+          <t>Presiden Republik Indonesia Prabowo Subianto dalam pidatonya pada pembukaan Kongres Biasa PSSI 2026 di Jakarta, Senin, ...</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677527/kelurahan-dukuh-jaktim-perketat-pengawasan-tps-liar-pascakebakaran</t>
+          <t>https://www.antaranews.com/berita/5677516/presiden-prabowo-memandang-indonesia-layak-tampil-di-piala-dunia-2030</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/InShot_20260803_145658796.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0004.jpg</t>
         </is>
       </c>
     </row>
@@ -3976,28 +3976,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BPBD Sulbar intensifkan edukasi pencegahan karhutla</t>
+          <t>BPK dorong kementerian terapkan prinsip ESG dalam pengelolaan anggaran</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:38:10 +0700</t>
+          <t>Mon, 03 Aug 2026 15:35:12 +0700</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Badan Penanggulangan Bencana Daerah (BPBD) Provinsi Sulawesi Barat mengintensifkan edukasi dan peningkatan kesadaran ...</t>
+          <t>Badan Pemeriksa Keuangan (BPK) RI mendorong kementerian dan lembaga mulai menerapkan prinsip Environmental, Social, and ...</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677523/bpbd-sulbar-intensifkan-edukasi-pencegahan-karhutla</t>
+          <t>https://www.antaranews.com/berita/5677512/bpk-dorong-kementerian-terapkan-prinsip-esg-dalam-pengelolaan-anggaran</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260309_224833.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001216419.jpg</t>
         </is>
       </c>
     </row>
@@ -4009,28 +4009,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Presiden Prabowo memandang Indonesia layak tampil di Piala Dunia 2030</t>
+          <t>BNPB: 1.485 jiwa terdampak kebakaran TPA Troketon Klaten</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:35:54 +0700</t>
+          <t>Mon, 03 Aug 2026 15:33:32 +0700</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Presiden Republik Indonesia Prabowo Subianto dalam pidatonya pada pembukaan Kongres Biasa PSSI 2026 di Jakarta, Senin, ...</t>
+          <t>Badan Nasional Penanggulangan Bencana (BNPB) mengoordinasikan penanganan dampak kebakaran Tempat Pemrosesan Akhir (TPA) ...</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677516/presiden-prabowo-memandang-indonesia-layak-tampil-di-piala-dunia-2030</t>
+          <t>https://www.antaranews.com/berita/5677509/bnpb-1485-jiwa-terdampak-kebakaran-tpa-troketon-klaten</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0004.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/10/16/33.jpg</t>
         </is>
       </c>
     </row>
@@ -4042,28 +4042,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BPK dorong kementerian terapkan prinsip ESG dalam pengelolaan anggaran</t>
+          <t>Menkomdigi sebut kreator rekam konten tanpa izin langgar UU PDP</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:35:12 +0700</t>
+          <t>Mon, 03 Aug 2026 15:32:10 +0700</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Badan Pemeriksa Keuangan (BPK) RI mendorong kementerian dan lembaga mulai menerapkan prinsip Environmental, Social, and ...</t>
+          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid menyebutkan kreator konten yang merekam video tanpa ...</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677512/bpk-dorong-kementerian-terapkan-prinsip-esg-dalam-pengelolaan-anggaran</t>
+          <t>https://www.antaranews.com/berita/5677508/menkomdigi-sebut-kreator-rekam-konten-tanpa-izin-langgar-uu-pdp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001216419.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0252.jpg</t>
         </is>
       </c>
     </row>
@@ -4075,28 +4075,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BNPB: 1.485 jiwa terdampak kebakaran TPA Troketon Klaten</t>
+          <t>Survei LKPI: Kepuasan publik terhadap Prabowo capai 79,3 persen</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:33:32 +0700</t>
+          <t>Mon, 03 Aug 2026 15:31:44 +0700</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Badan Nasional Penanggulangan Bencana (BNPB) mengoordinasikan penanganan dampak kebakaran Tempat Pemrosesan Akhir (TPA) ...</t>
+          <t>Survei Lembaga Kajian Pemilu Indonesia (LKPI) menunjukkan tingkat kepuasan publik terhadap kinerja Presiden Prabowo ...</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677509/bnpb-1485-jiwa-terdampak-kebakaran-tpa-troketon-klaten</t>
+          <t>https://www.antaranews.com/berita/5677504/survei-lkpi-kepuasan-publik-terhadap-prabowo-capai-793-persen</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/10/16/33.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG_3632.jpeg</t>
         </is>
       </c>
     </row>
@@ -4108,28 +4108,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Menkomdigi sebut kreator rekam konten tanpa izin langgar UU PDP</t>
+          <t>KONI Pusat harap Kongres Biasa PSSI diskusikan pembinaan prestasi</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:32:10 +0700</t>
+          <t>Mon, 03 Aug 2026 15:29:28 +0700</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid menyebutkan kreator konten yang merekam video tanpa ...</t>
+          <t>Ketua Umum Komite Olahraga Nasional Indonesia (KONI) Pusat Letjen TNI Purn. Marciano Norman berharap Kongres Biasa ...</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677508/menkomdigi-sebut-kreator-rekam-konten-tanpa-izin-langgar-uu-pdp</t>
+          <t>https://www.antaranews.com/berita/5677500/koni-pusat-harap-kongres-biasa-pssi-diskusikan-pembinaan-prestasi</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0252.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/11/Ketua-KONI-Pusat-Marciano-Norman.jpg</t>
         </is>
       </c>
     </row>
@@ -4141,28 +4141,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Survei LKPI: Kepuasan publik terhadap Prabowo capai 79,3 persen</t>
+          <t>KPK panggil anggota DPR RI Anwar Sadad pada kasus dana hibah Jatim</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:31:44 +0700</t>
+          <t>Mon, 03 Aug 2026 15:28:20 +0700</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Survei Lembaga Kajian Pemilu Indonesia (LKPI) menunjukkan tingkat kepuasan publik terhadap kinerja Presiden Prabowo ...</t>
+          <t>Komisi Pemberantasan Korupsi (KPK) memanggil anggota DPR RI Anwar Sadad (AS) untuk diperiksa dalam penyidikan kasus ...</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677504/survei-lkpi-kepuasan-publik-terhadap-prabowo-capai-793-persen</t>
+          <t>https://www.antaranews.com/berita/5677496/kpk-panggil-anggota-dpr-ri-anwar-sadad-pada-kasus-dana-hibah-jatim</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG_3632.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/07/23/IMG-20230723-WA0032.jpg</t>
         </is>
       </c>
     </row>
@@ -4174,61 +4174,61 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>KONI Pusat harap Kongres Biasa PSSI diskusikan pembinaan prestasi</t>
+          <t>Ditjenpas Kaltim gelar CKG bagi 12 ribu warga binaan</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:29:28 +0700</t>
+          <t>Mon, 03 Aug 2026 15:23:58 +0700</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ketua Umum Komite Olahraga Nasional Indonesia (KONI) Pusat Letjen TNI Purn. Marciano Norman berharap Kongres Biasa ...</t>
+          <t>ANTARA - Program Cek Kesehatan Gratis (CKG) menyasar warga binaan di Lembaga Pemasyarakatan (Lapas) dan Rumah Tahanan ...</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677500/koni-pusat-harap-kongres-biasa-pssi-diskusikan-pembinaan-prestasi</t>
+          <t>https://www.antaranews.com/video/5677480/ditjenpas-kaltim-gelar-ckg-bagi-12-ribu-warga-binaan</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/11/Ketua-KONI-Pusat-Marciano-Norman.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AYM_DITJENPAS-KALTIM-GELAR-CKG.jpg</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>KPK panggil anggota DPR RI Anwar Sadad pada kasus dana hibah Jatim</t>
+          <t>BPS prediksi produksi beras RI 28,71 juta ton hingga September 2026</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:28:20 +0700</t>
+          <t>Mon, 03 Aug 2026 15:23:12 +0700</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Komisi Pemberantasan Korupsi (KPK) memanggil anggota DPR RI Anwar Sadad (AS) untuk diperiksa dalam penyidikan kasus ...</t>
+          <t>Badan Pusat Statistik (BPS) memprediksi produksi beras sepanjang Januari–September 2026 mencapai 28,71 juta ton, ...</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677496/kpk-panggil-anggota-dpr-ri-anwar-sadad-pada-kasus-dana-hibah-jatim</t>
+          <t>https://www.antaranews.com/berita/5677485/bps-prediksi-produksi-beras-ri-2871-juta-ton-hingga-september-2026</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/07/23/IMG-20230723-WA0032.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/proyeksi-produksi-beras-konsumsi-2815573.jpg</t>
         </is>
       </c>
     </row>
@@ -4240,160 +4240,160 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ditjenpas Kaltim gelar CKG bagi 12 ribu warga binaan</t>
+          <t>Polda Jatim kerahkan 30 personel evakuasi KMP Mutiara Sentosa 2</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:23:58 +0700</t>
+          <t>Mon, 03 Aug 2026 15:22:46 +0700</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ANTARA - Program Cek Kesehatan Gratis (CKG) menyasar warga binaan di Lembaga Pemasyarakatan (Lapas) dan Rumah Tahanan ...</t>
+          <t>Kepolisian Daerah (Polda) Jawa Timur (Jatim) mengerahkan 30 personel SAR Direktorat Kepolisian Perairan dan Udara ...</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5677480/ditjenpas-kaltim-gelar-ckg-bagi-12-ribu-warga-binaan</t>
+          <t>https://www.antaranews.com/berita/5677483/polda-jatim-kerahkan-30-personel-evakuasi-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AYM_DITJENPAS-KALTIM-GELAR-CKG.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1319202.jpg</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BPS prediksi produksi beras RI 28,71 juta ton hingga September 2026</t>
+          <t>Komisi IX DPR: Putusan MK jadi momentum BGN desain ulang MBG</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:23:12 +0700</t>
+          <t>Mon, 03 Aug 2026 15:19:16 +0700</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) memprediksi produksi beras sepanjang Januari–September 2026 mencapai 28,71 juta ton, ...</t>
+          <t>Wakil Ketua Komisi IX DPR RI Charles Honoris mengatakan putusan Mahkamah Konstitusi Nomor 40/PUU-XXIV/2026 menjadi ...</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677485/bps-prediksi-produksi-beras-ri-2871-juta-ton-hingga-september-2026</t>
+          <t>https://www.antaranews.com/berita/5677477/komisi-ix-dpr-putusan-mk-jadi-momentum-bgn-desain-ulang-mbg</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/proyeksi-produksi-beras-konsumsi-2815573.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/15/tempImageigZXJC.jpg</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Polda Jatim kerahkan 30 personel evakuasi KMP Mutiara Sentosa 2</t>
+          <t>Ratusan korban selamat KMP Mutiara Santosa 2 tiba di Tanjung Perak</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:22:46 +0700</t>
+          <t>Mon, 03 Aug 2026 06:37:38 +0700</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kepolisian Daerah (Polda) Jawa Timur (Jatim) mengerahkan 30 personel SAR Direktorat Kepolisian Perairan dan Udara ...</t>
+          <t>Sebanyak 111 korban selamat dan dua meninggal dunia akibat kebakaran KMP Mutiara Santosa II di Perairan Utara ...</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677483/polda-jatim-kerahkan-30-personel-evakuasi-kmp-mutiara-sentosa-2</t>
+          <t>https://www.antaranews.com/berita/5676983/ratusan-korban-selamat-kmp-mutiara-santosa-2-tiba-di-tanjung-perak</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1319202.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/259549_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Komisi IX DPR: Putusan MK jadi momentum BGN desain ulang MBG</t>
+          <t>Sebagian Jakarta diguyur hujan ringan pada Senin sore hingga malam</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 15:19:16 +0700</t>
+          <t>Mon, 03 Aug 2026 06:11:02 +0700</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Wakil Ketua Komisi IX DPR RI Charles Honoris mengatakan putusan Mahkamah Konstitusi Nomor 40/PUU-XXIV/2026 menjadi ...</t>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) memprakirakan hujan ringan akan melanda sebagian wilayah Jakarta ...</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677477/komisi-ix-dpr-putusan-mk-jadi-momentum-bgn-desain-ulang-mbg</t>
+          <t>https://www.antaranews.com/berita/5676963/sebagian-jakarta-diguyur-hujan-ringan-pada-senin-sore-hingga-malam</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/15/tempImageigZXJC.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/01/IMG_20260301_073711.jpg</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, top-news</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Nusron sebut banyak laut di Batam telah dikapling tanpa prosedur sah</t>
+          <t>Atlet-atlet nasional borong 18 medali Poomsae Indonesia Open 2026</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:44:05 +0700</t>
+          <t>Mon, 03 Aug 2026 04:18:40 +0700</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Menteri Agraria dan Tata Ruang (ATR)/Kepala Badan Pertanahan Nasional (BPN) Nusron Wahid mengatakan, menerima banyak ...</t>
+          <t>Atlet-atlet tuan rumah Indonesia tampil impresif pada nomor Poomsae 8th Asian Taekwondo, Indonesia Open ...</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677425/nusron-sebut-banyak-laut-di-batam-telah-dikapling-tanpa-prosedur-sah</t>
+          <t>https://www.antaranews.com/berita/5676947/atlet-atlet-nasional-borong-18-medali-poomsae-indonesia-open-2026</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_142345.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships-2026-020826-dr-04.jpg</t>
         </is>
       </c>
     </row>
@@ -4405,3187 +4405,5795 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Menkomdigi panggil YouTube imbas temuan konten promosi vape sasar anak</t>
+          <t>Kemenhub kerahkan kapal patroli evakuasi KM Mutiara Sentosa II</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:22:09 +0700</t>
+          <t>Mon, 03 Aug 2026 00:03:37 +0700</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid merencanakan pemanggilan terhadap platform digital YouTube ...</t>
+          <t>Kementerian Perhubungan mengerahkan kapal patroli Kesatuan Penjagaan Laut dan Pantai (KPLP) serta memperkuat koordinasi ...</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677396/menkomdigi-panggil-youtube-imbas-temuan-konten-promosi-vape-sasar-anak</t>
+          <t>https://www.antaranews.com/berita/5676931/kemenhub-kerahkan-kapal-patroli-evakuasi-km-mutiara-sentosa-ii</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0225.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, top-news</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Kemnaker: Magang Nasional diharapkan menekan angka pengangguran muda</t>
+          <t>BPS catat pengeluaran wisman triwulan II-2026 mencapai 1.285 dolar AS</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:37:57 +0700</t>
+          <t>Mon, 03 Aug 2026 14:56:12 +0700</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Kementerian Ketenagakerjaan (Kemnaker) mengatakan program Magang Nasional (MagangHub) untuk mempersiapkan kompetensi ...</t>
+          <t>Badan Pusat Statistik (BPS) mencatat perkembangan pengeluaran wisatawan mancanegara (wisman) pada triwulan II tahun ...</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677364/kemnaker-magang-nasional-diharapkan-menekan-angka-pengangguran-muda</t>
+          <t>https://www.antaranews.com/berita/5677457/bps-catat-pengeluaran-wisman-triwulan-ii-2026-mencapai-1285-dolar-as</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/ff63afaf-7778-47fe-833d-5a8068af9a51_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG-20260731-WA0028.jpg</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Kemenag perkuat transformasi madrasah lewat revitalisasi-digitalisasi</t>
+          <t>Kapal Pertamina selamatkan 17 korban KMP Mutiara Sentosa 2</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:36:36 +0700</t>
+          <t>Mon, 03 Aug 2026 14:52:47 +0700</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Menteri Agama (Menag) Nasaruddin Umar menegaskan transformasi madrasah terus diperkuat melalui revitalisasi ...</t>
+          <t>Kapal Pertamina Patra Niaga MT Transko Arafura berhasil mengevakuasi 17 orang korban KMP Mutiara Sentosa 2 yang ...</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677363/kemenag-perkuat-transformasi-madrasah-lewat-revitalisasi-digitalisasi</t>
+          <t>https://www.antaranews.com/berita/5677445/kapal-pertamina-selamatkan-17-korban-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/14/1000173935_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-14.30.38.jpeg</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, top-news</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Lisensi IP Global Buka Peluang Bisnis Baru bagi Kreator Indonesia</t>
+          <t>PGN sasar pemanfaatan jargas untuk hotel hingga UMKM</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:34:30 +0700</t>
+          <t>Mon, 03 Aug 2026 14:50:20 +0700</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Wakil Menteri Ekonomi Kreatif Irene Umar mengatakan kolaborasi antara pemilik kekayaan intelektual (Intellectual ...</t>
+          <t>PT Perusahaan Gas Negara (Persero) Tbk (PGN) menyasar pemanfaatan jaringan gas (jargas) tidak hanya rumah ...</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677353/lisensi-ip-global-buka-peluang-bisnis-baru-bagi-kreator-indonesia</t>
+          <t>https://www.antaranews.com/berita/5677439/pgn-sasar-pemanfaatan-jargas-untuk-hotel-hingga-umkm</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000589873.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_2395.jpeg</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, top-news</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Nilai ekspor perdagangan RI Januari-Juni capai 140,81 miliar dolar AS</t>
+          <t>CORE: Harga Pertamax turun beri sentimen positif bagi inflasi</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:16:17 +0700</t>
+          <t>Mon, 03 Aug 2026 14:40:44 +0700</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat nilai ekspor Indonesia secara kumulatif dari Januari-Juni 2026 mencapai 140,81 ...</t>
+          <t>Ekonom Center of Reform on Economics (CORE) Yusuf Rendy Manilet menyampaikan penurunan harga Pertamax pada bulan ...</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677315/nilai-ekspor-perdagangan-ri-januari-juni-capai-14081-miliar-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5677420/core-harga-pertamax-turun-beri-sentimen-positif-bagi-inflasi</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/neraca-perdagangan-januari-mei-2026-surplus-2815779.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/penurunan-harga-bbm-jenis-pertamax-2831783.jpg</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Korban KMP Mutiara Sentosa II dievakuasi ke Pelabuhan Tanjung Perak</t>
+          <t>Askrindo bukukan laba Rp1,69 T pada 2025 ditopang tiga lini bisnis</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:06:15 +0700</t>
+          <t>Mon, 03 Aug 2026 14:38:49 +0700</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Tim SAR gabungan terus melakukan evakuasi korban terbakarnya KMP Mutiara Sentosa 2 ke darat, tepatnya ke Pelabuhan ...</t>
+          <t>PT Asuransi Kredit Indonesia (Persero) atau Askrindo membukukan laba setelah pajak sebesar Rp1,69 triliun pada 2025 ...</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677297/korban-kmp-mutiara-sentosa-ii-dievakuasi-ke-pelabuhan-tanjung-perak</t>
+          <t>https://www.antaranews.com/berita/5677419/askrindo-bukukan-laba-rp169-t-pada-2025-ditopang-tiga-lini-bisnis</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/260821_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-08.51.32.jpeg</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Aktor senior Diding Boneng meninggal dunia</t>
+          <t>Jasaraharja Putera menjamin santunan korban KMP Mutiara Sentosa II</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:39:03 +0700</t>
+          <t>Mon, 03 Aug 2026 14:30:17 +0700</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aktor sekaligus komedian tanah air, Zainal Abidin alias Diding Boneng dikabarkan meninggal dunia pada Senin (3/8) dalam ...</t>
+          <t>PT Jasaraharja Putera menjamin perlindungan dan santunan bagi seluruh korban kebakaran Kapal Motor Penyeberangan (KMP) ...</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677209/aktor-senior-diding-boneng-meninggal-dunia</t>
+          <t>https://www.antaranews.com/berita/5677412/jasaraharja-putera-menjamin-santunan-korban-kmp-mutiara-sentosa-ii</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/26f1eb88-3301-4ae1-badd-bed5078fe3dd.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176259.jpg</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Seskab: Prabowo dorong sinergi pemerintah dan dunia usaha</t>
+          <t>GMR bidik Indonesia dalam perluasan rute Bandara Bhogapuram India</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:17:50 +0700</t>
+          <t>Mon, 03 Aug 2026 14:29:34 +0700</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Sekretaris Kabinet Teddy Indra Wijaya menyampaikan bahwa Presiden Prabowo Subianto menekankan pentingnya sinergi antara ...</t>
+          <t>GMR Airports Limited (GMR Airports), salah satu pengelola jaringan bandara internasional, memprioritaskan Indonesia ...</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677191/seskab-prabowo-dorong-sinergi-pemerintah-dan-dunia-usaha</t>
+          <t>https://www.antaranews.com/berita/5677407/gmr-bidik-indonesia-dalam-perluasan-rute-bandara-bhogapuram-india</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0891_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0725.jpeg</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Red Velvet bersiap kembali lewat EP baru "Velvet Summer"</t>
+          <t>BPS: Wisman per Juni capai 7,45 juta kunjungan, tertinggi sejak 2020</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:24:37 +0700</t>
+          <t>Mon, 03 Aug 2026 14:22:48 +0700</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Grup idola K-pop Red Velvet akan kembali lewat rilis mini album atau extended play (EP) baru bertajuk “Velvet ...</t>
+          <t>Badan Pusat Statistik (BPS) mencatat total kunjungan wisatawan mancanegara dari Januari hingga bulan Juni 2026 mencapai ...</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677151/red-velvet-bersiap-kembali-lewat-ep-baru-velvet-summer</t>
+          <t>https://www.antaranews.com/berita/5677399/bps-wisman-per-juni-capai-745-juta-kunjungan-tertinggi-sejak-2020</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/ca97a3a8-aa17-45fc-be71-d36051dd9dcd.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/pelepasliaran-500-ekor-tukik-bali-290726-nhw-3_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Menaker pastikan komitmen pemerintah perkuat kesejahteraan pekerja</t>
+          <t>BPS catat nilai tukar petani di level 127,84 pada Juli 2026</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:16:19 +0700</t>
+          <t>Mon, 03 Aug 2026 13:18:40 +0700</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Menteri Ketenagakerjaan (Menaker) Yassierli memastikan pemerintah berkomitmen untuk memperkuat kesejahteraan, ...</t>
+          <t>Badan Pusat Statistik (BPS) mencatat nilai tukar petani (NTP) secara nasional pada bulan Juli 2026 berada di level ...</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677148/menaker-pastikan-komitmen-pemerintah-perkuat-kesejahteraan-pekerja</t>
+          <t>https://www.antaranews.com/berita/5677323/bps-catat-nilai-tukar-petani-di-level-12784-pada-juli-2026</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/09/20/pelepasan-peserta-pemagangan-ke-jepang-di-jawa-barat-2627513.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/02/20260302_083324.jpg</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>23 calon hakim agung dan ad hoc ikuti seleksi wawancara akhir</t>
+          <t>Menteri ATR sebut 400 Kantah sudah terapkan pengukuran terjadwal</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:15:01 +0700</t>
+          <t>Mon, 03 Aug 2026 13:13:29 +0700</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sebanyak 23 orang calon hakim agung dan ad hoc Mahkamah Agung Tahun 2026 mengikuti seleksi wawancara tahap akhir di ...</t>
+          <t>Menteri Agraria dan Tata Ruang/Kepala Badan Pertanahan Nasional (ATR/BPN) Nusron Wahid mengatakan bahwa sudah ada 400 ...</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677137/23-calon-hakim-agung-dan-ad-hoc-ikuti-seleksi-wawancara-akhir</t>
+          <t>https://www.antaranews.com/berita/5677308/menteri-atr-sebut-400-kantah-sudah-terapkan-pengukuran-terjadwal</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000012883_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_125328.jpg</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>BRIN perkuat kajian sungai bawah tanah di Kebumen untuk ketahanan air</t>
+          <t>Karhutla Tumbang Nusa meluas, 104 hektar gambut terbakar</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:57:19 +0700</t>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Badan Riset dan Inovasi Nasional (BRIN) memperkuat riset ketahanan air melalui pengembangan teknologi dan penelitian ...</t>
+          <t>ANTARA - Kebakaran hutan dan lahan (karhutla) di Desa Tumbang Nusa, Kecamatan Jabiren Raya, Kabupaten Pulang Pisau, Kalimantan Tengah, telah menghanguskan sekitar 104 hektare lahan gambut, Sabtu (1/8). Peristiwa tersebut memicu operasi penanganan terpadu yang melibatkan sekitar 416 personel gabungan melalui jalur darat, serta didukung dua unit helikopter water bombing untuk mempercepat pemadaman yang jauh dari tim darat. 
+(Redianto Tumon Sp/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677120/brin-perkuat-kajian-sungai-bawah-tanah-di-kebumen-untuk-ketahanan-air</t>
+          <t>https://www.antaranews.com/berita/5676013/karhutla-tumbang-nusa-meluas-104-hektar-gambut-terbakar</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1785706440-47672950-1.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/KARHUTLA-TUMBANG-NUSA-MELUAS-104-HEKTAR-GAMBUT-TERBAKAR.jpg</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Harga bensin turun pada pekan pertama Agustus</t>
+          <t>54 Atlet menembak Kalsel, bertanding pada Kejuaraan Wali Kota Cup</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:51:00 +0700</t>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Harga bahan bakar minyak (BBM) jenis bensin di stasiun pengisian bahan bakar umum (SPBU) Pertamina, Shell, dan bp ...</t>
+          <t>ANTARA - Pemerintah Kota Banjarmasin bersama Perbakin menggelar kejuaraan menembak Wali Kota Cup 2026. Kejuaraan diikuti oleh 54 atlet dari berbagai daerah di Kalsel sebagai wadah seleksi dan persiapan atlet kalimantan selatan menuju Pra-PON.
+(Latif Thohir/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677109/harga-bensin-turun-pada-pekan-pertama-agustus</t>
+          <t>https://www.antaranews.com/berita/5675995/54-atlet-menembak-kalsel-bertanding-pada-kejuaraan-wali-kota-cup</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/10/02/penuruanan-harga-bbm-011024-aaa-7.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/54-ATLET-MENEMBAK-KALSEL-BERTANDING-PADA-KEJUARAAN-WALI-KOTA-CUP.jpg</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Sean Gelael berbagi pengalaman di dunia balap ke pengunjung GIIAS 2026</t>
+          <t>Polda Riau kirim Tim Ekspedisi Merah Putih Presisi ke 17 desa 3T</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:34:53 +0700</t>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Pembalap Indonesia Sean Gelael berbagi pengalamannya di dunia balap ke pengunjung GAIKINDO Indonesia International ...</t>
+          <t>ANTARA - Kapolda Riau Irjen Pol Herry Heryawan melepas Tim Ekspedisi Merah Putih Presisi Polda Riau yang akan bertugas di 17 desa wilayah tertinggal, terdepan, dan terluar atau 3T, Sabtu (1/8). Ekspedisi yang berlangsung hingga 17 Agustus mendatang itu membawa berbagai program sosial, lingkungan, dan penguatan kebangsaan bagi masyarakat pesisir serta wilayah terluar di Provinsi Riau.
+(Farah Khadija/Annisa Firdausi/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677103/sean-gelael-berbagi-pengalaman-di-dunia-balap-ke-pengunjung-giias-2026</t>
+          <t>https://www.antaranews.com/berita/5675964/polda-riau-kirim-tim-ekspedisi-merah-putih-presisi-ke-17-desa-3t</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/16b70b87-326f-479a-a806-580ab846cc6f_1.jpeg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/POLDA-RIAU-KIRIM-TIM-EKSPEDISI-MERAH-PUTIH-PRESISI-KE-17-DESA-3T.jpg</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ekonomi-bursa, top-news</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>IHSG Senin dibuka menguat 36,49 poin ke posisi 6.272</t>
+          <t>Hadapi El Nino, pemerintah tingkatkan mitigasi karhutla</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:11:26 +0700</t>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin pagi dibuka menguat 36,49 poin atau 0,59 ...</t>
+          <t>ANTARA - Pemerintah memperkuat langkah antisipasi menghadapi potensi el nino yang diperkirakan meningkatkan risiko kebakaran hutan dan lahan. Menteri Lingkungan Hidup, Muhammad Jumhur Hidayat usai membuka Indonesia Net Zero Summit (INZS) 2026 yang diselenggarakan di Balai Kartini, Jakarta, pada Sabtu (1/8) menyebutkan, pihaknya menekan potensi karhutla sejak dini, salah satunya dengan membangun kanal blocking.
+(Irfan Hardiansah/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677071/ihsg-senin-dibuka-menguat-3649-poin-ke-posisi-6272</t>
+          <t>https://www.antaranews.com/berita/5675936/hadapi-el-nino-pemerintah-tingkatkan-mitigasi-karhutla</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/pergerakan-indeks-harga-saham-gabungan-2828631.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/HADAPI-EL-NINO-PEMERINTAH-TINGKATKAN-MITIGASI-KARHUTLA.jpg</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PLN Jakarta pastikan pasokan listrik sudah berhasil dipulihkan</t>
+          <t>Mensos resmikan Sekolah Rakyat Terintegrasi 1 Sukoharjo</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 08:36:26 +0700</t>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>PT PLN (Persero) Unit Induk Distribusi Jakarta Raya mengungkapkan pasokan listrik telah berhasil ...</t>
+          <t>ANTARA - Menteri Sosial Republik Indonesia Saifullah Yusuf membuka pelaksanaan Masa Pengenalan Lingkungan Sekolah (MPLS) di Sekolah Rakyat Terintegrasi (SRT) 1 Kabupaten Sukoharjo, Sabtu (1/8). Mensos menyebut meski proses pembangunan fisik belum sepenuhnya rampung, pihaknya memastikan kegiatan belajar mengajar sudah dapat dilaksanakan karena progres pembangunan telah mencapai sekitar 98 persen.(Denik Apriyani/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677043/pln-jakarta-pastikan-pasokan-listrik-sudah-berhasil-dipulihkan</t>
+          <t>https://www.antaranews.com/berita/5675924/mensos-resmikan-sekolah-rakyat-terintegrasi-1-sukoharjo</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20231217-WA0015-1.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/MENSOS-RESMIKAN-SEKOLAH-RAKYAT-TERINTEGRASI-1-SUKOHARJO.jpg</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ledakan di kantor polisi Pakistan tewaskan 14 orang</t>
+          <t>Lanud Sjamsudin Noor gelar Bakti Sosial Hari Bakti TNI AU ke-79</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 07:44:23 +0700</t>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Sebuah ledakan terjadi di luar sebuah kantor polisi di Kota Kabal, Pakistan, mengakibatkan 14 orang tewas dan 14 orang ...</t>
+          <t>ANTARA - Ratusan warga di Banjarbaru, Kalimantan Selatan, antusias mengikuti kegiatan bakti sosial yang diselenggarakan oleh Pangkalan Udara (Lanud) Sjamsudin Noor pada Sabtu (1/8). Kegiatan ini dilaksanakan sebagai rangkaian peringatan Hari Bhakti TNI Angkatan Udara Ke-79
+(Latif Thohir/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677020/ledakan-di-kantor-polisi-pakistan-tewaskan-14-orang</t>
+          <t>https://www.antaranews.com/berita/5675872/lanud-sjamsudin-noor-gelar-bakti-sosial-hari-bakti-tni-au-ke-79</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CmxztpE000019_20260803_PEPFN0A001.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/LANUD-SJAMSUDIN-NOOR-GELAR-BAKTI-SOSIAL-HARI-BAKTI-TNI-AU-KE-79.jpg</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ratusan korban selamat KMP Mutiara Santosa 2 tiba di Tanjung Perak</t>
+          <t>Prancis perketat pemeriksaan produk tani, lawan praktik francization</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:37:38 +0700</t>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Sebanyak 111 korban selamat dan dua meninggal dunia akibat kebakaran KMP Mutiara Santosa II di Perairan Utara ...</t>
+          <t>ANTARA - Prancis memperketat pemeriksaan terhadap asal-usul produk pertanian guna memberantas praktik "francization", yaitu pelabelan ulang produk impor agar tampak sebagai hasil produksi dalam negeri. Langkah ini diambil untuk melindungi konsumen dan produsen lokal, dengan pelanggar terancam denda hingga 300.000 euro dan hukuman penjara.(XINHUA/ Nabila Anisya Charisty/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676983/ratusan-korban-selamat-kmp-mutiara-santosa-2-tiba-di-tanjung-perak</t>
+          <t>https://www.antaranews.com/berita/5675865/prancis-perketat-pemeriksaan-produk-tani-lawan-praktik-francization</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/259549_1.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PRANCIS-PERKETAT-PEMERIKSAAN-PRODUK-TANI-LAWAN-PRAKTIK-FRANCIZATION.jpg</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Sebagian Jakarta diguyur hujan ringan pada Senin sore hingga malam</t>
+          <t>KM. Prince Soya terbakar saat bersandar di Pelabuhan Samarinda</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:11:02 +0700</t>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) memprakirakan hujan ringan akan melanda sebagian wilayah Jakarta ...</t>
+          <t>ANTARA - Kapal Motor (KM) Prince Soya terbakar pada Sabtu (1/8) saat bersandar di Pelabuhan Samarinda, Kalimantan Timur. Kapal penumpang yang biasa melayani rute Samarinda - Pare-Pare, Sulawesi Selatan itu terbakar di bagian dek sebelah kanan yang diduga bersumber dari tangki berisi pelumas mesin. (Hanifan Ma'ruf/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676963/sebagian-jakarta-diguyur-hujan-ringan-pada-senin-sore-hingga-malam</t>
+          <t>https://www.antaranews.com/berita/5675853/km-prince-soya-terbakar-saat-bersandar-di-pelabuhan-samarinda</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/01/IMG_20260301_073711.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/KM.PRINCE-SOYA-TERBAKAR-SAAT-BERSANDAR-DI-PELABUHAN-SAMARINDA.jpg</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Atlet-atlet nasional borong 18 medali Poomsae Indonesia Open 2026</t>
+          <t>St. Petersburg luncurkan festival sepeda motor untuk pertama kalinya</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 04:18:40 +0700</t>
+          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Atlet-atlet tuan rumah Indonesia tampil impresif pada nomor Poomsae 8th Asian Taekwondo, Indonesia Open ...</t>
+          <t>ANTARA - Saint Petersburg Motor Festival resmi dibuka, Jumat (31/7) selama tiga hari berturut-turut dalam pembukaan perdananya. Acara tersebut digelar untuk menghibur para penikmat sepeda motor, musik, serta pengunjung umum lainnya.(XINHUA/ Nabila Anisya Charisty/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676947/atlet-atlet-nasional-borong-18-medali-poomsae-indonesia-open-2026</t>
+          <t>https://www.antaranews.com/berita/5675828/st-petersburg-luncurkan-festival-sepeda-motor-untuk-pertama-kalinya</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/andi-sultan-raih-medali-emas-asian-taekwondo-indonesia-open-championships-2026-020826-dr-04.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/ST.PETERSBURG-LUNCURKAN-FESTIVAL-SEPEDA-MOTOR-UNTUK-PERTAMA-KALINYA.jpg</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Kemenhub kerahkan kapal patroli evakuasi KM Mutiara Sentosa II</t>
+          <t>PKB berbagi pengalaman dengan International Republican Institute</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 00:03:37 +0700</t>
+          <t>Mon, 03 Aug 2026 19:46:40 +0700</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Kementerian Perhubungan mengerahkan kapal patroli Kesatuan Penjagaan Laut dan Pantai (KPLP) serta memperkuat koordinasi ...</t>
+          <t>Partai Kebangkitan Bangsa (PKB) berbagi pengalaman dengan delegasi International Republican Institute (IRI) mengenai ...</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676931/kemenhub-kerahkan-kapal-patroli-evakuasi-km-mutiara-sentosa-ii</t>
+          <t>https://www.antaranews.com/berita/5678123/pkb-berbagi-pengalaman-dengan-international-republican-institute</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/KMP-Mutiara-Sentosa-2-terbakar-di-Sumenep-02082026-Um-9.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-19.00.16.jpeg</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Rupiah diperkirakan menguat seiring AS batalkan rencana serang Iran</t>
+          <t>Menbud buka pembinaan Gita Bahana Nusantara 2026</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:12:26 +0700</t>
+          <t>Mon, 03 Aug 2026 19:46:09 +0700</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Analis Doo Financial Futures, Lukman Leong memperkirakan rupiah menguat seiring Amerika Serikat (AS) membatalkan ...</t>
+          <t>ANTARA - Sebanyak 183 peserta Gita Bahana Nusantara (GBN) mulai menjalani pembinaan intensif dalam rangka menyemarakkan ...</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677132/rupiah-diperkirakan-menguat-seiring-as-batalkan-rencana-serang-iran</t>
+          <t>https://www.antaranews.com/video/5678104/menbud-buka-pembinaan-gita-bahana-nusantara-2026</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828847.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_MENBUD-BUKA-PEMBINAAN-GITA-BAHANA-NUSANTARA-2026.jpg</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Rupiah pada Senin pagi melemah jadi Rp18.031 per dolar AS</t>
+          <t>Kemenhaj gandeng UIN SATU - PWNU Jatim perluas literasi kebijakan haji</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:05:50 +0700</t>
+          <t>Mon, 03 Aug 2026 19:43:20 +0700</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Nilai tukar rupiah pada Senin pagi bergerak melemah 9 poin atau 0,05 persen menjadi Rp18.031 per dolar AS dibandingkan ...</t>
+          <t>Kanwil Kementerian Haji dan Umrah Provinsi Jawa Timur menggandeng Universitas Islam Negeri (UIN) Sayyid Ali Rahmatullah ...</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677063/rupiah-pada-senin-pagi-melemah-jadi-rp18031-per-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5678119/kemenhaj-gandeng-uin-satu-pwnu-jatim-perluas-literasi-kebijakan-haji</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/452192.jpg</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Komisi XI: PFII peluang RI tangkap momentum perpindahan modal global</t>
+          <t>Kemenkes: Teknologi TBScreen.AI mampu tingkatkan efisiensi skrining TB</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:53:34 +0700</t>
+          <t>Mon, 03 Aug 2026 19:43:05 +0700</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Wakil Ketua Komisi XI DPR RI Mohamad Hekal mengatakan percepatan pembentukan Pusat Finansial Internasional Indonesia ...</t>
+          <t>Kementerian Kesehatan mengatakan, teknologi TBScreen.AI ciptaan KONEKSI, platform kemitraan Australia-Indonesia untuk ...</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676995/komisi-xi-pfii-peluang-ri-tangkap-momentum-perpindahan-modal-global</t>
+          <t>https://www.antaranews.com/berita/5678115/kemenkes-teknologi-tbscreenai-mampu-tingkatkan-efisiensi-skrining-tb</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Saham-dan-oblogasi.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Rita-Aryati-Staf-Tim-Kerja-Tuberkulosis-TB-dan-Infeksi-Saluran-Pernapasan-Akut-ISPA-Kementerian-Kesehatan-Republik-Indonesia.jpg</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>BUMA International Group bukukan pertumbuhan EBITDA semester I/2026</t>
+          <t>Basarnas sebut cuaca pengaruhi evakuasi korban KMP Mutiara Sentosa II</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:17:40 +0700</t>
+          <t>Mon, 03 Aug 2026 19:38:49 +0700</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>PT BUMA Internasional Gorup membukukan pertumbuhan EBITDA pada semester pertama 2026 (1H26) di tengah penurunan ...</t>
+          <t>Kepala Basarnas Mohammad Syafii menyebut kondisi cuaca di perairan Sumenep sekitar lokasi kebakaran KMP Mutiara ...</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676967/buma-international-group-bukukan-pertumbuhan-ebitda-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5678109/basarnas-sebut-cuaca-pengaruhi-evakuasi-korban-kmp-mutiara-sentosa-ii</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/buma.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/262446.jpg</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>BPS catat pengeluaran wisman triwulan II-2026 mencapai 1.285 dolar AS</t>
+          <t>Kebakaran melanda gardu listrik di Kalideres Jakbar</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:56:12 +0700</t>
+          <t>Mon, 03 Aug 2026 19:36:50 +0700</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat perkembangan pengeluaran wisatawan mancanegara (wisman) pada triwulan II tahun ...</t>
+          <t>Kebakaran melanda gardu listrik di Jalan Peta Barat Nomor 35, RT 3/RW 7 Pegadungan, Kalideres, Jakarta Barat (Jakbar), ...</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677457/bps-catat-pengeluaran-wisman-triwulan-ii-2026-mencapai-1285-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5678108/kebakaran-melanda-gardu-listrik-di-kalideres-jakbar</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG-20260731-WA0028.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_192552.v1.jpg</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Kapal Pertamina selamatkan 17 korban KMP Mutiara Sentosa 2</t>
+          <t>Pemkab Sigi gandeng ESDM Sulteng cek semburan air bergas di Palolo</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:52:47 +0700</t>
+          <t>Mon, 03 Aug 2026 19:33:01 +0700</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Kapal Pertamina Patra Niaga MT Transko Arafura berhasil mengevakuasi 17 orang korban KMP Mutiara Sentosa 2 yang ...</t>
+          <t>Pemerintah Kabupaten (Pemkab) Sigi melibatkan Dinas Energi dan Sumber Daya Mineral (ESDM) Provinsi Sulawesi Tengah ...</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677445/kapal-pertamina-selamatkan-17-korban-kmp-mutiara-sentosa-2</t>
+          <t>https://www.antaranews.com/berita/5678101/pemkab-sigi-gandeng-esdm-sulteng-cek-semburan-air-bergas-di-palolo</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-14.30.38.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/380393.jpg</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PGN sasar pemanfaatan jargas untuk hotel hingga UMKM</t>
+          <t>Tolak prostetik Rp2 miliar, Denny Sumargo rela botak di film Baby Udon</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:50:20 +0700</t>
+          <t>Mon, 03 Aug 2026 19:32:21 +0700</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>PT Perusahaan Gas Negara (Persero) Tbk (PGN) menyasar pemanfaatan jaringan gas (jargas) tidak hanya rumah ...</t>
+          <t>Aktor Denny Sumargo mengaku terpaksa mencukur habis rambutnya hingga botak di film "Baby Udon" karena menolak ...</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677439/pgn-sasar-pemanfaatan-jargas-untuk-hotel-hingga-umkm</t>
+          <t>https://www.antaranews.com/berita/5678097/tolak-prostetik-rp2-miliar-denny-sumargo-rela-botak-di-film-baby-udon</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_2395.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_143755_BURST013.jpg</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CORE: Harga Pertamax turun beri sentimen positif bagi inflasi</t>
+          <t>Pekan ini ASDP terapkan penuh sterilisasi pelabuhan Ketapang-Gilimanuk</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:40:44 +0700</t>
+          <t>Mon, 03 Aug 2026 19:31:55 +0700</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Ekonom Center of Reform on Economics (CORE) Yusuf Rendy Manilet menyampaikan penurunan harga Pertamax pada bulan ...</t>
+          <t>PT ASDP Indonesia Ferry (Persero) menyatakan mulai 5 Agustus 2026 mengimplementasikan penerapan penuh sterilisasi ...</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677420/core-harga-pertamax-turun-beri-sentimen-positif-bagi-inflasi</t>
+          <t>https://www.antaranews.com/berita/5678096/pekan-ini-asdp-terapkan-penuh-sterilisasi-pelabuhan-ketapang-gilimanuk</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/penurunan-harga-bbm-jenis-pertamax-2831783.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/MG_6844.jpg</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Askrindo bukukan laba Rp1,69 T pada 2025 ditopang tiga lini bisnis</t>
+          <t>Prabowo: Kemitraan RI dan Thailand harus berdampak bagi rakyat</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:38:49 +0700</t>
+          <t>Mon, 03 Aug 2026 19:31:06 +0700</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>PT Asuransi Kredit Indonesia (Persero) atau Askrindo membukukan laba setelah pajak sebesar Rp1,69 triliun pada 2025 ...</t>
+          <t>Presiden Prabowo Subianto menegaskan pertemuan bilateral dengan Perdana Menteri Thailand Anutin Charnvirakul di Istana ...</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677419/askrindo-bukukan-laba-rp169-t-pada-2025-ditopang-tiga-lini-bisnis</t>
+          <t>https://www.antaranews.com/berita/5678092/prabowo-kemitraan-ri-dan-thailand-harus-berdampak-bagi-rakyat</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-08.51.32.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/presiden-prabowo-menerima-kunjungan-pm-thailand-2833223.jpg</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Jasaraharja Putera menjamin santunan korban KMP Mutiara Sentosa II</t>
+          <t>Mobil parkir sembarangan selama seminggu di Tebet Jaksel ditertibkan</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:30:17 +0700</t>
+          <t>Mon, 03 Aug 2026 19:30:07 +0700</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>PT Jasaraharja Putera menjamin perlindungan dan santunan bagi seluruh korban kebakaran Kapal Motor Penyeberangan (KMP) ...</t>
+          <t>Suku Dinas Perhubungan Jakarta Selatan (Sudinhub Jaksel) menertibkan mobil yang parkir sembarangan selama seminggu di ...</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677412/jasaraharja-putera-menjamin-santunan-korban-kmp-mutiara-sentosa-ii</t>
+          <t>https://www.antaranews.com/berita/5678088/mobil-parkir-sembarangan-selama-seminggu-di-tebet-jaksel-ditertibkan</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176259.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001010421.jpg</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>GMR bidik Indonesia dalam perluasan rute Bandara Bhogapuram India</t>
+          <t>Jumlah penumpang angkutan umum di Jakarta meningkat pada Juni 2026</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:29:34 +0700</t>
+          <t>Mon, 03 Aug 2026 19:23:04 +0700</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>GMR Airports Limited (GMR Airports), salah satu pengelola jaringan bandara internasional, memprioritaskan Indonesia ...</t>
+          <t>Badan Pusat Statistik (BPS) DKI Jakarta menyampaikan jumlah penumpang angkutan umum di Jakarta, yakni MRT Jakarta, LRT ...</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677407/gmr-bidik-indonesia-dalam-perluasan-rute-bandara-bhogapuram-india</t>
+          <t>https://www.antaranews.com/berita/5678083/jumlah-penumpang-angkutan-umum-di-jakarta-meningkat-pada-juni-2026</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0725.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/01/1000299365.jpg</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>terkini, top-news</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>BPS: Wisman per Juni capai 7,45 juta kunjungan, tertinggi sejak 2020</t>
+          <t>Prabowo dukung peningkatan latihan bersama militer RI-Thailand</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:22:48 +0700</t>
+          <t>Mon, 03 Aug 2026 19:21:32 +0700</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat total kunjungan wisatawan mancanegara dari Januari hingga bulan Juni 2026 mencapai ...</t>
+          <t>Presiden Prabowo Subianto mendukung peningkatan frekuensi latihan bersama antara Tentara Nasional Indonesia (TNI) dan ...</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677399/bps-wisman-per-juni-capai-745-juta-kunjungan-tertinggi-sejak-2020</t>
+          <t>https://www.antaranews.com/berita/5678081/prabowo-dukung-peningkatan-latihan-bersama-militer-ri-thailand</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/pelepasliaran-500-ekor-tukik-bali-290726-nhw-3_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.41.07.jpeg</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>BPS catat nilai tukar petani di level 127,84 pada Juli 2026</t>
+          <t>GMR Group menilai Danantara tingkatkan kepercayaan investor asing</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:18:40 +0700</t>
+          <t>Mon, 03 Aug 2026 19:18:34 +0700</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat nilai tukar petani (NTP) secara nasional pada bulan Juli 2026 berada di level ...</t>
+          <t>GMR Group, perusahaan multinasional yang bergerak di bidang infrastruktur, menilai adanya Badan Pengelola Investasi ...</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677323/bps-catat-nilai-tukar-petani-di-level-12784-pada-juli-2026</t>
+          <t>https://www.antaranews.com/berita/5678080/gmr-group-menilai-danantara-tingkatkan-kepercayaan-investor-asing</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/02/20260302_083324.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/5b406f4a-aeea-42ae-9194-16c4cace22d9.jpeg</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Menteri ATR sebut 400 Kantah sudah terapkan pengukuran terjadwal</t>
+          <t>Dukcapil Kepulauan Seribu terbaik dalamcapaian IKD di Rakornas 2026</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:13:29 +0700</t>
+          <t>Mon, 03 Aug 2026 19:17:51 +0700</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Menteri Agraria dan Tata Ruang/Kepala Badan Pertanahan Nasional (ATR/BPN) Nusron Wahid mengatakan bahwa sudah ada 400 ...</t>
+          <t>Suku Dinas Kependudukan dan Catatan Sipil (Sudin Dukcapil) Kabupaten Kepulauan Seribu menjadi yang terbaik dalam ...</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677308/menteri-atr-sebut-400-kantah-sudah-terapkan-pengukuran-terjadwal</t>
+          <t>https://www.antaranews.com/berita/5678072/dukcapil-kepulauan-seribu-terbaik-dalamcapaian-ikd-di-rakornas-2026</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_125328.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Screen-Shot-2026-08-03-at-18.15.44.jpg</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>IHSG awal pekan berpotensi variatif seiring sentimen global-domestik</t>
+          <t>BYD masih menyelidiki mobil listrik yang terbakar di Cikampek</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:42:28 +0700</t>
+          <t>Mon, 03 Aug 2026 19:17:16 +0700</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin berpotensi bergerak variatif dipicu oleh ...</t>
+          <t>Tim BYD Motor Indonesia masih menyelidiki mobil listrik yang terbakar di dekat gerbang jalan tol Cikampek di ...</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677104/ihsg-awal-pekan-berpotensi-variatif-seiring-sentimen-global-domestik</t>
+          <t>https://otomotif.antaranews.com/berita/5678069/byd-masih-menyelidiki-mobil-listrik-yang-terbakar-di-cikampek</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/12/12/ihsg-ditutup-menguat-2688871.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_3319.jpeg</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>humaniora</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Bantuan beras 30 kg cair mulai 17 Agustus 2026, ini jadwal dan cara cek penerimanya</t>
+          <t>BPS Bali: Panen melimpah dan permintaan tinggi buat makanan deflasi</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:27:14 +0700</t>
+          <t>Mon, 03 Aug 2026 19:16:38 +0700</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Pemerintah memastikan penyaluran bantuan pangan beras tahap II tahun 2026 akan dimulai pada 17 Agustus 2026. Bantuan ...</t>
+          <t>Badan Pusat Statistik (BPS) Bali melihat panen yang melimpah dan permintaan yang tinggi menyebabkan sejumlah komoditas ...</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677341/bantuan-beras-30-kg-cair-mulai-17-agustus-2026-ini-jadwal-dan-cara-cek-penerimanya</t>
+          <t>https://www.antaranews.com/berita/5678065/bps-bali-panen-melimpah-dan-permintaan-tinggi-buat-makanan-deflasi</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/26/kemensos-percepat-penyaluran-bansos-pkh-dan-bpnt-2778877.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0326.jpeg</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>10 ide lomba 17 Agustus untuk anak PAUD dan TK yang seru, edukatif, dan mudah digelar</t>
+          <t>Program Taruna Bakti Kepolisian latih siswa Sekolah Rakyat Lhokseumawe</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:38:29 +0700</t>
+          <t>Mon, 03 Aug 2026 19:15:13 +0700</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Perayaan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 dapat menjadi momen bagi anak usia PAUD dan TK ...</t>
+          <t>ANTARA - Ratusan siswa dari Sekolah Rakyat Lhokseumawe, Aceh, memperoleh edukasi kemandirian oleh Taruna Akademi ...</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677368/10-ide-lomba-17-agustus-untuk-anak-paud-dan-tk-yang-seru-edukatif-dan-mudah-digelar</t>
+          <t>https://www.antaranews.com/video/5678013/program-taruna-bakti-kepolisian-latih-siswa-sekolah-rakyat-lhokseumawe</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/08/03/WhatsApp-Image-2024-08-03-at-20.37.28.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_PROGRAM-TARUNA-BAKTI-KEPOLISIAN-LATIH-SISWA-SEKOLAH-RAKYAT-LHOKSEUMAWE.jpg</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Sering terbangun tengah malam? Kenali 7 penyebab dan cara mengatasinya</t>
+          <t>Basarnas terus evakuasi korban kebakaran KMP Mutiara Sentosa II</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:35:20 +0700</t>
+          <t>Mon, 03 Aug 2026 19:14:24 +0700</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Bangun di tengah malam sesekali merupakan hal yang normal. Namun, jika kondisi ini terjadi hampir setiap malam dan ...</t>
+          <t>Badan SAR Nasional terus melakukan evakuasi terhadap korban kebakaran Kapal Motor Penumpang (KMP) Mutiara Sentosa II di ...</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677357/sering-terbangun-tengah-malam-kenali-7-penyebab-dan-cara-mengatasinya</t>
+          <t>https://www.antaranews.com/berita/5678060/basarnas-terus-evakuasi-korban-kebakaran-kmp-mutiara-sentosa-ii</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/20/Penumpang-rela-menginap-menunggu-kereta-pertama-di-Stasiun-Cikarang-150726-ryl-5.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/262391.jpg</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Bahaya paparan pornografi pada anak: Dampak bagi otak, mental, dan perilaku</t>
+          <t>Di hadapan Charnvirakul, Prabowo akui dekat dengan Raja Vajiralongkorn</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:23:03 +0700</t>
+          <t>Mon, 03 Aug 2026 19:13:21 +0700</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Perkembangan teknologi membuat anak-anak dan remaja semakin akrab dengan internet sejak usia dini. Di satu sisi, ...</t>
+          <t>Presiden Prabowo Subianto saat pertemuan bilateral bersama Perdana Menteri (PM) Thailand Anutin Charnvirakul di Istana ...</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677332/bahaya-paparan-pornografi-pada-anak-dampak-bagi-otak-mental-dan-perilaku</t>
+          <t>https://www.antaranews.com/berita/5678059/di-hadapan-charnvirakul-prabowo-akui-dekat-dengan-raja-vajiralongkorn</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/02/ilustrasi-konten-berbau-pornografi.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/9d36af3c-bb87-4f6e-8c20-0b32c63b4cdb.jpeg</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Sudah ngantuk tapi sulit tidur pulas? Ini penyebab dan cara atasinya</t>
+          <t>Inflasi di Sumut sebesar 4,20 persen, emas menjadi penyumbang utama</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:28:54 +0700</t>
+          <t>Mon, 03 Aug 2026 19:12:35 +0700</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Rasa kantuk yang muncul di malam hari seharusnya menjadi pertanda bahwa tubuh siap beristirahat. Namun, tidak sedikit ...</t>
+          <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Sumatera Utara mencatat pada Juli 2026 Sumatera Utara mengalami inflasi ...</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677203/sudah-ngantuk-tapi-sulit-tidur-pulas-ini-penyebab-dan-cara-atasinya</t>
+          <t>https://www.antaranews.com/video/5677867/inflasi-di-sumut-sebesar-420-persenemas-menjadi-penyumbang-utama</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/17/Nafas.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_INFLASI-DI-SUMUT-SEBESAR-4-20-PERSEN-EMAS-MENJADI-PENYUMBANG-UTAMA.jpg</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>ekonomi-finansial, terkini, top-news</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Cara cepat tidur dalam 5 menit, efektif untuk yang sulit pulas</t>
+          <t>OJK: Kredit perbankan tumbuh 12,67 persen capai Rp9.080,9 triliun</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:25:40 +0700</t>
+          <t>Mon, 03 Aug 2026 19:12:24 +0700</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Sulit tidur meski badan sudah terasa lelah merupakan masalah yang kerap dialami banyak orang. Kondisi ini sering ...</t>
+          <t>Otoritas Jasa Keuangan (OJK) melaporkan penyaluran kredit perbankan di tanah air tumbuh 12,67 persen year on year ...</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677199/cara-cepat-tidur-dalam-5-menit-efektif-untuk-yang-sulit-pulas</t>
+          <t>https://www.antaranews.com/berita/5678057/ojk-kredit-perbankan-tumbuh-1267-persen-capai-rp90809-triliun</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/11/04/tidua.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.15.18_1.jpeg</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>tekno</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Cara mengganti password WiFi lewat HP dan laptop dengan mudah</t>
+          <t>Tim PKM-K USK raih pendanaan nasional dari inovasi nilam</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:16:14 +0700</t>
+          <t>Mon, 03 Aug 2026 19:11:12 +0700</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>WiFi yang tiba-tiba terasa lambat padahal sinyal penuh dan kuota internet masih banyak tentu membuat kesal. Salah satu ...</t>
+          <t>Tim Program Kreativitas Mahasiswa Bidang Kewirausahaan (PKM-K) Universitas Syiah Kuala (USK) meraih pendanaan nasional ...</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677312/cara-mengganti-password-wifi-lewat-hp-dan-laptop-dengan-mudah</t>
+          <t>https://www.antaranews.com/berita/5678056/tim-pkm-k-usk-raih-pendanaan-nasional-dari-inovasi-nilam</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2020/08/19/antarafoto-warga-sediakan-internet-gratis-bagi-pelajar-190820-ief-2-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/pamer-sera.jpeg</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Petani berbagi air sumur demi selamatkan tanaman tembakau</t>
+          <t>Prabowo sebut Indonesia dan Thailand perlu lebih sering bertemu</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:44:51 +0700</t>
+          <t>Mon, 03 Aug 2026 19:10:55 +0700</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Petani mengambil air dari sumur untuk menyiram tanaman tembakau di Lengkong, Nganjuk, Jawa Timur, Senin (3/8/2026). Sejumlah petani di kawasan tersebut saling berbagi air sumur untuk menjaga pasokan air irigasi dan mempertahankan produktivitas lahan di tengah terbatasnya ketersediaan air pada musim kemarau akibat El Nino. ANTARA FOTO/Muhammad Mada/tom.</t>
+          <t>Presiden RI Prabowo Subianto mendorong intensifikasi pertemuan dan koordinasi berkala antara Indonesia dan Thailand ...</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5677428/petani-berbagi-air-sumur-demi-selamatkan-tanaman-tembakau</t>
+          <t>https://www.antaranews.com/berita/5678053/prabowo-sebut-indonesia-dan-thailand-perlu-lebih-sering-bertemu</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/petani-tembakau-berbagi-air-sumur-antisipasi-dampak-el-nino-030826-mm-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/presiden-prabowo-menerima-kunjungan-pm-thailand-2833227.jpg</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Pemerintah bangun 1.416 Jembatan Garuda untuk hubungkan desa terpencil</t>
+          <t>Persela fokus bangun kekompakan tim melalui pemusatan latihan</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 12:53:00 +0700</t>
+          <t>Mon, 03 Aug 2026 19:09:07 +0700</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Foto udara pengendara sepeda motor melintasi Jembatan Gantung Garuda yang menghubungkan Desa Kertarahayu dan Desa Jayasampurna di Kabupaten Bekasi, Jawa Barat, Senin (3/8/2026). Hingga akhir Juli 2026, pemerintah telah membangun 1.416 unit Jembatan Garuda di daerah terpencil yang menghubungkan 7.371 desa dan kelurahan untuk mempermudah akses masyarakat serta mempersingkat waktu tempuh. ANTARA FOTO/Darryl Ramadhan/tom.</t>
+          <t>Persela Lamongan memfokuskan program pemusatan latihan (training camp/TC) dalam waktu dekat untuk membangun kekompakan ...</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5677284/pemerintah-bangun-1416-jembatan-garuda-untuk-hubungkan-desa-terpencil</t>
+          <t>https://www.antaranews.com/berita/5678051/persela-fokus-bangun-kekompakan-tim-melalui-pemusatan-latihan</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/Pembangunan-Jembatan-Garuda-percepat-akses-desa-030826-ryl-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_2426.jpeg</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Petugas evakuasi dua jenazah korban kebakaran KM Mutiara Sentosa II</t>
+          <t>Mensos nilai model penjangkauan Sekolah Rakyat Gresik efektif</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:03:11 +0700</t>
+          <t>Mon, 03 Aug 2026 19:06:21 +0700</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Sejumlah petugas mengangkat kantong berisi jenazah korban kebakaran KM Mutiara Sentosa II setelah tiba di Dermaga Jamrud Utara, Pelabuhan Tanjung Perak, Surabaya, Jawa Timur, Senin (3/8/2026). Kapal kargo Meratus Pematang Siantar mengevakuasi 111 penumpang selamat dan dua jenazah korban kebakaran KM Mutiara Sentosa II di perairan utara Madura pada Minggu (2/8). ANTARA FOTO/Didik Suhartono/tom.</t>
+          <t>Menteri Sosial (Mensos) Saifullah Yusuf menilai model penjangkauan calon peserta didik Sekolah Rakyat Terintegrasi ...</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5677056/petugas-evakuasi-dua-jenazah-korban-kebakaran-km-mutiara-sentosa-ii</t>
+          <t>https://www.antaranews.com/berita/5678047/mensos-nilai-model-penjangkauan-sekolah-rakyat-gresik-efektif</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/korban-kebakaran-km-mutiara-sentosa-2-030826-Ds-4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_2424.jpeg</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Menkomdigi kukuhkan komisioner KI Pusat, perkuat keterbukaan informasi</t>
+          <t>Gubernur Lampung: Satelit Lampung-1 hadirkan data perkuat tata kelola</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+          <t>Mon, 03 Aug 2026 19:03:30 +0700</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengambil sumpah jabatan dan mengukuhkan tujuh anggota Komisi Informasi Pusat (KIP) Periode 2026–2030 di Kantor Kementerian Komdigi Jakarta, Senin (3/8).  Komisioner KI Pusat Periode 2026–2030 akan melanjutkan tugas dan fungsi komisioner sebelumnya, yakni penyelesaian sengketa informasi publik secara adil, menetapkan kebijakan teknis di bidang keterbukaan informasi, dan memperkuat implementasi UU Nomor 14 Tahun 2008 tentang Keterbukaan Informasi Publik. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
+          <t>Gubernur Lampung Rahmat Mirzani Djausal mengatakan bahwa adanya Satelit Lampung-1 dapat menghadirkan data yang dapat ...</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677604/menkomdigi-kukuhkan-komisioner-ki-pusat-perkuat-keterbukaan-informasi</t>
+          <t>https://www.antaranews.com/berita/5678045/gubernur-lampung-satelit-lampung-1-hadirkan-data-perkuat-tata-kelola</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-KUKUHKAN-KOMISIONER-KI-PUSAT-PERKUAT-KETERBUKAAN-INFORMASI.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/aiOrWseraa2O3uCaQVIZM4OV576Qw9W8bnYIuRFD-1.jpg</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Partai Buruh Brasil calonkan Lula da Silva untuk masa jabatan keempat</t>
+          <t>Kemenperin meyakini pasar industri olahraga RI terus meningkat</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
+          <t>Mon, 03 Aug 2026 19:03:16 +0700</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
+          <t>Kementerian Perindustrian (Kemenperin) meyakini pasar industri olahraga nasional terus meningkat seiring perubahan gaya ...</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678041/kemenperin-meyakini-pasar-industri-olahraga-ri-terus-meningkat</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/AIS_0039_1.JPG-1-_edit_223911681240831.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>photo, terkini</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>TNI AL gagalkan penyelundupan pasir timah di Kepri</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:01:39 +0700</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Dankodaeral IV Laksamana Muda TNI Berkat Widjanarko (kanan) dan Kepala Seksi Tindak Pidana Umum Pada Kejaksaan Negeri ...</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5678039/tni-al-gagalkan-penyelundupan-pasir-timah-di-kepri</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Pengagalan-Penyelundupan-Pasir-Timah-Ilegal-030826-Adm-7.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Menkomdigi minta masyarakat waspadai lonjakan hoaks jelang HUT RI</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:01:26 +0700</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengingatkan masyarakat untuk mewaspadai meningkatnya penyebaran ...</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5677959/menkomdigi-minta-masyarakat-waspadai-lonjakan-hoaks-jelang-hut-ri</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_MENKOMDIGI-MINTA-MASYARAKAT-WASPADAI-LONJAKAN-HOAKS-JELANG-HUT-RI.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Ketegangan geopolitik, Prancis perketat pengawasan investasi asing</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:00:58 +0700</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Prancis telah memperketat kontrol terhadap investasi asing di perusahaan-perusahaan strategis, menurunkan ambang batas ...</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678037/ketegangan-geopolitik-prancis-perketat-pengawasan-investasi-asing</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/28/Prancis.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>terkini, top-news</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Menkomdigi: KIP garda depan informasi jernih dan perangi hoaks</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:00:50 +0700</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid mengatakan Komisi Informasi Pusat (KIP) menjadi garda terdepan ...</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678033/menkomdigi-kip-garda-depan-informasi-jernih-dan-perangi-hoaks</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0321.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Sulbar dan UGM gelar pangan murah stabilisasi harga pangan</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:59:54 +0700</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi Sulawesi Barat berkolaborasi dengan Universitas Gadjah Mada (UGM) melalui program KKN-PPM UGM ...</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678031/sulbar-dan-ugm-gelar-pangan-murah-stabilisasi-harga-pangan</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_191550.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Inggris pangkas anggaran kesehatan mental Rp605 miliar</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:59:30 +0700</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>London Mental Health Foundation berencana memangkas biaya lebih dari 25 juta pound sterling (sekitar ...</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678028/inggris-pangkas-anggaran-kesehatan-mental-rp605-miliar</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/22/Inggris.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>terkini, top-news</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Satu tahun Sekolah Rakyat, ratusan siswa torehkan prestasi</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:59:25 +0700</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Menteri Sosial (Mensos) Saifullah Yusuf menyatakan selama satu tahun Sekolah Rakyat berdiri sudah ratusan ...</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678024/satu-tahun-sekolah-rakyat-ratusan-siswa-torehkan-prestasi</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176441.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Belgia peringatkan gelombang panas, suhu tembus 36 derajat Celsius</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:57:57 +0700</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Institut Meteorologi Kerajaan Belgia mengeluarkan peringatan panas oranye untuk sebagian besar wilayah negara itu, ...</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678021/belgia-peringatkan-gelombang-panas-suhu-tembus-36-derajat-celsius</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/30/panas-ekstrem-Eropa.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Brantas Abipraya rampungkan Sekolah Rakyat Terintegrasi Cirebon</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:56:19 +0700</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>PT Brantas Abipraya (Persero) merampungkan pembangunan Sekolah Rakyat Terintegrasi Kabupaten Cirebon yang memasuki ...</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678019/brantas-abipraya-rampungkan-sekolah-rakyat-terintegrasi-cirebon</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/4643878B-8428-4EFC-9266-E070C27E50CC.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Pemkot Jakbar vaksinasi HPV ratusan siswa di SDN Meruya Utara 02</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:56:15 +0700</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota (Pemkot) Jakarta Barat (Jakbar) menggelar vaksinasi Human Papillomavirus (HPV) bagi murid laki-laki di ...</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678017/pemkot-jakbar-vaksinasi-hpv-ratusan-siswa-di-sdn-meruya-utara-02</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_181232.v1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Bahlil prioritaskan relaksasi RKAB untuk perusahaan royalti tinggi</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:53:41 +0700</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia memprioritaskan relaksasi Rencana Kerja dan Anggaran ...</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678009/bahlil-prioritaskan-relaksasi-rkab-untuk-perusahaan-royalti-tinggi</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-16.12.45-1.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini, top-news</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Menkeu: Realisasi anggaran MBG Rp101,1 T untuk 63,13 juta penerima</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:53:14 +0700</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa mengungkapkan bahwa realisasi anggaran Program Makan Bergizi Gratis ...</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678005/menkeu-realisasi-anggaran-mbg-rp1011-t-untuk-6313-juta-penerima</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29-2.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Menhan sebut program P3MD tepat untuk ciptaan SDM berkualitas</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:51:19 +0700</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Menteri Pertahanan Sjafrie Sjamsoeddin mengatakan Program Presiden untuk Pemimpin Masa Depan (P3MD) merupakan program ...</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678004/menhan-sebut-program-p3md-tepat-untuk-ciptaan-sdm-berkualitas</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001554793.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Kemensos luncurkan Taman Anak Sejahtera di Banyumas</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:50:24 +0700</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Kementerian Sosial melalui Direktorat Rehabilitasi Sosial Anak menggelar meluncurkan Taman Anak Sejahtera (TAS) dalam ...</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678000/kemensos-luncurkan-taman-anak-sejahtera-di-banyumas</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176439.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>JustMarkets mendedahkan bagaimana kejutan IHP memacu turun naik pasaran forex</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:47:49 +0700</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>JustMarkets baru sahaja mengeluarkan pandangan tentang bagaimana kejutan IHP benar-benar memacu turun naik pasaran ...</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677996/justmarkets-mendedahkan-bagaimana-kejutan-ihp-memacu-turun-naik-pasaran-forex</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/02/05/Logo-cision_2.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Polisi buru pelaku illegal tapping pipa Pertamina di lintas Sumatera</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:47:43 +0700</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Tim Kepolisian Resor (Polres) Jambi tengah memburu para pelaku pencurian minyak dengan cara illegal tapping pada pipa ...</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677995/polisi-buru-pelaku-illegal-tapping-pipa-pertamina-di-lintas-sumatera</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/363585.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Departemen Perang AS jalani misi napak tilas Perang Dunia II di Biak</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:47:23 +0700</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Sebuah tim Departemen Perang Amerika Serikat merampungkan misi napak tilas pencarian artefak sejarah dan jenazah ...</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677992/departemen-perang-as-jalani-misi-napak-tilas-perang-dunia-ii-di-biak</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Biak1-9900000000079e3c.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Kisah haru Lia Maharani saat pertama pakai seragam baru Sekolah Rakyat</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:47:01 +0700</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Membelikan seragam sekolah baru untuk anak menjadi momen biasa bagi sebagian orang tua murid. Namun, tidak bagi Titin ...</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677989/kisah-haru-lia-maharani-saat-pertama-pakai-seragam-baru-sekolah-rakyat</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176437.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>terkini, top-news</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Polri perkuat langkah preventif respons isu keamanan nasional</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:46:34 +0700</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Polri memastikan terus memperkuat langkah preventif untuk menjaga keamanan nasional sehingga aktivitas masyarakat dan ...</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677985/polri-perkuat-langkah-preventif-respons-isu-keamanan-nasional</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/1000086556.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Jaksel sterilisasi 441 ekor kucing selama Juli untuk tekan populasi</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:46:24 +0700</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Suku Dinas Ketahanan Pangan Kelautan dan Pertanian (Sudin KPKP) Jakarta Selatan (Jaksel) telah melakukan ...</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677981/jaksel-sterilisasi-441-ekor-kucing-selama-juli-untuk-tekan-populasi</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001010408.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Milken Institute Umumkan Asia Summit 2026, Dorong Kepemimpinan Cerdas di Era AI</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:44:50 +0700</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Di tengah meningkatnya ketegangan geopolitik global dan kemajuan teknologi yang pesat, Milken Institute menggelar ...</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677977/milken-institute-umumkan-asia-summit-2026-dorong-kepemimpinan-cerdas-di-era-ai</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/10/08/Milken_Institute_Logo.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Swalayan UMKM Kotim diproyeksikan jadi sentra oleh-oleh khas daerah</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:44:01 +0700</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Pemerintah Kabupaten Kotawaringin Timur (Kotim), Kalimantan Tengah menyiapkan Swalayan Usaha Mikro, Kecil dan Menengah ...</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677976/swalayan-umkm-kotim-diproyeksikan-jadi-sentra-oleh-oleh-khas-daerah</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001719121.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Prabowo dan PM Thailand bertemu empat mata di Istana Merdeka</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 17:49:52 +0700</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto dan Perdana Menteri Thailand Anutin Charnvirakul menggelar pertemuan empat mata di Istana ...</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677828/prabowo-dan-pm-thailand-bertemu-empat-mata-di-istana-merdeka</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_5162.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Kepala BGN tingkatkan status keracunan MBG jadi kejadian fatal</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 17:10:19 +0700</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>nya tidak dilanjutkan," ucap Sudaryono.
+Ia menegaskan BGN memberlakukan nol toleransi pada setiap status ...</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677743/kepala-bgn-tingkatkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/ZAM02548_edit_2028523819372755.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Harga minyak turun usai AS siap lanjutkan dialog dengan Iran</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 17:08:35 +0700</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Harga minyak turun lebih dari 5 persen, Senin, setelah Presiden Amerika Serikat Donald Trump ...</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677735/harga-minyak-turun-usai-as-siap-lanjutkan-dialog-dengan-iran</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/06/ilustrasi-isi-bensin-di-pom.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Australia konfirmasi kematian massal pertama satwa akibat flu burung</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:48:50 +0700</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Australia mengonfirmasi kematian massal satwa liar pertama terkait flu burung H5 yang mematikan, dengan burung camar ...</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677701/australia-konfirmasi-kematian-massal-pertama-satwa-akibat-flu-burung</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/26/Virus-flu-burung-penyakit-unggas.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Siklon 94 W,  waspada cuaca ekstrem &amp; gelombang tinggi di wilayah RI</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:30:38 +0700</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) mendeteksi pergerakan Bibit Siklon Tropis 94W di Laut Filipina ...</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677641/siklon-94-w-waspada-cuaca-ekstrem-gelombang-tinggi-di-wilayah-ri</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/27/1000395034.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>photo, top-news</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Petani berbagi air sumur demi selamatkan tanaman tembakau</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 14:44:51 +0700</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Petani mengambil air dari sumur untuk menyiram tanaman tembakau di Lengkong, Nganjuk, Jawa Timur, Senin (3/8/2026). ...</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5677428/petani-berbagi-air-sumur-demi-selamatkan-tanaman-tembakau</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/petani-tembakau-berbagi-air-sumur-antisipasi-dampak-el-nino-030826-mm-1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Nusron sebut banyak laut di Batam telah dikapling tanpa prosedur sah</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 14:44:05 +0700</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Menteri Agraria dan Tata Ruang (ATR)/Kepala Badan Pertanahan Nasional (BPN) Nusron Wahid mengatakan, menerima banyak ...</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677425/nusron-sebut-banyak-laut-di-batam-telah-dikapling-tanpa-prosedur-sah</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_142345.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Menkomdigi panggil YouTube imbas temuan konten promosi vape sasar anak</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 14:22:09 +0700</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid merencanakan pemanggilan terhadap platform digital YouTube ...</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677396/menkomdigi-panggil-youtube-imbas-temuan-konten-promosi-vape-sasar-anak</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0225.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Kemnaker: Magang Nasional diharapkan menekan angka pengangguran muda</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:37:57 +0700</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Kementerian Ketenagakerjaan (Kemnaker) mengatakan program Magang Nasional (MagangHub) untuk mempersiapkan kompetensi ...</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677364/kemnaker-magang-nasional-diharapkan-menekan-angka-pengangguran-muda</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/ff63afaf-7778-47fe-833d-5a8068af9a51_1.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Kemenag perkuat transformasi madrasah lewat revitalisasi-digitalisasi</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:36:36 +0700</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Menteri Agama (Menag) Nasaruddin Umar menegaskan transformasi madrasah terus diperkuat melalui revitalisasi ...</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677363/kemenag-perkuat-transformasi-madrasah-lewat-revitalisasi-digitalisasi</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/14/1000173935_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Lisensi IP Global Buka Peluang Bisnis Baru bagi Kreator Indonesia</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:34:30 +0700</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Ekonomi Kreatif Irene Umar mengatakan kolaborasi antara pemilik kekayaan intelektual (Intellectual ...</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677353/lisensi-ip-global-buka-peluang-bisnis-baru-bagi-kreator-indonesia</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000589873.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Nilai ekspor perdagangan RI Januari-Juni capai 140,81 miliar dolar AS</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:16:17 +0700</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) mencatat nilai ekspor Indonesia secara kumulatif dari Januari-Juni 2026 mencapai 140,81 ...</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677315/nilai-ekspor-perdagangan-ri-januari-juni-capai-14081-miliar-dolar-as</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/neraca-perdagangan-januari-mei-2026-surplus-2815779.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Korban KMP Mutiara Sentosa II dievakuasi ke Pelabuhan Tanjung Perak</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:06:15 +0700</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Tim SAR gabungan terus melakukan evakuasi korban terbakarnya KMP Mutiara Sentosa 2 ke darat, tepatnya ke Pelabuhan ...</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677297/korban-kmp-mutiara-sentosa-ii-dievakuasi-ke-pelabuhan-tanjung-perak</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/260821_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Aktor senior Diding Boneng meninggal dunia</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 11:39:03 +0700</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Aktor sekaligus komedian tanah air, Zainal Abidin alias Diding Boneng dikabarkan meninggal dunia pada Senin (3/8) dalam ...</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677209/aktor-senior-diding-boneng-meninggal-dunia</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/26f1eb88-3301-4ae1-badd-bed5078fe3dd.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Seskab: Prabowo dorong sinergi pemerintah dan dunia usaha</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 11:17:50 +0700</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Sekretaris Kabinet Teddy Indra Wijaya menyampaikan bahwa Presiden Prabowo Subianto menekankan pentingnya sinergi antara ...</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677191/seskab-prabowo-dorong-sinergi-pemerintah-dan-dunia-usaha</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0891_1.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Red Velvet bersiap kembali lewat EP baru "Velvet Summer"</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 10:24:37 +0700</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Grup idola K-pop Red Velvet akan kembali lewat rilis mini album atau extended play (EP) baru bertajuk “Velvet ...</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677151/red-velvet-bersiap-kembali-lewat-ep-baru-velvet-summer</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/ca97a3a8-aa17-45fc-be71-d36051dd9dcd.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Menaker pastikan komitmen pemerintah perkuat kesejahteraan pekerja</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 10:16:19 +0700</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Menteri Ketenagakerjaan (Menaker) Yassierli memastikan pemerintah berkomitmen untuk memperkuat kesejahteraan, ...</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677148/menaker-pastikan-komitmen-pemerintah-perkuat-kesejahteraan-pekerja</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/09/20/pelepasan-peserta-pemagangan-ke-jepang-di-jawa-barat-2627513.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>23 calon hakim agung dan ad hoc ikuti seleksi wawancara akhir</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 10:15:01 +0700</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Sebanyak 23 orang calon hakim agung dan ad hoc Mahkamah Agung Tahun 2026 mengikuti seleksi wawancara tahap akhir di ...</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677137/23-calon-hakim-agung-dan-ad-hoc-ikuti-seleksi-wawancara-akhir</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000012883_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>BRIN perkuat kajian sungai bawah tanah di Kebumen untuk ketahanan air</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 09:57:19 +0700</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Badan Riset dan Inovasi Nasional (BRIN) memperkuat riset ketahanan air melalui pengembangan teknologi dan penelitian ...</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677120/brin-perkuat-kajian-sungai-bawah-tanah-di-kebumen-untuk-ketahanan-air</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1785706440-47672950-1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Harga bensin turun pada pekan pertama Agustus</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 09:51:00 +0700</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Harga bahan bakar minyak (BBM) jenis bensin di stasiun pengisian bahan bakar umum (SPBU) Pertamina, Shell, dan bp ...</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677109/harga-bensin-turun-pada-pekan-pertama-agustus</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/10/02/penuruanan-harga-bbm-011024-aaa-7.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Sean Gelael berbagi pengalaman di dunia balap ke pengunjung GIIAS 2026</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 09:34:53 +0700</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Pembalap Indonesia Sean Gelael berbagi pengalamannya di dunia balap ke pengunjung GAIKINDO Indonesia International ...</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677103/sean-gelael-berbagi-pengalaman-di-dunia-balap-ke-pengunjung-giias-2026</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/16b70b87-326f-479a-a806-580ab846cc6f_1.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>ekonomi-bursa, top-news</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>IHSG Senin dibuka menguat 36,49 poin ke posisi 6.272</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 09:11:26 +0700</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin pagi dibuka menguat 36,49 poin atau 0,59 ...</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677071/ihsg-senin-dibuka-menguat-3649-poin-ke-posisi-6272</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/pergerakan-indeks-harga-saham-gabungan-2828631.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>PLN Jakarta pastikan pasokan listrik sudah berhasil dipulihkan</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 08:36:26 +0700</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>PT PLN (Persero) Unit Induk Distribusi Jakarta Raya mengungkapkan pasokan listrik telah berhasil ...</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677043/pln-jakarta-pastikan-pasokan-listrik-sudah-berhasil-dipulihkan</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20231217-WA0015-1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Ledakan di kantor polisi Pakistan tewaskan 14 orang</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 07:44:23 +0700</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Sebuah ledakan terjadi di luar sebuah kantor polisi di Kota Kabal, Pakistan, mengakibatkan 14 orang tewas dan 14 orang ...</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677020/ledakan-di-kantor-polisi-pakistan-tewaskan-14-orang</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CmxztpE000019_20260803_PEPFN0A001.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>KSSK prakirakan pertumbuhan ekonomi RI pada 2026 capai 5,6-6 persen</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:28:16 +0700</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Komite Stabilitas Sistem Keuangan (KSSK) memprakirakan ekonomi Indonesia sepanjang 2026 tumbuh dalam kisaran ...</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677935/kssk-prakirakan-pertumbuhan-ekonomi-ri-pada-2026-capai-56-6-persen</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.19.55.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Rupiah menguat dipengaruhi PMI manufaktur Indonesia naik jadi 50,2</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:58:46 +0700</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah terhadap dolar AS pada penutupan perdagangan Senin, bergerak menguat 25 poin atau 0,14 persen ...</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677712/rupiah-menguat-dipengaruhi-pmi-manufaktur-indonesia-naik-jadi-502</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/12/nilai-tukar-rupiah-melemah-115-poin-2788415.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>KSSK: Sistem keuangan TW-II tetap terjaga di tengah konflik geopolitik</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:26:03 +0700</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Komite Stabilitas Sistem Keuangan (KSSK) menilai kondisi fiskal, moneter dan sektor keuangan selama triwulan II 2026 ...</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677625/kssk-sistem-keuangan-tw-ii-tetap-terjaga-di-tengah-konflik-geopolitik</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Menjaga pintu air perekonomian Indonesia</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:04:40 +0700</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Bayangkan perekonomian Indonesia sebagai sebuah bendungan raksasa yang mengairi hamparan persawahan. Air yang mengalir ...</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677565/menjaga-pintu-air-perekonomian-indonesia</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/06/peringati-hari-bank-indonesia-doku-perkuat-ekosistem-pembayaran-2817675.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Rupiah diperkirakan menguat seiring AS batalkan rencana serang Iran</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 10:12:26 +0700</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Analis Doo Financial Futures, Lukman Leong memperkirakan rupiah menguat seiring Amerika Serikat (AS) membatalkan ...</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677132/rupiah-diperkirakan-menguat-seiring-as-batalkan-rencana-serang-iran</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828847.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Rupiah pada Senin pagi melemah jadi Rp18.031 per dolar AS</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 09:05:50 +0700</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah pada Senin pagi bergerak melemah 9 poin atau 0,05 persen menjadi Rp18.031 per dolar AS dibandingkan ...</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677063/rupiah-pada-senin-pagi-melemah-jadi-rp18031-per-dolar-as</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Komisi XI: PFII peluang RI tangkap momentum perpindahan modal global</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 06:53:34 +0700</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Komisi XI DPR RI Mohamad Hekal mengatakan percepatan pembentukan Pusat Finansial Internasional Indonesia ...</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676995/komisi-xi-pfii-peluang-ri-tangkap-momentum-perpindahan-modal-global</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Saham-dan-oblogasi.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>BUMA International Group bukukan pertumbuhan EBITDA semester I/2026</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 06:17:40 +0700</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>PT BUMA Internasional Gorup membukukan pertumbuhan EBITDA pada semester pertama 2026 (1H26) di tengah penurunan ...</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676967/buma-international-group-bukukan-pertumbuhan-ebitda-semester-i-2026</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/buma.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Musim panen tekan harga hortikultura bikin deflasi 0,35 persen di NTB</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:38:20 +0700</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) menyatakan musim panen menekan harga komoditas hortikultura dan memicu deflasi sebesar 0,35 ...</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677956/musim-panen-tekan-harga-hortikultura-bikin-deflasi-035-persen-di-ntb</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001432193.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Wamenperin optimistis PMI manufaktur RI terus meningkat</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:36:38 +0700</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Perindustrian (Wamenperin) Faisol Riza optimistis kinerja manufaktur Indonesia terus mengalami ...</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677952/wamenperin-optimistis-pmi-manufaktur-ri-terus-meningkat</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Wamenperin.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Menkop dorong pembentukan koperasi syariah perluas akses modal</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:34:52 +0700</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Menteri Koperasi (Menkop) Ferry Juliantono mendorong pembentukan koperasi syariah di lingkungan Wanita Pengusaha ...</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677948/menkop-dorong-pembentukan-koperasi-syariah-perluas-akses-modal</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-16.50.13.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Ekonom: Hilirisasi nikel perlu diimbangi penguatan ekspor pertanian</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:23:50 +0700</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Ekonom Center of Reform on Economics (CORE) Indonesia Yusuf Rendy Manilet menilai keberhasilan hilirisasi nikel dalam ...</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677921/ekonom-hilirisasi-nikel-perlu-diimbangi-penguatan-ekspor-pertanian</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/16/IMG_20251116_190439.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>CORE: Pertumbuhan ekspor ke AS sinyal positif daya saing produk RI</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:19:03 +0700</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Ekonom Center of Reform on Economics (CORE) Indonesia Yusuf Rendy Manilet menilai pertumbuhan ekspor Indonesia ke ...</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677908/core-pertumbuhan-ekspor-ke-as-sinyal-positif-daya-saing-produk-ri</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/28/1001021030.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>ATR/BPN tetapkan 15 Kantah jadi percontohan pelayanan peralihan hak</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:18:57 +0700</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Kementerian Agraria dan Tata Ruang/Badan Pertanahan Nasional (ATR/BPN) menyatakan terdapat 15 Kantor Pertanahan ...</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677904/atr-bpn-tetapkan-15-kantah-jadi-percontohan-pelayanan-peralihan-hak</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_175241.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Lebih maskulin, intip rupa hingga spek Suzuki Fronx SGX Hybrid Kuro</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:15:42 +0700</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Suzuki menghadirkan penyegaran pada varian tertinggi SUV Fronx melalui Suzuki Fronx SGX Hybrid Kuro, tampil lebih ...</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5677893/lebih-maskulin-intip-rupa-hingga-spek-suzuki-fronx-sgx-hybrid-kuro</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_1872.JPG.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>PMI manufaktur naik, Kadin: Didorong peningkatan produksi-permintaan</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:15:15 +0700</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Kamar Dagang dan Industri (Kadin) Indonesia menilai kenaikan Purchasing Managers’ Index (PMI) manufaktur ...</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677892/pmi-manufaktur-naik-kadin-didorong-peningkatan-produksi-permintaan</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/22/WhatsApp-Image-2026-02-22-at-8.24.35-AM_edit_336327027051281.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>ekonomi-bursa</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>OJK: Pasar modal jaga peran sumber pembiayaan di tengah gejolak global</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:33:35 +0700</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Ketua Dewan Komisioner Otoritas Jasa Keuangan (OJK) Friderica Widyasari Dewi alias Kiki memastikan bahwa pasar modal ...</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677944/ojk-pasar-modal-jaga-peran-sumber-pembiayaan-di-tengah-gejolak-global</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.15.18.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>ekonomi-bursa</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>IHSG awal pekan berpotensi variatif seiring sentimen global-domestik</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 09:42:28 +0700</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin berpotensi bergerak variatif dipicu oleh ...</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677104/ihsg-awal-pekan-berpotensi-variatif-seiring-sentimen-global-domestik</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/12/12/ihsg-ditutup-menguat-2688871.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>humaniora</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Bantuan beras 30 kg cair mulai 17 Agustus 2026, ini jadwal dan cara cek penerimanya</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:27:14 +0700</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Pemerintah memastikan penyaluran bantuan pangan beras tahap II tahun 2026 akan dimulai pada 17 Agustus 2026. Bantuan ...</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677341/bantuan-beras-30-kg-cair-mulai-17-agustus-2026-ini-jadwal-dan-cara-cek-penerimanya</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/26/kemensos-percepat-penyaluran-bansos-pkh-dan-bpnt-2778877.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>10 ide usaha menjelang 17 Agustus 2026 yang berpotensi laris dan menguntungkan</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:16:58 +0700</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Momentum peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 dapat menjadi peluang bagi pelaku ...</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677896/10-ide-usaha-menjelang-17-agustus-2026-yang-berpotensi-laris-dan-menguntungkan</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/08/02/sentra-penjualan-bendera-merah-putih-di-surabaya-020824-Ds-3.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>10 ide lomba 17 Agustus untuk anak PAUD dan TK yang seru, edukatif, dan mudah digelar</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:38:29 +0700</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Perayaan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 dapat menjadi momen bagi anak usia PAUD dan TK ...</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677368/10-ide-lomba-17-agustus-untuk-anak-paud-dan-tk-yang-seru-edukatif-dan-mudah-digelar</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/08/03/WhatsApp-Image-2024-08-03-at-20.37.28.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Sering terbangun tengah malam? Kenali 7 penyebab dan cara mengatasinya</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:35:20 +0700</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Bangun di tengah malam sesekali merupakan hal yang normal. Namun, jika kondisi ini terjadi hampir setiap malam dan ...</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677357/sering-terbangun-tengah-malam-kenali-7-penyebab-dan-cara-mengatasinya</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/20/Penumpang-rela-menginap-menunggu-kereta-pertama-di-Stasiun-Cikarang-150726-ryl-5.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Bahaya paparan pornografi pada anak: Dampak bagi otak, mental, dan perilaku</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:23:03 +0700</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Perkembangan teknologi membuat anak-anak dan remaja semakin akrab dengan internet sejak usia dini. Di satu sisi, ...</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677332/bahaya-paparan-pornografi-pada-anak-dampak-bagi-otak-mental-dan-perilaku</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/02/ilustrasi-konten-berbau-pornografi.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Sudah ngantuk tapi sulit tidur pulas? Ini penyebab dan cara atasinya</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 11:28:54 +0700</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Rasa kantuk yang muncul di malam hari seharusnya menjadi pertanda bahwa tubuh siap beristirahat. Namun, tidak sedikit ...</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677203/sudah-ngantuk-tapi-sulit-tidur-pulas-ini-penyebab-dan-cara-atasinya</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/17/Nafas.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Cara cepat tidur dalam 5 menit, efektif untuk yang sulit pulas</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 11:25:40 +0700</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Sulit tidur meski badan sudah terasa lelah merupakan masalah yang kerap dialami banyak orang. Kondisi ini sering ...</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677199/cara-cepat-tidur-dalam-5-menit-efektif-untuk-yang-sulit-pulas</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/04/tidua.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>tekno</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Cara mengganti password WiFi lewat HP dan laptop dengan mudah</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:16:14 +0700</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>WiFi yang tiba-tiba terasa lambat padahal sinyal penuh dan kuota internet masih banyak tentu membuat kesal. Salah satu ...</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677312/cara-mengganti-password-wifi-lewat-hp-dan-laptop-dengan-mudah</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2020/08/19/antarafoto-warga-sediakan-internet-gratis-bagi-pelajar-190820-ief-2-1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo terima kunjungan PM Thailand Anutin Charnvirakul</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 17:42:48 +0700</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto (kiri) bersama Perdana Menteri Thailand Anutin Charnvirakul (kedua kiri) bersiap melakukan penghormatan pada bendera saat upacara penyambutan kenegaraan di Istana Merdeka, Jakarta, Senin (3/8/2026). Kunjungan tersebut diantaranya untuk memperkuat kerja sama bilateral serta meluncurkan Peta Jalan Kemitraan Strategis Indonesia-Thailand 2026–2030 yang terfokus pada tiga bidang utama yaitu keamanan, pembangunan ekonomi dan sosial-budaya. ANTARA FOTO/Hafidz Mubarak A/sgd/agr</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5677811/presiden-prabowo-terima-kunjungan-pm-thailand-anutin-charnvirakul</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/Presiden-Prabowo-Terima-Kunjungan-PM-Thailand-030226-hma-5.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Pameran foto jurnalistik Prahara Pulau Emas di Museum Tsunami Aceh</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:52:45 +0700</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Pengunjung melihat karya pameran foto jurnalistik Prahara Pulau Emas di Museum Tsunami Aceh, Banda Aceh, Aceh, Senin (3/8/2026). Pameran foto yang menampilkan 65 karya dari anggota PFI tersebut merekam dampak bencana hidrometeorologi di Provinsi Aceh, Sumatera Utara dan Sumatera Barat pada akhir November 2025. ANTARA FOTO/Akramul Muslim/agr</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5677709/pameran-foto-jurnalistik-prahara-pulau-emas-di-museum-tsunami-aceh</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/Pameran-Foto-Prahara-Pulau-Emas-Di-Aceh-030826-Akm-7.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Jelang HUT RI, Polda Kepri bagikan bendera ke warga di pulau-pulau terluar</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:51:09 +0700</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Warga memasang Bendera Merah Putih di perahu serta pekarangan rumah panggung yang dibagikan Polda Kepri di Pulau Dapur Arang, Batam, Kepulauan Riau, Senin (3/8/2026). Polda Kepri membagikan Bendera Merah Putih kepada warga yang tinggal di pulau-pulau terluar Batam yang berbatasan langsung dengan Singapura guna menyemarakkan peringatan HUT Ke-81 Kemerdekaan Republik Indonesia sekaligus menanamkan rasa nasionalisme di wilayah perbatasan. ANTARA FOTO/Teguh Prihatna/agr</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5677539/jelang-hut-ri-polda-kepri-bagikan-bendera-ke-warga-di-pulau-pulau-terluar</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/Pembagian-Bendera-Merah-Putih-Di-Pulau-Pulau-Terluar-030826-tpp-2.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Pemerintah bangun 1.416 Jembatan Garuda untuk hubungkan desa terpencil</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 12:53:00 +0700</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Foto udara pengendara sepeda motor melintasi Jembatan Gantung Garuda yang menghubungkan Desa Kertarahayu dan Desa Jayasampurna di Kabupaten Bekasi, Jawa Barat, Senin (3/8/2026). Hingga akhir Juli 2026, pemerintah telah membangun 1.416 unit Jembatan Garuda di daerah terpencil yang menghubungkan 7.371 desa dan kelurahan untuk mempermudah akses masyarakat serta mempersingkat waktu tempuh. ANTARA FOTO/Darryl Ramadhan/tom.</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5677284/pemerintah-bangun-1416-jembatan-garuda-untuk-hubungkan-desa-terpencil</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/Pembangunan-Jembatan-Garuda-percepat-akses-desa-030826-ryl-1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Petugas evakuasi dua jenazah korban kebakaran KM Mutiara Sentosa II</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 09:03:11 +0700</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Sejumlah petugas mengangkat kantong berisi jenazah korban kebakaran KM Mutiara Sentosa II setelah tiba di Dermaga Jamrud Utara, Pelabuhan Tanjung Perak, Surabaya, Jawa Timur, Senin (3/8/2026). Kapal kargo Meratus Pematang Siantar mengevakuasi 111 penumpang selamat dan dua jenazah korban kebakaran KM Mutiara Sentosa II di perairan utara Madura pada Minggu (2/8). ANTARA FOTO/Didik Suhartono/tom.</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5677056/petugas-evakuasi-dua-jenazah-korban-kebakaran-km-mutiara-sentosa-ii</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/korban-kebakaran-km-mutiara-sentosa-2-030826-Ds-4.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Program Taruna Bakti Kepolisian latih siswa Sekolah Rakyat Lhokseumawe</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>ANTARA - Ratusan siswa dari Sekolah Rakyat Lhokseumawe, Aceh, memperoleh edukasi kemandirian oleh Taruna Akademi Kepolisian untuk mengubah prilaku, Senin (3/8). Kegiatan ini merupakan salah satu dari program Taruna Bakti, yang diinstruksikan langsung oleh Presiden RI Prabowo Subianto ke seluruh Sekolah Rakyat di Indonesia. (Try Vanny S/Andi Bagasela/Winanto)</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678013/program-taruna-bakti-kepolisian-latih-siswa-sekolah-rakyat-lhokseumawe</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PROGRAM-TARUNA-BAKTI-KEPOLISIAN-LATIH-SISWA-SEKOLAH-RAKYAT-LHOKSEUMAWE.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Menkomdigi minta masyarakat waspadai lonjakan hoaks jelang HUT RI</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengingatkan masyarakat untuk mewaspadai meningkatnya penyebaran hoaks menjelang peringatan Hari Ulang Tahun (HUT) ke-81 Republik Indonesia. Saat ditemui di Jakarta pada Senin (3/8), Menkomdigi  juga menegaskan tidak pernah melarang media melakukan peliputan, selama sesuai kaidah jurnalistik dan Undang-Undang Pers.(Sanya Dinda Susanti/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677959/menkomdigi-minta-masyarakat-waspadai-lonjakan-hoaks-jelang-hut-ri</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-MINTA-MASYARAKAT-WASPADAI-LONJAKAN-HOAKS-JELANG-HUT-RI.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Inflasi di Sumut sebesar 4,20 persen, emas menjadi penyumbang utama</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Sumatera Utara mencatat pada Juli 2026 Sumatera Utara mengalami inflasi 4,20 persen. Komoditas penyumbang inflasi pada bulan Juli 2026 yakni, emas perhiasan, cabai merah, cabai rawit, tomat dan bensin. (M. Valery Maulidzar S/Andi Bagasela/Winanto)</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677867/inflasi-di-sumut-sebesar-420-persenemas-menjadi-penyumbang-utama</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INFLASI-DI-SUMUT-SEBESAR-4-20-PERSEN-EMAS-MENJADI-PENYUMBANG-UTAMA.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Komdigi tegur YouTube soal pelibatan anak dalam promosi rokok elektrik</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengatakan telah melayangkan surat teguran pertama kepada YouTube yang memuat konten siaran langsung atau live streaming seorang pemengaruh yang menampilkan promosi produk rokok elektrik atau vape dengan melibatkan anak-anak. Menteri Komdigi Meutya Hafid, di Jakarta, Senin (3/8), mengatakan dalam tiga hari ke depan Komdigi juga akan memanggil pihak YouTube untuk meminta keterangan. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677812/komdigi-tegur-youtube-soal-pelibatan-anak-dalam-promosi-rokok-elektrik</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_KOMDIGI-TEGUR-YOUTUBE-SOAL-PELIBATAN-ANAK-DALAM-PROMOSI-ROKOK-ELEKTRIK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Pemkab Temanggung gandeng kemitraan kacang panjang dengan perusahaan</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>ANTARA - Dinas Penanaman Modal dan Pelayanan Terpadu Satu Pintu (DPMPTSP) Kabupaten Temanggung, Jawa Tengah, menjajaki peluang kemitraan budidaya kacang panjang dengan pihak perusahaan. Langkah ini dilakukan sebagai upaya memperluas akses pasar, sekaligus meningkatkan kesejahteraan petani melalui kepastian harga dan penyerapan hasil panen. (Firman Eko Handy/Andi Bagasela/Winanto)</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677779/pemkab-temanggung-gandeng-kemitraan-kacang-panjang-dengan-perusahaan</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PEMKAB-TEMANGGUNG-GANDENG-KEMITRAAN-KACANG-PANJANG-DENGAN-PERUSAHAN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Dinkes Lhokseumawe uji kualitas air Sekolah Rakyat</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>ANTARA - Dinas Kesehatan (Dinkes) Kota Lhokseumawe melakukan uji kualitas air baku dan air minum di Sekolah Rakyat, Desa Jeulikat, Kecamatan Blang Mangat, Senin (3/8). Pemeriksaan dilakukan untuk memastikan air yang digunakan ratusan siswa memenuhi standar kesehatan sebelum dikonsumsi. (Try Vanny S/Andi Bagasela/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677740/dinkes-lhokseumawe-uji-kualitas-air-sekolah-rakyat</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_DINKES-LHOKSEUMAWE-UJI-KUALITAS-AIR-SEKOLAH-RAKYAT.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>HPAI Jember tanam pohon untuk mitigasi longsor dan banjir</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>ANTARA - Himpunan Pegiat Adiwiyata Indonesia (HPAI) Kabupaten Jember menanam belasan bibit pohon beringin dan 20 bibit pohon karet kebo di kawasan Air Terjun Tancak, lereng selatan Pegunungan Hyang Argopuro, Kecamatan Panti, Senin (3/8). Penanaman dilakukan untuk mendukung konservasi kawasan, menjaga sumber air, serta mengurangi risiko longsor dan banjir bandang. (Hamka Agung Balya/Satrio Giri Marwanto/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677707/hpai-jember-tanam-pohon-untuk-mitigasi-longsor-dan-banjir</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/HPAI-JEMBER-TANAM-POHON-UNTUK-MITIGASI-LONGSOR-DAN-BANJIR.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>75 gerai Koperasi Merah Putih di Sulawesi Tenggara telah beroperasi</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>ANTARA - Sebanyak 75 gerai Koperasi Desa Kelurahan Merah Putih (KDKMP) di Provinsi Sulawesi Tenggara telah mulai beroperasi pada Juli 2026. Kantor Wilayah Direktorat Jenderal Perbendaharaan Provinsi Sulawesi Tenggara (Kanwil DJPb Sultra) menyebut sepanjang 2026, KDKMP di Sultra mencatatkan 1.055 transaksi dengan nilai Rp25,22 juta dengan transaksi didominasi komoditas kebutuhan pokok dan energi bersubsidi, antara lain beras medium SPHP, MinyaKita, gula, dan elpiji 3 kilogram. (Saharudin/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677680/75-gerai-koperasi-merah-putih-di-sulawesi-tenggara-telah-beroperasi</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_75-GERAI-KOPERASI-MERAH-PUTIH-DI-SULAWESI-TENGGARA-TELAH-BEROPERASI.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Pimpinan MPR RI bertemu Presiden sampaikan undangan Sidang Tahunan</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>ANTARA - Jajaran pimpinan MPR RI menyambangi Istana Kepresidenan Jakarta pada Senin (3/8). Ketua MPR RI Ahmad Muzani menyebut kunjungan itu salah satunya untuk menyampaikan undangan Sidang Tahunan MPR RI pada 14 Agustus 2026. (Aria Cindyara/Irfansyah Naufal Nasution/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677637/pimpinan-mpr-ri-bertemu-presiden-sampaikan-undangan-sidang-tahunan</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PIMPINAN-MPR-RI-BERTEMU-PRESIDEN-SAMPAIKAN-UNDANGAN-SIDANG-TAHUNAN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Menkomdigi kukuhkan komisioner KI Pusat, perkuat keterbukaan informasi</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengambil sumpah jabatan dan mengukuhkan tujuh anggota Komisi Informasi Pusat (KIP) Periode 2026–2030 di Kantor Kementerian Komdigi Jakarta, Senin (3/8).  Komisioner KI Pusat Periode 2026–2030 akan melanjutkan tugas dan fungsi komisioner sebelumnya, yakni penyelesaian sengketa informasi publik secara adil, menetapkan kebijakan teknis di bidang keterbukaan informasi, dan memperkuat implementasi UU Nomor 14 Tahun 2008 tentang Keterbukaan Informasi Publik. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677604/menkomdigi-kukuhkan-komisioner-ki-pusat-perkuat-keterbukaan-informasi</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-KUKUHKAN-KOMISIONER-KI-PUSAT-PERKUAT-KETERBUKAAN-INFORMASI.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Partai Buruh Brasil calonkan Lula da Silva untuk masa jabatan keempat</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr">
+        <is>
           <t>ANTARA - Partai Buruh di Brasil pada Minggu (2/8) waktu setempat, resmi mencalonkan petahana Luiz Inacio Lula da Silva sebagai kandidat dalam pemilihan presiden mendatang untuk masa jabatan keempat. Pada konvensi nasional partai di Sao Paulo, para delegasi secara resmi menyetujui pasangan Lula dengan Wakil Presiden petahana Geraldo Alckmin dari Partai Sosialis Brasil.
 (XINHUA /Winanto/Rizky Bagus Dhermawan/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
+      <c r="F256" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677541/partai-buruh-brasil-calonkan-lula-da-silva-untuk-masa-jabatan-keempat</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr">
+      <c r="G256" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-154005.jpg</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
+    <row r="257">
+      <c r="A257" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
+      <c r="B257" t="inlineStr">
         <is>
           <t>Kesbangpol Pontianak antisipasi konflik sosial akibat karhutla</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr">
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr">
         <is>
           <t>ANTARA - Badan Kesatuan Bangsa dan Politik (Kesbangpol) Kota Pontianak mengidentifikasi potensi gangguan keamanan dan konflik sosial akibat kebakaran hutan dan lahan (karhutla), Senin (3/8). Langkah yang dilakukan meliputi koordinasi lintas sektor, pemantauan situasi, hingga mediasi untuk menjaga kondusivitas selama penanganan karhutla. (Indra Budi Santoso/Rizky Bagus Dhermawan/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
+      <c r="F257" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677519/kesbangpol-pontianak-antisipasi-konflik-sosial-akibat-karhutla</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
+      <c r="G257" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KESBANGPOL-PONTIANAK-ANTISIPASI-KONFLIK-SOSIAL-AKIBAT-KARHUTLA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
+    <row r="258">
+      <c r="A258" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="B258" t="inlineStr">
         <is>
           <t>PSEL Serang Raya jadi solusi pengelolaan sampah tiga daerah</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr">
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr">
         <is>
           <t>ANTARA - Fasilitas Pengolahan Sampah menjadi Energi Listrik (PSEL) Serang Raya akan dibangun di TPSA Cilowong, Kota Serang, untuk melayani pengelolaan sampah Kabupaten Serang, Kota Serang, dan Kota Cilegon. Fasilitas berkapasitas 1.161 ton sampah per hari itu diharapkan mampu mengurangi beban tempat pemrosesan akhir sekaligus mengubah sampah menjadi energi listrik. (Susmiatun Hayati/Agha Yuninda Maulana/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr">
+      <c r="F258" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677492/psel-serang-raya-jadi-solusi-pengelolaan-sampah-tiga-daerah</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
+      <c r="G258" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PSEL-SERANG-RAYA-JADI-SOLUSI-PENGELOLAAN-SAMPAH.jpg</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
+    <row r="259">
+      <c r="A259" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="B259" t="inlineStr">
         <is>
           <t>Pemkot Ambon salurkan air bersih gratis jika kekeringan terjadi</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr">
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah Kota Ambon, Maluku, menyiapkan langkah antisipasi untuk menjamin ketersediaan air bersih bagi masyarakat dalam menghadapi potensi musim kemarau panjang akibat fenomena El Nino. Wali kota Ambon Bodewin Wattimena, Senin (3/8), mengatakan, pemerintah melakukan pemetaan wilayah yang rawan lalu mendistribusikan air bersih ke wilayah terdampak kekeringan. (Alfian Sanusi/Rizky Bagus Dhermawan/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
+      <c r="F259" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677489/pemkot-ambon-salurkan-air-bersih-gratis-jika-kekeringan-terjadi</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
+      <c r="G259" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-151844.jpg</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
+    <row r="260">
+      <c r="A260" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B260" t="inlineStr">
         <is>
           <t>Razia balap liar, Polres Temanggung sita 106 motor</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr">
         <is>
           <t>ANTARA - Kepolisian Resor (Polres) Temanggung, Jawa Tengah menyita 106 sepeda motor dalam razia balap liar yang digelar Minggu malam (2/8). Kegiatan razia tersebut digelar sebagai bagian  upaya kepolisian dalam menekan aksi balap liar  di Temanggung.(Firman Eko Handy/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
+      <c r="F260" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677488/razia-balap-liar-polres-temanggung-sita-106-motor</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
+      <c r="G260" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_RAZIA-BALAP-LIAR-POLRES-TEMANGGUNG-SITA-106-MOTOR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
+    <row r="261">
+      <c r="A261" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="B261" t="inlineStr">
         <is>
           <t>Ditjenpas Kaltim gelar CKG bagi 12 ribu warga binaan</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr">
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr">
         <is>
           <t>ANTARA - Program Cek Kesehatan Gratis (CKG) menyasar warga binaan di Lembaga Pemasyarakatan (Lapas) dan Rumah Tahanan (Rutan) di Kalimantan Timur. CKG untuk 12 ribu warga binaan bertujuan mengantisipasi penyebaran risiko penyakit menular di lapas. (Hanifan Ma'ruf/Agha Yuninda Maulana/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
+      <c r="F261" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677480/ditjenpas-kaltim-gelar-ckg-bagi-12-ribu-warga-binaan</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
+      <c r="G261" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_DITJENPAS-KALTIM-GELAR-CKG.jpg</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
+    <row r="262">
+      <c r="A262" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B262" t="inlineStr">
         <is>
           <t>Paus Leo XIV prihatin atas situasi krisis migran di Ceuta</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>ANTARA - Paus Leo XIV  menyampaikan keprihatinan atas situasi krisis migran di Enklave, Spanyol, Ceuta.  Saat memimpin doa angelus di Vatikan, Minggu (2/8), Paus berdoa agar terdapat solusi yang membawa perdamaian dan keadilan atas kondisi tersebut. (Ludmila Yusufin Diah Nastiti/Agha Yuninda Maulana/Winanto)</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>ANTARA - Paus Leo XIV  menyampaikan keprihatinan atas situasi krisis migran di Enklave, Spanyol, Ceuta.  Saat memimpin doa angelus di Vatikan, Minggu (2/8), Paus berdoa agar terdapat solusi yang membawa perdamaian dan keadilan atas kondisi tersebut. (ANADOLU/Ludmila Yusufin Diah Nastiti/Agha Yuninda Maulana/Winanto)</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677384/paus-leo-xiv-prihatin-atas-situasi-krisis-migran-di-ceuta</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
+      <c r="G262" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PAUS-LEO-XIV-PRIHATIN-ATAS-SITUASI-KRISIS.jpg</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
+    <row r="263">
+      <c r="A263" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B263" t="inlineStr">
         <is>
           <t>Resmi dibuka, Sekolah Rakyat Terintegrasi 2 Kendari tampung 339 siswa</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr">
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr">
         <is>
           <t>ANTARA - Sekolah Rakyat Terintegrasi 2 Kota Kendari resmi dibuka pada Senin (3/8), yang ditandai dengan Masa Pengenalan Lingkungan Sekolah (MPLS). Sekolah tersebut menampung total sebanyak 339 siswa untuk tahun ajaran 2026/2027, yang terdiri dari jenjang SD, SMP dan SMA.
 (Saharudin/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
+      <c r="F263" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677373/resmi-dibuka-sekolah-rakyat-terintegrasi-2-kendari-tampung-339-siswa</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
+      <c r="G263" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/RESMI-DIBUKA-SEKOLAH-RAKYAT-TERINTEGRASI-2-KENDARI-TAMPUNG-339-SISWA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
+    <row r="264">
+      <c r="A264" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B264" t="inlineStr">
         <is>
           <t>Dinkop UKM Cilegon targetkan 21 gerai baru KKMP beroperasi September</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr">
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Koperasi Usaha Kecil dan Menengah (Dinkop UKM) Kota Cilegon menargetkan pembangunan  21 gedung gerai Koperasi Kelurahan Merah Putih (KKMP) di wilayah setempat dapat selesai dan beroperasi pada bulan September mendatang. Kepala Dinkop UKM Kota Cilegon, Suhendi pada Senin (3/8) mengatakan saat ini tercatat baru sebanyak 10 gedung yang telah selesai dibangun.
 (Susmiatun Hayati/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr">
+      <c r="F264" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677301/dinkop-ukm-cilegon-targetkan-21-gerai-baru-kkmp-beroperasi-september</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr">
+      <c r="G264" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/DINKOP-UKM-CILEGON-TARGETKAN-21-GERAI-BARU-KKMP-BEROPERASI-SEPTEMBER.jpg</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
+    <row r="265">
+      <c r="A265" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B265" t="inlineStr">
         <is>
           <t>Menhub sebut segera evaluasi operator KMP Mutiara Sentosa 2</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr">
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah akan segera mengevaluasi kinerja PT Atosim Lampung Pelayaran yang merupakan operator KMP Mutiara Sentosa II. Hal tersebut disampaikan Menteri Perhubungan Dudy Purwagandhi saat meninjau para korban kebakaran KMP Mutiara Sentosa II di Surabaya, Jawa Timur, Senin (3/8). (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
+      <c r="F265" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677187/menhub-sebut-segera-evaluasi-operator-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr">
+      <c r="G265" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/MENHUB-SEBUT-SEGERA-EVALUASI-OPERATOR-KMP-MUTIARA-SENTOSA-2.jpg</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
+    <row r="266">
+      <c r="A266" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="B266" t="inlineStr">
         <is>
           <t>Keluarga dengan dua balita selamat dari maut KMP Mutiara Sentosa 2</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr">
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="inlineStr">
         <is>
           <t>ANTARA - Pasangan suami istri muda, Karhap dan Krisnawati bersama dua anak balitanya sempat terpisah saat terjun ke laut menyelamatkan diri dari kapal penumpang KMP Mutiara Sentosa 2 yang terbakar di perairan sebelah utara Pulau Madura pada Minggu (2/8). Keluarga kecil asal Sidenreng Rappang, Sulawesi Selatan tersebut kembali berkumpul pada Senin (3/8) setelah dievakuasi oleh kapal kargo Meratus Pematang Siantar yang kebetulan melintas di lokasi musibah terjadi. (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr">
+      <c r="F266" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677141/keluarga-dengan-dua-balita-selamat-dari-maut-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
+      <c r="G266" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KELUARGA-DENGAN-DUA-BALITA-SELAMAT-DARI-MAUT-KMP-MUTIARA-SENTOSA-2.jpg</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
+    <row r="267">
+      <c r="A267" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="B267" t="inlineStr">
         <is>
           <t>Lebih dari 100 korban KMP Mutiara Sentosa 2 tiba di Tanjung Perak</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr">
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr">
         <is>
           <t>ANTARA - Tim pencarian dan pertolongan (SAR) gabungan hingga Senin (3/8), telah mengevakuasi 234 penumpang KMP Mutiara Sentosa 2 yang sebelumnya terbakar di perairan sebelah utara Pulau Madura pada Minggu (2/8). Sebanyak 113 korban di antaranya, kini telah tiba di Pelabuhan Tanjung Perak Surabaya setelah diangkut menggunakan kapal kargo Meratus Pematang Siantar.  (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr">
+      <c r="F267" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677085/lebih-dari-100-korban-kmp-mutiara-sentosa-2-tiba-di-tanjung-perak</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr">
+      <c r="G267" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/LEBIH-DARI-100-KORBAN-KMP-MUTIARA-SENTOSA-2-TIBA-DI-TANJUNG-PERAK.jpg</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
+    <row r="268">
+      <c r="A268" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="B268" t="inlineStr">
         <is>
           <t>SAR evakuasi penumpang KM Mutiara Santosa 2 yang terbakar</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr">
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
         <is>
           <t>ANTARA - Tim pencarian dan pertolongan (SAR) gabungan telah mengevakuasi sebanyak 236 penumpang KM Mutiara Santosa 2 yang terbakar di perairan sebelah utara Pulau Madura, Minggu malam (2/8). Lima korban di antaranya meninggal dunia.(Hanif Nasrullah/Denno Ramdha Asmara/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
+      <c r="F268" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676992/sar-evakuasi-penumpang-km-mutiara-santosa-2-yang-terbakar</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
+      <c r="G268" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SAR-EVAKUASI-PENUMPANG-KM-MUTIARA-SANTOSA-2-YANG-TERBAKAR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
+    <row r="269">
+      <c r="A269" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B269" t="inlineStr">
         <is>
           <t>John Herdman tunggu hasil pemeriksaan Marselino jelang jamu Vietnam</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr">
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr">
         <is>
           <t>ANTARA - Pelatih Timnas Indonesia John Herdman di Jakarta, Minggu,(2/8), mengatakan kondisi kesehatan dan status gelandang Marselino Ferdinan dalam turnamen baru akan ditentukan setelah mendapat laporan lengkap dari tim medis. Hal itu disampaikan Herdman, usai Marselino kembali absen dalam latihan jelang laga Grup A Piala AFF 2026 melawan Timnas Vietnam pada Senin (2/8). (Anggah/Sandy Arizona/Gracia Simanjuntak)</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
+      <c r="F269" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676945/john-herdman-tunggu-hasil-pemeriksaan-marselino-jelang-jamu-vietnam</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
+      <c r="G269" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_JOHN-HERDMAN-TUNGGU-HASIL-PEMERIKSAAN-MARSELINO-JELANG-JAMU-VIETNAM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
+    <row r="270">
+      <c r="A270" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B270" t="inlineStr">
         <is>
           <t>John Herdman sebut laga RI Vs Vietnam ujian sangat berat</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr">
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr">
         <is>
           <t>ANTARA - Pelatih Timnas Indonesia John Herdman di Jakarta, Minggu(2/8), mengaku pertandingan melawan Timnas Vietnam akan menjadi ujian sangat berat bagi skuad Garuda di Grup A Piala AFF 2026 (ASEAN Championship 2026). Menurut Herdman. laga tersebut juga merupakan peluang untuk mengambil alih kendali grup dan memastikan langkah ke babak berikutnya. (Anggah/Sandy Arizona/Gracia Simanjuntak)</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr">
+      <c r="F270" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676944/john-herdman-sebut-laga-ri-vs-vietnam-ujian-sangat-berat</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
+      <c r="G270" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_JOHN-HERDMAN-SEBUT-LAGA-RI-VS-VIETNAM-UJIAN-SANGAT-BERAT.jpg</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
+    <row r="271">
+      <c r="A271" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B271" t="inlineStr">
         <is>
           <t>BI targetkan bawa wastra Sulsel ke pasar global</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr">
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
         <is>
           <t>ANTARA - Kantor Perwakilan Bank Indonesia Provinsi Sulawesi Selatan bersama Pemerintah Provinsi Sulsel menyasar penguatan pasar produk kain tradisional (wastra) di tingkat nasional hingga mancanegara melalui "Wastra Heritage Market 2026". Hal itu dikemukakan Kepala Kantor Perwakilan BI Sulsel Rizki Ernadi Wimanda di Makassar, Minggu (2/8). (Suriani Mappong/Sandy Arizona/Gracia Simanjuntak)</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
+      <c r="F271" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676935/bi-targetkan-bawa-wastra-sulsel-ke-pasar-global</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr">
+      <c r="G271" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_BI-TARGETKAN-BAWA-WASTRA-SULSEL-KE-PASAR-GLOBAL.jpg</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
+    <row r="272">
+      <c r="A272" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="B272" t="inlineStr">
         <is>
           <t>Tong Tong Night Market masuk KEN, angkat UMKM dan budaya lokal</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr">
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" t="inlineStr">
         <is>
           <t>ANTARA - ‎Memasuki satu dekade penyelenggaraan, Tong Tong Night Market kembali meramaikan Kota Malang. Festival budaya dan kuliner yang masuk dalam Karisma Event Nusantara (KEN) itu tak hanya menghadirkan nuansa tempo dulu, tetapi juga menjadi ajang promosi puluhan UMKM sekaligus upaya melestarikan budaya lokal. (Achmad Saif Hajarani/Sandy Arizona/Gracia Simanjuntak)</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr">
+      <c r="F272" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676927/tong-tong-night-market-masuk-ken-angkat-umkm-dan-budaya-lokal</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
+      <c r="G272" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_TONG-TONG-NIGHT-MARKET-MASUK-KEN-ANGKAT-UMKM-DAN-BUDAYA-LOKAL_1.jpg</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
+    <row r="273">
+      <c r="A273" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B273" t="inlineStr">
         <is>
           <t>Perputaran ekonomi Piala Presiden 2026 tembus Rp70 miliar</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr">
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr"/>
+      <c r="E273" t="inlineStr">
         <is>
           <t>ANTARA - Ketua Steering Committee Piala Presiden 2026 Maruarar Sirait menyebut perputaran ekonomi selama babak penyisihan turnamen di Surabaya dan Bandung telah mencapai lebih dari Rp70 miliar. Dampak ekonomi tersebut turut dirasakan pelaku usaha mikro, kecil, dan menengah (UMKM) serta dimanfaatkan untuk menyubsidi harga tiket pertandingan.
 (Hanif Nasrullah/Sandy Arizona/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
+      <c r="F273" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676895/perputaran-ekonomi-piala-presiden-2026-tembus-rp70-miliar</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
+      <c r="G273" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_PERPUTARAN-EKONOMI-PIALA-PRESIDEN-2026-TEMBUS-RP70-MILIAR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
+    <row r="274">
+      <c r="A274" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B274" t="inlineStr">
         <is>
           <t>Bahlil prioritaskan legalisasi 25 ribu sumur minyak rakyat di Sumsel</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr">
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyebut Sumatera Selatan menjadi salah satu daerah prioritas penerapan kebijakan legalisasi sumur minyak rakyat. Menurutnya, sekitar 25 ribu dari 45 ribu sumur minyak rakyat di Indonesia berada di provinsi tersebut sehingga pemerintah memfokuskan implementasi Peraturan Menteri ESDM Nomor 18 Tahun 2025 di wilayah itu.
 (Winda Tri Agustina/Sandy Arizona/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr">
+      <c r="F274" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676868/bahlil-prioritaskan-legalisasi-25-ribu-sumur-minyak-rakyat-di-sumsel</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr">
+      <c r="G274" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_BAHLIL-PRIORITASKAN-LEGALISASI-25-RIBU-SUMUR-MINYAK-RAKYAT-DI-SUMSEL.jpg</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
+    <row r="275">
+      <c r="A275" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
+      <c r="B275" t="inlineStr">
         <is>
           <t>Golkar optimistis tingkatkan perolehan kursi di Sumsel</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr">
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="inlineStr">
         <is>
           <t>ANTARA - Ketua Umum Partai Golkar Bahlil Lahadalia meminta seluruh jajaran partai memperkuat konsolidasi organisasi hingga tingkat desa sebagai strategi meningkatkan perolehan kursi legislatif pada Pemilu 2029, termasuk di Sumatera Selatan.
 (Winda Tri Agustina/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr">
+      <c r="F275" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676837/golkar-optimistis-tingkatkan-perolehan-kursi-di-sumsel</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr">
+      <c r="G275" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/GOLKAR-OPTIMISTIS-TINGKATKAN-PEROLEHAN-KURSI-DI-SUMSEL.jpg</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
+    <row r="276">
+      <c r="A276" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
+      <c r="B276" t="inlineStr">
         <is>
           <t>Presiden AS Trump tunda serangan baru ke Iran</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr">
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr">
         <is>
           <t>ANTARA - Presiden Amerika Serikat Donald Trump menunda rencana serangan baru terhadap Iran setelah mengklaim terdapat peluang kesepakatan. Namun, Trump menegaskan opsi militer tetap terbuka jika negosiasi gagal.
 (XINHUA/Arsy Fitriady/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr">
+      <c r="F276" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676776/presiden-as-trump-tunda-serangan-baru-ke-iran</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr">
+      <c r="G276" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-AS-TRUMP-TUNDA-SERANGAN-BARU-KE-IRAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
+    <row r="277">
+      <c r="A277" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
+      <c r="B277" t="inlineStr">
         <is>
           <t>TNI AU gelar pameran enam pesawat F-16 di Batam</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr">
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr">
         <is>
           <t>ANTARA - TNI Angkatan Udara menggelar pameran enam pesawat tempur F-16 yang dapat dikunjungi masyarakat secara gratis dalam kegiatan Batam Open Base di Bandara Internasional Hang Nadim, Batam. Kegiatan ini menjadi bagian dari peringatan Hari Ulang Tahun ke-81 Kemerdekaan Republik Indonesia sekaligus upaya mendekatkan TNI AU kepada masyarakat.
 (Angiela Chantiequ/Jessica Allifia Jaya Hidayat/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr">
+      <c r="F277" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676735/tni-au-gelar-pameran-enam-pesawat-f-16-di-batam</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr">
+      <c r="G277" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/TNI-AU-GELAR-PAMERAN-ENAM-PESAWAT-F-16-DI-BATAM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
+    <row r="278">
+      <c r="A278" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
+      <c r="B278" t="inlineStr">
         <is>
           <t>TNI kerahkan delapan helikopter salurkan bantuan ke Puncak</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr">
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="inlineStr">
         <is>
           <t>ANTARA - Komando Gabungan Wilayah Pertahanan (Kogabwilhan) III mengerahkan delapan helikopter TNI Angkatan Darat dan TNI Angkatan Udara untuk menyalurkan bantuan kemanusiaan ke tiga distrik di Kabupaten Puncak, Papua Tengah, yang terdampak kekeringan berkepanjangan hingga memicu krisis pangan. (Laksa Mahendra/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr">
+      <c r="F278" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676720/tni-kerahkan-delapan-helikopter-salurkan-bantuan-ke-puncak</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr">
+      <c r="G278" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/TNI-KERAHKAN-DELAPAN-HELIKOPTER-SALURKAN-BANTUAN-KE-PUNCAK.jpg</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
+    <row r="279">
+      <c r="A279" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
+      <c r="B279" t="inlineStr">
         <is>
           <t>Jakarta Watersport Festival dorong sport tourism di Danau Sunter</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr">
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr">
         <is>
           <t>ANTARA - Jakarta Watersport Festival 2026 digelar di Danau Sunter, Jakarta Utara, pada 1–2 Agustus. Festival ini menghadirkan kompetisi olahraga air, hiburan, dan bazar UMKM sebagai upaya mendorong sport tourism serta aktivitas ekonomi kreatif di ibu kota. (Nabila Athifa/Setyanka Harviana Putri/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr">
+      <c r="F279" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676713/jakarta-watersport-festival-dorong-sport-tourism-di-danau-sunter</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr">
+      <c r="G279" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/JAKARTA-WATERSPORT-FESTIVAL-DORONG-SPORT-TOURISM-DI-DANAU-SUNTER.jpg</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
+    <row r="280">
+      <c r="A280" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="B280" t="inlineStr">
         <is>
           <t>Ledakan restoran di Moskow tewaskan tiga orang</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr">
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="inlineStr">
         <is>
           <t>ANTARA - Tiga orang tewas dan sedikitnya 21 lainnya luka-luka setelah ledakan alat peledak rakitan terjadi di sebuah restoran di kawasan Kudrinskaya Square, pusat Kota Moskow, Rusia, Sabtu (1/8). Menurut Komite Antiterorisme Nasional Rusia, ledakan terjadi ketika seorang perempuan berupaya membawa alat peledak ke dalam restoran, namun dihentikan petugas keamanan. Penyelidikan terkait motif serangan masih berlangsung. (Arsy Fitriady/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr">
+      <c r="F280" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676660/ledakan-restoran-di-moskow-tewaskan-tiga-orang</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr">
+      <c r="G280" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/LEDAKAN-RESTORAN-DI-MOSKOW-TEWASKAN-TIGA-ORANG_1.jpg</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
+    <row r="281">
+      <c r="A281" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="B281" t="inlineStr">
         <is>
           <t>DKPPP Temanggung edukasi warga cegah zoonosis dari hewan piaraan</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr">
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Ketahanan Pangan, Pertanian, dan Perikanan (DKPPP) Kabupaten Temanggung bersama komunitas pecinta hewan mengedukasi masyarakat tentang pentingnya menjaga kesehatan hewan piaraan untuk mencegah zoonosis atau penyakit yang dapat menular dari hewan ke manusia. Edukasi meliputi pemberian nutrisi, vaksinasi, kebersihan, dan pemeriksaan kesehatan hewan secara berkala. (Firman Eko Handy/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr">
+      <c r="F281" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676647/dkppp-temanggung-edukasi-warga-cegah-zoonosis-dari-hewan-piaraan</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr">
+      <c r="G281" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/DKPPP-TEMANGGUNG-EDUKASI-WARGA-CEGAH-ZOONOSIS-DARI-HEWAN-PIARAAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
+    <row r="282">
+      <c r="A282" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
+      <c r="B282" t="inlineStr">
         <is>
           <t>BP Batam siapkan Sekolah Terintegrasi Merah Putih di Rempang</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr">
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pengusahaan (BP) Batam menyiapkan pembangunan Sekolah Terintegrasi Merah Putih di Rempang, Kepulauan Riau, sebagai sekolah gratis bagi siswa berprestasi. Sekolah yang dibangun di atas lahan seluas 18 hektare itu akan melayani jenjang sekolah dasar hingga sekolah menengah atas dengan fasilitas pendidikan dan olahraga yang lengkap. (Angiela Chantiequ/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr">
+      <c r="F282" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676644/bp-batam-siapkan-sekolah-terintegrasi-merah-putih-di-rempang</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr">
+      <c r="G282" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/BP-BATAM-SIAPKAN-SEKOLAH-TERINTEGRASI-MERAH-PUTIH-DI-REMPANG.jpg</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
+    <row r="283">
+      <c r="A283" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
+      <c r="B283" t="inlineStr">
         <is>
           <t>Aldila Sutjiadi juarai WTA 500 Mubadala DC Open 2026</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr">
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="inlineStr">
         <is>
           <t>ANTARA - Petenis ganda putri Indonesia Aldila Sutjiadi menjuarai nomor ganda Women's Tennis Association (WTA) 500 Mubadala DC Open 2026 di Washington, Amerika Serikat. Berpasangan dengan petenis Selandia Baru Erin Routliffe, Aldila mengalahkan Andreja Klepac dari Slovenia dan Makoto Ninomiya dari Jepang dua set langsung 6-4, 6-1 pada partai final. Gelar tersebut menjadi trofi WTA kedelapan dalam karier Aldila di nomor ganda sekaligus gelar kedua bersama Routliffe pada musim 2026.
 (Arsy Fitriady/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr">
+      <c r="F283" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676629/aldila-sutjiadi-juarai-wta-500-mubadala-dc-open-2026</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr">
+      <c r="G283" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/ALDILA-SUTJIADI-JUARAI-WTA-500-MUBADALA-DC-OPEN-2026.jpg</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
+    <row r="284">
+      <c r="A284" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
+      <c r="B284" t="inlineStr">
         <is>
           <t>KM Mutiara Sentosa 2 Terbakar Saat Berlayar ke Makassar</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr">
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr">
         <is>
           <t>ANTARA - Kapal Motor (KM) Mutiara Sentosa 2 terbakar di perairan utara Pulau Madura saat berlayar dari Pelabuhan Tanjung Perak Surabaya menuju Makassar, Minggu (2/8). Kapal tersebut mengangkut sekitar 250 orang. Tim SAR gabungan masih melakukan evakuasi penumpang, sementara penyebab kebakaran masih dalam penyelidikan. (Hanif Nasrullah/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr">
+      <c r="F284" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676617/km-mutiara-sentosa-2-terbakar-saat-berlayar-ke-makassar</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr">
+      <c r="G284" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KM-MUTIARA-SENTOSA-2-TERBAKAR-SAAT-BERLAYAR-KE-MAKASSAR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
+    <row r="285">
+      <c r="A285" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
+      <c r="B285" t="inlineStr">
         <is>
           <t>BI dan Pemkot Kendari Perkuat Digitalisasi UMKM</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr">
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr">
         <is>
           <t>ANTARA - Kantor Perwakilan Bank Indonesia Sulawesi Tenggara bersama Pemerintah Kota Kendari menggelar Festival Kuliner Sultra Maimo 2026 untuk memperkuat digitalisasi usaha mikro, kecil, dan menengah atau UMKM. Festival yang berlangsung pada 2 hingga 9 Agustus itu juga mendorong perluasan transaksi non-tunai berbasis QRIS. (Saharudin/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
+      <c r="F285" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676607/bi-dan-pemkot-kendari-perkuat-digitalisasi-umkm</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr">
+      <c r="G285" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/BI-DAN-PEMKOT-KENDARI-PERKUAT-DIGITALISASI-UMKM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
+    <row r="286">
+      <c r="A286" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
+      <c r="B286" t="inlineStr">
         <is>
           <t>El Nino menguat, negara fokus jaga ketersediaan air &amp; tangani karhutla</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
-      <c r="E198" t="inlineStr">
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="inlineStr">
         <is>
           <t>ANTARA - Gelombang panas sebagai akibat El Nino mulai dirasakan dampaknya di sejumlah belahan dunia. Kebakaran hutan dan lahan atau karhutla, juga mulai terjadi di dalam negeri, seperti di Pulau Sumatera dan Kalimantan.Selain kebakaran, bencana ekologi yang terjadi ialah kekeringan. Beberapa daerah di Pulau Jawa seperti Temanggung, Sukoharjo, Lumajang, Banten, lalu daerah luar Jawa seperti Nusa Tenggara Barat dan Timur, hingga Bangka Belitung mulai mengalami krisis air bersih.Presiden pun memanggil sejumlah kepala kementerian dan lembaga terkait, untuk memberi pemaparan dan masukan guna meredam dampak El Nino.Lalu bagaimana sikap antisipatif yang disiapkan pemerintah pada musim kemarau dan el nino tahun ini? Selengkapnya dalam PerANTARA! (Roy Rosa Bachtiar/Suci Nurhaliza/Gunawan Wibisono/Rizky Bagus Dhermawan/Farah Khadija)</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr">
+      <c r="F286" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676540/el-nino-menguat-negara-fokus-jaga-ketersediaan-air-tangani-karhutla</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr">
+      <c r="G286" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/DF.jpg</t>
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
+    <row r="287">
+      <c r="A287" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="B287" t="inlineStr">
         <is>
           <t>Padang Padang Cup Bali jadi ajang peselancar Nasional unjuk kehebatan</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr"/>
-      <c r="E199" t="inlineStr">
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="inlineStr">
         <is>
           <t>ANTARA - Kompetisi selancar ombak Internasional Rip Curl Cup Padang Padang kembali digelar dan berlangsung pada 1-31 Agustus 2026, di Pantai Padang Padang, Labuan Sait Pecatu, Kuta Selatan, Bali. Ajang ini menjadi ruang bagi peselancar Nasional menunjukkan kehebatan mereka bersaing dengan peselancar Internasional. (Rita Laura/Sandy Arizona/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr">
+      <c r="F287" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676257/padang-padang-cup-bali-jadi-ajang-peselancar-nasional-unjuk-kehebatan</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr">
+      <c r="G287" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_PADANG-PADANG-CUP-BALI-JADI-AJANG-PESELANCAR-NASIONAL-UNJUK-KEHEBATAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
+    <row r="288">
+      <c r="A288" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
+      <c r="B288" t="inlineStr">
         <is>
           <t>Bekuk Port FC, Persebaya gandeng Persija ke semifinal</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr">
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" t="inlineStr">
         <is>
           <t>ANTARA - Persebaya membekuk Port FC 2 - 1 di laga terakhir Grup B turnamen sepak Piala Presiden 2026. Dengan hasil ini Persija lolos ke babak semifinal bersama Persebaya sebagai wakil Grup B. (Hanif Nasrullah/Sandy Arizona/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr">
+      <c r="F288" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676252/bekuk-port-fc-persebaya-gandeng-persija-ke-semifinal</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr">
+      <c r="G288" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_BEKUK-PORT-FC-PERSEBAYA-GANDENG-PERSIJA-KE-SEMIFINAL.jpg</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
+    <row r="289">
+      <c r="A289" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
+      <c r="B289" t="inlineStr">
         <is>
           <t>Aston Villa unggul 3-1 dari Indonesia All Stars dalam tur pramusim</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr">
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr">
         <is>
           <t>ANTARA - Tim Indonesia All Stars, harus mengakui keunggulan atas Aston Villa dengan skor 3-1, saat laga Friendly Match di Stadion Utama Gelora Bung Karno (SUGBK) Senayan, Jakarta, pada Sabtu (1/8). Penjaga Gawang Aston Villa, James Wright, saat ditemui media di GBK mengapresiasi para pemain Indonesia All Stars, karena dinilai memiliki kualitas yang baik. (Ryan Rahman/Sandy Arizona/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr">
+      <c r="F289" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676239/aston-villa-unggul-3-1-dari-indonesia-all-stars-dalam-tur-pramusim</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr">
+      <c r="G289" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_ASTON-VILLA-UNGGUL-3-1-DARI-INDONESIA-ALL-STARS-DALAM-TUR-PRAMUSIM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
+    <row r="290">
+      <c r="A290" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
+      <c r="B290" t="inlineStr">
         <is>
           <t>Joko Widodo dinobatkan sebagai sesepuh oleh sembilan Raja Timor</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr">
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="inlineStr">
         <is>
           <t>ANTARA - Ribuan warga memadati kawasan Pantai Lahi Lai Bissi Kopan (LLBK) Kota Kupang, Nusa Tenggara Timur, untuk menyaksikan Karnaval Budaya yang dihadiri Presiden ke-7 Republik Indonesia, Joko Widodo. Dalam prosesi adat yang menjadi puncak acara, Joko Widodo dinobatkan sebagai sesepuh atau saudara oleh sembilan raja dari kerajaan-kerajaan di Pulau Timor sebagai bentuk penghormatan terhadap nilai persaudaraan dan budaya masyarakat Timor. (Johanes Viandinando/Sandy Arizona/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
+      <c r="F290" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676205/joko-widodo-dinobatkan-sebagai-sesepuh-oleh-sembilan-raja-timor</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
+      <c r="G290" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_JOKO-WIDODO-DINOBATKAN-SEBAGAI-SESEPUH-OLEH-SEMBILAN-RAJA-TIMOR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
+    <row r="291">
+      <c r="A291" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
+      <c r="B291" t="inlineStr">
         <is>
           <t>Menag: Indeks kerukunan umat beragama RI jadi 77,89 persen di 2025</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr">
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Agama Nasaruddin Umar menyebut indeks kerukunan umat beragama naik menjadi 77,89 persen pada tahun 2025, dari sebelumnya, yakni 76,47 persen pada tahun 2024. Hal tersebut disampaikan oleh Menag saat mengahdiri agenda Zikir dan Doa Kebangsaan "Indonesia Berdaulat, Adil dan Makmur" di Lapangan Silang Monas, Jakarta, Sabtu (1/8).
 (Afra Augesti/Nico Anggriawan/Sandy Arizona/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr">
+      <c r="F291" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676188/menag-indeks-kerukunan-umat-beragama-ri-jadi-7789-persen-di-2025</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr">
+      <c r="G291" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_MENAG-INDEKS-KERUKUNAN-UMAT-BERAGAMA-RI-JADI-77-89-PERSEN-DI-2025.jpg</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
+    <row r="292">
+      <c r="A292" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
+      <c r="B292" t="inlineStr">
         <is>
           <t>KKP bantu pelaku usaha perikanan terdampak bencana di Sumbar</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr">
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" t="inlineStr">
         <is>
           <t>ANTARA - Kementerian Kelautan dan Perikanan (KKP) bersama Tim Satuan Tugas Percepatan Rehabilitasi dan Rekonstruksi (PRR) Provinsi Sumatera Barat, mempercepat dan memastikan operasionalisasi budi daya, nelayan serta pengolahan ikan segera berjalan pascabencana hidrometeorologi yang terjadi akhir November tahun lalu. Untuk itu, KKP memberikan bantuan awal berupa bibit ikan dan pakan, dan ekskavator, kepada pelaku usaha perikanan yang terdampak bencana hidrometeorologis di Kota Padang, Kabupaten Padang Pariaman, Kabupaten Solok dan Kabupaten Agam.
 (Melani Friati/Sandy Arizona/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr">
+      <c r="F292" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676172/kkp-bantu-pelaku-usaha-perikanan-terdampak-bencana-di-sumbar</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr">
+      <c r="G292" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_KKP-BANTU-PELAKU-USAHA-PERIKANAN-TERDAMPAK-BENCANA-DI-SUMBAR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
+    <row r="293">
+      <c r="A293" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
+      <c r="B293" t="inlineStr">
         <is>
           <t>INZS 2026 perkuat komitmen Indonesia hadapi krisis iklim</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr"/>
-      <c r="E205" t="inlineStr">
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah Indonesia terus mempercepat transisi energi sebagai bagian dari upaya mengatasi perubahan iklim melalui berbagai proyek yang mulai direalisasikan. Komitmen tersebut mengemuka dalam Indonesia Net Zero Summit (INZS) 2026 di Balai Kartini, Jakarta, Sabtu (1/8). Pendiri Foreign Policy Community of Indonesia (FPCI), Dino Patti Djalal, menegaskan bahwa penanganan perubahan iklim harus menjadi prioritas karena dampaknya menyentuh hampir seluruh aspek kehidupan manusia.
 (Irfan Hardiansah/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr">
+      <c r="F293" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676087/inzs-2026-perkuat-komitmen-indonesia-hadapi-krisis-iklim</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr">
+      <c r="G293" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/INZS-2026-PERKUAT-KOMITMEN-INDONESIA-HADAPI-KRISIS-IKLIM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
+    <row r="294">
+      <c r="A294" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="B294" t="inlineStr">
         <is>
           <t>Kemeriahan menyambut bulan kemerdekaan Indonesia di Malaysia</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr">
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="inlineStr">
         <is>
           <t>ANTARA - Kegembiraan menyambut bulan kemerdekaan Republik Indonesia turut dirasakan para warga negara Indonesia yang berada di negeri jiran Malaysia. WNI dengan penuh antusias mengikuti berbagai perlombaan yang diselenggarakan Kedutaan Besar Republik Indonesia (KBRI) di Kuala Lumpur, Malaysia, Sabtu (1/8).
 (Rangga Pandu Asmara Jingga/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr">
+      <c r="F294" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676063/kemeriahan-menyambut-bulan-kemerdekaan-indonesia-di-malaysia</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr">
+      <c r="G294" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KEMERIAHAN-MENYAMBUT-BULAN-KEMERDEKAAN-INDONESIA-DI-MALAYSIA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
+    <row r="295">
+      <c r="A295" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B295" t="inlineStr">
         <is>
           <t>Cari Bibit unggul, Bogor gelar sirkuit panjat tebing anak dan remaja</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr">
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="inlineStr">
         <is>
           <t>ANTARA - Federasi Panjat Tebing Indonesia (FPTI) Kota Bogor menggelar Sirkuit Panjat Tebing se-Kota Bogor sebagai ajang pencarian bibit atlet muda, Sabtu (1/8). Dengan diikuti 100 peserta anak-anak dan remaja, kegiatan itu mempertandingkan kategori lead dan speed untuk kelompok umur under 11, under 13, dan under 19.
 (Fadzar Ilham Pangestu/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr">
+      <c r="F295" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676021/cari-bibit-unggul-bogor-gelar-sirkuit-panjat-tebing-anak-dan-remaja</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr">
+      <c r="G295" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/CARI-BIBIT-UNGGUL-BOGOR-GELAR-SIRKUIT-PANJAT-TEBING-ANAK-DAN-REMAJA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Karhutla Tumbang Nusa meluas, 104 hektar gambut terbakar</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>ANTARA - Kebakaran hutan dan lahan (karhutla) di Desa Tumbang Nusa, Kecamatan Jabiren Raya, Kabupaten Pulang Pisau, Kalimantan Tengah, telah menghanguskan sekitar 104 hektare lahan gambut, Sabtu (1/8). Peristiwa tersebut memicu operasi penanganan terpadu yang melibatkan sekitar 416 personel gabungan melalui jalur darat, serta didukung dua unit helikopter water bombing untuk mempercepat pemadaman yang jauh dari tim darat. 
-(Redianto Tumon Sp/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676013/karhutla-tumbang-nusa-meluas-104-hektar-gambut-terbakar</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/KARHUTLA-TUMBANG-NUSA-MELUAS-104-HEKTAR-GAMBUT-TERBAKAR.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>54 Atlet menembak Kalsel, bertanding pada Kejuaraan Wali Kota Cup</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>ANTARA - Pemerintah Kota Banjarmasin bersama Perbakin menggelar kejuaraan menembak Wali Kota Cup 2026. Kejuaraan diikuti oleh 54 atlet dari berbagai daerah di Kalsel sebagai wadah seleksi dan persiapan atlet kalimantan selatan menuju Pra-PON.
-(Latif Thohir/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5675995/54-atlet-menembak-kalsel-bertanding-pada-kejuaraan-wali-kota-cup</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/54-ATLET-MENEMBAK-KALSEL-BERTANDING-PADA-KEJUARAAN-WALI-KOTA-CUP.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Polda Riau kirim Tim Ekspedisi Merah Putih Presisi ke 17 desa 3T</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>ANTARA - Kapolda Riau Irjen Pol Herry Heryawan melepas Tim Ekspedisi Merah Putih Presisi Polda Riau yang akan bertugas di 17 desa wilayah tertinggal, terdepan, dan terluar atau 3T, Sabtu (1/8). Ekspedisi yang berlangsung hingga 17 Agustus mendatang itu membawa berbagai program sosial, lingkungan, dan penguatan kebangsaan bagi masyarakat pesisir serta wilayah terluar di Provinsi Riau.
-(Farah Khadija/Annisa Firdausi/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5675964/polda-riau-kirim-tim-ekspedisi-merah-putih-presisi-ke-17-desa-3t</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/POLDA-RIAU-KIRIM-TIM-EKSPEDISI-MERAH-PUTIH-PRESISI-KE-17-DESA-3T.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Hadapi El Nino, pemerintah tingkatkan mitigasi karhutla</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>ANTARA - Pemerintah memperkuat langkah antisipasi menghadapi potensi el nino yang diperkirakan meningkatkan risiko kebakaran hutan dan lahan. Menteri Lingkungan Hidup, Muhammad Jumhur Hidayat usai membuka Indonesia Net Zero Summit (INZS) 2026 yang diselenggarakan di Balai Kartini, Jakarta, pada Sabtu (1/8) menyebutkan, pihaknya menekan potensi karhutla sejak dini, salah satunya dengan membangun kanal blocking.
-(Irfan Hardiansah/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5675936/hadapi-el-nino-pemerintah-tingkatkan-mitigasi-karhutla</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/HADAPI-EL-NINO-PEMERINTAH-TINGKATKAN-MITIGASI-KARHUTLA.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Mensos resmikan Sekolah Rakyat Terintegrasi 1 Sukoharjo</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>ANTARA - Menteri Sosial Republik Indonesia Saifullah Yusuf membuka pelaksanaan Masa Pengenalan Lingkungan Sekolah (MPLS) di Sekolah Rakyat Terintegrasi (SRT) 1 Kabupaten Sukoharjo, Sabtu (1/8). Mensos menyebut meski proses pembangunan fisik belum sepenuhnya rampung, pihaknya memastikan kegiatan belajar mengajar sudah dapat dilaksanakan karena progres pembangunan telah mencapai sekitar 98 persen.(Denik Apriyani/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5675924/mensos-resmikan-sekolah-rakyat-terintegrasi-1-sukoharjo</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/MENSOS-RESMIKAN-SEKOLAH-RAKYAT-TERINTEGRASI-1-SUKOHARJO.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Lanud Sjamsudin Noor gelar Bakti Sosial Hari Bakti TNI AU ke-79</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>ANTARA - Ratusan warga di Banjarbaru, Kalimantan Selatan, antusias mengikuti kegiatan bakti sosial yang diselenggarakan oleh Pangkalan Udara (Lanud) Sjamsudin Noor pada Sabtu (1/8). Kegiatan ini dilaksanakan sebagai rangkaian peringatan Hari Bhakti TNI Angkatan Udara Ke-79
-(Latif Thohir/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5675872/lanud-sjamsudin-noor-gelar-bakti-sosial-hari-bakti-tni-au-ke-79</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/LANUD-SJAMSUDIN-NOOR-GELAR-BAKTI-SOSIAL-HARI-BAKTI-TNI-AU-KE-79.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Prancis perketat pemeriksaan produk tani, lawan praktik francization</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>ANTARA - Prancis memperketat pemeriksaan terhadap asal-usul produk pertanian guna memberantas praktik "francization", yaitu pelabelan ulang produk impor agar tampak sebagai hasil produksi dalam negeri. Langkah ini diambil untuk melindungi konsumen dan produsen lokal, dengan pelanggar terancam denda hingga 300.000 euro dan hukuman penjara.(XINHUA/ Nabila Anisya Charisty/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5675865/prancis-perketat-pemeriksaan-produk-tani-lawan-praktik-francization</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PRANCIS-PERKETAT-PEMERIKSAAN-PRODUK-TANI-LAWAN-PRAKTIK-FRANCIZATION.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>KM. Prince Soya terbakar saat bersandar di Pelabuhan Samarinda</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>ANTARA - Kapal Motor (KM) Prince Soya terbakar pada Sabtu (1/8) saat bersandar di Pelabuhan Samarinda, Kalimantan Timur. Kapal penumpang yang biasa melayani rute Samarinda - Pare-Pare, Sulawesi Selatan itu terbakar di bagian dek sebelah kanan yang diduga bersumber dari tangki berisi pelumas mesin. (Hanifan Ma'ruf/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5675853/km-prince-soya-terbakar-saat-bersandar-di-pelabuhan-samarinda</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/KM.PRINCE-SOYA-TERBAKAR-SAAT-BERSANDAR-DI-PELABUHAN-SAMARINDA.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>St. Petersburg luncurkan festival sepeda motor untuk pertama kalinya</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:25:02 +0700</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr"/>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>ANTARA - Saint Petersburg Motor Festival resmi dibuka, Jumat (31/7) selama tiga hari berturut-turut dalam pembukaan perdananya. Acara tersebut digelar untuk menghibur para penikmat sepeda motor, musik, serta pengunjung umum lainnya.(XINHUA/ Nabila Anisya Charisty/Satrio Giri Marwanto/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5675828/st-petersburg-luncurkan-festival-sepeda-motor-untuk-pertama-kalinya</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/ST.PETERSBURG-LUNCURKAN-FESTIVAL-SEPEDA-MOTOR-UNTUK-PERTAMA-KALINYA.jpg</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G216"/>
+  <autoFilter ref="A1:G295"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_antara_2026-08-03.xlsx
+++ b/data/berita_antara_2026-08-03.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$295</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$380</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,10 +419,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G295"/>
+  <dimension ref="A1:G380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -5461,99 +5461,99 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>terkini, top-news</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Prabowo dukung peningkatan latihan bersama militer RI-Thailand</t>
+          <t>GMR Group menilai Danantara tingkatkan kepercayaan investor asing</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:21:32 +0700</t>
+          <t>Mon, 03 Aug 2026 19:18:34 +0700</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Presiden Prabowo Subianto mendukung peningkatan frekuensi latihan bersama antara Tentara Nasional Indonesia (TNI) dan ...</t>
+          <t>GMR Group, perusahaan multinasional yang bergerak di bidang infrastruktur, menilai adanya Badan Pengelola Investasi ...</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678081/prabowo-dukung-peningkatan-latihan-bersama-militer-ri-thailand</t>
+          <t>https://www.antaranews.com/berita/5678080/gmr-group-menilai-danantara-tingkatkan-kepercayaan-investor-asing</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.41.07.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/5b406f4a-aeea-42ae-9194-16c4cace22d9.jpeg</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>GMR Group menilai Danantara tingkatkan kepercayaan investor asing</t>
+          <t>Dukcapil Kepulauan Seribu terbaik dalamcapaian IKD di Rakornas 2026</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:18:34 +0700</t>
+          <t>Mon, 03 Aug 2026 19:17:51 +0700</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>GMR Group, perusahaan multinasional yang bergerak di bidang infrastruktur, menilai adanya Badan Pengelola Investasi ...</t>
+          <t>Suku Dinas Kependudukan dan Catatan Sipil (Sudin Dukcapil) Kabupaten Kepulauan Seribu menjadi yang terbaik dalam ...</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678080/gmr-group-menilai-danantara-tingkatkan-kepercayaan-investor-asing</t>
+          <t>https://www.antaranews.com/berita/5678072/dukcapil-kepulauan-seribu-terbaik-dalamcapaian-ikd-di-rakornas-2026</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/5b406f4a-aeea-42ae-9194-16c4cace22d9.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Screen-Shot-2026-08-03-at-18.15.44.jpg</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Dukcapil Kepulauan Seribu terbaik dalamcapaian IKD di Rakornas 2026</t>
+          <t>BYD masih menyelidiki mobil listrik yang terbakar di Cikampek</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:17:51 +0700</t>
+          <t>Mon, 03 Aug 2026 19:17:16 +0700</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Suku Dinas Kependudukan dan Catatan Sipil (Sudin Dukcapil) Kabupaten Kepulauan Seribu menjadi yang terbaik dalam ...</t>
+          <t>Tim BYD Motor Indonesia masih menyelidiki mobil listrik yang terbakar di dekat gerbang jalan tol Cikampek di ...</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678072/dukcapil-kepulauan-seribu-terbaik-dalamcapaian-ikd-di-rakornas-2026</t>
+          <t>https://otomotif.antaranews.com/berita/5678069/byd-masih-menyelidiki-mobil-listrik-yang-terbakar-di-cikampek</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Screen-Shot-2026-08-03-at-18.15.44.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_3319.jpeg</t>
         </is>
       </c>
     </row>
@@ -5565,61 +5565,61 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>BYD masih menyelidiki mobil listrik yang terbakar di Cikampek</t>
+          <t>BPS Bali: Panen melimpah dan permintaan tinggi buat makanan deflasi</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:17:16 +0700</t>
+          <t>Mon, 03 Aug 2026 19:16:38 +0700</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Tim BYD Motor Indonesia masih menyelidiki mobil listrik yang terbakar di dekat gerbang jalan tol Cikampek di ...</t>
+          <t>Badan Pusat Statistik (BPS) Bali melihat panen yang melimpah dan permintaan yang tinggi menyebabkan sejumlah komoditas ...</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5678069/byd-masih-menyelidiki-mobil-listrik-yang-terbakar-di-cikampek</t>
+          <t>https://www.antaranews.com/berita/5678065/bps-bali-panen-melimpah-dan-permintaan-tinggi-buat-makanan-deflasi</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_3319.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0326.jpeg</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>BPS Bali: Panen melimpah dan permintaan tinggi buat makanan deflasi</t>
+          <t>Program Taruna Bakti Kepolisian latih siswa Sekolah Rakyat Lhokseumawe</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:16:38 +0700</t>
+          <t>Mon, 03 Aug 2026 19:15:13 +0700</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) Bali melihat panen yang melimpah dan permintaan yang tinggi menyebabkan sejumlah komoditas ...</t>
+          <t>ANTARA - Ratusan siswa dari Sekolah Rakyat Lhokseumawe, Aceh, memperoleh edukasi kemandirian oleh Taruna Akademi ...</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678065/bps-bali-panen-melimpah-dan-permintaan-tinggi-buat-makanan-deflasi</t>
+          <t>https://www.antaranews.com/video/5678013/program-taruna-bakti-kepolisian-latih-siswa-sekolah-rakyat-lhokseumawe</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0326.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_PROGRAM-TARUNA-BAKTI-KEPOLISIAN-LATIH-SISWA-SEKOLAH-RAKYAT-LHOKSEUMAWE.jpg</t>
         </is>
       </c>
     </row>
@@ -5631,28 +5631,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Program Taruna Bakti Kepolisian latih siswa Sekolah Rakyat Lhokseumawe</t>
+          <t>Basarnas terus evakuasi korban kebakaran KMP Mutiara Sentosa II</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:15:13 +0700</t>
+          <t>Mon, 03 Aug 2026 19:14:24 +0700</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>ANTARA - Ratusan siswa dari Sekolah Rakyat Lhokseumawe, Aceh, memperoleh edukasi kemandirian oleh Taruna Akademi ...</t>
+          <t>Badan SAR Nasional terus melakukan evakuasi terhadap korban kebakaran Kapal Motor Penumpang (KMP) Mutiara Sentosa II di ...</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678013/program-taruna-bakti-kepolisian-latih-siswa-sekolah-rakyat-lhokseumawe</t>
+          <t>https://www.antaranews.com/berita/5678060/basarnas-terus-evakuasi-korban-kebakaran-kmp-mutiara-sentosa-ii</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_PROGRAM-TARUNA-BAKTI-KEPOLISIAN-LATIH-SISWA-SEKOLAH-RAKYAT-LHOKSEUMAWE.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/262391.jpg</t>
         </is>
       </c>
     </row>
@@ -5664,28 +5664,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Basarnas terus evakuasi korban kebakaran KMP Mutiara Sentosa II</t>
+          <t>Di hadapan Charnvirakul, Prabowo akui dekat dengan Raja Vajiralongkorn</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:14:24 +0700</t>
+          <t>Mon, 03 Aug 2026 19:13:21 +0700</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Badan SAR Nasional terus melakukan evakuasi terhadap korban kebakaran Kapal Motor Penumpang (KMP) Mutiara Sentosa II di ...</t>
+          <t>Presiden Prabowo Subianto saat pertemuan bilateral bersama Perdana Menteri (PM) Thailand Anutin Charnvirakul di Istana ...</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678060/basarnas-terus-evakuasi-korban-kebakaran-kmp-mutiara-sentosa-ii</t>
+          <t>https://www.antaranews.com/berita/5678059/di-hadapan-charnvirakul-prabowo-akui-dekat-dengan-raja-vajiralongkorn</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/262391.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/9d36af3c-bb87-4f6e-8c20-0b32c63b4cdb.jpeg</t>
         </is>
       </c>
     </row>
@@ -5697,127 +5697,127 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Di hadapan Charnvirakul, Prabowo akui dekat dengan Raja Vajiralongkorn</t>
+          <t>Inflasi di Sumut sebesar 4,20 persen, emas menjadi penyumbang utama</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:13:21 +0700</t>
+          <t>Mon, 03 Aug 2026 19:12:35 +0700</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Presiden Prabowo Subianto saat pertemuan bilateral bersama Perdana Menteri (PM) Thailand Anutin Charnvirakul di Istana ...</t>
+          <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Sumatera Utara mencatat pada Juli 2026 Sumatera Utara mengalami inflasi ...</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678059/di-hadapan-charnvirakul-prabowo-akui-dekat-dengan-raja-vajiralongkorn</t>
+          <t>https://www.antaranews.com/video/5677867/inflasi-di-sumut-sebesar-420-persenemas-menjadi-penyumbang-utama</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/9d36af3c-bb87-4f6e-8c20-0b32c63b4cdb.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_INFLASI-DI-SUMUT-SEBESAR-4-20-PERSEN-EMAS-MENJADI-PENYUMBANG-UTAMA.jpg</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Inflasi di Sumut sebesar 4,20 persen, emas menjadi penyumbang utama</t>
+          <t>Tim PKM-K USK raih pendanaan nasional dari inovasi nilam</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:12:35 +0700</t>
+          <t>Mon, 03 Aug 2026 19:11:12 +0700</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Sumatera Utara mencatat pada Juli 2026 Sumatera Utara mengalami inflasi ...</t>
+          <t>Tim Program Kreativitas Mahasiswa Bidang Kewirausahaan (PKM-K) Universitas Syiah Kuala (USK) meraih pendanaan nasional ...</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5677867/inflasi-di-sumut-sebesar-420-persenemas-menjadi-penyumbang-utama</t>
+          <t>https://www.antaranews.com/berita/5678056/tim-pkm-k-usk-raih-pendanaan-nasional-dari-inovasi-nilam</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_INFLASI-DI-SUMUT-SEBESAR-4-20-PERSEN-EMAS-MENJADI-PENYUMBANG-UTAMA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/pamer-sera.jpeg</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ekonomi-finansial, terkini, top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>OJK: Kredit perbankan tumbuh 12,67 persen capai Rp9.080,9 triliun</t>
+          <t>Prabowo sebut Indonesia dan Thailand perlu lebih sering bertemu</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:12:24 +0700</t>
+          <t>Mon, 03 Aug 2026 19:10:55 +0700</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Otoritas Jasa Keuangan (OJK) melaporkan penyaluran kredit perbankan di tanah air tumbuh 12,67 persen year on year ...</t>
+          <t>Presiden RI Prabowo Subianto mendorong intensifikasi pertemuan dan koordinasi berkala antara Indonesia dan Thailand ...</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678057/ojk-kredit-perbankan-tumbuh-1267-persen-capai-rp90809-triliun</t>
+          <t>https://www.antaranews.com/berita/5678053/prabowo-sebut-indonesia-dan-thailand-perlu-lebih-sering-bertemu</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.15.18_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/presiden-prabowo-menerima-kunjungan-pm-thailand-2833227.jpg</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Tim PKM-K USK raih pendanaan nasional dari inovasi nilam</t>
+          <t>Persela fokus bangun kekompakan tim melalui pemusatan latihan</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:11:12 +0700</t>
+          <t>Mon, 03 Aug 2026 19:09:07 +0700</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Tim Program Kreativitas Mahasiswa Bidang Kewirausahaan (PKM-K) Universitas Syiah Kuala (USK) meraih pendanaan nasional ...</t>
+          <t>Persela Lamongan memfokuskan program pemusatan latihan (training camp/TC) dalam waktu dekat untuk membangun kekompakan ...</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678056/tim-pkm-k-usk-raih-pendanaan-nasional-dari-inovasi-nilam</t>
+          <t>https://www.antaranews.com/berita/5678051/persela-fokus-bangun-kekompakan-tim-melalui-pemusatan-latihan</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/pamer-sera.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_2426.jpeg</t>
         </is>
       </c>
     </row>
@@ -5829,193 +5829,193 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Prabowo sebut Indonesia dan Thailand perlu lebih sering bertemu</t>
+          <t>Mensos nilai model penjangkauan Sekolah Rakyat Gresik efektif</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:10:55 +0700</t>
+          <t>Mon, 03 Aug 2026 19:06:21 +0700</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Presiden RI Prabowo Subianto mendorong intensifikasi pertemuan dan koordinasi berkala antara Indonesia dan Thailand ...</t>
+          <t>Menteri Sosial (Mensos) Saifullah Yusuf menilai model penjangkauan calon peserta didik Sekolah Rakyat Terintegrasi ...</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678053/prabowo-sebut-indonesia-dan-thailand-perlu-lebih-sering-bertemu</t>
+          <t>https://www.antaranews.com/berita/5678047/mensos-nilai-model-penjangkauan-sekolah-rakyat-gresik-efektif</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/presiden-prabowo-menerima-kunjungan-pm-thailand-2833227.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_2424.jpeg</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Persela fokus bangun kekompakan tim melalui pemusatan latihan</t>
+          <t>Gubernur Lampung: Satelit Lampung-1 hadirkan data perkuat tata kelola</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:09:07 +0700</t>
+          <t>Mon, 03 Aug 2026 19:03:30 +0700</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Persela Lamongan memfokuskan program pemusatan latihan (training camp/TC) dalam waktu dekat untuk membangun kekompakan ...</t>
+          <t>Gubernur Lampung Rahmat Mirzani Djausal mengatakan bahwa adanya Satelit Lampung-1 dapat menghadirkan data yang dapat ...</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678051/persela-fokus-bangun-kekompakan-tim-melalui-pemusatan-latihan</t>
+          <t>https://www.antaranews.com/berita/5678045/gubernur-lampung-satelit-lampung-1-hadirkan-data-perkuat-tata-kelola</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_2426.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/aiOrWseraa2O3uCaQVIZM4OV576Qw9W8bnYIuRFD-1.jpg</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Mensos nilai model penjangkauan Sekolah Rakyat Gresik efektif</t>
+          <t>Kemenperin meyakini pasar industri olahraga RI terus meningkat</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:06:21 +0700</t>
+          <t>Mon, 03 Aug 2026 19:03:16 +0700</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Menteri Sosial (Mensos) Saifullah Yusuf menilai model penjangkauan calon peserta didik Sekolah Rakyat Terintegrasi ...</t>
+          <t>Kementerian Perindustrian (Kemenperin) meyakini pasar industri olahraga nasional terus meningkat seiring perubahan gaya ...</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678047/mensos-nilai-model-penjangkauan-sekolah-rakyat-gresik-efektif</t>
+          <t>https://www.antaranews.com/berita/5678041/kemenperin-meyakini-pasar-industri-olahraga-ri-terus-meningkat</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_2424.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/AIS_0039_1.JPG-1-_edit_223911681240831.jpg</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Gubernur Lampung: Satelit Lampung-1 hadirkan data perkuat tata kelola</t>
+          <t>Menkomdigi minta masyarakat waspadai lonjakan hoaks jelang HUT RI</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:03:30 +0700</t>
+          <t>Mon, 03 Aug 2026 19:01:26 +0700</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Gubernur Lampung Rahmat Mirzani Djausal mengatakan bahwa adanya Satelit Lampung-1 dapat menghadirkan data yang dapat ...</t>
+          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengingatkan masyarakat untuk mewaspadai meningkatnya penyebaran ...</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678045/gubernur-lampung-satelit-lampung-1-hadirkan-data-perkuat-tata-kelola</t>
+          <t>https://www.antaranews.com/video/5677959/menkomdigi-minta-masyarakat-waspadai-lonjakan-hoaks-jelang-hut-ri</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/aiOrWseraa2O3uCaQVIZM4OV576Qw9W8bnYIuRFD-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_MENKOMDIGI-MINTA-MASYARAKAT-WASPADAI-LONJAKAN-HOAKS-JELANG-HUT-RI.jpg</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Kemenperin meyakini pasar industri olahraga RI terus meningkat</t>
+          <t>Ketegangan geopolitik, Prancis perketat pengawasan investasi asing</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:03:16 +0700</t>
+          <t>Mon, 03 Aug 2026 19:00:58 +0700</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Kementerian Perindustrian (Kemenperin) meyakini pasar industri olahraga nasional terus meningkat seiring perubahan gaya ...</t>
+          <t>Prancis telah memperketat kontrol terhadap investasi asing di perusahaan-perusahaan strategis, menurunkan ambang batas ...</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678041/kemenperin-meyakini-pasar-industri-olahraga-ri-terus-meningkat</t>
+          <t>https://www.antaranews.com/berita/5678037/ketegangan-geopolitik-prancis-perketat-pengawasan-investasi-asing</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/AIS_0039_1.JPG-1-_edit_223911681240831.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/28/Prancis.jpg</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>photo, terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>TNI AL gagalkan penyelundupan pasir timah di Kepri</t>
+          <t>Sulbar dan UGM gelar pangan murah stabilisasi harga pangan</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:01:39 +0700</t>
+          <t>Mon, 03 Aug 2026 18:59:54 +0700</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Dankodaeral IV Laksamana Muda TNI Berkat Widjanarko (kanan) dan Kepala Seksi Tindak Pidana Umum Pada Kejaksaan Negeri ...</t>
+          <t>Pemerintah Provinsi Sulawesi Barat berkolaborasi dengan Universitas Gadjah Mada (UGM) melalui program KKN-PPM UGM ...</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5678039/tni-al-gagalkan-penyelundupan-pasir-timah-di-kepri</t>
+          <t>https://www.antaranews.com/berita/5678031/sulbar-dan-ugm-gelar-pangan-murah-stabilisasi-harga-pangan</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Pengagalan-Penyelundupan-Pasir-Timah-Ilegal-030826-Adm-7.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_191550.jpg</t>
         </is>
       </c>
     </row>
@@ -6027,28 +6027,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Menkomdigi minta masyarakat waspadai lonjakan hoaks jelang HUT RI</t>
+          <t>Inggris pangkas anggaran kesehatan mental Rp605 miliar</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:01:26 +0700</t>
+          <t>Mon, 03 Aug 2026 18:59:30 +0700</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengingatkan masyarakat untuk mewaspadai meningkatnya penyebaran ...</t>
+          <t>London Mental Health Foundation berencana memangkas biaya lebih dari 25 juta pound sterling (sekitar ...</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5677959/menkomdigi-minta-masyarakat-waspadai-lonjakan-hoaks-jelang-hut-ri</t>
+          <t>https://www.antaranews.com/berita/5678028/inggris-pangkas-anggaran-kesehatan-mental-rp605-miliar</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_MENKOMDIGI-MINTA-MASYARAKAT-WASPADAI-LONJAKAN-HOAKS-JELANG-HUT-RI.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/22/Inggris.jpg</t>
         </is>
       </c>
     </row>
@@ -6060,160 +6060,160 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ketegangan geopolitik, Prancis perketat pengawasan investasi asing</t>
+          <t>Belgia peringatkan gelombang panas, suhu tembus 36 derajat Celsius</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:00:58 +0700</t>
+          <t>Mon, 03 Aug 2026 18:57:57 +0700</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Prancis telah memperketat kontrol terhadap investasi asing di perusahaan-perusahaan strategis, menurunkan ambang batas ...</t>
+          <t>Institut Meteorologi Kerajaan Belgia mengeluarkan peringatan panas oranye untuk sebagian besar wilayah negara itu, ...</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678037/ketegangan-geopolitik-prancis-perketat-pengawasan-investasi-asing</t>
+          <t>https://www.antaranews.com/berita/5678021/belgia-peringatkan-gelombang-panas-suhu-tembus-36-derajat-celsius</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/28/Prancis.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/30/panas-ekstrem-Eropa.jpg</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>terkini, top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Menkomdigi: KIP garda depan informasi jernih dan perangi hoaks</t>
+          <t>Brantas Abipraya rampungkan Sekolah Rakyat Terintegrasi Cirebon</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:00:50 +0700</t>
+          <t>Mon, 03 Aug 2026 18:56:19 +0700</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid mengatakan Komisi Informasi Pusat (KIP) menjadi garda terdepan ...</t>
+          <t>PT Brantas Abipraya (Persero) merampungkan pembangunan Sekolah Rakyat Terintegrasi Kabupaten Cirebon yang memasuki ...</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678033/menkomdigi-kip-garda-depan-informasi-jernih-dan-perangi-hoaks</t>
+          <t>https://www.antaranews.com/berita/5678019/brantas-abipraya-rampungkan-sekolah-rakyat-terintegrasi-cirebon</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0321.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/4643878B-8428-4EFC-9266-E070C27E50CC.jpeg</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Sulbar dan UGM gelar pangan murah stabilisasi harga pangan</t>
+          <t>Pemkot Jakbar vaksinasi HPV ratusan siswa di SDN Meruya Utara 02</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:59:54 +0700</t>
+          <t>Mon, 03 Aug 2026 18:56:15 +0700</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Pemerintah Provinsi Sulawesi Barat berkolaborasi dengan Universitas Gadjah Mada (UGM) melalui program KKN-PPM UGM ...</t>
+          <t>Pemerintah Kota (Pemkot) Jakarta Barat (Jakbar) menggelar vaksinasi Human Papillomavirus (HPV) bagi murid laki-laki di ...</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678031/sulbar-dan-ugm-gelar-pangan-murah-stabilisasi-harga-pangan</t>
+          <t>https://www.antaranews.com/berita/5678017/pemkot-jakbar-vaksinasi-hpv-ratusan-siswa-di-sdn-meruya-utara-02</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_191550.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_181232.v1.jpg</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Inggris pangkas anggaran kesehatan mental Rp605 miliar</t>
+          <t>Bahlil prioritaskan relaksasi RKAB untuk perusahaan royalti tinggi</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:59:30 +0700</t>
+          <t>Mon, 03 Aug 2026 18:53:41 +0700</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>London Mental Health Foundation berencana memangkas biaya lebih dari 25 juta pound sterling (sekitar ...</t>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia memprioritaskan relaksasi Rencana Kerja dan Anggaran ...</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678028/inggris-pangkas-anggaran-kesehatan-mental-rp605-miliar</t>
+          <t>https://www.antaranews.com/berita/5678009/bahlil-prioritaskan-relaksasi-rkab-untuk-perusahaan-royalti-tinggi</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/22/Inggris.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-16.12.45-1.jpeg</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>terkini, top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Satu tahun Sekolah Rakyat, ratusan siswa torehkan prestasi</t>
+          <t>Menhan sebut program P3MD tepat untuk ciptaan SDM berkualitas</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:59:25 +0700</t>
+          <t>Mon, 03 Aug 2026 18:51:19 +0700</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Menteri Sosial (Mensos) Saifullah Yusuf menyatakan selama satu tahun Sekolah Rakyat berdiri sudah ratusan ...</t>
+          <t>Menteri Pertahanan Sjafrie Sjamsoeddin mengatakan Program Presiden untuk Pemimpin Masa Depan (P3MD) merupakan program ...</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678024/satu-tahun-sekolah-rakyat-ratusan-siswa-torehkan-prestasi</t>
+          <t>https://www.antaranews.com/berita/5678004/menhan-sebut-program-p3md-tepat-untuk-ciptaan-sdm-berkualitas</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176441.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001554793.jpg</t>
         </is>
       </c>
     </row>
@@ -6225,28 +6225,28 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Belgia peringatkan gelombang panas, suhu tembus 36 derajat Celsius</t>
+          <t>Kemensos luncurkan Taman Anak Sejahtera di Banyumas</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:57:57 +0700</t>
+          <t>Mon, 03 Aug 2026 18:50:24 +0700</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Institut Meteorologi Kerajaan Belgia mengeluarkan peringatan panas oranye untuk sebagian besar wilayah negara itu, ...</t>
+          <t>Kementerian Sosial melalui Direktorat Rehabilitasi Sosial Anak menggelar meluncurkan Taman Anak Sejahtera (TAS) dalam ...</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678021/belgia-peringatkan-gelombang-panas-suhu-tembus-36-derajat-celsius</t>
+          <t>https://www.antaranews.com/berita/5678000/kemensos-luncurkan-taman-anak-sejahtera-di-banyumas</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/30/panas-ekstrem-Eropa.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176439.jpg</t>
         </is>
       </c>
     </row>
@@ -6258,28 +6258,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Brantas Abipraya rampungkan Sekolah Rakyat Terintegrasi Cirebon</t>
+          <t>JustMarkets mendedahkan bagaimana kejutan IHP memacu turun naik pasaran forex</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:56:19 +0700</t>
+          <t>Mon, 03 Aug 2026 18:47:49 +0700</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>PT Brantas Abipraya (Persero) merampungkan pembangunan Sekolah Rakyat Terintegrasi Kabupaten Cirebon yang memasuki ...</t>
+          <t>JustMarkets baru sahaja mengeluarkan pandangan tentang bagaimana kejutan IHP benar-benar memacu turun naik pasaran ...</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678019/brantas-abipraya-rampungkan-sekolah-rakyat-terintegrasi-cirebon</t>
+          <t>https://www.antaranews.com/berita/5677996/justmarkets-mendedahkan-bagaimana-kejutan-ihp-memacu-turun-naik-pasaran-forex</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/4643878B-8428-4EFC-9266-E070C27E50CC.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/02/05/Logo-cision_2.jpg</t>
         </is>
       </c>
     </row>
@@ -6291,94 +6291,94 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Pemkot Jakbar vaksinasi HPV ratusan siswa di SDN Meruya Utara 02</t>
+          <t>Polisi buru pelaku illegal tapping pipa Pertamina di lintas Sumatera</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:56:15 +0700</t>
+          <t>Mon, 03 Aug 2026 18:47:43 +0700</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Pemerintah Kota (Pemkot) Jakarta Barat (Jakbar) menggelar vaksinasi Human Papillomavirus (HPV) bagi murid laki-laki di ...</t>
+          <t>Tim Kepolisian Resor (Polres) Jambi tengah memburu para pelaku pencurian minyak dengan cara illegal tapping pada pipa ...</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678017/pemkot-jakbar-vaksinasi-hpv-ratusan-siswa-di-sdn-meruya-utara-02</t>
+          <t>https://www.antaranews.com/berita/5677995/polisi-buru-pelaku-illegal-tapping-pipa-pertamina-di-lintas-sumatera</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_181232.v1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/363585.jpg</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Bahlil prioritaskan relaksasi RKAB untuk perusahaan royalti tinggi</t>
+          <t>Departemen Perang AS jalani misi napak tilas Perang Dunia II di Biak</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:53:41 +0700</t>
+          <t>Mon, 03 Aug 2026 18:47:23 +0700</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia memprioritaskan relaksasi Rencana Kerja dan Anggaran ...</t>
+          <t>Sebuah tim Departemen Perang Amerika Serikat merampungkan misi napak tilas pencarian artefak sejarah dan jenazah ...</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678009/bahlil-prioritaskan-relaksasi-rkab-untuk-perusahaan-royalti-tinggi</t>
+          <t>https://www.antaranews.com/berita/5677992/departemen-perang-as-jalani-misi-napak-tilas-perang-dunia-ii-di-biak</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-16.12.45-1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Biak1-9900000000079e3c.jpg</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini, top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Menkeu: Realisasi anggaran MBG Rp101,1 T untuk 63,13 juta penerima</t>
+          <t>Kisah haru Lia Maharani saat pertama pakai seragam baru Sekolah Rakyat</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:53:14 +0700</t>
+          <t>Mon, 03 Aug 2026 18:47:01 +0700</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa mengungkapkan bahwa realisasi anggaran Program Makan Bergizi Gratis ...</t>
+          <t>Membelikan seragam sekolah baru untuk anak menjadi momen biasa bagi sebagian orang tua murid. Namun, tidak bagi Titin ...</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678005/menkeu-realisasi-anggaran-mbg-rp1011-t-untuk-6313-juta-penerima</t>
+          <t>https://www.antaranews.com/berita/5677989/kisah-haru-lia-maharani-saat-pertama-pakai-seragam-baru-sekolah-rakyat</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29-2.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176437.jpg</t>
         </is>
       </c>
     </row>
@@ -6390,28 +6390,28 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Menhan sebut program P3MD tepat untuk ciptaan SDM berkualitas</t>
+          <t>Jaksel sterilisasi 441 ekor kucing selama Juli untuk tekan populasi</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:51:19 +0700</t>
+          <t>Mon, 03 Aug 2026 18:46:24 +0700</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Menteri Pertahanan Sjafrie Sjamsoeddin mengatakan Program Presiden untuk Pemimpin Masa Depan (P3MD) merupakan program ...</t>
+          <t>Suku Dinas Ketahanan Pangan Kelautan dan Pertanian (Sudin KPKP) Jakarta Selatan (Jaksel) telah melakukan ...</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678004/menhan-sebut-program-p3md-tepat-untuk-ciptaan-sdm-berkualitas</t>
+          <t>https://www.antaranews.com/berita/5677981/jaksel-sterilisasi-441-ekor-kucing-selama-juli-untuk-tekan-populasi</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001554793.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001010408.jpg</t>
         </is>
       </c>
     </row>
@@ -6423,3777 +6423,6585 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Kemensos luncurkan Taman Anak Sejahtera di Banyumas</t>
+          <t>Milken Institute Umumkan Asia Summit 2026, Dorong Kepemimpinan Cerdas di Era AI</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:50:24 +0700</t>
+          <t>Mon, 03 Aug 2026 18:44:50 +0700</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Kementerian Sosial melalui Direktorat Rehabilitasi Sosial Anak menggelar meluncurkan Taman Anak Sejahtera (TAS) dalam ...</t>
+          <t>Di tengah meningkatnya ketegangan geopolitik global dan kemajuan teknologi yang pesat, Milken Institute menggelar ...</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678000/kemensos-luncurkan-taman-anak-sejahtera-di-banyumas</t>
+          <t>https://www.antaranews.com/berita/5677977/milken-institute-umumkan-asia-summit-2026-dorong-kepemimpinan-cerdas-di-era-ai</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176439.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/10/08/Milken_Institute_Logo.jpg</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>JustMarkets mendedahkan bagaimana kejutan IHP memacu turun naik pasaran forex</t>
+          <t>Swalayan UMKM Kotim diproyeksikan jadi sentra oleh-oleh khas daerah</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:47:49 +0700</t>
+          <t>Mon, 03 Aug 2026 18:44:01 +0700</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>JustMarkets baru sahaja mengeluarkan pandangan tentang bagaimana kejutan IHP benar-benar memacu turun naik pasaran ...</t>
+          <t>Pemerintah Kabupaten Kotawaringin Timur (Kotim), Kalimantan Tengah menyiapkan Swalayan Usaha Mikro, Kecil dan Menengah ...</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677996/justmarkets-mendedahkan-bagaimana-kejutan-ihp-memacu-turun-naik-pasaran-forex</t>
+          <t>https://www.antaranews.com/berita/5677976/swalayan-umkm-kotim-diproyeksikan-jadi-sentra-oleh-oleh-khas-daerah</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/02/05/Logo-cision_2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001719121.jpg</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Polisi buru pelaku illegal tapping pipa Pertamina di lintas Sumatera</t>
+          <t>PLN Jakarta pastikan pasokan listrik sudah berhasil dipulihkan</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:47:43 +0700</t>
+          <t>Mon, 03 Aug 2026 08:36:26 +0700</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Tim Kepolisian Resor (Polres) Jambi tengah memburu para pelaku pencurian minyak dengan cara illegal tapping pada pipa ...</t>
+          <t>PT PLN (Persero) Unit Induk Distribusi Jakarta Raya mengungkapkan pasokan listrik telah berhasil ...</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677995/polisi-buru-pelaku-illegal-tapping-pipa-pertamina-di-lintas-sumatera</t>
+          <t>https://www.antaranews.com/berita/5677043/pln-jakarta-pastikan-pasokan-listrik-sudah-berhasil-dipulihkan</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/363585.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20231217-WA0015-1.jpg</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Departemen Perang AS jalani misi napak tilas Perang Dunia II di Biak</t>
+          <t>Ledakan di kantor polisi Pakistan tewaskan 14 orang</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:47:23 +0700</t>
+          <t>Mon, 03 Aug 2026 07:44:23 +0700</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Sebuah tim Departemen Perang Amerika Serikat merampungkan misi napak tilas pencarian artefak sejarah dan jenazah ...</t>
+          <t>Sebuah ledakan terjadi di luar sebuah kantor polisi di Kota Kabal, Pakistan, mengakibatkan 14 orang tewas dan 14 orang ...</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677992/departemen-perang-as-jalani-misi-napak-tilas-perang-dunia-ii-di-biak</t>
+          <t>https://www.antaranews.com/berita/5677020/ledakan-di-kantor-polisi-pakistan-tewaskan-14-orang</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Biak1-9900000000079e3c.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CmxztpE000019_20260803_PEPFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Kisah haru Lia Maharani saat pertama pakai seragam baru Sekolah Rakyat</t>
+          <t>Musim panen tekan harga hortikultura bikin deflasi 0,35 persen di NTB</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:47:01 +0700</t>
+          <t>Mon, 03 Aug 2026 18:38:20 +0700</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Membelikan seragam sekolah baru untuk anak menjadi momen biasa bagi sebagian orang tua murid. Namun, tidak bagi Titin ...</t>
+          <t>Badan Pusat Statistik (BPS) menyatakan musim panen menekan harga komoditas hortikultura dan memicu deflasi sebesar 0,35 ...</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677989/kisah-haru-lia-maharani-saat-pertama-pakai-seragam-baru-sekolah-rakyat</t>
+          <t>https://www.antaranews.com/berita/5677956/musim-panen-tekan-harga-hortikultura-bikin-deflasi-035-persen-di-ntb</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176437.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001432193.jpg</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>terkini, top-news</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Polri perkuat langkah preventif respons isu keamanan nasional</t>
+          <t>Wamenperin optimistis PMI manufaktur RI terus meningkat</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:46:34 +0700</t>
+          <t>Mon, 03 Aug 2026 18:36:38 +0700</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Polri memastikan terus memperkuat langkah preventif untuk menjaga keamanan nasional sehingga aktivitas masyarakat dan ...</t>
+          <t>Wakil Menteri Perindustrian (Wamenperin) Faisol Riza optimistis kinerja manufaktur Indonesia terus mengalami ...</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677985/polri-perkuat-langkah-preventif-respons-isu-keamanan-nasional</t>
+          <t>https://www.antaranews.com/berita/5677952/wamenperin-optimistis-pmi-manufaktur-ri-terus-meningkat</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/1000086556.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Wamenperin.jpg</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Jaksel sterilisasi 441 ekor kucing selama Juli untuk tekan populasi</t>
+          <t>Menkop dorong pembentukan koperasi syariah perluas akses modal</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:46:24 +0700</t>
+          <t>Mon, 03 Aug 2026 18:34:52 +0700</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Suku Dinas Ketahanan Pangan Kelautan dan Pertanian (Sudin KPKP) Jakarta Selatan (Jaksel) telah melakukan ...</t>
+          <t>Menteri Koperasi (Menkop) Ferry Juliantono mendorong pembentukan koperasi syariah di lingkungan Wanita Pengusaha ...</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677981/jaksel-sterilisasi-441-ekor-kucing-selama-juli-untuk-tekan-populasi</t>
+          <t>https://www.antaranews.com/berita/5677948/menkop-dorong-pembentukan-koperasi-syariah-perluas-akses-modal</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001010408.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-16.50.13.jpeg</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Milken Institute Umumkan Asia Summit 2026, Dorong Kepemimpinan Cerdas di Era AI</t>
+          <t>Ekonom: Hilirisasi nikel perlu diimbangi penguatan ekspor pertanian</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:44:50 +0700</t>
+          <t>Mon, 03 Aug 2026 18:23:50 +0700</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Di tengah meningkatnya ketegangan geopolitik global dan kemajuan teknologi yang pesat, Milken Institute menggelar ...</t>
+          <t>Ekonom Center of Reform on Economics (CORE) Indonesia Yusuf Rendy Manilet menilai keberhasilan hilirisasi nikel dalam ...</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677977/milken-institute-umumkan-asia-summit-2026-dorong-kepemimpinan-cerdas-di-era-ai</t>
+          <t>https://www.antaranews.com/berita/5677921/ekonom-hilirisasi-nikel-perlu-diimbangi-penguatan-ekspor-pertanian</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/10/08/Milken_Institute_Logo.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/16/IMG_20251116_190439.jpg</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Swalayan UMKM Kotim diproyeksikan jadi sentra oleh-oleh khas daerah</t>
+          <t>CORE: Pertumbuhan ekspor ke AS sinyal positif daya saing produk RI</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:44:01 +0700</t>
+          <t>Mon, 03 Aug 2026 18:19:03 +0700</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Pemerintah Kabupaten Kotawaringin Timur (Kotim), Kalimantan Tengah menyiapkan Swalayan Usaha Mikro, Kecil dan Menengah ...</t>
+          <t>Ekonom Center of Reform on Economics (CORE) Indonesia Yusuf Rendy Manilet menilai pertumbuhan ekspor Indonesia ke ...</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677976/swalayan-umkm-kotim-diproyeksikan-jadi-sentra-oleh-oleh-khas-daerah</t>
+          <t>https://www.antaranews.com/berita/5677908/core-pertumbuhan-ekspor-ke-as-sinyal-positif-daya-saing-produk-ri</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001719121.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/28/1001021030.jpg</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Prabowo dan PM Thailand bertemu empat mata di Istana Merdeka</t>
+          <t>ATR/BPN tetapkan 15 Kantah jadi percontohan pelayanan peralihan hak</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 17:49:52 +0700</t>
+          <t>Mon, 03 Aug 2026 18:18:57 +0700</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Presiden Prabowo Subianto dan Perdana Menteri Thailand Anutin Charnvirakul menggelar pertemuan empat mata di Istana ...</t>
+          <t>Kementerian Agraria dan Tata Ruang/Badan Pertanahan Nasional (ATR/BPN) menyatakan terdapat 15 Kantor Pertanahan ...</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677828/prabowo-dan-pm-thailand-bertemu-empat-mata-di-istana-merdeka</t>
+          <t>https://www.antaranews.com/berita/5677904/atr-bpn-tetapkan-15-kantah-jadi-percontohan-pelayanan-peralihan-hak</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_5162.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_175241.jpg</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Kepala BGN tingkatkan status keracunan MBG jadi kejadian fatal</t>
+          <t>Lebih maskulin, intip rupa hingga spek Suzuki Fronx SGX Hybrid Kuro</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 17:10:19 +0700</t>
+          <t>Mon, 03 Aug 2026 18:15:42 +0700</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
+          <t>Suzuki menghadirkan penyegaran pada varian tertinggi SUV Fronx melalui Suzuki Fronx SGX Hybrid Kuro, tampil lebih ...</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5677893/lebih-maskulin-intip-rupa-hingga-spek-suzuki-fronx-sgx-hybrid-kuro</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_1872.JPG.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>PMI manufaktur naik, Kadin: Didorong peningkatan produksi-permintaan</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:15:15 +0700</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Kamar Dagang dan Industri (Kadin) Indonesia menilai kenaikan Purchasing Managers’ Index (PMI) manufaktur ...</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677892/pmi-manufaktur-naik-kadin-didorong-peningkatan-produksi-permintaan</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/22/WhatsApp-Image-2026-02-22-at-8.24.35-AM_edit_336327027051281.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>TNI kerahkan delapan helikopter salurkan bantuan ke Puncak</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>ANTARA - Komando Gabungan Wilayah Pertahanan (Kogabwilhan) III mengerahkan delapan helikopter TNI Angkatan Darat dan TNI Angkatan Udara untuk menyalurkan bantuan kemanusiaan ke tiga distrik di Kabupaten Puncak, Papua Tengah, yang terdampak kekeringan berkepanjangan hingga memicu krisis pangan. (Laksa Mahendra/Satrio Giri Marwanto/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676720/tni-kerahkan-delapan-helikopter-salurkan-bantuan-ke-puncak</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/TNI-KERAHKAN-DELAPAN-HELIKOPTER-SALURKAN-BANTUAN-KE-PUNCAK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Jakarta Watersport Festival dorong sport tourism di Danau Sunter</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>ANTARA - Jakarta Watersport Festival 2026 digelar di Danau Sunter, Jakarta Utara, pada 1–2 Agustus. Festival ini menghadirkan kompetisi olahraga air, hiburan, dan bazar UMKM sebagai upaya mendorong sport tourism serta aktivitas ekonomi kreatif di ibu kota. (Nabila Athifa/Setyanka Harviana Putri/Satrio Giri Marwanto/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676713/jakarta-watersport-festival-dorong-sport-tourism-di-danau-sunter</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/JAKARTA-WATERSPORT-FESTIVAL-DORONG-SPORT-TOURISM-DI-DANAU-SUNTER.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Ledakan restoran di Moskow tewaskan tiga orang</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>ANTARA - Tiga orang tewas dan sedikitnya 21 lainnya luka-luka setelah ledakan alat peledak rakitan terjadi di sebuah restoran di kawasan Kudrinskaya Square, pusat Kota Moskow, Rusia, Sabtu (1/8). Menurut Komite Antiterorisme Nasional Rusia, ledakan terjadi ketika seorang perempuan berupaya membawa alat peledak ke dalam restoran, namun dihentikan petugas keamanan. Penyelidikan terkait motif serangan masih berlangsung. (Arsy Fitriady/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676660/ledakan-restoran-di-moskow-tewaskan-tiga-orang</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/LEDAKAN-RESTORAN-DI-MOSKOW-TEWASKAN-TIGA-ORANG_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>DKPPP Temanggung edukasi warga cegah zoonosis dari hewan piaraan</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>ANTARA - Dinas Ketahanan Pangan, Pertanian, dan Perikanan (DKPPP) Kabupaten Temanggung bersama komunitas pecinta hewan mengedukasi masyarakat tentang pentingnya menjaga kesehatan hewan piaraan untuk mencegah zoonosis atau penyakit yang dapat menular dari hewan ke manusia. Edukasi meliputi pemberian nutrisi, vaksinasi, kebersihan, dan pemeriksaan kesehatan hewan secara berkala. (Firman Eko Handy/Satrio Giri Marwanto/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676647/dkppp-temanggung-edukasi-warga-cegah-zoonosis-dari-hewan-piaraan</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/DKPPP-TEMANGGUNG-EDUKASI-WARGA-CEGAH-ZOONOSIS-DARI-HEWAN-PIARAAN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>BP Batam siapkan Sekolah Terintegrasi Merah Putih di Rempang</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Pengusahaan (BP) Batam menyiapkan pembangunan Sekolah Terintegrasi Merah Putih di Rempang, Kepulauan Riau, sebagai sekolah gratis bagi siswa berprestasi. Sekolah yang dibangun di atas lahan seluas 18 hektare itu akan melayani jenjang sekolah dasar hingga sekolah menengah atas dengan fasilitas pendidikan dan olahraga yang lengkap. (Angiela Chantiequ/Satrio Giri Marwanto/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676644/bp-batam-siapkan-sekolah-terintegrasi-merah-putih-di-rempang</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/BP-BATAM-SIAPKAN-SEKOLAH-TERINTEGRASI-MERAH-PUTIH-DI-REMPANG.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Aldila Sutjiadi juarai WTA 500 Mubadala DC Open 2026</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>ANTARA - Petenis ganda putri Indonesia Aldila Sutjiadi menjuarai nomor ganda Women's Tennis Association (WTA) 500 Mubadala DC Open 2026 di Washington, Amerika Serikat. Berpasangan dengan petenis Selandia Baru Erin Routliffe, Aldila mengalahkan Andreja Klepac dari Slovenia dan Makoto Ninomiya dari Jepang dua set langsung 6-4, 6-1 pada partai final. Gelar tersebut menjadi trofi WTA kedelapan dalam karier Aldila di nomor ganda sekaligus gelar kedua bersama Routliffe pada musim 2026.
+(Arsy Fitriady/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676629/aldila-sutjiadi-juarai-wta-500-mubadala-dc-open-2026</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/ALDILA-SUTJIADI-JUARAI-WTA-500-MUBADALA-DC-OPEN-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>KM Mutiara Sentosa 2 Terbakar Saat Berlayar ke Makassar</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>ANTARA - Kapal Motor (KM) Mutiara Sentosa 2 terbakar di perairan utara Pulau Madura saat berlayar dari Pelabuhan Tanjung Perak Surabaya menuju Makassar, Minggu (2/8). Kapal tersebut mengangkut sekitar 250 orang. Tim SAR gabungan masih melakukan evakuasi penumpang, sementara penyebab kebakaran masih dalam penyelidikan. (Hanif Nasrullah/Satrio Giri Marwanto/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676617/km-mutiara-sentosa-2-terbakar-saat-berlayar-ke-makassar</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/KM-MUTIARA-SENTOSA-2-TERBAKAR-SAAT-BERLAYAR-KE-MAKASSAR.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>BI dan Pemkot Kendari Perkuat Digitalisasi UMKM</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>ANTARA - Kantor Perwakilan Bank Indonesia Sulawesi Tenggara bersama Pemerintah Kota Kendari menggelar Festival Kuliner Sultra Maimo 2026 untuk memperkuat digitalisasi usaha mikro, kecil, dan menengah atau UMKM. Festival yang berlangsung pada 2 hingga 9 Agustus itu juga mendorong perluasan transaksi non-tunai berbasis QRIS. (Saharudin/Satrio Giri Marwanto/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676607/bi-dan-pemkot-kendari-perkuat-digitalisasi-umkm</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/BI-DAN-PEMKOT-KENDARI-PERKUAT-DIGITALISASI-UMKM.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>El Nino menguat, negara fokus jaga ketersediaan air &amp; tangani karhutla</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>ANTARA - Gelombang panas sebagai akibat El Nino mulai dirasakan dampaknya di sejumlah belahan dunia. Kebakaran hutan dan lahan atau karhutla, juga mulai terjadi di dalam negeri, seperti di Pulau Sumatera dan Kalimantan.Selain kebakaran, bencana ekologi yang terjadi ialah kekeringan. Beberapa daerah di Pulau Jawa seperti Temanggung, Sukoharjo, Lumajang, Banten, lalu daerah luar Jawa seperti Nusa Tenggara Barat dan Timur, hingga Bangka Belitung mulai mengalami krisis air bersih.Presiden pun memanggil sejumlah kepala kementerian dan lembaga terkait, untuk memberi pemaparan dan masukan guna meredam dampak El Nino.Lalu bagaimana sikap antisipatif yang disiapkan pemerintah pada musim kemarau dan el nino tahun ini? Selengkapnya dalam PerANTARA! (Roy Rosa Bachtiar/Suci Nurhaliza/Gunawan Wibisono/Rizky Bagus Dhermawan/Farah Khadija)</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676540/el-nino-menguat-negara-fokus-jaga-ketersediaan-air-tangani-karhutla</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/DF.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Padang Padang Cup Bali jadi ajang peselancar Nasional unjuk kehebatan</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>ANTARA - Kompetisi selancar ombak Internasional Rip Curl Cup Padang Padang kembali digelar dan berlangsung pada 1-31 Agustus 2026, di Pantai Padang Padang, Labuan Sait Pecatu, Kuta Selatan, Bali. Ajang ini menjadi ruang bagi peselancar Nasional menunjukkan kehebatan mereka bersaing dengan peselancar Internasional. (Rita Laura/Sandy Arizona/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676257/padang-padang-cup-bali-jadi-ajang-peselancar-nasional-unjuk-kehebatan</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_PADANG-PADANG-CUP-BALI-JADI-AJANG-PESELANCAR-NASIONAL-UNJUK-KEHEBATAN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Bekuk Port FC, Persebaya gandeng Persija ke semifinal</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>ANTARA - Persebaya membekuk Port FC 2 - 1 di laga terakhir Grup B turnamen sepak Piala Presiden 2026. Dengan hasil ini Persija lolos ke babak semifinal bersama Persebaya sebagai wakil Grup B. (Hanif Nasrullah/Sandy Arizona/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676252/bekuk-port-fc-persebaya-gandeng-persija-ke-semifinal</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_BEKUK-PORT-FC-PERSEBAYA-GANDENG-PERSIJA-KE-SEMIFINAL.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Aston Villa unggul 3-1 dari Indonesia All Stars dalam tur pramusim</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>ANTARA - Tim Indonesia All Stars, harus mengakui keunggulan atas Aston Villa dengan skor 3-1, saat laga Friendly Match di Stadion Utama Gelora Bung Karno (SUGBK) Senayan, Jakarta, pada Sabtu (1/8). Penjaga Gawang Aston Villa, James Wright, saat ditemui media di GBK mengapresiasi para pemain Indonesia All Stars, karena dinilai memiliki kualitas yang baik. (Ryan Rahman/Sandy Arizona/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676239/aston-villa-unggul-3-1-dari-indonesia-all-stars-dalam-tur-pramusim</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_ASTON-VILLA-UNGGUL-3-1-DARI-INDONESIA-ALL-STARS-DALAM-TUR-PRAMUSIM.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Joko Widodo dinobatkan sebagai sesepuh oleh sembilan Raja Timor</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>ANTARA - Ribuan warga memadati kawasan Pantai Lahi Lai Bissi Kopan (LLBK) Kota Kupang, Nusa Tenggara Timur, untuk menyaksikan Karnaval Budaya yang dihadiri Presiden ke-7 Republik Indonesia, Joko Widodo. Dalam prosesi adat yang menjadi puncak acara, Joko Widodo dinobatkan sebagai sesepuh atau saudara oleh sembilan raja dari kerajaan-kerajaan di Pulau Timor sebagai bentuk penghormatan terhadap nilai persaudaraan dan budaya masyarakat Timor. (Johanes Viandinando/Sandy Arizona/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676205/joko-widodo-dinobatkan-sebagai-sesepuh-oleh-sembilan-raja-timor</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_JOKO-WIDODO-DINOBATKAN-SEBAGAI-SESEPUH-OLEH-SEMBILAN-RAJA-TIMOR.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Menag: Indeks kerukunan umat beragama RI jadi 77,89 persen di 2025</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Agama Nasaruddin Umar menyebut indeks kerukunan umat beragama naik menjadi 77,89 persen pada tahun 2025, dari sebelumnya, yakni 76,47 persen pada tahun 2024. Hal tersebut disampaikan oleh Menag saat mengahdiri agenda Zikir dan Doa Kebangsaan "Indonesia Berdaulat, Adil dan Makmur" di Lapangan Silang Monas, Jakarta, Sabtu (1/8).
+(Afra Augesti/Nico Anggriawan/Sandy Arizona/Nabila Anisya Charisty)</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676188/menag-indeks-kerukunan-umat-beragama-ri-jadi-7789-persen-di-2025</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_MENAG-INDEKS-KERUKUNAN-UMAT-BERAGAMA-RI-JADI-77-89-PERSEN-DI-2025.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>KKP bantu pelaku usaha perikanan terdampak bencana di Sumbar</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>ANTARA - Kementerian Kelautan dan Perikanan (KKP) bersama Tim Satuan Tugas Percepatan Rehabilitasi dan Rekonstruksi (PRR) Provinsi Sumatera Barat, mempercepat dan memastikan operasionalisasi budi daya, nelayan serta pengolahan ikan segera berjalan pascabencana hidrometeorologi yang terjadi akhir November tahun lalu. Untuk itu, KKP memberikan bantuan awal berupa bibit ikan dan pakan, dan ekskavator, kepada pelaku usaha perikanan yang terdampak bencana hidrometeorologis di Kota Padang, Kabupaten Padang Pariaman, Kabupaten Solok dan Kabupaten Agam.
+(Melani Friati/Sandy Arizona/Nabila Anisya Charisty)</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676172/kkp-bantu-pelaku-usaha-perikanan-terdampak-bencana-di-sumbar</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_KKP-BANTU-PELAKU-USAHA-PERIKANAN-TERDAMPAK-BENCANA-DI-SUMBAR.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>INZS 2026 perkuat komitmen Indonesia hadapi krisis iklim</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Indonesia terus mempercepat transisi energi sebagai bagian dari upaya mengatasi perubahan iklim melalui berbagai proyek yang mulai direalisasikan. Komitmen tersebut mengemuka dalam Indonesia Net Zero Summit (INZS) 2026 di Balai Kartini, Jakarta, Sabtu (1/8). Pendiri Foreign Policy Community of Indonesia (FPCI), Dino Patti Djalal, menegaskan bahwa penanganan perubahan iklim harus menjadi prioritas karena dampaknya menyentuh hampir seluruh aspek kehidupan manusia.
+(Irfan Hardiansah/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676087/inzs-2026-perkuat-komitmen-indonesia-hadapi-krisis-iklim</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/INZS-2026-PERKUAT-KOMITMEN-INDONESIA-HADAPI-KRISIS-IKLIM.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Kemeriahan menyambut bulan kemerdekaan Indonesia di Malaysia</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>ANTARA - Kegembiraan menyambut bulan kemerdekaan Republik Indonesia turut dirasakan para warga negara Indonesia yang berada di negeri jiran Malaysia. WNI dengan penuh antusias mengikuti berbagai perlombaan yang diselenggarakan Kedutaan Besar Republik Indonesia (KBRI) di Kuala Lumpur, Malaysia, Sabtu (1/8).
+(Rangga Pandu Asmara Jingga/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676063/kemeriahan-menyambut-bulan-kemerdekaan-indonesia-di-malaysia</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/KEMERIAHAN-MENYAMBUT-BULAN-KEMERDEKAAN-INDONESIA-DI-MALAYSIA.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Cari Bibit unggul, Bogor gelar sirkuit panjat tebing anak dan remaja</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>ANTARA - Federasi Panjat Tebing Indonesia (FPTI) Kota Bogor menggelar Sirkuit Panjat Tebing se-Kota Bogor sebagai ajang pencarian bibit atlet muda, Sabtu (1/8). Dengan diikuti 100 peserta anak-anak dan remaja, kegiatan itu mempertandingkan kategori lead dan speed untuk kelompok umur under 11, under 13, dan under 19.
+(Fadzar Ilham Pangestu/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676021/cari-bibit-unggul-bogor-gelar-sirkuit-panjat-tebing-anak-dan-remaja</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/CARI-BIBIT-UNGGUL-BOGOR-GELAR-SIRKUIT-PANJAT-TEBING-ANAK-DAN-REMAJA.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Kepala BGN: Putusan MK perkuat Program Makan Bergizi Gratis</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:32:37 +0700</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono mengatakan putusan Mahkamah Konstitusi (MK) Nomor 40/PUU-XXIV/2026 yang ...</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678436/kepala-bgn-putusan-mk-perkuat-program-makan-bergizi-gratis</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/189743.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>photo, terkini</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Piala AFF 2026 : Indonesia takluk 0-3 dari Vietnam</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:26:45 +0700</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Pelatih Timnas Indonesia Jhon Herdman memberikan arahan kepada anak didiknya saat melawan Timnas Vietnam pada ...</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5678435/piala-aff-2026-indonesia-takluk-0-3-dari-vietnam</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Timnas-Indonesia-lawan-Vietnam-030826-Bay-11b.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Banjir kepung 15 titik di Kota Padang akibat cuaca ekstrem</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:25:29 +0700</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>ANTARA - Hujan lebat disertai angin kencang memicu bencana di Kabupaten Agam, Kota Pariaman, dan Kota Padang, Sumatera ...</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5678396/banjir-kepung-15-titik-di-kota-padang-akibat-cuaca-ekstrem</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BANJIR-KEPUNG-15-TITIK-DI-KOTA-PADANG-AKIBAT-CUACA-EKSTREM.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Pemkab Aceh Tenggara batasi pembelian BBM untuk cegah penimbunan</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:25:13 +0700</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Pemerintah Kabupaten Aceh Tenggara bersama Forkopimda setempat saat ini telah melakukan pembatasan pembelian bahan ...</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678431/pemkab-aceh-tenggara-batasi-pembelian-bbm-untuk-cegah-penimbunan</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/20260803-Bupati-Aceh-Tenggara-HM-Salim-Fakhry.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>MTI dorong kemudahan transaksi nirsentuh di MRT Jakarta</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:24:07 +0700</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>PT Mitra Transaksi Indonesia (MTI) atau YOKKE mendukung penerapan sistem pembayaran kartu nirsentuh berbasis Europay, ...</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678427/mti-dorong-kemudahan-transaksi-nirsentuh-di-mrt-jakarta</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.59.08.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Erick ungkap strategi sebelum kembali ke bursa calon Ketum PSSI 2027</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:22:41 +0700</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>ANTARA - Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir tidak menutup kemungkinan untuk ...</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5678327/erick-ungkap-strategi-sebelum-kembali-ke-bursa-calon-ketum-pssi-2027</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/ERICK-UNGKAP-STRATEGI-SEBELUM-KEMBALI-KE-BURSA-CALON-KETUM-PSSI-2027.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>ekonomi-bursa, terkini</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>BEI terbitkan aturan emiten belum penuhi "free float" dapat notasi "P"</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:18:19 +0700</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>PT Bursa Efek Indonesia (BEI) efektif memberlakukan dua Surat Edaran (SE) perihal Penambahan Tampilan Informasi Notasi ...</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678425/bei-terbitkan-aturan-emiten-belum-penuhi-free-float-dapat-notasi-p</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/pergerakan-indeks-harga-saham-gabungan-270726-dr-01.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>KPK dalami proyek Dinas PUPR Bengkulu saat periksa kepala dinas</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:16:44 +0700</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Komisi Pemberantasan Korupsi (KPK) mendalami sejumlah proyek di Dinas Pekerjaan Umum dan Penataan Ruang (PUPR) Kota ...</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678421/kpk-dalami-proyek-dinas-pupr-bengkulu-saat-periksa-kepala-dinas</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_8199.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Palestina: Kesepakatan fase 2 gencatan Gaza belum terwujud</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:16:19 +0700</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Otoritas Palestina (PA), Senin, mengatakan bahwa kesepakatan tentang implementasi fase kedua kesepakatan gencatan ...</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678419/palestina-kesepakatan-fase-2-gencatan-gaza-belum-terwujud</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/Gaza-luluh-lantak-setelah-2-tahun-diserbu-Israel.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>KP2MI gandeng BPJS Kesehatan, Kemensos lindungi pekerja migran</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:15:17 +0700</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Kementerian Pelindungan Pekerja Migran Indonesia (P2MI) menandatangani nota kesepahaman dengan BPJS Kesehatan dan ...</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678416/kp2mi-gandeng-bpjs-kesehatan-kemensos-lindungi-pekerja-migran</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/KP2MI-kerja-sama-dengan-BPJS-Kesehatan-dan-Kemensos-03082026-1.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Ketum PSSI utarakan pesan Presiden agar timnas tampil di Piala Dunia</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:13:08 +0700</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>ANTARA - Presiden Prabowo Subianto menyampaikan, Tim Nasional (Timnas) Indonesia sangat dekat untuk bisa tampil di ...</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5678179/ketum-pssi-utarakan-pesan-presiden-agar-timnas-tampil-di-piala-dunia</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KETUM-PSSI-UTARAKAN-PESAN-PRESIDEN-AGAR-TIMNAS-TAMPIL-DI-PIALA-DUNIA.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Prabowo ucapkan belasungkawa atas wafatnya Putri Bajrakitiyabha</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:11:29 +0700</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto menyampaikan belasungkawa kepada keluarga kerajaan dan rakyat Thailand atas wafatnya Putri ...</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678413/prabowo-ucapkan-belasungkawa-atas-wafatnya-putri-bajrakitiyabha</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_A022F56749B0-1.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Spesifikasi vivo S2 diungkap, termasuk layar dan kameranya</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:10:56 +0700</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Perusahaan teknologi vivo pada Senin mengungkap spesifikasi vivo S2, termasuk informasi tentang layar, ...</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678409/spesifikasi-vivo-s2-diungkap-termasuk-layar-dan-kameranya</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000857060.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Prabowo: Rute penerbangan baru pererat hubungan masyarakat RI-Thailand</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:08:38 +0700</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Presiden RI Prabowo Subianto menyambut baik peningkatan konektivitas dan rute penerbangan langsung antara Indonesia dan ...</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678407/prabowo-rute-penerbangan-baru-pererat-hubungan-masyarakat-ri-thailand</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-20.57.02.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>KI DKI dorong KI Pusat perkuat keterbukaan informasi di era digital</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:08:36 +0700</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Komisi Informasi (KI) DKI Jakarta mendorong kepengurusan baru Komisi Informasi Pusat (KIP) periode 2026-2030 untuk ...</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678403/ki-dki-dorong-ki-pusat-perkuat-keterbukaan-informasi-di-era-digital</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0028_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Pangkogabwilhan III ultimatum OPM hentikan kejahatan kemanusiaan</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:07:18 +0700</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Panglima Komando Gabungan Wilayah Pertahanan (Pangkogabwilhan) III Letjen TNI Lucky Avianto mengultimatum kelompok ...</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678399/pangkogabwilhan-iii-ultimatum-opm-hentikan-kejahatan-kemanusiaan</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/24/KOGABWILHAN-III-1_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Prabowo sambut kerja sama investasi sektor swasta Indonesia-Thailand</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:05:46 +0700</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto menyambut baik komitmen kerja sama dan investasi sektor swasta Indonesia dan Thailand yang ...</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678397/prabowo-sambut-kerja-sama-investasi-sektor-swasta-indonesia-thailand</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_A022F56749B0-1.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Pemprov NTB benahi tarif hingga infrastruktur Mandalika jelang MotoGP</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:04:56 +0700</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Provinsi Nusa Tenggara Barat benahi sejumlah aspek yang menjadi sorotan pada ajang MotoGP seri ...</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5678319/pemprov-ntb-benahi-tarif-hingga-infrastruktur-mandalika-jelang-motogp</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PEMPROV-NTB-BENAHI-TARIF-HINGGA-INFRASTRUKTUR-MANDALIKA-JELANG-MOTOGP.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Wabup Sumenep pastikan korban KMP Mutiara dapat layanan medis maksimal</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:02:59 +0700</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Wakil Bupati Sumenep KH Imam Hasyim memastikan para korban kebakaran KMP Mutiara Sentosa II yang kini sedang dirawat di ...</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678392/wabup-sumenep-pastikan-korban-kmp-mutiara-dapat-layanan-medis-maksimal</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Wabup-Sumenep-1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>MenPANRB sebut arsip fondasi pemerintahan dan pelayanan publik</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:01:22 +0700</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Menteri Pendayagunaan Aparatur Negara dan Reformasi Birokrasi Rini Widyantini menegaskan arsip merupakan aset strategis ...</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678388/menpanrb-sebut-arsip-fondasi-pemerintahan-dan-pelayanan-publik</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000578636.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Dua terdakwa kasus LPEI serahkan 172 alat bukti aliran dana pihak lain</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:01:02 +0700</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Sebanyak dua terdakwa kasua LPEI, Handoko Limaho dan Liu Raymond, menyerahkan 172 alat bukti terkait dugaan aliran dana ...</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678385/dua-terdakwa-kasus-lpei-serahkan-172-alat-bukti-aliran-dana-pihak-lain</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000468436.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>The Antheia Project salurkan ratusan paket sembako di Kepulauan Seribu</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:54:49 +0700</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>The Antheia Project menyalurkan 898 paket sembako kepada warga kurang mampu dan santunan kepada 314 anak di ...</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678384/the-antheia-project-salurkan-ratusan-paket-sembako-di-kepulauan-seribu</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/20260803150033.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial, terkini</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Cadangan devisa RI jadi 145 M dolar AS, BI sebut masih di level aman</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:52:44 +0700</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>ANTARA - Bank Indonesia (BI) mengungkapkan cadangan devisa pada akhir Juli 2026 berada di posisi 145 miliar dolar AS. ...</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5678347/cadangan-devisa-ri-jadi-145-m-dolar-as-bi-sebut-masih-di-level-aman</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_CADANGAN-DEVISA-RI-JADI-145-M-DOLAR-AS-BI-SEBUT-MASIH-DI-LEVEL-AMAN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial, terkini</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>BI: Inflasi Juli terjaga berkat sinergi bank sentral dan pemerintah</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:51:39 +0700</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Bank Indonesia (BI) memandang inflasi Indeks Harga Konsumen (IHK) pada Juli 2026 tetap terjaga dalam sasaran target, ...</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678380/bi-inflasi-juli-terjaga-berkat-sinergi-bank-sentral-dan-pemerintah</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/07/WhatsApp-Image-2026-07-07-at-14.31.59_edited.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Prabowo apresiasi bantuan Thailand pulangkan korban penipuan daring</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:50:55 +0700</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto mengapresiasi Pemerintah Thailand yang membantu memfasilitasi pemulangan hampir 1.000 warga ...</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678379/prabowo-apresiasi-bantuan-thailand-pulangkan-korban-penipuan-daring</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/keterangan-pers-presiden-prabowo-dan-pm-thailand-2833503.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Persipura akan berkandang di Jawa Timur untuk putaran pertama</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:49:41 +0700</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Persipura Jayapura akan berkandang di Jawa Timur pada putaran pertama kompetisi kasta kedua Championship musim ...</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678377/persipura-akan-berkandang-di-jawa-timur-untuk-putaran-pertama</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_9099.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>KONI apresiasi PP FISI jadi tuan rumah kejuaraan internasional</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:45:47 +0700</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Komite Olahraga Nasional Indonesia (KONI) diwakili Sekretaris Jenderal (Sekjen) Pusat Tb. Lukman Djajadikusuma ...</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678373/koni-apresiasi-pp-fisi-jadi-tuan-rumah-kejuaraan-internasional</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/kejuaraan-seluncur-es-terbuka-asia-2026-2833361.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Indonesia-Thailand adopsi peta jalan kemitraan strategis</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:45:42 +0700</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto dan Perdana Menteri Thailand Anutin Charnvirakul mengadopsi Peta Jalan Kemitraan Strategis ...</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678372/indonesia-thailand-adopsi-peta-jalan-kemitraan-strategis</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/tempImageSC2ajl.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Menjemput harapan korban kapal terbakar di perairan Sumenep</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:44:20 +0700</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Lampu di Gedung Gapura Surya Nusantara (GSN), Pelabuhan Tanjung Perak, Surabaya, belum juga padam ketika jarum jam ...</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678368/menjemput-harapan-korban-kapal-terbakar-di-perairan-sumenep</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/263329.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Denny Sumargo dan Vonny Anggraini reuni di film "Baby Udon"</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:43:16 +0700</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Aktor Denny Sumargo reuni dengan aktris Vonny Anggraini dalam film baru Sumargo Films berjudul "Baby ...</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678367/denny-sumargo-dan-vonny-anggraini-reuni-di-film-baby-udon</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_143722.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Indonesia tambah dua emas nomor kyorugi di Asian Taekwondo Open 2026</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:42:30 +0700</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Indonesia menambah dua medali emas dari nomor kyorugi (tarung) pada ajang 8th Asian Taekwondo Indonesia Open ...</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678364/indonesia-tambah-dua-emas-nomor-kyorugi-di-asian-taekwondo-open-2026</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/raihan-fadhila-raih-emas-asian-taekwondo-indonesia-open-championships-2833405.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Siapkan SDM Untuk Transisi Energi, PLN dan IT PLN Beri Pelatihan Energi Terbarukan Bagi Siswa SMA</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:41:18 +0700</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Jakarta (ANTARA) – PT PLN (Persero) bersama Institut Teknologi PLN (IT PLN) menggelar program pelatihan energi ...</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678363/siapkan-sdm-untuk-transisi-energi-pln-dan-it-pln-beri-pelatihan-energi-terbarukan-bagi-siswa-sma</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-20.14.56.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Indonesia-Thailand bertukar informasi bongkar kejahatan transnasional</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:40:28 +0700</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Pemerintah Indonesia dan Thailand sepakat memperkuat kerja sama penegakan hukum melalui pertukaran informasi, ...</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678361/indonesia-thailand-bertukar-informasi-bongkar-kejahatan-transnasional</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/presiden-prabowo-dan-pm-thailand-sepakati-dua-nota-kesepahaman-2833491.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Nelayan Ambunten bantu evakuasi korban kebakaran KMP Mutiara Sentosa 2</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:39:19 +0700</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Nelayan Ambunten, Sumenep, Jawa Timur membantu mengevakuasi satu orang korban kebakaran KMP Mutiara Sentosa II, ...</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678359/nelayan-ambunten-bantu-evakuasi-korban-kebakaran-kmp-mutiara-sentosa-2</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Polres-Sumenep-evakuasi.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Piala AFF: Indonesia tertinggal 0-2 dari Vietnam pada babak pertama</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:38:52 +0700</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia untuk sementara tertinggal 0-2 dari Vietnam pada babak pertama laga lanjutan Grup A ASEAN Championship ...</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678357/piala-aff-indonesia-tertinggal-0-2-dari-vietnam-pada-babak-pertama</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833517.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Gubernur tegaskan Sumut siap jadi pusat fashion Indonesia lewat wastra</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:37:04 +0700</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Gubernur Sumatera Utara (Sumut) Bobby Nasution menegaskan kesiapan Provinsi Sumut menjadi salah satu pusat fashion ...</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678355/gubernur-tegaskan-sumut-siap-jadi-pusat-fashion-indonesia-lewat-wastra</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001029105.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial, terkini</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>BI: Kepemilikan SRBI oleh bank guna kelola likuiditas, bukan investasi</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:35:49 +0700</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Bank Indonesia (BI) menegaskan bahwa Sekuritas Rupiah Bank Indonesia (SRBI) ditujukan sebagai instrumen pengelolaan ...</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678351/bi-kepemilikan-srbi-oleh-bank-guna-kelola-likuiditas-bukan-investasi</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-21.22.00.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Indonesia-Thailand targetkan perdagangan 20 miliar dolar AS pada 2030</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:34:45 +0700</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Pemerintah Indonesia dan Pemerintah Thailand menargetkan nilai perdagangan bilateral mencapai 20 miliar dolar AS pada ...</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678344/indonesia-thailand-targetkan-perdagangan-20-miliar-dolar-as-pada-2030</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_DE47DEAC0197-1.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Industri kreatif tunjukkan tren positif, musik dan film mendominasi</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:32:54 +0700</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa pertumbuhan ekosistem industri kreatif menunjukkan ...</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5678325/industri-kreatif-tunjukkan-tren-positif-musik-dan-film-mendominasi</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_INDUSTRI-KREATIF-TUNJUKKAN-TREN-POSITIF-MUSIK-DAN-FILM-MENDOMINASI.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Kapal BBM bermuatan 7.600 kiloliter masuk Lombok</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:32:28 +0700</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>PT Pertamina Patra Niaga mendatangkan kapal pengangkut bahan bakar minyak (BBM) dengan total muatan 7.600 kiloliter ...</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678341/kapal-bbm-bermuatan-7600-kiloliter-masuk-lombok</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001432720.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>734 ribu wisatawan China sambangi Indonesia sepanjang semester I-2026</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:29:36 +0700</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Sebanyak 734.691 wisatawan asal China menyambangi Indonesia sepanjang semester I-2026, meningkat 18,5 persen ...</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678340/734-ribu-wisatawan-china-sambangi-indonesia-sepanjang-semester-i-2026</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CjkinzN000032_20260803_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>ekonomi-bursa, terkini</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>OJK bertemu 100 investor global, apresiasi reformasi pasar modal RI</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:29:14 +0700</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Ketua Dewan Komisioner Otoritas Jasa Keuangan (OJK) Friderica Widyasari Dewi mengungkapkan bahwa OJK baru saja ...</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678337/ojk-bertemu-100-investor-global-apresiasi-reformasi-pasar-modal-ri</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.15.18_2.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Kejagung geledah kantor Don Ritto terkait kasus TPPU Febrie Adriansyah</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:29:05 +0700</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Kejaksaan Agung menggeledah sejumlah lokasi, termasuk kantor pihak swasta Don Ritto di Jakarta Selatan, dalam ...</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678333/kejagung-geledah-kantor-don-ritto-terkait-kasus-tppu-febrie-adriansyah</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/23/1000086033_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Whoosh-kereta api dominasi jalur masuk wisatawan mancanegara di Jabar</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:28:59 +0700</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Integrasi transportasi berbasis rel seperti Kereta Cepat Whoosh dan kereta api (KA) konvensional kian mengukuhkan ...</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678332/whoosh-kereta-api-dominasi-jalur-masuk-wisatawan-mancanegara-di-jabar</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1002076644.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Daop 6 Yogyakarta tutup perlintasan tak terjaga Petak Sentolo–Rewulu</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:28:06 +0700</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>PT Kereta Api Indonesia (Persero) Daerah Operasi 6 Yogyakarta terus berkolaborasi dengan pemerintah terkait, untuk ...</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678331/daop-6-yogyakarta-tutup-perlintasan-tak-terjaga-petak-sentolo-rewulu</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000029465.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Kementan usulkan telur masuk skema CPP demi lindungi peternak rakyat</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:27:37 +0700</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian (Kementan) mengusulkan komoditas telur ayam masuk dalam skema pengadaan Cadangan Pangan ...</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678329/kementan-usulkan-telur-masuk-skema-cpp-demi-lindungi-peternak-rakyat</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/9C2BC3E9-1C7E-4159-8805-C378B9294E25.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Lestari dorong distribusi buku diiringi penguatan budaya baca</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:22:14 +0700</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Wakil Ketua MPR RI Lestari Moerdijat mengatakan pendistribusian buku bacaan perlu diiringi upaya menumbuhkan minat baca ...</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678321/lestari-dorong-distribusi-buku-diiringi-penguatan-budaya-baca</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/13/upscalemedia-transformed-145.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Indonesia dan Thailand perkuat kerja sama ekonomi digital</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:18:04 +0700</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Pemerintah Indonesia dan Thailand sepakat memperkuat kerja sama di bidang ekonomi digital, termasuk memperluas ...</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678315/indonesia-dan-thailand-perkuat-kerja-sama-ekonomi-digital</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/prabowo-thiland.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Purbaya: Stabilitas sistem keuangan Indonesia tetap terjaga</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:17:49 +0700</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>ANTARA - Komite Stabilitas Sistem Keuangan (KSSK) memastikan stabilitas sistem keuangan Indonesia tetap terjaga pada ...</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5678257/purbaya-stabilitas-sistem-keuangan-indonesia-tetap-terjaga</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PURBAYA-STABILITAS-SISTEM-KEUANGAN-INDONESIA-TETAP-TERJAGA.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Korban insiden Bundaran HI jalani pemeriksaan Propam Polda Jabar</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:16:48 +0700</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Petugas keamanan proyek MRT di kawasan Bundaran HI, Jakarta Pusat, Fiktor Harefa (27) menjalani pemeriksaan oleh Bidang ...</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678312/korban-insiden-bundaran-hi-jalani-pemeriksaan-propam-polda-jabar</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/25/1000310635.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Prabowo terima tanda kehormatan dari Angkatan Bersenjata Thailand</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:59:35 +0700</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto menerima tanda kehormatan dari Angkatan Bersenjata Kerajaan Thailand yang diberikan pada saat ...</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678283/prabowo-terima-tanda-kehormatan-dari-angkatan-bersenjata-thailand</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/tempImageNOyDfK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:50:37 +0700</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan ...</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial, top-news</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Menkeu: Eskalasi konflik Timteng dorong imbal hasil SBN ke 7,14 persen</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:48:02 +0700</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa mengatakan eskalasi konflik di Timur Tengah mendorong kenaikan imbal hasil Surat ...</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678253/menkeu-eskalasi-konflik-timteng-dorong-imbal-hasil-sbn-ke-714-persen</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-20.38.31.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Prabowo dukung peningkatan latihan bersama militer RI-Thailand</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:21:32 +0700</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto mendukung peningkatan frekuensi latihan bersama antara Tentara Nasional Indonesia (TNI) dan ...</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678081/prabowo-dukung-peningkatan-latihan-bersama-militer-ri-thailand</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.41.07.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial, top-news</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>OJK: Kredit perbankan tumbuh 12,67 persen capai Rp9.080,9 triliun</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:12:24 +0700</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Otoritas Jasa Keuangan (OJK) melaporkan penyaluran kredit perbankan di tanah air tumbuh 12,67 persen year on year ...</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678057/ojk-kredit-perbankan-tumbuh-1267-persen-capai-rp90809-triliun</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.15.18_1.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Menkomdigi: KIP garda depan informasi jernih dan perangi hoaks</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:00:50 +0700</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid mengatakan Komisi Informasi Pusat (KIP) menjadi garda terdepan ...</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678033/menkomdigi-kip-garda-depan-informasi-jernih-dan-perangi-hoaks</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0321.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Satu tahun Sekolah Rakyat, ratusan siswa torehkan prestasi</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:59:25 +0700</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Menteri Sosial (Mensos) Saifullah Yusuf menyatakan selama satu tahun Sekolah Rakyat berdiri sudah ratusan ...</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678024/satu-tahun-sekolah-rakyat-ratusan-siswa-torehkan-prestasi</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176441.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Menkeu: Realisasi anggaran MBG Rp101,1 T untuk 63,13 juta penerima</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:53:14 +0700</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa mengungkapkan bahwa realisasi anggaran Program Makan Bergizi Gratis ...</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678005/menkeu-realisasi-anggaran-mbg-rp1011-t-untuk-6313-juta-penerima</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29-2.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Polri perkuat langkah preventif respons isu keamanan nasional</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:46:34 +0700</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Polri memastikan terus memperkuat langkah preventif untuk menjaga keamanan nasional sehingga aktivitas masyarakat dan ...</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677985/polri-perkuat-langkah-preventif-respons-isu-keamanan-nasional</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/1000086556.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Prabowo dan PM Thailand bertemu empat mata di Istana Merdeka</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 17:49:52 +0700</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto dan Perdana Menteri Thailand Anutin Charnvirakul menggelar pertemuan empat mata di Istana ...</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677828/prabowo-dan-pm-thailand-bertemu-empat-mata-di-istana-merdeka</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_5162.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Kepala BGN tingkatkan status keracunan MBG jadi kejadian fatal</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 17:10:19 +0700</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" t="inlineStr">
+        <is>
           <t>nya tidak dilanjutkan," ucap Sudaryono.
 Ia menegaskan BGN memberlakukan nol toleransi pada setiap status ...</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr">
+      <c r="F272" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677743/kepala-bgn-tingkatkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr">
+      <c r="G272" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/ZAM02548_edit_2028523819372755.jpg</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
+    <row r="273">
+      <c r="A273" t="inlineStr">
         <is>
           <t>top-news</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="B273" t="inlineStr">
         <is>
           <t>Harga minyak turun usai AS siap lanjutkan dialog dengan Iran</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
+      <c r="C273" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 17:08:35 +0700</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr">
+      <c r="D273" t="inlineStr"/>
+      <c r="E273" t="inlineStr">
         <is>
           <t>Harga minyak turun lebih dari 5 persen, Senin, setelah Presiden Amerika Serikat Donald Trump ...</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr">
+      <c r="F273" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677735/harga-minyak-turun-usai-as-siap-lanjutkan-dialog-dengan-iran</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr">
+      <c r="G273" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/05/06/ilustrasi-isi-bensin-di-pom.jpg</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
+    <row r="274">
+      <c r="A274" t="inlineStr">
         <is>
           <t>top-news</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
+      <c r="B274" t="inlineStr">
         <is>
           <t>Australia konfirmasi kematian massal pertama satwa akibat flu burung</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
+      <c r="C274" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 16:48:50 +0700</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr">
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="inlineStr">
         <is>
           <t>Australia mengonfirmasi kematian massal satwa liar pertama terkait flu burung H5 yang mematikan, dengan burung camar ...</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr">
+      <c r="F274" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677701/australia-konfirmasi-kematian-massal-pertama-satwa-akibat-flu-burung</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr">
+      <c r="G274" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/06/26/Virus-flu-burung-penyakit-unggas.jpg</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
+    <row r="275">
+      <c r="A275" t="inlineStr">
         <is>
           <t>top-news</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
+      <c r="B275" t="inlineStr">
         <is>
           <t>Siklon 94 W,  waspada cuaca ekstrem &amp; gelombang tinggi di wilayah RI</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
+      <c r="C275" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 16:30:38 +0700</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr">
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="inlineStr">
         <is>
           <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) mendeteksi pergerakan Bibit Siklon Tropis 94W di Laut Filipina ...</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr">
+      <c r="F275" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677641/siklon-94-w-waspada-cuaca-ekstrem-gelombang-tinggi-di-wilayah-ri</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr">
+      <c r="G275" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/05/27/1000395034.jpg</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
+    <row r="276">
+      <c r="A276" t="inlineStr">
         <is>
           <t>photo, top-news</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
+      <c r="B276" t="inlineStr">
         <is>
           <t>Petani berbagi air sumur demi selamatkan tanaman tembakau</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
+      <c r="C276" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 14:44:51 +0700</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr">
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr">
         <is>
           <t>Petani mengambil air dari sumur untuk menyiram tanaman tembakau di Lengkong, Nganjuk, Jawa Timur, Senin (3/8/2026). ...</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr">
+      <c r="F276" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/foto/5677428/petani-berbagi-air-sumur-demi-selamatkan-tanaman-tembakau</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr">
+      <c r="G276" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/petani-tembakau-berbagi-air-sumur-antisipasi-dampak-el-nino-030826-mm-1.jpg</t>
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
+    <row r="277">
+      <c r="A277" t="inlineStr">
         <is>
           <t>top-news</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
+      <c r="B277" t="inlineStr">
         <is>
           <t>Nusron sebut banyak laut di Batam telah dikapling tanpa prosedur sah</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
+      <c r="C277" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 14:44:05 +0700</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr">
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr">
         <is>
           <t>Menteri Agraria dan Tata Ruang (ATR)/Kepala Badan Pertanahan Nasional (BPN) Nusron Wahid mengatakan, menerima banyak ...</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
+      <c r="F277" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677425/nusron-sebut-banyak-laut-di-batam-telah-dikapling-tanpa-prosedur-sah</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr">
+      <c r="G277" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_142345.jpg</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
+    <row r="278">
+      <c r="A278" t="inlineStr">
         <is>
           <t>top-news</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
+      <c r="B278" t="inlineStr">
         <is>
           <t>Menkomdigi panggil YouTube imbas temuan konten promosi vape sasar anak</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
+      <c r="C278" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 14:22:09 +0700</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
-      <c r="E198" t="inlineStr">
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="inlineStr">
         <is>
           <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid merencanakan pemanggilan terhadap platform digital YouTube ...</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr">
+      <c r="F278" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677396/menkomdigi-panggil-youtube-imbas-temuan-konten-promosi-vape-sasar-anak</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr">
+      <c r="G278" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0225.jpg</t>
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
+    <row r="279">
+      <c r="A279" t="inlineStr">
         <is>
           <t>top-news</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="B279" t="inlineStr">
         <is>
           <t>Kemnaker: Magang Nasional diharapkan menekan angka pengangguran muda</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
+      <c r="C279" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 13:37:57 +0700</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
-      <c r="E199" t="inlineStr">
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr">
         <is>
           <t>Kementerian Ketenagakerjaan (Kemnaker) mengatakan program Magang Nasional (MagangHub) untuk mempersiapkan kompetensi ...</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr">
+      <c r="F279" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677364/kemnaker-magang-nasional-diharapkan-menekan-angka-pengangguran-muda</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr">
+      <c r="G279" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/ff63afaf-7778-47fe-833d-5a8068af9a51_1.jpeg</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
+    <row r="280">
+      <c r="A280" t="inlineStr">
         <is>
           <t>top-news</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
+      <c r="B280" t="inlineStr">
         <is>
           <t>Kemenag perkuat transformasi madrasah lewat revitalisasi-digitalisasi</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
+      <c r="C280" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 13:36:36 +0700</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr">
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="inlineStr">
         <is>
           <t>Menteri Agama (Menag) Nasaruddin Umar menegaskan transformasi madrasah terus diperkuat melalui revitalisasi ...</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr">
+      <c r="F280" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677363/kemenag-perkuat-transformasi-madrasah-lewat-revitalisasi-digitalisasi</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr">
+      <c r="G280" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/07/14/1000173935_1.jpg</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
+    <row r="281">
+      <c r="A281" t="inlineStr">
         <is>
           <t>top-news</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
+      <c r="B281" t="inlineStr">
         <is>
           <t>Lisensi IP Global Buka Peluang Bisnis Baru bagi Kreator Indonesia</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
+      <c r="C281" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 13:34:30 +0700</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr">
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr">
         <is>
           <t>Wakil Menteri Ekonomi Kreatif Irene Umar mengatakan kolaborasi antara pemilik kekayaan intelektual (Intellectual ...</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr">
+      <c r="F281" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677353/lisensi-ip-global-buka-peluang-bisnis-baru-bagi-kreator-indonesia</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr">
+      <c r="G281" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000589873.jpg</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
+    <row r="282">
+      <c r="A282" t="inlineStr">
         <is>
           <t>top-news</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
+      <c r="B282" t="inlineStr">
         <is>
           <t>Nilai ekspor perdagangan RI Januari-Juni capai 140,81 miliar dolar AS</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr">
+      <c r="C282" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 13:16:17 +0700</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr">
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr">
         <is>
           <t>Badan Pusat Statistik (BPS) mencatat nilai ekspor Indonesia secara kumulatif dari Januari-Juni 2026 mencapai 140,81 ...</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
+      <c r="F282" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677315/nilai-ekspor-perdagangan-ri-januari-juni-capai-14081-miliar-dolar-as</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
+      <c r="G282" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/neraca-perdagangan-januari-mei-2026-surplus-2815779.jpg</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
+    <row r="283">
+      <c r="A283" t="inlineStr">
         <is>
           <t>top-news</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
+      <c r="B283" t="inlineStr">
         <is>
           <t>Korban KMP Mutiara Sentosa II dievakuasi ke Pelabuhan Tanjung Perak</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
+      <c r="C283" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 13:06:15 +0700</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr">
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="inlineStr">
         <is>
           <t>Tim SAR gabungan terus melakukan evakuasi korban terbakarnya KMP Mutiara Sentosa 2 ke darat, tepatnya ke Pelabuhan ...</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr">
+      <c r="F283" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677297/korban-kmp-mutiara-sentosa-ii-dievakuasi-ke-pelabuhan-tanjung-perak</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr">
+      <c r="G283" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/260821_1.jpg</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
+    <row r="284">
+      <c r="A284" t="inlineStr">
         <is>
           <t>top-news</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
+      <c r="B284" t="inlineStr">
         <is>
           <t>Aktor senior Diding Boneng meninggal dunia</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr">
+      <c r="C284" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 11:39:03 +0700</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr">
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr">
         <is>
           <t>Aktor sekaligus komedian tanah air, Zainal Abidin alias Diding Boneng dikabarkan meninggal dunia pada Senin (3/8) dalam ...</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr">
+      <c r="F284" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677209/aktor-senior-diding-boneng-meninggal-dunia</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr">
+      <c r="G284" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/26f1eb88-3301-4ae1-badd-bed5078fe3dd.jpeg</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
+    <row r="285">
+      <c r="A285" t="inlineStr">
         <is>
           <t>top-news</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
+      <c r="B285" t="inlineStr">
         <is>
           <t>Seskab: Prabowo dorong sinergi pemerintah dan dunia usaha</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
+      <c r="C285" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 11:17:50 +0700</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
-      <c r="E205" t="inlineStr">
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr">
         <is>
           <t>Sekretaris Kabinet Teddy Indra Wijaya menyampaikan bahwa Presiden Prabowo Subianto menekankan pentingnya sinergi antara ...</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr">
+      <c r="F285" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677191/seskab-prabowo-dorong-sinergi-pemerintah-dan-dunia-usaha</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr">
+      <c r="G285" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0891_1.jpeg</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
+    <row r="286">
+      <c r="A286" t="inlineStr">
         <is>
           <t>top-news</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="B286" t="inlineStr">
         <is>
           <t>Red Velvet bersiap kembali lewat EP baru "Velvet Summer"</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr">
+      <c r="C286" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 10:24:37 +0700</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr">
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="inlineStr">
         <is>
           <t>Grup idola K-pop Red Velvet akan kembali lewat rilis mini album atau extended play (EP) baru bertajuk “Velvet ...</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr">
+      <c r="F286" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677151/red-velvet-bersiap-kembali-lewat-ep-baru-velvet-summer</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr">
+      <c r="G286" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/ca97a3a8-aa17-45fc-be71-d36051dd9dcd.jpeg</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
+    <row r="287">
+      <c r="A287" t="inlineStr">
         <is>
           <t>top-news</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B287" t="inlineStr">
         <is>
           <t>Menaker pastikan komitmen pemerintah perkuat kesejahteraan pekerja</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
+      <c r="C287" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 10:16:19 +0700</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr">
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="inlineStr">
         <is>
           <t>Menteri Ketenagakerjaan (Menaker) Yassierli memastikan pemerintah berkomitmen untuk memperkuat kesejahteraan, ...</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr">
+      <c r="F287" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677148/menaker-pastikan-komitmen-pemerintah-perkuat-kesejahteraan-pekerja</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr">
+      <c r="G287" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2025/09/20/pelepasan-peserta-pemagangan-ke-jepang-di-jawa-barat-2627513.jpg</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
+    <row r="288">
+      <c r="A288" t="inlineStr">
         <is>
           <t>top-news</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B288" t="inlineStr">
         <is>
           <t>23 calon hakim agung dan ad hoc ikuti seleksi wawancara akhir</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
+      <c r="C288" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 10:15:01 +0700</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr">
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" t="inlineStr">
         <is>
           <t>Sebanyak 23 orang calon hakim agung dan ad hoc Mahkamah Agung Tahun 2026 mengikuti seleksi wawancara tahap akhir di ...</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr">
+      <c r="F288" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677137/23-calon-hakim-agung-dan-ad-hoc-ikuti-seleksi-wawancara-akhir</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr">
+      <c r="G288" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000012883_1.jpg</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
+    <row r="289">
+      <c r="A289" t="inlineStr">
         <is>
           <t>top-news</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B289" t="inlineStr">
         <is>
           <t>BRIN perkuat kajian sungai bawah tanah di Kebumen untuk ketahanan air</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
+      <c r="C289" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 09:57:19 +0700</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr">
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr">
         <is>
           <t>Badan Riset dan Inovasi Nasional (BRIN) memperkuat riset ketahanan air melalui pengembangan teknologi dan penelitian ...</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
+      <c r="F289" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677120/brin-perkuat-kajian-sungai-bawah-tanah-di-kebumen-untuk-ketahanan-air</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr">
+      <c r="G289" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1785706440-47672950-1.jpg</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
+    <row r="290">
+      <c r="A290" t="inlineStr">
         <is>
           <t>top-news</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="B290" t="inlineStr">
         <is>
           <t>Harga bensin turun pada pekan pertama Agustus</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
+      <c r="C290" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 09:51:00 +0700</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr">
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="inlineStr">
         <is>
           <t>Harga bahan bakar minyak (BBM) jenis bensin di stasiun pengisian bahan bakar umum (SPBU) Pertamina, Shell, dan bp ...</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr">
+      <c r="F290" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677109/harga-bensin-turun-pada-pekan-pertama-agustus</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr">
+      <c r="G290" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2024/10/02/penuruanan-harga-bbm-011024-aaa-7.jpg</t>
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
+    <row r="291">
+      <c r="A291" t="inlineStr">
         <is>
           <t>top-news</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="B291" t="inlineStr">
         <is>
           <t>Sean Gelael berbagi pengalaman di dunia balap ke pengunjung GIIAS 2026</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
+      <c r="C291" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 09:34:53 +0700</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr">
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" t="inlineStr">
         <is>
           <t>Pembalap Indonesia Sean Gelael berbagi pengalamannya di dunia balap ke pengunjung GAIKINDO Indonesia International ...</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr">
+      <c r="F291" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677103/sean-gelael-berbagi-pengalaman-di-dunia-balap-ke-pengunjung-giias-2026</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
+      <c r="G291" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/16b70b87-326f-479a-a806-580ab846cc6f_1.jpeg</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>ekonomi-bursa, top-news</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>KSSK prakirakan pertumbuhan ekonomi RI pada 2026 capai 5,6-6 persen</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:28:16 +0700</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Komite Stabilitas Sistem Keuangan (KSSK) memprakirakan ekonomi Indonesia sepanjang 2026 tumbuh dalam kisaran ...</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677935/kssk-prakirakan-pertumbuhan-ekonomi-ri-pada-2026-capai-56-6-persen</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.19.55.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Rupiah menguat dipengaruhi PMI manufaktur Indonesia naik jadi 50,2</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:58:46 +0700</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah terhadap dolar AS pada penutupan perdagangan Senin, bergerak menguat 25 poin atau 0,14 persen ...</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677712/rupiah-menguat-dipengaruhi-pmi-manufaktur-indonesia-naik-jadi-502</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/12/nilai-tukar-rupiah-melemah-115-poin-2788415.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>KSSK: Sistem keuangan TW-II tetap terjaga di tengah konflik geopolitik</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:26:03 +0700</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Komite Stabilitas Sistem Keuangan (KSSK) menilai kondisi fiskal, moneter dan sektor keuangan selama triwulan II 2026 ...</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677625/kssk-sistem-keuangan-tw-ii-tetap-terjaga-di-tengah-konflik-geopolitik</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Menjaga pintu air perekonomian Indonesia</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:04:40 +0700</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Bayangkan perekonomian Indonesia sebagai sebuah bendungan raksasa yang mengairi hamparan persawahan. Air yang mengalir ...</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677565/menjaga-pintu-air-perekonomian-indonesia</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/06/peringati-hari-bank-indonesia-doku-perkuat-ekosistem-pembayaran-2817675.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Rupiah diperkirakan menguat seiring AS batalkan rencana serang Iran</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 10:12:26 +0700</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Analis Doo Financial Futures, Lukman Leong memperkirakan rupiah menguat seiring Amerika Serikat (AS) membatalkan ...</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677132/rupiah-diperkirakan-menguat-seiring-as-batalkan-rencana-serang-iran</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828847.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Rupiah pada Senin pagi melemah jadi Rp18.031 per dolar AS</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 09:05:50 +0700</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah pada Senin pagi bergerak melemah 9 poin atau 0,05 persen menjadi Rp18.031 per dolar AS dibandingkan ...</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677063/rupiah-pada-senin-pagi-melemah-jadi-rp18031-per-dolar-as</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Komisi XI: PFII peluang RI tangkap momentum perpindahan modal global</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 06:53:34 +0700</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Komisi XI DPR RI Mohamad Hekal mengatakan percepatan pembentukan Pusat Finansial Internasional Indonesia ...</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676995/komisi-xi-pfii-peluang-ri-tangkap-momentum-perpindahan-modal-global</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Saham-dan-oblogasi.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>BUMA International Group bukukan pertumbuhan EBITDA semester I/2026</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 06:17:40 +0700</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>PT BUMA Internasional Gorup membukukan pertumbuhan EBITDA pada semester pertama 2026 (1H26) di tengah penurunan ...</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5676967/buma-international-group-bukukan-pertumbuhan-ebitda-semester-i-2026</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/buma.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Asuransi Jasindo serahkan klaim ABMN Rp17,6 miliar atas aset Kemenag</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:10:05 +0700</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>PT Asuransi Jasa Indonesia (Persero) atau Asuransi Jasindo selaku Ketua Konsorsium Asuransi Barang Milik Negara (KABMN) ...</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678299/asuransi-jasindo-serahkan-klaim-abmn-rp176-miliar-atas-aset-kemenag</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176534.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Jumlah wisnas Kaltim naik didorong padatnya agenda kepariwisataan</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:05:06 +0700</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Jumlah wisatawan nusantara (wisnus) yang masuk ke Provinsi Kalimantan Timur (Kaltim) pada Juni 2026 mengalami kenaikan ...</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678291/jumlah-wisnas-kaltim-naik-didorong-padatnya-agenda-kepariwisataan</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000549241.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Banten masuk lima besar tujuan investasi nasional 2026</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:59:31 +0700</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi (Pemprov) Banten berhasil menempati posisi lima besar sebagai daerah tujuan penanaman modal atau ...</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678281/banten-masuk-lima-besar-tujuan-investasi-nasional-2026</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000868355.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>LPS merampungkan likuidasi tujuh BPR/BPRS di semester I-2026</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:55:57 +0700</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Lembaga Penjamin Simpanan (LPS) melaporkan telah menyelesaikan likuidasi sebanyak tujuh Bank Perekonomian Rakyat ...</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678269/lps-merampungkan-likuidasi-tujuh-bpr-bprs-di-semester-i-2026</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-20.41.53.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>BPS: Sulsel deflasi 0,18 persen dipengaruhi panen melimpah</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:52:16 +0700</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) Provinsi Sulawesi Selatan (Sulsel) mencatat tingkat perekonomian provinsi itu pada awal ...</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678264/bps-sulsel-deflasi-018-persen-dipengaruhi-panen-melimpah</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/ImgResizer_20251001_1702_01644-1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Waskita Karya garap 5 Sekolah Rakyat senilai Rp1,16 triliun di Jatim</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:44:01 +0700</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>PT Waskita Karya (Persero) Tbk (WSKT) sedang mengerjakan proyek pembangunan sebanyak lima Sekolah Rakyat di Provinsi ...</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678247/waskita-karya-garap-5-sekolah-rakyat-senilai-rp116-triliun-di-jatim</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/09/IMG_8606.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>ICPI soroti faktor multiplier effect dukung keberhasilan pariwisata</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:39:58 +0700</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Ketua Umum Ikatan Cendikiawan Pariwisata Indonesia (ICPI) Azril Azahari mengatakan keberhasilan pariwisata tidak cukup ...</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678239/icpi-soroti-faktor-multiplier-effect-dukung-keberhasilan-pariwisata</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/Festival-layang-layang-Internasional-di-Garut-010826-adb-4.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Menteri Bahlil siapkan skema pembiayaan untuk bioetanol</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:28:01 +0700</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyiapkan skema pembiayaan untuk program mandatori ...</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678217/menteri-bahlil-siapkan-skema-pembiayaan-untuk-bioetanol</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-16.12.46.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Komisaris Pertamina Patra Niaga apresiasi UMKM binaan tampil di IFW</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:18:57 +0700</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr"/>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Komisaris PT Pertamina Patra Niaga Tina Talisa mengapresiasi keikutsertaan UMKM binaan tampil dalam ajang Indonesia ...</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678200/komisaris-pertamina-patra-niaga-apresiasi-umkm-binaan-tampil-di-ifw</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000399671.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Kemenperin: PMI ekspansi bukti kepercayaan ke ketahanan industri</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:14:41 +0700</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Kementerian Perindustrian (Kemenperin) menyampaikan kembali masuknya Purchasing Managers's Index/PMI Manufaktur ...</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678196/kemenperin-pmi-ekspansi-bukti-kepercayaan-ke-ketahanan-industri</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IKI-Juli_2.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>BI Aceh dan SBA manfaatkan limbah uang kertas jadi bahan bakar semen</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:10:47 +0700</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Kantor Perwakilan Bank Indonesia (KPwBI) Aceh dan pabrik semen PT Solusi Bangun Andalas (SBA) menjalin kerja sama ...</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678181/bi-aceh-dan-sba-manfaatkan-limbah-uang-kertas-jadi-bahan-bakar-semen</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0021.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>BPS Jabar: Deflasi 0,05 persen Juli akibat MBG libur-panen melimpah</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:04:29 +0700</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) Jawa Barat mencatat deflasi sebesar 0,05 persen secara bulanan (month-to-month/mtm) pada ...</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678169/bps-jabar-deflasi-005-persen-juli-akibat-mbg-libur-panen-melimpah</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1002076290.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Guru Besar ITB: Manfaat gas Andaman datang dari industrialisasi Aceh</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:00:28 +0700</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Guru Besar Institut Teknologi Bandung (ITB) Prof Tutuka Ariadji menyatakan bahwa manfaat temuan gas di south Andaman ...</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678159/guru-besar-itb-manfaat-gas-andaman-datang-dari-industrialisasi-aceh</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0019_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>ekonomi-bursa</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>OJK: Pasar modal jaga peran sumber pembiayaan di tengah gejolak global</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:33:35 +0700</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Ketua Dewan Komisioner Otoritas Jasa Keuangan (OJK) Friderica Widyasari Dewi alias Kiki memastikan bahwa pasar modal ...</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677944/ojk-pasar-modal-jaga-peran-sumber-pembiayaan-di-tengah-gejolak-global</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.15.18.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>ekonomi-bursa</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>IHSG awal pekan berpotensi variatif seiring sentimen global-domestik</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 09:42:28 +0700</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin berpotensi bergerak variatif dipicu oleh ...</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677104/ihsg-awal-pekan-berpotensi-variatif-seiring-sentimen-global-domestik</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/12/12/ihsg-ditutup-menguat-2688871.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>ekonomi-bursa</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
         <is>
           <t>IHSG Senin dibuka menguat 36,49 poin ke posisi 6.272</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr">
+      <c r="C315" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 09:11:26 +0700</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr">
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
         <is>
           <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin pagi dibuka menguat 36,49 poin atau 0,59 ...</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr">
+      <c r="F315" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677071/ihsg-senin-dibuka-menguat-3649-poin-ke-posisi-6272</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr">
+      <c r="G315" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/pergerakan-indeks-harga-saham-gabungan-2828631.jpg</t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>top-news</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>PLN Jakarta pastikan pasokan listrik sudah berhasil dipulihkan</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 08:36:26 +0700</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>PT PLN (Persero) Unit Induk Distribusi Jakarta Raya mengungkapkan pasokan listrik telah berhasil ...</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677043/pln-jakarta-pastikan-pasokan-listrik-sudah-berhasil-dipulihkan</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20231217-WA0015-1.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>top-news</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Ledakan di kantor polisi Pakistan tewaskan 14 orang</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 07:44:23 +0700</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>Sebuah ledakan terjadi di luar sebuah kantor polisi di Kota Kabal, Pakistan, mengakibatkan 14 orang tewas dan 14 orang ...</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677020/ledakan-di-kantor-polisi-pakistan-tewaskan-14-orang</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/CmxztpE000019_20260803_PEPFN0A001.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>ekonomi-finansial</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>KSSK prakirakan pertumbuhan ekonomi RI pada 2026 capai 5,6-6 persen</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 18:28:16 +0700</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>Komite Stabilitas Sistem Keuangan (KSSK) memprakirakan ekonomi Indonesia sepanjang 2026 tumbuh dalam kisaran ...</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677935/kssk-prakirakan-pertumbuhan-ekonomi-ri-pada-2026-capai-56-6-persen</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.19.55.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>ekonomi-finansial</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Rupiah menguat dipengaruhi PMI manufaktur Indonesia naik jadi 50,2</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:58:46 +0700</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr"/>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>Nilai tukar rupiah terhadap dolar AS pada penutupan perdagangan Senin, bergerak menguat 25 poin atau 0,14 persen ...</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677712/rupiah-menguat-dipengaruhi-pmi-manufaktur-indonesia-naik-jadi-502</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/12/nilai-tukar-rupiah-melemah-115-poin-2788415.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>ekonomi-finansial</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>KSSK: Sistem keuangan TW-II tetap terjaga di tengah konflik geopolitik</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:26:03 +0700</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>Komite Stabilitas Sistem Keuangan (KSSK) menilai kondisi fiskal, moneter dan sektor keuangan selama triwulan II 2026 ...</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677625/kssk-sistem-keuangan-tw-ii-tetap-terjaga-di-tengah-konflik-geopolitik</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>ekonomi-finansial</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Menjaga pintu air perekonomian Indonesia</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:04:40 +0700</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>Bayangkan perekonomian Indonesia sebagai sebuah bendungan raksasa yang mengairi hamparan persawahan. Air yang mengalir ...</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677565/menjaga-pintu-air-perekonomian-indonesia</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/06/peringati-hari-bank-indonesia-doku-perkuat-ekosistem-pembayaran-2817675.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>ekonomi-finansial</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Rupiah diperkirakan menguat seiring AS batalkan rencana serang Iran</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 10:12:26 +0700</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>Analis Doo Financial Futures, Lukman Leong memperkirakan rupiah menguat seiring Amerika Serikat (AS) membatalkan ...</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677132/rupiah-diperkirakan-menguat-seiring-as-batalkan-rencana-serang-iran</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828847.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>ekonomi-finansial</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Rupiah pada Senin pagi melemah jadi Rp18.031 per dolar AS</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 09:05:50 +0700</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr"/>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>Nilai tukar rupiah pada Senin pagi bergerak melemah 9 poin atau 0,05 persen menjadi Rp18.031 per dolar AS dibandingkan ...</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677063/rupiah-pada-senin-pagi-melemah-jadi-rp18031-per-dolar-as</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>ekonomi-finansial</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Komisi XI: PFII peluang RI tangkap momentum perpindahan modal global</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 06:53:34 +0700</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr"/>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>Wakil Ketua Komisi XI DPR RI Mohamad Hekal mengatakan percepatan pembentukan Pusat Finansial Internasional Indonesia ...</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676995/komisi-xi-pfii-peluang-ri-tangkap-momentum-perpindahan-modal-global</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Saham-dan-oblogasi.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>ekonomi-finansial</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>BUMA International Group bukukan pertumbuhan EBITDA semester I/2026</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 06:17:40 +0700</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr"/>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>PT BUMA Internasional Gorup membukukan pertumbuhan EBITDA pada semester pertama 2026 (1H26) di tengah penurunan ...</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676967/buma-international-group-bukukan-pertumbuhan-ebitda-semester-i-2026</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/buma.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>ekonomi-bisnis</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Musim panen tekan harga hortikultura bikin deflasi 0,35 persen di NTB</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 18:38:20 +0700</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr"/>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>Badan Pusat Statistik (BPS) menyatakan musim panen menekan harga komoditas hortikultura dan memicu deflasi sebesar 0,35 ...</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677956/musim-panen-tekan-harga-hortikultura-bikin-deflasi-035-persen-di-ntb</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001432193.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>ekonomi-bisnis</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Wamenperin optimistis PMI manufaktur RI terus meningkat</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 18:36:38 +0700</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr"/>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>Wakil Menteri Perindustrian (Wamenperin) Faisol Riza optimistis kinerja manufaktur Indonesia terus mengalami ...</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677952/wamenperin-optimistis-pmi-manufaktur-ri-terus-meningkat</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Wamenperin.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>ekonomi-bisnis</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Menkop dorong pembentukan koperasi syariah perluas akses modal</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 18:34:52 +0700</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>Menteri Koperasi (Menkop) Ferry Juliantono mendorong pembentukan koperasi syariah di lingkungan Wanita Pengusaha ...</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677948/menkop-dorong-pembentukan-koperasi-syariah-perluas-akses-modal</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-16.50.13.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>ekonomi-bisnis</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Ekonom: Hilirisasi nikel perlu diimbangi penguatan ekspor pertanian</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 18:23:50 +0700</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>Ekonom Center of Reform on Economics (CORE) Indonesia Yusuf Rendy Manilet menilai keberhasilan hilirisasi nikel dalam ...</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677921/ekonom-hilirisasi-nikel-perlu-diimbangi-penguatan-ekspor-pertanian</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/11/16/IMG_20251116_190439.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>ekonomi-bisnis</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>CORE: Pertumbuhan ekspor ke AS sinyal positif daya saing produk RI</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 18:19:03 +0700</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>Ekonom Center of Reform on Economics (CORE) Indonesia Yusuf Rendy Manilet menilai pertumbuhan ekspor Indonesia ke ...</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677908/core-pertumbuhan-ekspor-ke-as-sinyal-positif-daya-saing-produk-ri</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/28/1001021030.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>ekonomi-bisnis</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>ATR/BPN tetapkan 15 Kantah jadi percontohan pelayanan peralihan hak</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 18:18:57 +0700</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>Kementerian Agraria dan Tata Ruang/Badan Pertanahan Nasional (ATR/BPN) menyatakan terdapat 15 Kantor Pertanahan ...</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677904/atr-bpn-tetapkan-15-kantah-jadi-percontohan-pelayanan-peralihan-hak</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_175241.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>ekonomi-bisnis</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Lebih maskulin, intip rupa hingga spek Suzuki Fronx SGX Hybrid Kuro</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 18:15:42 +0700</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>Suzuki menghadirkan penyegaran pada varian tertinggi SUV Fronx melalui Suzuki Fronx SGX Hybrid Kuro, tampil lebih ...</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>https://otomotif.antaranews.com/berita/5677893/lebih-maskulin-intip-rupa-hingga-spek-suzuki-fronx-sgx-hybrid-kuro</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_1872.JPG.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>ekonomi-bisnis</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>PMI manufaktur naik, Kadin: Didorong peningkatan produksi-permintaan</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 18:15:15 +0700</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr"/>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>Kamar Dagang dan Industri (Kadin) Indonesia menilai kenaikan Purchasing Managers’ Index (PMI) manufaktur ...</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677892/pmi-manufaktur-naik-kadin-didorong-peningkatan-produksi-permintaan</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/02/22/WhatsApp-Image-2026-02-22-at-8.24.35-AM_edit_336327027051281.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>ekonomi-bursa</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>OJK: Pasar modal jaga peran sumber pembiayaan di tengah gejolak global</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 18:33:35 +0700</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>Ketua Dewan Komisioner Otoritas Jasa Keuangan (OJK) Friderica Widyasari Dewi alias Kiki memastikan bahwa pasar modal ...</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677944/ojk-pasar-modal-jaga-peran-sumber-pembiayaan-di-tengah-gejolak-global</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.15.18.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>ekonomi-bursa</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>IHSG awal pekan berpotensi variatif seiring sentimen global-domestik</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 09:42:28 +0700</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr"/>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin berpotensi bergerak variatif dipicu oleh ...</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677104/ihsg-awal-pekan-berpotensi-variatif-seiring-sentimen-global-domestik</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/12/12/ihsg-ditutup-menguat-2688871.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
+    <row r="316">
+      <c r="A316" t="inlineStr">
         <is>
           <t>humaniora</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
+      <c r="B316" t="inlineStr">
         <is>
           <t>Bantuan beras 30 kg cair mulai 17 Agustus 2026, ini jadwal dan cara cek penerimanya</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
+      <c r="C316" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 13:27:14 +0700</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
-      <c r="E233" t="inlineStr">
+      <c r="D316" t="inlineStr"/>
+      <c r="E316" t="inlineStr">
         <is>
           <t>Pemerintah memastikan penyaluran bantuan pangan beras tahap II tahun 2026 akan dimulai pada 17 Agustus 2026. Bantuan ...</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr">
+      <c r="F316" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677341/bantuan-beras-30-kg-cair-mulai-17-agustus-2026-ini-jadwal-dan-cara-cek-penerimanya</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr">
+      <c r="G316" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/04/26/kemensos-percepat-penyaluran-bansos-pkh-dan-bpnt-2778877.jpg</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
+    <row r="317">
+      <c r="A317" t="inlineStr">
         <is>
           <t>lifestyle</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
+      <c r="B317" t="inlineStr">
         <is>
           <t>10 ide usaha menjelang 17 Agustus 2026 yang berpotensi laris dan menguntungkan</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
+      <c r="C317" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 18:16:58 +0700</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr">
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" t="inlineStr">
         <is>
           <t>Momentum peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 dapat menjadi peluang bagi pelaku ...</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr">
+      <c r="F317" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677896/10-ide-usaha-menjelang-17-agustus-2026-yang-berpotensi-laris-dan-menguntungkan</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr">
+      <c r="G317" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2024/08/02/sentra-penjualan-bendera-merah-putih-di-surabaya-020824-Ds-3.jpg</t>
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
+    <row r="318">
+      <c r="A318" t="inlineStr">
         <is>
           <t>lifestyle</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B318" t="inlineStr">
         <is>
           <t>10 ide lomba 17 Agustus untuk anak PAUD dan TK yang seru, edukatif, dan mudah digelar</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
+      <c r="C318" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 13:38:29 +0700</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr">
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" t="inlineStr">
         <is>
           <t>Perayaan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 dapat menjadi momen bagi anak usia PAUD dan TK ...</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr">
+      <c r="F318" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677368/10-ide-lomba-17-agustus-untuk-anak-paud-dan-tk-yang-seru-edukatif-dan-mudah-digelar</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr">
+      <c r="G318" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2024/08/03/WhatsApp-Image-2024-08-03-at-20.37.28.jpeg</t>
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
+    <row r="319">
+      <c r="A319" t="inlineStr">
         <is>
           <t>lifestyle</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
+      <c r="B319" t="inlineStr">
         <is>
           <t>Sering terbangun tengah malam? Kenali 7 penyebab dan cara mengatasinya</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
+      <c r="C319" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 13:35:20 +0700</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
-      <c r="E236" t="inlineStr">
+      <c r="D319" t="inlineStr"/>
+      <c r="E319" t="inlineStr">
         <is>
           <t>Bangun di tengah malam sesekali merupakan hal yang normal. Namun, jika kondisi ini terjadi hampir setiap malam dan ...</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr">
+      <c r="F319" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677357/sering-terbangun-tengah-malam-kenali-7-penyebab-dan-cara-mengatasinya</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr">
+      <c r="G319" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/07/20/Penumpang-rela-menginap-menunggu-kereta-pertama-di-Stasiun-Cikarang-150726-ryl-5.jpg</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
+    <row r="320">
+      <c r="A320" t="inlineStr">
         <is>
           <t>lifestyle</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
+      <c r="B320" t="inlineStr">
         <is>
           <t>Bahaya paparan pornografi pada anak: Dampak bagi otak, mental, dan perilaku</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
+      <c r="C320" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 13:23:03 +0700</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
-      <c r="E237" t="inlineStr">
+      <c r="D320" t="inlineStr"/>
+      <c r="E320" t="inlineStr">
         <is>
           <t>Perkembangan teknologi membuat anak-anak dan remaja semakin akrab dengan internet sejak usia dini. Di satu sisi, ...</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr">
+      <c r="F320" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677332/bahaya-paparan-pornografi-pada-anak-dampak-bagi-otak-mental-dan-perilaku</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr">
+      <c r="G320" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/06/02/ilustrasi-konten-berbau-pornografi.jpg</t>
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
+    <row r="321">
+      <c r="A321" t="inlineStr">
         <is>
           <t>lifestyle</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
+      <c r="B321" t="inlineStr">
         <is>
           <t>Sudah ngantuk tapi sulit tidur pulas? Ini penyebab dan cara atasinya</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr">
+      <c r="C321" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 11:28:54 +0700</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
-      <c r="E238" t="inlineStr">
+      <c r="D321" t="inlineStr"/>
+      <c r="E321" t="inlineStr">
         <is>
           <t>Rasa kantuk yang muncul di malam hari seharusnya menjadi pertanda bahwa tubuh siap beristirahat. Namun, tidak sedikit ...</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr">
+      <c r="F321" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677203/sudah-ngantuk-tapi-sulit-tidur-pulas-ini-penyebab-dan-cara-atasinya</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr">
+      <c r="G321" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/04/17/Nafas.jpeg</t>
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
+    <row r="322">
+      <c r="A322" t="inlineStr">
         <is>
           <t>lifestyle</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
+      <c r="B322" t="inlineStr">
         <is>
           <t>Cara cepat tidur dalam 5 menit, efektif untuk yang sulit pulas</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr">
+      <c r="C322" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 11:25:40 +0700</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
-      <c r="E239" t="inlineStr">
+      <c r="D322" t="inlineStr"/>
+      <c r="E322" t="inlineStr">
         <is>
           <t>Sulit tidur meski badan sudah terasa lelah merupakan masalah yang kerap dialami banyak orang. Kondisi ini sering ...</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr">
+      <c r="F322" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677199/cara-cepat-tidur-dalam-5-menit-efektif-untuk-yang-sulit-pulas</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr">
+      <c r="G322" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2025/11/04/tidua.jpg</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
+    <row r="323">
+      <c r="A323" t="inlineStr">
         <is>
           <t>tekno</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
+      <c r="B323" t="inlineStr">
         <is>
           <t>Cara mengganti password WiFi lewat HP dan laptop dengan mudah</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr">
+      <c r="C323" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 13:16:14 +0700</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
-      <c r="E240" t="inlineStr">
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" t="inlineStr">
         <is>
           <t>WiFi yang tiba-tiba terasa lambat padahal sinyal penuh dan kuota internet masih banyak tentu membuat kesal. Salah satu ...</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr">
+      <c r="F323" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677312/cara-mengganti-password-wifi-lewat-hp-dan-laptop-dengan-mudah</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr">
+      <c r="G323" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2020/08/19/antarafoto-warga-sediakan-internet-gratis-bagi-pelajar-190820-ief-2-1.jpg</t>
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
+    <row r="324">
+      <c r="A324" t="inlineStr">
         <is>
           <t>photo</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Polda Jatim identifikasi lima korban meninggal dalam kecelakaan KMP Mutiara Sentosa II</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:56:37 +0700</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Petugas merapikan posisi peti jenazah korban kecelakaan KMP Mutiara Sentosa II di Rumah Sakit Bhayangkara H.S. Samsoeri Mertojoso, Surabaya, Jawa Timur, Senin (3/8/2026). Tim Disaster Victim Identification (DVI) Polda Jawa Timur mengidentifikasi lima korban meninggal dunia kecelakaan KMP Mutiara Sentosa II di perairan utara Sumenep, Madura, dan menyatakan seluruh korban tidak meninggal akibat luka bakar.  ANTARA FOTO/Umarul Faruq/wsj.</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5678276/polda-jatim-identifikasi-lima-korban-meninggal-dalam-kecelakaan-kmp-mutiara-sentosa-ii</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/Identifikasi-lima-korban-KMP-Mutiara-Sentosa-II-03082026-Um-3.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>TNI AL gagalkan penyelundupan pasir timah di Kepri</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:01:39 +0700</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Dankodaeral IV Laksamana Muda TNI Berkat Widjanarko (kanan) dan Kepala Seksi Tindak Pidana Umum Pada Kejaksaan Negeri Lingga, Denny (kiri) memeriksa barang bukti saat keterangan pers terkait pengagalan penyelundupan pasir timah di Mako Lanal Dabo Singkep, Dabo Singkep, Kabupaten Lingga, Kepulauan Riau, Senin (3/8/2026). Prajurit TNI AL Mako Lanal Dabo Singkep di bawah jajaran Kodaeral IV berhasil mengagalkan upaya penyelundupan pasir timah ilegal ke Malaysia dengan modus operandi keramba apung di perairan Pekajang Besar, Kabupaten Lingga dengan barang bukti 1,6 ton timah, satu pucuk senapan, satu pucuk air soft gun serta mengamankan satu orang tersangka penyelundupan. ANTARA FOTO/Muhammad Adimaja/wsj.</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5678039/tni-al-gagalkan-penyelundupan-pasir-timah-di-kepri</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/Pengagalan-Penyelundupan-Pasir-Timah-Ilegal-030826-Adm-7.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
         <is>
           <t>Presiden Prabowo terima kunjungan PM Thailand Anutin Charnvirakul</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr">
+      <c r="C326" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 17:42:48 +0700</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
-      <c r="E241" t="inlineStr">
+      <c r="D326" t="inlineStr"/>
+      <c r="E326" t="inlineStr">
         <is>
           <t>Presiden Prabowo Subianto (kiri) bersama Perdana Menteri Thailand Anutin Charnvirakul (kedua kiri) bersiap melakukan penghormatan pada bendera saat upacara penyambutan kenegaraan di Istana Merdeka, Jakarta, Senin (3/8/2026). Kunjungan tersebut diantaranya untuk memperkuat kerja sama bilateral serta meluncurkan Peta Jalan Kemitraan Strategis Indonesia-Thailand 2026–2030 yang terfokus pada tiga bidang utama yaitu keamanan, pembangunan ekonomi dan sosial-budaya. ANTARA FOTO/Hafidz Mubarak A/sgd/agr</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr">
+      <c r="F326" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/foto/5677811/presiden-prabowo-terima-kunjungan-pm-thailand-anutin-charnvirakul</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr">
+      <c r="G326" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/Presiden-Prabowo-Terima-Kunjungan-PM-Thailand-030226-hma-5.jpg</t>
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
+    <row r="327">
+      <c r="A327" t="inlineStr">
         <is>
           <t>photo</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
+      <c r="B327" t="inlineStr">
         <is>
           <t>Pameran foto jurnalistik Prahara Pulau Emas di Museum Tsunami Aceh</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr">
+      <c r="C327" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 16:52:45 +0700</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
-      <c r="E242" t="inlineStr">
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" t="inlineStr">
         <is>
           <t>Pengunjung melihat karya pameran foto jurnalistik Prahara Pulau Emas di Museum Tsunami Aceh, Banda Aceh, Aceh, Senin (3/8/2026). Pameran foto yang menampilkan 65 karya dari anggota PFI tersebut merekam dampak bencana hidrometeorologi di Provinsi Aceh, Sumatera Utara dan Sumatera Barat pada akhir November 2025. ANTARA FOTO/Akramul Muslim/agr</t>
         </is>
       </c>
-      <c r="F242" t="inlineStr">
+      <c r="F327" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/foto/5677709/pameran-foto-jurnalistik-prahara-pulau-emas-di-museum-tsunami-aceh</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr">
+      <c r="G327" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/Pameran-Foto-Prahara-Pulau-Emas-Di-Aceh-030826-Akm-7.jpg</t>
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
+    <row r="328">
+      <c r="A328" t="inlineStr">
         <is>
           <t>photo</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
+      <c r="B328" t="inlineStr">
         <is>
           <t>Jelang HUT RI, Polda Kepri bagikan bendera ke warga di pulau-pulau terluar</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr">
+      <c r="C328" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 15:51:09 +0700</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
-      <c r="E243" t="inlineStr">
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr">
         <is>
           <t>Warga memasang Bendera Merah Putih di perahu serta pekarangan rumah panggung yang dibagikan Polda Kepri di Pulau Dapur Arang, Batam, Kepulauan Riau, Senin (3/8/2026). Polda Kepri membagikan Bendera Merah Putih kepada warga yang tinggal di pulau-pulau terluar Batam yang berbatasan langsung dengan Singapura guna menyemarakkan peringatan HUT Ke-81 Kemerdekaan Republik Indonesia sekaligus menanamkan rasa nasionalisme di wilayah perbatasan. ANTARA FOTO/Teguh Prihatna/agr</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr">
+      <c r="F328" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/foto/5677539/jelang-hut-ri-polda-kepri-bagikan-bendera-ke-warga-di-pulau-pulau-terluar</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr">
+      <c r="G328" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/Pembagian-Bendera-Merah-Putih-Di-Pulau-Pulau-Terluar-030826-tpp-2.jpg</t>
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
+    <row r="329">
+      <c r="A329" t="inlineStr">
         <is>
           <t>photo</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
+      <c r="B329" t="inlineStr">
         <is>
           <t>Pemerintah bangun 1.416 Jembatan Garuda untuk hubungkan desa terpencil</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr">
+      <c r="C329" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 12:53:00 +0700</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
-      <c r="E244" t="inlineStr">
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="inlineStr">
         <is>
           <t>Foto udara pengendara sepeda motor melintasi Jembatan Gantung Garuda yang menghubungkan Desa Kertarahayu dan Desa Jayasampurna di Kabupaten Bekasi, Jawa Barat, Senin (3/8/2026). Hingga akhir Juli 2026, pemerintah telah membangun 1.416 unit Jembatan Garuda di daerah terpencil yang menghubungkan 7.371 desa dan kelurahan untuk mempermudah akses masyarakat serta mempersingkat waktu tempuh. ANTARA FOTO/Darryl Ramadhan/tom.</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr">
+      <c r="F329" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/foto/5677284/pemerintah-bangun-1416-jembatan-garuda-untuk-hubungkan-desa-terpencil</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr">
+      <c r="G329" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/Pembangunan-Jembatan-Garuda-percepat-akses-desa-030826-ryl-1.jpg</t>
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
+    <row r="330">
+      <c r="A330" t="inlineStr">
         <is>
           <t>photo</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
+      <c r="B330" t="inlineStr">
         <is>
           <t>Petugas evakuasi dua jenazah korban kebakaran KM Mutiara Sentosa II</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
+      <c r="C330" t="inlineStr">
         <is>
           <t>Mon, 03 Aug 2026 09:03:11 +0700</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
-      <c r="E245" t="inlineStr">
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr">
         <is>
           <t>Sejumlah petugas mengangkat kantong berisi jenazah korban kebakaran KM Mutiara Sentosa II setelah tiba di Dermaga Jamrud Utara, Pelabuhan Tanjung Perak, Surabaya, Jawa Timur, Senin (3/8/2026). Kapal kargo Meratus Pematang Siantar mengevakuasi 111 penumpang selamat dan dua jenazah korban kebakaran KM Mutiara Sentosa II di perairan utara Madura pada Minggu (2/8). ANTARA FOTO/Didik Suhartono/tom.</t>
         </is>
       </c>
-      <c r="F245" t="inlineStr">
+      <c r="F330" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/foto/5677056/petugas-evakuasi-dua-jenazah-korban-kebakaran-km-mutiara-sentosa-ii</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr">
+      <c r="G330" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/korban-kebakaran-km-mutiara-sentosa-2-030826-Ds-4.jpg</t>
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
+    <row r="331">
+      <c r="A331" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Banjir kepung 15 titik di Kota Padang akibat cuaca ekstrem</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>ANTARA - Hujan lebat disertai angin kencang memicu bencana di Kabupaten Agam, Kota Pariaman, dan Kota Padang, Sumatera Barat, Senin (3/8). Kota Padang menjadi wilayah terdampak paling parah dengan banjir di 15 titik. BPBD Sumatera Barat bersama lintas instansi melakukan penanganan darurat dan evakuasi warga. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678396/banjir-kepung-15-titik-di-kota-padang-akibat-cuaca-ekstrem</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BANJIR-KEPUNG-15-TITIK-DI-KOTA-PADANG-AKIBAT-CUACA-EKSTREM.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Cadangan devisa RI jadi 145 M dolar AS, BI sebut masih di level aman</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>ANTARA - Bank Indonesia (BI) mengungkapkan cadangan devisa pada akhir Juli 2026 berada di posisi 145 miliar dolar AS. Meski menurun dari sebelumnya yang berjumlah 156 dolar AS, BI pun menyatakan posisi tersebut masih di level aman. (Setyanka Harviana Putri/Pradanna Putra Tampi/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678347/cadangan-devisa-ri-jadi-145-m-dolar-as-bi-sebut-masih-di-level-aman</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_CADANGAN-DEVISA-RI-JADI-145-M-DOLAR-AS-BI-SEBUT-MASIH-DI-LEVEL-AMAN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Erick ungkap strategi sebelum kembali ke bursa calon Ketum PSSI 2027</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>ANTARA - Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir tidak menutup kemungkinan untuk kembali mencalonkan diri sebagai Ketua Umum PSSI pada pemilihan Ketua Umum PSSI yang berlangsung pada 2027 mendatang. Hal ini disampaikan Erick, usai acara Kongres Biasa PSSI 2026, yang berlangsung di Jakarta, pada Senin (3/8). (Irfan Hardiansah/Chairul Fajri/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678327/erick-ungkap-strategi-sebelum-kembali-ke-bursa-calon-ketum-pssi-2027</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/ERICK-UNGKAP-STRATEGI-SEBELUM-KEMBALI-KE-BURSA-CALON-KETUM-PSSI-2027.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Industri kreatif tunjukkan tren positif, musik dan film mendominasi</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa pertumbuhan ekosistem industri kreatif menunjukkan tren positif. Menurutnya, pangsa pasar film Indonesia mencapai sekitar 67 persen, dan 80 persen masyarakat Indonesia lebih banyak mendengarkan musik karya musisi Tanah Air.
+(Cahya Sari/Ibnu Zaki/Andi Bagasela/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678325/industri-kreatif-tunjukkan-tren-positif-musik-dan-film-mendominasi</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDUSTRI-KREATIF-TUNJUKKAN-TREN-POSITIF-MUSIK-DAN-FILM-MENDOMINASI.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Pemprov NTB benahi tarif hingga infrastruktur Mandalika jelang MotoGP</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Provinsi Nusa Tenggara Barat benahi sejumlah aspek yang menjadi sorotan pada ajang MotoGP seri Indonesia di Sirkuit Mandalika pada 9 - 11 Oktober mendatang. Mulai dari persoalan tarif akomodasi hingga transportasi, serta perbaikan infrastruktur yang akan menunjang kenyamanan wisatawan penonton, dengan target 140 ribu orang. (Kusnandar/Chairul Fajri/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678319/pemprov-ntb-benahi-tarif-hingga-infrastruktur-mandalika-jelang-motogp</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PEMPROV-NTB-BENAHI-TARIF-HINGGA-INFRASTRUKTUR-MANDALIKA-JELANG-MOTOGP.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Purbaya: Stabilitas sistem keuangan Indonesia tetap terjaga</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>ANTARA - Komite Stabilitas Sistem Keuangan (KSSK) memastikan stabilitas sistem keuangan Indonesia tetap terjaga pada triwulan II 2026 meski dihadapkan pada meningkatnya risiko global akibat eskalasi konflik geopolitik dan gejolak pasar keuangan internasional.
+(Setyanka Harviana Putri/Pradanna Putra Tampi/Chairul Fajri/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678257/purbaya-stabilitas-sistem-keuangan-indonesia-tetap-terjaga</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PURBAYA-STABILITAS-SISTEM-KEUANGAN-INDONESIA-TETAP-TERJAGA.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan hingga ke tingkat desa maupun kelurahan. Indonesia memiliki 2.723 warisan budaya tak benda yang tercatat secara nasional, 16 di antaranya telah diakui oleh UNESCO. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Winanto)</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Polda Banten apel siaga waspada bencana dan karhutla di musim kemarau</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>ANTARA - Polda Banten bersama sejumlah instansi terkait, Senin (3/8), menggelar apel gabungan dalam rangka kesiapsiagaan tanggap darurat bencana dan kebakaran hutan dan lahan (karhutla) di Lapangan Apel Polda Banten, Serang. Apel ini menjadi langkah memperkuat sinergi lintas instansi dalam mengantisipasi potensi bencana dan karhutla selama masa kemarau. (Susmiatun Hayati/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678213/polda-banten-apel-siaga-waspada-bencana-dan-karhutla-di-musim-kemarau</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_POLDA-BANTEN-APEL-SIAGA-WASPADA-BENCANA-DAN-KARHUTLA-DI-MUSIM-KEMARAU.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>OJK catat penyaluran kredit perbankan capai Rp9.080,9 triliun</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>ANTARA - Otoritas Jasa Keuangan (OJK) mengungkapkan pertumbuhan kredit perbankan pada Juni 2026 tumbuh hingga 12,67% year-on-year (yoy). Di Jakarta, Senin (3/8), OJK pun memaparkan faktor yang mendukung pertumbuhan tersebut. (Setyanka Harviana Putri/Pradanna Putra Tampi/Arif Prada/Winanto)</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678208/ojk-catat-penyaluran-kredit-perbankan-capai-rp90809-triliun</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_15_15_01.Still474.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Lawan stunting dan isu iklim lewat program Cadiak Pandai</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>ANTARA - Pertamina Patra Niaga bersama Perkumpulan Keluarga Berencana Indonesia (PKBI) Sumatera Barat meluncurkan program "Cadiak Pandai Goes to School" di Kabupaten Padang Pariaman, Senin (3/8). Program ini membekali pelajar dengan edukasi gizi, kesehatan reproduksi, dan kepedulian lingkungan sebagai upaya mendukung percepatan penurunan stunting. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678187/lawan-stunting-dan-isu-iklim-lewat-program-cadiak-pandai</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_LAWAN-STUNTING-DAN-ISU-IKLIM-LEWAT-PROGRAM-CADIAK-PANDAI.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Ketum PSSI utarakan pesan Presiden agar timnas tampil di Piala Dunia</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>ANTARA - Presiden Prabowo Subianto menyampaikan, Tim Nasional (Timnas) Indonesia sangat dekat untuk bisa tampil di Pialaa Dunia 2026, jika tidak gugur pada babak kualifikasi putaran keempat di Arab Saudi, pada Oktober tahun lalu. Hal ini disampaikan Prabowo dalam pidatonya, pada pembukaan Kongres Biasa PSSI 2026, di Jakarta, pada Senin (3/8), yang dibacakan Ketua Umum PSSI sekaligus Menteri Pemuda dan Olahraga (Menpora) Erick Thohir. (Irfan Hardiansah/Soni Namura/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678179/ketum-pssi-utarakan-pesan-presiden-agar-timnas-tampil-di-piala-dunia</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/KETUM-PSSI-UTARAKAN-PESAN-PRESIDEN-AGAR-TIMNAS-TAMPIL-DI-PIALA-DUNIA.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>PMI dan Pemkot Semarang salurkan air bersih ke Jabungan</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>ANTARA - Palang Merah Indonesia (PMI) Kota Semarang bersama Pemerintah Kota Semarang menyalurkan bantuan air bersih bagi warga Kelurahan Jabungan, Kecamatan Banyumanik, Senin (3/8). Bantuan diberikan untuk memenuhi kebutuhan warga yang terdampak krisis air bersih akibat musim kemarau. (Fx. Suryo Wicaksono/Chairul Fajri/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678175/pmi-dan-pemkot-semarang-salurkan-air-bersih-ke-jabungan</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PMI-DAN-PEMKOT-SEMARANG-SALURKAN-AIR-BERSIH-KE-JABUNGAN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Pendaki Nirmal Purja dan tim tewas di longsoran salju di Broad Peak</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>ANTARA - Pendaki gunung, Nirmal Purja, meninggal saat mendaki salah satu gunung tertinggi ke-12 di dunia Broad Peak di Pakistan utara, Kamis (30/7). Dilansir dari AFP, tim penyelamat menemukan jenazah Nirmal Purja, pada Minggu (2/8), setelah longsoran salju menewaskannya bersama sembilan anggota timnya. (Ludmila Yusufin Diah Nastiti/Chairul Fajri/Winanto)</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678112/pendaki-nirmal-purja-dan-tim-tewas-di-longsoran-salju-di-broad-peak</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PENDAKI-NIRMAL-PURJA-DAN-TIM-TEWAS-DI-LONGSORAN-SALJU-DI-BROAD-PEAK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Menbud buka pembinaan Gita Bahana Nusantara 2026</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>ANTARA - Sebanyak 183 peserta Gita Bahana Nusantara (GBN) mulai menjalani pembinaan intensif dalam rangka menyemarakkan HUT ke-81 RI di Istana Merdeka, Jakarta. Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa GBN bukan sekadar kemampuan vokal dan musik, melainkan wujud persatuan Indonesia yang beragam. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678104/menbud-buka-pembinaan-gita-bahana-nusantara-2026</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENBUD-BUKA-PEMBINAAN-GITA-BAHANA-NUSANTARA-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Capai 78 persen, Sensus Ekonomi NTB 2026 dominan pada sektor pertanian</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Pusat Statistik (BPS) mencatat progres pendataan Sensus Ekonomi (SE) tahun 2026 di Provinsi Nusa Tenggara Barat mencapai 78 persen. Dengan capaian tertinggi diperoleh dari Kabupaten Dompu pada progres 92 persen, dan terendah dari Kota Mataram dengan progres 67 persen. (Kusnandar/Chairul Fajri/Winanto)</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678087/capai-78-persen-sensus-ekonomi-ntb-2026-dominan-pada-sektor-pertanian</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/CAPAI-78-PERSEN-SENSUS-EKONOMI-NTB-2026-DOMINAN-PADA-SEKTOR-PERTANIAN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Kodaeral IV gagalkan penyelundupan timah 1.6 ton senilai Rp1,3 miliar</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr"/>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>ANTARA - Komando Daerah Angkatan Laut (Kodaeral) IV menggagalkan upaya penyelundupan pasir timah sebanyak 42 karung seberat 1,6 ton, yang akan diselundupkan ke Malaysia dari wilayah Pekajang, Kabupaten Lingga, Kepulauan Riau. Dari penindakan itu nilai ekonomis yang berhasil diamankan ditaksir mencapai Rp 1,3 M, dan satu orang diamankan bersama barang bukti berupa satu senapan angin predator air gun, satu pistol airsoft gun jenis magnum jericho 941, dua ponsel serta satu buah KTP. (Angiela Chantiequ/Arif Prada/Winanto)</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678084/kodaeral-iv-gagalkan-penyelundupan-timah-16-ton-senilai-rp13-miliar</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_16_51_23.Still474.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>BPIP: Pelatihan Paskibraka bentuk calon pemimpin berkarakter Pancasila</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr"/>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Pembinaan Ideologi Pancasila (BPIP) menyatakan pemusatan pelatihan Pasukan Pengibar Bendera Pusaka (Paskibraka) nasional tidak hanya menjadi persiapan pengibaran bendera pada HUT ke-81 Kemerdekaan RI, tetapi juga bagian dari pembentukan calon pemimpin bangsa yang berkarakter Pancasila. Sebanyak 76 peserta dari 38 provinsi saat ini menjalani pelatihan di Depok, Jawa Barat. (Cahya Sari/Ibnu Zaki/Soni Namura/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678076/bpip-pelatihan-paskibraka-bentuk-calon-pemimpin-berkarakter-pancasila</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/BPIP-PELATIHAN-PASKIBRAKA-BENTUK-CALON-PEMIMPIN-BERKARAKTER-PANCASILA_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>BPS Bali catat peningkatan hunian hotel berbintang selama Juni 2026</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Bali mencatat tingkat penghunian kamar (TPK) hotel berbintang meningkat hingga 3,71 persen dibanding periode bulan Mei 2026. Sementara untuk meningkatkan kunjungan wisatawan mancanegara, Dinas Pariwisata Provinsi Bali mempromosikan wisata kesehatan atau wellness tourism. 
+(Rita Laura/Andi Bagasela/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678064/bps-bali-catat-peningkatan-hunian-hotel-berbintang-selama-juni-2026</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BPS-BALI-CATAT-PENINGKATAN-HUNIAN-HOTEL-BERBINTANG-SELAMA-JUNI-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
         <is>
           <t>Program Taruna Bakti Kepolisian latih siswa Sekolah Rakyat Lhokseumawe</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr"/>
-      <c r="E246" t="inlineStr">
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr"/>
+      <c r="E349" t="inlineStr">
         <is>
           <t>ANTARA - Ratusan siswa dari Sekolah Rakyat Lhokseumawe, Aceh, memperoleh edukasi kemandirian oleh Taruna Akademi Kepolisian untuk mengubah prilaku, Senin (3/8). Kegiatan ini merupakan salah satu dari program Taruna Bakti, yang diinstruksikan langsung oleh Presiden RI Prabowo Subianto ke seluruh Sekolah Rakyat di Indonesia. (Try Vanny S/Andi Bagasela/Winanto)</t>
         </is>
       </c>
-      <c r="F246" t="inlineStr">
+      <c r="F349" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678013/program-taruna-bakti-kepolisian-latih-siswa-sekolah-rakyat-lhokseumawe</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr">
+      <c r="G349" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PROGRAM-TARUNA-BAKTI-KEPOLISIAN-LATIH-SISWA-SEKOLAH-RAKYAT-LHOKSEUMAWE.jpg</t>
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
+    <row r="350">
+      <c r="A350" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
+      <c r="B350" t="inlineStr">
         <is>
           <t>Menkomdigi minta masyarakat waspadai lonjakan hoaks jelang HUT RI</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
-      <c r="E247" t="inlineStr">
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr"/>
+      <c r="E350" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengingatkan masyarakat untuk mewaspadai meningkatnya penyebaran hoaks menjelang peringatan Hari Ulang Tahun (HUT) ke-81 Republik Indonesia. Saat ditemui di Jakarta pada Senin (3/8), Menkomdigi  juga menegaskan tidak pernah melarang media melakukan peliputan, selama sesuai kaidah jurnalistik dan Undang-Undang Pers.(Sanya Dinda Susanti/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F247" t="inlineStr">
+      <c r="F350" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677959/menkomdigi-minta-masyarakat-waspadai-lonjakan-hoaks-jelang-hut-ri</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr">
+      <c r="G350" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-MINTA-MASYARAKAT-WASPADAI-LONJAKAN-HOAKS-JELANG-HUT-RI.jpg</t>
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
+    <row r="351">
+      <c r="A351" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
+      <c r="B351" t="inlineStr">
         <is>
           <t>Inflasi di Sumut sebesar 4,20 persen, emas menjadi penyumbang utama</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr"/>
-      <c r="E248" t="inlineStr">
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Sumatera Utara mencatat pada Juli 2026 Sumatera Utara mengalami inflasi 4,20 persen. Komoditas penyumbang inflasi pada bulan Juli 2026 yakni, emas perhiasan, cabai merah, cabai rawit, tomat dan bensin. (M. Valery Maulidzar S/Andi Bagasela/Winanto)</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr">
+      <c r="F351" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677867/inflasi-di-sumut-sebesar-420-persenemas-menjadi-penyumbang-utama</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr">
+      <c r="G351" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INFLASI-DI-SUMUT-SEBESAR-4-20-PERSEN-EMAS-MENJADI-PENYUMBANG-UTAMA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
+    <row r="352">
+      <c r="A352" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
+      <c r="B352" t="inlineStr">
         <is>
           <t>Komdigi tegur YouTube soal pelibatan anak dalam promosi rokok elektrik</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr"/>
-      <c r="E249" t="inlineStr">
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengatakan telah melayangkan surat teguran pertama kepada YouTube yang memuat konten siaran langsung atau live streaming seorang pemengaruh yang menampilkan promosi produk rokok elektrik atau vape dengan melibatkan anak-anak. Menteri Komdigi Meutya Hafid, di Jakarta, Senin (3/8), mengatakan dalam tiga hari ke depan Komdigi juga akan memanggil pihak YouTube untuk meminta keterangan. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr">
+      <c r="F352" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677812/komdigi-tegur-youtube-soal-pelibatan-anak-dalam-promosi-rokok-elektrik</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr">
+      <c r="G352" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_KOMDIGI-TEGUR-YOUTUBE-SOAL-PELIBATAN-ANAK-DALAM-PROMOSI-ROKOK-ELEKTRIK.jpg</t>
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
+    <row r="353">
+      <c r="A353" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
+      <c r="B353" t="inlineStr">
         <is>
           <t>Pemkab Temanggung gandeng kemitraan kacang panjang dengan perusahaan</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr">
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Penanaman Modal dan Pelayanan Terpadu Satu Pintu (DPMPTSP) Kabupaten Temanggung, Jawa Tengah, menjajaki peluang kemitraan budidaya kacang panjang dengan pihak perusahaan. Langkah ini dilakukan sebagai upaya memperluas akses pasar, sekaligus meningkatkan kesejahteraan petani melalui kepastian harga dan penyerapan hasil panen. (Firman Eko Handy/Andi Bagasela/Winanto)</t>
         </is>
       </c>
-      <c r="F250" t="inlineStr">
+      <c r="F353" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677779/pemkab-temanggung-gandeng-kemitraan-kacang-panjang-dengan-perusahaan</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr">
+      <c r="G353" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PEMKAB-TEMANGGUNG-GANDENG-KEMITRAAN-KACANG-PANJANG-DENGAN-PERUSAHAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
+    <row r="354">
+      <c r="A354" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
+      <c r="B354" t="inlineStr">
         <is>
           <t>Dinkes Lhokseumawe uji kualitas air Sekolah Rakyat</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr"/>
-      <c r="E251" t="inlineStr">
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Kesehatan (Dinkes) Kota Lhokseumawe melakukan uji kualitas air baku dan air minum di Sekolah Rakyat, Desa Jeulikat, Kecamatan Blang Mangat, Senin (3/8). Pemeriksaan dilakukan untuk memastikan air yang digunakan ratusan siswa memenuhi standar kesehatan sebelum dikonsumsi. (Try Vanny S/Andi Bagasela/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr">
+      <c r="F354" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677740/dinkes-lhokseumawe-uji-kualitas-air-sekolah-rakyat</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr">
+      <c r="G354" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_DINKES-LHOKSEUMAWE-UJI-KUALITAS-AIR-SEKOLAH-RAKYAT.jpg</t>
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
+    <row r="355">
+      <c r="A355" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
+      <c r="B355" t="inlineStr">
         <is>
           <t>HPAI Jember tanam pohon untuk mitigasi longsor dan banjir</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr">
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
+      <c r="E355" t="inlineStr">
         <is>
           <t>ANTARA - Himpunan Pegiat Adiwiyata Indonesia (HPAI) Kabupaten Jember menanam belasan bibit pohon beringin dan 20 bibit pohon karet kebo di kawasan Air Terjun Tancak, lereng selatan Pegunungan Hyang Argopuro, Kecamatan Panti, Senin (3/8). Penanaman dilakukan untuk mendukung konservasi kawasan, menjaga sumber air, serta mengurangi risiko longsor dan banjir bandang. (Hamka Agung Balya/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F252" t="inlineStr">
+      <c r="F355" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677707/hpai-jember-tanam-pohon-untuk-mitigasi-longsor-dan-banjir</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr">
+      <c r="G355" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/HPAI-JEMBER-TANAM-POHON-UNTUK-MITIGASI-LONGSOR-DAN-BANJIR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
+    <row r="356">
+      <c r="A356" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
+      <c r="B356" t="inlineStr">
         <is>
           <t>75 gerai Koperasi Merah Putih di Sulawesi Tenggara telah beroperasi</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr"/>
-      <c r="E253" t="inlineStr">
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
+      <c r="E356" t="inlineStr">
         <is>
           <t>ANTARA - Sebanyak 75 gerai Koperasi Desa Kelurahan Merah Putih (KDKMP) di Provinsi Sulawesi Tenggara telah mulai beroperasi pada Juli 2026. Kantor Wilayah Direktorat Jenderal Perbendaharaan Provinsi Sulawesi Tenggara (Kanwil DJPb Sultra) menyebut sepanjang 2026, KDKMP di Sultra mencatatkan 1.055 transaksi dengan nilai Rp25,22 juta dengan transaksi didominasi komoditas kebutuhan pokok dan energi bersubsidi, antara lain beras medium SPHP, MinyaKita, gula, dan elpiji 3 kilogram. (Saharudin/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F253" t="inlineStr">
+      <c r="F356" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677680/75-gerai-koperasi-merah-putih-di-sulawesi-tenggara-telah-beroperasi</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr">
+      <c r="G356" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_75-GERAI-KOPERASI-MERAH-PUTIH-DI-SULAWESI-TENGGARA-TELAH-BEROPERASI.jpg</t>
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
+    <row r="357">
+      <c r="A357" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
+      <c r="B357" t="inlineStr">
         <is>
           <t>Pimpinan MPR RI bertemu Presiden sampaikan undangan Sidang Tahunan</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr"/>
-      <c r="E254" t="inlineStr">
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
+      <c r="E357" t="inlineStr">
         <is>
           <t>ANTARA - Jajaran pimpinan MPR RI menyambangi Istana Kepresidenan Jakarta pada Senin (3/8). Ketua MPR RI Ahmad Muzani menyebut kunjungan itu salah satunya untuk menyampaikan undangan Sidang Tahunan MPR RI pada 14 Agustus 2026. (Aria Cindyara/Irfansyah Naufal Nasution/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr">
+      <c r="F357" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677637/pimpinan-mpr-ri-bertemu-presiden-sampaikan-undangan-sidang-tahunan</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr">
+      <c r="G357" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PIMPINAN-MPR-RI-BERTEMU-PRESIDEN-SAMPAIKAN-UNDANGAN-SIDANG-TAHUNAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
+    <row r="358">
+      <c r="A358" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
+      <c r="B358" t="inlineStr">
         <is>
           <t>Menkomdigi kukuhkan komisioner KI Pusat, perkuat keterbukaan informasi</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
-      <c r="E255" t="inlineStr">
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr"/>
+      <c r="E358" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengambil sumpah jabatan dan mengukuhkan tujuh anggota Komisi Informasi Pusat (KIP) Periode 2026–2030 di Kantor Kementerian Komdigi Jakarta, Senin (3/8).  Komisioner KI Pusat Periode 2026–2030 akan melanjutkan tugas dan fungsi komisioner sebelumnya, yakni penyelesaian sengketa informasi publik secara adil, menetapkan kebijakan teknis di bidang keterbukaan informasi, dan memperkuat implementasi UU Nomor 14 Tahun 2008 tentang Keterbukaan Informasi Publik. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr">
+      <c r="F358" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677604/menkomdigi-kukuhkan-komisioner-ki-pusat-perkuat-keterbukaan-informasi</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr">
+      <c r="G358" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-KUKUHKAN-KOMISIONER-KI-PUSAT-PERKUAT-KETERBUKAAN-INFORMASI.jpg</t>
         </is>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
+    <row r="359">
+      <c r="A359" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
+      <c r="B359" t="inlineStr">
         <is>
           <t>Partai Buruh Brasil calonkan Lula da Silva untuk masa jabatan keempat</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr"/>
-      <c r="E256" t="inlineStr">
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="inlineStr">
         <is>
           <t>ANTARA - Partai Buruh di Brasil pada Minggu (2/8) waktu setempat, resmi mencalonkan petahana Luiz Inacio Lula da Silva sebagai kandidat dalam pemilihan presiden mendatang untuk masa jabatan keempat. Pada konvensi nasional partai di Sao Paulo, para delegasi secara resmi menyetujui pasangan Lula dengan Wakil Presiden petahana Geraldo Alckmin dari Partai Sosialis Brasil.
 (XINHUA /Winanto/Rizky Bagus Dhermawan/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr">
+      <c r="F359" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677541/partai-buruh-brasil-calonkan-lula-da-silva-untuk-masa-jabatan-keempat</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr">
+      <c r="G359" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-154005.jpg</t>
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
+    <row r="360">
+      <c r="A360" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B360" t="inlineStr">
         <is>
           <t>Kesbangpol Pontianak antisipasi konflik sosial akibat karhutla</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr"/>
-      <c r="E257" t="inlineStr">
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr"/>
+      <c r="E360" t="inlineStr">
         <is>
           <t>ANTARA - Badan Kesatuan Bangsa dan Politik (Kesbangpol) Kota Pontianak mengidentifikasi potensi gangguan keamanan dan konflik sosial akibat kebakaran hutan dan lahan (karhutla), Senin (3/8). Langkah yang dilakukan meliputi koordinasi lintas sektor, pemantauan situasi, hingga mediasi untuk menjaga kondusivitas selama penanganan karhutla. (Indra Budi Santoso/Rizky Bagus Dhermawan/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr">
+      <c r="F360" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677519/kesbangpol-pontianak-antisipasi-konflik-sosial-akibat-karhutla</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr">
+      <c r="G360" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KESBANGPOL-PONTIANAK-ANTISIPASI-KONFLIK-SOSIAL-AKIBAT-KARHUTLA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
+    <row r="361">
+      <c r="A361" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
+      <c r="B361" t="inlineStr">
         <is>
           <t>PSEL Serang Raya jadi solusi pengelolaan sampah tiga daerah</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr">
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr"/>
+      <c r="E361" t="inlineStr">
         <is>
           <t>ANTARA - Fasilitas Pengolahan Sampah menjadi Energi Listrik (PSEL) Serang Raya akan dibangun di TPSA Cilowong, Kota Serang, untuk melayani pengelolaan sampah Kabupaten Serang, Kota Serang, dan Kota Cilegon. Fasilitas berkapasitas 1.161 ton sampah per hari itu diharapkan mampu mengurangi beban tempat pemrosesan akhir sekaligus mengubah sampah menjadi energi listrik. (Susmiatun Hayati/Agha Yuninda Maulana/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F258" t="inlineStr">
+      <c r="F361" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677492/psel-serang-raya-jadi-solusi-pengelolaan-sampah-tiga-daerah</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr">
+      <c r="G361" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PSEL-SERANG-RAYA-JADI-SOLUSI-PENGELOLAAN-SAMPAH.jpg</t>
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
+    <row r="362">
+      <c r="A362" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
+      <c r="B362" t="inlineStr">
         <is>
           <t>Pemkot Ambon salurkan air bersih gratis jika kekeringan terjadi</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr"/>
-      <c r="E259" t="inlineStr">
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr"/>
+      <c r="E362" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah Kota Ambon, Maluku, menyiapkan langkah antisipasi untuk menjamin ketersediaan air bersih bagi masyarakat dalam menghadapi potensi musim kemarau panjang akibat fenomena El Nino. Wali kota Ambon Bodewin Wattimena, Senin (3/8), mengatakan, pemerintah melakukan pemetaan wilayah yang rawan lalu mendistribusikan air bersih ke wilayah terdampak kekeringan. (Alfian Sanusi/Rizky Bagus Dhermawan/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F259" t="inlineStr">
+      <c r="F362" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677489/pemkot-ambon-salurkan-air-bersih-gratis-jika-kekeringan-terjadi</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr">
+      <c r="G362" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-151844.jpg</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
+    <row r="363">
+      <c r="A363" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
+      <c r="B363" t="inlineStr">
         <is>
           <t>Razia balap liar, Polres Temanggung sita 106 motor</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr"/>
-      <c r="E260" t="inlineStr">
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr"/>
+      <c r="E363" t="inlineStr">
         <is>
           <t>ANTARA - Kepolisian Resor (Polres) Temanggung, Jawa Tengah menyita 106 sepeda motor dalam razia balap liar yang digelar Minggu malam (2/8). Kegiatan razia tersebut digelar sebagai bagian  upaya kepolisian dalam menekan aksi balap liar  di Temanggung.(Firman Eko Handy/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F260" t="inlineStr">
+      <c r="F363" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677488/razia-balap-liar-polres-temanggung-sita-106-motor</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr">
+      <c r="G363" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_RAZIA-BALAP-LIAR-POLRES-TEMANGGUNG-SITA-106-MOTOR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
+    <row r="364">
+      <c r="A364" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
+      <c r="B364" t="inlineStr">
         <is>
           <t>Ditjenpas Kaltim gelar CKG bagi 12 ribu warga binaan</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr"/>
-      <c r="E261" t="inlineStr">
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr"/>
+      <c r="E364" t="inlineStr">
         <is>
           <t>ANTARA - Program Cek Kesehatan Gratis (CKG) menyasar warga binaan di Lembaga Pemasyarakatan (Lapas) dan Rumah Tahanan (Rutan) di Kalimantan Timur. CKG untuk 12 ribu warga binaan bertujuan mengantisipasi penyebaran risiko penyakit menular di lapas. (Hanifan Ma'ruf/Agha Yuninda Maulana/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr">
+      <c r="F364" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677480/ditjenpas-kaltim-gelar-ckg-bagi-12-ribu-warga-binaan</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr">
+      <c r="G364" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_DITJENPAS-KALTIM-GELAR-CKG.jpg</t>
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
+    <row r="365">
+      <c r="A365" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B365" t="inlineStr">
         <is>
           <t>Paus Leo XIV prihatin atas situasi krisis migran di Ceuta</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr"/>
-      <c r="E262" t="inlineStr">
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr"/>
+      <c r="E365" t="inlineStr">
         <is>
           <t>ANTARA - Paus Leo XIV  menyampaikan keprihatinan atas situasi krisis migran di Enklave, Spanyol, Ceuta.  Saat memimpin doa angelus di Vatikan, Minggu (2/8), Paus berdoa agar terdapat solusi yang membawa perdamaian dan keadilan atas kondisi tersebut. (ANADOLU/Ludmila Yusufin Diah Nastiti/Agha Yuninda Maulana/Winanto)</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr">
+      <c r="F365" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677384/paus-leo-xiv-prihatin-atas-situasi-krisis-migran-di-ceuta</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr">
+      <c r="G365" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PAUS-LEO-XIV-PRIHATIN-ATAS-SITUASI-KRISIS.jpg</t>
         </is>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
+    <row r="366">
+      <c r="A366" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
+      <c r="B366" t="inlineStr">
         <is>
           <t>Resmi dibuka, Sekolah Rakyat Terintegrasi 2 Kendari tampung 339 siswa</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr"/>
-      <c r="E263" t="inlineStr">
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr"/>
+      <c r="E366" t="inlineStr">
         <is>
           <t>ANTARA - Sekolah Rakyat Terintegrasi 2 Kota Kendari resmi dibuka pada Senin (3/8), yang ditandai dengan Masa Pengenalan Lingkungan Sekolah (MPLS). Sekolah tersebut menampung total sebanyak 339 siswa untuk tahun ajaran 2026/2027, yang terdiri dari jenjang SD, SMP dan SMA.
 (Saharudin/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr">
+      <c r="F366" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677373/resmi-dibuka-sekolah-rakyat-terintegrasi-2-kendari-tampung-339-siswa</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr">
+      <c r="G366" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/RESMI-DIBUKA-SEKOLAH-RAKYAT-TERINTEGRASI-2-KENDARI-TAMPUNG-339-SISWA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
+    <row r="367">
+      <c r="A367" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
+      <c r="B367" t="inlineStr">
         <is>
           <t>Dinkop UKM Cilegon targetkan 21 gerai baru KKMP beroperasi September</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr"/>
-      <c r="E264" t="inlineStr">
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr"/>
+      <c r="E367" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Koperasi Usaha Kecil dan Menengah (Dinkop UKM) Kota Cilegon menargetkan pembangunan  21 gedung gerai Koperasi Kelurahan Merah Putih (KKMP) di wilayah setempat dapat selesai dan beroperasi pada bulan September mendatang. Kepala Dinkop UKM Kota Cilegon, Suhendi pada Senin (3/8) mengatakan saat ini tercatat baru sebanyak 10 gedung yang telah selesai dibangun.
 (Susmiatun Hayati/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr">
+      <c r="F367" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677301/dinkop-ukm-cilegon-targetkan-21-gerai-baru-kkmp-beroperasi-september</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr">
+      <c r="G367" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/DINKOP-UKM-CILEGON-TARGETKAN-21-GERAI-BARU-KKMP-BEROPERASI-SEPTEMBER.jpg</t>
         </is>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
+    <row r="368">
+      <c r="A368" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr">
+      <c r="B368" t="inlineStr">
         <is>
           <t>Menhub sebut segera evaluasi operator KMP Mutiara Sentosa 2</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr"/>
-      <c r="E265" t="inlineStr">
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr"/>
+      <c r="E368" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah akan segera mengevaluasi kinerja PT Atosim Lampung Pelayaran yang merupakan operator KMP Mutiara Sentosa II. Hal tersebut disampaikan Menteri Perhubungan Dudy Purwagandhi saat meninjau para korban kebakaran KMP Mutiara Sentosa II di Surabaya, Jawa Timur, Senin (3/8). (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr">
+      <c r="F368" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677187/menhub-sebut-segera-evaluasi-operator-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr">
+      <c r="G368" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/MENHUB-SEBUT-SEGERA-EVALUASI-OPERATOR-KMP-MUTIARA-SENTOSA-2.jpg</t>
         </is>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
+    <row r="369">
+      <c r="A369" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr">
+      <c r="B369" t="inlineStr">
         <is>
           <t>Keluarga dengan dua balita selamat dari maut KMP Mutiara Sentosa 2</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr"/>
-      <c r="E266" t="inlineStr">
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr"/>
+      <c r="E369" t="inlineStr">
         <is>
           <t>ANTARA - Pasangan suami istri muda, Karhap dan Krisnawati bersama dua anak balitanya sempat terpisah saat terjun ke laut menyelamatkan diri dari kapal penumpang KMP Mutiara Sentosa 2 yang terbakar di perairan sebelah utara Pulau Madura pada Minggu (2/8). Keluarga kecil asal Sidenreng Rappang, Sulawesi Selatan tersebut kembali berkumpul pada Senin (3/8) setelah dievakuasi oleh kapal kargo Meratus Pematang Siantar yang kebetulan melintas di lokasi musibah terjadi. (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F266" t="inlineStr">
+      <c r="F369" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677141/keluarga-dengan-dua-balita-selamat-dari-maut-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr">
+      <c r="G369" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KELUARGA-DENGAN-DUA-BALITA-SELAMAT-DARI-MAUT-KMP-MUTIARA-SENTOSA-2.jpg</t>
         </is>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
+    <row r="370">
+      <c r="A370" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
+      <c r="B370" t="inlineStr">
         <is>
           <t>Lebih dari 100 korban KMP Mutiara Sentosa 2 tiba di Tanjung Perak</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr"/>
-      <c r="E267" t="inlineStr">
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr">
         <is>
           <t>ANTARA - Tim pencarian dan pertolongan (SAR) gabungan hingga Senin (3/8), telah mengevakuasi 234 penumpang KMP Mutiara Sentosa 2 yang sebelumnya terbakar di perairan sebelah utara Pulau Madura pada Minggu (2/8). Sebanyak 113 korban di antaranya, kini telah tiba di Pelabuhan Tanjung Perak Surabaya setelah diangkut menggunakan kapal kargo Meratus Pematang Siantar.  (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F267" t="inlineStr">
+      <c r="F370" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677085/lebih-dari-100-korban-kmp-mutiara-sentosa-2-tiba-di-tanjung-perak</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr">
+      <c r="G370" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/LEBIH-DARI-100-KORBAN-KMP-MUTIARA-SENTOSA-2-TIBA-DI-TANJUNG-PERAK.jpg</t>
         </is>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
+    <row r="371">
+      <c r="A371" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
+      <c r="B371" t="inlineStr">
         <is>
           <t>SAR evakuasi penumpang KM Mutiara Santosa 2 yang terbakar</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr"/>
-      <c r="E268" t="inlineStr">
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr"/>
+      <c r="E371" t="inlineStr">
         <is>
           <t>ANTARA - Tim pencarian dan pertolongan (SAR) gabungan telah mengevakuasi sebanyak 236 penumpang KM Mutiara Santosa 2 yang terbakar di perairan sebelah utara Pulau Madura, Minggu malam (2/8). Lima korban di antaranya meninggal dunia.(Hanif Nasrullah/Denno Ramdha Asmara/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F268" t="inlineStr">
+      <c r="F371" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676992/sar-evakuasi-penumpang-km-mutiara-santosa-2-yang-terbakar</t>
         </is>
       </c>
-      <c r="G268" t="inlineStr">
+      <c r="G371" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SAR-EVAKUASI-PENUMPANG-KM-MUTIARA-SANTOSA-2-YANG-TERBAKAR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
+    <row r="372">
+      <c r="A372" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
+      <c r="B372" t="inlineStr">
         <is>
           <t>John Herdman tunggu hasil pemeriksaan Marselino jelang jamu Vietnam</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
-      <c r="E269" t="inlineStr">
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr"/>
+      <c r="E372" t="inlineStr">
         <is>
           <t>ANTARA - Pelatih Timnas Indonesia John Herdman di Jakarta, Minggu,(2/8), mengatakan kondisi kesehatan dan status gelandang Marselino Ferdinan dalam turnamen baru akan ditentukan setelah mendapat laporan lengkap dari tim medis. Hal itu disampaikan Herdman, usai Marselino kembali absen dalam latihan jelang laga Grup A Piala AFF 2026 melawan Timnas Vietnam pada Senin (2/8). (Anggah/Sandy Arizona/Gracia Simanjuntak)</t>
         </is>
       </c>
-      <c r="F269" t="inlineStr">
+      <c r="F372" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676945/john-herdman-tunggu-hasil-pemeriksaan-marselino-jelang-jamu-vietnam</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr">
+      <c r="G372" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_JOHN-HERDMAN-TUNGGU-HASIL-PEMERIKSAAN-MARSELINO-JELANG-JAMU-VIETNAM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
+    <row r="373">
+      <c r="A373" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
+      <c r="B373" t="inlineStr">
         <is>
           <t>John Herdman sebut laga RI Vs Vietnam ujian sangat berat</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr"/>
-      <c r="E270" t="inlineStr">
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr"/>
+      <c r="E373" t="inlineStr">
         <is>
           <t>ANTARA - Pelatih Timnas Indonesia John Herdman di Jakarta, Minggu(2/8), mengaku pertandingan melawan Timnas Vietnam akan menjadi ujian sangat berat bagi skuad Garuda di Grup A Piala AFF 2026 (ASEAN Championship 2026). Menurut Herdman. laga tersebut juga merupakan peluang untuk mengambil alih kendali grup dan memastikan langkah ke babak berikutnya. (Anggah/Sandy Arizona/Gracia Simanjuntak)</t>
         </is>
       </c>
-      <c r="F270" t="inlineStr">
+      <c r="F373" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676944/john-herdman-sebut-laga-ri-vs-vietnam-ujian-sangat-berat</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr">
+      <c r="G373" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_JOHN-HERDMAN-SEBUT-LAGA-RI-VS-VIETNAM-UJIAN-SANGAT-BERAT.jpg</t>
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
+    <row r="374">
+      <c r="A374" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr">
+      <c r="B374" t="inlineStr">
         <is>
           <t>BI targetkan bawa wastra Sulsel ke pasar global</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr"/>
-      <c r="E271" t="inlineStr">
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr"/>
+      <c r="E374" t="inlineStr">
         <is>
           <t>ANTARA - Kantor Perwakilan Bank Indonesia Provinsi Sulawesi Selatan bersama Pemerintah Provinsi Sulsel menyasar penguatan pasar produk kain tradisional (wastra) di tingkat nasional hingga mancanegara melalui "Wastra Heritage Market 2026". Hal itu dikemukakan Kepala Kantor Perwakilan BI Sulsel Rizki Ernadi Wimanda di Makassar, Minggu (2/8). (Suriani Mappong/Sandy Arizona/Gracia Simanjuntak)</t>
         </is>
       </c>
-      <c r="F271" t="inlineStr">
+      <c r="F374" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676935/bi-targetkan-bawa-wastra-sulsel-ke-pasar-global</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr">
+      <c r="G374" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_BI-TARGETKAN-BAWA-WASTRA-SULSEL-KE-PASAR-GLOBAL.jpg</t>
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
+    <row r="375">
+      <c r="A375" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
+      <c r="B375" t="inlineStr">
         <is>
           <t>Tong Tong Night Market masuk KEN, angkat UMKM dan budaya lokal</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr"/>
-      <c r="E272" t="inlineStr">
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr"/>
+      <c r="E375" t="inlineStr">
         <is>
           <t>ANTARA - ‎Memasuki satu dekade penyelenggaraan, Tong Tong Night Market kembali meramaikan Kota Malang. Festival budaya dan kuliner yang masuk dalam Karisma Event Nusantara (KEN) itu tak hanya menghadirkan nuansa tempo dulu, tetapi juga menjadi ajang promosi puluhan UMKM sekaligus upaya melestarikan budaya lokal. (Achmad Saif Hajarani/Sandy Arizona/Gracia Simanjuntak)</t>
         </is>
       </c>
-      <c r="F272" t="inlineStr">
+      <c r="F375" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676927/tong-tong-night-market-masuk-ken-angkat-umkm-dan-budaya-lokal</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr">
+      <c r="G375" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_TONG-TONG-NIGHT-MARKET-MASUK-KEN-ANGKAT-UMKM-DAN-BUDAYA-LOKAL_1.jpg</t>
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
+    <row r="376">
+      <c r="A376" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
+      <c r="B376" t="inlineStr">
         <is>
           <t>Perputaran ekonomi Piala Presiden 2026 tembus Rp70 miliar</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr"/>
-      <c r="E273" t="inlineStr">
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr"/>
+      <c r="E376" t="inlineStr">
         <is>
           <t>ANTARA - Ketua Steering Committee Piala Presiden 2026 Maruarar Sirait menyebut perputaran ekonomi selama babak penyisihan turnamen di Surabaya dan Bandung telah mencapai lebih dari Rp70 miliar. Dampak ekonomi tersebut turut dirasakan pelaku usaha mikro, kecil, dan menengah (UMKM) serta dimanfaatkan untuk menyubsidi harga tiket pertandingan.
 (Hanif Nasrullah/Sandy Arizona/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F273" t="inlineStr">
+      <c r="F376" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676895/perputaran-ekonomi-piala-presiden-2026-tembus-rp70-miliar</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr">
+      <c r="G376" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_PERPUTARAN-EKONOMI-PIALA-PRESIDEN-2026-TEMBUS-RP70-MILIAR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
+    <row r="377">
+      <c r="A377" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
+      <c r="B377" t="inlineStr">
         <is>
           <t>Bahlil prioritaskan legalisasi 25 ribu sumur minyak rakyat di Sumsel</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
-      <c r="E274" t="inlineStr">
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
+      <c r="E377" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyebut Sumatera Selatan menjadi salah satu daerah prioritas penerapan kebijakan legalisasi sumur minyak rakyat. Menurutnya, sekitar 25 ribu dari 45 ribu sumur minyak rakyat di Indonesia berada di provinsi tersebut sehingga pemerintah memfokuskan implementasi Peraturan Menteri ESDM Nomor 18 Tahun 2025 di wilayah itu.
 (Winda Tri Agustina/Sandy Arizona/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F274" t="inlineStr">
+      <c r="F377" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676868/bahlil-prioritaskan-legalisasi-25-ribu-sumur-minyak-rakyat-di-sumsel</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr">
+      <c r="G377" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_BAHLIL-PRIORITASKAN-LEGALISASI-25-RIBU-SUMUR-MINYAK-RAKYAT-DI-SUMSEL.jpg</t>
         </is>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
+    <row r="378">
+      <c r="A378" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
+      <c r="B378" t="inlineStr">
         <is>
           <t>Golkar optimistis tingkatkan perolehan kursi di Sumsel</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr"/>
-      <c r="E275" t="inlineStr">
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr"/>
+      <c r="E378" t="inlineStr">
         <is>
           <t>ANTARA - Ketua Umum Partai Golkar Bahlil Lahadalia meminta seluruh jajaran partai memperkuat konsolidasi organisasi hingga tingkat desa sebagai strategi meningkatkan perolehan kursi legislatif pada Pemilu 2029, termasuk di Sumatera Selatan.
 (Winda Tri Agustina/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F275" t="inlineStr">
+      <c r="F378" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676837/golkar-optimistis-tingkatkan-perolehan-kursi-di-sumsel</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr">
+      <c r="G378" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/GOLKAR-OPTIMISTIS-TINGKATKAN-PEROLEHAN-KURSI-DI-SUMSEL.jpg</t>
         </is>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
+    <row r="379">
+      <c r="A379" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
+      <c r="B379" t="inlineStr">
         <is>
           <t>Presiden AS Trump tunda serangan baru ke Iran</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr"/>
-      <c r="E276" t="inlineStr">
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr"/>
+      <c r="E379" t="inlineStr">
         <is>
           <t>ANTARA - Presiden Amerika Serikat Donald Trump menunda rencana serangan baru terhadap Iran setelah mengklaim terdapat peluang kesepakatan. Namun, Trump menegaskan opsi militer tetap terbuka jika negosiasi gagal.
 (XINHUA/Arsy Fitriady/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F276" t="inlineStr">
+      <c r="F379" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676776/presiden-as-trump-tunda-serangan-baru-ke-iran</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr">
+      <c r="G379" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-AS-TRUMP-TUNDA-SERANGAN-BARU-KE-IRAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
+    <row r="380">
+      <c r="A380" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
+      <c r="B380" t="inlineStr">
         <is>
           <t>TNI AU gelar pameran enam pesawat F-16 di Batam</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr"/>
-      <c r="E277" t="inlineStr">
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr"/>
+      <c r="E380" t="inlineStr">
         <is>
           <t>ANTARA - TNI Angkatan Udara menggelar pameran enam pesawat tempur F-16 yang dapat dikunjungi masyarakat secara gratis dalam kegiatan Batam Open Base di Bandara Internasional Hang Nadim, Batam. Kegiatan ini menjadi bagian dari peringatan Hari Ulang Tahun ke-81 Kemerdekaan Republik Indonesia sekaligus upaya mendekatkan TNI AU kepada masyarakat.
 (Angiela Chantiequ/Jessica Allifia Jaya Hidayat/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F277" t="inlineStr">
+      <c r="F380" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5676735/tni-au-gelar-pameran-enam-pesawat-f-16-di-batam</t>
         </is>
       </c>
-      <c r="G277" t="inlineStr">
+      <c r="G380" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/TNI-AU-GELAR-PAMERAN-ENAM-PESAWAT-F-16-DI-BATAM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>TNI kerahkan delapan helikopter salurkan bantuan ke Puncak</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>ANTARA - Komando Gabungan Wilayah Pertahanan (Kogabwilhan) III mengerahkan delapan helikopter TNI Angkatan Darat dan TNI Angkatan Udara untuk menyalurkan bantuan kemanusiaan ke tiga distrik di Kabupaten Puncak, Papua Tengah, yang terdampak kekeringan berkepanjangan hingga memicu krisis pangan. (Laksa Mahendra/Satrio Giri Marwanto/Arsy Fitriady)</t>
-        </is>
-      </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676720/tni-kerahkan-delapan-helikopter-salurkan-bantuan-ke-puncak</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/TNI-KERAHKAN-DELAPAN-HELIKOPTER-SALURKAN-BANTUAN-KE-PUNCAK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>Jakarta Watersport Festival dorong sport tourism di Danau Sunter</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>ANTARA - Jakarta Watersport Festival 2026 digelar di Danau Sunter, Jakarta Utara, pada 1–2 Agustus. Festival ini menghadirkan kompetisi olahraga air, hiburan, dan bazar UMKM sebagai upaya mendorong sport tourism serta aktivitas ekonomi kreatif di ibu kota. (Nabila Athifa/Setyanka Harviana Putri/Satrio Giri Marwanto/Arsy Fitriady)</t>
-        </is>
-      </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676713/jakarta-watersport-festival-dorong-sport-tourism-di-danau-sunter</t>
-        </is>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/JAKARTA-WATERSPORT-FESTIVAL-DORONG-SPORT-TOURISM-DI-DANAU-SUNTER.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>Ledakan restoran di Moskow tewaskan tiga orang</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>ANTARA - Tiga orang tewas dan sedikitnya 21 lainnya luka-luka setelah ledakan alat peledak rakitan terjadi di sebuah restoran di kawasan Kudrinskaya Square, pusat Kota Moskow, Rusia, Sabtu (1/8). Menurut Komite Antiterorisme Nasional Rusia, ledakan terjadi ketika seorang perempuan berupaya membawa alat peledak ke dalam restoran, namun dihentikan petugas keamanan. Penyelidikan terkait motif serangan masih berlangsung. (Arsy Fitriady/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
-        </is>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676660/ledakan-restoran-di-moskow-tewaskan-tiga-orang</t>
-        </is>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/LEDAKAN-RESTORAN-DI-MOSKOW-TEWASKAN-TIGA-ORANG_1.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>DKPPP Temanggung edukasi warga cegah zoonosis dari hewan piaraan</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>ANTARA - Dinas Ketahanan Pangan, Pertanian, dan Perikanan (DKPPP) Kabupaten Temanggung bersama komunitas pecinta hewan mengedukasi masyarakat tentang pentingnya menjaga kesehatan hewan piaraan untuk mencegah zoonosis atau penyakit yang dapat menular dari hewan ke manusia. Edukasi meliputi pemberian nutrisi, vaksinasi, kebersihan, dan pemeriksaan kesehatan hewan secara berkala. (Firman Eko Handy/Satrio Giri Marwanto/Arsy Fitriady)</t>
-        </is>
-      </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676647/dkppp-temanggung-edukasi-warga-cegah-zoonosis-dari-hewan-piaraan</t>
-        </is>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/DKPPP-TEMANGGUNG-EDUKASI-WARGA-CEGAH-ZOONOSIS-DARI-HEWAN-PIARAAN.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>BP Batam siapkan Sekolah Terintegrasi Merah Putih di Rempang</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>ANTARA - Badan Pengusahaan (BP) Batam menyiapkan pembangunan Sekolah Terintegrasi Merah Putih di Rempang, Kepulauan Riau, sebagai sekolah gratis bagi siswa berprestasi. Sekolah yang dibangun di atas lahan seluas 18 hektare itu akan melayani jenjang sekolah dasar hingga sekolah menengah atas dengan fasilitas pendidikan dan olahraga yang lengkap. (Angiela Chantiequ/Satrio Giri Marwanto/Arsy Fitriady)</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676644/bp-batam-siapkan-sekolah-terintegrasi-merah-putih-di-rempang</t>
-        </is>
-      </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/BP-BATAM-SIAPKAN-SEKOLAH-TERINTEGRASI-MERAH-PUTIH-DI-REMPANG.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>Aldila Sutjiadi juarai WTA 500 Mubadala DC Open 2026</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr"/>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>ANTARA - Petenis ganda putri Indonesia Aldila Sutjiadi menjuarai nomor ganda Women's Tennis Association (WTA) 500 Mubadala DC Open 2026 di Washington, Amerika Serikat. Berpasangan dengan petenis Selandia Baru Erin Routliffe, Aldila mengalahkan Andreja Klepac dari Slovenia dan Makoto Ninomiya dari Jepang dua set langsung 6-4, 6-1 pada partai final. Gelar tersebut menjadi trofi WTA kedelapan dalam karier Aldila di nomor ganda sekaligus gelar kedua bersama Routliffe pada musim 2026.
-(Arsy Fitriady/Satrio Giri Marwanto/I Gusti Agung Ayu N)</t>
-        </is>
-      </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676629/aldila-sutjiadi-juarai-wta-500-mubadala-dc-open-2026</t>
-        </is>
-      </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/ALDILA-SUTJIADI-JUARAI-WTA-500-MUBADALA-DC-OPEN-2026.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>KM Mutiara Sentosa 2 Terbakar Saat Berlayar ke Makassar</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr"/>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>ANTARA - Kapal Motor (KM) Mutiara Sentosa 2 terbakar di perairan utara Pulau Madura saat berlayar dari Pelabuhan Tanjung Perak Surabaya menuju Makassar, Minggu (2/8). Kapal tersebut mengangkut sekitar 250 orang. Tim SAR gabungan masih melakukan evakuasi penumpang, sementara penyebab kebakaran masih dalam penyelidikan. (Hanif Nasrullah/Satrio Giri Marwanto/Arsy Fitriady)</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676617/km-mutiara-sentosa-2-terbakar-saat-berlayar-ke-makassar</t>
-        </is>
-      </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/KM-MUTIARA-SENTOSA-2-TERBAKAR-SAAT-BERLAYAR-KE-MAKASSAR.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>BI dan Pemkot Kendari Perkuat Digitalisasi UMKM</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr"/>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>ANTARA - Kantor Perwakilan Bank Indonesia Sulawesi Tenggara bersama Pemerintah Kota Kendari menggelar Festival Kuliner Sultra Maimo 2026 untuk memperkuat digitalisasi usaha mikro, kecil, dan menengah atau UMKM. Festival yang berlangsung pada 2 hingga 9 Agustus itu juga mendorong perluasan transaksi non-tunai berbasis QRIS. (Saharudin/Satrio Giri Marwanto/Arsy Fitriady)</t>
-        </is>
-      </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676607/bi-dan-pemkot-kendari-perkuat-digitalisasi-umkm</t>
-        </is>
-      </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/BI-DAN-PEMKOT-KENDARI-PERKUAT-DIGITALISASI-UMKM.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>El Nino menguat, negara fokus jaga ketersediaan air &amp; tangani karhutla</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr"/>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>ANTARA - Gelombang panas sebagai akibat El Nino mulai dirasakan dampaknya di sejumlah belahan dunia. Kebakaran hutan dan lahan atau karhutla, juga mulai terjadi di dalam negeri, seperti di Pulau Sumatera dan Kalimantan.Selain kebakaran, bencana ekologi yang terjadi ialah kekeringan. Beberapa daerah di Pulau Jawa seperti Temanggung, Sukoharjo, Lumajang, Banten, lalu daerah luar Jawa seperti Nusa Tenggara Barat dan Timur, hingga Bangka Belitung mulai mengalami krisis air bersih.Presiden pun memanggil sejumlah kepala kementerian dan lembaga terkait, untuk memberi pemaparan dan masukan guna meredam dampak El Nino.Lalu bagaimana sikap antisipatif yang disiapkan pemerintah pada musim kemarau dan el nino tahun ini? Selengkapnya dalam PerANTARA! (Roy Rosa Bachtiar/Suci Nurhaliza/Gunawan Wibisono/Rizky Bagus Dhermawan/Farah Khadija)</t>
-        </is>
-      </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676540/el-nino-menguat-negara-fokus-jaga-ketersediaan-air-tangani-karhutla</t>
-        </is>
-      </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/DF.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>Padang Padang Cup Bali jadi ajang peselancar Nasional unjuk kehebatan</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr"/>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>ANTARA - Kompetisi selancar ombak Internasional Rip Curl Cup Padang Padang kembali digelar dan berlangsung pada 1-31 Agustus 2026, di Pantai Padang Padang, Labuan Sait Pecatu, Kuta Selatan, Bali. Ajang ini menjadi ruang bagi peselancar Nasional menunjukkan kehebatan mereka bersaing dengan peselancar Internasional. (Rita Laura/Sandy Arizona/Rijalul Vikry)</t>
-        </is>
-      </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676257/padang-padang-cup-bali-jadi-ajang-peselancar-nasional-unjuk-kehebatan</t>
-        </is>
-      </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_PADANG-PADANG-CUP-BALI-JADI-AJANG-PESELANCAR-NASIONAL-UNJUK-KEHEBATAN.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>Bekuk Port FC, Persebaya gandeng Persija ke semifinal</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr"/>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>ANTARA - Persebaya membekuk Port FC 2 - 1 di laga terakhir Grup B turnamen sepak Piala Presiden 2026. Dengan hasil ini Persija lolos ke babak semifinal bersama Persebaya sebagai wakil Grup B. (Hanif Nasrullah/Sandy Arizona/Rijalul Vikry)</t>
-        </is>
-      </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676252/bekuk-port-fc-persebaya-gandeng-persija-ke-semifinal</t>
-        </is>
-      </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_BEKUK-PORT-FC-PERSEBAYA-GANDENG-PERSIJA-KE-SEMIFINAL.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>Aston Villa unggul 3-1 dari Indonesia All Stars dalam tur pramusim</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr"/>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>ANTARA - Tim Indonesia All Stars, harus mengakui keunggulan atas Aston Villa dengan skor 3-1, saat laga Friendly Match di Stadion Utama Gelora Bung Karno (SUGBK) Senayan, Jakarta, pada Sabtu (1/8). Penjaga Gawang Aston Villa, James Wright, saat ditemui media di GBK mengapresiasi para pemain Indonesia All Stars, karena dinilai memiliki kualitas yang baik. (Ryan Rahman/Sandy Arizona/Rijalul Vikry)</t>
-        </is>
-      </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676239/aston-villa-unggul-3-1-dari-indonesia-all-stars-dalam-tur-pramusim</t>
-        </is>
-      </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_ASTON-VILLA-UNGGUL-3-1-DARI-INDONESIA-ALL-STARS-DALAM-TUR-PRAMUSIM.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>Joko Widodo dinobatkan sebagai sesepuh oleh sembilan Raja Timor</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr"/>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>ANTARA - Ribuan warga memadati kawasan Pantai Lahi Lai Bissi Kopan (LLBK) Kota Kupang, Nusa Tenggara Timur, untuk menyaksikan Karnaval Budaya yang dihadiri Presiden ke-7 Republik Indonesia, Joko Widodo. Dalam prosesi adat yang menjadi puncak acara, Joko Widodo dinobatkan sebagai sesepuh atau saudara oleh sembilan raja dari kerajaan-kerajaan di Pulau Timor sebagai bentuk penghormatan terhadap nilai persaudaraan dan budaya masyarakat Timor. (Johanes Viandinando/Sandy Arizona/Rijalul Vikry)</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676205/joko-widodo-dinobatkan-sebagai-sesepuh-oleh-sembilan-raja-timor</t>
-        </is>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_JOKO-WIDODO-DINOBATKAN-SEBAGAI-SESEPUH-OLEH-SEMBILAN-RAJA-TIMOR.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>Menag: Indeks kerukunan umat beragama RI jadi 77,89 persen di 2025</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr"/>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>ANTARA - Menteri Agama Nasaruddin Umar menyebut indeks kerukunan umat beragama naik menjadi 77,89 persen pada tahun 2025, dari sebelumnya, yakni 76,47 persen pada tahun 2024. Hal tersebut disampaikan oleh Menag saat mengahdiri agenda Zikir dan Doa Kebangsaan "Indonesia Berdaulat, Adil dan Makmur" di Lapangan Silang Monas, Jakarta, Sabtu (1/8).
-(Afra Augesti/Nico Anggriawan/Sandy Arizona/Nabila Anisya Charisty)</t>
-        </is>
-      </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676188/menag-indeks-kerukunan-umat-beragama-ri-jadi-7789-persen-di-2025</t>
-        </is>
-      </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_MENAG-INDEKS-KERUKUNAN-UMAT-BERAGAMA-RI-JADI-77-89-PERSEN-DI-2025.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>KKP bantu pelaku usaha perikanan terdampak bencana di Sumbar</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr"/>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>ANTARA - Kementerian Kelautan dan Perikanan (KKP) bersama Tim Satuan Tugas Percepatan Rehabilitasi dan Rekonstruksi (PRR) Provinsi Sumatera Barat, mempercepat dan memastikan operasionalisasi budi daya, nelayan serta pengolahan ikan segera berjalan pascabencana hidrometeorologi yang terjadi akhir November tahun lalu. Untuk itu, KKP memberikan bantuan awal berupa bibit ikan dan pakan, dan ekskavator, kepada pelaku usaha perikanan yang terdampak bencana hidrometeorologis di Kota Padang, Kabupaten Padang Pariaman, Kabupaten Solok dan Kabupaten Agam.
-(Melani Friati/Sandy Arizona/Nabila Anisya Charisty)</t>
-        </is>
-      </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676172/kkp-bantu-pelaku-usaha-perikanan-terdampak-bencana-di-sumbar</t>
-        </is>
-      </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_KKP-BANTU-PELAKU-USAHA-PERIKANAN-TERDAMPAK-BENCANA-DI-SUMBAR.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>INZS 2026 perkuat komitmen Indonesia hadapi krisis iklim</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr"/>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>ANTARA - Pemerintah Indonesia terus mempercepat transisi energi sebagai bagian dari upaya mengatasi perubahan iklim melalui berbagai proyek yang mulai direalisasikan. Komitmen tersebut mengemuka dalam Indonesia Net Zero Summit (INZS) 2026 di Balai Kartini, Jakarta, Sabtu (1/8). Pendiri Foreign Policy Community of Indonesia (FPCI), Dino Patti Djalal, menegaskan bahwa penanganan perubahan iklim harus menjadi prioritas karena dampaknya menyentuh hampir seluruh aspek kehidupan manusia.
-(Irfan Hardiansah/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
-        </is>
-      </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676087/inzs-2026-perkuat-komitmen-indonesia-hadapi-krisis-iklim</t>
-        </is>
-      </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/INZS-2026-PERKUAT-KOMITMEN-INDONESIA-HADAPI-KRISIS-IKLIM.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>Kemeriahan menyambut bulan kemerdekaan Indonesia di Malaysia</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr"/>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>ANTARA - Kegembiraan menyambut bulan kemerdekaan Republik Indonesia turut dirasakan para warga negara Indonesia yang berada di negeri jiran Malaysia. WNI dengan penuh antusias mengikuti berbagai perlombaan yang diselenggarakan Kedutaan Besar Republik Indonesia (KBRI) di Kuala Lumpur, Malaysia, Sabtu (1/8).
-(Rangga Pandu Asmara Jingga/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676063/kemeriahan-menyambut-bulan-kemerdekaan-indonesia-di-malaysia</t>
-        </is>
-      </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/KEMERIAHAN-MENYAMBUT-BULAN-KEMERDEKAAN-INDONESIA-DI-MALAYSIA.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>Cari Bibit unggul, Bogor gelar sirkuit panjat tebing anak dan remaja</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 19:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr"/>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>ANTARA - Federasi Panjat Tebing Indonesia (FPTI) Kota Bogor menggelar Sirkuit Panjat Tebing se-Kota Bogor sebagai ajang pencarian bibit atlet muda, Sabtu (1/8). Dengan diikuti 100 peserta anak-anak dan remaja, kegiatan itu mempertandingkan kategori lead dan speed untuk kelompok umur under 11, under 13, dan under 19.
-(Fadzar Ilham Pangestu/Satrio Giri Marwanto/Nabila Anisya Charisty)</t>
-        </is>
-      </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676021/cari-bibit-unggul-bogor-gelar-sirkuit-panjat-tebing-anak-dan-remaja</t>
-        </is>
-      </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/CARI-BIBIT-UNGGUL-BOGOR-GELAR-SIRKUIT-PANJAT-TEBING-ANAK-DAN-REMAJA.jpg</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G295"/>
+  <autoFilter ref="A1:G380"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_antara_2026-08-03.xlsx
+++ b/data/berita_antara_2026-08-03.xlsx
@@ -10631,28 +10631,28 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Chelsea umumkan transfer gelandang Inggris Jordan Henderson</t>
+          <t>TNBTS tutup sebagian akses Bromo imbas kebakaran hutan Blok Batengan</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:59:34 +0700</t>
+          <t>Mon, 03 Aug 2026 22:44:14 +0700</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Chelsea resmi mengumumkan kedatangan gelandang senior asal Inggris Jordan Henderson dengan status bebas transfer ...</t>
+          <t>Balai Besar Taman Nasional Bromo Tengger Semeru (TNBTS) menutup sebagian akses wisata Gunung Bromo dari pintu masuk ...</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678548/chelsea-umumkan-transfer-gelandang-inggris-jordan-henderson</t>
+          <t>https://www.antaranews.com/berita/5678457/tnbts-tutup-sebagian-akses-bromo-imbas-kebakaran-hutan-blok-batengan</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000042505.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001396577.jpg</t>
         </is>
       </c>
     </row>
@@ -10664,28 +10664,28 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Nguyen Xuan Son ungkap alasan tak jadi starter saat kalahkan Indonesia</t>
+          <t>KPK hentikan penyidikan enam kasus, termasuk kasus Sekjen DPR</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:56:45 +0700</t>
+          <t>Mon, 03 Aug 2026 22:39:52 +0700</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Penyerang Timnas Vietnam Nguyen Xuan Son mengungkapkan alasan dirinya tidak dimainkan sebagai starter saat timnya ...</t>
+          <t>Komisi Pemberantasan Korupsi (KPK) menghentikan penyidikan enam kasus dugaan tindak pidana korupsi dengan menerbitkan ...</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678547/nguyen-xuan-son-ungkap-alasan-tak-jadi-starter-saat-kalahkan-indonesia</t>
+          <t>https://www.antaranews.com/berita/5678453/kpk-hentikan-penyidikan-enam-kasus-termasuk-kasus-sekjen-dpr</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1003314030.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_8208.jpg</t>
         </is>
       </c>
     </row>
@@ -10697,61 +10697,61 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
+          <t>Sekjen Golkar hingga eks Menpora bakal beri materi di Mubes Kosgoro</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:55:47 +0700</t>
+          <t>Mon, 03 Aug 2026 22:38:02 +0700</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ...</t>
+          <t>Sekjen DPP Partai Golkar Muhammad Sarmuji hingga Menpora periode 2023-2025 Dito Ariotedjo akan memberikan materi dalam ...</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+          <t>https://www.antaranews.com/berita/5678449/sekjen-golkar-hingga-eks-menpora-bakal-beri-materi-di-mubes-kosgoro</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000469031.jpg</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>BPS kaitkan kenaikan TPK hotel bintang dengan kualitas wisman</t>
+          <t>Briket ampas kopi inovasi dosen UTU Meulaboh kantongi sertifikat paten</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:53:51 +0700</t>
+          <t>Mon, 03 Aug 2026 22:37:22 +0700</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) Bali mengaitkan kenaikan tingkat penghunian kamar (TPK) hotel bintang pada Juni 2026 dengan ...</t>
+          <t>Inovasi pengolahan limbah ampas kopi menjadi briket bahan bakar padat yang efisien karya Dosen Fakultas Pertanian ...</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678543/bps-kaitkan-kenaikan-tpk-hotel-bintang-dengan-kualitas-wisman</t>
+          <t>https://www.antaranews.com/berita/5678445/briket-ampas-kopi-inovasi-dosen-utu-meulaboh-kantongi-sertifikat-paten</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0332.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/20260803-briket-ampas-kopi-dosen-utu-meulaboh.jpeg</t>
         </is>
       </c>
     </row>
@@ -10763,193 +10763,193 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Jogja Run'nShine 2026 targetkan diikuti 3.500 pelari</t>
+          <t>Indonesia-Thailand sepakat tingkatkan kerja sama pertahanan, keamanan</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:52:29 +0700</t>
+          <t>Mon, 03 Aug 2026 22:35:28 +0700</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Pergelaran Jogja Run'nShine 2026 menargetkan diikuti sebanyak 3.500 pelari dengan memberikan pengalaman konsep ...</t>
+          <t>Presiden Republik Indonesia Prabowo Subianto dan Perdana Menteri (PM) Thailand Anutin Charnvirakul sepakat untuk ...</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678540/jogja-runnshine-2026-targetkan-diikuti-3500-pelari</t>
+          <t>https://www.antaranews.com/berita/5678443/indonesia-thailand-sepakat-tingkatkan-kerja-sama-pertahanan-keamanan</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0103.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/tempImageXOTgJY.jpg</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Jenama perkakas otomotif Tekiro dapat pengakuan Guinnes World Records</t>
+          <t>Kepala BGN: Putusan MK perkuat Program Makan Bergizi Gratis</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:47:06 +0700</t>
+          <t>Mon, 03 Aug 2026 22:32:37 +0700</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Jenama perkakas otomotif Tekiro mendapat pengakuan dari Guiness World Records berkat ...</t>
+          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono mengatakan putusan Mahkamah Konstitusi (MK) Nomor 40/PUU-XXIV/2026 yang ...</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5678535/jenama-perkakas-otomotif-tekiro-dapat-pengakuan-guinnes-world-records</t>
+          <t>https://www.antaranews.com/berita/5678436/kepala-bgn-putusan-mk-perkuat-program-makan-bergizi-gratis</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-02-at-15.34.09-1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/189743.jpg</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Pemkab Sleman dukung kejuaraan dragbike tingkatkan ekonomi masyarakat</t>
+          <t>Banjir kepung 15 titik di Kota Padang akibat cuaca ekstrem</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:42:42 +0700</t>
+          <t>Mon, 03 Aug 2026 22:25:29 +0700</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Pemerintah Kabupaten Sleman, Daerah Istimewa Yogyakarta, mendukung penuh penyelenggaraan Kejuaraan Dragbike Super ...</t>
+          <t>ANTARA - Hujan lebat disertai angin kencang memicu bencana di Kabupaten Agam, Kota Pariaman, dan Kota Padang, Sumatera ...</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678532/pemkab-sleman-dukung-kejuaraan-dragbike-tingkatkan-ekonomi-masyarakat</t>
+          <t>https://www.antaranews.com/video/5678396/banjir-kepung-15-titik-di-kota-padang-akibat-cuaca-ekstrem</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000029422.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BANJIR-KEPUNG-15-TITIK-DI-KOTA-PADANG-AKIBAT-CUACA-EKSTREM.jpg</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GMR nilai akses penerbangan langsung buka peluang ekonomi RI-India</t>
+          <t>Erick ungkap strategi sebelum kembali ke bursa calon Ketum PSSI 2027</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:41:32 +0700</t>
+          <t>Mon, 03 Aug 2026 22:22:41 +0700</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>GMR Group, perusahaan multinasional India yang bergerak di bidang infrastruktur, menilai akses penerbangan langsung ...</t>
+          <t>ANTARA - Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir tidak menutup kemungkinan untuk ...</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678529/gmr-nilai-akses-penerbangan-langsung-buka-peluang-ekonomi-ri-india</t>
+          <t>https://www.antaranews.com/video/5678327/erick-ungkap-strategi-sebelum-kembali-ke-bursa-calon-ketum-pssi-2027</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/DSF3021.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/ERICK-UNGKAP-STRATEGI-SEBELUM-KEMBALI-KE-BURSA-CALON-KETUM-PSSI-2027.jpg</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>PSSI raup dana Rp722 miliar dalam laporan keuangan tahunan</t>
+          <t>Daop 6 Yogyakarta tutup perlintasan tak terjaga Petak Sentolo–Rewulu</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:37:46 +0700</t>
+          <t>Mon, 03 Aug 2026 21:28:06 +0700</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir menyebut organisasinya meraup dana senilai Rp722 ...</t>
+          <t>PT Kereta Api Indonesia (Persero) Daerah Operasi 6 Yogyakarta terus berkolaborasi dengan pemerintah terkait, untuk ...</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678528/pssi-raup-dana-rp722-miliar-dalam-laporan-keuangan-tahunan</t>
+          <t>https://www.antaranews.com/berita/5678331/daop-6-yogyakarta-tutup-perlintasan-tak-terjaga-petak-sentolo-rewulu</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0098_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000029465.jpg</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Otorita kolaborasi PNM untuk pengembangan ekonomi masyarakat IKN</t>
+          <t>Kementan usulkan telur masuk skema CPP demi lindungi peternak rakyat</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:30:50 +0700</t>
+          <t>Mon, 03 Aug 2026 21:27:37 +0700</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Otorita Ibu Kota Nusantara (IKN) melakukan kolaborasi dengan PT Permodalan Nasional Madani (Persero) untuk pengembangan ...</t>
+          <t>Kementerian Pertanian (Kementan) mengusulkan komoditas telur ayam masuk dalam skema pengadaan Cadangan Pangan ...</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678525/otorita-kolaborasi-pnm-untuk-pengembangan-ekonomi-masyarakat-ikn</t>
+          <t>https://www.antaranews.com/berita/5678329/kementan-usulkan-telur-masuk-skema-cpp-demi-lindungi-peternak-rakyat</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0012_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/9C2BC3E9-1C7E-4159-8805-C378B9294E25.jpeg</t>
         </is>
       </c>
     </row>
@@ -10961,28 +10961,28 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>DPR: Wacana Prabowo jembatani dialog Korea sesuai politik bebas aktif</t>
+          <t>Chelsea umumkan transfer gelandang Inggris Jordan Henderson</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:30:13 +0700</t>
+          <t>Mon, 03 Aug 2026 23:59:34 +0700</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Wakil Ketua Komisi I DPR RI Dave Laksono menilai wacana Presiden Prabowo Subianto untuk menjembatani dialog antara ...</t>
+          <t>Chelsea resmi mengumumkan kedatangan gelandang senior asal Inggris Jordan Henderson dengan status bebas transfer ...</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678521/dpr-wacana-prabowo-jembatani-dialog-korea-sesuai-politik-bebas-aktif</t>
+          <t>https://www.antaranews.com/berita/5678548/chelsea-umumkan-transfer-gelandang-inggris-jordan-henderson</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/22/IMG_20260422_175322.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000042505.jpg</t>
         </is>
       </c>
     </row>
@@ -10994,94 +10994,94 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Kongres PSSI sepakati pemilihan pengurus mundur ke Juli 2027</t>
+          <t>Nguyen Xuan Son ungkap alasan tak jadi starter saat kalahkan Indonesia</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:30:00 +0700</t>
+          <t>Mon, 03 Aug 2026 23:56:45 +0700</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>ANTARA - Kongres Biasa PSSI 2026 menyepakati perubahan jadwal Kongres Pemilihan Pengurus PSSI 2027 dari semula Mei ...</t>
+          <t>Penyerang Timnas Vietnam Nguyen Xuan Son mengungkapkan alasan dirinya tidak dimainkan sebagai starter saat timnya ...</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678395/kongres-pssi-sepakati-pemilihan-pengurus-mundur-ke-juli-2027</t>
+          <t>https://www.antaranews.com/berita/5678547/nguyen-xuan-son-ungkap-alasan-tak-jadi-starter-saat-kalahkan-indonesia</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KONGRES-PSSI-SEPAKATI-PEMILIHAN-PENGURUS-MUNDUR-KE-JULI-2027.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1003314030.jpg</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Toyota Astra Motor perkenalkan Hilux generasi ke-9</t>
+          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:25:20 +0700</t>
+          <t>Mon, 03 Aug 2026 23:55:47 +0700</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
-          <t>PT Toyota Astra Motor (TAM) memperkenalkan Hilux generasi ke-9 untuk mendukung pemenuhan kebutuhan operasional industri ...</t>
+          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ...</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5678519/toyota-astra-motor-perkenalkan-hilux-generasi-ke-9</t>
+          <t>https://www.antaranews.com/video/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/photo_6307309656757440820_w-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Sudin PPAPP Jakbar sosialisasikan Sekolah Siaga Kependudukan</t>
+          <t>BPS kaitkan kenaikan TPK hotel bintang dengan kualitas wisman</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:24:33 +0700</t>
+          <t>Mon, 03 Aug 2026 23:53:51 +0700</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Suku Dinas Pemberdayaan, Perlindungan Anak, dan Pengendalian Penduduk (Sudin PPAPP) Jakarta Barat (Jakbar) menggelar ...</t>
+          <t>Badan Pusat Statistik (BPS) Bali mengaitkan kenaikan tingkat penghunian kamar (TPK) hotel bintang pada Juni 2026 dengan ...</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678515/sudin-ppapp-jakbar-sosialisasikan-sekolah-siaga-kependudukan</t>
+          <t>https://www.antaranews.com/berita/5678543/bps-kaitkan-kenaikan-tpk-hotel-bintang-dengan-kualitas-wisman</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0031_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0332.jpeg</t>
         </is>
       </c>
     </row>
@@ -11093,28 +11093,28 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Klasemen Grup A Piala AFF : Timnas Indonesia turun ke peringkat tiga</t>
+          <t>Jogja Run'nShine 2026 targetkan diikuti 3.500 pelari</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:23:51 +0700</t>
+          <t>Mon, 03 Aug 2026 23:52:29 +0700</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Timnas Indonesia turun ke peringkat ketiga klasemen sementara Grup A Piala AFF 2026 setelah menelan kekalahan 0-3 dari ...</t>
+          <t>Pergelaran Jogja Run'nShine 2026 menargetkan diikuti sebanyak 3.500 pelari dengan memberikan pengalaman konsep ...</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678512/klasemen-grup-a-piala-aff-timnas-indonesia-turun-ke-peringkat-tiga</t>
+          <t>https://www.antaranews.com/berita/5678540/jogja-runnshine-2026-targetkan-diikuti-3500-pelari</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833516.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0103.jpg</t>
         </is>
       </c>
     </row>
@@ -11126,28 +11126,28 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>NTB menargetkan penonton MotoGP Mandalika tembus 140 ribu</t>
+          <t>Jenama perkakas otomotif Tekiro dapat pengakuan Guinnes World Records</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:23:01 +0700</t>
+          <t>Mon, 03 Aug 2026 23:47:06 +0700</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Pemerintah Provinsi Nusa Tenggara Barat menargetkan jumlah penonton MotoGP di Sirkuit Mandalika pada 9-11 Oktober 2026 ...</t>
+          <t>Jenama perkakas otomotif Tekiro mendapat pengakuan dari Guiness World Records berkat ...</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678508/ntb-menargetkan-penonton-motogp-mandalika-tembus-140-ribu</t>
+          <t>https://otomotif.antaranews.com/berita/5678535/jenama-perkakas-otomotif-tekiro-dapat-pengakuan-guinnes-world-records</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260109-WA0024_copy_1280x797.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-02-at-15.34.09-1.jpeg</t>
         </is>
       </c>
     </row>
@@ -11159,61 +11159,61 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Bulog: Margin naik jadi 7 persen, dukungan Presiden kawal swasembada</t>
+          <t>Pemkab Sleman dukung kejuaraan dragbike tingkatkan ekonomi masyarakat</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:19:51 +0700</t>
+          <t>Mon, 03 Aug 2026 23:42:42 +0700</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Direktur Utama Perum Bulog Ahmad Rizal Ramdhani menegaskan kenaikan margin fee menjadi 7 persen bentuk dukungan ...</t>
+          <t>Pemerintah Kabupaten Sleman, Daerah Istimewa Yogyakarta, mendukung penuh penyelenggaraan Kejuaraan Dragbike Super ...</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678504/bulog-margin-naik-jadi-7-persen-dukungan-presiden-kawal-swasembada</t>
+          <t>https://www.antaranews.com/berita/5678532/pemkab-sleman-dukung-kejuaraan-dragbike-tingkatkan-ekonomi-masyarakat</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/14C1B7CB-9D6F-49B9-9CD1-E40DD76E851C.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000029422.jpg</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Turkiye sebut serangan Israel sabotase upaya damai di Gaza</t>
+          <t>GMR nilai akses penerbangan langsung buka peluang ekonomi RI-India</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:18:30 +0700</t>
+          <t>Mon, 03 Aug 2026 23:41:32 +0700</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Pemerintah Turkiye pada Senin menilai serangan Israel di Jalur Gaza telah menghambat berbagai inisiatif diplomatik yang ...</t>
+          <t>GMR Group, perusahaan multinasional India yang bergerak di bidang infrastruktur, menilai akses penerbangan langsung ...</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678500/turkiye-sebut-serangan-israel-sabotase-upaya-damai-di-gaza</t>
+          <t>https://www.antaranews.com/berita/5678529/gmr-nilai-akses-penerbangan-langsung-buka-peluang-ekonomi-ri-india</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/thumbs_b_c_186832d7ab4775afec853057c8952c3d.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/DSF3021.jpeg</t>
         </is>
       </c>
     </row>
@@ -11225,61 +11225,61 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Purbaya pastikan tak ada lagi perdebatan soal penarikan SAL dari bank</t>
+          <t>PSSI raup dana Rp722 miliar dalam laporan keuangan tahunan</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:15:59 +0700</t>
+          <t>Mon, 03 Aug 2026 23:37:46 +0700</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Menteri Keuangan (Menkeu), Purbaya Yudhi Sadewa memastikan tidak ada lagi perdebatan mengenai penarikan dana ...</t>
+          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir menyebut organisasinya meraup dana senilai Rp722 ...</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678499/purbaya-pastikan-tak-ada-lagi-perdebatan-soal-penarikan-sal-dari-bank</t>
+          <t>https://www.antaranews.com/berita/5678528/pssi-raup-dana-rp722-miliar-dalam-laporan-keuangan-tahunan</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-23.02.47.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0098_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Tim 9 Kejagung didesak usut pemilik uang-emas di rumah eks Jampidsus</t>
+          <t>Otorita kolaborasi PNM untuk pengembangan ekonomi masyarakat IKN</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:10:43 +0700</t>
+          <t>Mon, 03 Aug 2026 23:30:50 +0700</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Tim 9 Kejaksaan Agung didesak mengusut tuntas pemilik uang tunai senilai Rp476 miliar dan emas batangan seberat 74 ...</t>
+          <t>Otorita Ibu Kota Nusantara (IKN) melakukan kolaborasi dengan PT Permodalan Nasional Madani (Persero) untuk pengembangan ...</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678495/tim-9-kejagung-didesak-usut-pemilik-uang-emas-di-rumah-eks-jampidsus</t>
+          <t>https://www.antaranews.com/berita/5678525/otorita-kolaborasi-pnm-untuk-pengembangan-ekonomi-masyarakat-ikn</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/1000175632.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0012_1.jpg</t>
         </is>
       </c>
     </row>
@@ -11291,94 +11291,94 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Kemenbud hadirkan GBN untuk membina talenta seni musik nasional</t>
+          <t>DPR: Wacana Prabowo jembatani dialog Korea sesuai politik bebas aktif</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:07:01 +0700</t>
+          <t>Mon, 03 Aug 2026 23:30:13 +0700</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Kementerian Kebudayaan (Kemenbud) menghadirkan program pembinaan talenta seni musik nasional yang mempertemukan ...</t>
+          <t>Wakil Ketua Komisi I DPR RI Dave Laksono menilai wacana Presiden Prabowo Subianto untuk menjembatani dialog antara ...</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678491/kemenbud-hadirkan-gbn-untuk-membina-talenta-seni-musik-nasional</t>
+          <t>https://www.antaranews.com/berita/5678521/dpr-wacana-prabowo-jembatani-dialog-korea-sesuai-politik-bebas-aktif</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-20.28.05.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/22/IMG_20260422_175322.jpg</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Wamen ATR: Ujian PPAT upaya berikan layanan yang baik</t>
+          <t>Kongres PSSI sepakati pemilihan pengurus mundur ke Juli 2027</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:05:29 +0700</t>
+          <t>Mon, 03 Aug 2026 23:30:00 +0700</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Wakil Menteri Agraria dan Tata Ruang/Wakil Kepala Badan Pertanahan Nasional (Wamen ATR/Waka BPN) Ossy Dermawan ...</t>
+          <t>ANTARA - Kongres Biasa PSSI 2026 menyepakati perubahan jadwal Kongres Pemilihan Pengurus PSSI 2027 dari semula Mei ...</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678489/wamen-atr-ujian-ppat-upaya-berikan-layanan-yang-baik</t>
+          <t>https://www.antaranews.com/video/5678395/kongres-pssi-sepakati-pemilihan-pengurus-mundur-ke-juli-2027</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_223512.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KONGRES-PSSI-SEPAKATI-PEMILIHAN-PENGURUS-MUNDUR-KE-JULI-2027.jpg</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PBSI buka suara soal absennya Jafar/Felisha di Kejuaraan Dunia BWF</t>
+          <t>Toyota Astra Motor perkenalkan Hilux generasi ke-9</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:03:05 +0700</t>
+          <t>Mon, 03 Aug 2026 23:25:20 +0700</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Pengurus Pusat PBSI menyatakan absennya dua pasangan ganda campuran Indonesia Jafar Hidayatullah/Felisha Alberta ...</t>
+          <t>PT Toyota Astra Motor (TAM) memperkenalkan Hilux generasi ke-9 untuk mendukung pemenuhan kebutuhan operasional industri ...</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678487/pbsi-buka-suara-soal-absennya-jafar-felisha-di-kejuaraan-dunia-bwf</t>
+          <t>https://otomotif.antaranews.com/berita/5678519/toyota-astra-motor-perkenalkan-hilux-generasi-ke-9</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/06/IMG_20251127_205351.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/photo_6307309656757440820_w-1.jpg</t>
         </is>
       </c>
     </row>
@@ -11390,28 +11390,28 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Presiden Prabowo terima kunjungan PM Thailand di Istana Merdeka</t>
+          <t>Sudin PPAPP Jakbar sosialisasikan Sekolah Siaga Kependudukan</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:59:27 +0700</t>
+          <t>Mon, 03 Aug 2026 23:24:33 +0700</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Prabowo Subianto menerima kunjungan resmi Perdana Menteri Thailand Anutin Charnvirakul di Istana ...</t>
+          <t>Suku Dinas Pemberdayaan, Perlindungan Anak, dan Pengendalian Penduduk (Sudin PPAPP) Jakarta Barat (Jakbar) menggelar ...</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678461/presiden-prabowo-terima-kunjungan-pm-thailand-di-istana-merdeka</t>
+          <t>https://www.antaranews.com/berita/5678515/sudin-ppapp-jakbar-sosialisasikan-sekolah-siaga-kependudukan</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PRESIDEN-PRABOWO-TERIMA-KUNJUNGAN-PM-THAILAND-DI-ISTANA-MERDEKA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0031_1.jpg</t>
         </is>
       </c>
     </row>
@@ -11423,28 +11423,28 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
+          <t>Klasemen Grup A Piala AFF : Timnas Indonesia turun ke peringkat tiga</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:58:38 +0700</t>
+          <t>Mon, 03 Aug 2026 23:23:51 +0700</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>ANTARA - Badan Pencarian dan Pertolongan Nasional (Basarnas) mengerahkan satu unit kapal untuk menjemput 66 korban ...</t>
+          <t>Timnas Indonesia turun ke peringkat ketiga klasemen sementara Grup A Piala AFF 2026 setelah menelan kekalahan 0-3 dari ...</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678472/basarnas-jemput-66-korban-km-mutiara-sentosa-ii-dari-masalembu</t>
+          <t>https://www.antaranews.com/berita/5678512/klasemen-grup-a-piala-aff-timnas-indonesia-turun-ke-peringkat-tiga</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BASARNAS-JEMPUT-66-KORBAN-KM-MUTIARA-SENTOSA-II-DARI-MASALEMBU.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833516.jpg</t>
         </is>
       </c>
     </row>
@@ -11456,61 +11456,61 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Kementerian ATR/BPN telah terbitkan 124 ribu SK sertifikat rumah MBR</t>
+          <t>NTB menargetkan penonton MotoGP Mandalika tembus 140 ribu</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:56:36 +0700</t>
+          <t>Mon, 03 Aug 2026 23:23:01 +0700</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Kementerian Agraria dan Tata Ruang/Badan Pertanahan Nasional (ATR/BPN) menyatakan telah menerbitkan surat keputusan ...</t>
+          <t>Pemerintah Provinsi Nusa Tenggara Barat menargetkan jumlah penonton MotoGP di Sirkuit Mandalika pada 9-11 Oktober 2026 ...</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678484/kementerian-atr-bpn-telah-terbitkan-124-ribu-sk-sertifikat-rumah-mbr</t>
+          <t>https://www.antaranews.com/berita/5678508/ntb-menargetkan-penonton-motogp-mandalika-tembus-140-ribu</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_224532.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260109-WA0024_copy_1280x797.jpg</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Timnas Indonesia dibungkam Vietnam 0-3</t>
+          <t>Bulog: Margin naik jadi 7 persen, dukungan Presiden kawal swasembada</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:54:01 +0700</t>
+          <t>Mon, 03 Aug 2026 23:19:51 +0700</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Timnas Indonesia dibungkam Vietnam 0-3 di kandang pada laga lanjutan Grup A Piala AFF 2026 di Stadion Pakansari, Bogor, ...</t>
+          <t>Direktur Utama Perum Bulog Ahmad Rizal Ramdhani menegaskan kenaikan margin fee menjadi 7 persen bentuk dukungan ...</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678480/timnas-indonesia-dibungkam-vietnam-0-3</t>
+          <t>https://www.antaranews.com/berita/5678504/bulog-margin-naik-jadi-7-persen-dukungan-presiden-kawal-swasembada</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Timnas-Indonesia-lawan-Vietnam-030826-Bay-21a.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/14C1B7CB-9D6F-49B9-9CD1-E40DD76E851C.jpeg</t>
         </is>
       </c>
     </row>
@@ -11522,28 +11522,28 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Prabowo-PM Thailand perkuat kemitraan strategis ASEAN</t>
+          <t>Turkiye sebut serangan Israel sabotase upaya damai di Gaza</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:52:55 +0700</t>
+          <t>Mon, 03 Aug 2026 23:18:30 +0700</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Presiden RI Prabowo Subianto dan Perdana Menteri (PM) Thailand Anutin Charnvirakul sepakat memperkuat kemitraan ...</t>
+          <t>Pemerintah Turkiye pada Senin menilai serangan Israel di Jalur Gaza telah menghambat berbagai inisiatif diplomatik yang ...</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678476/prabowo-pm-thailand-perkuat-kemitraan-strategis-asean</t>
+          <t>https://www.antaranews.com/berita/5678500/turkiye-sebut-serangan-israel-sabotase-upaya-damai-di-gaza</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_F6F7E006D3CC-1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/thumbs_b_c_186832d7ab4775afec853057c8952c3d.jpg</t>
         </is>
       </c>
     </row>
@@ -11555,61 +11555,61 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Galaxy Tab S12 Ultra mejeng di Geekbench, hadir dengan Dimensity 9500</t>
+          <t>Purbaya pastikan tak ada lagi perdebatan soal penarikan SAL dari bank</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:48:03 +0700</t>
+          <t>Mon, 03 Aug 2026 23:15:59 +0700</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Tab S12 Ultra dalam seri perangkat Galaxy Tab S12 yang diperkirakan dirilis September 2026 muncul di ...</t>
+          <t>Menteri Keuangan (Menkeu), Purbaya Yudhi Sadewa memastikan tidak ada lagi perdebatan mengenai penarikan dana ...</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678469/galaxy-tab-s12-ultra-mejeng-di-geekbench-hadir-dengan-dimensity-9500</t>
+          <t>https://www.antaranews.com/berita/5678499/purbaya-pastikan-tak-ada-lagi-perdebatan-soal-penarikan-sal-dari-bank</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/InShot_20260803_215836626.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-23.02.47.jpeg</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Menteri PKP tegaskan KUR Perumahan perkuat ekonomi keluarga</t>
+          <t>Tim 9 Kejagung didesak usut pemilik uang-emas di rumah eks Jampidsus</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:47:11 +0700</t>
+          <t>Mon, 03 Aug 2026 23:10:43 +0700</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Menteri Perumahan dan Kawasan Permukiman (PKP) Maruarar Sirait menegaskan bahwa Kredit Usaha Rakyat (KUR) Perumahan ...</t>
+          <t>Tim 9 Kejaksaan Agung didesak mengusut tuntas pemilik uang tunai senilai Rp476 miliar dan emas batangan seberat 74 ...</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678465/menteri-pkp-tegaskan-kur-perumahan-perkuat-ekonomi-keluarga</t>
+          <t>https://www.antaranews.com/berita/5678495/tim-9-kejagung-didesak-usut-pemilik-uang-emas-di-rumah-eks-jampidsus</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1321013.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/1000175632.jpg</t>
         </is>
       </c>
     </row>
@@ -11621,61 +11621,61 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>TNBTS tutup sebagian akses Bromo imbas kebakaran hutan Blok Batengan</t>
+          <t>Kemenbud hadirkan GBN untuk membina talenta seni musik nasional</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:44:14 +0700</t>
+          <t>Mon, 03 Aug 2026 23:07:01 +0700</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Balai Besar Taman Nasional Bromo Tengger Semeru (TNBTS) menutup sebagian akses wisata Gunung Bromo dari pintu masuk ...</t>
+          <t>Kementerian Kebudayaan (Kemenbud) menghadirkan program pembinaan talenta seni musik nasional yang mempertemukan ...</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678457/tnbts-tutup-sebagian-akses-bromo-imbas-kebakaran-hutan-blok-batengan</t>
+          <t>https://www.antaranews.com/berita/5678491/kemenbud-hadirkan-gbn-untuk-membina-talenta-seni-musik-nasional</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001396577.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-20.28.05.jpeg</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>KPK hentikan penyidikan enam kasus, termasuk kasus Sekjen DPR</t>
+          <t>Wamen ATR: Ujian PPAT upaya berikan layanan yang baik</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:39:52 +0700</t>
+          <t>Mon, 03 Aug 2026 23:05:29 +0700</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Komisi Pemberantasan Korupsi (KPK) menghentikan penyidikan enam kasus dugaan tindak pidana korupsi dengan menerbitkan ...</t>
+          <t>Wakil Menteri Agraria dan Tata Ruang/Wakil Kepala Badan Pertanahan Nasional (Wamen ATR/Waka BPN) Ossy Dermawan ...</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678453/kpk-hentikan-penyidikan-enam-kasus-termasuk-kasus-sekjen-dpr</t>
+          <t>https://www.antaranews.com/berita/5678489/wamen-atr-ujian-ppat-upaya-berikan-layanan-yang-baik</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_8208.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_223512.jpg</t>
         </is>
       </c>
     </row>
@@ -11687,28 +11687,28 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Sekjen Golkar hingga eks Menpora bakal beri materi di Mubes Kosgoro</t>
+          <t>PBSI buka suara soal absennya Jafar/Felisha di Kejuaraan Dunia BWF</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:38:02 +0700</t>
+          <t>Mon, 03 Aug 2026 23:03:05 +0700</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Sekjen DPP Partai Golkar Muhammad Sarmuji hingga Menpora periode 2023-2025 Dito Ariotedjo akan memberikan materi dalam ...</t>
+          <t>Pengurus Pusat PBSI menyatakan absennya dua pasangan ganda campuran Indonesia Jafar Hidayatullah/Felisha Alberta ...</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678449/sekjen-golkar-hingga-eks-menpora-bakal-beri-materi-di-mubes-kosgoro</t>
+          <t>https://www.antaranews.com/berita/5678487/pbsi-buka-suara-soal-absennya-jafar-felisha-di-kejuaraan-dunia-bwf</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000469031.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/06/IMG_20251127_205351.jpg</t>
         </is>
       </c>
     </row>
@@ -11720,28 +11720,28 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Briket ampas kopi inovasi dosen UTU Meulaboh kantongi sertifikat paten</t>
+          <t>Presiden Prabowo terima kunjungan PM Thailand di Istana Merdeka</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:37:22 +0700</t>
+          <t>Mon, 03 Aug 2026 22:59:27 +0700</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Inovasi pengolahan limbah ampas kopi menjadi briket bahan bakar padat yang efisien karya Dosen Fakultas Pertanian ...</t>
+          <t>ANTARA - Presiden Prabowo Subianto menerima kunjungan resmi Perdana Menteri Thailand Anutin Charnvirakul di Istana ...</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678445/briket-ampas-kopi-inovasi-dosen-utu-meulaboh-kantongi-sertifikat-paten</t>
+          <t>https://www.antaranews.com/video/5678461/presiden-prabowo-terima-kunjungan-pm-thailand-di-istana-merdeka</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/20260803-briket-ampas-kopi-dosen-utu-meulaboh.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PRESIDEN-PRABOWO-TERIMA-KUNJUNGAN-PM-THAILAND-DI-ISTANA-MERDEKA.jpg</t>
         </is>
       </c>
     </row>
@@ -11753,28 +11753,28 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Indonesia-Thailand sepakat tingkatkan kerja sama pertahanan, keamanan</t>
+          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:35:28 +0700</t>
+          <t>Mon, 03 Aug 2026 22:58:38 +0700</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Presiden Republik Indonesia Prabowo Subianto dan Perdana Menteri (PM) Thailand Anutin Charnvirakul sepakat untuk ...</t>
+          <t>ANTARA - Badan Pencarian dan Pertolongan Nasional (Basarnas) mengerahkan satu unit kapal untuk menjemput 66 korban ...</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678443/indonesia-thailand-sepakat-tingkatkan-kerja-sama-pertahanan-keamanan</t>
+          <t>https://www.antaranews.com/video/5678472/basarnas-jemput-66-korban-km-mutiara-sentosa-ii-dari-masalembu</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/tempImageXOTgJY.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BASARNAS-JEMPUT-66-KORBAN-KM-MUTIARA-SENTOSA-II-DARI-MASALEMBU.jpg</t>
         </is>
       </c>
     </row>
@@ -11786,28 +11786,28 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Ekonom: Inflasi mereda, semester II jadi momentum jaga keseimbangan</t>
+          <t>Kementerian ATR/BPN telah terbitkan 124 ribu SK sertifikat rumah MBR</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:34:25 +0700</t>
+          <t>Mon, 03 Aug 2026 22:56:36 +0700</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Kepala Ekonom Trimegah Sekuritas Indonesia Fakhrul Fulvian menilai semester II-2026 menjadi momentum untuk menjaga ...</t>
+          <t>Kementerian Agraria dan Tata Ruang/Badan Pertanahan Nasional (ATR/BPN) menyatakan telah menerbitkan surat keputusan ...</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678439/ekonom-inflasi-mereda-semester-ii-jadi-momentum-jaga-keseimbangan</t>
+          <t>https://www.antaranews.com/berita/5678484/kementerian-atr-bpn-telah-terbitkan-124-ribu-sk-sertifikat-rumah-mbr</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/01/21/IMG_2637.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_224532.jpg</t>
         </is>
       </c>
     </row>
@@ -11819,61 +11819,61 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Kepala BGN: Putusan MK perkuat Program Makan Bergizi Gratis</t>
+          <t>Timnas Indonesia dibungkam Vietnam 0-3</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:32:37 +0700</t>
+          <t>Mon, 03 Aug 2026 22:54:01 +0700</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono mengatakan putusan Mahkamah Konstitusi (MK) Nomor 40/PUU-XXIV/2026 yang ...</t>
+          <t>Timnas Indonesia dibungkam Vietnam 0-3 di kandang pada laga lanjutan Grup A Piala AFF 2026 di Stadion Pakansari, Bogor, ...</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678436/kepala-bgn-putusan-mk-perkuat-program-makan-bergizi-gratis</t>
+          <t>https://www.antaranews.com/berita/5678480/timnas-indonesia-dibungkam-vietnam-0-3</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/189743.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Timnas-Indonesia-lawan-Vietnam-030826-Bay-21a.jpg</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>photo, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Piala AFF 2026 : Indonesia takluk 0-3 dari Vietnam</t>
+          <t>Prabowo-PM Thailand perkuat kemitraan strategis ASEAN</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:26:45 +0700</t>
+          <t>Mon, 03 Aug 2026 22:52:55 +0700</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Pelatih Timnas Indonesia Jhon Herdman memberikan arahan kepada anak didiknya saat melawan Timnas Vietnam pada ...</t>
+          <t>Presiden RI Prabowo Subianto dan Perdana Menteri (PM) Thailand Anutin Charnvirakul sepakat memperkuat kemitraan ...</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5678435/piala-aff-2026-indonesia-takluk-0-3-dari-vietnam</t>
+          <t>https://www.antaranews.com/berita/5678476/prabowo-pm-thailand-perkuat-kemitraan-strategis-asean</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Timnas-Indonesia-lawan-Vietnam-030826-Bay-11b.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_F6F7E006D3CC-1.jpeg</t>
         </is>
       </c>
     </row>
@@ -11885,127 +11885,127 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Banjir kepung 15 titik di Kota Padang akibat cuaca ekstrem</t>
+          <t>Galaxy Tab S12 Ultra mejeng di Geekbench, hadir dengan Dimensity 9500</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:25:29 +0700</t>
+          <t>Mon, 03 Aug 2026 22:48:03 +0700</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
-          <t>ANTARA - Hujan lebat disertai angin kencang memicu bencana di Kabupaten Agam, Kota Pariaman, dan Kota Padang, Sumatera ...</t>
+          <t>Samsung Galaxy Tab S12 Ultra dalam seri perangkat Galaxy Tab S12 yang diperkirakan dirilis September 2026 muncul di ...</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678396/banjir-kepung-15-titik-di-kota-padang-akibat-cuaca-ekstrem</t>
+          <t>https://www.antaranews.com/berita/5678469/galaxy-tab-s12-ultra-mejeng-di-geekbench-hadir-dengan-dimensity-9500</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BANJIR-KEPUNG-15-TITIK-DI-KOTA-PADANG-AKIBAT-CUACA-EKSTREM.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/InShot_20260803_215836626.jpg</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Pemkab Aceh Tenggara batasi pembelian BBM untuk cegah penimbunan</t>
+          <t>Prabowo terima tanda kehormatan dari Angkatan Bersenjata Thailand</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:25:13 +0700</t>
+          <t>Mon, 03 Aug 2026 20:59:35 +0700</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Pemerintah Kabupaten Aceh Tenggara bersama Forkopimda setempat saat ini telah melakukan pembatasan pembelian bahan ...</t>
+          <t>Presiden Prabowo Subianto menerima tanda kehormatan dari Angkatan Bersenjata Kerajaan Thailand yang diberikan pada saat ...</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678431/pemkab-aceh-tenggara-batasi-pembelian-bbm-untuk-cegah-penimbunan</t>
+          <t>https://www.antaranews.com/berita/5678283/prabowo-terima-tanda-kehormatan-dari-angkatan-bersenjata-thailand</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/20260803-Bupati-Aceh-Tenggara-HM-Salim-Fakhry.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/tempImageNOyDfK.jpg</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>MTI dorong kemudahan transaksi nirsentuh di MRT Jakarta</t>
+          <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:24:07 +0700</t>
+          <t>Mon, 03 Aug 2026 20:50:37 +0700</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
-          <t>PT Mitra Transaksi Indonesia (MTI) atau YOKKE mendukung penerapan sistem pembayaran kartu nirsentuh berbasis Europay, ...</t>
+          <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan ...</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678427/mti-dorong-kemudahan-transaksi-nirsentuh-di-mrt-jakarta</t>
+          <t>https://www.antaranews.com/video/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.59.08.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-finansial, top-news</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Erick ungkap strategi sebelum kembali ke bursa calon Ketum PSSI 2027</t>
+          <t>Menkeu: Eskalasi konflik Timteng dorong imbal hasil SBN ke 7,14 persen</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:22:41 +0700</t>
+          <t>Mon, 03 Aug 2026 20:48:02 +0700</t>
         </is>
       </c>
       <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr">
         <is>
-          <t>ANTARA - Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir tidak menutup kemungkinan untuk ...</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa mengatakan eskalasi konflik di Timur Tengah mendorong kenaikan imbal hasil Surat ...</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678327/erick-ungkap-strategi-sebelum-kembali-ke-bursa-calon-ketum-pssi-2027</t>
+          <t>https://www.antaranews.com/berita/5678253/menkeu-eskalasi-konflik-timteng-dorong-imbal-hasil-sbn-ke-714-persen</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/ERICK-UNGKAP-STRATEGI-SEBELUM-KEMBALI-KE-BURSA-CALON-KETUM-PSSI-2027.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-20.38.31.jpeg</t>
         </is>
       </c>
     </row>
@@ -12017,94 +12017,94 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Prabowo terima tanda kehormatan dari Angkatan Bersenjata Thailand</t>
+          <t>Prabowo dukung peningkatan latihan bersama militer RI-Thailand</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 20:59:35 +0700</t>
+          <t>Mon, 03 Aug 2026 19:21:32 +0700</t>
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Presiden Prabowo Subianto menerima tanda kehormatan dari Angkatan Bersenjata Kerajaan Thailand yang diberikan pada saat ...</t>
+          <t>Presiden Prabowo Subianto mendukung peningkatan frekuensi latihan bersama antara Tentara Nasional Indonesia (TNI) dan ...</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678283/prabowo-terima-tanda-kehormatan-dari-angkatan-bersenjata-thailand</t>
+          <t>https://www.antaranews.com/berita/5678081/prabowo-dukung-peningkatan-latihan-bersama-militer-ri-thailand</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/tempImageNOyDfK.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.41.07.jpeg</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-finansial, top-news</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
+          <t>OJK: Kredit perbankan tumbuh 12,67 persen capai Rp9.080,9 triliun</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 20:50:37 +0700</t>
+          <t>Mon, 03 Aug 2026 19:12:24 +0700</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr">
         <is>
-          <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan ...</t>
+          <t>Otoritas Jasa Keuangan (OJK) melaporkan penyaluran kredit perbankan di tanah air tumbuh 12,67 persen year on year ...</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
+          <t>https://www.antaranews.com/berita/5678057/ojk-kredit-perbankan-tumbuh-1267-persen-capai-rp90809-triliun</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.15.18_1.jpeg</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>ekonomi-finansial, top-news</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Menkeu: Eskalasi konflik Timteng dorong imbal hasil SBN ke 7,14 persen</t>
+          <t>Menkomdigi: KIP garda depan informasi jernih dan perangi hoaks</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 20:48:02 +0700</t>
+          <t>Mon, 03 Aug 2026 19:00:50 +0700</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa mengatakan eskalasi konflik di Timur Tengah mendorong kenaikan imbal hasil Surat ...</t>
+          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid mengatakan Komisi Informasi Pusat (KIP) menjadi garda terdepan ...</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678253/menkeu-eskalasi-konflik-timteng-dorong-imbal-hasil-sbn-ke-714-persen</t>
+          <t>https://www.antaranews.com/berita/5678033/menkomdigi-kip-garda-depan-informasi-jernih-dan-perangi-hoaks</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-20.38.31.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0321.jpg</t>
         </is>
       </c>
     </row>
@@ -12116,61 +12116,61 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Prabowo dukung peningkatan latihan bersama militer RI-Thailand</t>
+          <t>Satu tahun Sekolah Rakyat, ratusan siswa torehkan prestasi</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:21:32 +0700</t>
+          <t>Mon, 03 Aug 2026 18:59:25 +0700</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Presiden Prabowo Subianto mendukung peningkatan frekuensi latihan bersama antara Tentara Nasional Indonesia (TNI) dan ...</t>
+          <t>Menteri Sosial (Mensos) Saifullah Yusuf menyatakan selama satu tahun Sekolah Rakyat berdiri sudah ratusan ...</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678081/prabowo-dukung-peningkatan-latihan-bersama-militer-ri-thailand</t>
+          <t>https://www.antaranews.com/berita/5678024/satu-tahun-sekolah-rakyat-ratusan-siswa-torehkan-prestasi</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.41.07.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176441.jpg</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>ekonomi-finansial, top-news</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>OJK: Kredit perbankan tumbuh 12,67 persen capai Rp9.080,9 triliun</t>
+          <t>Menkeu: Realisasi anggaran MBG Rp101,1 T untuk 63,13 juta penerima</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:12:24 +0700</t>
+          <t>Mon, 03 Aug 2026 18:53:14 +0700</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Otoritas Jasa Keuangan (OJK) melaporkan penyaluran kredit perbankan di tanah air tumbuh 12,67 persen year on year ...</t>
+          <t>Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa mengungkapkan bahwa realisasi anggaran Program Makan Bergizi Gratis ...</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678057/ojk-kredit-perbankan-tumbuh-1267-persen-capai-rp90809-triliun</t>
+          <t>https://www.antaranews.com/berita/5678005/menkeu-realisasi-anggaran-mbg-rp1011-t-untuk-6313-juta-penerima</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.15.18_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29-2.jpeg</t>
         </is>
       </c>
     </row>
@@ -12182,28 +12182,28 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Menkomdigi: KIP garda depan informasi jernih dan perangi hoaks</t>
+          <t>Polri perkuat langkah preventif respons isu keamanan nasional</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:00:50 +0700</t>
+          <t>Mon, 03 Aug 2026 18:46:34 +0700</t>
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid mengatakan Komisi Informasi Pusat (KIP) menjadi garda terdepan ...</t>
+          <t>Polri memastikan terus memperkuat langkah preventif untuk menjaga keamanan nasional sehingga aktivitas masyarakat dan ...</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678033/menkomdigi-kip-garda-depan-informasi-jernih-dan-perangi-hoaks</t>
+          <t>https://www.antaranews.com/berita/5677985/polri-perkuat-langkah-preventif-respons-isu-keamanan-nasional</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0321.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/1000086556.jpg</t>
         </is>
       </c>
     </row>
@@ -12215,28 +12215,28 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Satu tahun Sekolah Rakyat, ratusan siswa torehkan prestasi</t>
+          <t>Prabowo dan PM Thailand bertemu empat mata di Istana Merdeka</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:59:25 +0700</t>
+          <t>Mon, 03 Aug 2026 17:49:52 +0700</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Menteri Sosial (Mensos) Saifullah Yusuf menyatakan selama satu tahun Sekolah Rakyat berdiri sudah ratusan ...</t>
+          <t>Presiden Prabowo Subianto dan Perdana Menteri Thailand Anutin Charnvirakul menggelar pertemuan empat mata di Istana ...</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678024/satu-tahun-sekolah-rakyat-ratusan-siswa-torehkan-prestasi</t>
+          <t>https://www.antaranews.com/berita/5677828/prabowo-dan-pm-thailand-bertemu-empat-mata-di-istana-merdeka</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176441.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_5162.jpeg</t>
         </is>
       </c>
     </row>
@@ -12248,28 +12248,29 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Menkeu: Realisasi anggaran MBG Rp101,1 T untuk 63,13 juta penerima</t>
+          <t>Kepala BGN tingkatkan status keracunan MBG jadi kejadian fatal</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:53:14 +0700</t>
+          <t>Mon, 03 Aug 2026 17:10:19 +0700</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa mengungkapkan bahwa realisasi anggaran Program Makan Bergizi Gratis ...</t>
+          <t>nya tidak dilanjutkan," ucap Sudaryono.
+Ia menegaskan BGN memberlakukan nol toleransi pada setiap status ...</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678005/menkeu-realisasi-anggaran-mbg-rp1011-t-untuk-6313-juta-penerima</t>
+          <t>https://www.antaranews.com/berita/5677743/kepala-bgn-tingkatkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29-2.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/ZAM02548_edit_2028523819372755.jpg</t>
         </is>
       </c>
     </row>
@@ -12281,28 +12282,28 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Polri perkuat langkah preventif respons isu keamanan nasional</t>
+          <t>Harga minyak turun usai AS siap lanjutkan dialog dengan Iran</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:46:34 +0700</t>
+          <t>Mon, 03 Aug 2026 17:08:35 +0700</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Polri memastikan terus memperkuat langkah preventif untuk menjaga keamanan nasional sehingga aktivitas masyarakat dan ...</t>
+          <t>Harga minyak turun lebih dari 5 persen, Senin, setelah Presiden Amerika Serikat Donald Trump ...</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677985/polri-perkuat-langkah-preventif-respons-isu-keamanan-nasional</t>
+          <t>https://www.antaranews.com/berita/5677735/harga-minyak-turun-usai-as-siap-lanjutkan-dialog-dengan-iran</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/1000086556.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/06/ilustrasi-isi-bensin-di-pom.jpg</t>
         </is>
       </c>
     </row>
@@ -12314,28 +12315,28 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Prabowo dan PM Thailand bertemu empat mata di Istana Merdeka</t>
+          <t>Australia konfirmasi kematian massal pertama satwa akibat flu burung</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 17:49:52 +0700</t>
+          <t>Mon, 03 Aug 2026 16:48:50 +0700</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Presiden Prabowo Subianto dan Perdana Menteri Thailand Anutin Charnvirakul menggelar pertemuan empat mata di Istana ...</t>
+          <t>Australia mengonfirmasi kematian massal satwa liar pertama terkait flu burung H5 yang mematikan, dengan burung camar ...</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677828/prabowo-dan-pm-thailand-bertemu-empat-mata-di-istana-merdeka</t>
+          <t>https://www.antaranews.com/berita/5677701/australia-konfirmasi-kematian-massal-pertama-satwa-akibat-flu-burung</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_5162.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/26/Virus-flu-burung-penyakit-unggas.jpg</t>
         </is>
       </c>
     </row>
@@ -12347,62 +12348,61 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Kepala BGN tingkatkan status keracunan MBG jadi kejadian fatal</t>
+          <t>Siklon 94 W,  waspada cuaca ekstrem &amp; gelombang tinggi di wilayah RI</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 17:10:19 +0700</t>
+          <t>Mon, 03 Aug 2026 16:30:38 +0700</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr">
         <is>
-          <t>nya tidak dilanjutkan," ucap Sudaryono.
-Ia menegaskan BGN memberlakukan nol toleransi pada setiap status ...</t>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) mendeteksi pergerakan Bibit Siklon Tropis 94W di Laut Filipina ...</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677743/kepala-bgn-tingkatkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+          <t>https://www.antaranews.com/berita/5677641/siklon-94-w-waspada-cuaca-ekstrem-gelombang-tinggi-di-wilayah-ri</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/ZAM02548_edit_2028523819372755.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/27/1000395034.jpg</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>photo, top-news</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Harga minyak turun usai AS siap lanjutkan dialog dengan Iran</t>
+          <t>Petani berbagi air sumur demi selamatkan tanaman tembakau</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 17:08:35 +0700</t>
+          <t>Mon, 03 Aug 2026 14:44:51 +0700</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Harga minyak turun lebih dari 5 persen, Senin, setelah Presiden Amerika Serikat Donald Trump ...</t>
+          <t>Petani mengambil air dari sumur untuk menyiram tanaman tembakau di Lengkong, Nganjuk, Jawa Timur, Senin (3/8/2026). ...</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677735/harga-minyak-turun-usai-as-siap-lanjutkan-dialog-dengan-iran</t>
+          <t>https://www.antaranews.com/foto/5677428/petani-berbagi-air-sumur-demi-selamatkan-tanaman-tembakau</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/06/ilustrasi-isi-bensin-di-pom.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/petani-tembakau-berbagi-air-sumur-antisipasi-dampak-el-nino-030826-mm-1.jpg</t>
         </is>
       </c>
     </row>
@@ -12414,28 +12414,28 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Australia konfirmasi kematian massal pertama satwa akibat flu burung</t>
+          <t>Nusron sebut banyak laut di Batam telah dikapling tanpa prosedur sah</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:48:50 +0700</t>
+          <t>Mon, 03 Aug 2026 14:44:05 +0700</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Australia mengonfirmasi kematian massal satwa liar pertama terkait flu burung H5 yang mematikan, dengan burung camar ...</t>
+          <t>Menteri Agraria dan Tata Ruang (ATR)/Kepala Badan Pertanahan Nasional (BPN) Nusron Wahid mengatakan, menerima banyak ...</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677701/australia-konfirmasi-kematian-massal-pertama-satwa-akibat-flu-burung</t>
+          <t>https://www.antaranews.com/berita/5677425/nusron-sebut-banyak-laut-di-batam-telah-dikapling-tanpa-prosedur-sah</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/26/Virus-flu-burung-penyakit-unggas.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_142345.jpg</t>
         </is>
       </c>
     </row>
@@ -12447,61 +12447,61 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Siklon 94 W,  waspada cuaca ekstrem &amp; gelombang tinggi di wilayah RI</t>
+          <t>Menkomdigi panggil YouTube imbas temuan konten promosi vape sasar anak</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:30:38 +0700</t>
+          <t>Mon, 03 Aug 2026 14:22:09 +0700</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) mendeteksi pergerakan Bibit Siklon Tropis 94W di Laut Filipina ...</t>
+          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid merencanakan pemanggilan terhadap platform digital YouTube ...</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677641/siklon-94-w-waspada-cuaca-ekstrem-gelombang-tinggi-di-wilayah-ri</t>
+          <t>https://www.antaranews.com/berita/5677396/menkomdigi-panggil-youtube-imbas-temuan-konten-promosi-vape-sasar-anak</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/27/1000395034.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0225.jpg</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>photo, top-news</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Petani berbagi air sumur demi selamatkan tanaman tembakau</t>
+          <t>Kemnaker: Magang Nasional diharapkan menekan angka pengangguran muda</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:44:51 +0700</t>
+          <t>Mon, 03 Aug 2026 13:37:57 +0700</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Petani mengambil air dari sumur untuk menyiram tanaman tembakau di Lengkong, Nganjuk, Jawa Timur, Senin (3/8/2026). ...</t>
+          <t>Kementerian Ketenagakerjaan (Kemnaker) mengatakan program Magang Nasional (MagangHub) untuk mempersiapkan kompetensi ...</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5677428/petani-berbagi-air-sumur-demi-selamatkan-tanaman-tembakau</t>
+          <t>https://www.antaranews.com/berita/5677364/kemnaker-magang-nasional-diharapkan-menekan-angka-pengangguran-muda</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/petani-tembakau-berbagi-air-sumur-antisipasi-dampak-el-nino-030826-mm-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/ff63afaf-7778-47fe-833d-5a8068af9a51_1.jpeg</t>
         </is>
       </c>
     </row>
@@ -12513,28 +12513,28 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Nusron sebut banyak laut di Batam telah dikapling tanpa prosedur sah</t>
+          <t>Kemenag perkuat transformasi madrasah lewat revitalisasi-digitalisasi</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:44:05 +0700</t>
+          <t>Mon, 03 Aug 2026 13:36:36 +0700</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Menteri Agraria dan Tata Ruang (ATR)/Kepala Badan Pertanahan Nasional (BPN) Nusron Wahid mengatakan, menerima banyak ...</t>
+          <t>Menteri Agama (Menag) Nasaruddin Umar menegaskan transformasi madrasah terus diperkuat melalui revitalisasi ...</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677425/nusron-sebut-banyak-laut-di-batam-telah-dikapling-tanpa-prosedur-sah</t>
+          <t>https://www.antaranews.com/berita/5677363/kemenag-perkuat-transformasi-madrasah-lewat-revitalisasi-digitalisasi</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_142345.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/14/1000173935_1.jpg</t>
         </is>
       </c>
     </row>
@@ -12546,28 +12546,28 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Menkomdigi panggil YouTube imbas temuan konten promosi vape sasar anak</t>
+          <t>Lisensi IP Global Buka Peluang Bisnis Baru bagi Kreator Indonesia</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:22:09 +0700</t>
+          <t>Mon, 03 Aug 2026 13:34:30 +0700</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid merencanakan pemanggilan terhadap platform digital YouTube ...</t>
+          <t>Wakil Menteri Ekonomi Kreatif Irene Umar mengatakan kolaborasi antara pemilik kekayaan intelektual (Intellectual ...</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677396/menkomdigi-panggil-youtube-imbas-temuan-konten-promosi-vape-sasar-anak</t>
+          <t>https://www.antaranews.com/berita/5677353/lisensi-ip-global-buka-peluang-bisnis-baru-bagi-kreator-indonesia</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0225.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000589873.jpg</t>
         </is>
       </c>
     </row>
@@ -12579,28 +12579,28 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Kemnaker: Magang Nasional diharapkan menekan angka pengangguran muda</t>
+          <t>Nilai ekspor perdagangan RI Januari-Juni capai 140,81 miliar dolar AS</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:37:57 +0700</t>
+          <t>Mon, 03 Aug 2026 13:16:17 +0700</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Kementerian Ketenagakerjaan (Kemnaker) mengatakan program Magang Nasional (MagangHub) untuk mempersiapkan kompetensi ...</t>
+          <t>Badan Pusat Statistik (BPS) mencatat nilai ekspor Indonesia secara kumulatif dari Januari-Juni 2026 mencapai 140,81 ...</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677364/kemnaker-magang-nasional-diharapkan-menekan-angka-pengangguran-muda</t>
+          <t>https://www.antaranews.com/berita/5677315/nilai-ekspor-perdagangan-ri-januari-juni-capai-14081-miliar-dolar-as</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/ff63afaf-7778-47fe-833d-5a8068af9a51_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/neraca-perdagangan-januari-mei-2026-surplus-2815779.jpg</t>
         </is>
       </c>
     </row>
@@ -12612,28 +12612,28 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Kemenag perkuat transformasi madrasah lewat revitalisasi-digitalisasi</t>
+          <t>Korban KMP Mutiara Sentosa II dievakuasi ke Pelabuhan Tanjung Perak</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:36:36 +0700</t>
+          <t>Mon, 03 Aug 2026 13:06:15 +0700</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Menteri Agama (Menag) Nasaruddin Umar menegaskan transformasi madrasah terus diperkuat melalui revitalisasi ...</t>
+          <t>Tim SAR gabungan terus melakukan evakuasi korban terbakarnya KMP Mutiara Sentosa 2 ke darat, tepatnya ke Pelabuhan ...</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677363/kemenag-perkuat-transformasi-madrasah-lewat-revitalisasi-digitalisasi</t>
+          <t>https://www.antaranews.com/berita/5677297/korban-kmp-mutiara-sentosa-ii-dievakuasi-ke-pelabuhan-tanjung-perak</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/14/1000173935_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/260821_1.jpg</t>
         </is>
       </c>
     </row>
@@ -12645,28 +12645,28 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Lisensi IP Global Buka Peluang Bisnis Baru bagi Kreator Indonesia</t>
+          <t>Aktor senior Diding Boneng meninggal dunia</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:34:30 +0700</t>
+          <t>Mon, 03 Aug 2026 11:39:03 +0700</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Wakil Menteri Ekonomi Kreatif Irene Umar mengatakan kolaborasi antara pemilik kekayaan intelektual (Intellectual ...</t>
+          <t>Aktor sekaligus komedian tanah air, Zainal Abidin alias Diding Boneng dikabarkan meninggal dunia pada Senin (3/8) dalam ...</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677353/lisensi-ip-global-buka-peluang-bisnis-baru-bagi-kreator-indonesia</t>
+          <t>https://www.antaranews.com/berita/5677209/aktor-senior-diding-boneng-meninggal-dunia</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000589873.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/26f1eb88-3301-4ae1-badd-bed5078fe3dd.jpeg</t>
         </is>
       </c>
     </row>
@@ -12678,28 +12678,28 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Nilai ekspor perdagangan RI Januari-Juni capai 140,81 miliar dolar AS</t>
+          <t>Seskab: Prabowo dorong sinergi pemerintah dan dunia usaha</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:16:17 +0700</t>
+          <t>Mon, 03 Aug 2026 11:17:50 +0700</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat nilai ekspor Indonesia secara kumulatif dari Januari-Juni 2026 mencapai 140,81 ...</t>
+          <t>Sekretaris Kabinet Teddy Indra Wijaya menyampaikan bahwa Presiden Prabowo Subianto menekankan pentingnya sinergi antara ...</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677315/nilai-ekspor-perdagangan-ri-januari-juni-capai-14081-miliar-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5677191/seskab-prabowo-dorong-sinergi-pemerintah-dan-dunia-usaha</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/neraca-perdagangan-januari-mei-2026-surplus-2815779.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0891_1.jpeg</t>
         </is>
       </c>
     </row>
@@ -12711,28 +12711,28 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Korban KMP Mutiara Sentosa II dievakuasi ke Pelabuhan Tanjung Perak</t>
+          <t>Red Velvet bersiap kembali lewat EP baru "Velvet Summer"</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:06:15 +0700</t>
+          <t>Mon, 03 Aug 2026 10:24:37 +0700</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Tim SAR gabungan terus melakukan evakuasi korban terbakarnya KMP Mutiara Sentosa 2 ke darat, tepatnya ke Pelabuhan ...</t>
+          <t>Grup idola K-pop Red Velvet akan kembali lewat rilis mini album atau extended play (EP) baru bertajuk “Velvet ...</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677297/korban-kmp-mutiara-sentosa-ii-dievakuasi-ke-pelabuhan-tanjung-perak</t>
+          <t>https://www.antaranews.com/berita/5677151/red-velvet-bersiap-kembali-lewat-ep-baru-velvet-summer</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/260821_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/ca97a3a8-aa17-45fc-be71-d36051dd9dcd.jpeg</t>
         </is>
       </c>
     </row>
@@ -12744,28 +12744,28 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Aktor senior Diding Boneng meninggal dunia</t>
+          <t>Menaker pastikan komitmen pemerintah perkuat kesejahteraan pekerja</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:39:03 +0700</t>
+          <t>Mon, 03 Aug 2026 10:16:19 +0700</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Aktor sekaligus komedian tanah air, Zainal Abidin alias Diding Boneng dikabarkan meninggal dunia pada Senin (3/8) dalam ...</t>
+          <t>Menteri Ketenagakerjaan (Menaker) Yassierli memastikan pemerintah berkomitmen untuk memperkuat kesejahteraan, ...</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677209/aktor-senior-diding-boneng-meninggal-dunia</t>
+          <t>https://www.antaranews.com/berita/5677148/menaker-pastikan-komitmen-pemerintah-perkuat-kesejahteraan-pekerja</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/26f1eb88-3301-4ae1-badd-bed5078fe3dd.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/09/20/pelepasan-peserta-pemagangan-ke-jepang-di-jawa-barat-2627513.jpg</t>
         </is>
       </c>
     </row>
@@ -12777,28 +12777,28 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Seskab: Prabowo dorong sinergi pemerintah dan dunia usaha</t>
+          <t>23 calon hakim agung dan ad hoc ikuti seleksi wawancara akhir</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:17:50 +0700</t>
+          <t>Mon, 03 Aug 2026 10:15:01 +0700</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Sekretaris Kabinet Teddy Indra Wijaya menyampaikan bahwa Presiden Prabowo Subianto menekankan pentingnya sinergi antara ...</t>
+          <t>Sebanyak 23 orang calon hakim agung dan ad hoc Mahkamah Agung Tahun 2026 mengikuti seleksi wawancara tahap akhir di ...</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677191/seskab-prabowo-dorong-sinergi-pemerintah-dan-dunia-usaha</t>
+          <t>https://www.antaranews.com/berita/5677137/23-calon-hakim-agung-dan-ad-hoc-ikuti-seleksi-wawancara-akhir</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0891_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000012883_1.jpg</t>
         </is>
       </c>
     </row>
@@ -12810,28 +12810,28 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Red Velvet bersiap kembali lewat EP baru "Velvet Summer"</t>
+          <t>BRIN perkuat kajian sungai bawah tanah di Kebumen untuk ketahanan air</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:24:37 +0700</t>
+          <t>Mon, 03 Aug 2026 09:57:19 +0700</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Grup idola K-pop Red Velvet akan kembali lewat rilis mini album atau extended play (EP) baru bertajuk “Velvet ...</t>
+          <t>Badan Riset dan Inovasi Nasional (BRIN) memperkuat riset ketahanan air melalui pengembangan teknologi dan penelitian ...</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677151/red-velvet-bersiap-kembali-lewat-ep-baru-velvet-summer</t>
+          <t>https://www.antaranews.com/berita/5677120/brin-perkuat-kajian-sungai-bawah-tanah-di-kebumen-untuk-ketahanan-air</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/ca97a3a8-aa17-45fc-be71-d36051dd9dcd.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1785706440-47672950-1.jpg</t>
         </is>
       </c>
     </row>
@@ -12843,28 +12843,28 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Menaker pastikan komitmen pemerintah perkuat kesejahteraan pekerja</t>
+          <t>Harga bensin turun pada pekan pertama Agustus</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:16:19 +0700</t>
+          <t>Mon, 03 Aug 2026 09:51:00 +0700</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Menteri Ketenagakerjaan (Menaker) Yassierli memastikan pemerintah berkomitmen untuk memperkuat kesejahteraan, ...</t>
+          <t>Harga bahan bakar minyak (BBM) jenis bensin di stasiun pengisian bahan bakar umum (SPBU) Pertamina, Shell, dan bp ...</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677148/menaker-pastikan-komitmen-pemerintah-perkuat-kesejahteraan-pekerja</t>
+          <t>https://www.antaranews.com/berita/5677109/harga-bensin-turun-pada-pekan-pertama-agustus</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/09/20/pelepasan-peserta-pemagangan-ke-jepang-di-jawa-barat-2627513.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/10/02/penuruanan-harga-bbm-011024-aaa-7.jpg</t>
         </is>
       </c>
     </row>
@@ -12876,127 +12876,127 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>23 calon hakim agung dan ad hoc ikuti seleksi wawancara akhir</t>
+          <t>Sean Gelael berbagi pengalaman di dunia balap ke pengunjung GIIAS 2026</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:15:01 +0700</t>
+          <t>Mon, 03 Aug 2026 09:34:53 +0700</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Sebanyak 23 orang calon hakim agung dan ad hoc Mahkamah Agung Tahun 2026 mengikuti seleksi wawancara tahap akhir di ...</t>
+          <t>Pembalap Indonesia Sean Gelael berbagi pengalamannya di dunia balap ke pengunjung GAIKINDO Indonesia International ...</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677137/23-calon-hakim-agung-dan-ad-hoc-ikuti-seleksi-wawancara-akhir</t>
+          <t>https://www.antaranews.com/berita/5677103/sean-gelael-berbagi-pengalaman-di-dunia-balap-ke-pengunjung-giias-2026</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000012883_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/16b70b87-326f-479a-a806-580ab846cc6f_1.jpeg</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>BRIN perkuat kajian sungai bawah tanah di Kebumen untuk ketahanan air</t>
+          <t>Cadangan devisa RI jadi 145 M dolar AS, BI sebut masih di level aman</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:57:19 +0700</t>
+          <t>Mon, 03 Aug 2026 21:52:44 +0700</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Badan Riset dan Inovasi Nasional (BRIN) memperkuat riset ketahanan air melalui pengembangan teknologi dan penelitian ...</t>
+          <t>ANTARA - Bank Indonesia (BI) mengungkapkan cadangan devisa pada akhir Juli 2026 berada di posisi 145 miliar dolar AS. ...</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677120/brin-perkuat-kajian-sungai-bawah-tanah-di-kebumen-untuk-ketahanan-air</t>
+          <t>https://www.antaranews.com/video/5678347/cadangan-devisa-ri-jadi-145-m-dolar-as-bi-sebut-masih-di-level-aman</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1785706440-47672950-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_CADANGAN-DEVISA-RI-JADI-145-M-DOLAR-AS-BI-SEBUT-MASIH-DI-LEVEL-AMAN.jpg</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Harga bensin turun pada pekan pertama Agustus</t>
+          <t>BI: Inflasi Juli terjaga berkat sinergi bank sentral dan pemerintah</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:51:00 +0700</t>
+          <t>Mon, 03 Aug 2026 21:51:39 +0700</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Harga bahan bakar minyak (BBM) jenis bensin di stasiun pengisian bahan bakar umum (SPBU) Pertamina, Shell, dan bp ...</t>
+          <t>Bank Indonesia (BI) memandang inflasi Indeks Harga Konsumen (IHK) pada Juli 2026 tetap terjaga dalam sasaran target, ...</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677109/harga-bensin-turun-pada-pekan-pertama-agustus</t>
+          <t>https://www.antaranews.com/berita/5678380/bi-inflasi-juli-terjaga-berkat-sinergi-bank-sentral-dan-pemerintah</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/10/02/penuruanan-harga-bbm-011024-aaa-7.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/07/WhatsApp-Image-2026-07-07-at-14.31.59_edited.jpg</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Sean Gelael berbagi pengalaman di dunia balap ke pengunjung GIIAS 2026</t>
+          <t>BI: Kepemilikan SRBI oleh bank guna kelola likuiditas, bukan investasi</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:34:53 +0700</t>
+          <t>Mon, 03 Aug 2026 21:35:49 +0700</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Pembalap Indonesia Sean Gelael berbagi pengalamannya di dunia balap ke pengunjung GAIKINDO Indonesia International ...</t>
+          <t>Bank Indonesia (BI) menegaskan bahwa Sekuritas Rupiah Bank Indonesia (SRBI) ditujukan sebagai instrumen pengelolaan ...</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677103/sean-gelael-berbagi-pengalaman-di-dunia-balap-ke-pengunjung-giias-2026</t>
+          <t>https://www.antaranews.com/berita/5678351/bi-kepemilikan-srbi-oleh-bank-guna-kelola-likuiditas-bukan-investasi</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/16b70b87-326f-479a-a806-580ab846cc6f_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-21.22.00.jpeg</t>
         </is>
       </c>
     </row>
@@ -13008,28 +13008,28 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Cadangan devisa RI jadi 145 M dolar AS, BI sebut masih di level aman</t>
+          <t>KSSK prakirakan pertumbuhan ekonomi RI pada 2026 capai 5,6-6 persen</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:52:44 +0700</t>
+          <t>Mon, 03 Aug 2026 18:28:16 +0700</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr">
         <is>
-          <t>ANTARA - Bank Indonesia (BI) mengungkapkan cadangan devisa pada akhir Juli 2026 berada di posisi 145 miliar dolar AS. ...</t>
+          <t>Komite Stabilitas Sistem Keuangan (KSSK) memprakirakan ekonomi Indonesia sepanjang 2026 tumbuh dalam kisaran ...</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678347/cadangan-devisa-ri-jadi-145-m-dolar-as-bi-sebut-masih-di-level-aman</t>
+          <t>https://www.antaranews.com/berita/5677935/kssk-prakirakan-pertumbuhan-ekonomi-ri-pada-2026-capai-56-6-persen</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_CADANGAN-DEVISA-RI-JADI-145-M-DOLAR-AS-BI-SEBUT-MASIH-DI-LEVEL-AMAN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.19.55.jpeg</t>
         </is>
       </c>
     </row>
@@ -13041,28 +13041,28 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>BI: Inflasi Juli terjaga berkat sinergi bank sentral dan pemerintah</t>
+          <t>Rupiah menguat dipengaruhi PMI manufaktur Indonesia naik jadi 50,2</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:51:39 +0700</t>
+          <t>Mon, 03 Aug 2026 16:58:46 +0700</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Bank Indonesia (BI) memandang inflasi Indeks Harga Konsumen (IHK) pada Juli 2026 tetap terjaga dalam sasaran target, ...</t>
+          <t>Nilai tukar rupiah terhadap dolar AS pada penutupan perdagangan Senin, bergerak menguat 25 poin atau 0,14 persen ...</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678380/bi-inflasi-juli-terjaga-berkat-sinergi-bank-sentral-dan-pemerintah</t>
+          <t>https://www.antaranews.com/berita/5677712/rupiah-menguat-dipengaruhi-pmi-manufaktur-indonesia-naik-jadi-502</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/07/WhatsApp-Image-2026-07-07-at-14.31.59_edited.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/12/nilai-tukar-rupiah-melemah-115-poin-2788415.jpg</t>
         </is>
       </c>
     </row>
@@ -13074,28 +13074,28 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>BI: Kepemilikan SRBI oleh bank guna kelola likuiditas, bukan investasi</t>
+          <t>KSSK: Sistem keuangan TW-II tetap terjaga di tengah konflik geopolitik</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:35:49 +0700</t>
+          <t>Mon, 03 Aug 2026 16:26:03 +0700</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Bank Indonesia (BI) menegaskan bahwa Sekuritas Rupiah Bank Indonesia (SRBI) ditujukan sebagai instrumen pengelolaan ...</t>
+          <t>Komite Stabilitas Sistem Keuangan (KSSK) menilai kondisi fiskal, moneter dan sektor keuangan selama triwulan II 2026 ...</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678351/bi-kepemilikan-srbi-oleh-bank-guna-kelola-likuiditas-bukan-investasi</t>
+          <t>https://www.antaranews.com/berita/5677625/kssk-sistem-keuangan-tw-ii-tetap-terjaga-di-tengah-konflik-geopolitik</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-21.22.00.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29.jpeg</t>
         </is>
       </c>
     </row>
@@ -13107,28 +13107,28 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>KSSK prakirakan pertumbuhan ekonomi RI pada 2026 capai 5,6-6 persen</t>
+          <t>Menjaga pintu air perekonomian Indonesia</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:28:16 +0700</t>
+          <t>Mon, 03 Aug 2026 16:04:40 +0700</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Komite Stabilitas Sistem Keuangan (KSSK) memprakirakan ekonomi Indonesia sepanjang 2026 tumbuh dalam kisaran ...</t>
+          <t>Bayangkan perekonomian Indonesia sebagai sebuah bendungan raksasa yang mengairi hamparan persawahan. Air yang mengalir ...</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677935/kssk-prakirakan-pertumbuhan-ekonomi-ri-pada-2026-capai-56-6-persen</t>
+          <t>https://www.antaranews.com/berita/5677565/menjaga-pintu-air-perekonomian-indonesia</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.19.55.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/06/peringati-hari-bank-indonesia-doku-perkuat-ekosistem-pembayaran-2817675.jpg</t>
         </is>
       </c>
     </row>
@@ -13140,28 +13140,28 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Rupiah menguat dipengaruhi PMI manufaktur Indonesia naik jadi 50,2</t>
+          <t>Rupiah diperkirakan menguat seiring AS batalkan rencana serang Iran</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:58:46 +0700</t>
+          <t>Mon, 03 Aug 2026 10:12:26 +0700</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Nilai tukar rupiah terhadap dolar AS pada penutupan perdagangan Senin, bergerak menguat 25 poin atau 0,14 persen ...</t>
+          <t>Analis Doo Financial Futures, Lukman Leong memperkirakan rupiah menguat seiring Amerika Serikat (AS) membatalkan ...</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677712/rupiah-menguat-dipengaruhi-pmi-manufaktur-indonesia-naik-jadi-502</t>
+          <t>https://www.antaranews.com/berita/5677132/rupiah-diperkirakan-menguat-seiring-as-batalkan-rencana-serang-iran</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/12/nilai-tukar-rupiah-melemah-115-poin-2788415.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828847.jpg</t>
         </is>
       </c>
     </row>
@@ -13173,28 +13173,28 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>KSSK: Sistem keuangan TW-II tetap terjaga di tengah konflik geopolitik</t>
+          <t>Rupiah pada Senin pagi melemah jadi Rp18.031 per dolar AS</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:26:03 +0700</t>
+          <t>Mon, 03 Aug 2026 09:05:50 +0700</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Komite Stabilitas Sistem Keuangan (KSSK) menilai kondisi fiskal, moneter dan sektor keuangan selama triwulan II 2026 ...</t>
+          <t>Nilai tukar rupiah pada Senin pagi bergerak melemah 9 poin atau 0,05 persen menjadi Rp18.031 per dolar AS dibandingkan ...</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677625/kssk-sistem-keuangan-tw-ii-tetap-terjaga-di-tengah-konflik-geopolitik</t>
+          <t>https://www.antaranews.com/berita/5677063/rupiah-pada-senin-pagi-melemah-jadi-rp18031-per-dolar-as</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
         </is>
       </c>
     </row>
@@ -13206,28 +13206,28 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Menjaga pintu air perekonomian Indonesia</t>
+          <t>Komisi XI: PFII peluang RI tangkap momentum perpindahan modal global</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:04:40 +0700</t>
+          <t>Mon, 03 Aug 2026 06:53:34 +0700</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Bayangkan perekonomian Indonesia sebagai sebuah bendungan raksasa yang mengairi hamparan persawahan. Air yang mengalir ...</t>
+          <t>Wakil Ketua Komisi XI DPR RI Mohamad Hekal mengatakan percepatan pembentukan Pusat Finansial Internasional Indonesia ...</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677565/menjaga-pintu-air-perekonomian-indonesia</t>
+          <t>https://www.antaranews.com/berita/5676995/komisi-xi-pfii-peluang-ri-tangkap-momentum-perpindahan-modal-global</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/06/peringati-hari-bank-indonesia-doku-perkuat-ekosistem-pembayaran-2817675.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Saham-dan-oblogasi.jpg</t>
         </is>
       </c>
     </row>
@@ -13239,127 +13239,127 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Rupiah diperkirakan menguat seiring AS batalkan rencana serang Iran</t>
+          <t>BUMA International Group bukukan pertumbuhan EBITDA semester I/2026</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:12:26 +0700</t>
+          <t>Mon, 03 Aug 2026 06:17:40 +0700</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Analis Doo Financial Futures, Lukman Leong memperkirakan rupiah menguat seiring Amerika Serikat (AS) membatalkan ...</t>
+          <t>PT BUMA Internasional Gorup membukukan pertumbuhan EBITDA pada semester pertama 2026 (1H26) di tengah penurunan ...</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677132/rupiah-diperkirakan-menguat-seiring-as-batalkan-rencana-serang-iran</t>
+          <t>https://www.antaranews.com/berita/5676967/buma-international-group-bukukan-pertumbuhan-ebitda-semester-i-2026</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828847.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/buma.jpg</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Rupiah pada Senin pagi melemah jadi Rp18.031 per dolar AS</t>
+          <t>Menteri PKP tegaskan KUR Perumahan perkuat ekonomi keluarga</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:05:50 +0700</t>
+          <t>Mon, 03 Aug 2026 22:47:11 +0700</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Nilai tukar rupiah pada Senin pagi bergerak melemah 9 poin atau 0,05 persen menjadi Rp18.031 per dolar AS dibandingkan ...</t>
+          <t>Menteri Perumahan dan Kawasan Permukiman (PKP) Maruarar Sirait menegaskan bahwa Kredit Usaha Rakyat (KUR) Perumahan ...</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677063/rupiah-pada-senin-pagi-melemah-jadi-rp18031-per-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5678465/menteri-pkp-tegaskan-kur-perumahan-perkuat-ekonomi-keluarga</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1321013.jpg</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Komisi XI: PFII peluang RI tangkap momentum perpindahan modal global</t>
+          <t>Ekonom: Inflasi mereda, semester II jadi momentum jaga keseimbangan</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:53:34 +0700</t>
+          <t>Mon, 03 Aug 2026 22:34:25 +0700</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Wakil Ketua Komisi XI DPR RI Mohamad Hekal mengatakan percepatan pembentukan Pusat Finansial Internasional Indonesia ...</t>
+          <t>Kepala Ekonom Trimegah Sekuritas Indonesia Fakhrul Fulvian menilai semester II-2026 menjadi momentum untuk menjaga ...</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676995/komisi-xi-pfii-peluang-ri-tangkap-momentum-perpindahan-modal-global</t>
+          <t>https://www.antaranews.com/berita/5678439/ekonom-inflasi-mereda-semester-ii-jadi-momentum-jaga-keseimbangan</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Saham-dan-oblogasi.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/01/21/IMG_2637.jpeg</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>BUMA International Group bukukan pertumbuhan EBITDA semester I/2026</t>
+          <t>Pemkab Aceh Tenggara batasi pembelian BBM untuk cegah penimbunan</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:17:40 +0700</t>
+          <t>Mon, 03 Aug 2026 22:25:13 +0700</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr">
         <is>
-          <t>PT BUMA Internasional Gorup membukukan pertumbuhan EBITDA pada semester pertama 2026 (1H26) di tengah penurunan ...</t>
+          <t>Pemerintah Kabupaten Aceh Tenggara bersama Forkopimda setempat saat ini telah melakukan pembatasan pembelian bahan ...</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676967/buma-international-group-bukukan-pertumbuhan-ebitda-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5678431/pemkab-aceh-tenggara-batasi-pembelian-bbm-untuk-cegah-penimbunan</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/buma.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/20260803-Bupati-Aceh-Tenggara-HM-Salim-Fakhry.jpeg</t>
         </is>
       </c>
     </row>
@@ -13371,28 +13371,28 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Gubernur tegaskan Sumut siap jadi pusat fashion Indonesia lewat wastra</t>
+          <t>MTI dorong kemudahan transaksi nirsentuh di MRT Jakarta</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:37:04 +0700</t>
+          <t>Mon, 03 Aug 2026 22:24:07 +0700</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Gubernur Sumatera Utara (Sumut) Bobby Nasution menegaskan kesiapan Provinsi Sumut menjadi salah satu pusat fashion ...</t>
+          <t>PT Mitra Transaksi Indonesia (MTI) atau YOKKE mendukung penerapan sistem pembayaran kartu nirsentuh berbasis Europay, ...</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678355/gubernur-tegaskan-sumut-siap-jadi-pusat-fashion-indonesia-lewat-wastra</t>
+          <t>https://www.antaranews.com/berita/5678427/mti-dorong-kemudahan-transaksi-nirsentuh-di-mrt-jakarta</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001029105.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.59.08.jpeg</t>
         </is>
       </c>
     </row>
@@ -13404,28 +13404,28 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Kapal BBM bermuatan 7.600 kiloliter masuk Lombok</t>
+          <t>Gubernur tegaskan Sumut siap jadi pusat fashion Indonesia lewat wastra</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:32:28 +0700</t>
+          <t>Mon, 03 Aug 2026 21:37:04 +0700</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr">
         <is>
-          <t>PT Pertamina Patra Niaga mendatangkan kapal pengangkut bahan bakar minyak (BBM) dengan total muatan 7.600 kiloliter ...</t>
+          <t>Gubernur Sumatera Utara (Sumut) Bobby Nasution menegaskan kesiapan Provinsi Sumut menjadi salah satu pusat fashion ...</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678341/kapal-bbm-bermuatan-7600-kiloliter-masuk-lombok</t>
+          <t>https://www.antaranews.com/berita/5678355/gubernur-tegaskan-sumut-siap-jadi-pusat-fashion-indonesia-lewat-wastra</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001432720.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001029105.jpg</t>
         </is>
       </c>
     </row>
@@ -13437,28 +13437,28 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Whoosh-kereta api dominasi jalur masuk wisatawan mancanegara di Jabar</t>
+          <t>Kapal BBM bermuatan 7.600 kiloliter masuk Lombok</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:28:59 +0700</t>
+          <t>Mon, 03 Aug 2026 21:32:28 +0700</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Integrasi transportasi berbasis rel seperti Kereta Cepat Whoosh dan kereta api (KA) konvensional kian mengukuhkan ...</t>
+          <t>PT Pertamina Patra Niaga mendatangkan kapal pengangkut bahan bakar minyak (BBM) dengan total muatan 7.600 kiloliter ...</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678332/whoosh-kereta-api-dominasi-jalur-masuk-wisatawan-mancanegara-di-jabar</t>
+          <t>https://www.antaranews.com/berita/5678341/kapal-bbm-bermuatan-7600-kiloliter-masuk-lombok</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1002076644.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001432720.jpg</t>
         </is>
       </c>
     </row>
@@ -13470,61 +13470,61 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Daop 6 Yogyakarta tutup perlintasan tak terjaga Petak Sentolo–Rewulu</t>
+          <t>Whoosh-kereta api dominasi jalur masuk wisatawan mancanegara di Jabar</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:28:06 +0700</t>
+          <t>Mon, 03 Aug 2026 21:28:59 +0700</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
       <c r="E395" t="inlineStr">
         <is>
-          <t>PT Kereta Api Indonesia (Persero) Daerah Operasi 6 Yogyakarta terus berkolaborasi dengan pemerintah terkait, untuk ...</t>
+          <t>Integrasi transportasi berbasis rel seperti Kereta Cepat Whoosh dan kereta api (KA) konvensional kian mengukuhkan ...</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678331/daop-6-yogyakarta-tutup-perlintasan-tak-terjaga-petak-sentolo-rewulu</t>
+          <t>https://www.antaranews.com/berita/5678332/whoosh-kereta-api-dominasi-jalur-masuk-wisatawan-mancanegara-di-jabar</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000029465.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1002076644.jpg</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>ekonomi-bursa</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Kementan usulkan telur masuk skema CPP demi lindungi peternak rakyat</t>
+          <t>BEI terbitkan aturan emiten belum penuhi "free float" dapat notasi "P"</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:27:37 +0700</t>
+          <t>Mon, 03 Aug 2026 22:18:19 +0700</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Kementerian Pertanian (Kementan) mengusulkan komoditas telur ayam masuk dalam skema pengadaan Cadangan Pangan ...</t>
+          <t>PT Bursa Efek Indonesia (BEI) efektif memberlakukan dua Surat Edaran (SE) perihal Penambahan Tampilan Informasi Notasi ...</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678329/kementan-usulkan-telur-masuk-skema-cpp-demi-lindungi-peternak-rakyat</t>
+          <t>https://www.antaranews.com/berita/5678425/bei-terbitkan-aturan-emiten-belum-penuhi-free-float-dapat-notasi-p</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/9C2BC3E9-1C7E-4159-8805-C378B9294E25.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/pergerakan-indeks-harga-saham-gabungan-270726-dr-01.jpg</t>
         </is>
       </c>
     </row>
@@ -13536,28 +13536,28 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>BEI terbitkan aturan emiten belum penuhi "free float" dapat notasi "P"</t>
+          <t>OJK bertemu 100 investor global, apresiasi reformasi pasar modal RI</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:18:19 +0700</t>
+          <t>Mon, 03 Aug 2026 21:29:14 +0700</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
       <c r="E397" t="inlineStr">
         <is>
-          <t>PT Bursa Efek Indonesia (BEI) efektif memberlakukan dua Surat Edaran (SE) perihal Penambahan Tampilan Informasi Notasi ...</t>
+          <t>Ketua Dewan Komisioner Otoritas Jasa Keuangan (OJK) Friderica Widyasari Dewi mengungkapkan bahwa OJK baru saja ...</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678425/bei-terbitkan-aturan-emiten-belum-penuhi-free-float-dapat-notasi-p</t>
+          <t>https://www.antaranews.com/berita/5678337/ojk-bertemu-100-investor-global-apresiasi-reformasi-pasar-modal-ri</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/pergerakan-indeks-harga-saham-gabungan-270726-dr-01.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.15.18_2.jpeg</t>
         </is>
       </c>
     </row>
@@ -13569,28 +13569,28 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>OJK bertemu 100 investor global, apresiasi reformasi pasar modal RI</t>
+          <t>OJK: Pasar modal jaga peran sumber pembiayaan di tengah gejolak global</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:29:14 +0700</t>
+          <t>Mon, 03 Aug 2026 18:33:35 +0700</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Ketua Dewan Komisioner Otoritas Jasa Keuangan (OJK) Friderica Widyasari Dewi mengungkapkan bahwa OJK baru saja ...</t>
+          <t>Ketua Dewan Komisioner Otoritas Jasa Keuangan (OJK) Friderica Widyasari Dewi alias Kiki memastikan bahwa pasar modal ...</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678337/ojk-bertemu-100-investor-global-apresiasi-reformasi-pasar-modal-ri</t>
+          <t>https://www.antaranews.com/berita/5677944/ojk-pasar-modal-jaga-peran-sumber-pembiayaan-di-tengah-gejolak-global</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.15.18_2.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.15.18.jpeg</t>
         </is>
       </c>
     </row>
@@ -13602,28 +13602,28 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>OJK: Pasar modal jaga peran sumber pembiayaan di tengah gejolak global</t>
+          <t>IHSG awal pekan berpotensi variatif seiring sentimen global-domestik</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:33:35 +0700</t>
+          <t>Mon, 03 Aug 2026 09:42:28 +0700</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Ketua Dewan Komisioner Otoritas Jasa Keuangan (OJK) Friderica Widyasari Dewi alias Kiki memastikan bahwa pasar modal ...</t>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin berpotensi bergerak variatif dipicu oleh ...</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677944/ojk-pasar-modal-jaga-peran-sumber-pembiayaan-di-tengah-gejolak-global</t>
+          <t>https://www.antaranews.com/berita/5677104/ihsg-awal-pekan-berpotensi-variatif-seiring-sentimen-global-domestik</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.15.18.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/12/12/ihsg-ditutup-menguat-2688871.jpg</t>
         </is>
       </c>
     </row>
@@ -13635,94 +13635,94 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>IHSG awal pekan berpotensi variatif seiring sentimen global-domestik</t>
+          <t>IHSG Senin dibuka menguat 36,49 poin ke posisi 6.272</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:42:28 +0700</t>
+          <t>Mon, 03 Aug 2026 09:11:26 +0700</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin berpotensi bergerak variatif dipicu oleh ...</t>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin pagi dibuka menguat 36,49 poin atau 0,59 ...</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677104/ihsg-awal-pekan-berpotensi-variatif-seiring-sentimen-global-domestik</t>
+          <t>https://www.antaranews.com/berita/5677071/ihsg-senin-dibuka-menguat-3649-poin-ke-posisi-6272</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/12/12/ihsg-ditutup-menguat-2688871.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/pergerakan-indeks-harga-saham-gabungan-2828631.jpg</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>humaniora</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>IHSG Senin dibuka menguat 36,49 poin ke posisi 6.272</t>
+          <t>Bantuan beras 30 kg cair mulai 17 Agustus 2026, ini jadwal dan cara cek penerimanya</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:11:26 +0700</t>
+          <t>Mon, 03 Aug 2026 13:27:14 +0700</t>
         </is>
       </c>
       <c r="D401" t="inlineStr"/>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Senin pagi dibuka menguat 36,49 poin atau 0,59 ...</t>
+          <t>Pemerintah memastikan penyaluran bantuan pangan beras tahap II tahun 2026 akan dimulai pada 17 Agustus 2026. Bantuan ...</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677071/ihsg-senin-dibuka-menguat-3649-poin-ke-posisi-6272</t>
+          <t>https://www.antaranews.com/berita/5677341/bantuan-beras-30-kg-cair-mulai-17-agustus-2026-ini-jadwal-dan-cara-cek-penerimanya</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/pergerakan-indeks-harga-saham-gabungan-2828631.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/26/kemensos-percepat-penyaluran-bansos-pkh-dan-bpnt-2778877.jpg</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>humaniora</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Bantuan beras 30 kg cair mulai 17 Agustus 2026, ini jadwal dan cara cek penerimanya</t>
+          <t>10 ide usaha menjelang 17 Agustus 2026 yang berpotensi laris dan menguntungkan</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:27:14 +0700</t>
+          <t>Mon, 03 Aug 2026 18:16:58 +0700</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Pemerintah memastikan penyaluran bantuan pangan beras tahap II tahun 2026 akan dimulai pada 17 Agustus 2026. Bantuan ...</t>
+          <t>Momentum peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 dapat menjadi peluang bagi pelaku ...</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677341/bantuan-beras-30-kg-cair-mulai-17-agustus-2026-ini-jadwal-dan-cara-cek-penerimanya</t>
+          <t>https://www.antaranews.com/berita/5677896/10-ide-usaha-menjelang-17-agustus-2026-yang-berpotensi-laris-dan-menguntungkan</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/26/kemensos-percepat-penyaluran-bansos-pkh-dan-bpnt-2778877.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/08/02/sentra-penjualan-bendera-merah-putih-di-surabaya-020824-Ds-3.jpg</t>
         </is>
       </c>
     </row>
@@ -13734,28 +13734,28 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>10 ide usaha menjelang 17 Agustus 2026 yang berpotensi laris dan menguntungkan</t>
+          <t>10 ide lomba 17 Agustus untuk anak PAUD dan TK yang seru, edukatif, dan mudah digelar</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:16:58 +0700</t>
+          <t>Mon, 03 Aug 2026 13:38:29 +0700</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Momentum peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 dapat menjadi peluang bagi pelaku ...</t>
+          <t>Perayaan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 dapat menjadi momen bagi anak usia PAUD dan TK ...</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677896/10-ide-usaha-menjelang-17-agustus-2026-yang-berpotensi-laris-dan-menguntungkan</t>
+          <t>https://www.antaranews.com/berita/5677368/10-ide-lomba-17-agustus-untuk-anak-paud-dan-tk-yang-seru-edukatif-dan-mudah-digelar</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/08/02/sentra-penjualan-bendera-merah-putih-di-surabaya-020824-Ds-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/08/03/WhatsApp-Image-2024-08-03-at-20.37.28.jpeg</t>
         </is>
       </c>
     </row>
@@ -13767,28 +13767,28 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>10 ide lomba 17 Agustus untuk anak PAUD dan TK yang seru, edukatif, dan mudah digelar</t>
+          <t>Sering terbangun tengah malam? Kenali 7 penyebab dan cara mengatasinya</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:38:29 +0700</t>
+          <t>Mon, 03 Aug 2026 13:35:20 +0700</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Perayaan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 dapat menjadi momen bagi anak usia PAUD dan TK ...</t>
+          <t>Bangun di tengah malam sesekali merupakan hal yang normal. Namun, jika kondisi ini terjadi hampir setiap malam dan ...</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677368/10-ide-lomba-17-agustus-untuk-anak-paud-dan-tk-yang-seru-edukatif-dan-mudah-digelar</t>
+          <t>https://www.antaranews.com/berita/5677357/sering-terbangun-tengah-malam-kenali-7-penyebab-dan-cara-mengatasinya</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/08/03/WhatsApp-Image-2024-08-03-at-20.37.28.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/20/Penumpang-rela-menginap-menunggu-kereta-pertama-di-Stasiun-Cikarang-150726-ryl-5.jpg</t>
         </is>
       </c>
     </row>
@@ -13800,28 +13800,28 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Sering terbangun tengah malam? Kenali 7 penyebab dan cara mengatasinya</t>
+          <t>Bahaya paparan pornografi pada anak: Dampak bagi otak, mental, dan perilaku</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:35:20 +0700</t>
+          <t>Mon, 03 Aug 2026 13:23:03 +0700</t>
         </is>
       </c>
       <c r="D405" t="inlineStr"/>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Bangun di tengah malam sesekali merupakan hal yang normal. Namun, jika kondisi ini terjadi hampir setiap malam dan ...</t>
+          <t>Perkembangan teknologi membuat anak-anak dan remaja semakin akrab dengan internet sejak usia dini. Di satu sisi, ...</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677357/sering-terbangun-tengah-malam-kenali-7-penyebab-dan-cara-mengatasinya</t>
+          <t>https://www.antaranews.com/berita/5677332/bahaya-paparan-pornografi-pada-anak-dampak-bagi-otak-mental-dan-perilaku</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/20/Penumpang-rela-menginap-menunggu-kereta-pertama-di-Stasiun-Cikarang-150726-ryl-5.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/02/ilustrasi-konten-berbau-pornografi.jpg</t>
         </is>
       </c>
     </row>
@@ -13833,28 +13833,28 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Bahaya paparan pornografi pada anak: Dampak bagi otak, mental, dan perilaku</t>
+          <t>Sudah ngantuk tapi sulit tidur pulas? Ini penyebab dan cara atasinya</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:23:03 +0700</t>
+          <t>Mon, 03 Aug 2026 11:28:54 +0700</t>
         </is>
       </c>
       <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Perkembangan teknologi membuat anak-anak dan remaja semakin akrab dengan internet sejak usia dini. Di satu sisi, ...</t>
+          <t>Rasa kantuk yang muncul di malam hari seharusnya menjadi pertanda bahwa tubuh siap beristirahat. Namun, tidak sedikit ...</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677332/bahaya-paparan-pornografi-pada-anak-dampak-bagi-otak-mental-dan-perilaku</t>
+          <t>https://www.antaranews.com/berita/5677203/sudah-ngantuk-tapi-sulit-tidur-pulas-ini-penyebab-dan-cara-atasinya</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/02/ilustrasi-konten-berbau-pornografi.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/17/Nafas.jpeg</t>
         </is>
       </c>
     </row>
@@ -13866,94 +13866,94 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Sudah ngantuk tapi sulit tidur pulas? Ini penyebab dan cara atasinya</t>
+          <t>Cara cepat tidur dalam 5 menit, efektif untuk yang sulit pulas</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:28:54 +0700</t>
+          <t>Mon, 03 Aug 2026 11:25:40 +0700</t>
         </is>
       </c>
       <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Rasa kantuk yang muncul di malam hari seharusnya menjadi pertanda bahwa tubuh siap beristirahat. Namun, tidak sedikit ...</t>
+          <t>Sulit tidur meski badan sudah terasa lelah merupakan masalah yang kerap dialami banyak orang. Kondisi ini sering ...</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677203/sudah-ngantuk-tapi-sulit-tidur-pulas-ini-penyebab-dan-cara-atasinya</t>
+          <t>https://www.antaranews.com/berita/5677199/cara-cepat-tidur-dalam-5-menit-efektif-untuk-yang-sulit-pulas</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/17/Nafas.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/04/tidua.jpg</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>tekno</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Cara cepat tidur dalam 5 menit, efektif untuk yang sulit pulas</t>
+          <t>Cara mengganti password WiFi lewat HP dan laptop dengan mudah</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:25:40 +0700</t>
+          <t>Mon, 03 Aug 2026 13:16:14 +0700</t>
         </is>
       </c>
       <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Sulit tidur meski badan sudah terasa lelah merupakan masalah yang kerap dialami banyak orang. Kondisi ini sering ...</t>
+          <t>WiFi yang tiba-tiba terasa lambat padahal sinyal penuh dan kuota internet masih banyak tentu membuat kesal. Salah satu ...</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677199/cara-cepat-tidur-dalam-5-menit-efektif-untuk-yang-sulit-pulas</t>
+          <t>https://www.antaranews.com/berita/5677312/cara-mengganti-password-wifi-lewat-hp-dan-laptop-dengan-mudah</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/11/04/tidua.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2020/08/19/antarafoto-warga-sediakan-internet-gratis-bagi-pelajar-190820-ief-2-1.jpg</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>tekno</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Cara mengganti password WiFi lewat HP dan laptop dengan mudah</t>
+          <t>Piala AFF 2026 : Indonesia takluk 0-3 dari Vietnam</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:16:14 +0700</t>
+          <t>Mon, 03 Aug 2026 22:26:45 +0700</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr">
         <is>
-          <t>WiFi yang tiba-tiba terasa lambat padahal sinyal penuh dan kuota internet masih banyak tentu membuat kesal. Salah satu ...</t>
+          <t>Pelatih Timnas Indonesia Jhon Herdman memberikan arahan kepada anak didiknya saat melawan Timnas Vietnam pada pertandingan Grup A Piala AFF 2026 di Stadion Pakansari, Kabupaten Bogor, Jawa Barat, Senin (3/8/2026). ANTARA FOTO/Bayu Pratama S/mrh/wsj.</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677312/cara-mengganti-password-wifi-lewat-hp-dan-laptop-dengan-mudah</t>
+          <t>https://www.antaranews.com/foto/5678435/piala-aff-2026-indonesia-takluk-0-3-dari-vietnam</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2020/08/19/antarafoto-warga-sediakan-internet-gratis-bagi-pelajar-190820-ief-2-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/03/Timnas-Indonesia-lawan-Vietnam-030826-Bay-11b.jpg</t>
         </is>
       </c>
     </row>

--- a/data/berita_antara_2026-08-03.xlsx
+++ b/data/berita_antara_2026-08-03.xlsx
@@ -10961,28 +10961,28 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Chelsea umumkan transfer gelandang Inggris Jordan Henderson</t>
+          <t>Prabowo-PM Thailand perkuat kemitraan strategis ASEAN</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:59:34 +0700</t>
+          <t>Mon, 03 Aug 2026 22:52:55 +0700</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Chelsea resmi mengumumkan kedatangan gelandang senior asal Inggris Jordan Henderson dengan status bebas transfer ...</t>
+          <t>Presiden RI Prabowo Subianto dan Perdana Menteri (PM) Thailand Anutin Charnvirakul sepakat memperkuat kemitraan ...</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678548/chelsea-umumkan-transfer-gelandang-inggris-jordan-henderson</t>
+          <t>https://www.antaranews.com/berita/5678476/prabowo-pm-thailand-perkuat-kemitraan-strategis-asean</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000042505.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_F6F7E006D3CC-1.jpeg</t>
         </is>
       </c>
     </row>
@@ -10994,94 +10994,94 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Nguyen Xuan Son ungkap alasan tak jadi starter saat kalahkan Indonesia</t>
+          <t>Galaxy Tab S12 Ultra mejeng di Geekbench, hadir dengan Dimensity 9500</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:56:45 +0700</t>
+          <t>Mon, 03 Aug 2026 22:48:03 +0700</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Penyerang Timnas Vietnam Nguyen Xuan Son mengungkapkan alasan dirinya tidak dimainkan sebagai starter saat timnya ...</t>
+          <t>Samsung Galaxy Tab S12 Ultra dalam seri perangkat Galaxy Tab S12 yang diperkirakan dirilis September 2026 muncul di ...</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678547/nguyen-xuan-son-ungkap-alasan-tak-jadi-starter-saat-kalahkan-indonesia</t>
+          <t>https://www.antaranews.com/berita/5678469/galaxy-tab-s12-ultra-mejeng-di-geekbench-hadir-dengan-dimensity-9500</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1003314030.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/InShot_20260803_215836626.jpg</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
+          <t>Whoosh-kereta api dominasi jalur masuk wisatawan mancanegara di Jabar</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:55:47 +0700</t>
+          <t>Mon, 03 Aug 2026 21:28:59 +0700</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
-          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ...</t>
+          <t>Integrasi transportasi berbasis rel seperti Kereta Cepat Whoosh dan kereta api (KA) konvensional kian mengukuhkan ...</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+          <t>https://www.antaranews.com/berita/5678332/whoosh-kereta-api-dominasi-jalur-masuk-wisatawan-mancanegara-di-jabar</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1002076644.jpg</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>BPS kaitkan kenaikan TPK hotel bintang dengan kualitas wisman</t>
+          <t>Chelsea umumkan transfer gelandang Inggris Jordan Henderson</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:53:51 +0700</t>
+          <t>Mon, 03 Aug 2026 23:59:34 +0700</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) Bali mengaitkan kenaikan tingkat penghunian kamar (TPK) hotel bintang pada Juni 2026 dengan ...</t>
+          <t>Chelsea resmi mengumumkan kedatangan gelandang senior asal Inggris Jordan Henderson dengan status bebas transfer ...</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678543/bps-kaitkan-kenaikan-tpk-hotel-bintang-dengan-kualitas-wisman</t>
+          <t>https://www.antaranews.com/berita/5678548/chelsea-umumkan-transfer-gelandang-inggris-jordan-henderson</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0332.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000042505.jpg</t>
         </is>
       </c>
     </row>
@@ -11093,61 +11093,61 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Jogja Run'nShine 2026 targetkan diikuti 3.500 pelari</t>
+          <t>Nguyen Xuan Son ungkap alasan tak jadi starter saat kalahkan Indonesia</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:52:29 +0700</t>
+          <t>Mon, 03 Aug 2026 23:56:45 +0700</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Pergelaran Jogja Run'nShine 2026 menargetkan diikuti sebanyak 3.500 pelari dengan memberikan pengalaman konsep ...</t>
+          <t>Penyerang Timnas Vietnam Nguyen Xuan Son mengungkapkan alasan dirinya tidak dimainkan sebagai starter saat timnya ...</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678540/jogja-runnshine-2026-targetkan-diikuti-3500-pelari</t>
+          <t>https://www.antaranews.com/berita/5678547/nguyen-xuan-son-ungkap-alasan-tak-jadi-starter-saat-kalahkan-indonesia</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0103.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1003314030.jpg</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Jenama perkakas otomotif Tekiro dapat pengakuan Guinnes World Records</t>
+          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:47:06 +0700</t>
+          <t>Mon, 03 Aug 2026 23:55:47 +0700</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Jenama perkakas otomotif Tekiro mendapat pengakuan dari Guiness World Records berkat ...</t>
+          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ...</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5678535/jenama-perkakas-otomotif-tekiro-dapat-pengakuan-guinnes-world-records</t>
+          <t>https://www.antaranews.com/video/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-02-at-15.34.09-1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
         </is>
       </c>
     </row>
@@ -11159,94 +11159,94 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Pemkab Sleman dukung kejuaraan dragbike tingkatkan ekonomi masyarakat</t>
+          <t>BPS kaitkan kenaikan TPK hotel bintang dengan kualitas wisman</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:42:42 +0700</t>
+          <t>Mon, 03 Aug 2026 23:53:51 +0700</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Pemerintah Kabupaten Sleman, Daerah Istimewa Yogyakarta, mendukung penuh penyelenggaraan Kejuaraan Dragbike Super ...</t>
+          <t>Badan Pusat Statistik (BPS) Bali mengaitkan kenaikan tingkat penghunian kamar (TPK) hotel bintang pada Juni 2026 dengan ...</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678532/pemkab-sleman-dukung-kejuaraan-dragbike-tingkatkan-ekonomi-masyarakat</t>
+          <t>https://www.antaranews.com/berita/5678543/bps-kaitkan-kenaikan-tpk-hotel-bintang-dengan-kualitas-wisman</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000029422.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0332.jpeg</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>GMR nilai akses penerbangan langsung buka peluang ekonomi RI-India</t>
+          <t>Jogja Run'nShine 2026 targetkan diikuti 3.500 pelari</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:41:32 +0700</t>
+          <t>Mon, 03 Aug 2026 23:52:29 +0700</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
-          <t>GMR Group, perusahaan multinasional India yang bergerak di bidang infrastruktur, menilai akses penerbangan langsung ...</t>
+          <t>Pergelaran Jogja Run'nShine 2026 menargetkan diikuti sebanyak 3.500 pelari dengan memberikan pengalaman konsep ...</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678529/gmr-nilai-akses-penerbangan-langsung-buka-peluang-ekonomi-ri-india</t>
+          <t>https://www.antaranews.com/berita/5678540/jogja-runnshine-2026-targetkan-diikuti-3500-pelari</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/DSF3021.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0103.jpg</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PSSI raup dana Rp722 miliar dalam laporan keuangan tahunan</t>
+          <t>Jenama perkakas otomotif Tekiro dapat pengakuan Guinnes World Records</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:37:46 +0700</t>
+          <t>Mon, 03 Aug 2026 23:47:06 +0700</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir menyebut organisasinya meraup dana senilai Rp722 ...</t>
+          <t>Jenama perkakas otomotif Tekiro mendapat pengakuan dari Guiness World Records berkat ...</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678528/pssi-raup-dana-rp722-miliar-dalam-laporan-keuangan-tahunan</t>
+          <t>https://otomotif.antaranews.com/berita/5678535/jenama-perkakas-otomotif-tekiro-dapat-pengakuan-guinnes-world-records</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0098_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-02-at-15.34.09-1.jpeg</t>
         </is>
       </c>
     </row>
@@ -11258,61 +11258,61 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Otorita kolaborasi PNM untuk pengembangan ekonomi masyarakat IKN</t>
+          <t>Pemkab Sleman dukung kejuaraan dragbike tingkatkan ekonomi masyarakat</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:30:50 +0700</t>
+          <t>Mon, 03 Aug 2026 23:42:42 +0700</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Otorita Ibu Kota Nusantara (IKN) melakukan kolaborasi dengan PT Permodalan Nasional Madani (Persero) untuk pengembangan ...</t>
+          <t>Pemerintah Kabupaten Sleman, Daerah Istimewa Yogyakarta, mendukung penuh penyelenggaraan Kejuaraan Dragbike Super ...</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678525/otorita-kolaborasi-pnm-untuk-pengembangan-ekonomi-masyarakat-ikn</t>
+          <t>https://www.antaranews.com/berita/5678532/pemkab-sleman-dukung-kejuaraan-dragbike-tingkatkan-ekonomi-masyarakat</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0012_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000029422.jpg</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>DPR: Wacana Prabowo jembatani dialog Korea sesuai politik bebas aktif</t>
+          <t>GMR nilai akses penerbangan langsung buka peluang ekonomi RI-India</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:30:13 +0700</t>
+          <t>Mon, 03 Aug 2026 23:41:32 +0700</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Wakil Ketua Komisi I DPR RI Dave Laksono menilai wacana Presiden Prabowo Subianto untuk menjembatani dialog antara ...</t>
+          <t>GMR Group, perusahaan multinasional India yang bergerak di bidang infrastruktur, menilai akses penerbangan langsung ...</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678521/dpr-wacana-prabowo-jembatani-dialog-korea-sesuai-politik-bebas-aktif</t>
+          <t>https://www.antaranews.com/berita/5678529/gmr-nilai-akses-penerbangan-langsung-buka-peluang-ekonomi-ri-india</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/22/IMG_20260422_175322.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/DSF3021.jpeg</t>
         </is>
       </c>
     </row>
@@ -11324,28 +11324,28 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Kongres PSSI sepakati pemilihan pengurus mundur ke Juli 2027</t>
+          <t>PSSI raup dana Rp722 miliar dalam laporan keuangan tahunan</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:30:00 +0700</t>
+          <t>Mon, 03 Aug 2026 23:37:46 +0700</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
-          <t>ANTARA - Kongres Biasa PSSI 2026 menyepakati perubahan jadwal Kongres Pemilihan Pengurus PSSI 2027 dari semula Mei ...</t>
+          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir menyebut organisasinya meraup dana senilai Rp722 ...</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678395/kongres-pssi-sepakati-pemilihan-pengurus-mundur-ke-juli-2027</t>
+          <t>https://www.antaranews.com/berita/5678528/pssi-raup-dana-rp722-miliar-dalam-laporan-keuangan-tahunan</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KONGRES-PSSI-SEPAKATI-PEMILIHAN-PENGURUS-MUNDUR-KE-JULI-2027.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0098_1.jpg</t>
         </is>
       </c>
     </row>
@@ -11357,28 +11357,28 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Toyota Astra Motor perkenalkan Hilux generasi ke-9</t>
+          <t>Otorita kolaborasi PNM untuk pengembangan ekonomi masyarakat IKN</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:25:20 +0700</t>
+          <t>Mon, 03 Aug 2026 23:30:50 +0700</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
-          <t>PT Toyota Astra Motor (TAM) memperkenalkan Hilux generasi ke-9 untuk mendukung pemenuhan kebutuhan operasional industri ...</t>
+          <t>Otorita Ibu Kota Nusantara (IKN) melakukan kolaborasi dengan PT Permodalan Nasional Madani (Persero) untuk pengembangan ...</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5678519/toyota-astra-motor-perkenalkan-hilux-generasi-ke-9</t>
+          <t>https://www.antaranews.com/berita/5678525/otorita-kolaborasi-pnm-untuk-pengembangan-ekonomi-masyarakat-ikn</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/photo_6307309656757440820_w-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0012_1.jpg</t>
         </is>
       </c>
     </row>
@@ -11390,28 +11390,28 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Sudin PPAPP Jakbar sosialisasikan Sekolah Siaga Kependudukan</t>
+          <t>DPR: Wacana Prabowo jembatani dialog Korea sesuai politik bebas aktif</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:24:33 +0700</t>
+          <t>Mon, 03 Aug 2026 23:30:13 +0700</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Suku Dinas Pemberdayaan, Perlindungan Anak, dan Pengendalian Penduduk (Sudin PPAPP) Jakarta Barat (Jakbar) menggelar ...</t>
+          <t>Wakil Ketua Komisi I DPR RI Dave Laksono menilai wacana Presiden Prabowo Subianto untuk menjembatani dialog antara ...</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678515/sudin-ppapp-jakbar-sosialisasikan-sekolah-siaga-kependudukan</t>
+          <t>https://www.antaranews.com/berita/5678521/dpr-wacana-prabowo-jembatani-dialog-korea-sesuai-politik-bebas-aktif</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0031_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/22/IMG_20260422_175322.jpg</t>
         </is>
       </c>
     </row>
@@ -11423,28 +11423,28 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Klasemen Grup A Piala AFF : Timnas Indonesia turun ke peringkat tiga</t>
+          <t>Kongres PSSI sepakati pemilihan pengurus mundur ke Juli 2027</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:23:51 +0700</t>
+          <t>Mon, 03 Aug 2026 23:30:00 +0700</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Timnas Indonesia turun ke peringkat ketiga klasemen sementara Grup A Piala AFF 2026 setelah menelan kekalahan 0-3 dari ...</t>
+          <t>ANTARA - Kongres Biasa PSSI 2026 menyepakati perubahan jadwal Kongres Pemilihan Pengurus PSSI 2027 dari semula Mei ...</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678512/klasemen-grup-a-piala-aff-timnas-indonesia-turun-ke-peringkat-tiga</t>
+          <t>https://www.antaranews.com/video/5678395/kongres-pssi-sepakati-pemilihan-pengurus-mundur-ke-juli-2027</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833516.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KONGRES-PSSI-SEPAKATI-PEMILIHAN-PENGURUS-MUNDUR-KE-JULI-2027.jpg</t>
         </is>
       </c>
     </row>
@@ -11456,61 +11456,61 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>NTB menargetkan penonton MotoGP Mandalika tembus 140 ribu</t>
+          <t>Toyota Astra Motor perkenalkan Hilux generasi ke-9</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:23:01 +0700</t>
+          <t>Mon, 03 Aug 2026 23:25:20 +0700</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Pemerintah Provinsi Nusa Tenggara Barat menargetkan jumlah penonton MotoGP di Sirkuit Mandalika pada 9-11 Oktober 2026 ...</t>
+          <t>PT Toyota Astra Motor (TAM) memperkenalkan Hilux generasi ke-9 untuk mendukung pemenuhan kebutuhan operasional industri ...</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678508/ntb-menargetkan-penonton-motogp-mandalika-tembus-140-ribu</t>
+          <t>https://otomotif.antaranews.com/berita/5678519/toyota-astra-motor-perkenalkan-hilux-generasi-ke-9</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260109-WA0024_copy_1280x797.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/photo_6307309656757440820_w-1.jpg</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Bulog: Margin naik jadi 7 persen, dukungan Presiden kawal swasembada</t>
+          <t>Sudin PPAPP Jakbar sosialisasikan Sekolah Siaga Kependudukan</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:19:51 +0700</t>
+          <t>Mon, 03 Aug 2026 23:24:33 +0700</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Direktur Utama Perum Bulog Ahmad Rizal Ramdhani menegaskan kenaikan margin fee menjadi 7 persen bentuk dukungan ...</t>
+          <t>Suku Dinas Pemberdayaan, Perlindungan Anak, dan Pengendalian Penduduk (Sudin PPAPP) Jakarta Barat (Jakbar) menggelar ...</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678504/bulog-margin-naik-jadi-7-persen-dukungan-presiden-kawal-swasembada</t>
+          <t>https://www.antaranews.com/berita/5678515/sudin-ppapp-jakbar-sosialisasikan-sekolah-siaga-kependudukan</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/14C1B7CB-9D6F-49B9-9CD1-E40DD76E851C.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0031_1.jpg</t>
         </is>
       </c>
     </row>
@@ -11522,94 +11522,94 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Turkiye sebut serangan Israel sabotase upaya damai di Gaza</t>
+          <t>Klasemen Grup A Piala AFF : Timnas Indonesia turun ke peringkat tiga</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:18:30 +0700</t>
+          <t>Mon, 03 Aug 2026 23:23:51 +0700</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Pemerintah Turkiye pada Senin menilai serangan Israel di Jalur Gaza telah menghambat berbagai inisiatif diplomatik yang ...</t>
+          <t>Timnas Indonesia turun ke peringkat ketiga klasemen sementara Grup A Piala AFF 2026 setelah menelan kekalahan 0-3 dari ...</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678500/turkiye-sebut-serangan-israel-sabotase-upaya-damai-di-gaza</t>
+          <t>https://www.antaranews.com/berita/5678512/klasemen-grup-a-piala-aff-timnas-indonesia-turun-ke-peringkat-tiga</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/thumbs_b_c_186832d7ab4775afec853057c8952c3d.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833516.jpg</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Purbaya pastikan tak ada lagi perdebatan soal penarikan SAL dari bank</t>
+          <t>NTB menargetkan penonton MotoGP Mandalika tembus 140 ribu</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:15:59 +0700</t>
+          <t>Mon, 03 Aug 2026 23:23:01 +0700</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Menteri Keuangan (Menkeu), Purbaya Yudhi Sadewa memastikan tidak ada lagi perdebatan mengenai penarikan dana ...</t>
+          <t>Pemerintah Provinsi Nusa Tenggara Barat menargetkan jumlah penonton MotoGP di Sirkuit Mandalika pada 9-11 Oktober 2026 ...</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678499/purbaya-pastikan-tak-ada-lagi-perdebatan-soal-penarikan-sal-dari-bank</t>
+          <t>https://www.antaranews.com/berita/5678508/ntb-menargetkan-penonton-motogp-mandalika-tembus-140-ribu</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-23.02.47.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260109-WA0024_copy_1280x797.jpg</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Tim 9 Kejagung didesak usut pemilik uang-emas di rumah eks Jampidsus</t>
+          <t>Bulog: Margin naik jadi 7 persen, dukungan Presiden kawal swasembada</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:10:43 +0700</t>
+          <t>Mon, 03 Aug 2026 23:19:51 +0700</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Tim 9 Kejaksaan Agung didesak mengusut tuntas pemilik uang tunai senilai Rp476 miliar dan emas batangan seberat 74 ...</t>
+          <t>Direktur Utama Perum Bulog Ahmad Rizal Ramdhani menegaskan kenaikan margin fee menjadi 7 persen bentuk dukungan ...</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678495/tim-9-kejagung-didesak-usut-pemilik-uang-emas-di-rumah-eks-jampidsus</t>
+          <t>https://www.antaranews.com/berita/5678504/bulog-margin-naik-jadi-7-persen-dukungan-presiden-kawal-swasembada</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/1000175632.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/14C1B7CB-9D6F-49B9-9CD1-E40DD76E851C.jpeg</t>
         </is>
       </c>
     </row>
@@ -11621,61 +11621,61 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Kemenbud hadirkan GBN untuk membina talenta seni musik nasional</t>
+          <t>Turkiye sebut serangan Israel sabotase upaya damai di Gaza</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:07:01 +0700</t>
+          <t>Mon, 03 Aug 2026 23:18:30 +0700</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Kementerian Kebudayaan (Kemenbud) menghadirkan program pembinaan talenta seni musik nasional yang mempertemukan ...</t>
+          <t>Pemerintah Turkiye pada Senin menilai serangan Israel di Jalur Gaza telah menghambat berbagai inisiatif diplomatik yang ...</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678491/kemenbud-hadirkan-gbn-untuk-membina-talenta-seni-musik-nasional</t>
+          <t>https://www.antaranews.com/berita/5678500/turkiye-sebut-serangan-israel-sabotase-upaya-damai-di-gaza</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-20.28.05.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/thumbs_b_c_186832d7ab4775afec853057c8952c3d.jpg</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Wamen ATR: Ujian PPAT upaya berikan layanan yang baik</t>
+          <t>Purbaya pastikan tak ada lagi perdebatan soal penarikan SAL dari bank</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:05:29 +0700</t>
+          <t>Mon, 03 Aug 2026 23:15:59 +0700</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Wakil Menteri Agraria dan Tata Ruang/Wakil Kepala Badan Pertanahan Nasional (Wamen ATR/Waka BPN) Ossy Dermawan ...</t>
+          <t>Menteri Keuangan (Menkeu), Purbaya Yudhi Sadewa memastikan tidak ada lagi perdebatan mengenai penarikan dana ...</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678489/wamen-atr-ujian-ppat-upaya-berikan-layanan-yang-baik</t>
+          <t>https://www.antaranews.com/berita/5678499/purbaya-pastikan-tak-ada-lagi-perdebatan-soal-penarikan-sal-dari-bank</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_223512.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-23.02.47.jpeg</t>
         </is>
       </c>
     </row>
@@ -11687,28 +11687,28 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>PBSI buka suara soal absennya Jafar/Felisha di Kejuaraan Dunia BWF</t>
+          <t>Tim 9 Kejagung didesak usut pemilik uang-emas di rumah eks Jampidsus</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:03:05 +0700</t>
+          <t>Mon, 03 Aug 2026 23:10:43 +0700</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Pengurus Pusat PBSI menyatakan absennya dua pasangan ganda campuran Indonesia Jafar Hidayatullah/Felisha Alberta ...</t>
+          <t>Tim 9 Kejaksaan Agung didesak mengusut tuntas pemilik uang tunai senilai Rp476 miliar dan emas batangan seberat 74 ...</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678487/pbsi-buka-suara-soal-absennya-jafar-felisha-di-kejuaraan-dunia-bwf</t>
+          <t>https://www.antaranews.com/berita/5678495/tim-9-kejagung-didesak-usut-pemilik-uang-emas-di-rumah-eks-jampidsus</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/06/IMG_20251127_205351.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/1000175632.jpg</t>
         </is>
       </c>
     </row>
@@ -11720,94 +11720,94 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Presiden Prabowo terima kunjungan PM Thailand di Istana Merdeka</t>
+          <t>Kemenbud hadirkan GBN untuk membina talenta seni musik nasional</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:59:27 +0700</t>
+          <t>Mon, 03 Aug 2026 23:07:01 +0700</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Prabowo Subianto menerima kunjungan resmi Perdana Menteri Thailand Anutin Charnvirakul di Istana ...</t>
+          <t>Kementerian Kebudayaan (Kemenbud) menghadirkan program pembinaan talenta seni musik nasional yang mempertemukan ...</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678461/presiden-prabowo-terima-kunjungan-pm-thailand-di-istana-merdeka</t>
+          <t>https://www.antaranews.com/berita/5678491/kemenbud-hadirkan-gbn-untuk-membina-talenta-seni-musik-nasional</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PRESIDEN-PRABOWO-TERIMA-KUNJUNGAN-PM-THAILAND-DI-ISTANA-MERDEKA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-20.28.05.jpeg</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
+          <t>Wamen ATR: Ujian PPAT upaya berikan layanan yang baik</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:58:38 +0700</t>
+          <t>Mon, 03 Aug 2026 23:05:29 +0700</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>ANTARA - Badan Pencarian dan Pertolongan Nasional (Basarnas) mengerahkan satu unit kapal untuk menjemput 66 korban ...</t>
+          <t>Wakil Menteri Agraria dan Tata Ruang/Wakil Kepala Badan Pertanahan Nasional (Wamen ATR/Waka BPN) Ossy Dermawan ...</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678472/basarnas-jemput-66-korban-km-mutiara-sentosa-ii-dari-masalembu</t>
+          <t>https://www.antaranews.com/berita/5678489/wamen-atr-ujian-ppat-upaya-berikan-layanan-yang-baik</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BASARNAS-JEMPUT-66-KORBAN-KM-MUTIARA-SENTOSA-II-DARI-MASALEMBU.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_223512.jpg</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Kementerian ATR/BPN telah terbitkan 124 ribu SK sertifikat rumah MBR</t>
+          <t>PBSI buka suara soal absennya Jafar/Felisha di Kejuaraan Dunia BWF</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:56:36 +0700</t>
+          <t>Mon, 03 Aug 2026 23:03:05 +0700</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Kementerian Agraria dan Tata Ruang/Badan Pertanahan Nasional (ATR/BPN) menyatakan telah menerbitkan surat keputusan ...</t>
+          <t>Pengurus Pusat PBSI menyatakan absennya dua pasangan ganda campuran Indonesia Jafar Hidayatullah/Felisha Alberta ...</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678484/kementerian-atr-bpn-telah-terbitkan-124-ribu-sk-sertifikat-rumah-mbr</t>
+          <t>https://www.antaranews.com/berita/5678487/pbsi-buka-suara-soal-absennya-jafar-felisha-di-kejuaraan-dunia-bwf</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_224532.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/06/IMG_20251127_205351.jpg</t>
         </is>
       </c>
     </row>
@@ -11819,28 +11819,28 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Timnas Indonesia dibungkam Vietnam 0-3</t>
+          <t>Presiden Prabowo terima kunjungan PM Thailand di Istana Merdeka</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:54:01 +0700</t>
+          <t>Mon, 03 Aug 2026 22:59:27 +0700</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Timnas Indonesia dibungkam Vietnam 0-3 di kandang pada laga lanjutan Grup A Piala AFF 2026 di Stadion Pakansari, Bogor, ...</t>
+          <t>ANTARA - Presiden Prabowo Subianto menerima kunjungan resmi Perdana Menteri Thailand Anutin Charnvirakul di Istana ...</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678480/timnas-indonesia-dibungkam-vietnam-0-3</t>
+          <t>https://www.antaranews.com/video/5678461/presiden-prabowo-terima-kunjungan-pm-thailand-di-istana-merdeka</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Timnas-Indonesia-lawan-Vietnam-030826-Bay-21a.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PRESIDEN-PRABOWO-TERIMA-KUNJUNGAN-PM-THAILAND-DI-ISTANA-MERDEKA.jpg</t>
         </is>
       </c>
     </row>
@@ -11852,94 +11852,94 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Prabowo-PM Thailand perkuat kemitraan strategis ASEAN</t>
+          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:52:55 +0700</t>
+          <t>Mon, 03 Aug 2026 22:58:38 +0700</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Presiden RI Prabowo Subianto dan Perdana Menteri (PM) Thailand Anutin Charnvirakul sepakat memperkuat kemitraan ...</t>
+          <t>ANTARA - Badan Pencarian dan Pertolongan Nasional (Basarnas) mengerahkan satu unit kapal untuk menjemput 66 korban ...</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678476/prabowo-pm-thailand-perkuat-kemitraan-strategis-asean</t>
+          <t>https://www.antaranews.com/video/5678472/basarnas-jemput-66-korban-km-mutiara-sentosa-ii-dari-masalembu</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_F6F7E006D3CC-1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BASARNAS-JEMPUT-66-KORBAN-KM-MUTIARA-SENTOSA-II-DARI-MASALEMBU.jpg</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Galaxy Tab S12 Ultra mejeng di Geekbench, hadir dengan Dimensity 9500</t>
+          <t>Kementerian ATR/BPN telah terbitkan 124 ribu SK sertifikat rumah MBR</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:48:03 +0700</t>
+          <t>Mon, 03 Aug 2026 22:56:36 +0700</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Tab S12 Ultra dalam seri perangkat Galaxy Tab S12 yang diperkirakan dirilis September 2026 muncul di ...</t>
+          <t>Kementerian Agraria dan Tata Ruang/Badan Pertanahan Nasional (ATR/BPN) menyatakan telah menerbitkan surat keputusan ...</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678469/galaxy-tab-s12-ultra-mejeng-di-geekbench-hadir-dengan-dimensity-9500</t>
+          <t>https://www.antaranews.com/berita/5678484/kementerian-atr-bpn-telah-terbitkan-124-ribu-sk-sertifikat-rumah-mbr</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/InShot_20260803_215836626.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_224532.jpg</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Prabowo terima tanda kehormatan dari Angkatan Bersenjata Thailand</t>
+          <t>Timnas Indonesia dibungkam Vietnam 0-3</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 20:59:35 +0700</t>
+          <t>Mon, 03 Aug 2026 22:54:01 +0700</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Presiden Prabowo Subianto menerima tanda kehormatan dari Angkatan Bersenjata Kerajaan Thailand yang diberikan pada saat ...</t>
+          <t>Timnas Indonesia dibungkam Vietnam 0-3 di kandang pada laga lanjutan Grup A Piala AFF 2026 di Stadion Pakansari, Bogor, ...</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678283/prabowo-terima-tanda-kehormatan-dari-angkatan-bersenjata-thailand</t>
+          <t>https://www.antaranews.com/berita/5678480/timnas-indonesia-dibungkam-vietnam-0-3</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/tempImageNOyDfK.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Timnas-Indonesia-lawan-Vietnam-030826-Bay-21a.jpg</t>
         </is>
       </c>
     </row>
@@ -11951,160 +11951,160 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
+          <t>Prabowo terima tanda kehormatan dari Angkatan Bersenjata Thailand</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 20:50:37 +0700</t>
+          <t>Mon, 03 Aug 2026 20:59:35 +0700</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
-          <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan ...</t>
+          <t>Presiden Prabowo Subianto menerima tanda kehormatan dari Angkatan Bersenjata Kerajaan Thailand yang diberikan pada saat ...</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
+          <t>https://www.antaranews.com/berita/5678283/prabowo-terima-tanda-kehormatan-dari-angkatan-bersenjata-thailand</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/tempImageNOyDfK.jpg</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>ekonomi-finansial, top-news</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Menkeu: Eskalasi konflik Timteng dorong imbal hasil SBN ke 7,14 persen</t>
+          <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 20:48:02 +0700</t>
+          <t>Mon, 03 Aug 2026 20:50:37 +0700</t>
         </is>
       </c>
       <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa mengatakan eskalasi konflik di Timur Tengah mendorong kenaikan imbal hasil Surat ...</t>
+          <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan ...</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678253/menkeu-eskalasi-konflik-timteng-dorong-imbal-hasil-sbn-ke-714-persen</t>
+          <t>https://www.antaranews.com/video/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-20.38.31.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-finansial, top-news</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Prabowo dukung peningkatan latihan bersama militer RI-Thailand</t>
+          <t>Menkeu: Eskalasi konflik Timteng dorong imbal hasil SBN ke 7,14 persen</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:21:32 +0700</t>
+          <t>Mon, 03 Aug 2026 20:48:02 +0700</t>
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Presiden Prabowo Subianto mendukung peningkatan frekuensi latihan bersama antara Tentara Nasional Indonesia (TNI) dan ...</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa mengatakan eskalasi konflik di Timur Tengah mendorong kenaikan imbal hasil Surat ...</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678081/prabowo-dukung-peningkatan-latihan-bersama-militer-ri-thailand</t>
+          <t>https://www.antaranews.com/berita/5678253/menkeu-eskalasi-konflik-timteng-dorong-imbal-hasil-sbn-ke-714-persen</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.41.07.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-20.38.31.jpeg</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>ekonomi-finansial, top-news</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>OJK: Kredit perbankan tumbuh 12,67 persen capai Rp9.080,9 triliun</t>
+          <t>Prabowo dukung peningkatan latihan bersama militer RI-Thailand</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:12:24 +0700</t>
+          <t>Mon, 03 Aug 2026 19:21:32 +0700</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Otoritas Jasa Keuangan (OJK) melaporkan penyaluran kredit perbankan di tanah air tumbuh 12,67 persen year on year ...</t>
+          <t>Presiden Prabowo Subianto mendukung peningkatan frekuensi latihan bersama antara Tentara Nasional Indonesia (TNI) dan ...</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678057/ojk-kredit-perbankan-tumbuh-1267-persen-capai-rp90809-triliun</t>
+          <t>https://www.antaranews.com/berita/5678081/prabowo-dukung-peningkatan-latihan-bersama-militer-ri-thailand</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.15.18_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.41.07.jpeg</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-finansial, top-news</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Menkomdigi: KIP garda depan informasi jernih dan perangi hoaks</t>
+          <t>OJK: Kredit perbankan tumbuh 12,67 persen capai Rp9.080,9 triliun</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:00:50 +0700</t>
+          <t>Mon, 03 Aug 2026 19:12:24 +0700</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid mengatakan Komisi Informasi Pusat (KIP) menjadi garda terdepan ...</t>
+          <t>Otoritas Jasa Keuangan (OJK) melaporkan penyaluran kredit perbankan di tanah air tumbuh 12,67 persen year on year ...</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678033/menkomdigi-kip-garda-depan-informasi-jernih-dan-perangi-hoaks</t>
+          <t>https://www.antaranews.com/berita/5678057/ojk-kredit-perbankan-tumbuh-1267-persen-capai-rp90809-triliun</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0321.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.15.18_1.jpeg</t>
         </is>
       </c>
     </row>
@@ -12116,28 +12116,28 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Satu tahun Sekolah Rakyat, ratusan siswa torehkan prestasi</t>
+          <t>Menkomdigi: KIP garda depan informasi jernih dan perangi hoaks</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:59:25 +0700</t>
+          <t>Mon, 03 Aug 2026 19:00:50 +0700</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Menteri Sosial (Mensos) Saifullah Yusuf menyatakan selama satu tahun Sekolah Rakyat berdiri sudah ratusan ...</t>
+          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid mengatakan Komisi Informasi Pusat (KIP) menjadi garda terdepan ...</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678024/satu-tahun-sekolah-rakyat-ratusan-siswa-torehkan-prestasi</t>
+          <t>https://www.antaranews.com/berita/5678033/menkomdigi-kip-garda-depan-informasi-jernih-dan-perangi-hoaks</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176441.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0321.jpg</t>
         </is>
       </c>
     </row>
@@ -12149,28 +12149,28 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Menkeu: Realisasi anggaran MBG Rp101,1 T untuk 63,13 juta penerima</t>
+          <t>Satu tahun Sekolah Rakyat, ratusan siswa torehkan prestasi</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:53:14 +0700</t>
+          <t>Mon, 03 Aug 2026 18:59:25 +0700</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa mengungkapkan bahwa realisasi anggaran Program Makan Bergizi Gratis ...</t>
+          <t>Menteri Sosial (Mensos) Saifullah Yusuf menyatakan selama satu tahun Sekolah Rakyat berdiri sudah ratusan ...</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678005/menkeu-realisasi-anggaran-mbg-rp1011-t-untuk-6313-juta-penerima</t>
+          <t>https://www.antaranews.com/berita/5678024/satu-tahun-sekolah-rakyat-ratusan-siswa-torehkan-prestasi</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29-2.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176441.jpg</t>
         </is>
       </c>
     </row>
@@ -12182,28 +12182,28 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Polri perkuat langkah preventif respons isu keamanan nasional</t>
+          <t>Menkeu: Realisasi anggaran MBG Rp101,1 T untuk 63,13 juta penerima</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:46:34 +0700</t>
+          <t>Mon, 03 Aug 2026 18:53:14 +0700</t>
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Polri memastikan terus memperkuat langkah preventif untuk menjaga keamanan nasional sehingga aktivitas masyarakat dan ...</t>
+          <t>Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa mengungkapkan bahwa realisasi anggaran Program Makan Bergizi Gratis ...</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677985/polri-perkuat-langkah-preventif-respons-isu-keamanan-nasional</t>
+          <t>https://www.antaranews.com/berita/5678005/menkeu-realisasi-anggaran-mbg-rp1011-t-untuk-6313-juta-penerima</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/1000086556.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29-2.jpeg</t>
         </is>
       </c>
     </row>
@@ -12215,28 +12215,28 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Prabowo dan PM Thailand bertemu empat mata di Istana Merdeka</t>
+          <t>Polri perkuat langkah preventif respons isu keamanan nasional</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 17:49:52 +0700</t>
+          <t>Mon, 03 Aug 2026 18:46:34 +0700</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Presiden Prabowo Subianto dan Perdana Menteri Thailand Anutin Charnvirakul menggelar pertemuan empat mata di Istana ...</t>
+          <t>Polri memastikan terus memperkuat langkah preventif untuk menjaga keamanan nasional sehingga aktivitas masyarakat dan ...</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677828/prabowo-dan-pm-thailand-bertemu-empat-mata-di-istana-merdeka</t>
+          <t>https://www.antaranews.com/berita/5677985/polri-perkuat-langkah-preventif-respons-isu-keamanan-nasional</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_5162.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/1000086556.jpg</t>
         </is>
       </c>
     </row>
@@ -12248,62 +12248,62 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Kepala BGN tingkatkan status keracunan MBG jadi kejadian fatal</t>
+          <t>Prabowo dan PM Thailand bertemu empat mata di Istana Merdeka</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 17:10:19 +0700</t>
+          <t>Mon, 03 Aug 2026 17:49:52 +0700</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr">
         <is>
+          <t>Presiden Prabowo Subianto dan Perdana Menteri Thailand Anutin Charnvirakul menggelar pertemuan empat mata di Istana ...</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677828/prabowo-dan-pm-thailand-bertemu-empat-mata-di-istana-merdeka</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_5162.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Kepala BGN tingkatkan status keracunan MBG jadi kejadian fatal</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 17:10:19 +0700</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="inlineStr">
+        <is>
           <t>nya tidak dilanjutkan," ucap Sudaryono.
 Ia menegaskan BGN memberlakukan nol toleransi pada setiap status ...</t>
         </is>
       </c>
-      <c r="F358" t="inlineStr">
+      <c r="F359" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677743/kepala-bgn-tingkatkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
         </is>
       </c>
-      <c r="G358" t="inlineStr">
+      <c r="G359" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/ZAM02548_edit_2028523819372755.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>top-news</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>Harga minyak turun usai AS siap lanjutkan dialog dengan Iran</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 17:08:35 +0700</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr"/>
-      <c r="E359" t="inlineStr">
-        <is>
-          <t>Harga minyak turun lebih dari 5 persen, Senin, setelah Presiden Amerika Serikat Donald Trump ...</t>
-        </is>
-      </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677735/harga-minyak-turun-usai-as-siap-lanjutkan-dialog-dengan-iran</t>
-        </is>
-      </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/06/ilustrasi-isi-bensin-di-pom.jpg</t>
         </is>
       </c>
     </row>
@@ -12315,28 +12315,28 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Australia konfirmasi kematian massal pertama satwa akibat flu burung</t>
+          <t>Harga minyak turun usai AS siap lanjutkan dialog dengan Iran</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:48:50 +0700</t>
+          <t>Mon, 03 Aug 2026 17:08:35 +0700</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Australia mengonfirmasi kematian massal satwa liar pertama terkait flu burung H5 yang mematikan, dengan burung camar ...</t>
+          <t>Harga minyak turun lebih dari 5 persen, Senin, setelah Presiden Amerika Serikat Donald Trump ...</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677701/australia-konfirmasi-kematian-massal-pertama-satwa-akibat-flu-burung</t>
+          <t>https://www.antaranews.com/berita/5677735/harga-minyak-turun-usai-as-siap-lanjutkan-dialog-dengan-iran</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/26/Virus-flu-burung-penyakit-unggas.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/06/ilustrasi-isi-bensin-di-pom.jpg</t>
         </is>
       </c>
     </row>
@@ -12348,94 +12348,94 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Siklon 94 W,  waspada cuaca ekstrem &amp; gelombang tinggi di wilayah RI</t>
+          <t>Australia konfirmasi kematian massal pertama satwa akibat flu burung</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:30:38 +0700</t>
+          <t>Mon, 03 Aug 2026 16:48:50 +0700</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) mendeteksi pergerakan Bibit Siklon Tropis 94W di Laut Filipina ...</t>
+          <t>Australia mengonfirmasi kematian massal satwa liar pertama terkait flu burung H5 yang mematikan, dengan burung camar ...</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677641/siklon-94-w-waspada-cuaca-ekstrem-gelombang-tinggi-di-wilayah-ri</t>
+          <t>https://www.antaranews.com/berita/5677701/australia-konfirmasi-kematian-massal-pertama-satwa-akibat-flu-burung</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/27/1000395034.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/26/Virus-flu-burung-penyakit-unggas.jpg</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>photo, top-news</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Petani berbagi air sumur demi selamatkan tanaman tembakau</t>
+          <t>Siklon 94 W,  waspada cuaca ekstrem &amp; gelombang tinggi di wilayah RI</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:44:51 +0700</t>
+          <t>Mon, 03 Aug 2026 16:30:38 +0700</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Petani mengambil air dari sumur untuk menyiram tanaman tembakau di Lengkong, Nganjuk, Jawa Timur, Senin (3/8/2026). ...</t>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) mendeteksi pergerakan Bibit Siklon Tropis 94W di Laut Filipina ...</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5677428/petani-berbagi-air-sumur-demi-selamatkan-tanaman-tembakau</t>
+          <t>https://www.antaranews.com/berita/5677641/siklon-94-w-waspada-cuaca-ekstrem-gelombang-tinggi-di-wilayah-ri</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/petani-tembakau-berbagi-air-sumur-antisipasi-dampak-el-nino-030826-mm-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/27/1000395034.jpg</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>photo, top-news</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Nusron sebut banyak laut di Batam telah dikapling tanpa prosedur sah</t>
+          <t>Petani berbagi air sumur demi selamatkan tanaman tembakau</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:44:05 +0700</t>
+          <t>Mon, 03 Aug 2026 14:44:51 +0700</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Menteri Agraria dan Tata Ruang (ATR)/Kepala Badan Pertanahan Nasional (BPN) Nusron Wahid mengatakan, menerima banyak ...</t>
+          <t>Petani mengambil air dari sumur untuk menyiram tanaman tembakau di Lengkong, Nganjuk, Jawa Timur, Senin (3/8/2026). ...</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677425/nusron-sebut-banyak-laut-di-batam-telah-dikapling-tanpa-prosedur-sah</t>
+          <t>https://www.antaranews.com/foto/5677428/petani-berbagi-air-sumur-demi-selamatkan-tanaman-tembakau</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_142345.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/petani-tembakau-berbagi-air-sumur-antisipasi-dampak-el-nino-030826-mm-1.jpg</t>
         </is>
       </c>
     </row>
@@ -12447,28 +12447,28 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Menkomdigi panggil YouTube imbas temuan konten promosi vape sasar anak</t>
+          <t>Nusron sebut banyak laut di Batam telah dikapling tanpa prosedur sah</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:22:09 +0700</t>
+          <t>Mon, 03 Aug 2026 14:44:05 +0700</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid merencanakan pemanggilan terhadap platform digital YouTube ...</t>
+          <t>Menteri Agraria dan Tata Ruang (ATR)/Kepala Badan Pertanahan Nasional (BPN) Nusron Wahid mengatakan, menerima banyak ...</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677396/menkomdigi-panggil-youtube-imbas-temuan-konten-promosi-vape-sasar-anak</t>
+          <t>https://www.antaranews.com/berita/5677425/nusron-sebut-banyak-laut-di-batam-telah-dikapling-tanpa-prosedur-sah</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0225.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_142345.jpg</t>
         </is>
       </c>
     </row>
@@ -12480,28 +12480,28 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Kemnaker: Magang Nasional diharapkan menekan angka pengangguran muda</t>
+          <t>Menkomdigi panggil YouTube imbas temuan konten promosi vape sasar anak</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:37:57 +0700</t>
+          <t>Mon, 03 Aug 2026 14:22:09 +0700</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Kementerian Ketenagakerjaan (Kemnaker) mengatakan program Magang Nasional (MagangHub) untuk mempersiapkan kompetensi ...</t>
+          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid merencanakan pemanggilan terhadap platform digital YouTube ...</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677364/kemnaker-magang-nasional-diharapkan-menekan-angka-pengangguran-muda</t>
+          <t>https://www.antaranews.com/berita/5677396/menkomdigi-panggil-youtube-imbas-temuan-konten-promosi-vape-sasar-anak</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/ff63afaf-7778-47fe-833d-5a8068af9a51_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0225.jpg</t>
         </is>
       </c>
     </row>
@@ -12513,28 +12513,28 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Kemenag perkuat transformasi madrasah lewat revitalisasi-digitalisasi</t>
+          <t>Kemnaker: Magang Nasional diharapkan menekan angka pengangguran muda</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:36:36 +0700</t>
+          <t>Mon, 03 Aug 2026 13:37:57 +0700</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Menteri Agama (Menag) Nasaruddin Umar menegaskan transformasi madrasah terus diperkuat melalui revitalisasi ...</t>
+          <t>Kementerian Ketenagakerjaan (Kemnaker) mengatakan program Magang Nasional (MagangHub) untuk mempersiapkan kompetensi ...</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677363/kemenag-perkuat-transformasi-madrasah-lewat-revitalisasi-digitalisasi</t>
+          <t>https://www.antaranews.com/berita/5677364/kemnaker-magang-nasional-diharapkan-menekan-angka-pengangguran-muda</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/14/1000173935_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/ff63afaf-7778-47fe-833d-5a8068af9a51_1.jpeg</t>
         </is>
       </c>
     </row>
@@ -12546,28 +12546,28 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Lisensi IP Global Buka Peluang Bisnis Baru bagi Kreator Indonesia</t>
+          <t>Kemenag perkuat transformasi madrasah lewat revitalisasi-digitalisasi</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:34:30 +0700</t>
+          <t>Mon, 03 Aug 2026 13:36:36 +0700</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Wakil Menteri Ekonomi Kreatif Irene Umar mengatakan kolaborasi antara pemilik kekayaan intelektual (Intellectual ...</t>
+          <t>Menteri Agama (Menag) Nasaruddin Umar menegaskan transformasi madrasah terus diperkuat melalui revitalisasi ...</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677353/lisensi-ip-global-buka-peluang-bisnis-baru-bagi-kreator-indonesia</t>
+          <t>https://www.antaranews.com/berita/5677363/kemenag-perkuat-transformasi-madrasah-lewat-revitalisasi-digitalisasi</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000589873.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/14/1000173935_1.jpg</t>
         </is>
       </c>
     </row>
@@ -12579,28 +12579,28 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Nilai ekspor perdagangan RI Januari-Juni capai 140,81 miliar dolar AS</t>
+          <t>Lisensi IP Global Buka Peluang Bisnis Baru bagi Kreator Indonesia</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:16:17 +0700</t>
+          <t>Mon, 03 Aug 2026 13:34:30 +0700</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat nilai ekspor Indonesia secara kumulatif dari Januari-Juni 2026 mencapai 140,81 ...</t>
+          <t>Wakil Menteri Ekonomi Kreatif Irene Umar mengatakan kolaborasi antara pemilik kekayaan intelektual (Intellectual ...</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677315/nilai-ekspor-perdagangan-ri-januari-juni-capai-14081-miliar-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5677353/lisensi-ip-global-buka-peluang-bisnis-baru-bagi-kreator-indonesia</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/neraca-perdagangan-januari-mei-2026-surplus-2815779.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000589873.jpg</t>
         </is>
       </c>
     </row>
@@ -12612,28 +12612,28 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Korban KMP Mutiara Sentosa II dievakuasi ke Pelabuhan Tanjung Perak</t>
+          <t>Nilai ekspor perdagangan RI Januari-Juni capai 140,81 miliar dolar AS</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:06:15 +0700</t>
+          <t>Mon, 03 Aug 2026 13:16:17 +0700</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Tim SAR gabungan terus melakukan evakuasi korban terbakarnya KMP Mutiara Sentosa 2 ke darat, tepatnya ke Pelabuhan ...</t>
+          <t>Badan Pusat Statistik (BPS) mencatat nilai ekspor Indonesia secara kumulatif dari Januari-Juni 2026 mencapai 140,81 ...</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677297/korban-kmp-mutiara-sentosa-ii-dievakuasi-ke-pelabuhan-tanjung-perak</t>
+          <t>https://www.antaranews.com/berita/5677315/nilai-ekspor-perdagangan-ri-januari-juni-capai-14081-miliar-dolar-as</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/260821_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/neraca-perdagangan-januari-mei-2026-surplus-2815779.jpg</t>
         </is>
       </c>
     </row>
@@ -12645,28 +12645,28 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Aktor senior Diding Boneng meninggal dunia</t>
+          <t>Korban KMP Mutiara Sentosa II dievakuasi ke Pelabuhan Tanjung Perak</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:39:03 +0700</t>
+          <t>Mon, 03 Aug 2026 13:06:15 +0700</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Aktor sekaligus komedian tanah air, Zainal Abidin alias Diding Boneng dikabarkan meninggal dunia pada Senin (3/8) dalam ...</t>
+          <t>Tim SAR gabungan terus melakukan evakuasi korban terbakarnya KMP Mutiara Sentosa 2 ke darat, tepatnya ke Pelabuhan ...</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677209/aktor-senior-diding-boneng-meninggal-dunia</t>
+          <t>https://www.antaranews.com/berita/5677297/korban-kmp-mutiara-sentosa-ii-dievakuasi-ke-pelabuhan-tanjung-perak</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/26f1eb88-3301-4ae1-badd-bed5078fe3dd.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/260821_1.jpg</t>
         </is>
       </c>
     </row>
@@ -12678,28 +12678,28 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Seskab: Prabowo dorong sinergi pemerintah dan dunia usaha</t>
+          <t>Aktor senior Diding Boneng meninggal dunia</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:17:50 +0700</t>
+          <t>Mon, 03 Aug 2026 11:39:03 +0700</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Sekretaris Kabinet Teddy Indra Wijaya menyampaikan bahwa Presiden Prabowo Subianto menekankan pentingnya sinergi antara ...</t>
+          <t>Aktor sekaligus komedian tanah air, Zainal Abidin alias Diding Boneng dikabarkan meninggal dunia pada Senin (3/8) dalam ...</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677191/seskab-prabowo-dorong-sinergi-pemerintah-dan-dunia-usaha</t>
+          <t>https://www.antaranews.com/berita/5677209/aktor-senior-diding-boneng-meninggal-dunia</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0891_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/26f1eb88-3301-4ae1-badd-bed5078fe3dd.jpeg</t>
         </is>
       </c>
     </row>
@@ -12711,28 +12711,28 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Red Velvet bersiap kembali lewat EP baru "Velvet Summer"</t>
+          <t>Seskab: Prabowo dorong sinergi pemerintah dan dunia usaha</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:24:37 +0700</t>
+          <t>Mon, 03 Aug 2026 11:17:50 +0700</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Grup idola K-pop Red Velvet akan kembali lewat rilis mini album atau extended play (EP) baru bertajuk “Velvet ...</t>
+          <t>Sekretaris Kabinet Teddy Indra Wijaya menyampaikan bahwa Presiden Prabowo Subianto menekankan pentingnya sinergi antara ...</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677151/red-velvet-bersiap-kembali-lewat-ep-baru-velvet-summer</t>
+          <t>https://www.antaranews.com/berita/5677191/seskab-prabowo-dorong-sinergi-pemerintah-dan-dunia-usaha</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/ca97a3a8-aa17-45fc-be71-d36051dd9dcd.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0891_1.jpeg</t>
         </is>
       </c>
     </row>
@@ -12744,28 +12744,28 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Menaker pastikan komitmen pemerintah perkuat kesejahteraan pekerja</t>
+          <t>Red Velvet bersiap kembali lewat EP baru "Velvet Summer"</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:16:19 +0700</t>
+          <t>Mon, 03 Aug 2026 10:24:37 +0700</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Menteri Ketenagakerjaan (Menaker) Yassierli memastikan pemerintah berkomitmen untuk memperkuat kesejahteraan, ...</t>
+          <t>Grup idola K-pop Red Velvet akan kembali lewat rilis mini album atau extended play (EP) baru bertajuk “Velvet ...</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677148/menaker-pastikan-komitmen-pemerintah-perkuat-kesejahteraan-pekerja</t>
+          <t>https://www.antaranews.com/berita/5677151/red-velvet-bersiap-kembali-lewat-ep-baru-velvet-summer</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/09/20/pelepasan-peserta-pemagangan-ke-jepang-di-jawa-barat-2627513.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/ca97a3a8-aa17-45fc-be71-d36051dd9dcd.jpeg</t>
         </is>
       </c>
     </row>
@@ -12777,28 +12777,28 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>23 calon hakim agung dan ad hoc ikuti seleksi wawancara akhir</t>
+          <t>Menaker pastikan komitmen pemerintah perkuat kesejahteraan pekerja</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:15:01 +0700</t>
+          <t>Mon, 03 Aug 2026 10:16:19 +0700</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Sebanyak 23 orang calon hakim agung dan ad hoc Mahkamah Agung Tahun 2026 mengikuti seleksi wawancara tahap akhir di ...</t>
+          <t>Menteri Ketenagakerjaan (Menaker) Yassierli memastikan pemerintah berkomitmen untuk memperkuat kesejahteraan, ...</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677137/23-calon-hakim-agung-dan-ad-hoc-ikuti-seleksi-wawancara-akhir</t>
+          <t>https://www.antaranews.com/berita/5677148/menaker-pastikan-komitmen-pemerintah-perkuat-kesejahteraan-pekerja</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000012883_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/09/20/pelepasan-peserta-pemagangan-ke-jepang-di-jawa-barat-2627513.jpg</t>
         </is>
       </c>
     </row>
@@ -12810,28 +12810,28 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>BRIN perkuat kajian sungai bawah tanah di Kebumen untuk ketahanan air</t>
+          <t>23 calon hakim agung dan ad hoc ikuti seleksi wawancara akhir</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:57:19 +0700</t>
+          <t>Mon, 03 Aug 2026 10:15:01 +0700</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Badan Riset dan Inovasi Nasional (BRIN) memperkuat riset ketahanan air melalui pengembangan teknologi dan penelitian ...</t>
+          <t>Sebanyak 23 orang calon hakim agung dan ad hoc Mahkamah Agung Tahun 2026 mengikuti seleksi wawancara tahap akhir di ...</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677120/brin-perkuat-kajian-sungai-bawah-tanah-di-kebumen-untuk-ketahanan-air</t>
+          <t>https://www.antaranews.com/berita/5677137/23-calon-hakim-agung-dan-ad-hoc-ikuti-seleksi-wawancara-akhir</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1785706440-47672950-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000012883_1.jpg</t>
         </is>
       </c>
     </row>
@@ -12843,28 +12843,28 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Harga bensin turun pada pekan pertama Agustus</t>
+          <t>BRIN perkuat kajian sungai bawah tanah di Kebumen untuk ketahanan air</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:51:00 +0700</t>
+          <t>Mon, 03 Aug 2026 09:57:19 +0700</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Harga bahan bakar minyak (BBM) jenis bensin di stasiun pengisian bahan bakar umum (SPBU) Pertamina, Shell, dan bp ...</t>
+          <t>Badan Riset dan Inovasi Nasional (BRIN) memperkuat riset ketahanan air melalui pengembangan teknologi dan penelitian ...</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677109/harga-bensin-turun-pada-pekan-pertama-agustus</t>
+          <t>https://www.antaranews.com/berita/5677120/brin-perkuat-kajian-sungai-bawah-tanah-di-kebumen-untuk-ketahanan-air</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/10/02/penuruanan-harga-bbm-011024-aaa-7.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1785706440-47672950-1.jpg</t>
         </is>
       </c>
     </row>
@@ -12876,61 +12876,61 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Sean Gelael berbagi pengalaman di dunia balap ke pengunjung GIIAS 2026</t>
+          <t>Harga bensin turun pada pekan pertama Agustus</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:34:53 +0700</t>
+          <t>Mon, 03 Aug 2026 09:51:00 +0700</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Pembalap Indonesia Sean Gelael berbagi pengalamannya di dunia balap ke pengunjung GAIKINDO Indonesia International ...</t>
+          <t>Harga bahan bakar minyak (BBM) jenis bensin di stasiun pengisian bahan bakar umum (SPBU) Pertamina, Shell, dan bp ...</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677103/sean-gelael-berbagi-pengalaman-di-dunia-balap-ke-pengunjung-giias-2026</t>
+          <t>https://www.antaranews.com/berita/5677109/harga-bensin-turun-pada-pekan-pertama-agustus</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/16b70b87-326f-479a-a806-580ab846cc6f_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/10/02/penuruanan-harga-bbm-011024-aaa-7.jpg</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Cadangan devisa RI jadi 145 M dolar AS, BI sebut masih di level aman</t>
+          <t>Sean Gelael berbagi pengalaman di dunia balap ke pengunjung GIIAS 2026</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:52:44 +0700</t>
+          <t>Mon, 03 Aug 2026 09:34:53 +0700</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
-          <t>ANTARA - Bank Indonesia (BI) mengungkapkan cadangan devisa pada akhir Juli 2026 berada di posisi 145 miliar dolar AS. ...</t>
+          <t>Pembalap Indonesia Sean Gelael berbagi pengalamannya di dunia balap ke pengunjung GAIKINDO Indonesia International ...</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678347/cadangan-devisa-ri-jadi-145-m-dolar-as-bi-sebut-masih-di-level-aman</t>
+          <t>https://www.antaranews.com/berita/5677103/sean-gelael-berbagi-pengalaman-di-dunia-balap-ke-pengunjung-giias-2026</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_CADANGAN-DEVISA-RI-JADI-145-M-DOLAR-AS-BI-SEBUT-MASIH-DI-LEVEL-AMAN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/16b70b87-326f-479a-a806-580ab846cc6f_1.jpeg</t>
         </is>
       </c>
     </row>
@@ -12942,28 +12942,28 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>BI: Inflasi Juli terjaga berkat sinergi bank sentral dan pemerintah</t>
+          <t>Cadangan devisa RI jadi 145 M dolar AS, BI sebut masih di level aman</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:51:39 +0700</t>
+          <t>Mon, 03 Aug 2026 21:52:44 +0700</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Bank Indonesia (BI) memandang inflasi Indeks Harga Konsumen (IHK) pada Juli 2026 tetap terjaga dalam sasaran target, ...</t>
+          <t>ANTARA - Bank Indonesia (BI) mengungkapkan cadangan devisa pada akhir Juli 2026 berada di posisi 145 miliar dolar AS. ...</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678380/bi-inflasi-juli-terjaga-berkat-sinergi-bank-sentral-dan-pemerintah</t>
+          <t>https://www.antaranews.com/video/5678347/cadangan-devisa-ri-jadi-145-m-dolar-as-bi-sebut-masih-di-level-aman</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/07/WhatsApp-Image-2026-07-07-at-14.31.59_edited.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_CADANGAN-DEVISA-RI-JADI-145-M-DOLAR-AS-BI-SEBUT-MASIH-DI-LEVEL-AMAN.jpg</t>
         </is>
       </c>
     </row>
@@ -12975,28 +12975,28 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>BI: Kepemilikan SRBI oleh bank guna kelola likuiditas, bukan investasi</t>
+          <t>BI: Inflasi Juli terjaga berkat sinergi bank sentral dan pemerintah</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:35:49 +0700</t>
+          <t>Mon, 03 Aug 2026 21:51:39 +0700</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Bank Indonesia (BI) menegaskan bahwa Sekuritas Rupiah Bank Indonesia (SRBI) ditujukan sebagai instrumen pengelolaan ...</t>
+          <t>Bank Indonesia (BI) memandang inflasi Indeks Harga Konsumen (IHK) pada Juli 2026 tetap terjaga dalam sasaran target, ...</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678351/bi-kepemilikan-srbi-oleh-bank-guna-kelola-likuiditas-bukan-investasi</t>
+          <t>https://www.antaranews.com/berita/5678380/bi-inflasi-juli-terjaga-berkat-sinergi-bank-sentral-dan-pemerintah</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-21.22.00.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/07/WhatsApp-Image-2026-07-07-at-14.31.59_edited.jpg</t>
         </is>
       </c>
     </row>
@@ -13008,28 +13008,28 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>KSSK prakirakan pertumbuhan ekonomi RI pada 2026 capai 5,6-6 persen</t>
+          <t>BI: Kepemilikan SRBI oleh bank guna kelola likuiditas, bukan investasi</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:28:16 +0700</t>
+          <t>Mon, 03 Aug 2026 21:35:49 +0700</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Komite Stabilitas Sistem Keuangan (KSSK) memprakirakan ekonomi Indonesia sepanjang 2026 tumbuh dalam kisaran ...</t>
+          <t>Bank Indonesia (BI) menegaskan bahwa Sekuritas Rupiah Bank Indonesia (SRBI) ditujukan sebagai instrumen pengelolaan ...</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677935/kssk-prakirakan-pertumbuhan-ekonomi-ri-pada-2026-capai-56-6-persen</t>
+          <t>https://www.antaranews.com/berita/5678351/bi-kepemilikan-srbi-oleh-bank-guna-kelola-likuiditas-bukan-investasi</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.19.55.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-21.22.00.jpeg</t>
         </is>
       </c>
     </row>
@@ -13041,28 +13041,28 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Rupiah menguat dipengaruhi PMI manufaktur Indonesia naik jadi 50,2</t>
+          <t>KSSK prakirakan pertumbuhan ekonomi RI pada 2026 capai 5,6-6 persen</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:58:46 +0700</t>
+          <t>Mon, 03 Aug 2026 18:28:16 +0700</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Nilai tukar rupiah terhadap dolar AS pada penutupan perdagangan Senin, bergerak menguat 25 poin atau 0,14 persen ...</t>
+          <t>Komite Stabilitas Sistem Keuangan (KSSK) memprakirakan ekonomi Indonesia sepanjang 2026 tumbuh dalam kisaran ...</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677712/rupiah-menguat-dipengaruhi-pmi-manufaktur-indonesia-naik-jadi-502</t>
+          <t>https://www.antaranews.com/berita/5677935/kssk-prakirakan-pertumbuhan-ekonomi-ri-pada-2026-capai-56-6-persen</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/12/nilai-tukar-rupiah-melemah-115-poin-2788415.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.19.55.jpeg</t>
         </is>
       </c>
     </row>
@@ -13074,28 +13074,28 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>KSSK: Sistem keuangan TW-II tetap terjaga di tengah konflik geopolitik</t>
+          <t>Rupiah menguat dipengaruhi PMI manufaktur Indonesia naik jadi 50,2</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:26:03 +0700</t>
+          <t>Mon, 03 Aug 2026 16:58:46 +0700</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Komite Stabilitas Sistem Keuangan (KSSK) menilai kondisi fiskal, moneter dan sektor keuangan selama triwulan II 2026 ...</t>
+          <t>Nilai tukar rupiah terhadap dolar AS pada penutupan perdagangan Senin, bergerak menguat 25 poin atau 0,14 persen ...</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677625/kssk-sistem-keuangan-tw-ii-tetap-terjaga-di-tengah-konflik-geopolitik</t>
+          <t>https://www.antaranews.com/berita/5677712/rupiah-menguat-dipengaruhi-pmi-manufaktur-indonesia-naik-jadi-502</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/12/nilai-tukar-rupiah-melemah-115-poin-2788415.jpg</t>
         </is>
       </c>
     </row>
@@ -13107,28 +13107,28 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Menjaga pintu air perekonomian Indonesia</t>
+          <t>KSSK: Sistem keuangan TW-II tetap terjaga di tengah konflik geopolitik</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:04:40 +0700</t>
+          <t>Mon, 03 Aug 2026 16:26:03 +0700</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Bayangkan perekonomian Indonesia sebagai sebuah bendungan raksasa yang mengairi hamparan persawahan. Air yang mengalir ...</t>
+          <t>Komite Stabilitas Sistem Keuangan (KSSK) menilai kondisi fiskal, moneter dan sektor keuangan selama triwulan II 2026 ...</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677565/menjaga-pintu-air-perekonomian-indonesia</t>
+          <t>https://www.antaranews.com/berita/5677625/kssk-sistem-keuangan-tw-ii-tetap-terjaga-di-tengah-konflik-geopolitik</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/06/peringati-hari-bank-indonesia-doku-perkuat-ekosistem-pembayaran-2817675.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29.jpeg</t>
         </is>
       </c>
     </row>
@@ -13140,28 +13140,28 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Rupiah diperkirakan menguat seiring AS batalkan rencana serang Iran</t>
+          <t>Menjaga pintu air perekonomian Indonesia</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:12:26 +0700</t>
+          <t>Mon, 03 Aug 2026 16:04:40 +0700</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Analis Doo Financial Futures, Lukman Leong memperkirakan rupiah menguat seiring Amerika Serikat (AS) membatalkan ...</t>
+          <t>Bayangkan perekonomian Indonesia sebagai sebuah bendungan raksasa yang mengairi hamparan persawahan. Air yang mengalir ...</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677132/rupiah-diperkirakan-menguat-seiring-as-batalkan-rencana-serang-iran</t>
+          <t>https://www.antaranews.com/berita/5677565/menjaga-pintu-air-perekonomian-indonesia</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828847.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/06/peringati-hari-bank-indonesia-doku-perkuat-ekosistem-pembayaran-2817675.jpg</t>
         </is>
       </c>
     </row>
@@ -13173,28 +13173,28 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Rupiah pada Senin pagi melemah jadi Rp18.031 per dolar AS</t>
+          <t>Rupiah diperkirakan menguat seiring AS batalkan rencana serang Iran</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:05:50 +0700</t>
+          <t>Mon, 03 Aug 2026 10:12:26 +0700</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Nilai tukar rupiah pada Senin pagi bergerak melemah 9 poin atau 0,05 persen menjadi Rp18.031 per dolar AS dibandingkan ...</t>
+          <t>Analis Doo Financial Futures, Lukman Leong memperkirakan rupiah menguat seiring Amerika Serikat (AS) membatalkan ...</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677063/rupiah-pada-senin-pagi-melemah-jadi-rp18031-per-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5677132/rupiah-diperkirakan-menguat-seiring-as-batalkan-rencana-serang-iran</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828847.jpg</t>
         </is>
       </c>
     </row>
@@ -13206,28 +13206,28 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Komisi XI: PFII peluang RI tangkap momentum perpindahan modal global</t>
+          <t>Rupiah pada Senin pagi melemah jadi Rp18.031 per dolar AS</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:53:34 +0700</t>
+          <t>Mon, 03 Aug 2026 09:05:50 +0700</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Wakil Ketua Komisi XI DPR RI Mohamad Hekal mengatakan percepatan pembentukan Pusat Finansial Internasional Indonesia ...</t>
+          <t>Nilai tukar rupiah pada Senin pagi bergerak melemah 9 poin atau 0,05 persen menjadi Rp18.031 per dolar AS dibandingkan ...</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676995/komisi-xi-pfii-peluang-ri-tangkap-momentum-perpindahan-modal-global</t>
+          <t>https://www.antaranews.com/berita/5677063/rupiah-pada-senin-pagi-melemah-jadi-rp18031-per-dolar-as</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Saham-dan-oblogasi.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
         </is>
       </c>
     </row>
@@ -13239,61 +13239,61 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>BUMA International Group bukukan pertumbuhan EBITDA semester I/2026</t>
+          <t>Komisi XI: PFII peluang RI tangkap momentum perpindahan modal global</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:17:40 +0700</t>
+          <t>Mon, 03 Aug 2026 06:53:34 +0700</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr">
         <is>
-          <t>PT BUMA Internasional Gorup membukukan pertumbuhan EBITDA pada semester pertama 2026 (1H26) di tengah penurunan ...</t>
+          <t>Wakil Ketua Komisi XI DPR RI Mohamad Hekal mengatakan percepatan pembentukan Pusat Finansial Internasional Indonesia ...</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676967/buma-international-group-bukukan-pertumbuhan-ebitda-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5676995/komisi-xi-pfii-peluang-ri-tangkap-momentum-perpindahan-modal-global</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/buma.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Saham-dan-oblogasi.jpg</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Menteri PKP tegaskan KUR Perumahan perkuat ekonomi keluarga</t>
+          <t>BUMA International Group bukukan pertumbuhan EBITDA semester I/2026</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:47:11 +0700</t>
+          <t>Mon, 03 Aug 2026 06:17:40 +0700</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Menteri Perumahan dan Kawasan Permukiman (PKP) Maruarar Sirait menegaskan bahwa Kredit Usaha Rakyat (KUR) Perumahan ...</t>
+          <t>PT BUMA Internasional Gorup membukukan pertumbuhan EBITDA pada semester pertama 2026 (1H26) di tengah penurunan ...</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678465/menteri-pkp-tegaskan-kur-perumahan-perkuat-ekonomi-keluarga</t>
+          <t>https://www.antaranews.com/berita/5676967/buma-international-group-bukukan-pertumbuhan-ebitda-semester-i-2026</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1321013.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/buma.jpg</t>
         </is>
       </c>
     </row>
@@ -13305,28 +13305,28 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Ekonom: Inflasi mereda, semester II jadi momentum jaga keseimbangan</t>
+          <t>Menteri PKP tegaskan KUR Perumahan perkuat ekonomi keluarga</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:34:25 +0700</t>
+          <t>Mon, 03 Aug 2026 22:47:11 +0700</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Kepala Ekonom Trimegah Sekuritas Indonesia Fakhrul Fulvian menilai semester II-2026 menjadi momentum untuk menjaga ...</t>
+          <t>Menteri Perumahan dan Kawasan Permukiman (PKP) Maruarar Sirait menegaskan bahwa Kredit Usaha Rakyat (KUR) Perumahan ...</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678439/ekonom-inflasi-mereda-semester-ii-jadi-momentum-jaga-keseimbangan</t>
+          <t>https://www.antaranews.com/berita/5678465/menteri-pkp-tegaskan-kur-perumahan-perkuat-ekonomi-keluarga</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/01/21/IMG_2637.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1321013.jpg</t>
         </is>
       </c>
     </row>
@@ -13338,28 +13338,28 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Pemkab Aceh Tenggara batasi pembelian BBM untuk cegah penimbunan</t>
+          <t>Ekonom: Inflasi mereda, semester II jadi momentum jaga keseimbangan</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:25:13 +0700</t>
+          <t>Mon, 03 Aug 2026 22:34:25 +0700</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Pemerintah Kabupaten Aceh Tenggara bersama Forkopimda setempat saat ini telah melakukan pembatasan pembelian bahan ...</t>
+          <t>Kepala Ekonom Trimegah Sekuritas Indonesia Fakhrul Fulvian menilai semester II-2026 menjadi momentum untuk menjaga ...</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678431/pemkab-aceh-tenggara-batasi-pembelian-bbm-untuk-cegah-penimbunan</t>
+          <t>https://www.antaranews.com/berita/5678439/ekonom-inflasi-mereda-semester-ii-jadi-momentum-jaga-keseimbangan</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/20260803-Bupati-Aceh-Tenggara-HM-Salim-Fakhry.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/01/21/IMG_2637.jpeg</t>
         </is>
       </c>
     </row>
@@ -13371,28 +13371,28 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>MTI dorong kemudahan transaksi nirsentuh di MRT Jakarta</t>
+          <t>Pemkab Aceh Tenggara batasi pembelian BBM untuk cegah penimbunan</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:24:07 +0700</t>
+          <t>Mon, 03 Aug 2026 22:25:13 +0700</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
       <c r="E392" t="inlineStr">
         <is>
-          <t>PT Mitra Transaksi Indonesia (MTI) atau YOKKE mendukung penerapan sistem pembayaran kartu nirsentuh berbasis Europay, ...</t>
+          <t>Pemerintah Kabupaten Aceh Tenggara bersama Forkopimda setempat saat ini telah melakukan pembatasan pembelian bahan ...</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678427/mti-dorong-kemudahan-transaksi-nirsentuh-di-mrt-jakarta</t>
+          <t>https://www.antaranews.com/berita/5678431/pemkab-aceh-tenggara-batasi-pembelian-bbm-untuk-cegah-penimbunan</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.59.08.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/20260803-Bupati-Aceh-Tenggara-HM-Salim-Fakhry.jpeg</t>
         </is>
       </c>
     </row>
@@ -13404,28 +13404,28 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Gubernur tegaskan Sumut siap jadi pusat fashion Indonesia lewat wastra</t>
+          <t>MTI dorong kemudahan transaksi nirsentuh di MRT Jakarta</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:37:04 +0700</t>
+          <t>Mon, 03 Aug 2026 22:24:07 +0700</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Gubernur Sumatera Utara (Sumut) Bobby Nasution menegaskan kesiapan Provinsi Sumut menjadi salah satu pusat fashion ...</t>
+          <t>PT Mitra Transaksi Indonesia (MTI) atau YOKKE mendukung penerapan sistem pembayaran kartu nirsentuh berbasis Europay, ...</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678355/gubernur-tegaskan-sumut-siap-jadi-pusat-fashion-indonesia-lewat-wastra</t>
+          <t>https://www.antaranews.com/berita/5678427/mti-dorong-kemudahan-transaksi-nirsentuh-di-mrt-jakarta</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001029105.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.59.08.jpeg</t>
         </is>
       </c>
     </row>
@@ -13437,28 +13437,28 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Kapal BBM bermuatan 7.600 kiloliter masuk Lombok</t>
+          <t>Gubernur tegaskan Sumut siap jadi pusat fashion Indonesia lewat wastra</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:32:28 +0700</t>
+          <t>Mon, 03 Aug 2026 21:37:04 +0700</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr">
         <is>
-          <t>PT Pertamina Patra Niaga mendatangkan kapal pengangkut bahan bakar minyak (BBM) dengan total muatan 7.600 kiloliter ...</t>
+          <t>Gubernur Sumatera Utara (Sumut) Bobby Nasution menegaskan kesiapan Provinsi Sumut menjadi salah satu pusat fashion ...</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678341/kapal-bbm-bermuatan-7600-kiloliter-masuk-lombok</t>
+          <t>https://www.antaranews.com/berita/5678355/gubernur-tegaskan-sumut-siap-jadi-pusat-fashion-indonesia-lewat-wastra</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001432720.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001029105.jpg</t>
         </is>
       </c>
     </row>
@@ -13470,28 +13470,28 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Whoosh-kereta api dominasi jalur masuk wisatawan mancanegara di Jabar</t>
+          <t>Kapal BBM bermuatan 7.600 kiloliter masuk Lombok</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:28:59 +0700</t>
+          <t>Mon, 03 Aug 2026 21:32:28 +0700</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Integrasi transportasi berbasis rel seperti Kereta Cepat Whoosh dan kereta api (KA) konvensional kian mengukuhkan ...</t>
+          <t>PT Pertamina Patra Niaga mendatangkan kapal pengangkut bahan bakar minyak (BBM) dengan total muatan 7.600 kiloliter ...</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678332/whoosh-kereta-api-dominasi-jalur-masuk-wisatawan-mancanegara-di-jabar</t>
+          <t>https://www.antaranews.com/berita/5678341/kapal-bbm-bermuatan-7600-kiloliter-masuk-lombok</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1002076644.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001432720.jpg</t>
         </is>
       </c>
     </row>

--- a/data/berita_antara_2026-08-03.xlsx
+++ b/data/berita_antara_2026-08-03.xlsx
@@ -11060,28 +11060,28 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Chelsea umumkan transfer gelandang Inggris Jordan Henderson</t>
+          <t>Presiden Prabowo terima kunjungan PM Thailand di Istana Merdeka</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:59:34 +0700</t>
+          <t>Mon, 03 Aug 2026 22:59:27 +0700</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Chelsea resmi mengumumkan kedatangan gelandang senior asal Inggris Jordan Henderson dengan status bebas transfer ...</t>
+          <t>ANTARA - Presiden Prabowo Subianto menerima kunjungan resmi Perdana Menteri Thailand Anutin Charnvirakul di Istana ...</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678548/chelsea-umumkan-transfer-gelandang-inggris-jordan-henderson</t>
+          <t>https://www.antaranews.com/video/5678461/presiden-prabowo-terima-kunjungan-pm-thailand-di-istana-merdeka</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000042505.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PRESIDEN-PRABOWO-TERIMA-KUNJUNGAN-PM-THAILAND-DI-ISTANA-MERDEKA.jpg</t>
         </is>
       </c>
     </row>
@@ -11093,28 +11093,28 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Nguyen Xuan Son ungkap alasan tak jadi starter saat kalahkan Indonesia</t>
+          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:56:45 +0700</t>
+          <t>Mon, 03 Aug 2026 22:58:38 +0700</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Penyerang Timnas Vietnam Nguyen Xuan Son mengungkapkan alasan dirinya tidak dimainkan sebagai starter saat timnya ...</t>
+          <t>ANTARA - Badan Pencarian dan Pertolongan Nasional (Basarnas) mengerahkan satu unit kapal untuk menjemput 66 korban ...</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678547/nguyen-xuan-son-ungkap-alasan-tak-jadi-starter-saat-kalahkan-indonesia</t>
+          <t>https://www.antaranews.com/video/5678472/basarnas-jemput-66-korban-km-mutiara-sentosa-ii-dari-masalembu</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1003314030.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BASARNAS-JEMPUT-66-KORBAN-KM-MUTIARA-SENTOSA-II-DARI-MASALEMBU.jpg</t>
         </is>
       </c>
     </row>
@@ -11126,61 +11126,61 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
+          <t>Timnas Indonesia dibungkam Vietnam 0-3</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:55:47 +0700</t>
+          <t>Mon, 03 Aug 2026 22:54:01 +0700</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
-          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ...</t>
+          <t>Timnas Indonesia dibungkam Vietnam 0-3 di kandang pada laga lanjutan Grup A Piala AFF 2026 di Stadion Pakansari, Bogor, ...</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+          <t>https://www.antaranews.com/berita/5678480/timnas-indonesia-dibungkam-vietnam-0-3</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Timnas-Indonesia-lawan-Vietnam-030826-Bay-21a.jpg</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>BPS kaitkan kenaikan TPK hotel bintang dengan kualitas wisman</t>
+          <t>Chelsea umumkan transfer gelandang Inggris Jordan Henderson</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:53:51 +0700</t>
+          <t>Mon, 03 Aug 2026 23:59:34 +0700</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) Bali mengaitkan kenaikan tingkat penghunian kamar (TPK) hotel bintang pada Juni 2026 dengan ...</t>
+          <t>Chelsea resmi mengumumkan kedatangan gelandang senior asal Inggris Jordan Henderson dengan status bebas transfer ...</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678543/bps-kaitkan-kenaikan-tpk-hotel-bintang-dengan-kualitas-wisman</t>
+          <t>https://www.antaranews.com/berita/5678548/chelsea-umumkan-transfer-gelandang-inggris-jordan-henderson</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0332.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000042505.jpg</t>
         </is>
       </c>
     </row>
@@ -11192,61 +11192,61 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Jogja Run'nShine 2026 targetkan diikuti 3.500 pelari</t>
+          <t>Nguyen Xuan Son ungkap alasan tak jadi starter saat kalahkan Indonesia</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:52:29 +0700</t>
+          <t>Mon, 03 Aug 2026 23:56:45 +0700</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Pergelaran Jogja Run'nShine 2026 menargetkan diikuti sebanyak 3.500 pelari dengan memberikan pengalaman konsep ...</t>
+          <t>Penyerang Timnas Vietnam Nguyen Xuan Son mengungkapkan alasan dirinya tidak dimainkan sebagai starter saat timnya ...</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678540/jogja-runnshine-2026-targetkan-diikuti-3500-pelari</t>
+          <t>https://www.antaranews.com/berita/5678547/nguyen-xuan-son-ungkap-alasan-tak-jadi-starter-saat-kalahkan-indonesia</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0103.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1003314030.jpg</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Jenama perkakas otomotif Tekiro dapat pengakuan Guinnes World Records</t>
+          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:47:06 +0700</t>
+          <t>Mon, 03 Aug 2026 23:55:47 +0700</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Jenama perkakas otomotif Tekiro mendapat pengakuan dari Guiness World Records berkat ...</t>
+          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ...</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5678535/jenama-perkakas-otomotif-tekiro-dapat-pengakuan-guinnes-world-records</t>
+          <t>https://www.antaranews.com/video/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-02-at-15.34.09-1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
         </is>
       </c>
     </row>
@@ -11258,94 +11258,94 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Pemkab Sleman dukung kejuaraan dragbike tingkatkan ekonomi masyarakat</t>
+          <t>BPS kaitkan kenaikan TPK hotel bintang dengan kualitas wisman</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:42:42 +0700</t>
+          <t>Mon, 03 Aug 2026 23:53:51 +0700</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Pemerintah Kabupaten Sleman, Daerah Istimewa Yogyakarta, mendukung penuh penyelenggaraan Kejuaraan Dragbike Super ...</t>
+          <t>Badan Pusat Statistik (BPS) Bali mengaitkan kenaikan tingkat penghunian kamar (TPK) hotel bintang pada Juni 2026 dengan ...</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678532/pemkab-sleman-dukung-kejuaraan-dragbike-tingkatkan-ekonomi-masyarakat</t>
+          <t>https://www.antaranews.com/berita/5678543/bps-kaitkan-kenaikan-tpk-hotel-bintang-dengan-kualitas-wisman</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000029422.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0332.jpeg</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>GMR nilai akses penerbangan langsung buka peluang ekonomi RI-India</t>
+          <t>Jogja Run'nShine 2026 targetkan diikuti 3.500 pelari</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:41:32 +0700</t>
+          <t>Mon, 03 Aug 2026 23:52:29 +0700</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
-          <t>GMR Group, perusahaan multinasional India yang bergerak di bidang infrastruktur, menilai akses penerbangan langsung ...</t>
+          <t>Pergelaran Jogja Run'nShine 2026 menargetkan diikuti sebanyak 3.500 pelari dengan memberikan pengalaman konsep ...</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678529/gmr-nilai-akses-penerbangan-langsung-buka-peluang-ekonomi-ri-india</t>
+          <t>https://www.antaranews.com/berita/5678540/jogja-runnshine-2026-targetkan-diikuti-3500-pelari</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/DSF3021.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0103.jpg</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PSSI raup dana Rp722 miliar dalam laporan keuangan tahunan</t>
+          <t>Jenama perkakas otomotif Tekiro dapat pengakuan Guinnes World Records</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:37:46 +0700</t>
+          <t>Mon, 03 Aug 2026 23:47:06 +0700</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir menyebut organisasinya meraup dana senilai Rp722 ...</t>
+          <t>Jenama perkakas otomotif Tekiro mendapat pengakuan dari Guiness World Records berkat ...</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678528/pssi-raup-dana-rp722-miliar-dalam-laporan-keuangan-tahunan</t>
+          <t>https://otomotif.antaranews.com/berita/5678535/jenama-perkakas-otomotif-tekiro-dapat-pengakuan-guinnes-world-records</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0098_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-02-at-15.34.09-1.jpeg</t>
         </is>
       </c>
     </row>
@@ -11357,61 +11357,61 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Otorita kolaborasi PNM untuk pengembangan ekonomi masyarakat IKN</t>
+          <t>Pemkab Sleman dukung kejuaraan dragbike tingkatkan ekonomi masyarakat</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:30:50 +0700</t>
+          <t>Mon, 03 Aug 2026 23:42:42 +0700</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Otorita Ibu Kota Nusantara (IKN) melakukan kolaborasi dengan PT Permodalan Nasional Madani (Persero) untuk pengembangan ...</t>
+          <t>Pemerintah Kabupaten Sleman, Daerah Istimewa Yogyakarta, mendukung penuh penyelenggaraan Kejuaraan Dragbike Super ...</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678525/otorita-kolaborasi-pnm-untuk-pengembangan-ekonomi-masyarakat-ikn</t>
+          <t>https://www.antaranews.com/berita/5678532/pemkab-sleman-dukung-kejuaraan-dragbike-tingkatkan-ekonomi-masyarakat</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0012_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000029422.jpg</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>DPR: Wacana Prabowo jembatani dialog Korea sesuai politik bebas aktif</t>
+          <t>GMR nilai akses penerbangan langsung buka peluang ekonomi RI-India</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:30:13 +0700</t>
+          <t>Mon, 03 Aug 2026 23:41:32 +0700</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Wakil Ketua Komisi I DPR RI Dave Laksono menilai wacana Presiden Prabowo Subianto untuk menjembatani dialog antara ...</t>
+          <t>GMR Group, perusahaan multinasional India yang bergerak di bidang infrastruktur, menilai akses penerbangan langsung ...</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678521/dpr-wacana-prabowo-jembatani-dialog-korea-sesuai-politik-bebas-aktif</t>
+          <t>https://www.antaranews.com/berita/5678529/gmr-nilai-akses-penerbangan-langsung-buka-peluang-ekonomi-ri-india</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/22/IMG_20260422_175322.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/DSF3021.jpeg</t>
         </is>
       </c>
     </row>
@@ -11423,28 +11423,28 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Kongres PSSI sepakati pemilihan pengurus mundur ke Juli 2027</t>
+          <t>PSSI raup dana Rp722 miliar dalam laporan keuangan tahunan</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:30:00 +0700</t>
+          <t>Mon, 03 Aug 2026 23:37:46 +0700</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>ANTARA - Kongres Biasa PSSI 2026 menyepakati perubahan jadwal Kongres Pemilihan Pengurus PSSI 2027 dari semula Mei ...</t>
+          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir menyebut organisasinya meraup dana senilai Rp722 ...</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678395/kongres-pssi-sepakati-pemilihan-pengurus-mundur-ke-juli-2027</t>
+          <t>https://www.antaranews.com/berita/5678528/pssi-raup-dana-rp722-miliar-dalam-laporan-keuangan-tahunan</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KONGRES-PSSI-SEPAKATI-PEMILIHAN-PENGURUS-MUNDUR-KE-JULI-2027.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0098_1.jpg</t>
         </is>
       </c>
     </row>
@@ -11456,28 +11456,28 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Toyota Astra Motor perkenalkan Hilux generasi ke-9</t>
+          <t>Otorita kolaborasi PNM untuk pengembangan ekonomi masyarakat IKN</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:25:20 +0700</t>
+          <t>Mon, 03 Aug 2026 23:30:50 +0700</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>PT Toyota Astra Motor (TAM) memperkenalkan Hilux generasi ke-9 untuk mendukung pemenuhan kebutuhan operasional industri ...</t>
+          <t>Otorita Ibu Kota Nusantara (IKN) melakukan kolaborasi dengan PT Permodalan Nasional Madani (Persero) untuk pengembangan ...</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5678519/toyota-astra-motor-perkenalkan-hilux-generasi-ke-9</t>
+          <t>https://www.antaranews.com/berita/5678525/otorita-kolaborasi-pnm-untuk-pengembangan-ekonomi-masyarakat-ikn</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/photo_6307309656757440820_w-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0012_1.jpg</t>
         </is>
       </c>
     </row>
@@ -11489,28 +11489,28 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Sudin PPAPP Jakbar sosialisasikan Sekolah Siaga Kependudukan</t>
+          <t>DPR: Wacana Prabowo jembatani dialog Korea sesuai politik bebas aktif</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:24:33 +0700</t>
+          <t>Mon, 03 Aug 2026 23:30:13 +0700</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Suku Dinas Pemberdayaan, Perlindungan Anak, dan Pengendalian Penduduk (Sudin PPAPP) Jakarta Barat (Jakbar) menggelar ...</t>
+          <t>Wakil Ketua Komisi I DPR RI Dave Laksono menilai wacana Presiden Prabowo Subianto untuk menjembatani dialog antara ...</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678515/sudin-ppapp-jakbar-sosialisasikan-sekolah-siaga-kependudukan</t>
+          <t>https://www.antaranews.com/berita/5678521/dpr-wacana-prabowo-jembatani-dialog-korea-sesuai-politik-bebas-aktif</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0031_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/22/IMG_20260422_175322.jpg</t>
         </is>
       </c>
     </row>
@@ -11522,28 +11522,28 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Klasemen Grup A Piala AFF : Timnas Indonesia turun ke peringkat tiga</t>
+          <t>Kongres PSSI sepakati pemilihan pengurus mundur ke Juli 2027</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:23:51 +0700</t>
+          <t>Mon, 03 Aug 2026 23:30:00 +0700</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Timnas Indonesia turun ke peringkat ketiga klasemen sementara Grup A Piala AFF 2026 setelah menelan kekalahan 0-3 dari ...</t>
+          <t>ANTARA - Kongres Biasa PSSI 2026 menyepakati perubahan jadwal Kongres Pemilihan Pengurus PSSI 2027 dari semula Mei ...</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678512/klasemen-grup-a-piala-aff-timnas-indonesia-turun-ke-peringkat-tiga</t>
+          <t>https://www.antaranews.com/video/5678395/kongres-pssi-sepakati-pemilihan-pengurus-mundur-ke-juli-2027</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833516.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KONGRES-PSSI-SEPAKATI-PEMILIHAN-PENGURUS-MUNDUR-KE-JULI-2027.jpg</t>
         </is>
       </c>
     </row>
@@ -11555,61 +11555,61 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>NTB menargetkan penonton MotoGP Mandalika tembus 140 ribu</t>
+          <t>Toyota Astra Motor perkenalkan Hilux generasi ke-9</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:23:01 +0700</t>
+          <t>Mon, 03 Aug 2026 23:25:20 +0700</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Pemerintah Provinsi Nusa Tenggara Barat menargetkan jumlah penonton MotoGP di Sirkuit Mandalika pada 9-11 Oktober 2026 ...</t>
+          <t>PT Toyota Astra Motor (TAM) memperkenalkan Hilux generasi ke-9 untuk mendukung pemenuhan kebutuhan operasional industri ...</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678508/ntb-menargetkan-penonton-motogp-mandalika-tembus-140-ribu</t>
+          <t>https://otomotif.antaranews.com/berita/5678519/toyota-astra-motor-perkenalkan-hilux-generasi-ke-9</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260109-WA0024_copy_1280x797.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/photo_6307309656757440820_w-1.jpg</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Bulog: Margin naik jadi 7 persen, dukungan Presiden kawal swasembada</t>
+          <t>Sudin PPAPP Jakbar sosialisasikan Sekolah Siaga Kependudukan</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:19:51 +0700</t>
+          <t>Mon, 03 Aug 2026 23:24:33 +0700</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Direktur Utama Perum Bulog Ahmad Rizal Ramdhani menegaskan kenaikan margin fee menjadi 7 persen bentuk dukungan ...</t>
+          <t>Suku Dinas Pemberdayaan, Perlindungan Anak, dan Pengendalian Penduduk (Sudin PPAPP) Jakarta Barat (Jakbar) menggelar ...</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678504/bulog-margin-naik-jadi-7-persen-dukungan-presiden-kawal-swasembada</t>
+          <t>https://www.antaranews.com/berita/5678515/sudin-ppapp-jakbar-sosialisasikan-sekolah-siaga-kependudukan</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/14C1B7CB-9D6F-49B9-9CD1-E40DD76E851C.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0031_1.jpg</t>
         </is>
       </c>
     </row>
@@ -11621,94 +11621,94 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Turkiye sebut serangan Israel sabotase upaya damai di Gaza</t>
+          <t>Klasemen Grup A Piala AFF : Timnas Indonesia turun ke peringkat tiga</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:18:30 +0700</t>
+          <t>Mon, 03 Aug 2026 23:23:51 +0700</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Pemerintah Turkiye pada Senin menilai serangan Israel di Jalur Gaza telah menghambat berbagai inisiatif diplomatik yang ...</t>
+          <t>Timnas Indonesia turun ke peringkat ketiga klasemen sementara Grup A Piala AFF 2026 setelah menelan kekalahan 0-3 dari ...</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678500/turkiye-sebut-serangan-israel-sabotase-upaya-damai-di-gaza</t>
+          <t>https://www.antaranews.com/berita/5678512/klasemen-grup-a-piala-aff-timnas-indonesia-turun-ke-peringkat-tiga</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/thumbs_b_c_186832d7ab4775afec853057c8952c3d.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833516.jpg</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Purbaya pastikan tak ada lagi perdebatan soal penarikan SAL dari bank</t>
+          <t>NTB menargetkan penonton MotoGP Mandalika tembus 140 ribu</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:15:59 +0700</t>
+          <t>Mon, 03 Aug 2026 23:23:01 +0700</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Menteri Keuangan (Menkeu), Purbaya Yudhi Sadewa memastikan tidak ada lagi perdebatan mengenai penarikan dana ...</t>
+          <t>Pemerintah Provinsi Nusa Tenggara Barat menargetkan jumlah penonton MotoGP di Sirkuit Mandalika pada 9-11 Oktober 2026 ...</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678499/purbaya-pastikan-tak-ada-lagi-perdebatan-soal-penarikan-sal-dari-bank</t>
+          <t>https://www.antaranews.com/berita/5678508/ntb-menargetkan-penonton-motogp-mandalika-tembus-140-ribu</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-23.02.47.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260109-WA0024_copy_1280x797.jpg</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Tim 9 Kejagung didesak usut pemilik uang-emas di rumah eks Jampidsus</t>
+          <t>Bulog: Margin naik jadi 7 persen, dukungan Presiden kawal swasembada</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:10:43 +0700</t>
+          <t>Mon, 03 Aug 2026 23:19:51 +0700</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Tim 9 Kejaksaan Agung didesak mengusut tuntas pemilik uang tunai senilai Rp476 miliar dan emas batangan seberat 74 ...</t>
+          <t>Direktur Utama Perum Bulog Ahmad Rizal Ramdhani menegaskan kenaikan margin fee menjadi 7 persen bentuk dukungan ...</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678495/tim-9-kejagung-didesak-usut-pemilik-uang-emas-di-rumah-eks-jampidsus</t>
+          <t>https://www.antaranews.com/berita/5678504/bulog-margin-naik-jadi-7-persen-dukungan-presiden-kawal-swasembada</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/1000175632.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/14C1B7CB-9D6F-49B9-9CD1-E40DD76E851C.jpeg</t>
         </is>
       </c>
     </row>
@@ -11720,61 +11720,61 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Kemenbud hadirkan GBN untuk membina talenta seni musik nasional</t>
+          <t>Turkiye sebut serangan Israel sabotase upaya damai di Gaza</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:07:01 +0700</t>
+          <t>Mon, 03 Aug 2026 23:18:30 +0700</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Kementerian Kebudayaan (Kemenbud) menghadirkan program pembinaan talenta seni musik nasional yang mempertemukan ...</t>
+          <t>Pemerintah Turkiye pada Senin menilai serangan Israel di Jalur Gaza telah menghambat berbagai inisiatif diplomatik yang ...</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678491/kemenbud-hadirkan-gbn-untuk-membina-talenta-seni-musik-nasional</t>
+          <t>https://www.antaranews.com/berita/5678500/turkiye-sebut-serangan-israel-sabotase-upaya-damai-di-gaza</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-20.28.05.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/thumbs_b_c_186832d7ab4775afec853057c8952c3d.jpg</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Wamen ATR: Ujian PPAT upaya berikan layanan yang baik</t>
+          <t>Purbaya pastikan tak ada lagi perdebatan soal penarikan SAL dari bank</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:05:29 +0700</t>
+          <t>Mon, 03 Aug 2026 23:15:59 +0700</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Wakil Menteri Agraria dan Tata Ruang/Wakil Kepala Badan Pertanahan Nasional (Wamen ATR/Waka BPN) Ossy Dermawan ...</t>
+          <t>Menteri Keuangan (Menkeu), Purbaya Yudhi Sadewa memastikan tidak ada lagi perdebatan mengenai penarikan dana ...</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678489/wamen-atr-ujian-ppat-upaya-berikan-layanan-yang-baik</t>
+          <t>https://www.antaranews.com/berita/5678499/purbaya-pastikan-tak-ada-lagi-perdebatan-soal-penarikan-sal-dari-bank</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_223512.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-23.02.47.jpeg</t>
         </is>
       </c>
     </row>
@@ -11786,28 +11786,28 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>PBSI buka suara soal absennya Jafar/Felisha di Kejuaraan Dunia BWF</t>
+          <t>Tim 9 Kejagung didesak usut pemilik uang-emas di rumah eks Jampidsus</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:03:05 +0700</t>
+          <t>Mon, 03 Aug 2026 23:10:43 +0700</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Pengurus Pusat PBSI menyatakan absennya dua pasangan ganda campuran Indonesia Jafar Hidayatullah/Felisha Alberta ...</t>
+          <t>Tim 9 Kejaksaan Agung didesak mengusut tuntas pemilik uang tunai senilai Rp476 miliar dan emas batangan seberat 74 ...</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678487/pbsi-buka-suara-soal-absennya-jafar-felisha-di-kejuaraan-dunia-bwf</t>
+          <t>https://www.antaranews.com/berita/5678495/tim-9-kejagung-didesak-usut-pemilik-uang-emas-di-rumah-eks-jampidsus</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/06/IMG_20251127_205351.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/1000175632.jpg</t>
         </is>
       </c>
     </row>
@@ -11819,127 +11819,127 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Presiden Prabowo terima kunjungan PM Thailand di Istana Merdeka</t>
+          <t>Kemenbud hadirkan GBN untuk membina talenta seni musik nasional</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:59:27 +0700</t>
+          <t>Mon, 03 Aug 2026 23:07:01 +0700</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Prabowo Subianto menerima kunjungan resmi Perdana Menteri Thailand Anutin Charnvirakul di Istana ...</t>
+          <t>Kementerian Kebudayaan (Kemenbud) menghadirkan program pembinaan talenta seni musik nasional yang mempertemukan ...</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678461/presiden-prabowo-terima-kunjungan-pm-thailand-di-istana-merdeka</t>
+          <t>https://www.antaranews.com/berita/5678491/kemenbud-hadirkan-gbn-untuk-membina-talenta-seni-musik-nasional</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PRESIDEN-PRABOWO-TERIMA-KUNJUNGAN-PM-THAILAND-DI-ISTANA-MERDEKA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-20.28.05.jpeg</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
+          <t>Wamen ATR: Ujian PPAT upaya berikan layanan yang baik</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:58:38 +0700</t>
+          <t>Mon, 03 Aug 2026 23:05:29 +0700</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
-          <t>ANTARA - Badan Pencarian dan Pertolongan Nasional (Basarnas) mengerahkan satu unit kapal untuk menjemput 66 korban ...</t>
+          <t>Wakil Menteri Agraria dan Tata Ruang/Wakil Kepala Badan Pertanahan Nasional (Wamen ATR/Waka BPN) Ossy Dermawan ...</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678472/basarnas-jemput-66-korban-km-mutiara-sentosa-ii-dari-masalembu</t>
+          <t>https://www.antaranews.com/berita/5678489/wamen-atr-ujian-ppat-upaya-berikan-layanan-yang-baik</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BASARNAS-JEMPUT-66-KORBAN-KM-MUTIARA-SENTOSA-II-DARI-MASALEMBU.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_223512.jpg</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Kementerian ATR/BPN telah terbitkan 124 ribu SK sertifikat rumah MBR</t>
+          <t>PBSI buka suara soal absennya Jafar/Felisha di Kejuaraan Dunia BWF</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:56:36 +0700</t>
+          <t>Mon, 03 Aug 2026 23:03:05 +0700</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Kementerian Agraria dan Tata Ruang/Badan Pertanahan Nasional (ATR/BPN) menyatakan telah menerbitkan surat keputusan ...</t>
+          <t>Pengurus Pusat PBSI menyatakan absennya dua pasangan ganda campuran Indonesia Jafar Hidayatullah/Felisha Alberta ...</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678484/kementerian-atr-bpn-telah-terbitkan-124-ribu-sk-sertifikat-rumah-mbr</t>
+          <t>https://www.antaranews.com/berita/5678487/pbsi-buka-suara-soal-absennya-jafar-felisha-di-kejuaraan-dunia-bwf</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_224532.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/06/IMG_20251127_205351.jpg</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Timnas Indonesia dibungkam Vietnam 0-3</t>
+          <t>Prabowo terima tanda kehormatan dari Angkatan Bersenjata Thailand</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:54:01 +0700</t>
+          <t>Mon, 03 Aug 2026 20:59:35 +0700</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Timnas Indonesia dibungkam Vietnam 0-3 di kandang pada laga lanjutan Grup A Piala AFF 2026 di Stadion Pakansari, Bogor, ...</t>
+          <t>Presiden Prabowo Subianto menerima tanda kehormatan dari Angkatan Bersenjata Kerajaan Thailand yang diberikan pada saat ...</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678480/timnas-indonesia-dibungkam-vietnam-0-3</t>
+          <t>https://www.antaranews.com/berita/5678283/prabowo-terima-tanda-kehormatan-dari-angkatan-bersenjata-thailand</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Timnas-Indonesia-lawan-Vietnam-030826-Bay-21a.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/tempImageNOyDfK.jpg</t>
         </is>
       </c>
     </row>
@@ -11951,160 +11951,160 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Prabowo terima tanda kehormatan dari Angkatan Bersenjata Thailand</t>
+          <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 20:59:35 +0700</t>
+          <t>Mon, 03 Aug 2026 20:50:37 +0700</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Presiden Prabowo Subianto menerima tanda kehormatan dari Angkatan Bersenjata Kerajaan Thailand yang diberikan pada saat ...</t>
+          <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan ...</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678283/prabowo-terima-tanda-kehormatan-dari-angkatan-bersenjata-thailand</t>
+          <t>https://www.antaranews.com/video/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/tempImageNOyDfK.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-finansial, top-news</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
+          <t>Menkeu: Eskalasi konflik Timteng dorong imbal hasil SBN ke 7,14 persen</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 20:50:37 +0700</t>
+          <t>Mon, 03 Aug 2026 20:48:02 +0700</t>
         </is>
       </c>
       <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr">
         <is>
-          <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan ...</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa mengatakan eskalasi konflik di Timur Tengah mendorong kenaikan imbal hasil Surat ...</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
+          <t>https://www.antaranews.com/berita/5678253/menkeu-eskalasi-konflik-timteng-dorong-imbal-hasil-sbn-ke-714-persen</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-20.38.31.jpeg</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>ekonomi-finansial, top-news</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Menkeu: Eskalasi konflik Timteng dorong imbal hasil SBN ke 7,14 persen</t>
+          <t>Prabowo dukung peningkatan latihan bersama militer RI-Thailand</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 20:48:02 +0700</t>
+          <t>Mon, 03 Aug 2026 19:21:32 +0700</t>
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa mengatakan eskalasi konflik di Timur Tengah mendorong kenaikan imbal hasil Surat ...</t>
+          <t>Presiden Prabowo Subianto mendukung peningkatan frekuensi latihan bersama antara Tentara Nasional Indonesia (TNI) dan ...</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678253/menkeu-eskalasi-konflik-timteng-dorong-imbal-hasil-sbn-ke-714-persen</t>
+          <t>https://www.antaranews.com/berita/5678081/prabowo-dukung-peningkatan-latihan-bersama-militer-ri-thailand</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-20.38.31.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.41.07.jpeg</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-finansial, top-news</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Prabowo dukung peningkatan latihan bersama militer RI-Thailand</t>
+          <t>OJK: Kredit perbankan tumbuh 12,67 persen capai Rp9.080,9 triliun</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:21:32 +0700</t>
+          <t>Mon, 03 Aug 2026 19:12:24 +0700</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Presiden Prabowo Subianto mendukung peningkatan frekuensi latihan bersama antara Tentara Nasional Indonesia (TNI) dan ...</t>
+          <t>Otoritas Jasa Keuangan (OJK) melaporkan penyaluran kredit perbankan di tanah air tumbuh 12,67 persen year on year ...</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678081/prabowo-dukung-peningkatan-latihan-bersama-militer-ri-thailand</t>
+          <t>https://www.antaranews.com/berita/5678057/ojk-kredit-perbankan-tumbuh-1267-persen-capai-rp90809-triliun</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.41.07.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.15.18_1.jpeg</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>ekonomi-finansial, top-news</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>OJK: Kredit perbankan tumbuh 12,67 persen capai Rp9.080,9 triliun</t>
+          <t>Menkomdigi: KIP garda depan informasi jernih dan perangi hoaks</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:12:24 +0700</t>
+          <t>Mon, 03 Aug 2026 19:00:50 +0700</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Otoritas Jasa Keuangan (OJK) melaporkan penyaluran kredit perbankan di tanah air tumbuh 12,67 persen year on year ...</t>
+          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid mengatakan Komisi Informasi Pusat (KIP) menjadi garda terdepan ...</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678057/ojk-kredit-perbankan-tumbuh-1267-persen-capai-rp90809-triliun</t>
+          <t>https://www.antaranews.com/berita/5678033/menkomdigi-kip-garda-depan-informasi-jernih-dan-perangi-hoaks</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.15.18_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0321.jpg</t>
         </is>
       </c>
     </row>
@@ -12116,28 +12116,28 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Menkomdigi: KIP garda depan informasi jernih dan perangi hoaks</t>
+          <t>Satu tahun Sekolah Rakyat, ratusan siswa torehkan prestasi</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:00:50 +0700</t>
+          <t>Mon, 03 Aug 2026 18:59:25 +0700</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid mengatakan Komisi Informasi Pusat (KIP) menjadi garda terdepan ...</t>
+          <t>Menteri Sosial (Mensos) Saifullah Yusuf menyatakan selama satu tahun Sekolah Rakyat berdiri sudah ratusan ...</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678033/menkomdigi-kip-garda-depan-informasi-jernih-dan-perangi-hoaks</t>
+          <t>https://www.antaranews.com/berita/5678024/satu-tahun-sekolah-rakyat-ratusan-siswa-torehkan-prestasi</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0321.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176441.jpg</t>
         </is>
       </c>
     </row>
@@ -12149,28 +12149,28 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Satu tahun Sekolah Rakyat, ratusan siswa torehkan prestasi</t>
+          <t>Menkeu: Realisasi anggaran MBG Rp101,1 T untuk 63,13 juta penerima</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:59:25 +0700</t>
+          <t>Mon, 03 Aug 2026 18:53:14 +0700</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Menteri Sosial (Mensos) Saifullah Yusuf menyatakan selama satu tahun Sekolah Rakyat berdiri sudah ratusan ...</t>
+          <t>Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa mengungkapkan bahwa realisasi anggaran Program Makan Bergizi Gratis ...</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678024/satu-tahun-sekolah-rakyat-ratusan-siswa-torehkan-prestasi</t>
+          <t>https://www.antaranews.com/berita/5678005/menkeu-realisasi-anggaran-mbg-rp1011-t-untuk-6313-juta-penerima</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176441.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29-2.jpeg</t>
         </is>
       </c>
     </row>
@@ -12182,28 +12182,28 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Menkeu: Realisasi anggaran MBG Rp101,1 T untuk 63,13 juta penerima</t>
+          <t>Polri perkuat langkah preventif respons isu keamanan nasional</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:53:14 +0700</t>
+          <t>Mon, 03 Aug 2026 18:46:34 +0700</t>
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa mengungkapkan bahwa realisasi anggaran Program Makan Bergizi Gratis ...</t>
+          <t>Polri memastikan terus memperkuat langkah preventif untuk menjaga keamanan nasional sehingga aktivitas masyarakat dan ...</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678005/menkeu-realisasi-anggaran-mbg-rp1011-t-untuk-6313-juta-penerima</t>
+          <t>https://www.antaranews.com/berita/5677985/polri-perkuat-langkah-preventif-respons-isu-keamanan-nasional</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29-2.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/1000086556.jpg</t>
         </is>
       </c>
     </row>
@@ -12215,28 +12215,28 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Polri perkuat langkah preventif respons isu keamanan nasional</t>
+          <t>Prabowo dan PM Thailand bertemu empat mata di Istana Merdeka</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:46:34 +0700</t>
+          <t>Mon, 03 Aug 2026 17:49:52 +0700</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Polri memastikan terus memperkuat langkah preventif untuk menjaga keamanan nasional sehingga aktivitas masyarakat dan ...</t>
+          <t>Presiden Prabowo Subianto dan Perdana Menteri Thailand Anutin Charnvirakul menggelar pertemuan empat mata di Istana ...</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677985/polri-perkuat-langkah-preventif-respons-isu-keamanan-nasional</t>
+          <t>https://www.antaranews.com/berita/5677828/prabowo-dan-pm-thailand-bertemu-empat-mata-di-istana-merdeka</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/1000086556.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_5162.jpeg</t>
         </is>
       </c>
     </row>
@@ -12248,28 +12248,29 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Prabowo dan PM Thailand bertemu empat mata di Istana Merdeka</t>
+          <t>Kepala BGN tingkatkan status keracunan MBG jadi kejadian fatal</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 17:49:52 +0700</t>
+          <t>Mon, 03 Aug 2026 17:10:19 +0700</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Presiden Prabowo Subianto dan Perdana Menteri Thailand Anutin Charnvirakul menggelar pertemuan empat mata di Istana ...</t>
+          <t>nya tidak dilanjutkan," ucap Sudaryono.
+Ia menegaskan BGN memberlakukan nol toleransi pada setiap status ...</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677828/prabowo-dan-pm-thailand-bertemu-empat-mata-di-istana-merdeka</t>
+          <t>https://www.antaranews.com/berita/5677743/kepala-bgn-tingkatkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_5162.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/ZAM02548_edit_2028523819372755.jpg</t>
         </is>
       </c>
     </row>
@@ -12281,29 +12282,28 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Kepala BGN tingkatkan status keracunan MBG jadi kejadian fatal</t>
+          <t>Harga minyak turun usai AS siap lanjutkan dialog dengan Iran</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 17:10:19 +0700</t>
+          <t>Mon, 03 Aug 2026 17:08:35 +0700</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr">
         <is>
-          <t>nya tidak dilanjutkan," ucap Sudaryono.
-Ia menegaskan BGN memberlakukan nol toleransi pada setiap status ...</t>
+          <t>Harga minyak turun lebih dari 5 persen, Senin, setelah Presiden Amerika Serikat Donald Trump ...</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677743/kepala-bgn-tingkatkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+          <t>https://www.antaranews.com/berita/5677735/harga-minyak-turun-usai-as-siap-lanjutkan-dialog-dengan-iran</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/ZAM02548_edit_2028523819372755.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/06/ilustrasi-isi-bensin-di-pom.jpg</t>
         </is>
       </c>
     </row>
@@ -12315,28 +12315,28 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Harga minyak turun usai AS siap lanjutkan dialog dengan Iran</t>
+          <t>Australia konfirmasi kematian massal pertama satwa akibat flu burung</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 17:08:35 +0700</t>
+          <t>Mon, 03 Aug 2026 16:48:50 +0700</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Harga minyak turun lebih dari 5 persen, Senin, setelah Presiden Amerika Serikat Donald Trump ...</t>
+          <t>Australia mengonfirmasi kematian massal satwa liar pertama terkait flu burung H5 yang mematikan, dengan burung camar ...</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677735/harga-minyak-turun-usai-as-siap-lanjutkan-dialog-dengan-iran</t>
+          <t>https://www.antaranews.com/berita/5677701/australia-konfirmasi-kematian-massal-pertama-satwa-akibat-flu-burung</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/06/ilustrasi-isi-bensin-di-pom.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/26/Virus-flu-burung-penyakit-unggas.jpg</t>
         </is>
       </c>
     </row>
@@ -12348,94 +12348,94 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Australia konfirmasi kematian massal pertama satwa akibat flu burung</t>
+          <t>Siklon 94 W,  waspada cuaca ekstrem &amp; gelombang tinggi di wilayah RI</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:48:50 +0700</t>
+          <t>Mon, 03 Aug 2026 16:30:38 +0700</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Australia mengonfirmasi kematian massal satwa liar pertama terkait flu burung H5 yang mematikan, dengan burung camar ...</t>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) mendeteksi pergerakan Bibit Siklon Tropis 94W di Laut Filipina ...</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677701/australia-konfirmasi-kematian-massal-pertama-satwa-akibat-flu-burung</t>
+          <t>https://www.antaranews.com/berita/5677641/siklon-94-w-waspada-cuaca-ekstrem-gelombang-tinggi-di-wilayah-ri</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/26/Virus-flu-burung-penyakit-unggas.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/27/1000395034.jpg</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>photo, top-news</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Siklon 94 W,  waspada cuaca ekstrem &amp; gelombang tinggi di wilayah RI</t>
+          <t>Petani berbagi air sumur demi selamatkan tanaman tembakau</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:30:38 +0700</t>
+          <t>Mon, 03 Aug 2026 14:44:51 +0700</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) mendeteksi pergerakan Bibit Siklon Tropis 94W di Laut Filipina ...</t>
+          <t>Petani mengambil air dari sumur untuk menyiram tanaman tembakau di Lengkong, Nganjuk, Jawa Timur, Senin (3/8/2026). ...</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677641/siklon-94-w-waspada-cuaca-ekstrem-gelombang-tinggi-di-wilayah-ri</t>
+          <t>https://www.antaranews.com/foto/5677428/petani-berbagi-air-sumur-demi-selamatkan-tanaman-tembakau</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/27/1000395034.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/petani-tembakau-berbagi-air-sumur-antisipasi-dampak-el-nino-030826-mm-1.jpg</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>photo, top-news</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Petani berbagi air sumur demi selamatkan tanaman tembakau</t>
+          <t>Nusron sebut banyak laut di Batam telah dikapling tanpa prosedur sah</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:44:51 +0700</t>
+          <t>Mon, 03 Aug 2026 14:44:05 +0700</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Petani mengambil air dari sumur untuk menyiram tanaman tembakau di Lengkong, Nganjuk, Jawa Timur, Senin (3/8/2026). ...</t>
+          <t>Menteri Agraria dan Tata Ruang (ATR)/Kepala Badan Pertanahan Nasional (BPN) Nusron Wahid mengatakan, menerima banyak ...</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5677428/petani-berbagi-air-sumur-demi-selamatkan-tanaman-tembakau</t>
+          <t>https://www.antaranews.com/berita/5677425/nusron-sebut-banyak-laut-di-batam-telah-dikapling-tanpa-prosedur-sah</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/petani-tembakau-berbagi-air-sumur-antisipasi-dampak-el-nino-030826-mm-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_142345.jpg</t>
         </is>
       </c>
     </row>
@@ -12447,28 +12447,28 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Nusron sebut banyak laut di Batam telah dikapling tanpa prosedur sah</t>
+          <t>Menkomdigi panggil YouTube imbas temuan konten promosi vape sasar anak</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:44:05 +0700</t>
+          <t>Mon, 03 Aug 2026 14:22:09 +0700</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Menteri Agraria dan Tata Ruang (ATR)/Kepala Badan Pertanahan Nasional (BPN) Nusron Wahid mengatakan, menerima banyak ...</t>
+          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid merencanakan pemanggilan terhadap platform digital YouTube ...</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677425/nusron-sebut-banyak-laut-di-batam-telah-dikapling-tanpa-prosedur-sah</t>
+          <t>https://www.antaranews.com/berita/5677396/menkomdigi-panggil-youtube-imbas-temuan-konten-promosi-vape-sasar-anak</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_142345.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0225.jpg</t>
         </is>
       </c>
     </row>
@@ -12480,28 +12480,28 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Menkomdigi panggil YouTube imbas temuan konten promosi vape sasar anak</t>
+          <t>Kemnaker: Magang Nasional diharapkan menekan angka pengangguran muda</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:22:09 +0700</t>
+          <t>Mon, 03 Aug 2026 13:37:57 +0700</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid merencanakan pemanggilan terhadap platform digital YouTube ...</t>
+          <t>Kementerian Ketenagakerjaan (Kemnaker) mengatakan program Magang Nasional (MagangHub) untuk mempersiapkan kompetensi ...</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677396/menkomdigi-panggil-youtube-imbas-temuan-konten-promosi-vape-sasar-anak</t>
+          <t>https://www.antaranews.com/berita/5677364/kemnaker-magang-nasional-diharapkan-menekan-angka-pengangguran-muda</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0225.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/ff63afaf-7778-47fe-833d-5a8068af9a51_1.jpeg</t>
         </is>
       </c>
     </row>
@@ -12513,28 +12513,28 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Kemnaker: Magang Nasional diharapkan menekan angka pengangguran muda</t>
+          <t>Kemenag perkuat transformasi madrasah lewat revitalisasi-digitalisasi</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:37:57 +0700</t>
+          <t>Mon, 03 Aug 2026 13:36:36 +0700</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Kementerian Ketenagakerjaan (Kemnaker) mengatakan program Magang Nasional (MagangHub) untuk mempersiapkan kompetensi ...</t>
+          <t>Menteri Agama (Menag) Nasaruddin Umar menegaskan transformasi madrasah terus diperkuat melalui revitalisasi ...</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677364/kemnaker-magang-nasional-diharapkan-menekan-angka-pengangguran-muda</t>
+          <t>https://www.antaranews.com/berita/5677363/kemenag-perkuat-transformasi-madrasah-lewat-revitalisasi-digitalisasi</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/ff63afaf-7778-47fe-833d-5a8068af9a51_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/14/1000173935_1.jpg</t>
         </is>
       </c>
     </row>
@@ -12546,28 +12546,28 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Kemenag perkuat transformasi madrasah lewat revitalisasi-digitalisasi</t>
+          <t>Lisensi IP Global Buka Peluang Bisnis Baru bagi Kreator Indonesia</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:36:36 +0700</t>
+          <t>Mon, 03 Aug 2026 13:34:30 +0700</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Menteri Agama (Menag) Nasaruddin Umar menegaskan transformasi madrasah terus diperkuat melalui revitalisasi ...</t>
+          <t>Wakil Menteri Ekonomi Kreatif Irene Umar mengatakan kolaborasi antara pemilik kekayaan intelektual (Intellectual ...</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677363/kemenag-perkuat-transformasi-madrasah-lewat-revitalisasi-digitalisasi</t>
+          <t>https://www.antaranews.com/berita/5677353/lisensi-ip-global-buka-peluang-bisnis-baru-bagi-kreator-indonesia</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/14/1000173935_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000589873.jpg</t>
         </is>
       </c>
     </row>
@@ -12579,28 +12579,28 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Lisensi IP Global Buka Peluang Bisnis Baru bagi Kreator Indonesia</t>
+          <t>Nilai ekspor perdagangan RI Januari-Juni capai 140,81 miliar dolar AS</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:34:30 +0700</t>
+          <t>Mon, 03 Aug 2026 13:16:17 +0700</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Wakil Menteri Ekonomi Kreatif Irene Umar mengatakan kolaborasi antara pemilik kekayaan intelektual (Intellectual ...</t>
+          <t>Badan Pusat Statistik (BPS) mencatat nilai ekspor Indonesia secara kumulatif dari Januari-Juni 2026 mencapai 140,81 ...</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677353/lisensi-ip-global-buka-peluang-bisnis-baru-bagi-kreator-indonesia</t>
+          <t>https://www.antaranews.com/berita/5677315/nilai-ekspor-perdagangan-ri-januari-juni-capai-14081-miliar-dolar-as</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000589873.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/neraca-perdagangan-januari-mei-2026-surplus-2815779.jpg</t>
         </is>
       </c>
     </row>
@@ -12612,28 +12612,28 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Nilai ekspor perdagangan RI Januari-Juni capai 140,81 miliar dolar AS</t>
+          <t>Korban KMP Mutiara Sentosa II dievakuasi ke Pelabuhan Tanjung Perak</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:16:17 +0700</t>
+          <t>Mon, 03 Aug 2026 13:06:15 +0700</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat nilai ekspor Indonesia secara kumulatif dari Januari-Juni 2026 mencapai 140,81 ...</t>
+          <t>Tim SAR gabungan terus melakukan evakuasi korban terbakarnya KMP Mutiara Sentosa 2 ke darat, tepatnya ke Pelabuhan ...</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677315/nilai-ekspor-perdagangan-ri-januari-juni-capai-14081-miliar-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5677297/korban-kmp-mutiara-sentosa-ii-dievakuasi-ke-pelabuhan-tanjung-perak</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/neraca-perdagangan-januari-mei-2026-surplus-2815779.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/260821_1.jpg</t>
         </is>
       </c>
     </row>
@@ -12645,28 +12645,28 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Korban KMP Mutiara Sentosa II dievakuasi ke Pelabuhan Tanjung Perak</t>
+          <t>Aktor senior Diding Boneng meninggal dunia</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:06:15 +0700</t>
+          <t>Mon, 03 Aug 2026 11:39:03 +0700</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Tim SAR gabungan terus melakukan evakuasi korban terbakarnya KMP Mutiara Sentosa 2 ke darat, tepatnya ke Pelabuhan ...</t>
+          <t>Aktor sekaligus komedian tanah air, Zainal Abidin alias Diding Boneng dikabarkan meninggal dunia pada Senin (3/8) dalam ...</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677297/korban-kmp-mutiara-sentosa-ii-dievakuasi-ke-pelabuhan-tanjung-perak</t>
+          <t>https://www.antaranews.com/berita/5677209/aktor-senior-diding-boneng-meninggal-dunia</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/260821_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/26f1eb88-3301-4ae1-badd-bed5078fe3dd.jpeg</t>
         </is>
       </c>
     </row>
@@ -12678,28 +12678,28 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Aktor senior Diding Boneng meninggal dunia</t>
+          <t>Seskab: Prabowo dorong sinergi pemerintah dan dunia usaha</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:39:03 +0700</t>
+          <t>Mon, 03 Aug 2026 11:17:50 +0700</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Aktor sekaligus komedian tanah air, Zainal Abidin alias Diding Boneng dikabarkan meninggal dunia pada Senin (3/8) dalam ...</t>
+          <t>Sekretaris Kabinet Teddy Indra Wijaya menyampaikan bahwa Presiden Prabowo Subianto menekankan pentingnya sinergi antara ...</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677209/aktor-senior-diding-boneng-meninggal-dunia</t>
+          <t>https://www.antaranews.com/berita/5677191/seskab-prabowo-dorong-sinergi-pemerintah-dan-dunia-usaha</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/26f1eb88-3301-4ae1-badd-bed5078fe3dd.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0891_1.jpeg</t>
         </is>
       </c>
     </row>
@@ -12711,28 +12711,28 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Seskab: Prabowo dorong sinergi pemerintah dan dunia usaha</t>
+          <t>Red Velvet bersiap kembali lewat EP baru "Velvet Summer"</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:17:50 +0700</t>
+          <t>Mon, 03 Aug 2026 10:24:37 +0700</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Sekretaris Kabinet Teddy Indra Wijaya menyampaikan bahwa Presiden Prabowo Subianto menekankan pentingnya sinergi antara ...</t>
+          <t>Grup idola K-pop Red Velvet akan kembali lewat rilis mini album atau extended play (EP) baru bertajuk “Velvet ...</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677191/seskab-prabowo-dorong-sinergi-pemerintah-dan-dunia-usaha</t>
+          <t>https://www.antaranews.com/berita/5677151/red-velvet-bersiap-kembali-lewat-ep-baru-velvet-summer</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0891_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/ca97a3a8-aa17-45fc-be71-d36051dd9dcd.jpeg</t>
         </is>
       </c>
     </row>
@@ -12744,28 +12744,28 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Red Velvet bersiap kembali lewat EP baru "Velvet Summer"</t>
+          <t>Menaker pastikan komitmen pemerintah perkuat kesejahteraan pekerja</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:24:37 +0700</t>
+          <t>Mon, 03 Aug 2026 10:16:19 +0700</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Grup idola K-pop Red Velvet akan kembali lewat rilis mini album atau extended play (EP) baru bertajuk “Velvet ...</t>
+          <t>Menteri Ketenagakerjaan (Menaker) Yassierli memastikan pemerintah berkomitmen untuk memperkuat kesejahteraan, ...</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677151/red-velvet-bersiap-kembali-lewat-ep-baru-velvet-summer</t>
+          <t>https://www.antaranews.com/berita/5677148/menaker-pastikan-komitmen-pemerintah-perkuat-kesejahteraan-pekerja</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/ca97a3a8-aa17-45fc-be71-d36051dd9dcd.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/09/20/pelepasan-peserta-pemagangan-ke-jepang-di-jawa-barat-2627513.jpg</t>
         </is>
       </c>
     </row>
@@ -12777,28 +12777,28 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Menaker pastikan komitmen pemerintah perkuat kesejahteraan pekerja</t>
+          <t>23 calon hakim agung dan ad hoc ikuti seleksi wawancara akhir</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:16:19 +0700</t>
+          <t>Mon, 03 Aug 2026 10:15:01 +0700</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Menteri Ketenagakerjaan (Menaker) Yassierli memastikan pemerintah berkomitmen untuk memperkuat kesejahteraan, ...</t>
+          <t>Sebanyak 23 orang calon hakim agung dan ad hoc Mahkamah Agung Tahun 2026 mengikuti seleksi wawancara tahap akhir di ...</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677148/menaker-pastikan-komitmen-pemerintah-perkuat-kesejahteraan-pekerja</t>
+          <t>https://www.antaranews.com/berita/5677137/23-calon-hakim-agung-dan-ad-hoc-ikuti-seleksi-wawancara-akhir</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/09/20/pelepasan-peserta-pemagangan-ke-jepang-di-jawa-barat-2627513.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000012883_1.jpg</t>
         </is>
       </c>
     </row>
@@ -12810,28 +12810,28 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>23 calon hakim agung dan ad hoc ikuti seleksi wawancara akhir</t>
+          <t>BRIN perkuat kajian sungai bawah tanah di Kebumen untuk ketahanan air</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:15:01 +0700</t>
+          <t>Mon, 03 Aug 2026 09:57:19 +0700</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Sebanyak 23 orang calon hakim agung dan ad hoc Mahkamah Agung Tahun 2026 mengikuti seleksi wawancara tahap akhir di ...</t>
+          <t>Badan Riset dan Inovasi Nasional (BRIN) memperkuat riset ketahanan air melalui pengembangan teknologi dan penelitian ...</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677137/23-calon-hakim-agung-dan-ad-hoc-ikuti-seleksi-wawancara-akhir</t>
+          <t>https://www.antaranews.com/berita/5677120/brin-perkuat-kajian-sungai-bawah-tanah-di-kebumen-untuk-ketahanan-air</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000012883_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1785706440-47672950-1.jpg</t>
         </is>
       </c>
     </row>
@@ -12843,28 +12843,28 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>BRIN perkuat kajian sungai bawah tanah di Kebumen untuk ketahanan air</t>
+          <t>Harga bensin turun pada pekan pertama Agustus</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:57:19 +0700</t>
+          <t>Mon, 03 Aug 2026 09:51:00 +0700</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Badan Riset dan Inovasi Nasional (BRIN) memperkuat riset ketahanan air melalui pengembangan teknologi dan penelitian ...</t>
+          <t>Harga bahan bakar minyak (BBM) jenis bensin di stasiun pengisian bahan bakar umum (SPBU) Pertamina, Shell, dan bp ...</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677120/brin-perkuat-kajian-sungai-bawah-tanah-di-kebumen-untuk-ketahanan-air</t>
+          <t>https://www.antaranews.com/berita/5677109/harga-bensin-turun-pada-pekan-pertama-agustus</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1785706440-47672950-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/10/02/penuruanan-harga-bbm-011024-aaa-7.jpg</t>
         </is>
       </c>
     </row>
@@ -12876,61 +12876,61 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Harga bensin turun pada pekan pertama Agustus</t>
+          <t>Sean Gelael berbagi pengalaman di dunia balap ke pengunjung GIIAS 2026</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:51:00 +0700</t>
+          <t>Mon, 03 Aug 2026 09:34:53 +0700</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Harga bahan bakar minyak (BBM) jenis bensin di stasiun pengisian bahan bakar umum (SPBU) Pertamina, Shell, dan bp ...</t>
+          <t>Pembalap Indonesia Sean Gelael berbagi pengalamannya di dunia balap ke pengunjung GAIKINDO Indonesia International ...</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677109/harga-bensin-turun-pada-pekan-pertama-agustus</t>
+          <t>https://www.antaranews.com/berita/5677103/sean-gelael-berbagi-pengalaman-di-dunia-balap-ke-pengunjung-giias-2026</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/10/02/penuruanan-harga-bbm-011024-aaa-7.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/16b70b87-326f-479a-a806-580ab846cc6f_1.jpeg</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Sean Gelael berbagi pengalaman di dunia balap ke pengunjung GIIAS 2026</t>
+          <t>Cadangan devisa RI jadi 145 M dolar AS, BI sebut masih di level aman</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:34:53 +0700</t>
+          <t>Mon, 03 Aug 2026 21:52:44 +0700</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Pembalap Indonesia Sean Gelael berbagi pengalamannya di dunia balap ke pengunjung GAIKINDO Indonesia International ...</t>
+          <t>ANTARA - Bank Indonesia (BI) mengungkapkan cadangan devisa pada akhir Juli 2026 berada di posisi 145 miliar dolar AS. ...</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677103/sean-gelael-berbagi-pengalaman-di-dunia-balap-ke-pengunjung-giias-2026</t>
+          <t>https://www.antaranews.com/video/5678347/cadangan-devisa-ri-jadi-145-m-dolar-as-bi-sebut-masih-di-level-aman</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/16b70b87-326f-479a-a806-580ab846cc6f_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_CADANGAN-DEVISA-RI-JADI-145-M-DOLAR-AS-BI-SEBUT-MASIH-DI-LEVEL-AMAN.jpg</t>
         </is>
       </c>
     </row>
@@ -12942,28 +12942,28 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Cadangan devisa RI jadi 145 M dolar AS, BI sebut masih di level aman</t>
+          <t>BI: Inflasi Juli terjaga berkat sinergi bank sentral dan pemerintah</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:52:44 +0700</t>
+          <t>Mon, 03 Aug 2026 21:51:39 +0700</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>ANTARA - Bank Indonesia (BI) mengungkapkan cadangan devisa pada akhir Juli 2026 berada di posisi 145 miliar dolar AS. ...</t>
+          <t>Bank Indonesia (BI) memandang inflasi Indeks Harga Konsumen (IHK) pada Juli 2026 tetap terjaga dalam sasaran target, ...</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678347/cadangan-devisa-ri-jadi-145-m-dolar-as-bi-sebut-masih-di-level-aman</t>
+          <t>https://www.antaranews.com/berita/5678380/bi-inflasi-juli-terjaga-berkat-sinergi-bank-sentral-dan-pemerintah</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_CADANGAN-DEVISA-RI-JADI-145-M-DOLAR-AS-BI-SEBUT-MASIH-DI-LEVEL-AMAN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/07/WhatsApp-Image-2026-07-07-at-14.31.59_edited.jpg</t>
         </is>
       </c>
     </row>
@@ -12975,28 +12975,28 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>BI: Inflasi Juli terjaga berkat sinergi bank sentral dan pemerintah</t>
+          <t>BI: Kepemilikan SRBI oleh bank guna kelola likuiditas, bukan investasi</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:51:39 +0700</t>
+          <t>Mon, 03 Aug 2026 21:35:49 +0700</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Bank Indonesia (BI) memandang inflasi Indeks Harga Konsumen (IHK) pada Juli 2026 tetap terjaga dalam sasaran target, ...</t>
+          <t>Bank Indonesia (BI) menegaskan bahwa Sekuritas Rupiah Bank Indonesia (SRBI) ditujukan sebagai instrumen pengelolaan ...</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678380/bi-inflasi-juli-terjaga-berkat-sinergi-bank-sentral-dan-pemerintah</t>
+          <t>https://www.antaranews.com/berita/5678351/bi-kepemilikan-srbi-oleh-bank-guna-kelola-likuiditas-bukan-investasi</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/07/WhatsApp-Image-2026-07-07-at-14.31.59_edited.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-21.22.00.jpeg</t>
         </is>
       </c>
     </row>
@@ -13008,28 +13008,28 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>BI: Kepemilikan SRBI oleh bank guna kelola likuiditas, bukan investasi</t>
+          <t>KSSK prakirakan pertumbuhan ekonomi RI pada 2026 capai 5,6-6 persen</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:35:49 +0700</t>
+          <t>Mon, 03 Aug 2026 18:28:16 +0700</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Bank Indonesia (BI) menegaskan bahwa Sekuritas Rupiah Bank Indonesia (SRBI) ditujukan sebagai instrumen pengelolaan ...</t>
+          <t>Komite Stabilitas Sistem Keuangan (KSSK) memprakirakan ekonomi Indonesia sepanjang 2026 tumbuh dalam kisaran ...</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678351/bi-kepemilikan-srbi-oleh-bank-guna-kelola-likuiditas-bukan-investasi</t>
+          <t>https://www.antaranews.com/berita/5677935/kssk-prakirakan-pertumbuhan-ekonomi-ri-pada-2026-capai-56-6-persen</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-21.22.00.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.19.55.jpeg</t>
         </is>
       </c>
     </row>
@@ -13041,28 +13041,28 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>KSSK prakirakan pertumbuhan ekonomi RI pada 2026 capai 5,6-6 persen</t>
+          <t>Rupiah menguat dipengaruhi PMI manufaktur Indonesia naik jadi 50,2</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:28:16 +0700</t>
+          <t>Mon, 03 Aug 2026 16:58:46 +0700</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Komite Stabilitas Sistem Keuangan (KSSK) memprakirakan ekonomi Indonesia sepanjang 2026 tumbuh dalam kisaran ...</t>
+          <t>Nilai tukar rupiah terhadap dolar AS pada penutupan perdagangan Senin, bergerak menguat 25 poin atau 0,14 persen ...</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677935/kssk-prakirakan-pertumbuhan-ekonomi-ri-pada-2026-capai-56-6-persen</t>
+          <t>https://www.antaranews.com/berita/5677712/rupiah-menguat-dipengaruhi-pmi-manufaktur-indonesia-naik-jadi-502</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.19.55.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/12/nilai-tukar-rupiah-melemah-115-poin-2788415.jpg</t>
         </is>
       </c>
     </row>
@@ -13074,28 +13074,28 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Rupiah menguat dipengaruhi PMI manufaktur Indonesia naik jadi 50,2</t>
+          <t>KSSK: Sistem keuangan TW-II tetap terjaga di tengah konflik geopolitik</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:58:46 +0700</t>
+          <t>Mon, 03 Aug 2026 16:26:03 +0700</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Nilai tukar rupiah terhadap dolar AS pada penutupan perdagangan Senin, bergerak menguat 25 poin atau 0,14 persen ...</t>
+          <t>Komite Stabilitas Sistem Keuangan (KSSK) menilai kondisi fiskal, moneter dan sektor keuangan selama triwulan II 2026 ...</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677712/rupiah-menguat-dipengaruhi-pmi-manufaktur-indonesia-naik-jadi-502</t>
+          <t>https://www.antaranews.com/berita/5677625/kssk-sistem-keuangan-tw-ii-tetap-terjaga-di-tengah-konflik-geopolitik</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/12/nilai-tukar-rupiah-melemah-115-poin-2788415.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29.jpeg</t>
         </is>
       </c>
     </row>
@@ -13107,28 +13107,28 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>KSSK: Sistem keuangan TW-II tetap terjaga di tengah konflik geopolitik</t>
+          <t>Menjaga pintu air perekonomian Indonesia</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:26:03 +0700</t>
+          <t>Mon, 03 Aug 2026 16:04:40 +0700</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Komite Stabilitas Sistem Keuangan (KSSK) menilai kondisi fiskal, moneter dan sektor keuangan selama triwulan II 2026 ...</t>
+          <t>Bayangkan perekonomian Indonesia sebagai sebuah bendungan raksasa yang mengairi hamparan persawahan. Air yang mengalir ...</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677625/kssk-sistem-keuangan-tw-ii-tetap-terjaga-di-tengah-konflik-geopolitik</t>
+          <t>https://www.antaranews.com/berita/5677565/menjaga-pintu-air-perekonomian-indonesia</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/06/peringati-hari-bank-indonesia-doku-perkuat-ekosistem-pembayaran-2817675.jpg</t>
         </is>
       </c>
     </row>
@@ -13140,28 +13140,28 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Menjaga pintu air perekonomian Indonesia</t>
+          <t>Rupiah diperkirakan menguat seiring AS batalkan rencana serang Iran</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:04:40 +0700</t>
+          <t>Mon, 03 Aug 2026 10:12:26 +0700</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Bayangkan perekonomian Indonesia sebagai sebuah bendungan raksasa yang mengairi hamparan persawahan. Air yang mengalir ...</t>
+          <t>Analis Doo Financial Futures, Lukman Leong memperkirakan rupiah menguat seiring Amerika Serikat (AS) membatalkan ...</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677565/menjaga-pintu-air-perekonomian-indonesia</t>
+          <t>https://www.antaranews.com/berita/5677132/rupiah-diperkirakan-menguat-seiring-as-batalkan-rencana-serang-iran</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/06/peringati-hari-bank-indonesia-doku-perkuat-ekosistem-pembayaran-2817675.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828847.jpg</t>
         </is>
       </c>
     </row>
@@ -13173,28 +13173,28 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Rupiah diperkirakan menguat seiring AS batalkan rencana serang Iran</t>
+          <t>Rupiah pada Senin pagi melemah jadi Rp18.031 per dolar AS</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:12:26 +0700</t>
+          <t>Mon, 03 Aug 2026 09:05:50 +0700</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Analis Doo Financial Futures, Lukman Leong memperkirakan rupiah menguat seiring Amerika Serikat (AS) membatalkan ...</t>
+          <t>Nilai tukar rupiah pada Senin pagi bergerak melemah 9 poin atau 0,05 persen menjadi Rp18.031 per dolar AS dibandingkan ...</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677132/rupiah-diperkirakan-menguat-seiring-as-batalkan-rencana-serang-iran</t>
+          <t>https://www.antaranews.com/berita/5677063/rupiah-pada-senin-pagi-melemah-jadi-rp18031-per-dolar-as</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828847.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
         </is>
       </c>
     </row>
@@ -13206,28 +13206,28 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Rupiah pada Senin pagi melemah jadi Rp18.031 per dolar AS</t>
+          <t>Komisi XI: PFII peluang RI tangkap momentum perpindahan modal global</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:05:50 +0700</t>
+          <t>Mon, 03 Aug 2026 06:53:34 +0700</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Nilai tukar rupiah pada Senin pagi bergerak melemah 9 poin atau 0,05 persen menjadi Rp18.031 per dolar AS dibandingkan ...</t>
+          <t>Wakil Ketua Komisi XI DPR RI Mohamad Hekal mengatakan percepatan pembentukan Pusat Finansial Internasional Indonesia ...</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677063/rupiah-pada-senin-pagi-melemah-jadi-rp18031-per-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5676995/komisi-xi-pfii-peluang-ri-tangkap-momentum-perpindahan-modal-global</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Saham-dan-oblogasi.jpg</t>
         </is>
       </c>
     </row>
@@ -13239,61 +13239,61 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Komisi XI: PFII peluang RI tangkap momentum perpindahan modal global</t>
+          <t>BUMA International Group bukukan pertumbuhan EBITDA semester I/2026</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:53:34 +0700</t>
+          <t>Mon, 03 Aug 2026 06:17:40 +0700</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Wakil Ketua Komisi XI DPR RI Mohamad Hekal mengatakan percepatan pembentukan Pusat Finansial Internasional Indonesia ...</t>
+          <t>PT BUMA Internasional Gorup membukukan pertumbuhan EBITDA pada semester pertama 2026 (1H26) di tengah penurunan ...</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676995/komisi-xi-pfii-peluang-ri-tangkap-momentum-perpindahan-modal-global</t>
+          <t>https://www.antaranews.com/berita/5676967/buma-international-group-bukukan-pertumbuhan-ebitda-semester-i-2026</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Saham-dan-oblogasi.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/buma.jpg</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>BUMA International Group bukukan pertumbuhan EBITDA semester I/2026</t>
+          <t>Kementerian ATR/BPN telah terbitkan 124 ribu SK sertifikat rumah MBR</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:17:40 +0700</t>
+          <t>Mon, 03 Aug 2026 22:56:36 +0700</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr">
         <is>
-          <t>PT BUMA Internasional Gorup membukukan pertumbuhan EBITDA pada semester pertama 2026 (1H26) di tengah penurunan ...</t>
+          <t>Kementerian Agraria dan Tata Ruang/Badan Pertanahan Nasional (ATR/BPN) menyatakan telah menerbitkan surat keputusan ...</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676967/buma-international-group-bukukan-pertumbuhan-ebitda-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5678484/kementerian-atr-bpn-telah-terbitkan-124-ribu-sk-sertifikat-rumah-mbr</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/buma.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_224532.jpg</t>
         </is>
       </c>
     </row>

--- a/data/berita_antara_2026-08-03.xlsx
+++ b/data/berita_antara_2026-08-03.xlsx
@@ -11159,28 +11159,28 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Chelsea umumkan transfer gelandang Inggris Jordan Henderson</t>
+          <t>Kemenbud hadirkan GBN untuk membina talenta seni musik nasional</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:59:34 +0700</t>
+          <t>Mon, 03 Aug 2026 23:07:01 +0700</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Chelsea resmi mengumumkan kedatangan gelandang senior asal Inggris Jordan Henderson dengan status bebas transfer ...</t>
+          <t>Kementerian Kebudayaan (Kemenbud) menghadirkan program pembinaan talenta seni musik nasional yang mempertemukan ...</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678548/chelsea-umumkan-transfer-gelandang-inggris-jordan-henderson</t>
+          <t>https://www.antaranews.com/berita/5678491/kemenbud-hadirkan-gbn-untuk-membina-talenta-seni-musik-nasional</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000042505.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-20.28.05.jpeg</t>
         </is>
       </c>
     </row>
@@ -11192,28 +11192,28 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Nguyen Xuan Son ungkap alasan tak jadi starter saat kalahkan Indonesia</t>
+          <t>PBSI buka suara soal absennya Jafar/Felisha di Kejuaraan Dunia BWF</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:56:45 +0700</t>
+          <t>Mon, 03 Aug 2026 23:03:05 +0700</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Penyerang Timnas Vietnam Nguyen Xuan Son mengungkapkan alasan dirinya tidak dimainkan sebagai starter saat timnya ...</t>
+          <t>Pengurus Pusat PBSI menyatakan absennya dua pasangan ganda campuran Indonesia Jafar Hidayatullah/Felisha Alberta ...</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678547/nguyen-xuan-son-ungkap-alasan-tak-jadi-starter-saat-kalahkan-indonesia</t>
+          <t>https://www.antaranews.com/berita/5678487/pbsi-buka-suara-soal-absennya-jafar-felisha-di-kejuaraan-dunia-bwf</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1003314030.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/06/IMG_20251127_205351.jpg</t>
         </is>
       </c>
     </row>
@@ -11225,61 +11225,61 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
+          <t>Chelsea umumkan transfer gelandang Inggris Jordan Henderson</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:55:47 +0700</t>
+          <t>Mon, 03 Aug 2026 23:59:34 +0700</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ...</t>
+          <t>Chelsea resmi mengumumkan kedatangan gelandang senior asal Inggris Jordan Henderson dengan status bebas transfer ...</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+          <t>https://www.antaranews.com/berita/5678548/chelsea-umumkan-transfer-gelandang-inggris-jordan-henderson</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000042505.jpg</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>BPS kaitkan kenaikan TPK hotel bintang dengan kualitas wisman</t>
+          <t>Nguyen Xuan Son ungkap alasan tak jadi starter saat kalahkan Indonesia</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:53:51 +0700</t>
+          <t>Mon, 03 Aug 2026 23:56:45 +0700</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) Bali mengaitkan kenaikan tingkat penghunian kamar (TPK) hotel bintang pada Juni 2026 dengan ...</t>
+          <t>Penyerang Timnas Vietnam Nguyen Xuan Son mengungkapkan alasan dirinya tidak dimainkan sebagai starter saat timnya ...</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678543/bps-kaitkan-kenaikan-tpk-hotel-bintang-dengan-kualitas-wisman</t>
+          <t>https://www.antaranews.com/berita/5678547/nguyen-xuan-son-ungkap-alasan-tak-jadi-starter-saat-kalahkan-indonesia</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0332.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1003314030.jpg</t>
         </is>
       </c>
     </row>
@@ -11291,28 +11291,28 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Jogja Run'nShine 2026 targetkan diikuti 3.500 pelari</t>
+          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:52:29 +0700</t>
+          <t>Mon, 03 Aug 2026 23:55:47 +0700</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Pergelaran Jogja Run'nShine 2026 menargetkan diikuti sebanyak 3.500 pelari dengan memberikan pengalaman konsep ...</t>
+          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ...</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678540/jogja-runnshine-2026-targetkan-diikuti-3500-pelari</t>
+          <t>https://www.antaranews.com/video/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0103.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
         </is>
       </c>
     </row>
@@ -11324,61 +11324,61 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Jenama perkakas otomotif Tekiro dapat pengakuan Guinnes World Records</t>
+          <t>BPS kaitkan kenaikan TPK hotel bintang dengan kualitas wisman</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:47:06 +0700</t>
+          <t>Mon, 03 Aug 2026 23:53:51 +0700</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Jenama perkakas otomotif Tekiro mendapat pengakuan dari Guiness World Records berkat ...</t>
+          <t>Badan Pusat Statistik (BPS) Bali mengaitkan kenaikan tingkat penghunian kamar (TPK) hotel bintang pada Juni 2026 dengan ...</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5678535/jenama-perkakas-otomotif-tekiro-dapat-pengakuan-guinnes-world-records</t>
+          <t>https://www.antaranews.com/berita/5678543/bps-kaitkan-kenaikan-tpk-hotel-bintang-dengan-kualitas-wisman</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-02-at-15.34.09-1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0332.jpeg</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Pemkab Sleman dukung kejuaraan dragbike tingkatkan ekonomi masyarakat</t>
+          <t>Jogja Run'nShine 2026 targetkan diikuti 3.500 pelari</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:42:42 +0700</t>
+          <t>Mon, 03 Aug 2026 23:52:29 +0700</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Pemerintah Kabupaten Sleman, Daerah Istimewa Yogyakarta, mendukung penuh penyelenggaraan Kejuaraan Dragbike Super ...</t>
+          <t>Pergelaran Jogja Run'nShine 2026 menargetkan diikuti sebanyak 3.500 pelari dengan memberikan pengalaman konsep ...</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678532/pemkab-sleman-dukung-kejuaraan-dragbike-tingkatkan-ekonomi-masyarakat</t>
+          <t>https://www.antaranews.com/berita/5678540/jogja-runnshine-2026-targetkan-diikuti-3500-pelari</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000029422.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0103.jpg</t>
         </is>
       </c>
     </row>
@@ -11390,61 +11390,61 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>GMR nilai akses penerbangan langsung buka peluang ekonomi RI-India</t>
+          <t>Jenama perkakas otomotif Tekiro dapat pengakuan Guinnes World Records</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:41:32 +0700</t>
+          <t>Mon, 03 Aug 2026 23:47:06 +0700</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
-          <t>GMR Group, perusahaan multinasional India yang bergerak di bidang infrastruktur, menilai akses penerbangan langsung ...</t>
+          <t>Jenama perkakas otomotif Tekiro mendapat pengakuan dari Guiness World Records berkat ...</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678529/gmr-nilai-akses-penerbangan-langsung-buka-peluang-ekonomi-ri-india</t>
+          <t>https://otomotif.antaranews.com/berita/5678535/jenama-perkakas-otomotif-tekiro-dapat-pengakuan-guinnes-world-records</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/DSF3021.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-02-at-15.34.09-1.jpeg</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>PSSI raup dana Rp722 miliar dalam laporan keuangan tahunan</t>
+          <t>Pemkab Sleman dukung kejuaraan dragbike tingkatkan ekonomi masyarakat</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:37:46 +0700</t>
+          <t>Mon, 03 Aug 2026 23:42:42 +0700</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir menyebut organisasinya meraup dana senilai Rp722 ...</t>
+          <t>Pemerintah Kabupaten Sleman, Daerah Istimewa Yogyakarta, mendukung penuh penyelenggaraan Kejuaraan Dragbike Super ...</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678528/pssi-raup-dana-rp722-miliar-dalam-laporan-keuangan-tahunan</t>
+          <t>https://www.antaranews.com/berita/5678532/pemkab-sleman-dukung-kejuaraan-dragbike-tingkatkan-ekonomi-masyarakat</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0098_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000029422.jpg</t>
         </is>
       </c>
     </row>
@@ -11456,28 +11456,28 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Otorita kolaborasi PNM untuk pengembangan ekonomi masyarakat IKN</t>
+          <t>GMR nilai akses penerbangan langsung buka peluang ekonomi RI-India</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:30:50 +0700</t>
+          <t>Mon, 03 Aug 2026 23:41:32 +0700</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Otorita Ibu Kota Nusantara (IKN) melakukan kolaborasi dengan PT Permodalan Nasional Madani (Persero) untuk pengembangan ...</t>
+          <t>GMR Group, perusahaan multinasional India yang bergerak di bidang infrastruktur, menilai akses penerbangan langsung ...</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678525/otorita-kolaborasi-pnm-untuk-pengembangan-ekonomi-masyarakat-ikn</t>
+          <t>https://www.antaranews.com/berita/5678529/gmr-nilai-akses-penerbangan-langsung-buka-peluang-ekonomi-ri-india</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0012_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/DSF3021.jpeg</t>
         </is>
       </c>
     </row>
@@ -11489,94 +11489,94 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>DPR: Wacana Prabowo jembatani dialog Korea sesuai politik bebas aktif</t>
+          <t>PSSI raup dana Rp722 miliar dalam laporan keuangan tahunan</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:30:13 +0700</t>
+          <t>Mon, 03 Aug 2026 23:37:46 +0700</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Wakil Ketua Komisi I DPR RI Dave Laksono menilai wacana Presiden Prabowo Subianto untuk menjembatani dialog antara ...</t>
+          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir menyebut organisasinya meraup dana senilai Rp722 ...</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678521/dpr-wacana-prabowo-jembatani-dialog-korea-sesuai-politik-bebas-aktif</t>
+          <t>https://www.antaranews.com/berita/5678528/pssi-raup-dana-rp722-miliar-dalam-laporan-keuangan-tahunan</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/22/IMG_20260422_175322.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0098_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Kongres PSSI sepakati pemilihan pengurus mundur ke Juli 2027</t>
+          <t>Otorita kolaborasi PNM untuk pengembangan ekonomi masyarakat IKN</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:30:00 +0700</t>
+          <t>Mon, 03 Aug 2026 23:30:50 +0700</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
-          <t>ANTARA - Kongres Biasa PSSI 2026 menyepakati perubahan jadwal Kongres Pemilihan Pengurus PSSI 2027 dari semula Mei ...</t>
+          <t>Otorita Ibu Kota Nusantara (IKN) melakukan kolaborasi dengan PT Permodalan Nasional Madani (Persero) untuk pengembangan ...</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678395/kongres-pssi-sepakati-pemilihan-pengurus-mundur-ke-juli-2027</t>
+          <t>https://www.antaranews.com/berita/5678525/otorita-kolaborasi-pnm-untuk-pengembangan-ekonomi-masyarakat-ikn</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KONGRES-PSSI-SEPAKATI-PEMILIHAN-PENGURUS-MUNDUR-KE-JULI-2027.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0012_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Toyota Astra Motor perkenalkan Hilux generasi ke-9</t>
+          <t>DPR: Wacana Prabowo jembatani dialog Korea sesuai politik bebas aktif</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:25:20 +0700</t>
+          <t>Mon, 03 Aug 2026 23:30:13 +0700</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
-          <t>PT Toyota Astra Motor (TAM) memperkenalkan Hilux generasi ke-9 untuk mendukung pemenuhan kebutuhan operasional industri ...</t>
+          <t>Wakil Ketua Komisi I DPR RI Dave Laksono menilai wacana Presiden Prabowo Subianto untuk menjembatani dialog antara ...</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5678519/toyota-astra-motor-perkenalkan-hilux-generasi-ke-9</t>
+          <t>https://www.antaranews.com/berita/5678521/dpr-wacana-prabowo-jembatani-dialog-korea-sesuai-politik-bebas-aktif</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/photo_6307309656757440820_w-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/22/IMG_20260422_175322.jpg</t>
         </is>
       </c>
     </row>
@@ -11588,193 +11588,193 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Sudin PPAPP Jakbar sosialisasikan Sekolah Siaga Kependudukan</t>
+          <t>Kongres PSSI sepakati pemilihan pengurus mundur ke Juli 2027</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:24:33 +0700</t>
+          <t>Mon, 03 Aug 2026 23:30:00 +0700</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Suku Dinas Pemberdayaan, Perlindungan Anak, dan Pengendalian Penduduk (Sudin PPAPP) Jakarta Barat (Jakbar) menggelar ...</t>
+          <t>ANTARA - Kongres Biasa PSSI 2026 menyepakati perubahan jadwal Kongres Pemilihan Pengurus PSSI 2027 dari semula Mei ...</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678515/sudin-ppapp-jakbar-sosialisasikan-sekolah-siaga-kependudukan</t>
+          <t>https://www.antaranews.com/video/5678395/kongres-pssi-sepakati-pemilihan-pengurus-mundur-ke-juli-2027</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0031_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KONGRES-PSSI-SEPAKATI-PEMILIHAN-PENGURUS-MUNDUR-KE-JULI-2027.jpg</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Klasemen Grup A Piala AFF : Timnas Indonesia turun ke peringkat tiga</t>
+          <t>Toyota Astra Motor perkenalkan Hilux generasi ke-9</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:23:51 +0700</t>
+          <t>Mon, 03 Aug 2026 23:25:20 +0700</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Timnas Indonesia turun ke peringkat ketiga klasemen sementara Grup A Piala AFF 2026 setelah menelan kekalahan 0-3 dari ...</t>
+          <t>PT Toyota Astra Motor (TAM) memperkenalkan Hilux generasi ke-9 untuk mendukung pemenuhan kebutuhan operasional industri ...</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678512/klasemen-grup-a-piala-aff-timnas-indonesia-turun-ke-peringkat-tiga</t>
+          <t>https://otomotif.antaranews.com/berita/5678519/toyota-astra-motor-perkenalkan-hilux-generasi-ke-9</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833516.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/photo_6307309656757440820_w-1.jpg</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>NTB menargetkan penonton MotoGP Mandalika tembus 140 ribu</t>
+          <t>Sudin PPAPP Jakbar sosialisasikan Sekolah Siaga Kependudukan</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:23:01 +0700</t>
+          <t>Mon, 03 Aug 2026 23:24:33 +0700</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Pemerintah Provinsi Nusa Tenggara Barat menargetkan jumlah penonton MotoGP di Sirkuit Mandalika pada 9-11 Oktober 2026 ...</t>
+          <t>Suku Dinas Pemberdayaan, Perlindungan Anak, dan Pengendalian Penduduk (Sudin PPAPP) Jakarta Barat (Jakbar) menggelar ...</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678508/ntb-menargetkan-penonton-motogp-mandalika-tembus-140-ribu</t>
+          <t>https://www.antaranews.com/berita/5678515/sudin-ppapp-jakbar-sosialisasikan-sekolah-siaga-kependudukan</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260109-WA0024_copy_1280x797.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0031_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Bulog: Margin naik jadi 7 persen, dukungan Presiden kawal swasembada</t>
+          <t>Klasemen Grup A Piala AFF : Timnas Indonesia turun ke peringkat tiga</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:19:51 +0700</t>
+          <t>Mon, 03 Aug 2026 23:23:51 +0700</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Direktur Utama Perum Bulog Ahmad Rizal Ramdhani menegaskan kenaikan margin fee menjadi 7 persen bentuk dukungan ...</t>
+          <t>Timnas Indonesia turun ke peringkat ketiga klasemen sementara Grup A Piala AFF 2026 setelah menelan kekalahan 0-3 dari ...</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678504/bulog-margin-naik-jadi-7-persen-dukungan-presiden-kawal-swasembada</t>
+          <t>https://www.antaranews.com/berita/5678512/klasemen-grup-a-piala-aff-timnas-indonesia-turun-ke-peringkat-tiga</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/14C1B7CB-9D6F-49B9-9CD1-E40DD76E851C.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833516.jpg</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Turkiye sebut serangan Israel sabotase upaya damai di Gaza</t>
+          <t>NTB menargetkan penonton MotoGP Mandalika tembus 140 ribu</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:18:30 +0700</t>
+          <t>Mon, 03 Aug 2026 23:23:01 +0700</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Pemerintah Turkiye pada Senin menilai serangan Israel di Jalur Gaza telah menghambat berbagai inisiatif diplomatik yang ...</t>
+          <t>Pemerintah Provinsi Nusa Tenggara Barat menargetkan jumlah penonton MotoGP di Sirkuit Mandalika pada 9-11 Oktober 2026 ...</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678500/turkiye-sebut-serangan-israel-sabotase-upaya-damai-di-gaza</t>
+          <t>https://www.antaranews.com/berita/5678508/ntb-menargetkan-penonton-motogp-mandalika-tembus-140-ribu</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/thumbs_b_c_186832d7ab4775afec853057c8952c3d.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260109-WA0024_copy_1280x797.jpg</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Purbaya pastikan tak ada lagi perdebatan soal penarikan SAL dari bank</t>
+          <t>Bulog: Margin naik jadi 7 persen, dukungan Presiden kawal swasembada</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:15:59 +0700</t>
+          <t>Mon, 03 Aug 2026 23:19:51 +0700</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Menteri Keuangan (Menkeu), Purbaya Yudhi Sadewa memastikan tidak ada lagi perdebatan mengenai penarikan dana ...</t>
+          <t>Direktur Utama Perum Bulog Ahmad Rizal Ramdhani menegaskan kenaikan margin fee menjadi 7 persen bentuk dukungan ...</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678499/purbaya-pastikan-tak-ada-lagi-perdebatan-soal-penarikan-sal-dari-bank</t>
+          <t>https://www.antaranews.com/berita/5678504/bulog-margin-naik-jadi-7-persen-dukungan-presiden-kawal-swasembada</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-23.02.47.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/14C1B7CB-9D6F-49B9-9CD1-E40DD76E851C.jpeg</t>
         </is>
       </c>
     </row>
@@ -11786,28 +11786,28 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Tim 9 Kejagung didesak usut pemilik uang-emas di rumah eks Jampidsus</t>
+          <t>Turkiye sebut serangan Israel sabotase upaya damai di Gaza</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:10:43 +0700</t>
+          <t>Mon, 03 Aug 2026 23:18:30 +0700</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Tim 9 Kejaksaan Agung didesak mengusut tuntas pemilik uang tunai senilai Rp476 miliar dan emas batangan seberat 74 ...</t>
+          <t>Pemerintah Turkiye pada Senin menilai serangan Israel di Jalur Gaza telah menghambat berbagai inisiatif diplomatik yang ...</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678495/tim-9-kejagung-didesak-usut-pemilik-uang-emas-di-rumah-eks-jampidsus</t>
+          <t>https://www.antaranews.com/berita/5678500/turkiye-sebut-serangan-israel-sabotase-upaya-damai-di-gaza</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/1000175632.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/thumbs_b_c_186832d7ab4775afec853057c8952c3d.jpg</t>
         </is>
       </c>
     </row>
@@ -11819,94 +11819,94 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Kemenbud hadirkan GBN untuk membina talenta seni musik nasional</t>
+          <t>Purbaya pastikan tak ada lagi perdebatan soal penarikan SAL dari bank</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:07:01 +0700</t>
+          <t>Mon, 03 Aug 2026 23:15:59 +0700</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Kementerian Kebudayaan (Kemenbud) menghadirkan program pembinaan talenta seni musik nasional yang mempertemukan ...</t>
+          <t>Menteri Keuangan (Menkeu), Purbaya Yudhi Sadewa memastikan tidak ada lagi perdebatan mengenai penarikan dana ...</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678491/kemenbud-hadirkan-gbn-untuk-membina-talenta-seni-musik-nasional</t>
+          <t>https://www.antaranews.com/berita/5678499/purbaya-pastikan-tak-ada-lagi-perdebatan-soal-penarikan-sal-dari-bank</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-20.28.05.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-23.02.47.jpeg</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Wamen ATR: Ujian PPAT upaya berikan layanan yang baik</t>
+          <t>Tim 9 Kejagung didesak usut pemilik uang-emas di rumah eks Jampidsus</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:05:29 +0700</t>
+          <t>Mon, 03 Aug 2026 23:10:43 +0700</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Wakil Menteri Agraria dan Tata Ruang/Wakil Kepala Badan Pertanahan Nasional (Wamen ATR/Waka BPN) Ossy Dermawan ...</t>
+          <t>Tim 9 Kejaksaan Agung didesak mengusut tuntas pemilik uang tunai senilai Rp476 miliar dan emas batangan seberat 74 ...</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678489/wamen-atr-ujian-ppat-upaya-berikan-layanan-yang-baik</t>
+          <t>https://www.antaranews.com/berita/5678495/tim-9-kejagung-didesak-usut-pemilik-uang-emas-di-rumah-eks-jampidsus</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_223512.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/1000175632.jpg</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>PBSI buka suara soal absennya Jafar/Felisha di Kejuaraan Dunia BWF</t>
+          <t>Prabowo terima tanda kehormatan dari Angkatan Bersenjata Thailand</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:03:05 +0700</t>
+          <t>Mon, 03 Aug 2026 20:59:35 +0700</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Pengurus Pusat PBSI menyatakan absennya dua pasangan ganda campuran Indonesia Jafar Hidayatullah/Felisha Alberta ...</t>
+          <t>Presiden Prabowo Subianto menerima tanda kehormatan dari Angkatan Bersenjata Kerajaan Thailand yang diberikan pada saat ...</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678487/pbsi-buka-suara-soal-absennya-jafar-felisha-di-kejuaraan-dunia-bwf</t>
+          <t>https://www.antaranews.com/berita/5678283/prabowo-terima-tanda-kehormatan-dari-angkatan-bersenjata-thailand</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/06/IMG_20251127_205351.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/tempImageNOyDfK.jpg</t>
         </is>
       </c>
     </row>
@@ -11918,160 +11918,160 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Prabowo terima tanda kehormatan dari Angkatan Bersenjata Thailand</t>
+          <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 20:59:35 +0700</t>
+          <t>Mon, 03 Aug 2026 20:50:37 +0700</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Presiden Prabowo Subianto menerima tanda kehormatan dari Angkatan Bersenjata Kerajaan Thailand yang diberikan pada saat ...</t>
+          <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan ...</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678283/prabowo-terima-tanda-kehormatan-dari-angkatan-bersenjata-thailand</t>
+          <t>https://www.antaranews.com/video/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/tempImageNOyDfK.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-finansial, top-news</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
+          <t>Menkeu: Eskalasi konflik Timteng dorong imbal hasil SBN ke 7,14 persen</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 20:50:37 +0700</t>
+          <t>Mon, 03 Aug 2026 20:48:02 +0700</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
-          <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan ...</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa mengatakan eskalasi konflik di Timur Tengah mendorong kenaikan imbal hasil Surat ...</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
+          <t>https://www.antaranews.com/berita/5678253/menkeu-eskalasi-konflik-timteng-dorong-imbal-hasil-sbn-ke-714-persen</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-20.38.31.jpeg</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>ekonomi-finansial, top-news</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Menkeu: Eskalasi konflik Timteng dorong imbal hasil SBN ke 7,14 persen</t>
+          <t>Prabowo dukung peningkatan latihan bersama militer RI-Thailand</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 20:48:02 +0700</t>
+          <t>Mon, 03 Aug 2026 19:21:32 +0700</t>
         </is>
       </c>
       <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa mengatakan eskalasi konflik di Timur Tengah mendorong kenaikan imbal hasil Surat ...</t>
+          <t>Presiden Prabowo Subianto mendukung peningkatan frekuensi latihan bersama antara Tentara Nasional Indonesia (TNI) dan ...</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678253/menkeu-eskalasi-konflik-timteng-dorong-imbal-hasil-sbn-ke-714-persen</t>
+          <t>https://www.antaranews.com/berita/5678081/prabowo-dukung-peningkatan-latihan-bersama-militer-ri-thailand</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-20.38.31.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.41.07.jpeg</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-finansial, top-news</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Prabowo dukung peningkatan latihan bersama militer RI-Thailand</t>
+          <t>OJK: Kredit perbankan tumbuh 12,67 persen capai Rp9.080,9 triliun</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:21:32 +0700</t>
+          <t>Mon, 03 Aug 2026 19:12:24 +0700</t>
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Presiden Prabowo Subianto mendukung peningkatan frekuensi latihan bersama antara Tentara Nasional Indonesia (TNI) dan ...</t>
+          <t>Otoritas Jasa Keuangan (OJK) melaporkan penyaluran kredit perbankan di tanah air tumbuh 12,67 persen year on year ...</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678081/prabowo-dukung-peningkatan-latihan-bersama-militer-ri-thailand</t>
+          <t>https://www.antaranews.com/berita/5678057/ojk-kredit-perbankan-tumbuh-1267-persen-capai-rp90809-triliun</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.41.07.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.15.18_1.jpeg</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>ekonomi-finansial, top-news</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>OJK: Kredit perbankan tumbuh 12,67 persen capai Rp9.080,9 triliun</t>
+          <t>Menkomdigi: KIP garda depan informasi jernih dan perangi hoaks</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:12:24 +0700</t>
+          <t>Mon, 03 Aug 2026 19:00:50 +0700</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Otoritas Jasa Keuangan (OJK) melaporkan penyaluran kredit perbankan di tanah air tumbuh 12,67 persen year on year ...</t>
+          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid mengatakan Komisi Informasi Pusat (KIP) menjadi garda terdepan ...</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678057/ojk-kredit-perbankan-tumbuh-1267-persen-capai-rp90809-triliun</t>
+          <t>https://www.antaranews.com/berita/5678033/menkomdigi-kip-garda-depan-informasi-jernih-dan-perangi-hoaks</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.15.18_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0321.jpg</t>
         </is>
       </c>
     </row>
@@ -12083,28 +12083,28 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Menkomdigi: KIP garda depan informasi jernih dan perangi hoaks</t>
+          <t>Satu tahun Sekolah Rakyat, ratusan siswa torehkan prestasi</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:00:50 +0700</t>
+          <t>Mon, 03 Aug 2026 18:59:25 +0700</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid mengatakan Komisi Informasi Pusat (KIP) menjadi garda terdepan ...</t>
+          <t>Menteri Sosial (Mensos) Saifullah Yusuf menyatakan selama satu tahun Sekolah Rakyat berdiri sudah ratusan ...</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678033/menkomdigi-kip-garda-depan-informasi-jernih-dan-perangi-hoaks</t>
+          <t>https://www.antaranews.com/berita/5678024/satu-tahun-sekolah-rakyat-ratusan-siswa-torehkan-prestasi</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0321.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176441.jpg</t>
         </is>
       </c>
     </row>
@@ -12116,28 +12116,28 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Satu tahun Sekolah Rakyat, ratusan siswa torehkan prestasi</t>
+          <t>Menkeu: Realisasi anggaran MBG Rp101,1 T untuk 63,13 juta penerima</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:59:25 +0700</t>
+          <t>Mon, 03 Aug 2026 18:53:14 +0700</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Menteri Sosial (Mensos) Saifullah Yusuf menyatakan selama satu tahun Sekolah Rakyat berdiri sudah ratusan ...</t>
+          <t>Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa mengungkapkan bahwa realisasi anggaran Program Makan Bergizi Gratis ...</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678024/satu-tahun-sekolah-rakyat-ratusan-siswa-torehkan-prestasi</t>
+          <t>https://www.antaranews.com/berita/5678005/menkeu-realisasi-anggaran-mbg-rp1011-t-untuk-6313-juta-penerima</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176441.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29-2.jpeg</t>
         </is>
       </c>
     </row>
@@ -12149,28 +12149,28 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Menkeu: Realisasi anggaran MBG Rp101,1 T untuk 63,13 juta penerima</t>
+          <t>Polri perkuat langkah preventif respons isu keamanan nasional</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:53:14 +0700</t>
+          <t>Mon, 03 Aug 2026 18:46:34 +0700</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa mengungkapkan bahwa realisasi anggaran Program Makan Bergizi Gratis ...</t>
+          <t>Polri memastikan terus memperkuat langkah preventif untuk menjaga keamanan nasional sehingga aktivitas masyarakat dan ...</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678005/menkeu-realisasi-anggaran-mbg-rp1011-t-untuk-6313-juta-penerima</t>
+          <t>https://www.antaranews.com/berita/5677985/polri-perkuat-langkah-preventif-respons-isu-keamanan-nasional</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29-2.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/1000086556.jpg</t>
         </is>
       </c>
     </row>
@@ -12182,28 +12182,28 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Polri perkuat langkah preventif respons isu keamanan nasional</t>
+          <t>Prabowo dan PM Thailand bertemu empat mata di Istana Merdeka</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:46:34 +0700</t>
+          <t>Mon, 03 Aug 2026 17:49:52 +0700</t>
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Polri memastikan terus memperkuat langkah preventif untuk menjaga keamanan nasional sehingga aktivitas masyarakat dan ...</t>
+          <t>Presiden Prabowo Subianto dan Perdana Menteri Thailand Anutin Charnvirakul menggelar pertemuan empat mata di Istana ...</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677985/polri-perkuat-langkah-preventif-respons-isu-keamanan-nasional</t>
+          <t>https://www.antaranews.com/berita/5677828/prabowo-dan-pm-thailand-bertemu-empat-mata-di-istana-merdeka</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/1000086556.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_5162.jpeg</t>
         </is>
       </c>
     </row>
@@ -12215,28 +12215,29 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Prabowo dan PM Thailand bertemu empat mata di Istana Merdeka</t>
+          <t>Kepala BGN tingkatkan status keracunan MBG jadi kejadian fatal</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 17:49:52 +0700</t>
+          <t>Mon, 03 Aug 2026 17:10:19 +0700</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Presiden Prabowo Subianto dan Perdana Menteri Thailand Anutin Charnvirakul menggelar pertemuan empat mata di Istana ...</t>
+          <t>nya tidak dilanjutkan," ucap Sudaryono.
+Ia menegaskan BGN memberlakukan nol toleransi pada setiap status ...</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677828/prabowo-dan-pm-thailand-bertemu-empat-mata-di-istana-merdeka</t>
+          <t>https://www.antaranews.com/berita/5677743/kepala-bgn-tingkatkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_5162.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/ZAM02548_edit_2028523819372755.jpg</t>
         </is>
       </c>
     </row>
@@ -12248,29 +12249,28 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Kepala BGN tingkatkan status keracunan MBG jadi kejadian fatal</t>
+          <t>Harga minyak turun usai AS siap lanjutkan dialog dengan Iran</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 17:10:19 +0700</t>
+          <t>Mon, 03 Aug 2026 17:08:35 +0700</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr">
         <is>
-          <t>nya tidak dilanjutkan," ucap Sudaryono.
-Ia menegaskan BGN memberlakukan nol toleransi pada setiap status ...</t>
+          <t>Harga minyak turun lebih dari 5 persen, Senin, setelah Presiden Amerika Serikat Donald Trump ...</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677743/kepala-bgn-tingkatkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+          <t>https://www.antaranews.com/berita/5677735/harga-minyak-turun-usai-as-siap-lanjutkan-dialog-dengan-iran</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/ZAM02548_edit_2028523819372755.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/06/ilustrasi-isi-bensin-di-pom.jpg</t>
         </is>
       </c>
     </row>
@@ -12282,28 +12282,28 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Harga minyak turun usai AS siap lanjutkan dialog dengan Iran</t>
+          <t>Australia konfirmasi kematian massal pertama satwa akibat flu burung</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 17:08:35 +0700</t>
+          <t>Mon, 03 Aug 2026 16:48:50 +0700</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Harga minyak turun lebih dari 5 persen, Senin, setelah Presiden Amerika Serikat Donald Trump ...</t>
+          <t>Australia mengonfirmasi kematian massal satwa liar pertama terkait flu burung H5 yang mematikan, dengan burung camar ...</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677735/harga-minyak-turun-usai-as-siap-lanjutkan-dialog-dengan-iran</t>
+          <t>https://www.antaranews.com/berita/5677701/australia-konfirmasi-kematian-massal-pertama-satwa-akibat-flu-burung</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/06/ilustrasi-isi-bensin-di-pom.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/26/Virus-flu-burung-penyakit-unggas.jpg</t>
         </is>
       </c>
     </row>
@@ -12315,94 +12315,94 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Australia konfirmasi kematian massal pertama satwa akibat flu burung</t>
+          <t>Siklon 94 W,  waspada cuaca ekstrem &amp; gelombang tinggi di wilayah RI</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:48:50 +0700</t>
+          <t>Mon, 03 Aug 2026 16:30:38 +0700</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Australia mengonfirmasi kematian massal satwa liar pertama terkait flu burung H5 yang mematikan, dengan burung camar ...</t>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) mendeteksi pergerakan Bibit Siklon Tropis 94W di Laut Filipina ...</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677701/australia-konfirmasi-kematian-massal-pertama-satwa-akibat-flu-burung</t>
+          <t>https://www.antaranews.com/berita/5677641/siklon-94-w-waspada-cuaca-ekstrem-gelombang-tinggi-di-wilayah-ri</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/26/Virus-flu-burung-penyakit-unggas.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/27/1000395034.jpg</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>photo, top-news</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Siklon 94 W,  waspada cuaca ekstrem &amp; gelombang tinggi di wilayah RI</t>
+          <t>Petani berbagi air sumur demi selamatkan tanaman tembakau</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:30:38 +0700</t>
+          <t>Mon, 03 Aug 2026 14:44:51 +0700</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) mendeteksi pergerakan Bibit Siklon Tropis 94W di Laut Filipina ...</t>
+          <t>Petani mengambil air dari sumur untuk menyiram tanaman tembakau di Lengkong, Nganjuk, Jawa Timur, Senin (3/8/2026). ...</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677641/siklon-94-w-waspada-cuaca-ekstrem-gelombang-tinggi-di-wilayah-ri</t>
+          <t>https://www.antaranews.com/foto/5677428/petani-berbagi-air-sumur-demi-selamatkan-tanaman-tembakau</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/27/1000395034.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/petani-tembakau-berbagi-air-sumur-antisipasi-dampak-el-nino-030826-mm-1.jpg</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>photo, top-news</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Petani berbagi air sumur demi selamatkan tanaman tembakau</t>
+          <t>Nusron sebut banyak laut di Batam telah dikapling tanpa prosedur sah</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:44:51 +0700</t>
+          <t>Mon, 03 Aug 2026 14:44:05 +0700</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Petani mengambil air dari sumur untuk menyiram tanaman tembakau di Lengkong, Nganjuk, Jawa Timur, Senin (3/8/2026). ...</t>
+          <t>Menteri Agraria dan Tata Ruang (ATR)/Kepala Badan Pertanahan Nasional (BPN) Nusron Wahid mengatakan, menerima banyak ...</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5677428/petani-berbagi-air-sumur-demi-selamatkan-tanaman-tembakau</t>
+          <t>https://www.antaranews.com/berita/5677425/nusron-sebut-banyak-laut-di-batam-telah-dikapling-tanpa-prosedur-sah</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/petani-tembakau-berbagi-air-sumur-antisipasi-dampak-el-nino-030826-mm-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_142345.jpg</t>
         </is>
       </c>
     </row>
@@ -12414,28 +12414,28 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Nusron sebut banyak laut di Batam telah dikapling tanpa prosedur sah</t>
+          <t>Menkomdigi panggil YouTube imbas temuan konten promosi vape sasar anak</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:44:05 +0700</t>
+          <t>Mon, 03 Aug 2026 14:22:09 +0700</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Menteri Agraria dan Tata Ruang (ATR)/Kepala Badan Pertanahan Nasional (BPN) Nusron Wahid mengatakan, menerima banyak ...</t>
+          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid merencanakan pemanggilan terhadap platform digital YouTube ...</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677425/nusron-sebut-banyak-laut-di-batam-telah-dikapling-tanpa-prosedur-sah</t>
+          <t>https://www.antaranews.com/berita/5677396/menkomdigi-panggil-youtube-imbas-temuan-konten-promosi-vape-sasar-anak</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_142345.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0225.jpg</t>
         </is>
       </c>
     </row>
@@ -12447,28 +12447,28 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Menkomdigi panggil YouTube imbas temuan konten promosi vape sasar anak</t>
+          <t>Kemnaker: Magang Nasional diharapkan menekan angka pengangguran muda</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:22:09 +0700</t>
+          <t>Mon, 03 Aug 2026 13:37:57 +0700</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid merencanakan pemanggilan terhadap platform digital YouTube ...</t>
+          <t>Kementerian Ketenagakerjaan (Kemnaker) mengatakan program Magang Nasional (MagangHub) untuk mempersiapkan kompetensi ...</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677396/menkomdigi-panggil-youtube-imbas-temuan-konten-promosi-vape-sasar-anak</t>
+          <t>https://www.antaranews.com/berita/5677364/kemnaker-magang-nasional-diharapkan-menekan-angka-pengangguran-muda</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0225.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/ff63afaf-7778-47fe-833d-5a8068af9a51_1.jpeg</t>
         </is>
       </c>
     </row>
@@ -12480,28 +12480,28 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Kemnaker: Magang Nasional diharapkan menekan angka pengangguran muda</t>
+          <t>Kemenag perkuat transformasi madrasah lewat revitalisasi-digitalisasi</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:37:57 +0700</t>
+          <t>Mon, 03 Aug 2026 13:36:36 +0700</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Kementerian Ketenagakerjaan (Kemnaker) mengatakan program Magang Nasional (MagangHub) untuk mempersiapkan kompetensi ...</t>
+          <t>Menteri Agama (Menag) Nasaruddin Umar menegaskan transformasi madrasah terus diperkuat melalui revitalisasi ...</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677364/kemnaker-magang-nasional-diharapkan-menekan-angka-pengangguran-muda</t>
+          <t>https://www.antaranews.com/berita/5677363/kemenag-perkuat-transformasi-madrasah-lewat-revitalisasi-digitalisasi</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/ff63afaf-7778-47fe-833d-5a8068af9a51_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/14/1000173935_1.jpg</t>
         </is>
       </c>
     </row>
@@ -12513,28 +12513,28 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Kemenag perkuat transformasi madrasah lewat revitalisasi-digitalisasi</t>
+          <t>Lisensi IP Global Buka Peluang Bisnis Baru bagi Kreator Indonesia</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:36:36 +0700</t>
+          <t>Mon, 03 Aug 2026 13:34:30 +0700</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Menteri Agama (Menag) Nasaruddin Umar menegaskan transformasi madrasah terus diperkuat melalui revitalisasi ...</t>
+          <t>Wakil Menteri Ekonomi Kreatif Irene Umar mengatakan kolaborasi antara pemilik kekayaan intelektual (Intellectual ...</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677363/kemenag-perkuat-transformasi-madrasah-lewat-revitalisasi-digitalisasi</t>
+          <t>https://www.antaranews.com/berita/5677353/lisensi-ip-global-buka-peluang-bisnis-baru-bagi-kreator-indonesia</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/14/1000173935_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000589873.jpg</t>
         </is>
       </c>
     </row>
@@ -12546,28 +12546,28 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Lisensi IP Global Buka Peluang Bisnis Baru bagi Kreator Indonesia</t>
+          <t>Nilai ekspor perdagangan RI Januari-Juni capai 140,81 miliar dolar AS</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:34:30 +0700</t>
+          <t>Mon, 03 Aug 2026 13:16:17 +0700</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Wakil Menteri Ekonomi Kreatif Irene Umar mengatakan kolaborasi antara pemilik kekayaan intelektual (Intellectual ...</t>
+          <t>Badan Pusat Statistik (BPS) mencatat nilai ekspor Indonesia secara kumulatif dari Januari-Juni 2026 mencapai 140,81 ...</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677353/lisensi-ip-global-buka-peluang-bisnis-baru-bagi-kreator-indonesia</t>
+          <t>https://www.antaranews.com/berita/5677315/nilai-ekspor-perdagangan-ri-januari-juni-capai-14081-miliar-dolar-as</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000589873.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/neraca-perdagangan-januari-mei-2026-surplus-2815779.jpg</t>
         </is>
       </c>
     </row>
@@ -12579,28 +12579,28 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Nilai ekspor perdagangan RI Januari-Juni capai 140,81 miliar dolar AS</t>
+          <t>Korban KMP Mutiara Sentosa II dievakuasi ke Pelabuhan Tanjung Perak</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:16:17 +0700</t>
+          <t>Mon, 03 Aug 2026 13:06:15 +0700</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat nilai ekspor Indonesia secara kumulatif dari Januari-Juni 2026 mencapai 140,81 ...</t>
+          <t>Tim SAR gabungan terus melakukan evakuasi korban terbakarnya KMP Mutiara Sentosa 2 ke darat, tepatnya ke Pelabuhan ...</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677315/nilai-ekspor-perdagangan-ri-januari-juni-capai-14081-miliar-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5677297/korban-kmp-mutiara-sentosa-ii-dievakuasi-ke-pelabuhan-tanjung-perak</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/neraca-perdagangan-januari-mei-2026-surplus-2815779.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/260821_1.jpg</t>
         </is>
       </c>
     </row>
@@ -12612,28 +12612,28 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Korban KMP Mutiara Sentosa II dievakuasi ke Pelabuhan Tanjung Perak</t>
+          <t>Aktor senior Diding Boneng meninggal dunia</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:06:15 +0700</t>
+          <t>Mon, 03 Aug 2026 11:39:03 +0700</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Tim SAR gabungan terus melakukan evakuasi korban terbakarnya KMP Mutiara Sentosa 2 ke darat, tepatnya ke Pelabuhan ...</t>
+          <t>Aktor sekaligus komedian tanah air, Zainal Abidin alias Diding Boneng dikabarkan meninggal dunia pada Senin (3/8) dalam ...</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677297/korban-kmp-mutiara-sentosa-ii-dievakuasi-ke-pelabuhan-tanjung-perak</t>
+          <t>https://www.antaranews.com/berita/5677209/aktor-senior-diding-boneng-meninggal-dunia</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/260821_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/26f1eb88-3301-4ae1-badd-bed5078fe3dd.jpeg</t>
         </is>
       </c>
     </row>
@@ -12645,28 +12645,28 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Aktor senior Diding Boneng meninggal dunia</t>
+          <t>Seskab: Prabowo dorong sinergi pemerintah dan dunia usaha</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:39:03 +0700</t>
+          <t>Mon, 03 Aug 2026 11:17:50 +0700</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Aktor sekaligus komedian tanah air, Zainal Abidin alias Diding Boneng dikabarkan meninggal dunia pada Senin (3/8) dalam ...</t>
+          <t>Sekretaris Kabinet Teddy Indra Wijaya menyampaikan bahwa Presiden Prabowo Subianto menekankan pentingnya sinergi antara ...</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677209/aktor-senior-diding-boneng-meninggal-dunia</t>
+          <t>https://www.antaranews.com/berita/5677191/seskab-prabowo-dorong-sinergi-pemerintah-dan-dunia-usaha</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/26f1eb88-3301-4ae1-badd-bed5078fe3dd.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0891_1.jpeg</t>
         </is>
       </c>
     </row>
@@ -12678,28 +12678,28 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Seskab: Prabowo dorong sinergi pemerintah dan dunia usaha</t>
+          <t>Red Velvet bersiap kembali lewat EP baru "Velvet Summer"</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:17:50 +0700</t>
+          <t>Mon, 03 Aug 2026 10:24:37 +0700</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Sekretaris Kabinet Teddy Indra Wijaya menyampaikan bahwa Presiden Prabowo Subianto menekankan pentingnya sinergi antara ...</t>
+          <t>Grup idola K-pop Red Velvet akan kembali lewat rilis mini album atau extended play (EP) baru bertajuk “Velvet ...</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677191/seskab-prabowo-dorong-sinergi-pemerintah-dan-dunia-usaha</t>
+          <t>https://www.antaranews.com/berita/5677151/red-velvet-bersiap-kembali-lewat-ep-baru-velvet-summer</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0891_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/ca97a3a8-aa17-45fc-be71-d36051dd9dcd.jpeg</t>
         </is>
       </c>
     </row>
@@ -12711,28 +12711,28 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Red Velvet bersiap kembali lewat EP baru "Velvet Summer"</t>
+          <t>Menaker pastikan komitmen pemerintah perkuat kesejahteraan pekerja</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:24:37 +0700</t>
+          <t>Mon, 03 Aug 2026 10:16:19 +0700</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Grup idola K-pop Red Velvet akan kembali lewat rilis mini album atau extended play (EP) baru bertajuk “Velvet ...</t>
+          <t>Menteri Ketenagakerjaan (Menaker) Yassierli memastikan pemerintah berkomitmen untuk memperkuat kesejahteraan, ...</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677151/red-velvet-bersiap-kembali-lewat-ep-baru-velvet-summer</t>
+          <t>https://www.antaranews.com/berita/5677148/menaker-pastikan-komitmen-pemerintah-perkuat-kesejahteraan-pekerja</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/ca97a3a8-aa17-45fc-be71-d36051dd9dcd.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/09/20/pelepasan-peserta-pemagangan-ke-jepang-di-jawa-barat-2627513.jpg</t>
         </is>
       </c>
     </row>
@@ -12744,28 +12744,28 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Menaker pastikan komitmen pemerintah perkuat kesejahteraan pekerja</t>
+          <t>23 calon hakim agung dan ad hoc ikuti seleksi wawancara akhir</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:16:19 +0700</t>
+          <t>Mon, 03 Aug 2026 10:15:01 +0700</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Menteri Ketenagakerjaan (Menaker) Yassierli memastikan pemerintah berkomitmen untuk memperkuat kesejahteraan, ...</t>
+          <t>Sebanyak 23 orang calon hakim agung dan ad hoc Mahkamah Agung Tahun 2026 mengikuti seleksi wawancara tahap akhir di ...</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677148/menaker-pastikan-komitmen-pemerintah-perkuat-kesejahteraan-pekerja</t>
+          <t>https://www.antaranews.com/berita/5677137/23-calon-hakim-agung-dan-ad-hoc-ikuti-seleksi-wawancara-akhir</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/09/20/pelepasan-peserta-pemagangan-ke-jepang-di-jawa-barat-2627513.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000012883_1.jpg</t>
         </is>
       </c>
     </row>
@@ -12777,28 +12777,28 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>23 calon hakim agung dan ad hoc ikuti seleksi wawancara akhir</t>
+          <t>BRIN perkuat kajian sungai bawah tanah di Kebumen untuk ketahanan air</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:15:01 +0700</t>
+          <t>Mon, 03 Aug 2026 09:57:19 +0700</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Sebanyak 23 orang calon hakim agung dan ad hoc Mahkamah Agung Tahun 2026 mengikuti seleksi wawancara tahap akhir di ...</t>
+          <t>Badan Riset dan Inovasi Nasional (BRIN) memperkuat riset ketahanan air melalui pengembangan teknologi dan penelitian ...</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677137/23-calon-hakim-agung-dan-ad-hoc-ikuti-seleksi-wawancara-akhir</t>
+          <t>https://www.antaranews.com/berita/5677120/brin-perkuat-kajian-sungai-bawah-tanah-di-kebumen-untuk-ketahanan-air</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000012883_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1785706440-47672950-1.jpg</t>
         </is>
       </c>
     </row>
@@ -12810,28 +12810,28 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>BRIN perkuat kajian sungai bawah tanah di Kebumen untuk ketahanan air</t>
+          <t>Harga bensin turun pada pekan pertama Agustus</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:57:19 +0700</t>
+          <t>Mon, 03 Aug 2026 09:51:00 +0700</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Badan Riset dan Inovasi Nasional (BRIN) memperkuat riset ketahanan air melalui pengembangan teknologi dan penelitian ...</t>
+          <t>Harga bahan bakar minyak (BBM) jenis bensin di stasiun pengisian bahan bakar umum (SPBU) Pertamina, Shell, dan bp ...</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677120/brin-perkuat-kajian-sungai-bawah-tanah-di-kebumen-untuk-ketahanan-air</t>
+          <t>https://www.antaranews.com/berita/5677109/harga-bensin-turun-pada-pekan-pertama-agustus</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1785706440-47672950-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/10/02/penuruanan-harga-bbm-011024-aaa-7.jpg</t>
         </is>
       </c>
     </row>
@@ -12843,61 +12843,61 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Harga bensin turun pada pekan pertama Agustus</t>
+          <t>Sean Gelael berbagi pengalaman di dunia balap ke pengunjung GIIAS 2026</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:51:00 +0700</t>
+          <t>Mon, 03 Aug 2026 09:34:53 +0700</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Harga bahan bakar minyak (BBM) jenis bensin di stasiun pengisian bahan bakar umum (SPBU) Pertamina, Shell, dan bp ...</t>
+          <t>Pembalap Indonesia Sean Gelael berbagi pengalamannya di dunia balap ke pengunjung GAIKINDO Indonesia International ...</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677109/harga-bensin-turun-pada-pekan-pertama-agustus</t>
+          <t>https://www.antaranews.com/berita/5677103/sean-gelael-berbagi-pengalaman-di-dunia-balap-ke-pengunjung-giias-2026</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/10/02/penuruanan-harga-bbm-011024-aaa-7.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/16b70b87-326f-479a-a806-580ab846cc6f_1.jpeg</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Sean Gelael berbagi pengalaman di dunia balap ke pengunjung GIIAS 2026</t>
+          <t>Cadangan devisa RI jadi 145 M dolar AS, BI sebut masih di level aman</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:34:53 +0700</t>
+          <t>Mon, 03 Aug 2026 21:52:44 +0700</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Pembalap Indonesia Sean Gelael berbagi pengalamannya di dunia balap ke pengunjung GAIKINDO Indonesia International ...</t>
+          <t>ANTARA - Bank Indonesia (BI) mengungkapkan cadangan devisa pada akhir Juli 2026 berada di posisi 145 miliar dolar AS. ...</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677103/sean-gelael-berbagi-pengalaman-di-dunia-balap-ke-pengunjung-giias-2026</t>
+          <t>https://www.antaranews.com/video/5678347/cadangan-devisa-ri-jadi-145-m-dolar-as-bi-sebut-masih-di-level-aman</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/16b70b87-326f-479a-a806-580ab846cc6f_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_CADANGAN-DEVISA-RI-JADI-145-M-DOLAR-AS-BI-SEBUT-MASIH-DI-LEVEL-AMAN.jpg</t>
         </is>
       </c>
     </row>
@@ -12909,28 +12909,28 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Cadangan devisa RI jadi 145 M dolar AS, BI sebut masih di level aman</t>
+          <t>BI: Inflasi Juli terjaga berkat sinergi bank sentral dan pemerintah</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:52:44 +0700</t>
+          <t>Mon, 03 Aug 2026 21:51:39 +0700</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
-          <t>ANTARA - Bank Indonesia (BI) mengungkapkan cadangan devisa pada akhir Juli 2026 berada di posisi 145 miliar dolar AS. ...</t>
+          <t>Bank Indonesia (BI) memandang inflasi Indeks Harga Konsumen (IHK) pada Juli 2026 tetap terjaga dalam sasaran target, ...</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678347/cadangan-devisa-ri-jadi-145-m-dolar-as-bi-sebut-masih-di-level-aman</t>
+          <t>https://www.antaranews.com/berita/5678380/bi-inflasi-juli-terjaga-berkat-sinergi-bank-sentral-dan-pemerintah</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_CADANGAN-DEVISA-RI-JADI-145-M-DOLAR-AS-BI-SEBUT-MASIH-DI-LEVEL-AMAN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/07/WhatsApp-Image-2026-07-07-at-14.31.59_edited.jpg</t>
         </is>
       </c>
     </row>
@@ -12942,28 +12942,28 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>BI: Inflasi Juli terjaga berkat sinergi bank sentral dan pemerintah</t>
+          <t>BI: Kepemilikan SRBI oleh bank guna kelola likuiditas, bukan investasi</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:51:39 +0700</t>
+          <t>Mon, 03 Aug 2026 21:35:49 +0700</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Bank Indonesia (BI) memandang inflasi Indeks Harga Konsumen (IHK) pada Juli 2026 tetap terjaga dalam sasaran target, ...</t>
+          <t>Bank Indonesia (BI) menegaskan bahwa Sekuritas Rupiah Bank Indonesia (SRBI) ditujukan sebagai instrumen pengelolaan ...</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678380/bi-inflasi-juli-terjaga-berkat-sinergi-bank-sentral-dan-pemerintah</t>
+          <t>https://www.antaranews.com/berita/5678351/bi-kepemilikan-srbi-oleh-bank-guna-kelola-likuiditas-bukan-investasi</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/07/WhatsApp-Image-2026-07-07-at-14.31.59_edited.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-21.22.00.jpeg</t>
         </is>
       </c>
     </row>
@@ -12975,28 +12975,28 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>BI: Kepemilikan SRBI oleh bank guna kelola likuiditas, bukan investasi</t>
+          <t>KSSK prakirakan pertumbuhan ekonomi RI pada 2026 capai 5,6-6 persen</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:35:49 +0700</t>
+          <t>Mon, 03 Aug 2026 18:28:16 +0700</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Bank Indonesia (BI) menegaskan bahwa Sekuritas Rupiah Bank Indonesia (SRBI) ditujukan sebagai instrumen pengelolaan ...</t>
+          <t>Komite Stabilitas Sistem Keuangan (KSSK) memprakirakan ekonomi Indonesia sepanjang 2026 tumbuh dalam kisaran ...</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678351/bi-kepemilikan-srbi-oleh-bank-guna-kelola-likuiditas-bukan-investasi</t>
+          <t>https://www.antaranews.com/berita/5677935/kssk-prakirakan-pertumbuhan-ekonomi-ri-pada-2026-capai-56-6-persen</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-21.22.00.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.19.55.jpeg</t>
         </is>
       </c>
     </row>
@@ -13008,28 +13008,28 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>KSSK prakirakan pertumbuhan ekonomi RI pada 2026 capai 5,6-6 persen</t>
+          <t>Rupiah menguat dipengaruhi PMI manufaktur Indonesia naik jadi 50,2</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:28:16 +0700</t>
+          <t>Mon, 03 Aug 2026 16:58:46 +0700</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Komite Stabilitas Sistem Keuangan (KSSK) memprakirakan ekonomi Indonesia sepanjang 2026 tumbuh dalam kisaran ...</t>
+          <t>Nilai tukar rupiah terhadap dolar AS pada penutupan perdagangan Senin, bergerak menguat 25 poin atau 0,14 persen ...</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677935/kssk-prakirakan-pertumbuhan-ekonomi-ri-pada-2026-capai-56-6-persen</t>
+          <t>https://www.antaranews.com/berita/5677712/rupiah-menguat-dipengaruhi-pmi-manufaktur-indonesia-naik-jadi-502</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.19.55.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/12/nilai-tukar-rupiah-melemah-115-poin-2788415.jpg</t>
         </is>
       </c>
     </row>
@@ -13041,28 +13041,28 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Rupiah menguat dipengaruhi PMI manufaktur Indonesia naik jadi 50,2</t>
+          <t>KSSK: Sistem keuangan TW-II tetap terjaga di tengah konflik geopolitik</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:58:46 +0700</t>
+          <t>Mon, 03 Aug 2026 16:26:03 +0700</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Nilai tukar rupiah terhadap dolar AS pada penutupan perdagangan Senin, bergerak menguat 25 poin atau 0,14 persen ...</t>
+          <t>Komite Stabilitas Sistem Keuangan (KSSK) menilai kondisi fiskal, moneter dan sektor keuangan selama triwulan II 2026 ...</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677712/rupiah-menguat-dipengaruhi-pmi-manufaktur-indonesia-naik-jadi-502</t>
+          <t>https://www.antaranews.com/berita/5677625/kssk-sistem-keuangan-tw-ii-tetap-terjaga-di-tengah-konflik-geopolitik</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/12/nilai-tukar-rupiah-melemah-115-poin-2788415.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29.jpeg</t>
         </is>
       </c>
     </row>
@@ -13074,28 +13074,28 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>KSSK: Sistem keuangan TW-II tetap terjaga di tengah konflik geopolitik</t>
+          <t>Menjaga pintu air perekonomian Indonesia</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:26:03 +0700</t>
+          <t>Mon, 03 Aug 2026 16:04:40 +0700</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Komite Stabilitas Sistem Keuangan (KSSK) menilai kondisi fiskal, moneter dan sektor keuangan selama triwulan II 2026 ...</t>
+          <t>Bayangkan perekonomian Indonesia sebagai sebuah bendungan raksasa yang mengairi hamparan persawahan. Air yang mengalir ...</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677625/kssk-sistem-keuangan-tw-ii-tetap-terjaga-di-tengah-konflik-geopolitik</t>
+          <t>https://www.antaranews.com/berita/5677565/menjaga-pintu-air-perekonomian-indonesia</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/06/peringati-hari-bank-indonesia-doku-perkuat-ekosistem-pembayaran-2817675.jpg</t>
         </is>
       </c>
     </row>
@@ -13107,28 +13107,28 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Menjaga pintu air perekonomian Indonesia</t>
+          <t>Rupiah diperkirakan menguat seiring AS batalkan rencana serang Iran</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:04:40 +0700</t>
+          <t>Mon, 03 Aug 2026 10:12:26 +0700</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Bayangkan perekonomian Indonesia sebagai sebuah bendungan raksasa yang mengairi hamparan persawahan. Air yang mengalir ...</t>
+          <t>Analis Doo Financial Futures, Lukman Leong memperkirakan rupiah menguat seiring Amerika Serikat (AS) membatalkan ...</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677565/menjaga-pintu-air-perekonomian-indonesia</t>
+          <t>https://www.antaranews.com/berita/5677132/rupiah-diperkirakan-menguat-seiring-as-batalkan-rencana-serang-iran</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/06/peringati-hari-bank-indonesia-doku-perkuat-ekosistem-pembayaran-2817675.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828847.jpg</t>
         </is>
       </c>
     </row>
@@ -13140,28 +13140,28 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Rupiah diperkirakan menguat seiring AS batalkan rencana serang Iran</t>
+          <t>Rupiah pada Senin pagi melemah jadi Rp18.031 per dolar AS</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:12:26 +0700</t>
+          <t>Mon, 03 Aug 2026 09:05:50 +0700</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Analis Doo Financial Futures, Lukman Leong memperkirakan rupiah menguat seiring Amerika Serikat (AS) membatalkan ...</t>
+          <t>Nilai tukar rupiah pada Senin pagi bergerak melemah 9 poin atau 0,05 persen menjadi Rp18.031 per dolar AS dibandingkan ...</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677132/rupiah-diperkirakan-menguat-seiring-as-batalkan-rencana-serang-iran</t>
+          <t>https://www.antaranews.com/berita/5677063/rupiah-pada-senin-pagi-melemah-jadi-rp18031-per-dolar-as</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828847.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
         </is>
       </c>
     </row>
@@ -13173,28 +13173,28 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Rupiah pada Senin pagi melemah jadi Rp18.031 per dolar AS</t>
+          <t>Komisi XI: PFII peluang RI tangkap momentum perpindahan modal global</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:05:50 +0700</t>
+          <t>Mon, 03 Aug 2026 06:53:34 +0700</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Nilai tukar rupiah pada Senin pagi bergerak melemah 9 poin atau 0,05 persen menjadi Rp18.031 per dolar AS dibandingkan ...</t>
+          <t>Wakil Ketua Komisi XI DPR RI Mohamad Hekal mengatakan percepatan pembentukan Pusat Finansial Internasional Indonesia ...</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677063/rupiah-pada-senin-pagi-melemah-jadi-rp18031-per-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5676995/komisi-xi-pfii-peluang-ri-tangkap-momentum-perpindahan-modal-global</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Saham-dan-oblogasi.jpg</t>
         </is>
       </c>
     </row>
@@ -13206,61 +13206,61 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Komisi XI: PFII peluang RI tangkap momentum perpindahan modal global</t>
+          <t>BUMA International Group bukukan pertumbuhan EBITDA semester I/2026</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:53:34 +0700</t>
+          <t>Mon, 03 Aug 2026 06:17:40 +0700</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Wakil Ketua Komisi XI DPR RI Mohamad Hekal mengatakan percepatan pembentukan Pusat Finansial Internasional Indonesia ...</t>
+          <t>PT BUMA Internasional Gorup membukukan pertumbuhan EBITDA pada semester pertama 2026 (1H26) di tengah penurunan ...</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676995/komisi-xi-pfii-peluang-ri-tangkap-momentum-perpindahan-modal-global</t>
+          <t>https://www.antaranews.com/berita/5676967/buma-international-group-bukukan-pertumbuhan-ebitda-semester-i-2026</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Saham-dan-oblogasi.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/buma.jpg</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>BUMA International Group bukukan pertumbuhan EBITDA semester I/2026</t>
+          <t>Wamen ATR: Ujian PPAT upaya berikan layanan yang baik</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:17:40 +0700</t>
+          <t>Mon, 03 Aug 2026 23:05:29 +0700</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr">
         <is>
-          <t>PT BUMA Internasional Gorup membukukan pertumbuhan EBITDA pada semester pertama 2026 (1H26) di tengah penurunan ...</t>
+          <t>Wakil Menteri Agraria dan Tata Ruang/Wakil Kepala Badan Pertanahan Nasional (Wamen ATR/Waka BPN) Ossy Dermawan ...</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676967/buma-international-group-bukukan-pertumbuhan-ebitda-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5678489/wamen-atr-ujian-ppat-upaya-berikan-layanan-yang-baik</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/buma.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_223512.jpg</t>
         </is>
       </c>
     </row>

--- a/data/berita_antara_2026-08-03.xlsx
+++ b/data/berita_antara_2026-08-03.xlsx
@@ -11225,28 +11225,28 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Chelsea umumkan transfer gelandang Inggris Jordan Henderson</t>
+          <t>Sudin PPAPP Jakbar sosialisasikan Sekolah Siaga Kependudukan</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:59:34 +0700</t>
+          <t>Mon, 03 Aug 2026 23:24:33 +0700</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Chelsea resmi mengumumkan kedatangan gelandang senior asal Inggris Jordan Henderson dengan status bebas transfer ...</t>
+          <t>Suku Dinas Pemberdayaan, Perlindungan Anak, dan Pengendalian Penduduk (Sudin PPAPP) Jakarta Barat (Jakbar) menggelar ...</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678548/chelsea-umumkan-transfer-gelandang-inggris-jordan-henderson</t>
+          <t>https://www.antaranews.com/berita/5678515/sudin-ppapp-jakbar-sosialisasikan-sekolah-siaga-kependudukan</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000042505.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0031_1.jpg</t>
         </is>
       </c>
     </row>
@@ -11258,28 +11258,28 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Nguyen Xuan Son ungkap alasan tak jadi starter saat kalahkan Indonesia</t>
+          <t>Klasemen Grup A Piala AFF : Timnas Indonesia turun ke peringkat tiga</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:56:45 +0700</t>
+          <t>Mon, 03 Aug 2026 23:23:51 +0700</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Penyerang Timnas Vietnam Nguyen Xuan Son mengungkapkan alasan dirinya tidak dimainkan sebagai starter saat timnya ...</t>
+          <t>Timnas Indonesia turun ke peringkat ketiga klasemen sementara Grup A Piala AFF 2026 setelah menelan kekalahan 0-3 dari ...</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678547/nguyen-xuan-son-ungkap-alasan-tak-jadi-starter-saat-kalahkan-indonesia</t>
+          <t>https://www.antaranews.com/berita/5678512/klasemen-grup-a-piala-aff-timnas-indonesia-turun-ke-peringkat-tiga</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1003314030.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833516.jpg</t>
         </is>
       </c>
     </row>
@@ -11291,61 +11291,61 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
+          <t>Turkiye sebut serangan Israel sabotase upaya damai di Gaza</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:55:47 +0700</t>
+          <t>Mon, 03 Aug 2026 23:18:30 +0700</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
-          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ...</t>
+          <t>Pemerintah Turkiye pada Senin menilai serangan Israel di Jalur Gaza telah menghambat berbagai inisiatif diplomatik yang ...</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+          <t>https://www.antaranews.com/berita/5678500/turkiye-sebut-serangan-israel-sabotase-upaya-damai-di-gaza</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/thumbs_b_c_186832d7ab4775afec853057c8952c3d.jpg</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>BPS kaitkan kenaikan TPK hotel bintang dengan kualitas wisman</t>
+          <t>Purbaya pastikan tak ada lagi perdebatan soal penarikan SAL dari bank</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:53:51 +0700</t>
+          <t>Mon, 03 Aug 2026 23:15:59 +0700</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) Bali mengaitkan kenaikan tingkat penghunian kamar (TPK) hotel bintang pada Juni 2026 dengan ...</t>
+          <t>Menteri Keuangan (Menkeu), Purbaya Yudhi Sadewa memastikan tidak ada lagi perdebatan mengenai penarikan dana ...</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678543/bps-kaitkan-kenaikan-tpk-hotel-bintang-dengan-kualitas-wisman</t>
+          <t>https://www.antaranews.com/berita/5678499/purbaya-pastikan-tak-ada-lagi-perdebatan-soal-penarikan-sal-dari-bank</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0332.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-23.02.47.jpeg</t>
         </is>
       </c>
     </row>
@@ -11357,127 +11357,127 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Jogja Run'nShine 2026 targetkan diikuti 3.500 pelari</t>
+          <t>Tim 9 Kejagung didesak usut pemilik uang-emas di rumah eks Jampidsus</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:52:29 +0700</t>
+          <t>Mon, 03 Aug 2026 23:10:43 +0700</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Pergelaran Jogja Run'nShine 2026 menargetkan diikuti sebanyak 3.500 pelari dengan memberikan pengalaman konsep ...</t>
+          <t>Tim 9 Kejaksaan Agung didesak mengusut tuntas pemilik uang tunai senilai Rp476 miliar dan emas batangan seberat 74 ...</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678540/jogja-runnshine-2026-targetkan-diikuti-3500-pelari</t>
+          <t>https://www.antaranews.com/berita/5678495/tim-9-kejagung-didesak-usut-pemilik-uang-emas-di-rumah-eks-jampidsus</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0103.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/1000175632.jpg</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Jenama perkakas otomotif Tekiro dapat pengakuan Guinnes World Records</t>
+          <t>Sean Gelael berbagi pengalaman di dunia balap ke pengunjung GIIAS 2026</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:47:06 +0700</t>
+          <t>Mon, 03 Aug 2026 09:34:53 +0700</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Jenama perkakas otomotif Tekiro mendapat pengakuan dari Guiness World Records berkat ...</t>
+          <t>Pembalap Indonesia Sean Gelael berbagi pengalamannya di dunia balap ke pengunjung GAIKINDO Indonesia International ...</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5678535/jenama-perkakas-otomotif-tekiro-dapat-pengakuan-guinnes-world-records</t>
+          <t>https://www.antaranews.com/berita/5677103/sean-gelael-berbagi-pengalaman-di-dunia-balap-ke-pengunjung-giias-2026</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-02-at-15.34.09-1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/16b70b87-326f-479a-a806-580ab846cc6f_1.jpeg</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Pemkab Sleman dukung kejuaraan dragbike tingkatkan ekonomi masyarakat</t>
+          <t>Gubernur tegaskan Sumut siap jadi pusat fashion Indonesia lewat wastra</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:42:42 +0700</t>
+          <t>Mon, 03 Aug 2026 21:37:04 +0700</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Pemerintah Kabupaten Sleman, Daerah Istimewa Yogyakarta, mendukung penuh penyelenggaraan Kejuaraan Dragbike Super ...</t>
+          <t>Gubernur Sumatera Utara (Sumut) Bobby Nasution menegaskan kesiapan Provinsi Sumut menjadi salah satu pusat fashion ...</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678532/pemkab-sleman-dukung-kejuaraan-dragbike-tingkatkan-ekonomi-masyarakat</t>
+          <t>https://www.antaranews.com/berita/5678355/gubernur-tegaskan-sumut-siap-jadi-pusat-fashion-indonesia-lewat-wastra</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000029422.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001029105.jpg</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>GMR nilai akses penerbangan langsung buka peluang ekonomi RI-India</t>
+          <t>Kapal BBM bermuatan 7.600 kiloliter masuk Lombok</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:41:32 +0700</t>
+          <t>Mon, 03 Aug 2026 21:32:28 +0700</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>GMR Group, perusahaan multinasional India yang bergerak di bidang infrastruktur, menilai akses penerbangan langsung ...</t>
+          <t>PT Pertamina Patra Niaga mendatangkan kapal pengangkut bahan bakar minyak (BBM) dengan total muatan 7.600 kiloliter ...</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678529/gmr-nilai-akses-penerbangan-langsung-buka-peluang-ekonomi-ri-india</t>
+          <t>https://www.antaranews.com/berita/5678341/kapal-bbm-bermuatan-7600-kiloliter-masuk-lombok</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/DSF3021.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001432720.jpg</t>
         </is>
       </c>
     </row>
@@ -11489,61 +11489,61 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PSSI raup dana Rp722 miliar dalam laporan keuangan tahunan</t>
+          <t>Chelsea umumkan transfer gelandang Inggris Jordan Henderson</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:37:46 +0700</t>
+          <t>Mon, 03 Aug 2026 23:59:34 +0700</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir menyebut organisasinya meraup dana senilai Rp722 ...</t>
+          <t>Chelsea resmi mengumumkan kedatangan gelandang senior asal Inggris Jordan Henderson dengan status bebas transfer ...</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678528/pssi-raup-dana-rp722-miliar-dalam-laporan-keuangan-tahunan</t>
+          <t>https://www.antaranews.com/berita/5678548/chelsea-umumkan-transfer-gelandang-inggris-jordan-henderson</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0098_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000042505.jpg</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Otorita kolaborasi PNM untuk pengembangan ekonomi masyarakat IKN</t>
+          <t>Nguyen Xuan Son ungkap alasan tak jadi starter saat kalahkan Indonesia</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:30:50 +0700</t>
+          <t>Mon, 03 Aug 2026 23:56:45 +0700</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Otorita Ibu Kota Nusantara (IKN) melakukan kolaborasi dengan PT Permodalan Nasional Madani (Persero) untuk pengembangan ...</t>
+          <t>Penyerang Timnas Vietnam Nguyen Xuan Son mengungkapkan alasan dirinya tidak dimainkan sebagai starter saat timnya ...</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678525/otorita-kolaborasi-pnm-untuk-pengembangan-ekonomi-masyarakat-ikn</t>
+          <t>https://www.antaranews.com/berita/5678547/nguyen-xuan-son-ungkap-alasan-tak-jadi-starter-saat-kalahkan-indonesia</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0012_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1003314030.jpg</t>
         </is>
       </c>
     </row>
@@ -11555,160 +11555,160 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>DPR: Wacana Prabowo jembatani dialog Korea sesuai politik bebas aktif</t>
+          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:30:13 +0700</t>
+          <t>Mon, 03 Aug 2026 23:55:47 +0700</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Wakil Ketua Komisi I DPR RI Dave Laksono menilai wacana Presiden Prabowo Subianto untuk menjembatani dialog antara ...</t>
+          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ...</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678521/dpr-wacana-prabowo-jembatani-dialog-korea-sesuai-politik-bebas-aktif</t>
+          <t>https://www.antaranews.com/video/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/22/IMG_20260422_175322.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Kongres PSSI sepakati pemilihan pengurus mundur ke Juli 2027</t>
+          <t>BPS kaitkan kenaikan TPK hotel bintang dengan kualitas wisman</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:30:00 +0700</t>
+          <t>Mon, 03 Aug 2026 23:53:51 +0700</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
-          <t>ANTARA - Kongres Biasa PSSI 2026 menyepakati perubahan jadwal Kongres Pemilihan Pengurus PSSI 2027 dari semula Mei ...</t>
+          <t>Badan Pusat Statistik (BPS) Bali mengaitkan kenaikan tingkat penghunian kamar (TPK) hotel bintang pada Juni 2026 dengan ...</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678395/kongres-pssi-sepakati-pemilihan-pengurus-mundur-ke-juli-2027</t>
+          <t>https://www.antaranews.com/berita/5678543/bps-kaitkan-kenaikan-tpk-hotel-bintang-dengan-kualitas-wisman</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KONGRES-PSSI-SEPAKATI-PEMILIHAN-PENGURUS-MUNDUR-KE-JULI-2027.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0332.jpeg</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Toyota Astra Motor perkenalkan Hilux generasi ke-9</t>
+          <t>Jogja Run'nShine 2026 targetkan diikuti 3.500 pelari</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:25:20 +0700</t>
+          <t>Mon, 03 Aug 2026 23:52:29 +0700</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr">
         <is>
-          <t>PT Toyota Astra Motor (TAM) memperkenalkan Hilux generasi ke-9 untuk mendukung pemenuhan kebutuhan operasional industri ...</t>
+          <t>Pergelaran Jogja Run'nShine 2026 menargetkan diikuti sebanyak 3.500 pelari dengan memberikan pengalaman konsep ...</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5678519/toyota-astra-motor-perkenalkan-hilux-generasi-ke-9</t>
+          <t>https://www.antaranews.com/berita/5678540/jogja-runnshine-2026-targetkan-diikuti-3500-pelari</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/photo_6307309656757440820_w-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0103.jpg</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Sudin PPAPP Jakbar sosialisasikan Sekolah Siaga Kependudukan</t>
+          <t>Jenama perkakas otomotif Tekiro dapat pengakuan Guinnes World Records</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:24:33 +0700</t>
+          <t>Mon, 03 Aug 2026 23:47:06 +0700</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Suku Dinas Pemberdayaan, Perlindungan Anak, dan Pengendalian Penduduk (Sudin PPAPP) Jakarta Barat (Jakbar) menggelar ...</t>
+          <t>Jenama perkakas otomotif Tekiro mendapat pengakuan dari Guiness World Records berkat ...</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678515/sudin-ppapp-jakbar-sosialisasikan-sekolah-siaga-kependudukan</t>
+          <t>https://otomotif.antaranews.com/berita/5678535/jenama-perkakas-otomotif-tekiro-dapat-pengakuan-guinnes-world-records</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0031_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-02-at-15.34.09-1.jpeg</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Klasemen Grup A Piala AFF : Timnas Indonesia turun ke peringkat tiga</t>
+          <t>Pemkab Sleman dukung kejuaraan dragbike tingkatkan ekonomi masyarakat</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:23:51 +0700</t>
+          <t>Mon, 03 Aug 2026 23:42:42 +0700</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Timnas Indonesia turun ke peringkat ketiga klasemen sementara Grup A Piala AFF 2026 setelah menelan kekalahan 0-3 dari ...</t>
+          <t>Pemerintah Kabupaten Sleman, Daerah Istimewa Yogyakarta, mendukung penuh penyelenggaraan Kejuaraan Dragbike Super ...</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678512/klasemen-grup-a-piala-aff-timnas-indonesia-turun-ke-peringkat-tiga</t>
+          <t>https://www.antaranews.com/berita/5678532/pemkab-sleman-dukung-kejuaraan-dragbike-tingkatkan-ekonomi-masyarakat</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833516.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000029422.jpg</t>
         </is>
       </c>
     </row>
@@ -11720,94 +11720,94 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>NTB menargetkan penonton MotoGP Mandalika tembus 140 ribu</t>
+          <t>GMR nilai akses penerbangan langsung buka peluang ekonomi RI-India</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:23:01 +0700</t>
+          <t>Mon, 03 Aug 2026 23:41:32 +0700</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Pemerintah Provinsi Nusa Tenggara Barat menargetkan jumlah penonton MotoGP di Sirkuit Mandalika pada 9-11 Oktober 2026 ...</t>
+          <t>GMR Group, perusahaan multinasional India yang bergerak di bidang infrastruktur, menilai akses penerbangan langsung ...</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678508/ntb-menargetkan-penonton-motogp-mandalika-tembus-140-ribu</t>
+          <t>https://www.antaranews.com/berita/5678529/gmr-nilai-akses-penerbangan-langsung-buka-peluang-ekonomi-ri-india</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260109-WA0024_copy_1280x797.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/DSF3021.jpeg</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Bulog: Margin naik jadi 7 persen, dukungan Presiden kawal swasembada</t>
+          <t>PSSI raup dana Rp722 miliar dalam laporan keuangan tahunan</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:19:51 +0700</t>
+          <t>Mon, 03 Aug 2026 23:37:46 +0700</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Direktur Utama Perum Bulog Ahmad Rizal Ramdhani menegaskan kenaikan margin fee menjadi 7 persen bentuk dukungan ...</t>
+          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir menyebut organisasinya meraup dana senilai Rp722 ...</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678504/bulog-margin-naik-jadi-7-persen-dukungan-presiden-kawal-swasembada</t>
+          <t>https://www.antaranews.com/berita/5678528/pssi-raup-dana-rp722-miliar-dalam-laporan-keuangan-tahunan</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/14C1B7CB-9D6F-49B9-9CD1-E40DD76E851C.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0098_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Turkiye sebut serangan Israel sabotase upaya damai di Gaza</t>
+          <t>Otorita kolaborasi PNM untuk pengembangan ekonomi masyarakat IKN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:18:30 +0700</t>
+          <t>Mon, 03 Aug 2026 23:30:50 +0700</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Pemerintah Turkiye pada Senin menilai serangan Israel di Jalur Gaza telah menghambat berbagai inisiatif diplomatik yang ...</t>
+          <t>Otorita Ibu Kota Nusantara (IKN) melakukan kolaborasi dengan PT Permodalan Nasional Madani (Persero) untuk pengembangan ...</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678500/turkiye-sebut-serangan-israel-sabotase-upaya-damai-di-gaza</t>
+          <t>https://www.antaranews.com/berita/5678525/otorita-kolaborasi-pnm-untuk-pengembangan-ekonomi-masyarakat-ikn</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/thumbs_b_c_186832d7ab4775afec853057c8952c3d.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0012_1.jpg</t>
         </is>
       </c>
     </row>
@@ -11819,28 +11819,28 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Purbaya pastikan tak ada lagi perdebatan soal penarikan SAL dari bank</t>
+          <t>DPR: Wacana Prabowo jembatani dialog Korea sesuai politik bebas aktif</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:15:59 +0700</t>
+          <t>Mon, 03 Aug 2026 23:30:13 +0700</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Menteri Keuangan (Menkeu), Purbaya Yudhi Sadewa memastikan tidak ada lagi perdebatan mengenai penarikan dana ...</t>
+          <t>Wakil Ketua Komisi I DPR RI Dave Laksono menilai wacana Presiden Prabowo Subianto untuk menjembatani dialog antara ...</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678499/purbaya-pastikan-tak-ada-lagi-perdebatan-soal-penarikan-sal-dari-bank</t>
+          <t>https://www.antaranews.com/berita/5678521/dpr-wacana-prabowo-jembatani-dialog-korea-sesuai-politik-bebas-aktif</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-23.02.47.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/22/IMG_20260422_175322.jpg</t>
         </is>
       </c>
     </row>
@@ -11852,28 +11852,28 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Tim 9 Kejagung didesak usut pemilik uang-emas di rumah eks Jampidsus</t>
+          <t>Kongres PSSI sepakati pemilihan pengurus mundur ke Juli 2027</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:10:43 +0700</t>
+          <t>Mon, 03 Aug 2026 23:30:00 +0700</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Tim 9 Kejaksaan Agung didesak mengusut tuntas pemilik uang tunai senilai Rp476 miliar dan emas batangan seberat 74 ...</t>
+          <t>ANTARA - Kongres Biasa PSSI 2026 menyepakati perubahan jadwal Kongres Pemilihan Pengurus PSSI 2027 dari semula Mei ...</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678495/tim-9-kejagung-didesak-usut-pemilik-uang-emas-di-rumah-eks-jampidsus</t>
+          <t>https://www.antaranews.com/video/5678395/kongres-pssi-sepakati-pemilihan-pengurus-mundur-ke-juli-2027</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/1000175632.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KONGRES-PSSI-SEPAKATI-PEMILIHAN-PENGURUS-MUNDUR-KE-JULI-2027.jpg</t>
         </is>
       </c>
     </row>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-20.38.31.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/konpers-hasil-rapat-berkala-kssk-iii-tahun-2026-2833267.jpg</t>
         </is>
       </c>
     </row>
@@ -12005,7 +12005,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.41.07.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Pertemuan-bilateral-antara-Indonesia-Thailand-di-Istana-Merdeka-03082026-gp-3.jpg</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.15.18_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Konpers-hasil-rapat-berkala-KSSK-III-tahun-2026-382026-pma-1.jpg</t>
         </is>
       </c>
     </row>
@@ -12104,7 +12104,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000176441.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000176441.jpg</t>
         </is>
       </c>
     </row>
@@ -12137,7 +12137,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29-2.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Konpers-hasil-rapat-berkala-KSSK-III-tahun-2026-382026-pma-8.jpg</t>
         </is>
       </c>
     </row>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/1000086556.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000086556.jpg</t>
         </is>
       </c>
     </row>
@@ -12203,7 +12203,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_5162.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/presiden-prabowo-terima-PM-Thailand-030226-gp-4.jpg</t>
         </is>
       </c>
     </row>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/06/ilustrasi-isi-bensin-di-pom.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/ilustrasi-isi-bensin-di-pom.jpg</t>
         </is>
       </c>
     </row>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/27/1000395034.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Peringatan-zona-merah-gelombang-tinggi-di-perairan-ntb-220125-AS-5.jpg</t>
         </is>
       </c>
     </row>
@@ -12838,33 +12838,33 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Sean Gelael berbagi pengalaman di dunia balap ke pengunjung GIIAS 2026</t>
+          <t>Cadangan devisa RI jadi 145 M dolar AS, BI sebut masih di level aman</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:34:53 +0700</t>
+          <t>Mon, 03 Aug 2026 21:52:44 +0700</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Pembalap Indonesia Sean Gelael berbagi pengalamannya di dunia balap ke pengunjung GAIKINDO Indonesia International ...</t>
+          <t>ANTARA - Bank Indonesia (BI) mengungkapkan cadangan devisa pada akhir Juli 2026 berada di posisi 145 miliar dolar AS. ...</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677103/sean-gelael-berbagi-pengalaman-di-dunia-balap-ke-pengunjung-giias-2026</t>
+          <t>https://www.antaranews.com/video/5678347/cadangan-devisa-ri-jadi-145-m-dolar-as-bi-sebut-masih-di-level-aman</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/16b70b87-326f-479a-a806-580ab846cc6f_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_CADANGAN-DEVISA-RI-JADI-145-M-DOLAR-AS-BI-SEBUT-MASIH-DI-LEVEL-AMAN.jpg</t>
         </is>
       </c>
     </row>
@@ -12876,28 +12876,28 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Cadangan devisa RI jadi 145 M dolar AS, BI sebut masih di level aman</t>
+          <t>BI: Inflasi Juli terjaga berkat sinergi bank sentral dan pemerintah</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:52:44 +0700</t>
+          <t>Mon, 03 Aug 2026 21:51:39 +0700</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>ANTARA - Bank Indonesia (BI) mengungkapkan cadangan devisa pada akhir Juli 2026 berada di posisi 145 miliar dolar AS. ...</t>
+          <t>Bank Indonesia (BI) memandang inflasi Indeks Harga Konsumen (IHK) pada Juli 2026 tetap terjaga dalam sasaran target, ...</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678347/cadangan-devisa-ri-jadi-145-m-dolar-as-bi-sebut-masih-di-level-aman</t>
+          <t>https://www.antaranews.com/berita/5678380/bi-inflasi-juli-terjaga-berkat-sinergi-bank-sentral-dan-pemerintah</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_CADANGAN-DEVISA-RI-JADI-145-M-DOLAR-AS-BI-SEBUT-MASIH-DI-LEVEL-AMAN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/07/WhatsApp-Image-2026-07-07-at-14.31.59_edited.jpg</t>
         </is>
       </c>
     </row>
@@ -12909,28 +12909,28 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>BI: Inflasi Juli terjaga berkat sinergi bank sentral dan pemerintah</t>
+          <t>BI: Kepemilikan SRBI oleh bank guna kelola likuiditas, bukan investasi</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:51:39 +0700</t>
+          <t>Mon, 03 Aug 2026 21:35:49 +0700</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Bank Indonesia (BI) memandang inflasi Indeks Harga Konsumen (IHK) pada Juli 2026 tetap terjaga dalam sasaran target, ...</t>
+          <t>Bank Indonesia (BI) menegaskan bahwa Sekuritas Rupiah Bank Indonesia (SRBI) ditujukan sebagai instrumen pengelolaan ...</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678380/bi-inflasi-juli-terjaga-berkat-sinergi-bank-sentral-dan-pemerintah</t>
+          <t>https://www.antaranews.com/berita/5678351/bi-kepemilikan-srbi-oleh-bank-guna-kelola-likuiditas-bukan-investasi</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/07/WhatsApp-Image-2026-07-07-at-14.31.59_edited.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-21.22.00.jpeg</t>
         </is>
       </c>
     </row>
@@ -12942,28 +12942,28 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>BI: Kepemilikan SRBI oleh bank guna kelola likuiditas, bukan investasi</t>
+          <t>KSSK prakirakan pertumbuhan ekonomi RI pada 2026 capai 5,6-6 persen</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:35:49 +0700</t>
+          <t>Mon, 03 Aug 2026 18:28:16 +0700</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Bank Indonesia (BI) menegaskan bahwa Sekuritas Rupiah Bank Indonesia (SRBI) ditujukan sebagai instrumen pengelolaan ...</t>
+          <t>Komite Stabilitas Sistem Keuangan (KSSK) memprakirakan ekonomi Indonesia sepanjang 2026 tumbuh dalam kisaran ...</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678351/bi-kepemilikan-srbi-oleh-bank-guna-kelola-likuiditas-bukan-investasi</t>
+          <t>https://www.antaranews.com/berita/5677935/kssk-prakirakan-pertumbuhan-ekonomi-ri-pada-2026-capai-56-6-persen</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-21.22.00.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.19.55.jpeg</t>
         </is>
       </c>
     </row>
@@ -12975,28 +12975,28 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>KSSK prakirakan pertumbuhan ekonomi RI pada 2026 capai 5,6-6 persen</t>
+          <t>Rupiah menguat dipengaruhi PMI manufaktur Indonesia naik jadi 50,2</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:28:16 +0700</t>
+          <t>Mon, 03 Aug 2026 16:58:46 +0700</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Komite Stabilitas Sistem Keuangan (KSSK) memprakirakan ekonomi Indonesia sepanjang 2026 tumbuh dalam kisaran ...</t>
+          <t>Nilai tukar rupiah terhadap dolar AS pada penutupan perdagangan Senin, bergerak menguat 25 poin atau 0,14 persen ...</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677935/kssk-prakirakan-pertumbuhan-ekonomi-ri-pada-2026-capai-56-6-persen</t>
+          <t>https://www.antaranews.com/berita/5677712/rupiah-menguat-dipengaruhi-pmi-manufaktur-indonesia-naik-jadi-502</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.19.55.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/12/nilai-tukar-rupiah-melemah-115-poin-2788415.jpg</t>
         </is>
       </c>
     </row>
@@ -13008,28 +13008,28 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Rupiah menguat dipengaruhi PMI manufaktur Indonesia naik jadi 50,2</t>
+          <t>KSSK: Sistem keuangan TW-II tetap terjaga di tengah konflik geopolitik</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:58:46 +0700</t>
+          <t>Mon, 03 Aug 2026 16:26:03 +0700</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Nilai tukar rupiah terhadap dolar AS pada penutupan perdagangan Senin, bergerak menguat 25 poin atau 0,14 persen ...</t>
+          <t>Komite Stabilitas Sistem Keuangan (KSSK) menilai kondisi fiskal, moneter dan sektor keuangan selama triwulan II 2026 ...</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677712/rupiah-menguat-dipengaruhi-pmi-manufaktur-indonesia-naik-jadi-502</t>
+          <t>https://www.antaranews.com/berita/5677625/kssk-sistem-keuangan-tw-ii-tetap-terjaga-di-tengah-konflik-geopolitik</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/12/nilai-tukar-rupiah-melemah-115-poin-2788415.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29.jpeg</t>
         </is>
       </c>
     </row>
@@ -13041,28 +13041,28 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>KSSK: Sistem keuangan TW-II tetap terjaga di tengah konflik geopolitik</t>
+          <t>Menjaga pintu air perekonomian Indonesia</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:26:03 +0700</t>
+          <t>Mon, 03 Aug 2026 16:04:40 +0700</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Komite Stabilitas Sistem Keuangan (KSSK) menilai kondisi fiskal, moneter dan sektor keuangan selama triwulan II 2026 ...</t>
+          <t>Bayangkan perekonomian Indonesia sebagai sebuah bendungan raksasa yang mengairi hamparan persawahan. Air yang mengalir ...</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677625/kssk-sistem-keuangan-tw-ii-tetap-terjaga-di-tengah-konflik-geopolitik</t>
+          <t>https://www.antaranews.com/berita/5677565/menjaga-pintu-air-perekonomian-indonesia</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-15.32.29.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/06/peringati-hari-bank-indonesia-doku-perkuat-ekosistem-pembayaran-2817675.jpg</t>
         </is>
       </c>
     </row>
@@ -13074,28 +13074,28 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Menjaga pintu air perekonomian Indonesia</t>
+          <t>Rupiah diperkirakan menguat seiring AS batalkan rencana serang Iran</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 16:04:40 +0700</t>
+          <t>Mon, 03 Aug 2026 10:12:26 +0700</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Bayangkan perekonomian Indonesia sebagai sebuah bendungan raksasa yang mengairi hamparan persawahan. Air yang mengalir ...</t>
+          <t>Analis Doo Financial Futures, Lukman Leong memperkirakan rupiah menguat seiring Amerika Serikat (AS) membatalkan ...</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677565/menjaga-pintu-air-perekonomian-indonesia</t>
+          <t>https://www.antaranews.com/berita/5677132/rupiah-diperkirakan-menguat-seiring-as-batalkan-rencana-serang-iran</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/06/peringati-hari-bank-indonesia-doku-perkuat-ekosistem-pembayaran-2817675.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828847.jpg</t>
         </is>
       </c>
     </row>
@@ -13107,28 +13107,28 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Rupiah diperkirakan menguat seiring AS batalkan rencana serang Iran</t>
+          <t>Rupiah pada Senin pagi melemah jadi Rp18.031 per dolar AS</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:12:26 +0700</t>
+          <t>Mon, 03 Aug 2026 09:05:50 +0700</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Analis Doo Financial Futures, Lukman Leong memperkirakan rupiah menguat seiring Amerika Serikat (AS) membatalkan ...</t>
+          <t>Nilai tukar rupiah pada Senin pagi bergerak melemah 9 poin atau 0,05 persen menjadi Rp18.031 per dolar AS dibandingkan ...</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677132/rupiah-diperkirakan-menguat-seiring-as-batalkan-rencana-serang-iran</t>
+          <t>https://www.antaranews.com/berita/5677063/rupiah-pada-senin-pagi-melemah-jadi-rp18031-per-dolar-as</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828847.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
         </is>
       </c>
     </row>
@@ -13140,28 +13140,28 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Rupiah pada Senin pagi melemah jadi Rp18.031 per dolar AS</t>
+          <t>Komisi XI: PFII peluang RI tangkap momentum perpindahan modal global</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 09:05:50 +0700</t>
+          <t>Mon, 03 Aug 2026 06:53:34 +0700</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Nilai tukar rupiah pada Senin pagi bergerak melemah 9 poin atau 0,05 persen menjadi Rp18.031 per dolar AS dibandingkan ...</t>
+          <t>Wakil Ketua Komisi XI DPR RI Mohamad Hekal mengatakan percepatan pembentukan Pusat Finansial Internasional Indonesia ...</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677063/rupiah-pada-senin-pagi-melemah-jadi-rp18031-per-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5676995/komisi-xi-pfii-peluang-ri-tangkap-momentum-perpindahan-modal-global</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Saham-dan-oblogasi.jpg</t>
         </is>
       </c>
     </row>
@@ -13173,61 +13173,61 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Komisi XI: PFII peluang RI tangkap momentum perpindahan modal global</t>
+          <t>BUMA International Group bukukan pertumbuhan EBITDA semester I/2026</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:53:34 +0700</t>
+          <t>Mon, 03 Aug 2026 06:17:40 +0700</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Wakil Ketua Komisi XI DPR RI Mohamad Hekal mengatakan percepatan pembentukan Pusat Finansial Internasional Indonesia ...</t>
+          <t>PT BUMA Internasional Gorup membukukan pertumbuhan EBITDA pada semester pertama 2026 (1H26) di tengah penurunan ...</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676995/komisi-xi-pfii-peluang-ri-tangkap-momentum-perpindahan-modal-global</t>
+          <t>https://www.antaranews.com/berita/5676967/buma-international-group-bukukan-pertumbuhan-ebitda-semester-i-2026</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Saham-dan-oblogasi.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/buma.jpg</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>BUMA International Group bukukan pertumbuhan EBITDA semester I/2026</t>
+          <t>Toyota Astra Motor perkenalkan Hilux generasi ke-9</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 06:17:40 +0700</t>
+          <t>Mon, 03 Aug 2026 23:25:20 +0700</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr">
         <is>
-          <t>PT BUMA Internasional Gorup membukukan pertumbuhan EBITDA pada semester pertama 2026 (1H26) di tengah penurunan ...</t>
+          <t>PT Toyota Astra Motor (TAM) memperkenalkan Hilux generasi ke-9 untuk mendukung pemenuhan kebutuhan operasional industri ...</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5676967/buma-international-group-bukukan-pertumbuhan-ebitda-semester-i-2026</t>
+          <t>https://otomotif.antaranews.com/berita/5678519/toyota-astra-motor-perkenalkan-hilux-generasi-ke-9</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/buma.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/photo_6307309656757440820_w-1.jpg</t>
         </is>
       </c>
     </row>
@@ -13239,28 +13239,28 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Wamen ATR: Ujian PPAT upaya berikan layanan yang baik</t>
+          <t>NTB menargetkan penonton MotoGP Mandalika tembus 140 ribu</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:05:29 +0700</t>
+          <t>Mon, 03 Aug 2026 23:23:01 +0700</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Wakil Menteri Agraria dan Tata Ruang/Wakil Kepala Badan Pertanahan Nasional (Wamen ATR/Waka BPN) Ossy Dermawan ...</t>
+          <t>Pemerintah Provinsi Nusa Tenggara Barat menargetkan jumlah penonton MotoGP di Sirkuit Mandalika pada 9-11 Oktober 2026 ...</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678489/wamen-atr-ujian-ppat-upaya-berikan-layanan-yang-baik</t>
+          <t>https://www.antaranews.com/berita/5678508/ntb-menargetkan-penonton-motogp-mandalika-tembus-140-ribu</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_223512.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260109-WA0024_copy_1280x797.jpg</t>
         </is>
       </c>
     </row>
@@ -13272,28 +13272,28 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Kementerian ATR/BPN telah terbitkan 124 ribu SK sertifikat rumah MBR</t>
+          <t>Bulog: Margin naik jadi 7 persen, dukungan Presiden kawal swasembada</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:56:36 +0700</t>
+          <t>Mon, 03 Aug 2026 23:19:51 +0700</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Kementerian Agraria dan Tata Ruang/Badan Pertanahan Nasional (ATR/BPN) menyatakan telah menerbitkan surat keputusan ...</t>
+          <t>Direktur Utama Perum Bulog Ahmad Rizal Ramdhani menegaskan kenaikan margin fee menjadi 7 persen bentuk dukungan ...</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678484/kementerian-atr-bpn-telah-terbitkan-124-ribu-sk-sertifikat-rumah-mbr</t>
+          <t>https://www.antaranews.com/berita/5678504/bulog-margin-naik-jadi-7-persen-dukungan-presiden-kawal-swasembada</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_224532.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/14C1B7CB-9D6F-49B9-9CD1-E40DD76E851C.jpeg</t>
         </is>
       </c>
     </row>
@@ -13305,28 +13305,28 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Menteri PKP tegaskan KUR Perumahan perkuat ekonomi keluarga</t>
+          <t>Wamen ATR: Ujian PPAT upaya berikan layanan yang baik</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:47:11 +0700</t>
+          <t>Mon, 03 Aug 2026 23:05:29 +0700</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Menteri Perumahan dan Kawasan Permukiman (PKP) Maruarar Sirait menegaskan bahwa Kredit Usaha Rakyat (KUR) Perumahan ...</t>
+          <t>Wakil Menteri Agraria dan Tata Ruang/Wakil Kepala Badan Pertanahan Nasional (Wamen ATR/Waka BPN) Ossy Dermawan ...</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678465/menteri-pkp-tegaskan-kur-perumahan-perkuat-ekonomi-keluarga</t>
+          <t>https://www.antaranews.com/berita/5678489/wamen-atr-ujian-ppat-upaya-berikan-layanan-yang-baik</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1321013.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_223512.jpg</t>
         </is>
       </c>
     </row>
@@ -13338,28 +13338,28 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Ekonom: Inflasi mereda, semester II jadi momentum jaga keseimbangan</t>
+          <t>Kementerian ATR/BPN telah terbitkan 124 ribu SK sertifikat rumah MBR</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:34:25 +0700</t>
+          <t>Mon, 03 Aug 2026 22:56:36 +0700</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Kepala Ekonom Trimegah Sekuritas Indonesia Fakhrul Fulvian menilai semester II-2026 menjadi momentum untuk menjaga ...</t>
+          <t>Kementerian Agraria dan Tata Ruang/Badan Pertanahan Nasional (ATR/BPN) menyatakan telah menerbitkan surat keputusan ...</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678439/ekonom-inflasi-mereda-semester-ii-jadi-momentum-jaga-keseimbangan</t>
+          <t>https://www.antaranews.com/berita/5678484/kementerian-atr-bpn-telah-terbitkan-124-ribu-sk-sertifikat-rumah-mbr</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/01/21/IMG_2637.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_224532.jpg</t>
         </is>
       </c>
     </row>
@@ -13371,28 +13371,28 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Pemkab Aceh Tenggara batasi pembelian BBM untuk cegah penimbunan</t>
+          <t>Menteri PKP tegaskan KUR Perumahan perkuat ekonomi keluarga</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:25:13 +0700</t>
+          <t>Mon, 03 Aug 2026 22:47:11 +0700</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Pemerintah Kabupaten Aceh Tenggara bersama Forkopimda setempat saat ini telah melakukan pembatasan pembelian bahan ...</t>
+          <t>Menteri Perumahan dan Kawasan Permukiman (PKP) Maruarar Sirait menegaskan bahwa Kredit Usaha Rakyat (KUR) Perumahan ...</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678431/pemkab-aceh-tenggara-batasi-pembelian-bbm-untuk-cegah-penimbunan</t>
+          <t>https://www.antaranews.com/berita/5678465/menteri-pkp-tegaskan-kur-perumahan-perkuat-ekonomi-keluarga</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/20260803-Bupati-Aceh-Tenggara-HM-Salim-Fakhry.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1321013.jpg</t>
         </is>
       </c>
     </row>
@@ -13404,28 +13404,28 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>MTI dorong kemudahan transaksi nirsentuh di MRT Jakarta</t>
+          <t>Ekonom: Inflasi mereda, semester II jadi momentum jaga keseimbangan</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:24:07 +0700</t>
+          <t>Mon, 03 Aug 2026 22:34:25 +0700</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr">
         <is>
-          <t>PT Mitra Transaksi Indonesia (MTI) atau YOKKE mendukung penerapan sistem pembayaran kartu nirsentuh berbasis Europay, ...</t>
+          <t>Kepala Ekonom Trimegah Sekuritas Indonesia Fakhrul Fulvian menilai semester II-2026 menjadi momentum untuk menjaga ...</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678427/mti-dorong-kemudahan-transaksi-nirsentuh-di-mrt-jakarta</t>
+          <t>https://www.antaranews.com/berita/5678439/ekonom-inflasi-mereda-semester-ii-jadi-momentum-jaga-keseimbangan</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.59.08.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/01/21/IMG_2637.jpeg</t>
         </is>
       </c>
     </row>
@@ -13437,28 +13437,28 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Gubernur tegaskan Sumut siap jadi pusat fashion Indonesia lewat wastra</t>
+          <t>Pemkab Aceh Tenggara batasi pembelian BBM untuk cegah penimbunan</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:37:04 +0700</t>
+          <t>Mon, 03 Aug 2026 22:25:13 +0700</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Gubernur Sumatera Utara (Sumut) Bobby Nasution menegaskan kesiapan Provinsi Sumut menjadi salah satu pusat fashion ...</t>
+          <t>Pemerintah Kabupaten Aceh Tenggara bersama Forkopimda setempat saat ini telah melakukan pembatasan pembelian bahan ...</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678355/gubernur-tegaskan-sumut-siap-jadi-pusat-fashion-indonesia-lewat-wastra</t>
+          <t>https://www.antaranews.com/berita/5678431/pemkab-aceh-tenggara-batasi-pembelian-bbm-untuk-cegah-penimbunan</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001029105.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/20260803-Bupati-Aceh-Tenggara-HM-Salim-Fakhry.jpeg</t>
         </is>
       </c>
     </row>
@@ -13470,28 +13470,28 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Kapal BBM bermuatan 7.600 kiloliter masuk Lombok</t>
+          <t>MTI dorong kemudahan transaksi nirsentuh di MRT Jakarta</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:32:28 +0700</t>
+          <t>Mon, 03 Aug 2026 22:24:07 +0700</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
       <c r="E395" t="inlineStr">
         <is>
-          <t>PT Pertamina Patra Niaga mendatangkan kapal pengangkut bahan bakar minyak (BBM) dengan total muatan 7.600 kiloliter ...</t>
+          <t>PT Mitra Transaksi Indonesia (MTI) atau YOKKE mendukung penerapan sistem pembayaran kartu nirsentuh berbasis Europay, ...</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678341/kapal-bbm-bermuatan-7600-kiloliter-masuk-lombok</t>
+          <t>https://www.antaranews.com/berita/5678427/mti-dorong-kemudahan-transaksi-nirsentuh-di-mrt-jakarta</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001432720.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.59.08.jpeg</t>
         </is>
       </c>
     </row>

--- a/data/berita_antara_2026-08-03.xlsx
+++ b/data/berita_antara_2026-08-03.xlsx
@@ -11583,33 +11583,33 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>BPS kaitkan kenaikan TPK hotel bintang dengan kualitas wisman</t>
+          <t>Jogja Run'nShine 2026 targetkan diikuti 3.500 pelari</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:53:51 +0700</t>
+          <t>Mon, 03 Aug 2026 23:52:29 +0700</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) Bali mengaitkan kenaikan tingkat penghunian kamar (TPK) hotel bintang pada Juni 2026 dengan ...</t>
+          <t>Pergelaran Jogja Run'nShine 2026 menargetkan diikuti sebanyak 3.500 pelari dengan memberikan pengalaman konsep ...</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678543/bps-kaitkan-kenaikan-tpk-hotel-bintang-dengan-kualitas-wisman</t>
+          <t>https://www.antaranews.com/berita/5678540/jogja-runnshine-2026-targetkan-diikuti-3500-pelari</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0332.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0103.jpg</t>
         </is>
       </c>
     </row>
@@ -11621,358 +11621,358 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Jogja Run'nShine 2026 targetkan diikuti 3.500 pelari</t>
+          <t>PSSI raup dana Rp722 miliar dalam laporan keuangan tahunan</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:52:29 +0700</t>
+          <t>Mon, 03 Aug 2026 23:37:46 +0700</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Pergelaran Jogja Run'nShine 2026 menargetkan diikuti sebanyak 3.500 pelari dengan memberikan pengalaman konsep ...</t>
+          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir menyebut organisasinya meraup dana senilai Rp722 ...</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678540/jogja-runnshine-2026-targetkan-diikuti-3500-pelari</t>
+          <t>https://www.antaranews.com/berita/5678528/pssi-raup-dana-rp722-miliar-dalam-laporan-keuangan-tahunan</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0103.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0098_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Jenama perkakas otomotif Tekiro dapat pengakuan Guinnes World Records</t>
+          <t>DPR: Wacana Prabowo jembatani dialog Korea sesuai politik bebas aktif</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:47:06 +0700</t>
+          <t>Mon, 03 Aug 2026 23:30:13 +0700</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Jenama perkakas otomotif Tekiro mendapat pengakuan dari Guiness World Records berkat ...</t>
+          <t>Wakil Ketua Komisi I DPR RI Dave Laksono menilai wacana Presiden Prabowo Subianto untuk menjembatani dialog antara ...</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5678535/jenama-perkakas-otomotif-tekiro-dapat-pengakuan-guinnes-world-records</t>
+          <t>https://www.antaranews.com/berita/5678521/dpr-wacana-prabowo-jembatani-dialog-korea-sesuai-politik-bebas-aktif</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-02-at-15.34.09-1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/22/IMG_20260422_175322.jpg</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Pemkab Sleman dukung kejuaraan dragbike tingkatkan ekonomi masyarakat</t>
+          <t>Kongres PSSI sepakati pemilihan pengurus mundur ke Juli 2027</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:42:42 +0700</t>
+          <t>Mon, 03 Aug 2026 23:30:00 +0700</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Pemerintah Kabupaten Sleman, Daerah Istimewa Yogyakarta, mendukung penuh penyelenggaraan Kejuaraan Dragbike Super ...</t>
+          <t>ANTARA - Kongres Biasa PSSI 2026 menyepakati perubahan jadwal Kongres Pemilihan Pengurus PSSI 2027 dari semula Mei ...</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678532/pemkab-sleman-dukung-kejuaraan-dragbike-tingkatkan-ekonomi-masyarakat</t>
+          <t>https://www.antaranews.com/video/5678395/kongres-pssi-sepakati-pemilihan-pengurus-mundur-ke-juli-2027</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000029422.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KONGRES-PSSI-SEPAKATI-PEMILIHAN-PENGURUS-MUNDUR-KE-JULI-2027.jpg</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>GMR nilai akses penerbangan langsung buka peluang ekonomi RI-India</t>
+          <t>23 calon hakim agung dan ad hoc ikuti seleksi wawancara akhir</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:41:32 +0700</t>
+          <t>Mon, 03 Aug 2026 10:15:01 +0700</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>GMR Group, perusahaan multinasional India yang bergerak di bidang infrastruktur, menilai akses penerbangan langsung ...</t>
+          <t>Sebanyak 23 orang calon hakim agung dan ad hoc Mahkamah Agung Tahun 2026 mengikuti seleksi wawancara tahap akhir di ...</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678529/gmr-nilai-akses-penerbangan-langsung-buka-peluang-ekonomi-ri-india</t>
+          <t>https://www.antaranews.com/berita/5677137/23-calon-hakim-agung-dan-ad-hoc-ikuti-seleksi-wawancara-akhir</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/DSF3021.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000012883_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>PSSI raup dana Rp722 miliar dalam laporan keuangan tahunan</t>
+          <t>BRIN perkuat kajian sungai bawah tanah di Kebumen untuk ketahanan air</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:37:46 +0700</t>
+          <t>Mon, 03 Aug 2026 09:57:19 +0700</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir menyebut organisasinya meraup dana senilai Rp722 ...</t>
+          <t>Badan Riset dan Inovasi Nasional (BRIN) memperkuat riset ketahanan air melalui pengembangan teknologi dan penelitian ...</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678528/pssi-raup-dana-rp722-miliar-dalam-laporan-keuangan-tahunan</t>
+          <t>https://www.antaranews.com/berita/5677120/brin-perkuat-kajian-sungai-bawah-tanah-di-kebumen-untuk-ketahanan-air</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0098_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1785706440-47672950-1.jpg</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Otorita kolaborasi PNM untuk pengembangan ekonomi masyarakat IKN</t>
+          <t>Harga bensin turun pada pekan pertama Agustus</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:30:50 +0700</t>
+          <t>Mon, 03 Aug 2026 09:51:00 +0700</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Otorita Ibu Kota Nusantara (IKN) melakukan kolaborasi dengan PT Permodalan Nasional Madani (Persero) untuk pengembangan ...</t>
+          <t>Harga bahan bakar minyak (BBM) jenis bensin di stasiun pengisian bahan bakar umum (SPBU) Pertamina, Shell, dan bp ...</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678525/otorita-kolaborasi-pnm-untuk-pengembangan-ekonomi-masyarakat-ikn</t>
+          <t>https://www.antaranews.com/berita/5677109/harga-bensin-turun-pada-pekan-pertama-agustus</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0012_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/10/02/penuruanan-harga-bbm-011024-aaa-7.jpg</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>DPR: Wacana Prabowo jembatani dialog Korea sesuai politik bebas aktif</t>
+          <t>Menteri PKP tegaskan KUR Perumahan perkuat ekonomi keluarga</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:30:13 +0700</t>
+          <t>Mon, 03 Aug 2026 22:47:11 +0700</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Wakil Ketua Komisi I DPR RI Dave Laksono menilai wacana Presiden Prabowo Subianto untuk menjembatani dialog antara ...</t>
+          <t>Menteri Perumahan dan Kawasan Permukiman (PKP) Maruarar Sirait menegaskan bahwa Kredit Usaha Rakyat (KUR) Perumahan ...</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678521/dpr-wacana-prabowo-jembatani-dialog-korea-sesuai-politik-bebas-aktif</t>
+          <t>https://www.antaranews.com/berita/5678465/menteri-pkp-tegaskan-kur-perumahan-perkuat-ekonomi-keluarga</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/22/IMG_20260422_175322.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1321013.jpg</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Kongres PSSI sepakati pemilihan pengurus mundur ke Juli 2027</t>
+          <t>Ekonom: Inflasi mereda, semester II jadi momentum jaga keseimbangan</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 23:30:00 +0700</t>
+          <t>Mon, 03 Aug 2026 22:34:25 +0700</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
-          <t>ANTARA - Kongres Biasa PSSI 2026 menyepakati perubahan jadwal Kongres Pemilihan Pengurus PSSI 2027 dari semula Mei ...</t>
+          <t>Kepala Ekonom Trimegah Sekuritas Indonesia Fakhrul Fulvian menilai semester II-2026 menjadi momentum untuk menjaga ...</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678395/kongres-pssi-sepakati-pemilihan-pengurus-mundur-ke-juli-2027</t>
+          <t>https://www.antaranews.com/berita/5678439/ekonom-inflasi-mereda-semester-ii-jadi-momentum-jaga-keseimbangan</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KONGRES-PSSI-SEPAKATI-PEMILIHAN-PENGURUS-MUNDUR-KE-JULI-2027.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/01/21/IMG_2637.jpeg</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Prabowo terima tanda kehormatan dari Angkatan Bersenjata Thailand</t>
+          <t>Pemkab Aceh Tenggara batasi pembelian BBM untuk cegah penimbunan</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 20:59:35 +0700</t>
+          <t>Mon, 03 Aug 2026 22:25:13 +0700</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Presiden Prabowo Subianto menerima tanda kehormatan dari Angkatan Bersenjata Kerajaan Thailand yang diberikan pada saat ...</t>
+          <t>Pemerintah Kabupaten Aceh Tenggara bersama Forkopimda setempat saat ini telah melakukan pembatasan pembelian bahan ...</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678283/prabowo-terima-tanda-kehormatan-dari-angkatan-bersenjata-thailand</t>
+          <t>https://www.antaranews.com/berita/5678431/pemkab-aceh-tenggara-batasi-pembelian-bbm-untuk-cegah-penimbunan</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/tempImageNOyDfK.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/20260803-Bupati-Aceh-Tenggara-HM-Salim-Fakhry.jpeg</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
+          <t>MTI dorong kemudahan transaksi nirsentuh di MRT Jakarta</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 20:50:37 +0700</t>
+          <t>Mon, 03 Aug 2026 22:24:07 +0700</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr">
         <is>
-          <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan ...</t>
+          <t>PT Mitra Transaksi Indonesia (MTI) atau YOKKE mendukung penerapan sistem pembayaran kartu nirsentuh berbasis Europay, ...</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
+          <t>https://www.antaranews.com/berita/5678427/mti-dorong-kemudahan-transaksi-nirsentuh-di-mrt-jakarta</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-18.59.08.jpeg</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>ekonomi-finansial, top-news</t>
+          <t>ekonomi-bisnis, top-news</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Menkeu: Eskalasi konflik Timteng dorong imbal hasil SBN ke 7,14 persen</t>
+          <t>Otorita kolaborasi PNM untuk pengembangan ekonomi masyarakat IKN</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 20:48:02 +0700</t>
+          <t>Mon, 03 Aug 2026 23:30:50 +0700</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa mengatakan eskalasi konflik di Timur Tengah mendorong kenaikan imbal hasil Surat ...</t>
+          <t>Otorita Ibu Kota Nusantara (IKN) melakukan kolaborasi dengan PT Permodalan Nasional Madani (Persero) untuk pengembangan ...</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678253/menkeu-eskalasi-konflik-timteng-dorong-imbal-hasil-sbn-ke-714-persen</t>
+          <t>https://www.antaranews.com/berita/5678525/otorita-kolaborasi-pnm-untuk-pengembangan-ekonomi-masyarakat-ikn</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/konpers-hasil-rapat-berkala-kssk-iii-tahun-2026-2833267.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0012_1.jpg</t>
         </is>
       </c>
     </row>
@@ -11984,94 +11984,94 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Prabowo dukung peningkatan latihan bersama militer RI-Thailand</t>
+          <t>Prabowo terima tanda kehormatan dari Angkatan Bersenjata Thailand</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:21:32 +0700</t>
+          <t>Mon, 03 Aug 2026 20:59:35 +0700</t>
         </is>
       </c>
       <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Presiden Prabowo Subianto mendukung peningkatan frekuensi latihan bersama antara Tentara Nasional Indonesia (TNI) dan ...</t>
+          <t>Presiden Prabowo Subianto menerima tanda kehormatan dari Angkatan Bersenjata Kerajaan Thailand yang diberikan pada saat ...</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678081/prabowo-dukung-peningkatan-latihan-bersama-militer-ri-thailand</t>
+          <t>https://www.antaranews.com/berita/5678283/prabowo-terima-tanda-kehormatan-dari-angkatan-bersenjata-thailand</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Pertemuan-bilateral-antara-Indonesia-Thailand-di-Istana-Merdeka-03082026-gp-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/tempImageNOyDfK.jpg</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>ekonomi-finansial, top-news</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>OJK: Kredit perbankan tumbuh 12,67 persen capai Rp9.080,9 triliun</t>
+          <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:12:24 +0700</t>
+          <t>Mon, 03 Aug 2026 20:50:37 +0700</t>
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Otoritas Jasa Keuangan (OJK) melaporkan penyaluran kredit perbankan di tanah air tumbuh 12,67 persen year on year ...</t>
+          <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan ...</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678057/ojk-kredit-perbankan-tumbuh-1267-persen-capai-rp90809-triliun</t>
+          <t>https://www.antaranews.com/video/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Konpers-hasil-rapat-berkala-KSSK-III-tahun-2026-382026-pma-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-finansial, top-news</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Menkomdigi: KIP garda depan informasi jernih dan perangi hoaks</t>
+          <t>Menkeu: Eskalasi konflik Timteng dorong imbal hasil SBN ke 7,14 persen</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 19:00:50 +0700</t>
+          <t>Mon, 03 Aug 2026 20:48:02 +0700</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid mengatakan Komisi Informasi Pusat (KIP) menjadi garda terdepan ...</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa mengatakan eskalasi konflik di Timur Tengah mendorong kenaikan imbal hasil Surat ...</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678033/menkomdigi-kip-garda-depan-informasi-jernih-dan-perangi-hoaks</t>
+          <t>https://www.antaranews.com/berita/5678253/menkeu-eskalasi-konflik-timteng-dorong-imbal-hasil-sbn-ke-714-persen</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0321.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/konpers-hasil-rapat-berkala-kssk-iii-tahun-2026-2833267.jpg</t>
         </is>
       </c>
     </row>
@@ -12083,61 +12083,61 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Satu tahun Sekolah Rakyat, ratusan siswa torehkan prestasi</t>
+          <t>Prabowo dukung peningkatan latihan bersama militer RI-Thailand</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:59:25 +0700</t>
+          <t>Mon, 03 Aug 2026 19:21:32 +0700</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Menteri Sosial (Mensos) Saifullah Yusuf menyatakan selama satu tahun Sekolah Rakyat berdiri sudah ratusan ...</t>
+          <t>Presiden Prabowo Subianto mendukung peningkatan frekuensi latihan bersama antara Tentara Nasional Indonesia (TNI) dan ...</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678024/satu-tahun-sekolah-rakyat-ratusan-siswa-torehkan-prestasi</t>
+          <t>https://www.antaranews.com/berita/5678081/prabowo-dukung-peningkatan-latihan-bersama-militer-ri-thailand</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000176441.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Pertemuan-bilateral-antara-Indonesia-Thailand-di-Istana-Merdeka-03082026-gp-3.jpg</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-finansial, top-news</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Menkeu: Realisasi anggaran MBG Rp101,1 T untuk 63,13 juta penerima</t>
+          <t>OJK: Kredit perbankan tumbuh 12,67 persen capai Rp9.080,9 triliun</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:53:14 +0700</t>
+          <t>Mon, 03 Aug 2026 19:12:24 +0700</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa mengungkapkan bahwa realisasi anggaran Program Makan Bergizi Gratis ...</t>
+          <t>Otoritas Jasa Keuangan (OJK) melaporkan penyaluran kredit perbankan di tanah air tumbuh 12,67 persen year on year ...</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678005/menkeu-realisasi-anggaran-mbg-rp1011-t-untuk-6313-juta-penerima</t>
+          <t>https://www.antaranews.com/berita/5678057/ojk-kredit-perbankan-tumbuh-1267-persen-capai-rp90809-triliun</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Konpers-hasil-rapat-berkala-KSSK-III-tahun-2026-382026-pma-8.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Konpers-hasil-rapat-berkala-KSSK-III-tahun-2026-382026-pma-1.jpg</t>
         </is>
       </c>
     </row>
@@ -12149,28 +12149,28 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Polri perkuat langkah preventif respons isu keamanan nasional</t>
+          <t>Menkomdigi: KIP garda depan informasi jernih dan perangi hoaks</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 18:46:34 +0700</t>
+          <t>Mon, 03 Aug 2026 19:00:50 +0700</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Polri memastikan terus memperkuat langkah preventif untuk menjaga keamanan nasional sehingga aktivitas masyarakat dan ...</t>
+          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid mengatakan Komisi Informasi Pusat (KIP) menjadi garda terdepan ...</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677985/polri-perkuat-langkah-preventif-respons-isu-keamanan-nasional</t>
+          <t>https://www.antaranews.com/berita/5678033/menkomdigi-kip-garda-depan-informasi-jernih-dan-perangi-hoaks</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000086556.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0321.jpg</t>
         </is>
       </c>
     </row>
@@ -12182,28 +12182,28 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Prabowo dan PM Thailand bertemu empat mata di Istana Merdeka</t>
+          <t>Satu tahun Sekolah Rakyat, ratusan siswa torehkan prestasi</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 17:49:52 +0700</t>
+          <t>Mon, 03 Aug 2026 18:59:25 +0700</t>
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Presiden Prabowo Subianto dan Perdana Menteri Thailand Anutin Charnvirakul menggelar pertemuan empat mata di Istana ...</t>
+          <t>Menteri Sosial (Mensos) Saifullah Yusuf menyatakan selama satu tahun Sekolah Rakyat berdiri sudah ratusan ...</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677828/prabowo-dan-pm-thailand-bertemu-empat-mata-di-istana-merdeka</t>
+          <t>https://www.antaranews.com/berita/5678024/satu-tahun-sekolah-rakyat-ratusan-siswa-torehkan-prestasi</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/presiden-prabowo-terima-PM-Thailand-030226-gp-4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000176441.jpg</t>
         </is>
       </c>
     </row>
@@ -12215,161 +12215,161 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Kepala BGN tingkatkan status keracunan MBG jadi kejadian fatal</t>
+          <t>Menkeu: Realisasi anggaran MBG Rp101,1 T untuk 63,13 juta penerima</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 17:10:19 +0700</t>
+          <t>Mon, 03 Aug 2026 18:53:14 +0700</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
+          <t>Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa mengungkapkan bahwa realisasi anggaran Program Makan Bergizi Gratis ...</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678005/menkeu-realisasi-anggaran-mbg-rp1011-t-untuk-6313-juta-penerima</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Konpers-hasil-rapat-berkala-KSSK-III-tahun-2026-382026-pma-8.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Polri perkuat langkah preventif respons isu keamanan nasional</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:46:34 +0700</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr"/>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Polri memastikan terus memperkuat langkah preventif untuk menjaga keamanan nasional sehingga aktivitas masyarakat dan ...</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677985/polri-perkuat-langkah-preventif-respons-isu-keamanan-nasional</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000086556.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Prabowo dan PM Thailand bertemu empat mata di Istana Merdeka</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 17:49:52 +0700</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto dan Perdana Menteri Thailand Anutin Charnvirakul menggelar pertemuan empat mata di Istana ...</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677828/prabowo-dan-pm-thailand-bertemu-empat-mata-di-istana-merdeka</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/presiden-prabowo-terima-PM-Thailand-030226-gp-4.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Kepala BGN tingkatkan status keracunan MBG jadi kejadian fatal</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 17:10:19 +0700</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr"/>
+      <c r="E360" t="inlineStr">
+        <is>
           <t>nya tidak dilanjutkan," ucap Sudaryono.
 Ia menegaskan BGN memberlakukan nol toleransi pada setiap status ...</t>
         </is>
       </c>
-      <c r="F357" t="inlineStr">
+      <c r="F360" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677743/kepala-bgn-tingkatkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
         </is>
       </c>
-      <c r="G357" t="inlineStr">
+      <c r="G360" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/ZAM02548_edit_2028523819372755.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>top-news</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>Harga minyak turun usai AS siap lanjutkan dialog dengan Iran</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 17:08:35 +0700</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr"/>
-      <c r="E358" t="inlineStr">
-        <is>
-          <t>Harga minyak turun lebih dari 5 persen, Senin, setelah Presiden Amerika Serikat Donald Trump ...</t>
-        </is>
-      </c>
-      <c r="F358" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677735/harga-minyak-turun-usai-as-siap-lanjutkan-dialog-dengan-iran</t>
-        </is>
-      </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/ilustrasi-isi-bensin-di-pom.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>top-news</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>Australia konfirmasi kematian massal pertama satwa akibat flu burung</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:48:50 +0700</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr"/>
-      <c r="E359" t="inlineStr">
-        <is>
-          <t>Australia mengonfirmasi kematian massal satwa liar pertama terkait flu burung H5 yang mematikan, dengan burung camar ...</t>
-        </is>
-      </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677701/australia-konfirmasi-kematian-massal-pertama-satwa-akibat-flu-burung</t>
-        </is>
-      </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/26/Virus-flu-burung-penyakit-unggas.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>top-news</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>Siklon 94 W,  waspada cuaca ekstrem &amp; gelombang tinggi di wilayah RI</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 16:30:38 +0700</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr"/>
-      <c r="E360" t="inlineStr">
-        <is>
-          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) mendeteksi pergerakan Bibit Siklon Tropis 94W di Laut Filipina ...</t>
-        </is>
-      </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677641/siklon-94-w-waspada-cuaca-ekstrem-gelombang-tinggi-di-wilayah-ri</t>
-        </is>
-      </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Peringatan-zona-merah-gelombang-tinggi-di-perairan-ntb-220125-AS-5.jpg</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>photo, top-news</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Petani berbagi air sumur demi selamatkan tanaman tembakau</t>
+          <t>Harga minyak turun usai AS siap lanjutkan dialog dengan Iran</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:44:51 +0700</t>
+          <t>Mon, 03 Aug 2026 17:08:35 +0700</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Petani mengambil air dari sumur untuk menyiram tanaman tembakau di Lengkong, Nganjuk, Jawa Timur, Senin (3/8/2026). ...</t>
+          <t>Harga minyak turun lebih dari 5 persen, Senin, setelah Presiden Amerika Serikat Donald Trump ...</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5677428/petani-berbagi-air-sumur-demi-selamatkan-tanaman-tembakau</t>
+          <t>https://www.antaranews.com/berita/5677735/harga-minyak-turun-usai-as-siap-lanjutkan-dialog-dengan-iran</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/petani-tembakau-berbagi-air-sumur-antisipasi-dampak-el-nino-030826-mm-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/ilustrasi-isi-bensin-di-pom.jpg</t>
         </is>
       </c>
     </row>
@@ -12381,28 +12381,28 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Nusron sebut banyak laut di Batam telah dikapling tanpa prosedur sah</t>
+          <t>Australia konfirmasi kematian massal pertama satwa akibat flu burung</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:44:05 +0700</t>
+          <t>Mon, 03 Aug 2026 16:48:50 +0700</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Menteri Agraria dan Tata Ruang (ATR)/Kepala Badan Pertanahan Nasional (BPN) Nusron Wahid mengatakan, menerima banyak ...</t>
+          <t>Australia mengonfirmasi kematian massal satwa liar pertama terkait flu burung H5 yang mematikan, dengan burung camar ...</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677425/nusron-sebut-banyak-laut-di-batam-telah-dikapling-tanpa-prosedur-sah</t>
+          <t>https://www.antaranews.com/berita/5677701/australia-konfirmasi-kematian-massal-pertama-satwa-akibat-flu-burung</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_142345.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/26/Virus-flu-burung-penyakit-unggas.jpg</t>
         </is>
       </c>
     </row>
@@ -12414,61 +12414,61 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Menkomdigi panggil YouTube imbas temuan konten promosi vape sasar anak</t>
+          <t>Siklon 94 W,  waspada cuaca ekstrem &amp; gelombang tinggi di wilayah RI</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 14:22:09 +0700</t>
+          <t>Mon, 03 Aug 2026 16:30:38 +0700</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid merencanakan pemanggilan terhadap platform digital YouTube ...</t>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) mendeteksi pergerakan Bibit Siklon Tropis 94W di Laut Filipina ...</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677396/menkomdigi-panggil-youtube-imbas-temuan-konten-promosi-vape-sasar-anak</t>
+          <t>https://www.antaranews.com/berita/5677641/siklon-94-w-waspada-cuaca-ekstrem-gelombang-tinggi-di-wilayah-ri</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0225.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Peringatan-zona-merah-gelombang-tinggi-di-perairan-ntb-220125-AS-5.jpg</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>photo, top-news</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Kemnaker: Magang Nasional diharapkan menekan angka pengangguran muda</t>
+          <t>Petani berbagi air sumur demi selamatkan tanaman tembakau</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:37:57 +0700</t>
+          <t>Mon, 03 Aug 2026 14:44:51 +0700</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Kementerian Ketenagakerjaan (Kemnaker) mengatakan program Magang Nasional (MagangHub) untuk mempersiapkan kompetensi ...</t>
+          <t>Petani mengambil air dari sumur untuk menyiram tanaman tembakau di Lengkong, Nganjuk, Jawa Timur, Senin (3/8/2026). ...</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677364/kemnaker-magang-nasional-diharapkan-menekan-angka-pengangguran-muda</t>
+          <t>https://www.antaranews.com/foto/5677428/petani-berbagi-air-sumur-demi-selamatkan-tanaman-tembakau</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/ff63afaf-7778-47fe-833d-5a8068af9a51_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/petani-tembakau-berbagi-air-sumur-antisipasi-dampak-el-nino-030826-mm-1.jpg</t>
         </is>
       </c>
     </row>
@@ -12480,28 +12480,28 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Kemenag perkuat transformasi madrasah lewat revitalisasi-digitalisasi</t>
+          <t>Nusron sebut banyak laut di Batam telah dikapling tanpa prosedur sah</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:36:36 +0700</t>
+          <t>Mon, 03 Aug 2026 14:44:05 +0700</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Menteri Agama (Menag) Nasaruddin Umar menegaskan transformasi madrasah terus diperkuat melalui revitalisasi ...</t>
+          <t>Menteri Agraria dan Tata Ruang (ATR)/Kepala Badan Pertanahan Nasional (BPN) Nusron Wahid mengatakan, menerima banyak ...</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677363/kemenag-perkuat-transformasi-madrasah-lewat-revitalisasi-digitalisasi</t>
+          <t>https://www.antaranews.com/berita/5677425/nusron-sebut-banyak-laut-di-batam-telah-dikapling-tanpa-prosedur-sah</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/14/1000173935_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_20260803_142345.jpg</t>
         </is>
       </c>
     </row>
@@ -12513,28 +12513,28 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Lisensi IP Global Buka Peluang Bisnis Baru bagi Kreator Indonesia</t>
+          <t>Menkomdigi panggil YouTube imbas temuan konten promosi vape sasar anak</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:34:30 +0700</t>
+          <t>Mon, 03 Aug 2026 14:22:09 +0700</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Wakil Menteri Ekonomi Kreatif Irene Umar mengatakan kolaborasi antara pemilik kekayaan intelektual (Intellectual ...</t>
+          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid merencanakan pemanggilan terhadap platform digital YouTube ...</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677353/lisensi-ip-global-buka-peluang-bisnis-baru-bagi-kreator-indonesia</t>
+          <t>https://www.antaranews.com/berita/5677396/menkomdigi-panggil-youtube-imbas-temuan-konten-promosi-vape-sasar-anak</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000589873.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG-20260803-WA0225.jpg</t>
         </is>
       </c>
     </row>
@@ -12546,28 +12546,28 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Nilai ekspor perdagangan RI Januari-Juni capai 140,81 miliar dolar AS</t>
+          <t>Kemnaker: Magang Nasional diharapkan menekan angka pengangguran muda</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:16:17 +0700</t>
+          <t>Mon, 03 Aug 2026 13:37:57 +0700</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) mencatat nilai ekspor Indonesia secara kumulatif dari Januari-Juni 2026 mencapai 140,81 ...</t>
+          <t>Kementerian Ketenagakerjaan (Kemnaker) mengatakan program Magang Nasional (MagangHub) untuk mempersiapkan kompetensi ...</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677315/nilai-ekspor-perdagangan-ri-januari-juni-capai-14081-miliar-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5677364/kemnaker-magang-nasional-diharapkan-menekan-angka-pengangguran-muda</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/neraca-perdagangan-januari-mei-2026-surplus-2815779.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/23/ff63afaf-7778-47fe-833d-5a8068af9a51_1.jpeg</t>
         </is>
       </c>
     </row>
@@ -12579,28 +12579,28 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Korban KMP Mutiara Sentosa II dievakuasi ke Pelabuhan Tanjung Perak</t>
+          <t>Kemenag perkuat transformasi madrasah lewat revitalisasi-digitalisasi</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 13:06:15 +0700</t>
+          <t>Mon, 03 Aug 2026 13:36:36 +0700</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Tim SAR gabungan terus melakukan evakuasi korban terbakarnya KMP Mutiara Sentosa 2 ke darat, tepatnya ke Pelabuhan ...</t>
+          <t>Menteri Agama (Menag) Nasaruddin Umar menegaskan transformasi madrasah terus diperkuat melalui revitalisasi ...</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677297/korban-kmp-mutiara-sentosa-ii-dievakuasi-ke-pelabuhan-tanjung-perak</t>
+          <t>https://www.antaranews.com/berita/5677363/kemenag-perkuat-transformasi-madrasah-lewat-revitalisasi-digitalisasi</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/260821_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/14/1000173935_1.jpg</t>
         </is>
       </c>
     </row>
@@ -12612,28 +12612,28 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Aktor senior Diding Boneng meninggal dunia</t>
+          <t>Lisensi IP Global Buka Peluang Bisnis Baru bagi Kreator Indonesia</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:39:03 +0700</t>
+          <t>Mon, 03 Aug 2026 13:34:30 +0700</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Aktor sekaligus komedian tanah air, Zainal Abidin alias Diding Boneng dikabarkan meninggal dunia pada Senin (3/8) dalam ...</t>
+          <t>Wakil Menteri Ekonomi Kreatif Irene Umar mengatakan kolaborasi antara pemilik kekayaan intelektual (Intellectual ...</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677209/aktor-senior-diding-boneng-meninggal-dunia</t>
+          <t>https://www.antaranews.com/berita/5677353/lisensi-ip-global-buka-peluang-bisnis-baru-bagi-kreator-indonesia</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/26f1eb88-3301-4ae1-badd-bed5078fe3dd.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000589873.jpg</t>
         </is>
       </c>
     </row>
@@ -12645,28 +12645,28 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Seskab: Prabowo dorong sinergi pemerintah dan dunia usaha</t>
+          <t>Nilai ekspor perdagangan RI Januari-Juni capai 140,81 miliar dolar AS</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 11:17:50 +0700</t>
+          <t>Mon, 03 Aug 2026 13:16:17 +0700</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Sekretaris Kabinet Teddy Indra Wijaya menyampaikan bahwa Presiden Prabowo Subianto menekankan pentingnya sinergi antara ...</t>
+          <t>Badan Pusat Statistik (BPS) mencatat nilai ekspor Indonesia secara kumulatif dari Januari-Juni 2026 mencapai 140,81 ...</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677191/seskab-prabowo-dorong-sinergi-pemerintah-dan-dunia-usaha</t>
+          <t>https://www.antaranews.com/berita/5677315/nilai-ekspor-perdagangan-ri-januari-juni-capai-14081-miliar-dolar-as</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_0891_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/neraca-perdagangan-januari-mei-2026-surplus-2815779.jpg</t>
         </is>
       </c>
     </row>
@@ -12678,28 +12678,28 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Red Velvet bersiap kembali lewat EP baru "Velvet Summer"</t>
+          <t>Korban KMP Mutiara Sentosa II dievakuasi ke Pelabuhan Tanjung Perak</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:24:37 +0700</t>
+          <t>Mon, 03 Aug 2026 13:06:15 +0700</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Grup idola K-pop Red Velvet akan kembali lewat rilis mini album atau extended play (EP) baru bertajuk “Velvet ...</t>
+          <t>Tim SAR gabungan terus melakukan evakuasi korban terbakarnya KMP Mutiara Sentosa 2 ke darat, tepatnya ke Pelabuhan ...</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677151/red-velvet-bersiap-kembali-lewat-ep-baru-velvet-summer</t>
+          <t>https://www.antaranews.com/berita/5677297/korban-kmp-mutiara-sentosa-ii-dievakuasi-ke-pelabuhan-tanjung-perak</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/ca97a3a8-aa17-45fc-be71-d36051dd9dcd.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/260821_1.jpg</t>
         </is>
       </c>
     </row>
@@ -12711,28 +12711,28 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Menaker pastikan komitmen pemerintah perkuat kesejahteraan pekerja</t>
+          <t>Aktor senior Diding Boneng meninggal dunia</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:16:19 +0700</t>
+          <t>Mon, 03 Aug 2026 11:39:03 +0700</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Menteri Ketenagakerjaan (Menaker) Yassierli memastikan pemerintah berkomitmen untuk memperkuat kesejahteraan, ...</t>
+          <t>Aktor sekaligus komedian tanah air, Zainal Abidin alias Diding Boneng dikabarkan meninggal dunia pada Senin (3/8) dalam ...</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677148/menaker-pastikan-komitmen-pemerintah-perkuat-kesejahteraan-pekerja</t>
+          <t>https://www.antaranews.com/berita/5677209/aktor-senior-diding-boneng-meninggal-dunia</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/09/20/pelepasan-peserta-pemagangan-ke-jepang-di-jawa-barat-2627513.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/26f1eb88-3301-4ae1-badd-bed5078fe3dd.jpeg</t>
         </is>
       </c>
     </row>
@@ -12744,28 +12744,28 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>23 calon hakim agung dan ad hoc ikuti seleksi wawancara akhir</t>
+          <t>Seskab: Prabowo dorong sinergi pemerintah dan dunia usaha</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 10:15:01 +0700</t>
+          <t>Mon, 03 Aug 2026 11:17:50 +0700</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Sebanyak 23 orang calon hakim agung dan ad hoc Mahkamah Agung 